--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>565270</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>8.57999992370605</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>7.81500005722046</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>8.42500019073486</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>7.94500017166138</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>190805</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>8.05500030517578</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>7.83500003814697</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>7.93499994277954</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>7.94500017166138</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>223637</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>8.24499988555908</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>8.17500019073486</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>241992</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>8.35999965667725</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>8.17000007629395</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>8.22999954223633</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>8.28999996185303</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>190468</v>
+        <v>236075</v>
       </c>
       <c r="C2715" t="n">
-        <v>7.61999988555908</v>
+        <v>7.96000003814697</v>
       </c>
       <c r="D2715" t="n">
-        <v>7.36499977111816</v>
+        <v>7.40500020980835</v>
       </c>
       <c r="E2715" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="F2715" t="n">
         <v>7.46500015258789</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>7.6100001335144</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>160845</v>
+        <v>190468</v>
       </c>
       <c r="C2716" t="n">
-        <v>7.65999984741211</v>
+        <v>7.61999988555908</v>
       </c>
       <c r="D2716" t="n">
-        <v>7.44999980926514</v>
+        <v>7.36499977111816</v>
       </c>
       <c r="E2716" t="n">
-        <v>7.65000009536743</v>
+        <v>7.46500015258789</v>
       </c>
       <c r="F2716" t="n">
-        <v>7.44999980926514</v>
+        <v>7.6100001335144</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>1074051</v>
+        <v>160845</v>
       </c>
       <c r="C2717" t="n">
-        <v>8.0600004196167</v>
+        <v>7.65999984741211</v>
       </c>
       <c r="D2717" t="n">
-        <v>7.42999982833862</v>
+        <v>7.44999980926514</v>
       </c>
       <c r="E2717" t="n">
-        <v>7.69000005722046</v>
+        <v>7.65000009536743</v>
       </c>
       <c r="F2717" t="n">
-        <v>7.69500017166138</v>
+        <v>7.44999980926514</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>1750460</v>
+        <v>1074051</v>
       </c>
       <c r="C2718" t="n">
-        <v>8.53499984741211</v>
+        <v>8.0600004196167</v>
       </c>
       <c r="D2718" t="n">
-        <v>7.80000019073486</v>
+        <v>7.42999982833862</v>
       </c>
       <c r="E2718" t="n">
-        <v>7.80000019073486</v>
+        <v>7.69000005722046</v>
       </c>
       <c r="F2718" t="n">
-        <v>8.53499984741211</v>
+        <v>7.69500017166138</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>565270</v>
+        <v>1750460</v>
       </c>
       <c r="C2719" t="n">
-        <v>8.57999992370605</v>
+        <v>8.53499984741211</v>
       </c>
       <c r="D2719" t="n">
-        <v>7.81500005722046</v>
+        <v>7.80000019073486</v>
       </c>
       <c r="E2719" t="n">
-        <v>8.42500019073486</v>
+        <v>7.80000019073486</v>
       </c>
       <c r="F2719" t="n">
-        <v>7.94500017166138</v>
+        <v>8.53499984741211</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,19 +62911,19 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>190805</v>
+        <v>565270</v>
       </c>
       <c r="C2720" t="n">
-        <v>8.05500030517578</v>
+        <v>8.57999992370605</v>
       </c>
       <c r="D2720" t="n">
-        <v>7.83500003814697</v>
+        <v>7.81500005722046</v>
       </c>
       <c r="E2720" t="n">
-        <v>7.93499994277954</v>
+        <v>8.42500019073486</v>
       </c>
       <c r="F2720" t="n">
         <v>7.94500017166138</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>223637</v>
+        <v>190805</v>
       </c>
       <c r="C2721" t="n">
-        <v>8.24499988555908</v>
+        <v>8.05500030517578</v>
       </c>
       <c r="D2721" t="n">
-        <v>7.92000007629395</v>
+        <v>7.83500003814697</v>
       </c>
       <c r="E2721" t="n">
-        <v>7.92000007629395</v>
+        <v>7.93499994277954</v>
       </c>
       <c r="F2721" t="n">
-        <v>8.17500019073486</v>
+        <v>7.94500017166138</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>241992</v>
+        <v>223637</v>
       </c>
       <c r="C2722" t="n">
+        <v>8.24499988555908</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>8.17500019073486</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>130016</v>
+      </c>
+      <c r="C2723" t="n">
         <v>8.35999965667725</v>
       </c>
-      <c r="D2722" t="n">
-        <v>8.17000007629395</v>
-      </c>
-      <c r="E2722" t="n">
-        <v>8.22999954223633</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>8.28999996185303</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="D2723" t="n">
+        <v>7.94500017166138</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>8.35999965667725</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -577,7 +577,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>5.29453277587891</v>
+        <v>5.29453325271606</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>4.94245004653931</v>
+        <v>4.94244956970215</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>4.74980115890503</v>
+        <v>4.74980068206787</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>4.58372402191162</v>
+        <v>4.58372354507446</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>4.74980115890503</v>
+        <v>4.74980068206787</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>4.82951784133911</v>
+        <v>4.82951831817627</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>4.82951784133911</v>
+        <v>4.82951831817627</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>4.88598442077637</v>
+        <v>4.88598394393921</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>4.96902179718018</v>
+        <v>4.96902227401733</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>4.97234344482422</v>
+        <v>4.97234439849854</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>4.88598442077637</v>
+        <v>4.88598394393921</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>4.94909286499023</v>
+        <v>4.94909238815308</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>4.93248462677002</v>
+        <v>4.93248558044434</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.59368801116943</v>
+        <v>4.59368848800659</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>4.4575047492981</v>
+        <v>4.45750522613525</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>4.61029624938965</v>
+        <v>4.61029577255249</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.75</v>
       </c>
       <c r="G30" t="n">
-        <v>4.48407697677612</v>
+        <v>4.48407745361328</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>4.62690353393555</v>
+        <v>4.62690401077271</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.67340517044067</v>
+        <v>4.67340469360352</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G36" t="n">
-        <v>5.02880954742432</v>
+        <v>5.02881002426147</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.75</v>
       </c>
       <c r="G39" t="n">
-        <v>5.14838552474976</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>5.51375532150269</v>
+        <v>5.51375484466553</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G43" t="n">
-        <v>5.69311666488647</v>
+        <v>5.69311714172363</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>5.75290584564209</v>
+        <v>5.75290536880493</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>5.53368330001831</v>
+        <v>5.53368377685547</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G47" t="n">
-        <v>5.68315362930298</v>
+        <v>5.68315267562866</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>5.14174175262451</v>
+        <v>5.14174222946167</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.75</v>
       </c>
       <c r="G64" t="n">
-        <v>5.14838552474976</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.26796054840088</v>
+        <v>5.26796007156372</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.5</v>
       </c>
       <c r="G66" t="n">
-        <v>4.98230743408203</v>
+        <v>4.98230791091919</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>4.96902179718018</v>
+        <v>4.96902227401733</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.75</v>
       </c>
       <c r="G70" t="n">
-        <v>5.14838552474976</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>5.08859729766846</v>
+        <v>5.08859777450562</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G74" t="n">
-        <v>5.04209613800049</v>
+        <v>5.04209661483765</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G75" t="n">
-        <v>5.0354528427124</v>
+        <v>5.03545331954956</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>5.08195495605469</v>
+        <v>5.08195447921753</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.11516952514648</v>
+        <v>5.1151704788208</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>5.06202507019043</v>
+        <v>5.06202554702759</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.20153045654297</v>
+        <v>5.20152997970581</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>5.11184883117676</v>
+        <v>5.1118483543396</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>5.06202507019043</v>
+        <v>5.06202554702759</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.08195495605469</v>
+        <v>5.08195447921753</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.0719895362854</v>
+        <v>5.07199001312256</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G89" t="n">
-        <v>5.33439159393311</v>
+        <v>5.33439111709595</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G90" t="n">
-        <v>5.74733304977417</v>
+        <v>5.74733257293701</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G91" t="n">
-        <v>5.53747797012329</v>
+        <v>5.53747749328613</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G92" t="n">
-        <v>5.54763174057007</v>
+        <v>5.54763221740723</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G93" t="n">
-        <v>5.42916584014893</v>
+        <v>5.42916536331177</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.5</v>
       </c>
       <c r="G95" t="n">
-        <v>5.07714939117432</v>
+        <v>5.07714891433716</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G97" t="n">
-        <v>4.66420793533325</v>
+        <v>4.66420745849609</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>4.58297300338745</v>
+        <v>4.58297348022461</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>4.43404388427734</v>
+        <v>4.4340443611145</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.5</v>
       </c>
       <c r="G103" t="n">
-        <v>4.40019559860229</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.44758319854736</v>
+        <v>4.44758272171021</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G106" t="n">
-        <v>4.49496936798096</v>
+        <v>4.49496984481812</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>4.2986536026001</v>
+        <v>4.29865312576294</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>4.3291163444519</v>
+        <v>4.32911586761475</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.25</v>
       </c>
       <c r="G110" t="n">
-        <v>4.23095750808716</v>
+        <v>4.23095798492432</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G112" t="n">
-        <v>4.15649271011353</v>
+        <v>4.15649318695068</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>4.048180103302</v>
+        <v>4.04818058013916</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G118" t="n">
-        <v>3.7977077960968</v>
+        <v>3.79770803451538</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.93648290634155</v>
+        <v>3.93648338317871</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94663786888123</v>
+        <v>3.94663739204407</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32925653457642</v>
+        <v>3.32925605773926</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>3.47615528106689</v>
+        <v>3.47615456581116</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G128" t="n">
-        <v>3.48969388008118</v>
+        <v>3.4896936416626</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G129" t="n">
-        <v>3.48969388008118</v>
+        <v>3.4896936416626</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>3.15731048583984</v>
+        <v>3.15731000900269</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22906732559204</v>
+        <v>3.22906684875488</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G134" t="n">
-        <v>3.29540848731995</v>
+        <v>3.29540824890137</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G135" t="n">
-        <v>3.3251941204071</v>
+        <v>3.32519459724426</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.58785223960876</v>
+        <v>3.58785176277161</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G137" t="n">
-        <v>3.47615528106689</v>
+        <v>3.47615456581116</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49984765052795</v>
+        <v>3.49984860420227</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.48630952835083</v>
+        <v>3.48630928993225</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G141" t="n">
-        <v>3.51677227020264</v>
+        <v>3.51677203178406</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>3.60477590560913</v>
+        <v>3.60477614402771</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G145" t="n">
-        <v>3.63185381889343</v>
+        <v>3.63185405731201</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.61154532432556</v>
+        <v>3.61154556274414</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.79093790054321</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>3.70293378829956</v>
+        <v>3.7029345035553</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G150" t="n">
-        <v>3.71308851242065</v>
+        <v>3.71308875083923</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>3.5201563835144</v>
+        <v>3.52015709877014</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G152" t="n">
-        <v>3.56077480316162</v>
+        <v>3.5607738494873</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>3.6149308681488</v>
+        <v>3.61493062973022</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.6792414188385</v>
+        <v>3.67924118041992</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G155" t="n">
-        <v>3.64877724647522</v>
+        <v>3.64877772331238</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>3.79093790054321</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>3.79093790054321</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>3.8383252620697</v>
+        <v>3.83832550048828</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G161" t="n">
-        <v>3.7841694355011</v>
+        <v>3.78416872024536</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G162" t="n">
-        <v>3.81124687194824</v>
+        <v>3.81124711036682</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G163" t="n">
-        <v>3.81124687194824</v>
+        <v>3.81124711036682</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>3.7570903301239</v>
+        <v>3.75709009170532</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>3.7570903301239</v>
+        <v>3.75709009170532</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>3.98725461959839</v>
+        <v>3.98725509643555</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>3.95340657234192</v>
+        <v>3.95340704917908</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>4.07525777816772</v>
+        <v>4.07525825500488</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G172" t="n">
-        <v>4.02787160873413</v>
+        <v>4.02787208557129</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>3.93986845016479</v>
+        <v>3.93986749649048</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>4.07525777816772</v>
+        <v>4.07525825500488</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.98725461959839</v>
+        <v>3.98725509643555</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.02787160873413</v>
+        <v>4.02787208557129</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G181" t="n">
-        <v>3.96694660186768</v>
+        <v>3.96694564819336</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G182" t="n">
-        <v>3.88909673690796</v>
+        <v>3.8890962600708</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G183" t="n">
-        <v>3.44907665252686</v>
+        <v>3.44907689094543</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5</v>
       </c>
       <c r="G184" t="n">
-        <v>3.38476610183716</v>
+        <v>3.38476634025574</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>3.31707096099854</v>
+        <v>3.31707072257996</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>3.2602071762085</v>
+        <v>3.26020693778992</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G188" t="n">
-        <v>3.3306097984314</v>
+        <v>3.33061027526855</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G193" t="n">
-        <v>3.34956455230713</v>
+        <v>3.34956479072571</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>3.49984765052795</v>
+        <v>3.49984860420227</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G195" t="n">
-        <v>3.46261620521545</v>
+        <v>3.4626157283783</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>4.11587524414062</v>
+        <v>4.11587572097778</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>4.19710969924927</v>
+        <v>4.19711065292358</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>4.35619449615479</v>
+        <v>4.35619401931763</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G201" t="n">
-        <v>4.18357038497925</v>
+        <v>4.18357086181641</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>4.25803565979004</v>
+        <v>4.2580361366272</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>4.26480579376221</v>
+        <v>4.26480531692505</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>4.4408130645752</v>
+        <v>4.44081401824951</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>4.46450614929199</v>
+        <v>4.46450662612915</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>4.4408130645752</v>
+        <v>4.44081401824951</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>4.4408130645752</v>
+        <v>4.44081401824951</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>4.36973333358765</v>
+        <v>4.36973285675049</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>4.58297300338745</v>
+        <v>4.58297348022461</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.75</v>
       </c>
       <c r="G214" t="n">
-        <v>4.56943416595459</v>
+        <v>4.56943464279175</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G217" t="n">
-        <v>4.37988805770874</v>
+        <v>4.37988758087158</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>4.30203771591187</v>
+        <v>4.30203819274902</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G220" t="n">
-        <v>4.43404388427734</v>
+        <v>4.4340443611145</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G221" t="n">
-        <v>4.40696620941162</v>
+        <v>4.40696573257446</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.5</v>
       </c>
       <c r="G223" t="n">
-        <v>4.40019559860229</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="n">
-        <v>4.40019559860229</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>4.3291163444519</v>
+        <v>4.32911586761475</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.43404388427734</v>
+        <v>4.4340443611145</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>4.43404388427734</v>
+        <v>4.4340443611145</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>4.35957908630371</v>
+        <v>4.35957860946655</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.41035079956055</v>
+        <v>4.41035032272339</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>4.50850868225098</v>
+        <v>4.50850820541382</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G233" t="n">
-        <v>4.43742847442627</v>
+        <v>4.43742895126343</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G235" t="n">
-        <v>4.3528094291687</v>
+        <v>4.35280895233154</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G239" t="n">
-        <v>4.41711950302124</v>
+        <v>4.41712045669556</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>4.49835443496704</v>
+        <v>4.49835395812988</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.48820066452026</v>
+        <v>4.48820018768311</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G245" t="n">
-        <v>4.50850868225098</v>
+        <v>4.50850820541382</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>4.45435190200806</v>
+        <v>4.45435237884521</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.51866340637207</v>
+        <v>4.51866245269775</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G248" t="n">
-        <v>4.5355863571167</v>
+        <v>4.53558683395386</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G253" t="n">
-        <v>4.75898122787476</v>
+        <v>4.75898218154907</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G254" t="n">
-        <v>4.74544286727905</v>
+        <v>4.74544191360474</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G258" t="n">
-        <v>4.86390924453735</v>
+        <v>4.8639087677002</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G259" t="n">
-        <v>4.81652164459229</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G262" t="n">
-        <v>4.76236629486084</v>
+        <v>4.76236581802368</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.78944396972656</v>
+        <v>4.7894434928894</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>4.86729383468628</v>
+        <v>4.86729431152344</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78944396972656</v>
+        <v>4.7894434928894</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>4.84021615982056</v>
+        <v>4.8402156829834</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>4.81652164459229</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>4.83683109283447</v>
+        <v>4.83683013916016</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>4.84021615982056</v>
+        <v>4.8402156829834</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G275" t="n">
-        <v>4.82667636871338</v>
+        <v>4.82667684555054</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G276" t="n">
-        <v>4.80298280715942</v>
+        <v>4.80298328399658</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G277" t="n">
-        <v>4.81652164459229</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65066862106323</v>
+        <v>4.65066909790039</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.6574387550354</v>
+        <v>4.65743827819824</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G281" t="n">
-        <v>4.69805479049683</v>
+        <v>4.6980562210083</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>4.67097759246826</v>
+        <v>4.6709771156311</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>4.65066862106323</v>
+        <v>4.65066909790039</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>4.65066862106323</v>
+        <v>4.65066909790039</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G285" t="n">
-        <v>4.59989738464355</v>
+        <v>4.59989786148071</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G286" t="n">
-        <v>4.67097759246826</v>
+        <v>4.6709771156311</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74205780029297</v>
+        <v>4.74205684661865</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>5.04330205917358</v>
+        <v>5.04330158233643</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G291" t="n">
-        <v>5.07038021087646</v>
+        <v>5.07037925720215</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>5.02299356460571</v>
+        <v>5.02299308776855</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G294" t="n">
-        <v>5.00268507003784</v>
+        <v>5.00268411636353</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G296" t="n">
-        <v>4.9756064414978</v>
+        <v>4.97560691833496</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G297" t="n">
-        <v>4.96883726119995</v>
+        <v>4.96883678436279</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>4.9756064414978</v>
+        <v>4.97560691833496</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93160390853882</v>
+        <v>4.93160438537598</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>5.06361055374146</v>
+        <v>5.0636100769043</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>5.04330205917358</v>
+        <v>5.04330158233643</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G303" t="n">
-        <v>5.03991651535034</v>
+        <v>5.03991746902466</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637815475464</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>5.02299356460571</v>
+        <v>5.02299308776855</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G306" t="n">
-        <v>5.08391952514648</v>
+        <v>5.08391904830933</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G307" t="n">
-        <v>5.07038021087646</v>
+        <v>5.07037925720215</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>7.5</v>
       </c>
       <c r="G308" t="n">
-        <v>5.07714939117432</v>
+        <v>5.07714891433716</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G309" t="n">
-        <v>5.00268507003784</v>
+        <v>5.00268411636353</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>5.27346515655518</v>
+        <v>5.27346563339233</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G313" t="n">
-        <v>5.29377460479736</v>
+        <v>5.29377412796021</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G316" t="n">
-        <v>5.37500858306885</v>
+        <v>5.37500905990601</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>5.38177824020386</v>
+        <v>5.3817777633667</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G318" t="n">
-        <v>5.38177824020386</v>
+        <v>5.3817777633667</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>7.875</v>
       </c>
       <c r="G320" t="n">
-        <v>5.33100700378418</v>
+        <v>5.33100652694702</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>5.40208673477173</v>
+        <v>5.40208625793457</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>5.38177824020386</v>
+        <v>5.3817777633667</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G323" t="n">
-        <v>5.3276219367981</v>
+        <v>5.32762145996094</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>5.17869234085083</v>
+        <v>5.17869281768799</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>5.2159252166748</v>
+        <v>5.21592473983765</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>5.17869234085083</v>
+        <v>5.17869281768799</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>5.14484405517578</v>
+        <v>5.14484453201294</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.56500005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>5.12115144729614</v>
+        <v>5.12115097045898</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.94852828979492</v>
+        <v>4.94852781295776</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>4.92483472824097</v>
+        <v>4.92483520507812</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>4.95868253707886</v>
+        <v>4.9586820602417</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>5.11099720001221</v>
+        <v>5.11099767684937</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G340" t="n">
-        <v>5.08391952514648</v>
+        <v>5.08391904830933</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>7.5</v>
       </c>
       <c r="G342" t="n">
-        <v>5.07714939117432</v>
+        <v>5.07714891433716</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.23200082778931</v>
+        <v>5.23200130462646</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>5.15617513656616</v>
+        <v>5.15617418289185</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G349" t="n">
-        <v>5.12170791625977</v>
+        <v>5.12170743942261</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>4.71500444412231</v>
+        <v>4.71500492095947</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G352" t="n">
-        <v>4.6253924369812</v>
+        <v>4.62539148330688</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>4.6770920753479</v>
+        <v>4.67709112167358</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>4.68053865432739</v>
+        <v>4.68053817749023</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G357" t="n">
-        <v>4.59092569351196</v>
+        <v>4.5909252166748</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G358" t="n">
-        <v>4.58747863769531</v>
+        <v>4.58747959136963</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G359" t="n">
-        <v>4.61849784851074</v>
+        <v>4.6184983253479</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>4.4116997718811</v>
+        <v>4.41170024871826</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>4.36689424514771</v>
+        <v>4.36689472198486</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.27383422851562</v>
+        <v>4.27383470535278</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>4.2600474357605</v>
+        <v>4.26004791259766</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>4.23936796188354</v>
+        <v>4.23936748504639</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G370" t="n">
-        <v>4.37378740310669</v>
+        <v>4.37378692626953</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>4.32898092269897</v>
+        <v>4.32898139953613</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G373" t="n">
-        <v>4.27728128433228</v>
+        <v>4.27728033065796</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.25</v>
       </c>
       <c r="G375" t="n">
-        <v>4.30830097198486</v>
+        <v>4.30830144882202</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G376" t="n">
-        <v>4.17732906341553</v>
+        <v>4.17732810974121</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>4.20834922790527</v>
+        <v>4.20834875106812</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G380" t="n">
-        <v>4.26349401473999</v>
+        <v>4.26349449157715</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.125</v>
       </c>
       <c r="G382" t="n">
-        <v>4.22213506698608</v>
+        <v>4.22213459014893</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>4.37378740310669</v>
+        <v>4.37378692626953</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>4.51509952545166</v>
+        <v>4.51510000228882</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>4.49786615371704</v>
+        <v>4.4978666305542</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>4.44961357116699</v>
+        <v>4.44961309432983</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G389" t="n">
-        <v>4.32898092269897</v>
+        <v>4.32898139953613</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>4.49441957473755</v>
+        <v>4.49442005157471</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.625</v>
       </c>
       <c r="G391" t="n">
-        <v>4.5667986869812</v>
+        <v>4.56679916381836</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>4.62883806228638</v>
+        <v>4.62883901596069</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>4.52888631820679</v>
+        <v>4.52888584136963</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>4.70811128616333</v>
+        <v>4.70811176300049</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>4.6253924369812</v>
+        <v>4.62539148330688</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>4.50820636749268</v>
+        <v>4.50820589065552</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>4.58403253555298</v>
+        <v>4.58403205871582</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>4.52199268341064</v>
+        <v>4.5219931602478</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>4.53577899932861</v>
+        <v>4.53577947616577</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>4.49786615371704</v>
+        <v>4.4978666305542</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G409" t="n">
-        <v>4.48408031463623</v>
+        <v>4.48407983779907</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>4.58403253555298</v>
+        <v>4.58403205871582</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>4.48408031463623</v>
+        <v>4.48407983779907</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.46340036392212</v>
+        <v>4.4633994102478</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.39101982116699</v>
+        <v>4.39102029800415</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.42203998565674</v>
+        <v>4.4220404624939</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>4.23936796188354</v>
+        <v>4.23936748504639</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G423" t="n">
-        <v>4.2669415473938</v>
+        <v>4.26694107055664</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G424" t="n">
-        <v>4.27728128433228</v>
+        <v>4.27728033065796</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>4.20490169525146</v>
+        <v>4.20490121841431</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G426" t="n">
-        <v>4.2669415473938</v>
+        <v>4.26694107055664</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G427" t="n">
-        <v>4.28762102127075</v>
+        <v>4.28762149810791</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G429" t="n">
-        <v>4.24626207351685</v>
+        <v>4.24626159667969</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>4.20490169525146</v>
+        <v>4.20490121841431</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G434" t="n">
-        <v>4.2669415473938</v>
+        <v>4.26694107055664</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.125</v>
       </c>
       <c r="G437" t="n">
-        <v>4.22213506698608</v>
+        <v>4.22213459014893</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>4.17732906341553</v>
+        <v>4.17732810974121</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>3.52936053276062</v>
+        <v>3.52936005592346</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>3.44664072990417</v>
+        <v>3.44664120674133</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5</v>
       </c>
       <c r="G441" t="n">
-        <v>3.44664072990417</v>
+        <v>3.44664120674133</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G444" t="n">
-        <v>3.44250512123108</v>
+        <v>3.44250464439392</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G445" t="n">
-        <v>3.44526267051697</v>
+        <v>3.44526195526123</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G446" t="n">
-        <v>3.42458295822144</v>
+        <v>3.4245822429657</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G448" t="n">
-        <v>3.43699026107788</v>
+        <v>3.4369900226593</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G450" t="n">
-        <v>3.38046455383301</v>
+        <v>3.38046503067017</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G452" t="n">
-        <v>3.23984217643738</v>
+        <v>3.2398419380188</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G453" t="n">
-        <v>3.15436601638794</v>
+        <v>3.15436553955078</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G455" t="n">
-        <v>2.99719882011414</v>
+        <v>2.99719905853271</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>3.129549741745</v>
+        <v>3.12954998016357</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>3.06751012802124</v>
+        <v>3.06751036643982</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G460" t="n">
-        <v>2.93653845787048</v>
+        <v>2.9365382194519</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G461" t="n">
-        <v>2.95446038246155</v>
+        <v>2.95446014404297</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G463" t="n">
-        <v>2.84830403327942</v>
+        <v>2.84830379486084</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G464" t="n">
-        <v>2.8772554397583</v>
+        <v>2.87725567817688</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G466" t="n">
-        <v>2.98479104042053</v>
+        <v>2.98479056358337</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>2.86071181297302</v>
+        <v>2.86071228981018</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>2.97789764404297</v>
+        <v>2.97789788246155</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.86071181297302</v>
+        <v>2.86071228981018</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G479" t="n">
-        <v>2.80556583404541</v>
+        <v>2.80556559562683</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.8469250202179</v>
+        <v>2.84692549705505</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G486" t="n">
-        <v>2.76420640945435</v>
+        <v>2.76420593261719</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G492" t="n">
-        <v>2.78764343261719</v>
+        <v>2.78764295578003</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>2.88139152526855</v>
+        <v>2.88139176368713</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G494" t="n">
-        <v>2.90896463394165</v>
+        <v>2.90896487236023</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>2.94756722450256</v>
+        <v>2.94756746292114</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G496" t="n">
-        <v>2.88690662384033</v>
+        <v>2.88690638542175</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G501" t="n">
-        <v>2.8772554397583</v>
+        <v>2.87725567817688</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G504" t="n">
-        <v>2.81935238838196</v>
+        <v>2.81935214996338</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>2.86760520935059</v>
+        <v>2.86760544776917</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G507" t="n">
-        <v>2.85106158256531</v>
+        <v>2.85106134414673</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G509" t="n">
-        <v>2.8993136882782</v>
+        <v>2.89931416511536</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G510" t="n">
-        <v>2.88690662384033</v>
+        <v>2.88690638542175</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>2.90207147598267</v>
+        <v>2.90207171440125</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.0744035243988</v>
+        <v>3.07440376281738</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>3.1192102432251</v>
+        <v>3.11920976638794</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>3.02270412445068</v>
+        <v>3.0227038860321</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>3.05717062950134</v>
+        <v>3.05717039108276</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.13299632072449</v>
+        <v>3.13299655914307</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>3.0744035243988</v>
+        <v>3.07440376281738</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>3.08819031715393</v>
+        <v>3.08819055557251</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>3.13988971710205</v>
+        <v>3.13988995552063</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>3.09508299827576</v>
+        <v>3.09508323669434</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G529" t="n">
-        <v>3.09508299827576</v>
+        <v>3.09508323669434</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G532" t="n">
-        <v>3.05027770996094</v>
+        <v>3.05027723312378</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>3.03304386138916</v>
+        <v>3.03304409980774</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>2.98479104042053</v>
+        <v>2.98479056358337</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>2.84003210067749</v>
+        <v>2.84003233909607</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.7848858833313</v>
+        <v>2.78488564491272</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G541" t="n">
-        <v>2.78143906593323</v>
+        <v>2.78143882751465</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.71595287322998</v>
+        <v>2.71595311164856</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>3.08129668235779</v>
+        <v>3.08129692077637</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>3.0744035243988</v>
+        <v>3.07440376281738</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>3.08819031715393</v>
+        <v>3.08819055557251</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06406354904175</v>
+        <v>3.06406378746033</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>3.04338383674622</v>
+        <v>3.04338359832764</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G549" t="n">
-        <v>3.02615070343018</v>
+        <v>3.0261504650116</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G552" t="n">
-        <v>3.02270412445068</v>
+        <v>3.0227038860321</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G553" t="n">
-        <v>3.00547122955322</v>
+        <v>3.00547051429749</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>2.90551829338074</v>
+        <v>2.90551805496216</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.90207147598267</v>
+        <v>2.90207171440125</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>3.0744035243988</v>
+        <v>3.07440376281738</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>3.06061744689941</v>
+        <v>3.06061720848083</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G561" t="n">
-        <v>2.96755766868591</v>
+        <v>2.96755790710449</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G562" t="n">
-        <v>2.87794518470764</v>
+        <v>2.87794542312622</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.88483858108521</v>
+        <v>2.88483834266663</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>2.84003210067749</v>
+        <v>2.84003233909607</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>2.87794518470764</v>
+        <v>2.87794542312622</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.84003210067749</v>
+        <v>2.84003233909607</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G568" t="n">
-        <v>2.90896463394165</v>
+        <v>2.90896487236023</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>2.86760520935059</v>
+        <v>2.86760544776917</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G570" t="n">
-        <v>2.84003210067749</v>
+        <v>2.84003233909607</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>2.8469250202179</v>
+        <v>2.84692549705505</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>2.98134422302246</v>
+        <v>2.98134398460388</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>2.94687819480896</v>
+        <v>2.94687795639038</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>2.99168467521667</v>
+        <v>2.9916844367981</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G578" t="n">
-        <v>2.97789764404297</v>
+        <v>2.97789788246155</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G580" t="n">
-        <v>2.99513101577759</v>
+        <v>2.99513077735901</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>2.97789764404297</v>
+        <v>2.97789788246155</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G584" t="n">
-        <v>2.98134422302246</v>
+        <v>2.98134398460388</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>2.98823761940002</v>
+        <v>2.9882378578186</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G586" t="n">
-        <v>2.99168467521667</v>
+        <v>2.9916844367981</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G588" t="n">
-        <v>3.03649091720581</v>
+        <v>3.03649067878723</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>3.06751012802124</v>
+        <v>3.06751036643982</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G592" t="n">
-        <v>3.02270412445068</v>
+        <v>3.0227038860321</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G594" t="n">
-        <v>3.02270412445068</v>
+        <v>3.0227038860321</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03304386138916</v>
+        <v>3.03304409980774</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.375</v>
       </c>
       <c r="G599" t="n">
-        <v>3.01581120491028</v>
+        <v>3.01581048965454</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>3.03649091720581</v>
+        <v>3.03649067878723</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G602" t="n">
-        <v>3.02270412445068</v>
+        <v>3.0227038860321</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G605" t="n">
-        <v>2.9480254650116</v>
+        <v>2.94802522659302</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.87690305709839</v>
+        <v>2.87690281867981</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.58530068397522</v>
+        <v>2.5853009223938</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.58530068397522</v>
+        <v>2.5853009223938</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.61019372940063</v>
+        <v>2.61019349098206</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G626" t="n">
-        <v>2.7026526927948</v>
+        <v>2.70265316963196</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G632" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>2.49995374679565</v>
+        <v>2.49995398521423</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>2.59241318702698</v>
+        <v>2.5924129486084</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.71687746047974</v>
+        <v>2.71687722206116</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G641" t="n">
-        <v>2.74177026748657</v>
+        <v>2.74177050590515</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G642" t="n">
-        <v>2.79155611991882</v>
+        <v>2.79155588150024</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G651" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G652" t="n">
-        <v>2.68842840194702</v>
+        <v>2.6884286403656</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>2.63864302635193</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.68842840194702</v>
+        <v>2.6884286403656</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.63864302635193</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G670" t="n">
-        <v>2.60663771629333</v>
+        <v>2.60663795471191</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>2.64575457572937</v>
+        <v>2.64575481414795</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>2.82711720466614</v>
+        <v>2.82711696624756</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>2.64931106567383</v>
+        <v>2.64931082725525</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G684" t="n">
-        <v>2.64931106567383</v>
+        <v>2.64931082725525</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>2.61019372940063</v>
+        <v>2.61019349098206</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G689" t="n">
-        <v>2.60308194160461</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>2.54973983764648</v>
+        <v>2.54973959922791</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>2.60663771629333</v>
+        <v>2.60663795471191</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>2.77021908760071</v>
+        <v>2.77021932601929</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G695" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G697" t="n">
-        <v>2.74177026748657</v>
+        <v>2.74177050590515</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G707" t="n">
-        <v>2.63864302635193</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730599403381</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G712" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G713" t="n">
-        <v>2.55329585075378</v>
+        <v>2.55329561233521</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G714" t="n">
-        <v>2.52840280532837</v>
+        <v>2.52840304374695</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G715" t="n">
-        <v>2.47861695289612</v>
+        <v>2.4786171913147</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>2.54973983764648</v>
+        <v>2.54973959922791</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G717" t="n">
-        <v>2.55329585075378</v>
+        <v>2.55329561233521</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>2.60308194160461</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730599403381</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G725" t="n">
-        <v>2.77021908760071</v>
+        <v>2.77021932601929</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.82356119155884</v>
+        <v>2.82356142997742</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.90179562568665</v>
+        <v>2.90179586410522</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>2.83067321777344</v>
+        <v>2.83067345619202</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G743" t="n">
-        <v>2.7026526927948</v>
+        <v>2.70265316963196</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G744" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G747" t="n">
-        <v>2.68842840194702</v>
+        <v>2.6884286403656</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G748" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730599403381</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.59241318702698</v>
+        <v>2.5924129486084</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.59241318702698</v>
+        <v>2.5924129486084</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G755" t="n">
-        <v>2.63864302635193</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>2.60308194160461</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60663771629333</v>
+        <v>2.60663795471191</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>2.61019372940063</v>
+        <v>2.61019349098206</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>2.56040787696838</v>
+        <v>2.5604076385498</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>2.51773452758789</v>
+        <v>2.51773476600647</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G764" t="n">
-        <v>2.62797451019287</v>
+        <v>2.62797427177429</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>2.64931106567383</v>
+        <v>2.64931082725525</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.62441825866699</v>
+        <v>2.62441849708557</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G768" t="n">
-        <v>2.67420411109924</v>
+        <v>2.67420434951782</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G772" t="n">
-        <v>2.73110175132751</v>
+        <v>2.73110151290894</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G777" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71687746047974</v>
+        <v>2.71687722206116</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>2.63864302635193</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>2.84134197235107</v>
+        <v>2.8413417339325</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>2.64575457572937</v>
+        <v>2.64575481414795</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G789" t="n">
-        <v>2.67420411109924</v>
+        <v>2.67420434951782</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G796" t="n">
-        <v>2.51417851448059</v>
+        <v>2.51417827606201</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.49995374679565</v>
+        <v>2.49995398521423</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G800" t="n">
-        <v>2.51773452758789</v>
+        <v>2.51773476600647</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G803" t="n">
-        <v>2.52840280532837</v>
+        <v>2.52840304374695</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G804" t="n">
-        <v>2.49639797210693</v>
+        <v>2.49639821052551</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>2.49284195899963</v>
+        <v>2.49284172058105</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>2.49639797210693</v>
+        <v>2.49639821052551</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.375</v>
       </c>
       <c r="G810" t="n">
-        <v>2.40038251876831</v>
+        <v>2.40038275718689</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>2.3257040977478</v>
+        <v>2.32570385932922</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G817" t="n">
-        <v>2.27236199378967</v>
+        <v>2.27236223220825</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G818" t="n">
-        <v>2.27591800689697</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G819" t="n">
-        <v>2.27591800689697</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G820" t="n">
-        <v>2.27591800689697</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G821" t="n">
-        <v>2.27591800689697</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>2.27236199378967</v>
+        <v>2.27236223220825</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G828" t="n">
-        <v>2.32214760780334</v>
+        <v>2.32214784622192</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G831" t="n">
-        <v>2.35770916938782</v>
+        <v>2.35770893096924</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>2.36837768554688</v>
+        <v>2.3683774471283</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G833" t="n">
-        <v>2.30792331695557</v>
+        <v>2.30792307853699</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.41105103492737</v>
+        <v>2.41105079650879</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G840" t="n">
-        <v>2.4430558681488</v>
+        <v>2.44305610656738</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G843" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>2.58530068397522</v>
+        <v>2.5853009223938</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.60308194160461</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G848" t="n">
-        <v>2.47861695289612</v>
+        <v>2.4786171913147</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42883133888245</v>
+        <v>2.42883157730103</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.375</v>
       </c>
       <c r="G850" t="n">
-        <v>2.40038251876831</v>
+        <v>2.40038275718689</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G851" t="n">
-        <v>2.4430558681488</v>
+        <v>2.44305610656738</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>2.43540239334106</v>
+        <v>2.43540215492249</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G856" t="n">
-        <v>2.42057466506958</v>
+        <v>2.42057490348816</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>2.45764350891113</v>
+        <v>2.45764327049255</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.37238550186157</v>
+        <v>2.37238574028015</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G862" t="n">
-        <v>2.26488709449768</v>
+        <v>2.2648868560791</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G865" t="n">
-        <v>2.21669793128967</v>
+        <v>2.21669769287109</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G866" t="n">
-        <v>2.21669793128967</v>
+        <v>2.21669769287109</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G868" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05359625816345</v>
+        <v>2.05359649658203</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>2.06842374801636</v>
+        <v>2.06842398643494</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G875" t="n">
-        <v>2.08325147628784</v>
+        <v>2.08325123786926</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G877" t="n">
-        <v>2.20187067985535</v>
+        <v>2.20187044143677</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G881" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G882" t="n">
-        <v>2.11661267280579</v>
+        <v>2.11661291122437</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G884" t="n">
-        <v>2.03135538101196</v>
+        <v>2.03135514259338</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G885" t="n">
-        <v>1.99799335002899</v>
+        <v>1.99799358844757</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>2.37609267234802</v>
+        <v>2.3760929107666</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.28342151641846</v>
+        <v>2.28342127799988</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G893" t="n">
-        <v>2.24635291099548</v>
+        <v>2.2463526725769</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G896" t="n">
-        <v>2.26488709449768</v>
+        <v>2.2648868560791</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G897" t="n">
-        <v>2.26488709449768</v>
+        <v>2.2648868560791</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G898" t="n">
-        <v>2.27230072021484</v>
+        <v>2.27230048179626</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G899" t="n">
-        <v>2.27971434593201</v>
+        <v>2.27971410751343</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.30566239356995</v>
+        <v>2.30566263198853</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G901" t="n">
-        <v>2.28342151641846</v>
+        <v>2.28342127799988</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G904" t="n">
-        <v>2.26118016242981</v>
+        <v>2.26117992401123</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G906" t="n">
-        <v>2.26118016242981</v>
+        <v>2.26117992401123</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.24635291099548</v>
+        <v>2.2463526725769</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>2.28342151641846</v>
+        <v>2.28342127799988</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G911" t="n">
-        <v>2.25005960464478</v>
+        <v>2.25005984306335</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G913" t="n">
-        <v>2.21669793128967</v>
+        <v>2.21669769287109</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G914" t="n">
-        <v>2.18704295158386</v>
+        <v>2.18704319000244</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G920" t="n">
-        <v>2.17221593856812</v>
+        <v>2.17221570014954</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G921" t="n">
-        <v>2.15368151664734</v>
+        <v>2.15368127822876</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G922" t="n">
-        <v>2.14626789093018</v>
+        <v>2.1462676525116</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>2.19074964523315</v>
+        <v>2.19074988365173</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G926" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G930" t="n">
-        <v>2.14626789093018</v>
+        <v>2.1462676525116</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G937" t="n">
-        <v>2.2982485294342</v>
+        <v>2.29824876785278</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G939" t="n">
-        <v>2.52807378768921</v>
+        <v>2.52807354927063</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G943" t="n">
-        <v>2.78755331039429</v>
+        <v>2.78755354881287</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G944" t="n">
-        <v>2.77272605895996</v>
+        <v>2.77272582054138</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G945" t="n">
-        <v>2.7578980922699</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>2.7578980922699</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G947" t="n">
-        <v>2.7578980922699</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G949" t="n">
-        <v>2.73565721511841</v>
+        <v>2.73565745353699</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G950" t="n">
-        <v>2.73565721511841</v>
+        <v>2.73565745353699</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G952" t="n">
-        <v>2.7578980922699</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>2.73565721511841</v>
+        <v>2.73565745353699</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G958" t="n">
-        <v>2.72824382781982</v>
+        <v>2.72824358940125</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>2.71712303161621</v>
+        <v>2.71712327003479</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G960" t="n">
-        <v>2.7578980922699</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G961" t="n">
-        <v>2.76160526275635</v>
+        <v>2.76160502433777</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G965" t="n">
-        <v>2.7578980922699</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G970" t="n">
-        <v>2.6689338684082</v>
+        <v>2.66893362998962</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>2.75048494338989</v>
+        <v>2.75048470497131</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>2.80238056182861</v>
+        <v>2.80238080024719</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G976" t="n">
-        <v>2.76160526275635</v>
+        <v>2.76160502433777</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G980" t="n">
-        <v>2.90987944602966</v>
+        <v>2.90987920761108</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>2.94694781303406</v>
+        <v>2.94694757461548</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.9358274936676</v>
+        <v>2.93582725524902</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>2.96177554130554</v>
+        <v>2.96177530288696</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>3.41771841049194</v>
+        <v>3.41771864891052</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G998" t="n">
-        <v>3.4807345867157</v>
+        <v>3.48073506355286</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.52892374992371</v>
+        <v>3.52892398834229</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.5993537902832</v>
+        <v>3.59935402870178</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.59564709663391</v>
+        <v>3.59564685821533</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.68461155891418</v>
+        <v>3.68461179733276</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.82547211647034</v>
+        <v>3.82547163963318</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.79581761360168</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.79581761360168</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.76616215705872</v>
+        <v>3.76616263389587</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.80323123931885</v>
+        <v>3.80323076248169</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.79581761360168</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.76616215705872</v>
+        <v>3.76616263389587</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.81064414978027</v>
+        <v>3.81064462661743</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.79581761360168</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.84029936790466</v>
+        <v>3.84029912948608</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.85512638092041</v>
+        <v>3.85512685775757</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.86995387077332</v>
+        <v>3.86995434761047</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.85512638092041</v>
+        <v>3.85512685775757</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.81064414978027</v>
+        <v>3.81064462661743</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.85512638092041</v>
+        <v>3.85512685775757</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.78840351104736</v>
+        <v>3.78840398788452</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.83288526535034</v>
+        <v>3.83288621902466</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.79581761360168</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.76616215705872</v>
+        <v>3.76616263389587</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.60676765441895</v>
+        <v>3.60676741600037</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.47332119941711</v>
+        <v>3.47332096099854</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.60306072235107</v>
+        <v>3.60306119918823</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.7290940284729</v>
+        <v>3.72909450531006</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.76616215705872</v>
+        <v>3.76616263389587</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.70685267448425</v>
+        <v>3.70685315132141</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.6771981716156</v>
+        <v>3.67719769477844</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.83288526535034</v>
+        <v>3.83288621902466</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.13684749603271</v>
+        <v>4.13684797286987</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.0478835105896</v>
+        <v>4.04788303375244</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.06271076202393</v>
+        <v>4.06271028518677</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.79581761360168</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.80323123931885</v>
+        <v>3.80323076248169</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.78840351104736</v>
+        <v>3.78840398788452</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.70685267448425</v>
+        <v>3.70685315132141</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.5659921169281</v>
+        <v>3.56599235534668</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.71426630020142</v>
+        <v>3.71426653862</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.62159490585327</v>
+        <v>3.62159538269043</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.55857872962952</v>
+        <v>3.55857849121094</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.5132462978363</v>
+        <v>2.51324605941772</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.29083466529846</v>
+        <v>2.29083490371704</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.06471681594849</v>
+        <v>2.06471705436707</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.20928430557251</v>
+        <v>2.20928406715393</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.31307601928711</v>
+        <v>2.31307625770569</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.37238550186157</v>
+        <v>2.37238574028015</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.34273099899292</v>
+        <v>2.34273076057434</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.28342151641846</v>
+        <v>2.28342127799988</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.26118016242981</v>
+        <v>2.26117992401123</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.2982485294342</v>
+        <v>2.29824876785278</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.53548717498779</v>
+        <v>2.53548741340637</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.6689338684082</v>
+        <v>2.66893362998962</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.57996964454651</v>
+        <v>2.57996940612793</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.06927394866943</v>
+        <v>3.06927418708801</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.07668781280518</v>
+        <v>3.07668805122375</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.1285834312439</v>
+        <v>3.12858366966248</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.06927394866943</v>
+        <v>3.06927418708801</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.94324111938477</v>
+        <v>2.94324135780334</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.97289633750916</v>
+        <v>2.972895860672</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.06927394866943</v>
+        <v>3.06927418708801</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.16194534301758</v>
+        <v>3.161945104599</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.18047976493835</v>
+        <v>3.18047952651978</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.26944422721863</v>
+        <v>3.26944398880005</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.29168558120728</v>
+        <v>3.2916853427887</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.20642757415771</v>
+        <v>3.20642733573914</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.28056526184082</v>
+        <v>3.28056502342224</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.18047976493835</v>
+        <v>3.18047952651978</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17677235603333</v>
+        <v>3.17677283287048</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.73936438560486</v>
+        <v>2.73936414718628</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.75048494338989</v>
+        <v>2.75048470497131</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.80238056182861</v>
+        <v>2.80238080024719</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.9358274936676</v>
+        <v>2.93582725524902</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.82832837104797</v>
+        <v>2.82832884788513</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.80238056182861</v>
+        <v>2.80238080024719</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85798335075378</v>
+        <v>2.85798358917236</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.97289633750916</v>
+        <v>2.972895860672</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.1285834312439</v>
+        <v>3.12858366966248</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.19160008430481</v>
+        <v>3.19160032272339</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.21754860877991</v>
+        <v>3.21754837036133</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.375</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.24349641799927</v>
+        <v>3.24349594116211</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.35099530220032</v>
+        <v>3.35099482536316</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.32875323295593</v>
+        <v>3.32875347137451</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.37323617935181</v>
+        <v>3.37323594093323</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.55857872962952</v>
+        <v>3.55857849121094</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.56969928741455</v>
+        <v>3.56969904899597</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41771841049194</v>
+        <v>3.41771864891052</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.6771981716156</v>
+        <v>3.67719769477844</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.86995387077332</v>
+        <v>3.86995434761047</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.79581761360168</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.86254024505615</v>
+        <v>3.86254072189331</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.34443187713623</v>
+        <v>4.34443140029907</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.55942869186401</v>
+        <v>4.55942821502686</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.50011920928955</v>
+        <v>4.50011968612671</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.81149482727051</v>
+        <v>4.81149435043335</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.01907825469971</v>
+        <v>5.01907873153687</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>6.75</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.00425100326538</v>
+        <v>5.00425148010254</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1207" t="n">
-        <v>5.59734773635864</v>
+        <v>5.5973482131958</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.65665674209595</v>
+        <v>5.65665769577026</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.76044940948486</v>
+        <v>5.76044988632202</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.56769323348999</v>
+        <v>5.56769275665283</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.5232105255127</v>
+        <v>5.52321004867554</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1222" t="n">
-        <v>5.44165992736816</v>
+        <v>5.44165945053101</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.40459156036377</v>
+        <v>5.40459108352661</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1226" t="n">
-        <v>5.09321546554565</v>
+        <v>5.09321594238281</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.1747670173645</v>
+        <v>5.17476654052734</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1228" t="n">
-        <v>5.16735219955444</v>
+        <v>5.1673526763916</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>5.40459156036377</v>
+        <v>5.40459108352661</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.59734773635864</v>
+        <v>5.5973482131958</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.76044940948486</v>
+        <v>5.76044988632202</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.6937255859375</v>
+        <v>5.69372510910034</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.66407108306885</v>
+        <v>5.66407060623169</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1236" t="n">
-        <v>5.65665674209595</v>
+        <v>5.65665769577026</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.51664686203003</v>
+        <v>6.51664733886719</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1240" t="n">
-        <v>6.50182008743286</v>
+        <v>6.5018196105957</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1241" t="n">
-        <v>6.56854295730591</v>
+        <v>6.56854343414307</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1242" t="n">
-        <v>6.59078407287598</v>
+        <v>6.59078502655029</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1243" t="n">
-        <v>6.3387188911438</v>
+        <v>6.33871793746948</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1248" t="n">
-        <v>6.24975395202637</v>
+        <v>6.24975347518921</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1253" t="n">
-        <v>6.58337116241455</v>
+        <v>6.58337068557739</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1254" t="n">
-        <v>6.57595682144165</v>
+        <v>6.57595634460449</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.11715745925903</v>
+        <v>7.11715698242188</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1257" t="n">
-        <v>7.05784749984741</v>
+        <v>7.05784797668457</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1258" t="n">
-        <v>7.065260887146</v>
+        <v>7.06526136398315</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.05043458938599</v>
+        <v>7.05043411254883</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1262" t="n">
-        <v>7.6064624786377</v>
+        <v>7.60646152496338</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>7.93266487121582</v>
+        <v>7.9326639175415</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>10.5</v>
       </c>
       <c r="G1264" t="n">
-        <v>7.78439092636108</v>
+        <v>7.78438997268677</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1265" t="n">
-        <v>7.93266487121582</v>
+        <v>7.9326639175415</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1266" t="n">
-        <v>7.94749212265015</v>
+        <v>7.94749307632446</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.99197340011597</v>
+        <v>7.99197435379028</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1271" t="n">
-        <v>8.05128479003906</v>
+        <v>8.05128288269043</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.68059873580933</v>
+        <v>7.68059825897217</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.59163522720337</v>
+        <v>7.59163427352905</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>7.38404989242554</v>
+        <v>7.38405132293701</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.3543963432312</v>
+        <v>7.35439538955688</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.23577642440796</v>
+        <v>7.23577690124512</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>7.3543963432312</v>
+        <v>7.35439538955688</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.32474184036255</v>
+        <v>7.32474088668823</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.05784749984741</v>
+        <v>7.05784797668457</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1287" t="n">
-        <v>7.32474184036255</v>
+        <v>7.32474088668823</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1288" t="n">
-        <v>7.08008909225464</v>
+        <v>7.08008861541748</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.19129419326782</v>
+        <v>7.19129371643066</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1290" t="n">
-        <v>7.02077960968018</v>
+        <v>7.02078008651733</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1291" t="n">
-        <v>7.1393985748291</v>
+        <v>7.13939809799194</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>10</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.41370534896851</v>
+        <v>7.41370630264282</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1300" t="n">
-        <v>8.27369499206543</v>
+        <v>8.27369594573975</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>8.28852462768555</v>
+        <v>8.28852367401123</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1306" t="n">
-        <v>8.31817722320557</v>
+        <v>8.31817817687988</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1307" t="n">
-        <v>8.51093196868896</v>
+        <v>8.51093292236328</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1309" t="n">
-        <v>7.99197340011597</v>
+        <v>7.99197435379028</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.84370088577271</v>
+        <v>7.84369993209839</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1311" t="n">
-        <v>7.73990774154663</v>
+        <v>7.73990869522095</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1316" t="n">
-        <v>7.29508638381958</v>
+        <v>7.29508686065674</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>10.5</v>
       </c>
       <c r="G1318" t="n">
-        <v>7.78439092636108</v>
+        <v>7.78438997268677</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1320" t="n">
-        <v>7.59163522720337</v>
+        <v>7.59163427352905</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1322" t="n">
-        <v>7.75473642349243</v>
+        <v>7.75473546981812</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1324" t="n">
-        <v>7.62128829956055</v>
+        <v>7.62128925323486</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1325" t="n">
-        <v>7.62128829956055</v>
+        <v>7.62128925323486</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>7.65094423294067</v>
+        <v>7.65094327926636</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>10.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>7.78439092636108</v>
+        <v>7.78438997268677</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1329" t="n">
-        <v>7.84370088577271</v>
+        <v>7.84369993209839</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1332" t="n">
-        <v>7.99197340011597</v>
+        <v>7.99197435379028</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1334" t="n">
-        <v>8.08093929290771</v>
+        <v>8.0809383392334</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1336" t="n">
-        <v>8.42196846008301</v>
+        <v>8.42196941375732</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1337" t="n">
-        <v>8.5850715637207</v>
+        <v>8.58507061004639</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1339" t="n">
-        <v>9.75643634796143</v>
+        <v>9.75643730163574</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>13.5</v>
       </c>
       <c r="G1340" t="n">
-        <v>10.0085020065308</v>
+        <v>10.0085029602051</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.68229866027832</v>
+        <v>9.68229961395264</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1343" t="n">
-        <v>10.2457408905029</v>
+        <v>10.2457418441772</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.95660591125488</v>
+        <v>9.95660781860352</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1350" t="n">
-        <v>10.1122951507568</v>
+        <v>10.1122941970825</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1351" t="n">
-        <v>10.060399055481</v>
+        <v>10.0603981018066</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1352" t="n">
-        <v>10.060399055481</v>
+        <v>10.0603981018066</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>13.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>10.0085020065308</v>
+        <v>10.0085029602051</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1354" t="n">
-        <v>10.1271209716797</v>
+        <v>10.127121925354</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.95660591125488</v>
+        <v>9.95660781860352</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1356" t="n">
-        <v>10.1048803329468</v>
+        <v>10.1048812866211</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G1359" t="n">
-        <v>10.0285968780518</v>
+        <v>10.0285978317261</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1369" t="n">
-        <v>10.7002582550049</v>
+        <v>10.7002573013306</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G1373" t="n">
-        <v>10.8160629272461</v>
+        <v>10.8160619735718</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1375" t="n">
-        <v>11.2252349853516</v>
+        <v>11.2252359390259</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1376" t="n">
-        <v>11.3796405792236</v>
+        <v>11.3796396255493</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>14.75</v>
       </c>
       <c r="G1377" t="n">
-        <v>11.3873615264893</v>
+        <v>11.3873605728149</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.7888145446777</v>
+        <v>11.7888135910034</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1383" t="n">
-        <v>11.9046173095703</v>
+        <v>11.9046182632446</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1385" t="n">
-        <v>11.7810926437378</v>
+        <v>11.7810935974121</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>11.6575689315796</v>
+        <v>11.6575698852539</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1387" t="n">
-        <v>11.6730098724365</v>
+        <v>11.6730089187622</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1388" t="n">
-        <v>11.7038908004761</v>
+        <v>11.7038898468018</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1389" t="n">
-        <v>11.9895391464233</v>
+        <v>11.9895401000977</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1390" t="n">
-        <v>11.8582954406738</v>
+        <v>11.8582944869995</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.4954452514648</v>
+        <v>11.4954442977905</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1392" t="n">
-        <v>11.6035280227661</v>
+        <v>11.6035270690918</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>15</v>
       </c>
       <c r="G1393" t="n">
-        <v>11.5803661346436</v>
+        <v>11.5803670883179</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1394" t="n">
-        <v>11.6575689315796</v>
+        <v>11.6575698852539</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>11.6575689315796</v>
+        <v>11.6575698852539</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1400" t="n">
-        <v>11.634407043457</v>
+        <v>11.6344079971313</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1401" t="n">
-        <v>11.9586582183838</v>
+        <v>11.9586591720581</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>12.2365884780884</v>
+        <v>12.2365875244141</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.1017112731934</v>
+        <v>11.1017122268677</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1411" t="n">
-        <v>11.3950805664062</v>
+        <v>11.3950815200806</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G1412" t="n">
-        <v>11.5958080291748</v>
+        <v>11.5958070755005</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1413" t="n">
-        <v>11.8505764007568</v>
+        <v>11.8505754470825</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1414" t="n">
-        <v>11.7810926437378</v>
+        <v>11.7810935974121</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1416" t="n">
-        <v>11.6035280227661</v>
+        <v>11.6035270690918</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1418" t="n">
-        <v>11.9895391464233</v>
+        <v>11.9895401000977</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.2365884780884</v>
+        <v>12.2365875244141</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1426" t="n">
-        <v>12.8001651763916</v>
+        <v>12.8001642227173</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1427" t="n">
-        <v>12.7847242355347</v>
+        <v>12.784725189209</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G1429" t="n">
-        <v>12.329231262207</v>
+        <v>12.3292303085327</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1432" t="n">
-        <v>12.2829093933105</v>
+        <v>12.2829084396362</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.0435829162598</v>
+        <v>12.0435819625854</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1435" t="n">
-        <v>11.8505764007568</v>
+        <v>11.8505754470825</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1436" t="n">
-        <v>12.0899038314819</v>
+        <v>12.0899028778076</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>12.0435829162598</v>
+        <v>12.0435819625854</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.2751893997192</v>
+        <v>12.2751884460449</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G1444" t="n">
-        <v>12.3755531311035</v>
+        <v>12.3755521774292</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1446" t="n">
-        <v>10.8392238616943</v>
+        <v>10.8392248153687</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1447" t="n">
-        <v>10.5149717330933</v>
+        <v>10.5149726867676</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>13</v>
       </c>
       <c r="G1448" t="n">
-        <v>10.0363168716431</v>
+        <v>10.0363178253174</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>9.6889066696167</v>
+        <v>9.68890762329102</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0749187469482</v>
+        <v>10.0749197006226</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1456" t="n">
-        <v>9.34149646759033</v>
+        <v>9.34149551391602</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G1457" t="n">
-        <v>9.58082389831543</v>
+        <v>9.58082294464111</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.71615505218506</v>
+        <v>8.71615600585938</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.73159790039062</v>
+        <v>8.73159694671631</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1463" t="n">
-        <v>8.77019691467285</v>
+        <v>8.77019786834717</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1469" t="n">
-        <v>8.67755508422852</v>
+        <v>8.6775541305542</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1475" t="n">
-        <v>9.04040622711182</v>
+        <v>9.04040718078613</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1478" t="n">
-        <v>9.12532806396484</v>
+        <v>9.12532901763916</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1480" t="n">
-        <v>9.15620899200439</v>
+        <v>9.15620994567871</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1481" t="n">
-        <v>8.71615505218506</v>
+        <v>8.71615600585938</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1483" t="n">
-        <v>8.66211414337158</v>
+        <v>8.6621150970459</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1486" t="n">
-        <v>9.31833553314209</v>
+        <v>9.31833457946777</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1487" t="n">
-        <v>9.60398387908936</v>
+        <v>9.60398483276367</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1491" t="n">
-        <v>9.5653829574585</v>
+        <v>9.56538391113281</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>12.25</v>
       </c>
       <c r="G1493" t="n">
-        <v>9.45730018615723</v>
+        <v>9.45729923248291</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1495" t="n">
-        <v>9.99771690368652</v>
+        <v>9.99771595001221</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>9.70434761047363</v>
+        <v>9.70434665679932</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1500" t="n">
-        <v>9.00952434539795</v>
+        <v>9.00952529907227</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1501" t="n">
-        <v>9.06356620788574</v>
+        <v>9.06356716156006</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>9.25657272338867</v>
+        <v>9.25657367706299</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G1507" t="n">
-        <v>9.44185829162598</v>
+        <v>9.44185924530029</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1513" t="n">
-        <v>9.94367599487305</v>
+        <v>9.94367504119873</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1518" t="n">
-        <v>9.12532806396484</v>
+        <v>9.12532901763916</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1519" t="n">
-        <v>9.15620899200439</v>
+        <v>9.15620994567871</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1520" t="n">
-        <v>9.30289363861084</v>
+        <v>9.30289554595947</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1523" t="n">
-        <v>9.79699039459229</v>
+        <v>9.79698944091797</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>13</v>
       </c>
       <c r="G1528" t="n">
-        <v>10.0363168716431</v>
+        <v>10.0363178253174</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.99408531188965</v>
+        <v>8.99408435821533</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1533" t="n">
-        <v>9.23341274261475</v>
+        <v>9.23341178894043</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1534" t="n">
-        <v>9.44957828521729</v>
+        <v>9.4495792388916</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1537" t="n">
-        <v>9.61170482635498</v>
+        <v>9.61170387268066</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1539" t="n">
-        <v>9.34149646759033</v>
+        <v>9.34149551391602</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G1541" t="n">
-        <v>9.39553737640381</v>
+        <v>9.39553833007812</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1542" t="n">
-        <v>9.04040622711182</v>
+        <v>9.04040718078613</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>12.25</v>
       </c>
       <c r="G1545" t="n">
-        <v>9.45730018615723</v>
+        <v>9.45729923248291</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>9.12532806396484</v>
+        <v>9.12532901763916</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G1555" t="n">
-        <v>9.44185829162598</v>
+        <v>9.44185924530029</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1558" t="n">
-        <v>9.30289363861084</v>
+        <v>9.30289554595947</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1560" t="n">
-        <v>9.00952434539795</v>
+        <v>9.00952529907227</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1564" t="n">
-        <v>8.71615505218506</v>
+        <v>8.71615600585938</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1566" t="n">
-        <v>8.66211414337158</v>
+        <v>8.6621150970459</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1567" t="n">
-        <v>8.60807228088379</v>
+        <v>8.60807132720947</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1568" t="n">
-        <v>8.27610206604004</v>
+        <v>8.27610301971436</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1569" t="n">
-        <v>8.22206020355225</v>
+        <v>8.22205924987793</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1570" t="n">
-        <v>7.85148954391479</v>
+        <v>7.85148859024048</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.25702905654907</v>
+        <v>7.25702953338623</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1572" t="n">
-        <v>6.82469654083252</v>
+        <v>6.82469606399536</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.08718490600586</v>
+        <v>7.08718538284302</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>7.10648488998413</v>
+        <v>7.10648536682129</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1577" t="n">
-        <v>7.26474952697754</v>
+        <v>7.2647500038147</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.43459606170654</v>
+        <v>7.43459510803223</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.32265090942383</v>
+        <v>7.32265186309814</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>7.30335092544556</v>
+        <v>7.30335140228271</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.48863744735718</v>
+        <v>7.48863649368286</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1585" t="n">
-        <v>7.43459606170654</v>
+        <v>7.43459510803223</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.53881978988647</v>
+        <v>7.53881883621216</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G1594" t="n">
-        <v>7.23000812530518</v>
+        <v>7.23000860214233</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1595" t="n">
-        <v>7.15280675888062</v>
+        <v>7.15280628204346</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.36511421203613</v>
+        <v>7.36511278152466</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.39213466644287</v>
+        <v>7.39213371276855</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.30721187591553</v>
+        <v>7.30721092224121</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1600" t="n">
-        <v>7.26474952697754</v>
+        <v>7.2647500038147</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.58514070510864</v>
+        <v>7.58513975143433</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1606" t="n">
-        <v>6.86216259002686</v>
+        <v>6.8621621131897</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>8.71500015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.11949348449707</v>
+        <v>7.11949396133423</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1613" t="n">
-        <v>6.86216259002686</v>
+        <v>6.8621621131897</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>8.25</v>
       </c>
       <c r="G1619" t="n">
-        <v>6.73962354660034</v>
+        <v>6.7396240234375</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1621" t="n">
-        <v>6.82131671905518</v>
+        <v>6.82131719589233</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1626" t="n">
-        <v>6.08199977874756</v>
+        <v>6.08200025558472</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1627" t="n">
-        <v>6.20045471191406</v>
+        <v>6.2004542350769</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G1630" t="n">
-        <v>6.62933921813965</v>
+        <v>6.62933874130249</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1634" t="n">
-        <v>6.43736171722412</v>
+        <v>6.43736219406128</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1635" t="n">
-        <v>6.63342380523682</v>
+        <v>6.63342332839966</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1637" t="n">
-        <v>6.52722311019897</v>
+        <v>6.52722358703613</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1638" t="n">
-        <v>6.3229923248291</v>
+        <v>6.32299280166626</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1639" t="n">
-        <v>6.00439214706421</v>
+        <v>6.00439262390137</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1640" t="n">
-        <v>6.00847673416138</v>
+        <v>6.00847721099854</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1643" t="n">
-        <v>6.00847673416138</v>
+        <v>6.00847721099854</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1644" t="n">
-        <v>6.08199977874756</v>
+        <v>6.08200025558472</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1647" t="n">
-        <v>5.99622297286987</v>
+        <v>5.99622344970703</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1651" t="n">
-        <v>5.9798846244812</v>
+        <v>5.97988414764404</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G1657" t="n">
-        <v>5.49381446838379</v>
+        <v>5.49381494522095</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1661" t="n">
-        <v>5.72663831710815</v>
+        <v>5.726637840271</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.65311527252197</v>
+        <v>5.65311479568481</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.57959175109863</v>
+        <v>5.57959222793579</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.73072290420532</v>
+        <v>5.73072242736816</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.81649971008301</v>
+        <v>5.81649923324585</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1682" t="n">
-        <v>5.72663831710815</v>
+        <v>5.726637840271</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1685" t="n">
-        <v>5.99622297286987</v>
+        <v>5.99622344970703</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.90971422195435</v>
+        <v>4.90971374511719</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G1701" t="n">
-        <v>4.83210611343384</v>
+        <v>4.832106590271</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1702" t="n">
-        <v>4.94239091873169</v>
+        <v>4.94239139556885</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1703" t="n">
-        <v>5.07309913635254</v>
+        <v>5.07309865951538</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1709" t="n">
-        <v>4.89337539672852</v>
+        <v>4.89337491989136</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.9464750289917</v>
+        <v>4.94647550582886</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.90562963485718</v>
+        <v>4.90562915802002</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G1715" t="n">
-        <v>4.90562963485718</v>
+        <v>4.90562915802002</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G1717" t="n">
-        <v>4.90562963485718</v>
+        <v>4.90562915802002</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.26099109649658</v>
+        <v>5.26099157333374</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.13845300674438</v>
+        <v>5.13845252990723</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G1723" t="n">
-        <v>4.84844493865967</v>
+        <v>4.84844446182251</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>5.1670446395874</v>
+        <v>5.16704511642456</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.24873733520508</v>
+        <v>5.24873781204224</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.45705318450928</v>
+        <v>5.45705270767212</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.64086151123047</v>
+        <v>5.64086103439331</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1740" t="n">
-        <v>5.48972988128662</v>
+        <v>5.48973035812378</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G1742" t="n">
-        <v>5.48156118392944</v>
+        <v>5.48156070709229</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>5.84917640686035</v>
+        <v>5.84917688369751</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G1746" t="n">
-        <v>5.79607677459717</v>
+        <v>5.79607629776001</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1747" t="n">
-        <v>5.89819240570068</v>
+        <v>5.89819192886353</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1752" t="n">
-        <v>5.81649971008301</v>
+        <v>5.81649923324585</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G1753" t="n">
-        <v>5.91044569015503</v>
+        <v>5.91044616699219</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G1755" t="n">
-        <v>5.81241512298584</v>
+        <v>5.81241464614868</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G1760" t="n">
-        <v>5.73889255523682</v>
+        <v>5.73889207839966</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1764" t="n">
-        <v>5.72663831710815</v>
+        <v>5.726637840271</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1769" t="n">
-        <v>5.50606822967529</v>
+        <v>5.50606870651245</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1776" t="n">
-        <v>5.48972988128662</v>
+        <v>5.48973035812378</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1778" t="n">
-        <v>5.50606822967529</v>
+        <v>5.50606870651245</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1781" t="n">
-        <v>5.57959175109863</v>
+        <v>5.57959222793579</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1787" t="n">
-        <v>5.69396066665649</v>
+        <v>5.69396114349365</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1790" t="n">
-        <v>5.99213838577271</v>
+        <v>5.99213886260986</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G1794" t="n">
-        <v>6.04932355880737</v>
+        <v>6.04932308197021</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>5.95537710189819</v>
+        <v>5.95537662506104</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1798" t="n">
-        <v>6.07791519165039</v>
+        <v>6.07791566848755</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1802" t="n">
-        <v>5.95537710189819</v>
+        <v>5.95537662506104</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1807" t="n">
-        <v>6.08199977874756</v>
+        <v>6.08200025558472</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1812" t="n">
-        <v>6.00847673416138</v>
+        <v>6.00847721099854</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G1816" t="n">
-        <v>6.11467742919922</v>
+        <v>6.11467695236206</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>6.04523897171021</v>
+        <v>6.04523849487305</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1822" t="n">
-        <v>5.48972988128662</v>
+        <v>5.48973035812378</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1825" t="n">
-        <v>5.9145302772522</v>
+        <v>5.91453075408936</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G1826" t="n">
-        <v>5.89002323150635</v>
+        <v>5.89002275466919</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1827" t="n">
-        <v>5.97171545028687</v>
+        <v>5.97171497344971</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>7.25</v>
       </c>
       <c r="G1829" t="n">
-        <v>5.92269945144653</v>
+        <v>5.92269992828369</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1832" t="n">
-        <v>6.18411588668823</v>
+        <v>6.18411540985107</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>8.25</v>
       </c>
       <c r="G1836" t="n">
-        <v>6.73962354660034</v>
+        <v>6.7396240234375</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G1837" t="n">
-        <v>6.79272365570068</v>
+        <v>6.79272317886353</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.1235785484314</v>
+        <v>7.12357807159424</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.20118522644043</v>
+        <v>7.20118570327759</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.30330085754395</v>
+        <v>7.3033013343811</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.5320405960083</v>
+        <v>7.53204154968262</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.43401050567627</v>
+        <v>7.43400955200195</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1853" t="n">
-        <v>7.25428676605225</v>
+        <v>7.25428581237793</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1854" t="n">
-        <v>7.19710206985474</v>
+        <v>7.19710159301758</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1855" t="n">
-        <v>7.22160911560059</v>
+        <v>7.22160959243774</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1856" t="n">
-        <v>7.22160911560059</v>
+        <v>7.22160959243774</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G1857" t="n">
-        <v>7.20118522644043</v>
+        <v>7.20118570327759</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>8.10000038146973</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>125107</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>8.25500011444092</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>7.94000005722046</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>7.99499988555908</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>8.1850004196167</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>8.1850004196167</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.44732332229614</v>
+        <v>5.4473237991333</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G3" t="n">
-        <v>5.55361270904541</v>
+        <v>5.55361318588257</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G4" t="n">
-        <v>5.38089323043823</v>
+        <v>5.38089370727539</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>5.29453277587891</v>
+        <v>5.29453325271606</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>5.33106899261475</v>
+        <v>5.3310694694519</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>4.94244956970215</v>
+        <v>4.94245004653931</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>4.84612560272217</v>
+        <v>4.84612512588501</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>4.82951736450195</v>
+        <v>4.82951784133911</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>4.82951736450195</v>
+        <v>4.82951784133911</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G19" t="n">
-        <v>4.87601947784424</v>
+        <v>4.87601852416992</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>4.97234392166138</v>
+        <v>4.97234344482422</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>4.94909286499023</v>
+        <v>4.94909238815308</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.59368801116943</v>
+        <v>4.59368848800659</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>4.4575047492981</v>
+        <v>4.45750570297241</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>4.61029624938965</v>
+        <v>4.61029577255249</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.75</v>
       </c>
       <c r="G30" t="n">
-        <v>4.48407793045044</v>
+        <v>4.48407745361328</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>4.70662117004395</v>
+        <v>4.70662021636963</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>7.375</v>
       </c>
       <c r="G34" t="n">
-        <v>4.89927005767822</v>
+        <v>4.89927053451538</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G36" t="n">
-        <v>5.02881097793579</v>
+        <v>5.02881050109863</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.75</v>
       </c>
       <c r="G39" t="n">
-        <v>5.14838552474976</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G40" t="n">
-        <v>5.24138784408569</v>
+        <v>5.24138832092285</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>5.31446170806885</v>
+        <v>5.31446266174316</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>5.51375389099121</v>
+        <v>5.51375532150269</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G43" t="n">
-        <v>5.69311714172363</v>
+        <v>5.69311761856079</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G47" t="n">
-        <v>5.68315315246582</v>
+        <v>5.68315362930298</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G51" t="n">
-        <v>5.387535572052</v>
+        <v>5.38753604888916</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G52" t="n">
-        <v>5.50378942489624</v>
+        <v>5.5037899017334</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>5.45396661758423</v>
+        <v>5.45396709442139</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>5.44732332229614</v>
+        <v>5.4473237991333</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.44732332229614</v>
+        <v>5.4473237991333</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>5.41410827636719</v>
+        <v>5.41410779953003</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>5.31446170806885</v>
+        <v>5.31446266174316</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>5.18160104751587</v>
+        <v>5.18160057067871</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>5.14174222946167</v>
+        <v>5.14174270629883</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G62" t="n">
-        <v>5.24138784408569</v>
+        <v>5.24138832092285</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>5.27460289001465</v>
+        <v>5.27460384368896</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.75</v>
       </c>
       <c r="G64" t="n">
-        <v>5.14838552474976</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.26796054840088</v>
+        <v>5.26796102523804</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.5</v>
       </c>
       <c r="G66" t="n">
-        <v>4.98230886459351</v>
+        <v>4.98230838775635</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>5.0753116607666</v>
+        <v>5.07531070709229</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.75</v>
       </c>
       <c r="G70" t="n">
-        <v>5.14838552474976</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>5.08859777450562</v>
+        <v>5.08859729766846</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>5.27460289001465</v>
+        <v>5.27460384368896</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G73" t="n">
-        <v>5.28124618530273</v>
+        <v>5.28124713897705</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G75" t="n">
-        <v>5.0354528427124</v>
+        <v>5.03545331954956</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>5.08195495605469</v>
+        <v>5.08195447921753</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.11517000198364</v>
+        <v>5.11516952514648</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>5.06202507019043</v>
+        <v>5.06202554702759</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G80" t="n">
-        <v>4.98895168304443</v>
+        <v>4.98895120620728</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>4.95905733108521</v>
+        <v>4.95905780792236</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.20152997970581</v>
+        <v>5.20153045654297</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>5.11184883117676</v>
+        <v>5.1118483543396</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>5.06202507019043</v>
+        <v>5.06202554702759</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.08195495605469</v>
+        <v>5.08195447921753</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.07199001312256</v>
+        <v>5.07199048995972</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G90" t="n">
-        <v>5.74733352661133</v>
+        <v>5.74733304977417</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>5.52393817901611</v>
+        <v>5.52393770217896</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>4.66759300231934</v>
+        <v>4.66759252548218</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G97" t="n">
-        <v>4.66420793533325</v>
+        <v>4.66420745849609</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>4.58297300338745</v>
+        <v>4.58297395706177</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.5</v>
       </c>
       <c r="G103" t="n">
-        <v>4.40019655227661</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G104" t="n">
-        <v>4.30542325973511</v>
+        <v>4.30542278289795</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.44758272171021</v>
+        <v>4.44758319854736</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G106" t="n">
-        <v>4.49496984481812</v>
+        <v>4.49496936798096</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>4.34942436218262</v>
+        <v>4.34942483901978</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>4.29865264892578</v>
+        <v>4.29865312576294</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.25</v>
       </c>
       <c r="G110" t="n">
-        <v>4.23095750808716</v>
+        <v>4.23095798492432</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>4.24788188934326</v>
+        <v>4.2478814125061</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G112" t="n">
-        <v>4.15649271011353</v>
+        <v>4.15649318695068</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.02448749542236</v>
+        <v>4.02448701858521</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G116" t="n">
-        <v>3.87217283248901</v>
+        <v>3.87217235565186</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>3.865403175354</v>
+        <v>3.86540269851685</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>4.01094770431519</v>
+        <v>4.01094818115234</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.93648266792297</v>
+        <v>3.93648314476013</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.96356177330017</v>
+        <v>3.96356129646301</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94663715362549</v>
+        <v>3.94663763046265</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>3.99402379989624</v>
+        <v>3.99402475357056</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>3.76385998725891</v>
+        <v>3.76386022567749</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32925629615784</v>
+        <v>3.32925605773926</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.40169048309326</v>
+        <v>3.4016900062561</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>3.47615456581116</v>
+        <v>3.47615504264832</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>3.45246148109436</v>
+        <v>3.45246195793152</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>3.3983051776886</v>
+        <v>3.39830541610718</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>3.15730977058411</v>
+        <v>3.15731000900269</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G134" t="n">
-        <v>3.29540848731995</v>
+        <v>3.29540872573853</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.58785247802734</v>
+        <v>3.58785176277161</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G137" t="n">
-        <v>3.47615456581116</v>
+        <v>3.47615504264832</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49984836578369</v>
+        <v>3.49984812736511</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57092905044556</v>
+        <v>3.57092881202698</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G141" t="n">
-        <v>3.51677203178406</v>
+        <v>3.51677227020264</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G142" t="n">
-        <v>3.57431316375732</v>
+        <v>3.57431292533875</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G144" t="n">
-        <v>3.5946216583252</v>
+        <v>3.59462213516235</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G145" t="n">
-        <v>3.63185405731201</v>
+        <v>3.63185358047485</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.61154556274414</v>
+        <v>3.61154580116272</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.79093766212463</v>
+        <v>3.79093790054321</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>3.70293378829956</v>
+        <v>3.7029345035553</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>3.78078365325928</v>
+        <v>3.78078389167786</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G150" t="n">
-        <v>3.71308898925781</v>
+        <v>3.71308851242065</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G152" t="n">
-        <v>3.56077480316162</v>
+        <v>3.56077408790588</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>3.61492991447449</v>
+        <v>3.6149308681488</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G155" t="n">
-        <v>3.64877867698669</v>
+        <v>3.64877796173096</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>3.79093766212463</v>
+        <v>3.79093790054321</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>3.79093766212463</v>
+        <v>3.79093790054321</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>3.83832406997681</v>
+        <v>3.83832454681396</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82140040397644</v>
+        <v>3.8214008808136</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G160" t="n">
-        <v>3.81801652908325</v>
+        <v>3.81801605224609</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G161" t="n">
-        <v>3.78416872024536</v>
+        <v>3.78416848182678</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>3.98725533485413</v>
+        <v>3.98725509643555</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G168" t="n">
-        <v>4.13618469238281</v>
+        <v>4.13618421554565</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G170" t="n">
-        <v>4.02448749542236</v>
+        <v>4.02448701858521</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>3.99402379989624</v>
+        <v>3.99402475357056</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G172" t="n">
-        <v>4.02787208557129</v>
+        <v>4.02787160873413</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>3.96356177330017</v>
+        <v>3.96356129646301</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>3.93986892700195</v>
+        <v>3.93986749649048</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.98725533485413</v>
+        <v>3.98725509643555</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.02787208557129</v>
+        <v>4.02787160873413</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G181" t="n">
-        <v>3.96694660186768</v>
+        <v>3.96694612503052</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G183" t="n">
-        <v>3.44907665252686</v>
+        <v>3.44907689094543</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5</v>
       </c>
       <c r="G184" t="n">
-        <v>3.38476634025574</v>
+        <v>3.38476610183716</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G187" t="n">
-        <v>3.28322291374207</v>
+        <v>3.28322339057922</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G188" t="n">
-        <v>3.3306097984314</v>
+        <v>3.33061027526855</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>3.38815069198608</v>
+        <v>3.38815116882324</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>3.30353188514709</v>
+        <v>3.30353164672852</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G191" t="n">
-        <v>3.3427951335907</v>
+        <v>3.34279489517212</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G192" t="n">
-        <v>3.37122702598572</v>
+        <v>3.3712272644043</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G193" t="n">
-        <v>3.34956479072571</v>
+        <v>3.34956455230713</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>3.49984836578369</v>
+        <v>3.49984812736511</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>4.11587572097778</v>
+        <v>4.11587524414062</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>4.24449634552002</v>
+        <v>4.24449682235718</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>4.44081401824951</v>
+        <v>4.4408130645752</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>4.44081401824951</v>
+        <v>4.4408130645752</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>4.44081401824951</v>
+        <v>4.4408130645752</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>4.58297300338745</v>
+        <v>4.58297395706177</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.75</v>
       </c>
       <c r="G214" t="n">
-        <v>4.56943464279175</v>
+        <v>4.56943416595459</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G217" t="n">
-        <v>4.37988758087158</v>
+        <v>4.37988710403442</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>4.30203771591187</v>
+        <v>4.30203819274902</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>4.38665723800659</v>
+        <v>4.38665676116943</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G221" t="n">
-        <v>4.4069652557373</v>
+        <v>4.40696573257446</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.5</v>
       </c>
       <c r="G223" t="n">
-        <v>4.40019655227661</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="n">
-        <v>4.40019655227661</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.41035079956055</v>
+        <v>4.41035032272339</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G233" t="n">
-        <v>4.43742847442627</v>
+        <v>4.43742895126343</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G237" t="n">
-        <v>4.24449634552002</v>
+        <v>4.24449682235718</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G239" t="n">
-        <v>4.4171199798584</v>
+        <v>4.41712045669556</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>4.49835443496704</v>
+        <v>4.49835395812988</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.51866340637207</v>
+        <v>4.51866292953491</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G248" t="n">
-        <v>4.5355863571167</v>
+        <v>4.53558731079102</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G252" t="n">
-        <v>4.71836423873901</v>
+        <v>4.71836376190186</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G255" t="n">
-        <v>4.71836423873901</v>
+        <v>4.71836376190186</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G262" t="n">
-        <v>4.76236629486084</v>
+        <v>4.76236581802368</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>4.86729335784912</v>
+        <v>4.86729431152344</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>7.125</v>
       </c>
       <c r="G271" t="n">
-        <v>4.82329225540161</v>
+        <v>4.82329177856445</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G273" t="n">
-        <v>4.72851800918579</v>
+        <v>4.72851896286011</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G275" t="n">
-        <v>4.82667589187622</v>
+        <v>4.82667684555054</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G276" t="n">
-        <v>4.80298376083374</v>
+        <v>4.80298328399658</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65066909790039</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.65743827819824</v>
+        <v>4.6574387550354</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>4.67097759246826</v>
+        <v>4.67097806930542</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>4.65066909790039</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>4.65066909790039</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G285" t="n">
-        <v>4.5998969078064</v>
+        <v>4.59989738464355</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G286" t="n">
-        <v>4.67097759246826</v>
+        <v>4.67097806930542</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>5.02299308776855</v>
+        <v>5.02299356460571</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G293" t="n">
-        <v>5.06699514389038</v>
+        <v>5.06699466705322</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G294" t="n">
-        <v>5.00268411636353</v>
+        <v>5.00268507003784</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G296" t="n">
-        <v>4.97560596466064</v>
+        <v>4.9756064414978</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G297" t="n">
-        <v>4.96883726119995</v>
+        <v>4.96883630752563</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>4.97560596466064</v>
+        <v>4.9756064414978</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93160486221313</v>
+        <v>4.93160438537598</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G300" t="n">
-        <v>5.05684089660645</v>
+        <v>5.05684041976929</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>5.06361103057861</v>
+        <v>5.06361055374146</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G303" t="n">
-        <v>5.0399169921875</v>
+        <v>5.03991651535034</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.02637815475464</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>5.02299308776855</v>
+        <v>5.02299356460571</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G306" t="n">
-        <v>5.08391904830933</v>
+        <v>5.08391857147217</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G309" t="n">
-        <v>5.00268411636353</v>
+        <v>5.00268507003784</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G310" t="n">
-        <v>5.06699514389038</v>
+        <v>5.06699466705322</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>5.27346611022949</v>
+        <v>5.27346563339233</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.24638795852661</v>
+        <v>5.24638748168945</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>5.29039001464844</v>
+        <v>5.29038953781128</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G315" t="n">
-        <v>5.23284912109375</v>
+        <v>5.23284864425659</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G316" t="n">
-        <v>5.37500810623169</v>
+        <v>5.37500858306885</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>5.3817777633667</v>
+        <v>5.38177824020386</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G318" t="n">
-        <v>5.3817777633667</v>
+        <v>5.38177824020386</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8</v>
       </c>
       <c r="G319" t="n">
-        <v>5.41562557220459</v>
+        <v>5.41562604904175</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>5.40208673477173</v>
+        <v>5.40208721160889</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>5.3817777633667</v>
+        <v>5.38177824020386</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G323" t="n">
-        <v>5.3276219367981</v>
+        <v>5.32762241363525</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>5.17869281768799</v>
+        <v>5.17869234085083</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>5.21592473983765</v>
+        <v>5.21592426300049</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>5.17869281768799</v>
+        <v>5.17869234085083</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>5.14484453201294</v>
+        <v>5.1448450088501</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.56500005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>5.12115144729614</v>
+        <v>5.12115097045898</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.83344650268555</v>
+        <v>4.83344602584839</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>4.97899150848389</v>
+        <v>4.97899198532104</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>4.95868301391602</v>
+        <v>4.95868253707886</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G337" t="n">
-        <v>5.17192316055298</v>
+        <v>5.17192268371582</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>5.11099767684937</v>
+        <v>5.11099720001221</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.09745788574219</v>
+        <v>5.09745836257935</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G340" t="n">
-        <v>5.08391904830933</v>
+        <v>5.08391857147217</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G341" t="n">
-        <v>5.09745788574219</v>
+        <v>5.09745836257935</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G344" t="n">
-        <v>5.09068775177002</v>
+        <v>5.09068918228149</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.23200082778931</v>
+        <v>5.23200130462646</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G346" t="n">
-        <v>5.3905463218689</v>
+        <v>5.39054679870605</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>5.15617513656616</v>
+        <v>5.156174659729</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G350" t="n">
-        <v>4.81840419769287</v>
+        <v>4.81840372085571</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>4.71500492095947</v>
+        <v>4.71500539779663</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>4.68053817749023</v>
+        <v>4.68053865432739</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G359" t="n">
-        <v>4.6184983253479</v>
+        <v>4.61849880218506</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>4.41170072555542</v>
+        <v>4.41170024871826</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G364" t="n">
-        <v>4.44616651535034</v>
+        <v>4.4461669921875</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.27383470535278</v>
+        <v>4.27383422851562</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>4.2393684387207</v>
+        <v>4.23936796188354</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G370" t="n">
-        <v>4.37378740310669</v>
+        <v>4.37378692626953</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.25</v>
       </c>
       <c r="G375" t="n">
-        <v>4.30830097198486</v>
+        <v>4.30830144882202</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G376" t="n">
-        <v>4.17732906341553</v>
+        <v>4.17732858657837</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>4.37378740310669</v>
+        <v>4.37378692626953</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.35655450820923</v>
+        <v>4.35655403137207</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>4.49786615371704</v>
+        <v>4.4978666305542</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>4.44961309432983</v>
+        <v>4.44961357116699</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>4.37723350524902</v>
+        <v>4.37723398208618</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>4.49441909790039</v>
+        <v>4.49441957473755</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>4.59781932830811</v>
+        <v>4.59781885147095</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>4.58403253555298</v>
+        <v>4.58403205871582</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.59781932830811</v>
+        <v>4.59781885147095</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>4.5219931602478</v>
+        <v>4.52199268341064</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>4.49786615371704</v>
+        <v>4.4978666305542</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>4.50475978851318</v>
+        <v>4.50475931167603</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.44616651535034</v>
+        <v>4.4461669921875</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G408" t="n">
-        <v>4.45995330810547</v>
+        <v>4.45995283126831</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>4.58403253555298</v>
+        <v>4.58403205871582</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.46339988708496</v>
+        <v>4.4633994102478</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G415" t="n">
-        <v>4.44616651535034</v>
+        <v>4.4461669921875</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G418" t="n">
-        <v>4.35655450820923</v>
+        <v>4.35655403137207</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G419" t="n">
-        <v>4.3427677154541</v>
+        <v>4.34276723861694</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>4.2393684387207</v>
+        <v>4.23936796188354</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>4.20490121841431</v>
+        <v>4.20490169525146</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G429" t="n">
-        <v>4.24626159667969</v>
+        <v>4.24626111984253</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>4.20490121841431</v>
+        <v>4.20490169525146</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G436" t="n">
-        <v>4.2324743270874</v>
+        <v>4.23247528076172</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>4.17732906341553</v>
+        <v>4.17732858657837</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>3.52935981750488</v>
+        <v>3.52936029434204</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G444" t="n">
-        <v>3.4425048828125</v>
+        <v>3.44250512123108</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G445" t="n">
-        <v>3.44526243209839</v>
+        <v>3.44526267051697</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>3.42596101760864</v>
+        <v>3.42596125602722</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.42596101760864</v>
+        <v>3.42596125602722</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G450" t="n">
-        <v>3.38046526908875</v>
+        <v>3.38046550750732</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G452" t="n">
-        <v>3.23984265327454</v>
+        <v>3.23984217643738</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G454" t="n">
-        <v>3.05372333526611</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>3.12954998016357</v>
+        <v>3.129549741745</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>3.06751036643982</v>
+        <v>3.06751012802124</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.40399980545044</v>
       </c>
       <c r="G458" t="n">
-        <v>3.03580093383789</v>
+        <v>3.03580117225647</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G459" t="n">
-        <v>2.9530816078186</v>
+        <v>2.95308184623718</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G460" t="n">
-        <v>2.93653798103333</v>
+        <v>2.9365382194519</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G461" t="n">
-        <v>2.95446014404297</v>
+        <v>2.95446038246155</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G462" t="n">
-        <v>2.86898422241211</v>
+        <v>2.86898398399353</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G466" t="n">
-        <v>2.98479104042053</v>
+        <v>2.98479056358337</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>2.86071181297302</v>
+        <v>2.8607120513916</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G470" t="n">
-        <v>2.8372745513916</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G471" t="n">
-        <v>2.86898422241211</v>
+        <v>2.86898398399353</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G474" t="n">
-        <v>3.07026791572571</v>
+        <v>3.07026743888855</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>2.94343090057373</v>
+        <v>2.94343113899231</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.86071181297302</v>
+        <v>2.8607120513916</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G480" t="n">
-        <v>2.61117506027222</v>
+        <v>2.6111752986908</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G481" t="n">
-        <v>2.70492386817932</v>
+        <v>2.70492362976074</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692525863647</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G484" t="n">
-        <v>2.85519742965698</v>
+        <v>2.8551971912384</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G485" t="n">
-        <v>2.85795474052429</v>
+        <v>2.85795450210571</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4</v>
       </c>
       <c r="G489" t="n">
-        <v>2.75731253623962</v>
+        <v>2.7573127746582</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4</v>
       </c>
       <c r="G490" t="n">
-        <v>2.75731253623962</v>
+        <v>2.7573127746582</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G491" t="n">
-        <v>2.8372745513916</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G492" t="n">
-        <v>2.78764343261719</v>
+        <v>2.78764319419861</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.25</v>
       </c>
       <c r="G497" t="n">
-        <v>2.92964482307434</v>
+        <v>2.92964506149292</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G498" t="n">
-        <v>2.9530816078186</v>
+        <v>2.95308184623718</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.25</v>
       </c>
       <c r="G499" t="n">
-        <v>2.92964482307434</v>
+        <v>2.92964506149292</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G502" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210922241211</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G504" t="n">
-        <v>2.81935214996338</v>
+        <v>2.81935238838196</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G509" t="n">
-        <v>2.89931440353394</v>
+        <v>2.89931416511536</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G511" t="n">
-        <v>2.8372745513916</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>2.9399847984314</v>
+        <v>2.93998456001282</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.07440376281738</v>
+        <v>3.07440328598022</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G516" t="n">
-        <v>3.22605562210083</v>
+        <v>3.22605586051941</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>3.1192102432251</v>
+        <v>3.11921000480652</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>3.05717039108276</v>
+        <v>3.05717062950134</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G521" t="n">
-        <v>3.17780303955078</v>
+        <v>3.1778028011322</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G522" t="n">
-        <v>3.16746282577515</v>
+        <v>3.16746306419373</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>3.07440376281738</v>
+        <v>3.07440328598022</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>3.08819055557251</v>
+        <v>3.08819007873535</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>3.13988971710205</v>
+        <v>3.13988995552063</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>3.09508323669434</v>
+        <v>3.09508371353149</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G529" t="n">
-        <v>3.09508323669434</v>
+        <v>3.09508371353149</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>3.14333605766296</v>
+        <v>3.14333653450012</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G532" t="n">
-        <v>3.05027723312378</v>
+        <v>3.05027747154236</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>3.02959728240967</v>
+        <v>3.02959704399109</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>3.03304386138916</v>
+        <v>3.03304409980774</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>2.98479104042053</v>
+        <v>2.98479056358337</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G538" t="n">
-        <v>2.91585826873779</v>
+        <v>2.91585803031921</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>2.81245899200439</v>
+        <v>2.81245875358582</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.78488564491272</v>
+        <v>2.7848858833313</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G541" t="n">
-        <v>2.78143882751465</v>
+        <v>2.78143930435181</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>3.07440376281738</v>
+        <v>3.07440328598022</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>3.08819055557251</v>
+        <v>3.08819007873535</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06406402587891</v>
+        <v>3.06406426429749</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>3.04338407516479</v>
+        <v>3.04338359832764</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G549" t="n">
-        <v>3.0261504650116</v>
+        <v>3.02615070343018</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G550" t="n">
-        <v>3.05372333526611</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G551" t="n">
-        <v>3.01236367225647</v>
+        <v>3.01236414909363</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G552" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G553" t="n">
-        <v>3.00547099113464</v>
+        <v>3.00547075271606</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>2.96066474914551</v>
+        <v>2.96066451072693</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>2.90551829338074</v>
+        <v>2.90551853179932</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G557" t="n">
-        <v>3.05372333526611</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>3.07440376281738</v>
+        <v>3.07440328598022</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>3.06061720848083</v>
+        <v>3.06061697006226</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.88483810424805</v>
+        <v>2.88483834266663</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G570" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692525863647</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>2.87449836730957</v>
+        <v>2.87449812889099</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>2.96066474914551</v>
+        <v>2.96066451072693</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>3.06751036643982</v>
+        <v>3.06751012802124</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>3.07095670700073</v>
+        <v>3.07095718383789</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G592" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G594" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03304386138916</v>
+        <v>3.03304409980774</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.375</v>
       </c>
       <c r="G599" t="n">
-        <v>3.0158109664917</v>
+        <v>3.01581072807312</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G602" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G605" t="n">
-        <v>2.9480254650116</v>
+        <v>2.94802522659302</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>2.9551374912262</v>
+        <v>2.95513772964478</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.9195761680603</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.87690305709839</v>
+        <v>2.87690329551697</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>2.62086224555969</v>
+        <v>2.62086200714111</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>2.65286684036255</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G618" t="n">
-        <v>2.65286684036255</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G619" t="n">
-        <v>2.57107639312744</v>
+        <v>2.57107615470886</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.58530116081238</v>
+        <v>2.5853009223938</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.625</v>
       </c>
       <c r="G621" t="n">
-        <v>2.57818865776062</v>
+        <v>2.5781888961792</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57463264465332</v>
+        <v>2.57463240623474</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.58530116081238</v>
+        <v>2.5853009223938</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.61019396781921</v>
+        <v>2.61019349098206</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.75</v>
       </c>
       <c r="G625" t="n">
-        <v>2.66709208488464</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G626" t="n">
-        <v>2.70265293121338</v>
+        <v>2.7026526927948</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G627" t="n">
-        <v>2.67776036262512</v>
+        <v>2.67776012420654</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>2.6990966796875</v>
+        <v>2.69909691810608</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G636" t="n">
-        <v>2.56752038002014</v>
+        <v>2.56752014160156</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>2.6990966796875</v>
+        <v>2.69909691810608</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.71687769889832</v>
+        <v>2.71687722206116</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G641" t="n">
-        <v>2.74177026748657</v>
+        <v>2.74177050590515</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G642" t="n">
-        <v>2.79155564308167</v>
+        <v>2.79155588150024</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G643" t="n">
-        <v>2.86267876625061</v>
+        <v>2.86267852783203</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>2.9195761680603</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4</v>
       </c>
       <c r="G645" t="n">
-        <v>2.84489798545837</v>
+        <v>2.84489774703979</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3.875</v>
       </c>
       <c r="G649" t="n">
-        <v>2.75599503517151</v>
+        <v>2.75599455833435</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.75</v>
       </c>
       <c r="G655" t="n">
-        <v>2.66709208488464</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G660" t="n">
-        <v>2.70620918273926</v>
+        <v>2.70620942115784</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>2.63864278793335</v>
+        <v>2.63864302635193</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.75</v>
       </c>
       <c r="G664" t="n">
-        <v>2.66709208488464</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.63864278793335</v>
+        <v>2.63864302635193</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G670" t="n">
-        <v>2.60663747787476</v>
+        <v>2.60663771629333</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.875</v>
       </c>
       <c r="G673" t="n">
-        <v>2.75599503517151</v>
+        <v>2.75599455833435</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>2.82711696624756</v>
+        <v>2.82711720466614</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G675" t="n">
-        <v>2.77377581596375</v>
+        <v>2.77377557754517</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>2.77377581596375</v>
+        <v>2.77377557754517</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G677" t="n">
-        <v>2.74532628059387</v>
+        <v>2.74532651901245</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.625</v>
       </c>
       <c r="G681" t="n">
-        <v>2.57818865776062</v>
+        <v>2.5781888961792</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>2.65997934341431</v>
+        <v>2.65997958183289</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65997934341431</v>
+        <v>2.65997958183289</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>2.61019396781921</v>
+        <v>2.61019349098206</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>2.54973959922791</v>
+        <v>2.54973983764648</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>2.60663747787476</v>
+        <v>2.60663771629333</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.65286684036255</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021884918213</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G697" t="n">
-        <v>2.74177026748657</v>
+        <v>2.74177050590515</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G704" t="n">
-        <v>2.78088736534119</v>
+        <v>2.78088784217834</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>2.6990966796875</v>
+        <v>2.69909691810608</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G707" t="n">
-        <v>2.63864278793335</v>
+        <v>2.63864302635193</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>2.61730599403381</v>
+        <v>2.61730623245239</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G709" t="n">
-        <v>2.55685210227966</v>
+        <v>2.55685186386108</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50350999832153</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G711" t="n">
-        <v>2.57107639312744</v>
+        <v>2.57107615470886</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G714" t="n">
-        <v>2.52840352058411</v>
+        <v>2.52840328216553</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G715" t="n">
-        <v>2.47861742973328</v>
+        <v>2.4786171913147</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>2.54973959922791</v>
+        <v>2.54973983764648</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G719" t="n">
-        <v>2.56752038002014</v>
+        <v>2.56752014160156</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61730599403381</v>
+        <v>2.61730623245239</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G722" t="n">
-        <v>2.70620918273926</v>
+        <v>2.70620942115784</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G725" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021884918213</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.90179586410522</v>
+        <v>2.90179562568665</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G729" t="n">
-        <v>2.9124641418457</v>
+        <v>2.91246390342712</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G730" t="n">
-        <v>2.9195761680603</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>2.9195761680603</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G732" t="n">
-        <v>2.89468383789062</v>
+        <v>2.89468359947205</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G735" t="n">
-        <v>2.91602039337158</v>
+        <v>2.916020154953</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.75</v>
       </c>
       <c r="G737" t="n">
-        <v>2.66709208488464</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G738" t="n">
-        <v>2.61374998092651</v>
+        <v>2.61374974250793</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.625</v>
       </c>
       <c r="G741" t="n">
-        <v>2.57818865776062</v>
+        <v>2.5781888961792</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.75</v>
       </c>
       <c r="G742" t="n">
-        <v>2.66709208488464</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G743" t="n">
-        <v>2.70265293121338</v>
+        <v>2.7026526927948</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G744" t="n">
-        <v>2.65997934341431</v>
+        <v>2.65997958183289</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G748" t="n">
-        <v>2.61730599403381</v>
+        <v>2.61730623245239</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G750" t="n">
-        <v>2.56752038002014</v>
+        <v>2.56752014160156</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57107639312744</v>
+        <v>2.57107615470886</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.62086224555969</v>
+        <v>2.62086200714111</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G755" t="n">
-        <v>2.63864278793335</v>
+        <v>2.63864302635193</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G756" t="n">
-        <v>2.61374998092651</v>
+        <v>2.61374974250793</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60663747787476</v>
+        <v>2.60663771629333</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>2.61019396781921</v>
+        <v>2.61019349098206</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>2.56040787696838</v>
+        <v>2.56040811538696</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>2.51773476600647</v>
+        <v>2.51773452758789</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G764" t="n">
-        <v>2.62797427177429</v>
+        <v>2.62797451019287</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.62441825866699</v>
+        <v>2.62441802024841</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.65286684036255</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G768" t="n">
-        <v>2.67420387268066</v>
+        <v>2.67420411109924</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>2.79511213302612</v>
+        <v>2.7951123714447</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G772" t="n">
-        <v>2.73110175132751</v>
+        <v>2.73110198974609</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G773" t="n">
-        <v>2.74532628059387</v>
+        <v>2.74532651901245</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71687769889832</v>
+        <v>2.71687722206116</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>2.63864278793335</v>
+        <v>2.63864302635193</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G781" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.77377581596375</v>
+        <v>2.77377557754517</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G785" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.75</v>
       </c>
       <c r="G788" t="n">
-        <v>2.66709208488464</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G789" t="n">
-        <v>2.67420387268066</v>
+        <v>2.67420411109924</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G791" t="n">
-        <v>2.56396412849426</v>
+        <v>2.56396389007568</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G800" t="n">
-        <v>2.51773476600647</v>
+        <v>2.51773452758789</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G803" t="n">
-        <v>2.52840352058411</v>
+        <v>2.52840328216553</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>2.49284195899963</v>
+        <v>2.49284172058105</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>2.50350999832153</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.375</v>
       </c>
       <c r="G810" t="n">
-        <v>2.40038275718689</v>
+        <v>2.40038251876831</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>2.3719334602356</v>
+        <v>2.37193369865417</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>2.3754894733429</v>
+        <v>2.37548971176147</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G813" t="n">
-        <v>2.3754894733429</v>
+        <v>2.37548971176147</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G816" t="n">
-        <v>2.29369878768921</v>
+        <v>2.29369902610779</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G817" t="n">
-        <v>2.27236223220825</v>
+        <v>2.27236199378967</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>2.27236223220825</v>
+        <v>2.27236199378967</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>2.29369878768921</v>
+        <v>2.29369902610779</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>2.26880598068237</v>
+        <v>2.26880621910095</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>2.35415315628052</v>
+        <v>2.35415267944336</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>2.3719334602356</v>
+        <v>2.37193369865417</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G831" t="n">
-        <v>2.35770916938782</v>
+        <v>2.35770893096924</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>2.3683774471283</v>
+        <v>2.36837720870972</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G833" t="n">
-        <v>2.30792331695557</v>
+        <v>2.30792307853699</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G834" t="n">
-        <v>2.30081129074097</v>
+        <v>2.30081105232239</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>2.29369878768921</v>
+        <v>2.29369902610779</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G837" t="n">
-        <v>2.36126518249512</v>
+        <v>2.3612654209137</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G838" t="n">
-        <v>2.3754894733429</v>
+        <v>2.37548971176147</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.41105103492737</v>
+        <v>2.41105079650879</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G844" t="n">
-        <v>2.53907155990601</v>
+        <v>2.53907132148743</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G845" t="n">
-        <v>2.5817449092865</v>
+        <v>2.58174514770508</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>2.58530116081238</v>
+        <v>2.5853009223938</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G848" t="n">
-        <v>2.47861742973328</v>
+        <v>2.4786171913147</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42883133888245</v>
+        <v>2.42883157730103</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.375</v>
       </c>
       <c r="G850" t="n">
-        <v>2.40038275718689</v>
+        <v>2.40038251876831</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G852" t="n">
-        <v>2.35415315628052</v>
+        <v>2.35415267944336</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.36126518249512</v>
+        <v>2.3612654209137</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>2.43540215492249</v>
+        <v>2.43540239334106</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>2.45764350891113</v>
+        <v>2.45764327049255</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.37238574028015</v>
+        <v>2.37238597869873</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G863" t="n">
-        <v>2.23893880844116</v>
+        <v>2.23893904685974</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>2.23893880844116</v>
+        <v>2.23893904685974</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G867" t="n">
-        <v>2.21299123764038</v>
+        <v>2.2129909992218</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>2.06842374801636</v>
+        <v>2.06842350959778</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G877" t="n">
-        <v>2.20187044143677</v>
+        <v>2.20187067985535</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>2.875</v>
       </c>
       <c r="G880" t="n">
-        <v>2.13144016265869</v>
+        <v>2.13144040107727</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G882" t="n">
-        <v>2.11661314964294</v>
+        <v>2.11661291122437</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G883" t="n">
-        <v>2.1091992855072</v>
+        <v>2.10919904708862</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G885" t="n">
-        <v>1.99799370765686</v>
+        <v>1.99799346923828</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>2.37609267234802</v>
+        <v>2.37609243392944</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G889" t="n">
-        <v>2.27600765228271</v>
+        <v>2.27600789070129</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.2834210395813</v>
+        <v>2.28342127799988</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>2.23893880844116</v>
+        <v>2.23893904685974</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>2.23152542114258</v>
+        <v>2.23152565956116</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G895" t="n">
-        <v>2.23893880844116</v>
+        <v>2.23893904685974</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G898" t="n">
-        <v>2.27230048179626</v>
+        <v>2.27230072021484</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G901" t="n">
-        <v>2.2834210395813</v>
+        <v>2.28342127799988</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G902" t="n">
-        <v>2.27600765228271</v>
+        <v>2.27600789070129</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G904" t="n">
-        <v>2.26118016242981</v>
+        <v>2.26117992401123</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.28712821006775</v>
+        <v>2.28712844848633</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G906" t="n">
-        <v>2.26118016242981</v>
+        <v>2.26117992401123</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>2.2834210395813</v>
+        <v>2.28342127799988</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>2.26859378814697</v>
+        <v>2.26859402656555</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G910" t="n">
-        <v>2.23523211479187</v>
+        <v>2.23523259162903</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G911" t="n">
-        <v>2.25005960464478</v>
+        <v>2.25005984306335</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G912" t="n">
-        <v>2.27600765228271</v>
+        <v>2.27600789070129</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G914" t="n">
-        <v>2.18704295158386</v>
+        <v>2.18704319000244</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G915" t="n">
-        <v>2.17962956428528</v>
+        <v>2.17962980270386</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G916" t="n">
-        <v>2.17962956428528</v>
+        <v>2.17962980270386</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G927" t="n">
-        <v>2.1091992855072</v>
+        <v>2.10919904708862</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G928" t="n">
-        <v>2.09807848930359</v>
+        <v>2.09807872772217</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>2.16850900650024</v>
+        <v>2.16850876808167</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G939" t="n">
-        <v>2.52807354927063</v>
+        <v>2.52807331085205</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G940" t="n">
-        <v>2.55772829055786</v>
+        <v>2.55772852897644</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>2.63927936553955</v>
+        <v>2.63927912712097</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G943" t="n">
-        <v>2.78755331039429</v>
+        <v>2.78755354881287</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G949" t="n">
-        <v>2.73565745353699</v>
+        <v>2.73565721511841</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G950" t="n">
-        <v>2.73565745353699</v>
+        <v>2.73565721511841</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>2.73565745353699</v>
+        <v>2.73565721511841</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G955" t="n">
-        <v>2.67264103889465</v>
+        <v>2.67264080047607</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G956" t="n">
-        <v>2.68376159667969</v>
+        <v>2.68376135826111</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>2.71712279319763</v>
+        <v>2.71712303161621</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G961" t="n">
-        <v>2.76160502433777</v>
+        <v>2.76160526275635</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G963" t="n">
-        <v>2.76531195640564</v>
+        <v>2.76531219482422</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>2.76531195640564</v>
+        <v>2.76531219482422</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.68005466461182</v>
+        <v>2.68005442619324</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>2.75048470497131</v>
+        <v>2.75048494338989</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>2.80238032341003</v>
+        <v>2.80238080024719</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G976" t="n">
-        <v>2.76160502433777</v>
+        <v>2.76160526275635</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G978" t="n">
-        <v>2.86169004440308</v>
+        <v>2.86169028282166</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>2.89875864982605</v>
+        <v>2.89875912666321</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G980" t="n">
-        <v>2.90987920761108</v>
+        <v>2.90987944602966</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G983" t="n">
-        <v>2.95806837081909</v>
+        <v>2.95806860923767</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.875</v>
       </c>
       <c r="G986" t="n">
-        <v>2.87281107902527</v>
+        <v>2.87281084060669</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G990" t="n">
-        <v>2.92841386795044</v>
+        <v>2.92841362953186</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G991" t="n">
-        <v>2.97660279273987</v>
+        <v>2.97660255432129</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G994" t="n">
-        <v>3.3065128326416</v>
+        <v>3.30651235580444</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>3.41771841049194</v>
+        <v>3.41771817207336</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.52892351150513</v>
+        <v>3.52892374992371</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.5993537902832</v>
+        <v>3.59935402870178</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.59564685821533</v>
+        <v>3.59564709663391</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.65866327285767</v>
+        <v>3.65866351127625</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.82547235488892</v>
+        <v>3.82547187805176</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.80323100090027</v>
+        <v>3.80323076248169</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.95891904830933</v>
+        <v>3.95891857147217</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.8847815990448</v>
+        <v>3.88478112220764</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.8847815990448</v>
+        <v>3.88478112220764</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.84771347045898</v>
+        <v>3.84771299362183</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.8328857421875</v>
+        <v>3.83288526535034</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.47332143783569</v>
+        <v>3.47332096099854</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.60306072235107</v>
+        <v>3.60306119918823</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.72909426689148</v>
+        <v>3.7290940284729</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.70685291290283</v>
+        <v>3.70685267448425</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.77357649803162</v>
+        <v>3.77357602119446</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.8328857421875</v>
+        <v>3.83288526535034</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.13684749603271</v>
+        <v>4.13684701919556</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.80323100090027</v>
+        <v>3.80323076248169</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.70685291290283</v>
+        <v>3.70685267448425</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.63271594047546</v>
+        <v>3.63271617889404</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.66607737541199</v>
+        <v>3.66607761383057</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.16565203666687</v>
+        <v>3.16565227508545</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.5132462978363</v>
+        <v>2.51324605941772</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.29083490371704</v>
+        <v>2.29083514213562</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.17962956428528</v>
+        <v>2.17962980270386</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.37238574028015</v>
+        <v>2.37238597869873</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.38721299171448</v>
+        <v>2.38721323013306</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.2834210395813</v>
+        <v>2.28342127799988</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.26118016242981</v>
+        <v>2.26117992401123</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.33531713485718</v>
+        <v>2.33531737327576</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.53548717498779</v>
+        <v>2.53548741340637</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.67264103889465</v>
+        <v>2.67264080047607</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.67264103889465</v>
+        <v>2.67264080047607</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.06927394866943</v>
+        <v>3.06927418708801</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.17306637763977</v>
+        <v>3.17306613922119</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.07668805122375</v>
+        <v>3.07668781280518</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.11375617980957</v>
+        <v>3.11375594139099</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.06927394866943</v>
+        <v>3.06927418708801</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.00255084037781</v>
+        <v>3.00255107879639</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.97289609909058</v>
+        <v>2.97289633750916</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.06927394866943</v>
+        <v>3.06927418708801</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.16194558143616</v>
+        <v>3.16194534301758</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.26944422721863</v>
+        <v>3.26944398880005</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.2916853427887</v>
+        <v>3.29168510437012</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.20642781257629</v>
+        <v>3.20642757415771</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.1767725944519</v>
+        <v>3.17677235603333</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.10634279251099</v>
+        <v>3.10634255409241</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.77643275260925</v>
+        <v>2.77643251419067</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.75048470497131</v>
+        <v>2.75048494338989</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.77643275260925</v>
+        <v>2.77643251419067</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.80238032341003</v>
+        <v>2.80238080024719</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.80238032341003</v>
+        <v>2.80238080024719</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85798335075378</v>
+        <v>2.85798358917236</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.95436143875122</v>
+        <v>2.9543616771698</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.00255084037781</v>
+        <v>3.00255107879639</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.97289609909058</v>
+        <v>2.97289633750916</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.12117004394531</v>
+        <v>3.12116980552673</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.13229012489319</v>
+        <v>3.13229036331177</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.06556749343872</v>
+        <v>3.06556725502014</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.09892892837524</v>
+        <v>3.09892868995667</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.1841869354248</v>
+        <v>3.18418669700623</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.10634279251099</v>
+        <v>3.10634255409241</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.13970446586609</v>
+        <v>3.13970422744751</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.375</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.24349617958069</v>
+        <v>3.24349594116211</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.32875347137451</v>
+        <v>3.32875370979309</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.65866327285767</v>
+        <v>3.65866351127625</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.58082032203674</v>
+        <v>3.58081960678101</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41771841049194</v>
+        <v>3.41771817207336</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.70314598083496</v>
+        <v>3.70314574241638</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.84771347045898</v>
+        <v>3.84771299362183</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.86254048347473</v>
+        <v>3.86254096031189</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>6</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.44822311401367</v>
+        <v>4.44822359085083</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.47046422958374</v>
+        <v>4.47046518325806</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.50011920928955</v>
+        <v>4.50011968612671</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>6</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.44822311401367</v>
+        <v>4.44822359085083</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>6.75</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.00425148010254</v>
+        <v>5.00425100326538</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.11545658111572</v>
+        <v>5.11545705795288</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.46390104293823</v>
+        <v>5.46390056610107</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.5</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.56027984619141</v>
+        <v>5.56027936935425</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>7.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.56027984619141</v>
+        <v>5.56027936935425</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.62700223922729</v>
+        <v>5.62700271606445</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.76044940948486</v>
+        <v>5.76044893264771</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.56769323348999</v>
+        <v>5.56769275665283</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.52321004867554</v>
+        <v>5.5232105255127</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1222" t="n">
-        <v>5.44165992736816</v>
+        <v>5.44165945053101</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.40459108352661</v>
+        <v>5.40459156036377</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1225" t="n">
-        <v>5.15252542495728</v>
+        <v>5.15252494812012</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.1747670173645</v>
+        <v>5.17476654052734</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>5.40459108352661</v>
+        <v>5.40459156036377</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.76044940948486</v>
+        <v>5.76044893264771</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.6937255859375</v>
+        <v>5.69372606277466</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.66407108306885</v>
+        <v>5.66407060623169</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>7.75</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.74562215805054</v>
+        <v>5.74562168121338</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.79010391235352</v>
+        <v>5.79010486602783</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.51664781570435</v>
+        <v>6.51664686203003</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1240" t="n">
-        <v>6.50182008743286</v>
+        <v>6.5018196105957</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1242" t="n">
-        <v>6.59078407287598</v>
+        <v>6.59078502655029</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1244" t="n">
-        <v>6.27940893173218</v>
+        <v>6.27940845489502</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1245" t="n">
-        <v>6.24234008789062</v>
+        <v>6.24233961105347</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1249" t="n">
-        <v>6.19785785675049</v>
+        <v>6.19785737991333</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1251" t="n">
-        <v>6.62043952941895</v>
+        <v>6.62043905258179</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1253" t="n">
-        <v>6.58337068557739</v>
+        <v>6.58337020874023</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1254" t="n">
-        <v>6.57595634460449</v>
+        <v>6.57595682144165</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1257" t="n">
-        <v>7.05784702301025</v>
+        <v>7.05784749984741</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1258" t="n">
-        <v>7.065260887146</v>
+        <v>7.06526136398315</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1261" t="n">
-        <v>7.54715299606323</v>
+        <v>7.54715204238892</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1262" t="n">
-        <v>7.60646200180054</v>
+        <v>7.60646152496338</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>10.5</v>
       </c>
       <c r="G1264" t="n">
-        <v>7.78439044952393</v>
+        <v>7.78439140319824</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.8733549118042</v>
+        <v>7.87335586547852</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.99197483062744</v>
+        <v>7.99197387695312</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1271" t="n">
-        <v>8.05128383636475</v>
+        <v>8.05128288269043</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1273" t="n">
-        <v>7.443359375</v>
+        <v>7.44335985183716</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>7.54715299606323</v>
+        <v>7.54715204238892</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.59163331985474</v>
+        <v>7.59163427352905</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1277" t="n">
-        <v>7.30250024795532</v>
+        <v>7.30250072479248</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G1280" t="n">
-        <v>7.33215475082397</v>
+        <v>7.33215522766113</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1284" t="n">
-        <v>7.30250024795532</v>
+        <v>7.30250072479248</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.32474136352539</v>
+        <v>7.32474088668823</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.05784702301025</v>
+        <v>7.05784749984741</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1287" t="n">
-        <v>7.32474136352539</v>
+        <v>7.32474088668823</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1288" t="n">
-        <v>7.08008861541748</v>
+        <v>7.0800895690918</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.19129371643066</v>
+        <v>7.19129419326782</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.28025817871094</v>
+        <v>7.2802586555481</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>10</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.41370582580566</v>
+        <v>7.41370534896851</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.8733549118042</v>
+        <v>7.87335586547852</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1298" t="n">
-        <v>7.9771466255188</v>
+        <v>7.97714757919312</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1300" t="n">
-        <v>8.27369499206543</v>
+        <v>8.27369403839111</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1306" t="n">
-        <v>8.31817722320557</v>
+        <v>8.31817817687988</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1308" t="n">
-        <v>8.16990375518799</v>
+        <v>8.1699047088623</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1309" t="n">
-        <v>7.99197483062744</v>
+        <v>7.99197387695312</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.443359375</v>
+        <v>7.44335985183716</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1315" t="n">
-        <v>7.30250024795532</v>
+        <v>7.30250072479248</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1316" t="n">
-        <v>7.29508638381958</v>
+        <v>7.29508686065674</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1317" t="n">
-        <v>7.443359375</v>
+        <v>7.44335985183716</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>10.5</v>
       </c>
       <c r="G1318" t="n">
-        <v>7.78439044952393</v>
+        <v>7.78439140319824</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>7.69542694091797</v>
+        <v>7.69542598724365</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1320" t="n">
-        <v>7.59163331985474</v>
+        <v>7.59163427352905</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1321" t="n">
-        <v>7.51749849319458</v>
+        <v>7.51749753952026</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1323" t="n">
-        <v>7.50267124176025</v>
+        <v>7.50267028808594</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>7.65094470977783</v>
+        <v>7.65094375610352</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1327" t="n">
-        <v>7.91783809661865</v>
+        <v>7.91783714294434</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>10.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>7.78439044952393</v>
+        <v>7.78439140319824</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1332" t="n">
-        <v>7.99197483062744</v>
+        <v>7.99197387695312</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1333" t="n">
-        <v>7.9771466255188</v>
+        <v>7.97714757919312</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1334" t="n">
-        <v>8.08093929290771</v>
+        <v>8.0809383392334</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1336" t="n">
-        <v>8.42196846008301</v>
+        <v>8.42196941375732</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>13.5</v>
       </c>
       <c r="G1340" t="n">
-        <v>10.0085029602051</v>
+        <v>10.0085020065308</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.95660591125488</v>
+        <v>9.9566068649292</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1350" t="n">
-        <v>10.1122941970825</v>
+        <v>10.1122932434082</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1351" t="n">
-        <v>10.0603981018066</v>
+        <v>10.060399055481</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1352" t="n">
-        <v>10.0603981018066</v>
+        <v>10.060399055481</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>13.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>10.0085029602051</v>
+        <v>10.0085020065308</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1354" t="n">
-        <v>10.1271209716797</v>
+        <v>10.127121925354</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.95660591125488</v>
+        <v>9.9566068649292</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1357" t="n">
-        <v>9.97884750366211</v>
+        <v>9.97884654998779</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G1374" t="n">
-        <v>11.0631093978882</v>
+        <v>11.0631103515625</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.4722833633423</v>
+        <v>11.472282409668</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.7888135910034</v>
+        <v>11.7888145446777</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1383" t="n">
-        <v>11.904616355896</v>
+        <v>11.9046173095703</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1385" t="n">
-        <v>11.7810935974121</v>
+        <v>11.7810926437378</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1387" t="n">
-        <v>11.6730108261108</v>
+        <v>11.6730098724365</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1388" t="n">
-        <v>11.7038908004761</v>
+        <v>11.7038898468018</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.4954442977905</v>
+        <v>11.4954433441162</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1395" t="n">
-        <v>11.4259624481201</v>
+        <v>11.4259614944458</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G1398" t="n">
-        <v>11.6652889251709</v>
+        <v>11.6652898788452</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1406" t="n">
-        <v>12.2134256362915</v>
+        <v>12.2134265899658</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G1408" t="n">
-        <v>11.8351345062256</v>
+        <v>11.8351354598999</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1414" t="n">
-        <v>11.7810935974121</v>
+        <v>11.7810926437378</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.5649261474609</v>
+        <v>11.5649251937866</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1423" t="n">
-        <v>12.1671047210693</v>
+        <v>12.1671056747437</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G1428" t="n">
-        <v>12.2674694061279</v>
+        <v>12.2674684524536</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G1429" t="n">
-        <v>12.3292303085327</v>
+        <v>12.3292293548584</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1430" t="n">
-        <v>12.2134256362915</v>
+        <v>12.2134265899658</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.0435819625854</v>
+        <v>12.0435829162598</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>12.0435819625854</v>
+        <v>12.0435829162598</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.2751884460449</v>
+        <v>12.2751893997192</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="n">
-        <v>12.352391242981</v>
+        <v>12.3523921966553</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1446" t="n">
-        <v>10.8392238616943</v>
+        <v>10.83922290802</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1447" t="n">
-        <v>10.5149726867676</v>
+        <v>10.5149736404419</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>13</v>
       </c>
       <c r="G1448" t="n">
-        <v>10.0363178253174</v>
+        <v>10.0363187789917</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>9.72750854492188</v>
+        <v>9.72750949859619</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1453" t="n">
-        <v>9.61942386627197</v>
+        <v>9.61942481994629</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>12</v>
       </c>
       <c r="G1458" t="n">
-        <v>9.2642936706543</v>
+        <v>9.26429462432861</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1459" t="n">
-        <v>9.10988903045654</v>
+        <v>9.10988807678223</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1463" t="n">
-        <v>8.77019786834717</v>
+        <v>8.77019691467285</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.52315044403076</v>
+        <v>8.52314949035645</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>9.18709087371826</v>
+        <v>9.18708992004395</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1477" t="n">
-        <v>9.10988903045654</v>
+        <v>9.10988807678223</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1480" t="n">
-        <v>9.15620994567871</v>
+        <v>9.15620899200439</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1484" t="n">
-        <v>8.94004344940186</v>
+        <v>8.94004249572754</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1486" t="n">
-        <v>9.31833457946777</v>
+        <v>9.31833362579346</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G1488" t="n">
-        <v>9.62714576721191</v>
+        <v>9.6271448135376</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1489" t="n">
-        <v>9.59626483917236</v>
+        <v>9.59626388549805</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1498" t="n">
-        <v>9.58854293823242</v>
+        <v>9.58854389190674</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1500" t="n">
-        <v>9.00952625274658</v>
+        <v>9.00952529907227</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1502" t="n">
-        <v>9.18709087371826</v>
+        <v>9.18708992004395</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1515" t="n">
-        <v>9.36465644836426</v>
+        <v>9.36465549468994</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1519" t="n">
-        <v>9.15620994567871</v>
+        <v>9.15620899200439</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>13</v>
       </c>
       <c r="G1528" t="n">
-        <v>10.0363178253174</v>
+        <v>10.0363187789917</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.99408435821533</v>
+        <v>8.99408531188965</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1533" t="n">
-        <v>9.23341274261475</v>
+        <v>9.23341178894043</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1534" t="n">
-        <v>9.44957828521729</v>
+        <v>9.4495792388916</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1536" t="n">
-        <v>9.36465644836426</v>
+        <v>9.36465549468994</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1547" t="n">
-        <v>9.32605457305908</v>
+        <v>9.3260555267334</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1550" t="n">
-        <v>9.37237644195557</v>
+        <v>9.37237739562988</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>9.10988903045654</v>
+        <v>9.10988807678223</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1556" t="n">
-        <v>9.32605457305908</v>
+        <v>9.3260555267334</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1559" t="n">
-        <v>9.21797180175781</v>
+        <v>9.2179708480835</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1560" t="n">
-        <v>9.00952625274658</v>
+        <v>9.00952529907227</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1563" t="n">
-        <v>8.63123416900635</v>
+        <v>8.63123321533203</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.25702953338623</v>
+        <v>7.25703001022339</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.3226523399353</v>
+        <v>7.32265138626099</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.48863697052002</v>
+        <v>7.48863744735718</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1584" t="n">
-        <v>7.42687511444092</v>
+        <v>7.42687559127808</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.53881883621216</v>
+        <v>7.53881931304932</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.70866346359253</v>
+        <v>7.70866441726685</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>7.42687511444092</v>
+        <v>7.42687559127808</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1595" t="n">
-        <v>7.15280675888062</v>
+        <v>7.15280628204346</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.36511373519897</v>
+        <v>7.36511421203613</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.39213371276855</v>
+        <v>7.3921332359314</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1599" t="n">
-        <v>7.38441371917725</v>
+        <v>7.38441324234009</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G1602" t="n">
-        <v>7.46161603927612</v>
+        <v>7.46161651611328</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.58513927459717</v>
+        <v>7.58514022827148</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>8.14000034332275</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>83046</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>8.22500038146973</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>8.22500038146973</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>8.01500034332275</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>8.01500034332275</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>7.96000003814697</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>8.01000022888184</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>142636</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>8.27999973297119</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>8.01000022888184</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>8.01000022888184</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>8.20499992370605</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>132487</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>8.24499988555908</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>7.96999979019165</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>8.15999984741211</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>8.15999984741211</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>8.06999969482422</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>115640</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>8.14000034332275</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>7.8899998664856</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>7.96500015258789</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>7.96500015258789</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>7.96500015258789</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>70991</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>8.17500019073486</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>98548</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>8.17000007629395</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>7.92500019073486</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>8.00500011444092</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>7.92500019073486</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.44732332229614</v>
+        <v>5.4473237991333</v>
       </c>
       <c r="H2" t="n">
         <v>113188</v>
@@ -456,7 +456,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G3" t="n">
-        <v>5.55361318588257</v>
+        <v>5.55361223220825</v>
       </c>
       <c r="H3" t="n">
         <v>66887</v>
@@ -514,7 +514,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G5" t="n">
-        <v>5.32774877548218</v>
+        <v>5.32774829864502</v>
       </c>
       <c r="H5" t="n">
         <v>104860</v>
@@ -572,7 +572,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G7" t="n">
-        <v>5.21481609344482</v>
+        <v>5.21481561660767</v>
       </c>
       <c r="H7" t="n">
         <v>108677</v>
@@ -601,7 +601,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>5.29453229904175</v>
+        <v>5.29453325271606</v>
       </c>
       <c r="H8" t="n">
         <v>216037</v>
@@ -630,7 +630,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>5.33106994628906</v>
+        <v>5.3310694694519</v>
       </c>
       <c r="H9" t="n">
         <v>49371</v>
@@ -688,7 +688,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>4.94245004653931</v>
+        <v>4.94245052337646</v>
       </c>
       <c r="H11" t="n">
         <v>159704</v>
@@ -746,7 +746,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>4.84612560272217</v>
+        <v>4.84612512588501</v>
       </c>
       <c r="H13" t="n">
         <v>91026</v>
@@ -833,7 +833,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>4.82951784133911</v>
+        <v>4.82951688766479</v>
       </c>
       <c r="H16" t="n">
         <v>117197</v>
@@ -862,7 +862,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>4.82951784133911</v>
+        <v>4.82951688766479</v>
       </c>
       <c r="H17" t="n">
         <v>66239</v>
@@ -949,7 +949,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>4.91587686538696</v>
+        <v>4.91587734222412</v>
       </c>
       <c r="H20" t="n">
         <v>109639</v>
@@ -1007,7 +1007,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>4.97234392166138</v>
+        <v>4.97234439849854</v>
       </c>
       <c r="H22" t="n">
         <v>54344</v>
@@ -1065,7 +1065,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>4.94909286499023</v>
+        <v>4.94909238815308</v>
       </c>
       <c r="H24" t="n">
         <v>115223</v>
@@ -1094,7 +1094,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>4.93248558044434</v>
+        <v>4.93248605728149</v>
       </c>
       <c r="H25" t="n">
         <v>117119</v>
@@ -1152,7 +1152,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.59368753433228</v>
+        <v>4.59368801116943</v>
       </c>
       <c r="H27" t="n">
         <v>190986</v>
@@ -1181,7 +1181,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>4.45750570297241</v>
+        <v>4.45750522613525</v>
       </c>
       <c r="H28" t="n">
         <v>305032</v>
@@ -1239,7 +1239,7 @@
         <v>6.75</v>
       </c>
       <c r="G30" t="n">
-        <v>4.48407745361328</v>
+        <v>4.48407793045044</v>
       </c>
       <c r="H30" t="n">
         <v>162247</v>
@@ -1268,7 +1268,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>4.62690353393555</v>
+        <v>4.62690305709839</v>
       </c>
       <c r="H31" t="n">
         <v>118549</v>
@@ -1297,7 +1297,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>4.70662021636963</v>
+        <v>4.70661973953247</v>
       </c>
       <c r="H32" t="n">
         <v>54106</v>
@@ -1355,7 +1355,7 @@
         <v>7.375</v>
       </c>
       <c r="G34" t="n">
-        <v>4.89926958084106</v>
+        <v>4.89927053451538</v>
       </c>
       <c r="H34" t="n">
         <v>59630</v>
@@ -1384,7 +1384,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G35" t="n">
-        <v>5.19488668441772</v>
+        <v>5.19488716125488</v>
       </c>
       <c r="H35" t="n">
         <v>145821</v>
@@ -1442,7 +1442,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>5.21481609344482</v>
+        <v>5.21481561660767</v>
       </c>
       <c r="H37" t="n">
         <v>79314</v>
@@ -1471,7 +1471,7 @@
         <v>7.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.02548885345459</v>
+        <v>5.02548837661743</v>
       </c>
       <c r="H38" t="n">
         <v>81136</v>
@@ -1500,7 +1500,7 @@
         <v>7.75</v>
       </c>
       <c r="G39" t="n">
-        <v>5.14838552474976</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H39" t="n">
         <v>73305</v>
@@ -1558,7 +1558,7 @@
         <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>5.31446266174316</v>
+        <v>5.31446218490601</v>
       </c>
       <c r="H41" t="n">
         <v>66693</v>
@@ -1587,7 +1587,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>5.51375532150269</v>
+        <v>5.51375389099121</v>
       </c>
       <c r="H42" t="n">
         <v>150009</v>
@@ -1645,7 +1645,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>5.75290536880493</v>
+        <v>5.75290489196777</v>
       </c>
       <c r="H44" t="n">
         <v>122191</v>
@@ -1732,7 +1732,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G47" t="n">
-        <v>5.68315315246582</v>
+        <v>5.68315362930298</v>
       </c>
       <c r="H47" t="n">
         <v>127631</v>
@@ -1761,7 +1761,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>5.7263331413269</v>
+        <v>5.72633266448975</v>
       </c>
       <c r="H48" t="n">
         <v>97982</v>
@@ -1819,7 +1819,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>5.35432100296021</v>
+        <v>5.35432147979736</v>
       </c>
       <c r="H50" t="n">
         <v>105600</v>
@@ -1848,7 +1848,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G51" t="n">
-        <v>5.38753604888916</v>
+        <v>5.38753652572632</v>
       </c>
       <c r="H51" t="n">
         <v>191706</v>
@@ -1877,7 +1877,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G52" t="n">
-        <v>5.5037899017334</v>
+        <v>5.50378942489624</v>
       </c>
       <c r="H52" t="n">
         <v>91415</v>
@@ -1935,7 +1935,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>5.44732332229614</v>
+        <v>5.4473237991333</v>
       </c>
       <c r="H54" t="n">
         <v>43227</v>
@@ -1993,7 +1993,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.44732332229614</v>
+        <v>5.4473237991333</v>
       </c>
       <c r="H56" t="n">
         <v>148456</v>
@@ -2022,7 +2022,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G57" t="n">
-        <v>5.38421440124512</v>
+        <v>5.38421392440796</v>
       </c>
       <c r="H57" t="n">
         <v>103959</v>
@@ -2051,7 +2051,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>5.41410875320435</v>
+        <v>5.41410827636719</v>
       </c>
       <c r="H58" t="n">
         <v>147032</v>
@@ -2080,7 +2080,7 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>5.31446266174316</v>
+        <v>5.31446218490601</v>
       </c>
       <c r="H59" t="n">
         <v>81757</v>
@@ -2138,7 +2138,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>5.14174270629883</v>
+        <v>5.14174222946167</v>
       </c>
       <c r="H61" t="n">
         <v>103759</v>
@@ -2196,7 +2196,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>5.27460384368896</v>
+        <v>5.27460336685181</v>
       </c>
       <c r="H63" t="n">
         <v>44868</v>
@@ -2225,7 +2225,7 @@
         <v>7.75</v>
       </c>
       <c r="G64" t="n">
-        <v>5.14838552474976</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H64" t="n">
         <v>96421</v>
@@ -2254,7 +2254,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.26796102523804</v>
+        <v>5.26796054840088</v>
       </c>
       <c r="H65" t="n">
         <v>87527</v>
@@ -2370,7 +2370,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>5.0753116607666</v>
+        <v>5.07531118392944</v>
       </c>
       <c r="H69" t="n">
         <v>43182</v>
@@ -2399,7 +2399,7 @@
         <v>7.75</v>
       </c>
       <c r="G70" t="n">
-        <v>5.14838552474976</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H70" t="n">
         <v>22243</v>
@@ -2428,7 +2428,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>5.08859729766846</v>
+        <v>5.08859777450562</v>
       </c>
       <c r="H71" t="n">
         <v>44738</v>
@@ -2457,7 +2457,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>5.27460384368896</v>
+        <v>5.27460336685181</v>
       </c>
       <c r="H72" t="n">
         <v>51680</v>
@@ -2515,7 +2515,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G74" t="n">
-        <v>5.04209661483765</v>
+        <v>5.04209613800049</v>
       </c>
       <c r="H74" t="n">
         <v>83664</v>
@@ -2544,7 +2544,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G75" t="n">
-        <v>5.03545331954956</v>
+        <v>5.0354528427124</v>
       </c>
       <c r="H75" t="n">
         <v>54297</v>
@@ -2573,7 +2573,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>5.08195400238037</v>
+        <v>5.08195447921753</v>
       </c>
       <c r="H76" t="n">
         <v>52690</v>
@@ -2602,7 +2602,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>5.04873895645142</v>
+        <v>5.04873943328857</v>
       </c>
       <c r="H77" t="n">
         <v>29830</v>
@@ -2631,7 +2631,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.11516952514648</v>
+        <v>5.11517000198364</v>
       </c>
       <c r="H78" t="n">
         <v>43914</v>
@@ -2660,7 +2660,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>5.06202507019043</v>
+        <v>5.06202554702759</v>
       </c>
       <c r="H79" t="n">
         <v>31701</v>
@@ -2747,7 +2747,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>5.0553822517395</v>
+        <v>5.05538272857666</v>
       </c>
       <c r="H82" t="n">
         <v>36158</v>
@@ -2863,7 +2863,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>5.06202507019043</v>
+        <v>5.06202554702759</v>
       </c>
       <c r="H86" t="n">
         <v>36585</v>
@@ -2892,7 +2892,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.08195400238037</v>
+        <v>5.08195447921753</v>
       </c>
       <c r="H87" t="n">
         <v>21885</v>
@@ -2921,7 +2921,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.0719895362854</v>
+        <v>5.07199048995972</v>
       </c>
       <c r="H88" t="n">
         <v>6172</v>
@@ -2979,7 +2979,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G90" t="n">
-        <v>5.74733304977417</v>
+        <v>5.74733209609985</v>
       </c>
       <c r="H90" t="n">
         <v>226380</v>
@@ -3037,7 +3037,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G92" t="n">
-        <v>5.54763174057007</v>
+        <v>5.54763126373291</v>
       </c>
       <c r="H92" t="n">
         <v>108705</v>
@@ -3066,7 +3066,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G93" t="n">
-        <v>5.42916584014893</v>
+        <v>5.42916536331177</v>
       </c>
       <c r="H93" t="n">
         <v>60550</v>
@@ -3095,7 +3095,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>5.52393817901611</v>
+        <v>5.52393865585327</v>
       </c>
       <c r="H94" t="n">
         <v>43648</v>
@@ -3153,7 +3153,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>4.66759252548218</v>
+        <v>4.66759300231934</v>
       </c>
       <c r="H96" t="n">
         <v>383206</v>
@@ -3182,7 +3182,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G97" t="n">
-        <v>4.66420793533325</v>
+        <v>4.66420745849609</v>
       </c>
       <c r="H97" t="n">
         <v>146046</v>
@@ -3298,7 +3298,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>4.47804546356201</v>
+        <v>4.47804594039917</v>
       </c>
       <c r="H101" t="n">
         <v>121440</v>
@@ -3501,7 +3501,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>4.29865264892578</v>
+        <v>4.29865312576294</v>
       </c>
       <c r="H108" t="n">
         <v>89317</v>
@@ -3530,7 +3530,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>4.32911682128906</v>
+        <v>4.3291163444519</v>
       </c>
       <c r="H109" t="n">
         <v>121684</v>
@@ -3559,7 +3559,7 @@
         <v>6.25</v>
       </c>
       <c r="G110" t="n">
-        <v>4.23095798492432</v>
+        <v>4.23095750808716</v>
       </c>
       <c r="H110" t="n">
         <v>156920</v>
@@ -3617,7 +3617,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G112" t="n">
-        <v>4.15649271011353</v>
+        <v>4.15649318695068</v>
       </c>
       <c r="H112" t="n">
         <v>139833</v>
@@ -3646,7 +3646,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>4.048180103302</v>
+        <v>4.04818058013916</v>
       </c>
       <c r="H113" t="n">
         <v>122772</v>
@@ -3675,7 +3675,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>4.12264490127563</v>
+        <v>4.12264537811279</v>
       </c>
       <c r="H114" t="n">
         <v>91431</v>
@@ -3704,7 +3704,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.02448797225952</v>
+        <v>4.02448749542236</v>
       </c>
       <c r="H115" t="n">
         <v>158085</v>
@@ -3762,7 +3762,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>3.86540293693542</v>
+        <v>3.865403175354</v>
       </c>
       <c r="H117" t="n">
         <v>92272</v>
@@ -3791,7 +3791,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G118" t="n">
-        <v>3.79770755767822</v>
+        <v>3.79770827293396</v>
       </c>
       <c r="H118" t="n">
         <v>144969</v>
@@ -3820,7 +3820,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>4.01094818115234</v>
+        <v>4.0109486579895</v>
       </c>
       <c r="H119" t="n">
         <v>162964</v>
@@ -3849,7 +3849,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.93648314476013</v>
+        <v>3.93648386001587</v>
       </c>
       <c r="H120" t="n">
         <v>167668</v>
@@ -3878,7 +3878,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.96356129646301</v>
+        <v>3.96356081962585</v>
       </c>
       <c r="H121" t="n">
         <v>108290</v>
@@ -3907,7 +3907,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94663763046265</v>
+        <v>3.94663739204407</v>
       </c>
       <c r="H122" t="n">
         <v>66243</v>
@@ -3936,7 +3936,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>3.99402403831482</v>
+        <v>3.99402451515198</v>
       </c>
       <c r="H123" t="n">
         <v>85572</v>
@@ -3965,7 +3965,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>3.76386046409607</v>
+        <v>3.76385998725891</v>
       </c>
       <c r="H124" t="n">
         <v>198048</v>
@@ -4023,7 +4023,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.40169024467468</v>
+        <v>3.40169048309326</v>
       </c>
       <c r="H126" t="n">
         <v>297033</v>
@@ -4052,7 +4052,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>3.47615575790405</v>
+        <v>3.47615528106689</v>
       </c>
       <c r="H127" t="n">
         <v>184937</v>
@@ -4081,7 +4081,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G128" t="n">
-        <v>3.48969435691833</v>
+        <v>3.48969411849976</v>
       </c>
       <c r="H128" t="n">
         <v>107107</v>
@@ -4110,7 +4110,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G129" t="n">
-        <v>3.48969435691833</v>
+        <v>3.48969411849976</v>
       </c>
       <c r="H129" t="n">
         <v>134491</v>
@@ -4197,7 +4197,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>3.15730977058411</v>
+        <v>3.15731024742126</v>
       </c>
       <c r="H132" t="n">
         <v>707649</v>
@@ -4226,7 +4226,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22906684875488</v>
+        <v>3.22906708717346</v>
       </c>
       <c r="H133" t="n">
         <v>75468</v>
@@ -4284,7 +4284,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G135" t="n">
-        <v>3.32519459724426</v>
+        <v>3.32519435882568</v>
       </c>
       <c r="H135" t="n">
         <v>50898</v>
@@ -4313,7 +4313,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.58785176277161</v>
+        <v>3.58785247802734</v>
       </c>
       <c r="H136" t="n">
         <v>115636</v>
@@ -4342,7 +4342,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G137" t="n">
-        <v>3.47615575790405</v>
+        <v>3.47615528106689</v>
       </c>
       <c r="H137" t="n">
         <v>87648</v>
@@ -4371,7 +4371,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49984860420227</v>
+        <v>3.49984788894653</v>
       </c>
       <c r="H138" t="n">
         <v>69291</v>
@@ -4400,7 +4400,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.48630905151367</v>
+        <v>3.48630952835083</v>
       </c>
       <c r="H139" t="n">
         <v>109570</v>
@@ -4429,7 +4429,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>3.5709285736084</v>
+        <v>3.57092833518982</v>
       </c>
       <c r="H140" t="n">
         <v>95057</v>
@@ -4487,7 +4487,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G142" t="n">
-        <v>3.57431268692017</v>
+        <v>3.57431364059448</v>
       </c>
       <c r="H142" t="n">
         <v>38892</v>
@@ -4516,7 +4516,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>3.60477638244629</v>
+        <v>3.60477566719055</v>
       </c>
       <c r="H143" t="n">
         <v>103724</v>
@@ -4545,7 +4545,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G144" t="n">
-        <v>3.5946216583252</v>
+        <v>3.59462141990662</v>
       </c>
       <c r="H144" t="n">
         <v>67888</v>
@@ -4632,7 +4632,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.79093861579895</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H147" t="n">
         <v>91695</v>
@@ -4690,7 +4690,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>3.78078365325928</v>
+        <v>3.78078389167786</v>
       </c>
       <c r="H149" t="n">
         <v>32010</v>
@@ -4719,7 +4719,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G150" t="n">
-        <v>3.71308875083923</v>
+        <v>3.71308898925781</v>
       </c>
       <c r="H150" t="n">
         <v>72315</v>
@@ -4748,7 +4748,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>3.52015686035156</v>
+        <v>3.5201563835144</v>
       </c>
       <c r="H151" t="n">
         <v>107282</v>
@@ -4777,7 +4777,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G152" t="n">
-        <v>3.56077480316162</v>
+        <v>3.56077456474304</v>
       </c>
       <c r="H152" t="n">
         <v>56391</v>
@@ -4806,7 +4806,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>3.61492991447449</v>
+        <v>3.61493062973022</v>
       </c>
       <c r="H153" t="n">
         <v>30739</v>
@@ -4835,7 +4835,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.67924022674561</v>
+        <v>3.67924070358276</v>
       </c>
       <c r="H154" t="n">
         <v>20938</v>
@@ -4893,7 +4893,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>3.79093861579895</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H156" t="n">
         <v>57929</v>
@@ -4922,7 +4922,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>3.79093861579895</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H157" t="n">
         <v>34686</v>
@@ -4980,7 +4980,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82140111923218</v>
+        <v>3.82140135765076</v>
       </c>
       <c r="H159" t="n">
         <v>39413</v>
@@ -5067,7 +5067,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G162" t="n">
-        <v>3.81124663352966</v>
+        <v>3.8112473487854</v>
       </c>
       <c r="H162" t="n">
         <v>24479</v>
@@ -5096,7 +5096,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G163" t="n">
-        <v>3.81124663352966</v>
+        <v>3.8112473487854</v>
       </c>
       <c r="H163" t="n">
         <v>58927</v>
@@ -5183,7 +5183,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>3.98725438117981</v>
+        <v>3.98725461959839</v>
       </c>
       <c r="H166" t="n">
         <v>125514</v>
@@ -5241,7 +5241,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G168" t="n">
-        <v>4.13618421554565</v>
+        <v>4.13618469238281</v>
       </c>
       <c r="H168" t="n">
         <v>165803</v>
@@ -5270,7 +5270,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>4.07525825500488</v>
+        <v>4.07525873184204</v>
       </c>
       <c r="H169" t="n">
         <v>48601</v>
@@ -5299,7 +5299,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G170" t="n">
-        <v>4.02448797225952</v>
+        <v>4.02448749542236</v>
       </c>
       <c r="H170" t="n">
         <v>39849</v>
@@ -5328,7 +5328,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>3.99402403831482</v>
+        <v>3.99402451515198</v>
       </c>
       <c r="H171" t="n">
         <v>44191</v>
@@ -5386,7 +5386,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>4.05833435058594</v>
+        <v>4.0583348274231</v>
       </c>
       <c r="H173" t="n">
         <v>31122</v>
@@ -5415,7 +5415,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>3.96356129646301</v>
+        <v>3.96356081962585</v>
       </c>
       <c r="H174" t="n">
         <v>171483</v>
@@ -5444,7 +5444,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>3.93986797332764</v>
+        <v>3.93986773490906</v>
       </c>
       <c r="H175" t="n">
         <v>201408</v>
@@ -5502,7 +5502,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>4.05833435058594</v>
+        <v>4.0583348274231</v>
       </c>
       <c r="H177" t="n">
         <v>34907</v>
@@ -5531,7 +5531,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>4.07525825500488</v>
+        <v>4.07525873184204</v>
       </c>
       <c r="H178" t="n">
         <v>17063</v>
@@ -5560,7 +5560,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.98725438117981</v>
+        <v>3.98725461959839</v>
       </c>
       <c r="H179" t="n">
         <v>91126</v>
@@ -5618,7 +5618,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G181" t="n">
-        <v>3.96694588661194</v>
+        <v>3.96694612503052</v>
       </c>
       <c r="H181" t="n">
         <v>146337</v>
@@ -5676,7 +5676,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G183" t="n">
-        <v>3.44907712936401</v>
+        <v>3.44907641410828</v>
       </c>
       <c r="H183" t="n">
         <v>558094</v>
@@ -5705,7 +5705,7 @@
         <v>5</v>
       </c>
       <c r="G184" t="n">
-        <v>3.38476657867432</v>
+        <v>3.38476610183716</v>
       </c>
       <c r="H184" t="n">
         <v>271176</v>
@@ -5734,7 +5734,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>3.31707072257996</v>
+        <v>3.31707096099854</v>
       </c>
       <c r="H185" t="n">
         <v>255286</v>
@@ -5763,7 +5763,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>3.26020669937134</v>
+        <v>3.26020693778992</v>
       </c>
       <c r="H186" t="n">
         <v>102093</v>
@@ -5821,7 +5821,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G188" t="n">
-        <v>3.33061051368713</v>
+        <v>3.3306097984314</v>
       </c>
       <c r="H188" t="n">
         <v>74303</v>
@@ -5879,7 +5879,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>3.30353212356567</v>
+        <v>3.30353164672852</v>
       </c>
       <c r="H190" t="n">
         <v>156871</v>
@@ -5908,7 +5908,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G191" t="n">
-        <v>3.34279537200928</v>
+        <v>3.3427951335907</v>
       </c>
       <c r="H191" t="n">
         <v>52063</v>
@@ -5937,7 +5937,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G192" t="n">
-        <v>3.3712272644043</v>
+        <v>3.37122750282288</v>
       </c>
       <c r="H192" t="n">
         <v>58791</v>
@@ -5966,7 +5966,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G193" t="n">
-        <v>3.34956479072571</v>
+        <v>3.34956502914429</v>
       </c>
       <c r="H193" t="n">
         <v>82212</v>
@@ -5995,7 +5995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>3.49984860420227</v>
+        <v>3.49984788894653</v>
       </c>
       <c r="H194" t="n">
         <v>152264</v>
@@ -6024,7 +6024,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G195" t="n">
-        <v>3.46261620521545</v>
+        <v>3.46261596679688</v>
       </c>
       <c r="H195" t="n">
         <v>36886</v>
@@ -6053,7 +6053,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>4.11587572097778</v>
+        <v>4.11587524414062</v>
       </c>
       <c r="H196" t="n">
         <v>609931</v>
@@ -6082,7 +6082,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G197" t="n">
-        <v>4.21064901351929</v>
+        <v>4.21064949035645</v>
       </c>
       <c r="H197" t="n">
         <v>1252342</v>
@@ -6140,7 +6140,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>4.35619401931763</v>
+        <v>4.35619449615479</v>
       </c>
       <c r="H199" t="n">
         <v>608292</v>
@@ -6169,7 +6169,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>4.21064901351929</v>
+        <v>4.21064949035645</v>
       </c>
       <c r="H200" t="n">
         <v>336110</v>
@@ -6198,7 +6198,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G201" t="n">
-        <v>4.18357133865356</v>
+        <v>4.18357086181641</v>
       </c>
       <c r="H201" t="n">
         <v>191685</v>
@@ -6285,7 +6285,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>4.26480531692505</v>
+        <v>4.26480579376221</v>
       </c>
       <c r="H204" t="n">
         <v>104103</v>
@@ -6372,7 +6372,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>4.46450710296631</v>
+        <v>4.46450662612915</v>
       </c>
       <c r="H207" t="n">
         <v>103319</v>
@@ -6546,7 +6546,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G213" t="n">
-        <v>4.58974266052246</v>
+        <v>4.58974313735962</v>
       </c>
       <c r="H213" t="n">
         <v>124219</v>
@@ -6604,7 +6604,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G215" t="n">
-        <v>4.56266403198242</v>
+        <v>4.56266450881958</v>
       </c>
       <c r="H215" t="n">
         <v>38526</v>
@@ -6720,7 +6720,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>4.38665771484375</v>
+        <v>4.38665723800659</v>
       </c>
       <c r="H219" t="n">
         <v>126233</v>
@@ -6894,7 +6894,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>4.32911682128906</v>
+        <v>4.3291163444519</v>
       </c>
       <c r="H225" t="n">
         <v>55893</v>
@@ -7010,7 +7010,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>4.35957860946655</v>
+        <v>4.35957908630371</v>
       </c>
       <c r="H229" t="n">
         <v>200260</v>
@@ -7068,7 +7068,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>4.50850820541382</v>
+        <v>4.50850915908813</v>
       </c>
       <c r="H231" t="n">
         <v>229527</v>
@@ -7097,7 +7097,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G232" t="n">
-        <v>4.47804546356201</v>
+        <v>4.47804594039917</v>
       </c>
       <c r="H232" t="n">
         <v>54961</v>
@@ -7126,7 +7126,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G233" t="n">
-        <v>4.43742895126343</v>
+        <v>4.43742847442627</v>
       </c>
       <c r="H233" t="n">
         <v>66735</v>
@@ -7155,7 +7155,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G234" t="n">
-        <v>4.29526853561401</v>
+        <v>4.2952675819397</v>
       </c>
       <c r="H234" t="n">
         <v>197038</v>
@@ -7271,7 +7271,7 @@
         <v>6.375</v>
       </c>
       <c r="G238" t="n">
-        <v>4.31557750701904</v>
+        <v>4.31557703018188</v>
       </c>
       <c r="H238" t="n">
         <v>102989</v>
@@ -7387,7 +7387,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G242" t="n">
-        <v>4.56266403198242</v>
+        <v>4.56266450881958</v>
       </c>
       <c r="H242" t="n">
         <v>108996</v>
@@ -7445,7 +7445,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.48819971084595</v>
+        <v>4.48820018768311</v>
       </c>
       <c r="H244" t="n">
         <v>56395</v>
@@ -7474,7 +7474,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G245" t="n">
-        <v>4.50850820541382</v>
+        <v>4.50850915908813</v>
       </c>
       <c r="H245" t="n">
         <v>73219</v>
@@ -7503,7 +7503,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>4.45435237884521</v>
+        <v>4.45435190200806</v>
       </c>
       <c r="H246" t="n">
         <v>58966</v>
@@ -7532,7 +7532,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.51866340637207</v>
+        <v>4.51866292953491</v>
       </c>
       <c r="H247" t="n">
         <v>77287</v>
@@ -7590,7 +7590,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G249" t="n">
-        <v>4.54912519454956</v>
+        <v>4.54912614822388</v>
       </c>
       <c r="H249" t="n">
         <v>62594</v>
@@ -7619,7 +7619,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G250" t="n">
-        <v>4.62359046936035</v>
+        <v>4.62359094619751</v>
       </c>
       <c r="H250" t="n">
         <v>229951</v>
@@ -7677,7 +7677,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G252" t="n">
-        <v>4.71836376190186</v>
+        <v>4.7183632850647</v>
       </c>
       <c r="H252" t="n">
         <v>148227</v>
@@ -7706,7 +7706,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G253" t="n">
-        <v>4.75898170471191</v>
+        <v>4.75898122787476</v>
       </c>
       <c r="H253" t="n">
         <v>40012</v>
@@ -7764,7 +7764,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G255" t="n">
-        <v>4.71836376190186</v>
+        <v>4.7183632850647</v>
       </c>
       <c r="H255" t="n">
         <v>44487</v>
@@ -7851,7 +7851,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G258" t="n">
-        <v>4.86390972137451</v>
+        <v>4.8639087677002</v>
       </c>
       <c r="H258" t="n">
         <v>67486</v>
@@ -7880,7 +7880,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G259" t="n">
-        <v>4.81652307510376</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H259" t="n">
         <v>83473</v>
@@ -7909,7 +7909,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G260" t="n">
-        <v>4.78605937957764</v>
+        <v>4.78605985641479</v>
       </c>
       <c r="H260" t="n">
         <v>69615</v>
@@ -7967,7 +7967,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G262" t="n">
-        <v>4.76236629486084</v>
+        <v>4.76236581802368</v>
       </c>
       <c r="H262" t="n">
         <v>139601</v>
@@ -7996,7 +7996,7 @@
         <v>7</v>
       </c>
       <c r="G263" t="n">
-        <v>4.73867321014404</v>
+        <v>4.73867273330688</v>
       </c>
       <c r="H263" t="n">
         <v>75411</v>
@@ -8054,7 +8054,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>4.86729383468628</v>
+        <v>4.86729431152344</v>
       </c>
       <c r="H265" t="n">
         <v>82243</v>
@@ -8141,7 +8141,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>4.81652307510376</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H268" t="n">
         <v>15823</v>
@@ -8170,7 +8170,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>4.83683109283447</v>
+        <v>4.83683156967163</v>
       </c>
       <c r="H269" t="n">
         <v>40098</v>
@@ -8199,7 +8199,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G270" t="n">
-        <v>4.83006238937378</v>
+        <v>4.83006143569946</v>
       </c>
       <c r="H270" t="n">
         <v>13830</v>
@@ -8228,7 +8228,7 @@
         <v>7.125</v>
       </c>
       <c r="G271" t="n">
-        <v>4.82329225540161</v>
+        <v>4.82329177856445</v>
       </c>
       <c r="H271" t="n">
         <v>22605</v>
@@ -8286,7 +8286,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G273" t="n">
-        <v>4.72851896286011</v>
+        <v>4.72851848602295</v>
       </c>
       <c r="H273" t="n">
         <v>28889</v>
@@ -8315,7 +8315,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G274" t="n">
-        <v>4.83006238937378</v>
+        <v>4.83006143569946</v>
       </c>
       <c r="H274" t="n">
         <v>32565</v>
@@ -8373,7 +8373,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G276" t="n">
-        <v>4.80298376083374</v>
+        <v>4.80298328399658</v>
       </c>
       <c r="H276" t="n">
         <v>89643</v>
@@ -8402,7 +8402,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G277" t="n">
-        <v>4.81652307510376</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H277" t="n">
         <v>53288</v>
@@ -8431,7 +8431,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65066909790039</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H278" t="n">
         <v>80211</v>
@@ -8489,7 +8489,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.6574387550354</v>
+        <v>4.65743827819824</v>
       </c>
       <c r="H280" t="n">
         <v>45461</v>
@@ -8518,7 +8518,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G281" t="n">
-        <v>4.69805526733398</v>
+        <v>4.69805574417114</v>
       </c>
       <c r="H281" t="n">
         <v>48954</v>
@@ -8576,7 +8576,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>4.65066909790039</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H283" t="n">
         <v>39226</v>
@@ -8605,7 +8605,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>4.65066909790039</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H284" t="n">
         <v>31328</v>
@@ -8692,7 +8692,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74205827713013</v>
+        <v>4.74205732345581</v>
       </c>
       <c r="H287" t="n">
         <v>26431</v>
@@ -8779,7 +8779,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>5.04330158233643</v>
+        <v>5.04330205917358</v>
       </c>
       <c r="H290" t="n">
         <v>270928</v>
@@ -8808,7 +8808,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G291" t="n">
-        <v>5.07037973403931</v>
+        <v>5.07038021087646</v>
       </c>
       <c r="H291" t="n">
         <v>225000</v>
@@ -8837,7 +8837,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>5.02299308776855</v>
+        <v>5.0229926109314</v>
       </c>
       <c r="H292" t="n">
         <v>56483</v>
@@ -8895,7 +8895,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G294" t="n">
-        <v>5.00268411636353</v>
+        <v>5.00268459320068</v>
       </c>
       <c r="H294" t="n">
         <v>22069</v>
@@ -8924,7 +8924,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G295" t="n">
-        <v>4.99930047988892</v>
+        <v>4.99930000305176</v>
       </c>
       <c r="H295" t="n">
         <v>48006</v>
@@ -8982,7 +8982,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G297" t="n">
-        <v>4.96883630752563</v>
+        <v>4.96883678436279</v>
       </c>
       <c r="H297" t="n">
         <v>116952</v>
@@ -9040,7 +9040,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93160390853882</v>
+        <v>4.93160438537598</v>
       </c>
       <c r="H299" t="n">
         <v>39182</v>
@@ -9098,7 +9098,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>5.0636100769043</v>
+        <v>5.06360960006714</v>
       </c>
       <c r="H301" t="n">
         <v>60114</v>
@@ -9127,7 +9127,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>5.04330158233643</v>
+        <v>5.04330205917358</v>
       </c>
       <c r="H302" t="n">
         <v>60086</v>
@@ -9156,7 +9156,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G303" t="n">
-        <v>5.03991746902466</v>
+        <v>5.03991651535034</v>
       </c>
       <c r="H303" t="n">
         <v>64927</v>
@@ -9214,7 +9214,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>5.02299308776855</v>
+        <v>5.0229926109314</v>
       </c>
       <c r="H305" t="n">
         <v>157822</v>
@@ -9272,7 +9272,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G307" t="n">
-        <v>5.07037973403931</v>
+        <v>5.07038021087646</v>
       </c>
       <c r="H307" t="n">
         <v>101547</v>
@@ -9330,7 +9330,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G309" t="n">
-        <v>5.00268411636353</v>
+        <v>5.00268459320068</v>
       </c>
       <c r="H309" t="n">
         <v>46538</v>
@@ -9417,7 +9417,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.24638748168945</v>
+        <v>5.24638795852661</v>
       </c>
       <c r="H312" t="n">
         <v>141942</v>
@@ -9446,7 +9446,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G313" t="n">
-        <v>5.29377412796021</v>
+        <v>5.29377508163452</v>
       </c>
       <c r="H313" t="n">
         <v>49635</v>
@@ -9620,7 +9620,7 @@
         <v>8</v>
       </c>
       <c r="G319" t="n">
-        <v>5.41562604904175</v>
+        <v>5.41562652587891</v>
       </c>
       <c r="H319" t="n">
         <v>179752</v>
@@ -9649,7 +9649,7 @@
         <v>7.875</v>
       </c>
       <c r="G320" t="n">
-        <v>5.33100652694702</v>
+        <v>5.33100605010986</v>
       </c>
       <c r="H320" t="n">
         <v>67075</v>
@@ -9736,7 +9736,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G323" t="n">
-        <v>5.32762241363525</v>
+        <v>5.3276219367981</v>
       </c>
       <c r="H323" t="n">
         <v>45868</v>
@@ -9794,7 +9794,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>5.17869234085083</v>
+        <v>5.17869281768799</v>
       </c>
       <c r="H325" t="n">
         <v>114001</v>
@@ -9852,7 +9852,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>5.17869234085083</v>
+        <v>5.17869281768799</v>
       </c>
       <c r="H327" t="n">
         <v>28662</v>
@@ -9881,7 +9881,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>5.14484453201294</v>
+        <v>5.1448450088501</v>
       </c>
       <c r="H328" t="n">
         <v>90125</v>
@@ -9910,7 +9910,7 @@
         <v>7.56500005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>5.12115144729614</v>
+        <v>5.12115097045898</v>
       </c>
       <c r="H329" t="n">
         <v>147045</v>
@@ -9968,7 +9968,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.94852876663208</v>
+        <v>4.94852828979492</v>
       </c>
       <c r="H331" t="n">
         <v>123182</v>
@@ -10026,7 +10026,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>4.97899103164673</v>
+        <v>4.97899150848389</v>
       </c>
       <c r="H333" t="n">
         <v>75688</v>
@@ -10055,7 +10055,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>4.92483568191528</v>
+        <v>4.92483520507812</v>
       </c>
       <c r="H334" t="n">
         <v>56297</v>
@@ -10084,7 +10084,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>4.95868253707886</v>
+        <v>4.95868301391602</v>
       </c>
       <c r="H335" t="n">
         <v>87438</v>
@@ -10374,7 +10374,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.23200082778931</v>
+        <v>5.23200130462646</v>
       </c>
       <c r="H345" t="n">
         <v>74072</v>
@@ -10432,7 +10432,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G347" t="n">
-        <v>5.26302099227905</v>
+        <v>5.26302051544189</v>
       </c>
       <c r="H347" t="n">
         <v>109151</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>5.156174659729</v>
+        <v>5.15617418289185</v>
       </c>
       <c r="H348" t="n">
         <v>77577</v>
@@ -10490,7 +10490,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G349" t="n">
-        <v>5.12170839309692</v>
+        <v>5.12170743942261</v>
       </c>
       <c r="H349" t="n">
         <v>53144</v>
@@ -10519,7 +10519,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G350" t="n">
-        <v>4.81840372085571</v>
+        <v>4.81840419769287</v>
       </c>
       <c r="H350" t="n">
         <v>315554</v>
@@ -10548,7 +10548,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>4.71500396728516</v>
+        <v>4.71500444412231</v>
       </c>
       <c r="H351" t="n">
         <v>350968</v>
@@ -10577,7 +10577,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G352" t="n">
-        <v>4.6253924369812</v>
+        <v>4.62539196014404</v>
       </c>
       <c r="H352" t="n">
         <v>133593</v>
@@ -10606,7 +10606,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>4.6770920753479</v>
+        <v>4.67709159851074</v>
       </c>
       <c r="H353" t="n">
         <v>174018</v>
@@ -10635,7 +10635,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>4.72189855575562</v>
+        <v>4.72189807891846</v>
       </c>
       <c r="H354" t="n">
         <v>62590</v>
@@ -10751,7 +10751,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G358" t="n">
-        <v>4.58747863769531</v>
+        <v>4.58747911453247</v>
       </c>
       <c r="H358" t="n">
         <v>52219</v>
@@ -10780,7 +10780,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G359" t="n">
-        <v>4.61849880218506</v>
+        <v>4.6184983253479</v>
       </c>
       <c r="H359" t="n">
         <v>63329</v>
@@ -10809,7 +10809,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G360" t="n">
-        <v>4.54611921310425</v>
+        <v>4.54611873626709</v>
       </c>
       <c r="H360" t="n">
         <v>35793</v>
@@ -10925,7 +10925,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G364" t="n">
-        <v>4.44616651535034</v>
+        <v>4.4461669921875</v>
       </c>
       <c r="H364" t="n">
         <v>42653</v>
@@ -10954,7 +10954,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>4.36689329147339</v>
+        <v>4.36689376831055</v>
       </c>
       <c r="H365" t="n">
         <v>92594</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>4.26004838943481</v>
+        <v>4.26004791259766</v>
       </c>
       <c r="H367" t="n">
         <v>48450</v>
@@ -11099,7 +11099,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G370" t="n">
-        <v>4.37378692626953</v>
+        <v>4.37378644943237</v>
       </c>
       <c r="H370" t="n">
         <v>115367</v>
@@ -11128,7 +11128,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>4.32898044586182</v>
+        <v>4.32898139953613</v>
       </c>
       <c r="H371" t="n">
         <v>89129</v>
@@ -11215,7 +11215,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>4.17043590545654</v>
+        <v>4.17043542861938</v>
       </c>
       <c r="H374" t="n">
         <v>551406</v>
@@ -11244,7 +11244,7 @@
         <v>6.25</v>
       </c>
       <c r="G375" t="n">
-        <v>4.30830144882202</v>
+        <v>4.30830097198486</v>
       </c>
       <c r="H375" t="n">
         <v>83151</v>
@@ -11331,7 +11331,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>4.23592138290405</v>
+        <v>4.23592185974121</v>
       </c>
       <c r="H378" t="n">
         <v>77420</v>
@@ -11360,7 +11360,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>4.20834827423096</v>
+        <v>4.20834875106812</v>
       </c>
       <c r="H379" t="n">
         <v>84265</v>
@@ -11389,7 +11389,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G380" t="n">
-        <v>4.26349496841431</v>
+        <v>4.26349449157715</v>
       </c>
       <c r="H380" t="n">
         <v>44696</v>
@@ -11476,7 +11476,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>4.37378692626953</v>
+        <v>4.37378644943237</v>
       </c>
       <c r="H383" t="n">
         <v>133689</v>
@@ -11534,7 +11534,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>4.51510000228882</v>
+        <v>4.51509952545166</v>
       </c>
       <c r="H385" t="n">
         <v>184215</v>
@@ -11563,7 +11563,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>4.49786615371704</v>
+        <v>4.4978666305542</v>
       </c>
       <c r="H386" t="n">
         <v>69957</v>
@@ -11592,7 +11592,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>4.44961309432983</v>
+        <v>4.44961357116699</v>
       </c>
       <c r="H387" t="n">
         <v>59662</v>
@@ -11621,7 +11621,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>4.37723350524902</v>
+        <v>4.37723398208618</v>
       </c>
       <c r="H388" t="n">
         <v>60247</v>
@@ -11650,7 +11650,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G389" t="n">
-        <v>4.32898044586182</v>
+        <v>4.32898139953613</v>
       </c>
       <c r="H389" t="n">
         <v>38008</v>
@@ -11679,7 +11679,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>4.49442005157471</v>
+        <v>4.49441909790039</v>
       </c>
       <c r="H390" t="n">
         <v>149419</v>
@@ -11708,7 +11708,7 @@
         <v>6.625</v>
       </c>
       <c r="G391" t="n">
-        <v>4.56679964065552</v>
+        <v>4.5667986869812</v>
       </c>
       <c r="H391" t="n">
         <v>195950</v>
@@ -11737,7 +11737,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>4.62883901596069</v>
+        <v>4.62883853912354</v>
       </c>
       <c r="H392" t="n">
         <v>73105</v>
@@ -11853,7 +11853,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>4.70811128616333</v>
+        <v>4.70811176300049</v>
       </c>
       <c r="H396" t="n">
         <v>978763</v>
@@ -11882,7 +11882,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G397" t="n">
-        <v>4.64262533187866</v>
+        <v>4.64262580871582</v>
       </c>
       <c r="H397" t="n">
         <v>509615</v>
@@ -11911,7 +11911,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>4.6253924369812</v>
+        <v>4.62539196014404</v>
       </c>
       <c r="H398" t="n">
         <v>86308</v>
@@ -11940,7 +11940,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>4.50820589065552</v>
+        <v>4.50820636749268</v>
       </c>
       <c r="H399" t="n">
         <v>56545</v>
@@ -11969,7 +11969,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>4.58403253555298</v>
+        <v>4.58403205871582</v>
       </c>
       <c r="H400" t="n">
         <v>49686</v>
@@ -12027,7 +12027,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>4.5219931602478</v>
+        <v>4.52199268341064</v>
       </c>
       <c r="H402" t="n">
         <v>98507</v>
@@ -12056,7 +12056,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>4.53577899932861</v>
+        <v>4.53577947616577</v>
       </c>
       <c r="H403" t="n">
         <v>44497</v>
@@ -12085,7 +12085,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>4.42548656463623</v>
+        <v>4.42548704147339</v>
       </c>
       <c r="H404" t="n">
         <v>58646</v>
@@ -12114,7 +12114,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>4.49786615371704</v>
+        <v>4.4978666305542</v>
       </c>
       <c r="H405" t="n">
         <v>38550</v>
@@ -12172,7 +12172,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.44616651535034</v>
+        <v>4.4461669921875</v>
       </c>
       <c r="H407" t="n">
         <v>69081</v>
@@ -12201,7 +12201,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G408" t="n">
-        <v>4.45995330810547</v>
+        <v>4.45995283126831</v>
       </c>
       <c r="H408" t="n">
         <v>41217</v>
@@ -12288,7 +12288,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>4.58403253555298</v>
+        <v>4.58403205871582</v>
       </c>
       <c r="H411" t="n">
         <v>48654</v>
@@ -12346,7 +12346,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.46339988708496</v>
+        <v>4.46340036392212</v>
       </c>
       <c r="H413" t="n">
         <v>62096</v>
@@ -12375,7 +12375,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.39102029800415</v>
+        <v>4.39101982116699</v>
       </c>
       <c r="H414" t="n">
         <v>238804</v>
@@ -12404,7 +12404,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G415" t="n">
-        <v>4.44616651535034</v>
+        <v>4.4461669921875</v>
       </c>
       <c r="H415" t="n">
         <v>62047</v>
@@ -12462,7 +12462,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>4.42548656463623</v>
+        <v>4.42548704147339</v>
       </c>
       <c r="H417" t="n">
         <v>91936</v>
@@ -12578,7 +12578,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G421" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281549453735</v>
       </c>
       <c r="H421" t="n">
         <v>57686</v>
@@ -12636,7 +12636,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G423" t="n">
-        <v>4.26694107055664</v>
+        <v>4.2669415473938</v>
       </c>
       <c r="H423" t="n">
         <v>19643</v>
@@ -12723,7 +12723,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G426" t="n">
-        <v>4.26694107055664</v>
+        <v>4.2669415473938</v>
       </c>
       <c r="H426" t="n">
         <v>27461</v>
@@ -12868,7 +12868,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281549453735</v>
       </c>
       <c r="H431" t="n">
         <v>97071</v>
@@ -12926,7 +12926,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281549453735</v>
       </c>
       <c r="H433" t="n">
         <v>49792</v>
@@ -12955,7 +12955,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G434" t="n">
-        <v>4.26694107055664</v>
+        <v>4.2669415473938</v>
       </c>
       <c r="H434" t="n">
         <v>73386</v>
@@ -12984,7 +12984,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>4.28072834014893</v>
+        <v>4.28072786331177</v>
       </c>
       <c r="H435" t="n">
         <v>67345</v>
@@ -13216,7 +13216,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G443" t="n">
-        <v>3.37081456184387</v>
+        <v>3.37081480026245</v>
       </c>
       <c r="H443" t="n">
         <v>202384</v>
@@ -13245,7 +13245,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G444" t="n">
-        <v>3.4425048828125</v>
+        <v>3.44250512123108</v>
       </c>
       <c r="H444" t="n">
         <v>322860</v>
@@ -13274,7 +13274,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G445" t="n">
-        <v>3.44526219367981</v>
+        <v>3.44526243209839</v>
       </c>
       <c r="H445" t="n">
         <v>243913</v>
@@ -13303,7 +13303,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G446" t="n">
-        <v>3.42458248138428</v>
+        <v>3.4245822429657</v>
       </c>
       <c r="H446" t="n">
         <v>285105</v>
@@ -13332,7 +13332,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>3.42596101760864</v>
+        <v>3.42596077919006</v>
       </c>
       <c r="H447" t="n">
         <v>173870</v>
@@ -13361,7 +13361,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G448" t="n">
-        <v>3.43699026107788</v>
+        <v>3.4369900226593</v>
       </c>
       <c r="H448" t="n">
         <v>109773</v>
@@ -13390,7 +13390,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.42596101760864</v>
+        <v>3.42596077919006</v>
       </c>
       <c r="H449" t="n">
         <v>172863</v>
@@ -13419,7 +13419,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G450" t="n">
-        <v>3.38046550750732</v>
+        <v>3.38046526908875</v>
       </c>
       <c r="H450" t="n">
         <v>226892</v>
@@ -13477,7 +13477,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G452" t="n">
-        <v>3.2398419380188</v>
+        <v>3.23984217643738</v>
       </c>
       <c r="H452" t="n">
         <v>504346</v>
@@ -13535,7 +13535,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G454" t="n">
-        <v>3.05372381210327</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H454" t="n">
         <v>402906</v>
@@ -13564,7 +13564,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G455" t="n">
-        <v>2.99719858169556</v>
+        <v>2.99719905853271</v>
       </c>
       <c r="H455" t="n">
         <v>496484</v>
@@ -13622,7 +13622,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>3.06751036643982</v>
+        <v>3.0675106048584</v>
       </c>
       <c r="H457" t="n">
         <v>523527</v>
@@ -13738,7 +13738,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G461" t="n">
-        <v>2.95446038246155</v>
+        <v>2.95446062088013</v>
       </c>
       <c r="H461" t="n">
         <v>328173</v>
@@ -13767,7 +13767,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G462" t="n">
-        <v>2.86898374557495</v>
+        <v>2.86898398399353</v>
       </c>
       <c r="H462" t="n">
         <v>600471</v>
@@ -13796,7 +13796,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G463" t="n">
-        <v>2.84830403327942</v>
+        <v>2.84830379486084</v>
       </c>
       <c r="H463" t="n">
         <v>341520</v>
@@ -13825,7 +13825,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G464" t="n">
-        <v>2.8772554397583</v>
+        <v>2.87725567817688</v>
       </c>
       <c r="H464" t="n">
         <v>725032</v>
@@ -13854,7 +13854,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>2.99857711791992</v>
+        <v>2.99857759475708</v>
       </c>
       <c r="H465" t="n">
         <v>452097</v>
@@ -13883,7 +13883,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G466" t="n">
-        <v>2.98479080200195</v>
+        <v>2.98479127883911</v>
       </c>
       <c r="H466" t="n">
         <v>406773</v>
@@ -13912,7 +13912,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G467" t="n">
-        <v>2.99857711791992</v>
+        <v>2.99857759475708</v>
       </c>
       <c r="H467" t="n">
         <v>369874</v>
@@ -13941,7 +13941,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G468" t="n">
-        <v>2.89655709266663</v>
+        <v>2.89655685424805</v>
       </c>
       <c r="H468" t="n">
         <v>587468</v>
@@ -13970,7 +13970,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>2.86071228981018</v>
+        <v>2.86071181297302</v>
       </c>
       <c r="H469" t="n">
         <v>326227</v>
@@ -13999,7 +13999,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G470" t="n">
-        <v>2.83727502822876</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H470" t="n">
         <v>239632</v>
@@ -14028,7 +14028,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G471" t="n">
-        <v>2.86898374557495</v>
+        <v>2.86898398399353</v>
       </c>
       <c r="H471" t="n">
         <v>254832</v>
@@ -14057,7 +14057,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G472" t="n">
-        <v>3.04545187950134</v>
+        <v>3.04545211791992</v>
       </c>
       <c r="H472" t="n">
         <v>1192003</v>
@@ -14115,7 +14115,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G474" t="n">
-        <v>3.07026743888855</v>
+        <v>3.07026767730713</v>
       </c>
       <c r="H474" t="n">
         <v>582857</v>
@@ -14173,7 +14173,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>2.94343113899231</v>
+        <v>2.94343137741089</v>
       </c>
       <c r="H476" t="n">
         <v>398406</v>
@@ -14202,7 +14202,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.86071228981018</v>
+        <v>2.86071181297302</v>
       </c>
       <c r="H477" t="n">
         <v>523481</v>
@@ -14231,7 +14231,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>2.82624530792236</v>
+        <v>2.82624554634094</v>
       </c>
       <c r="H478" t="n">
         <v>369252</v>
@@ -14289,7 +14289,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G480" t="n">
-        <v>2.6111752986908</v>
+        <v>2.61117506027222</v>
       </c>
       <c r="H480" t="n">
         <v>1100000</v>
@@ -14318,7 +14318,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G481" t="n">
-        <v>2.7049241065979</v>
+        <v>2.70492386817932</v>
       </c>
       <c r="H481" t="n">
         <v>410944</v>
@@ -14347,7 +14347,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692525863647</v>
       </c>
       <c r="H482" t="n">
         <v>511759</v>
@@ -14608,7 +14608,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G491" t="n">
-        <v>2.83727502822876</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H491" t="n">
         <v>684752</v>
@@ -14666,7 +14666,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>2.88139176368713</v>
+        <v>2.88139152526855</v>
       </c>
       <c r="H493" t="n">
         <v>495399</v>
@@ -14695,7 +14695,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G494" t="n">
-        <v>2.90896439552307</v>
+        <v>2.90896463394165</v>
       </c>
       <c r="H494" t="n">
         <v>188877</v>
@@ -14724,7 +14724,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>2.94756746292114</v>
+        <v>2.94756722450256</v>
       </c>
       <c r="H495" t="n">
         <v>203717</v>
@@ -14753,7 +14753,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G496" t="n">
-        <v>2.88690662384033</v>
+        <v>2.88690638542175</v>
       </c>
       <c r="H496" t="n">
         <v>205236</v>
@@ -14898,7 +14898,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G501" t="n">
-        <v>2.8772554397583</v>
+        <v>2.87725567817688</v>
       </c>
       <c r="H501" t="n">
         <v>128616</v>
@@ -14985,7 +14985,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G504" t="n">
-        <v>2.81935238838196</v>
+        <v>2.81935214996338</v>
       </c>
       <c r="H504" t="n">
         <v>148517</v>
@@ -15014,7 +15014,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>2.86760497093201</v>
+        <v>2.86760520935059</v>
       </c>
       <c r="H505" t="n">
         <v>191845</v>
@@ -15043,7 +15043,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>2.82624530792236</v>
+        <v>2.82624554634094</v>
       </c>
       <c r="H506" t="n">
         <v>127666</v>
@@ -15159,7 +15159,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G510" t="n">
-        <v>2.88690662384033</v>
+        <v>2.88690638542175</v>
       </c>
       <c r="H510" t="n">
         <v>93443</v>
@@ -15188,7 +15188,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G511" t="n">
-        <v>2.83727502822876</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H511" t="n">
         <v>100855</v>
@@ -15217,7 +15217,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>2.90207195281982</v>
+        <v>2.90207147598267</v>
       </c>
       <c r="H512" t="n">
         <v>89744</v>
@@ -15275,7 +15275,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G514" t="n">
-        <v>2.95032477378845</v>
+        <v>2.95032501220703</v>
       </c>
       <c r="H514" t="n">
         <v>134249</v>
@@ -15304,7 +15304,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.07440400123596</v>
+        <v>3.0744035243988</v>
       </c>
       <c r="H515" t="n">
         <v>445325</v>
@@ -15333,7 +15333,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G516" t="n">
-        <v>3.22605562210083</v>
+        <v>3.22605609893799</v>
       </c>
       <c r="H516" t="n">
         <v>664170</v>
@@ -15362,7 +15362,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>3.16401648521423</v>
+        <v>3.16401624679565</v>
       </c>
       <c r="H517" t="n">
         <v>613794</v>
@@ -15420,7 +15420,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H519" t="n">
         <v>718475</v>
@@ -15478,7 +15478,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G521" t="n">
-        <v>3.1778028011322</v>
+        <v>3.17780327796936</v>
       </c>
       <c r="H521" t="n">
         <v>462498</v>
@@ -15507,7 +15507,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G522" t="n">
-        <v>3.16746258735657</v>
+        <v>3.16746282577515</v>
       </c>
       <c r="H522" t="n">
         <v>493955</v>
@@ -15536,7 +15536,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.13299655914307</v>
+        <v>3.13299679756165</v>
       </c>
       <c r="H523" t="n">
         <v>379353</v>
@@ -15565,7 +15565,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>3.07440400123596</v>
+        <v>3.0744035243988</v>
       </c>
       <c r="H524" t="n">
         <v>415874</v>
@@ -15652,7 +15652,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G527" t="n">
-        <v>3.14678311347961</v>
+        <v>3.14678335189819</v>
       </c>
       <c r="H527" t="n">
         <v>306906</v>
@@ -15681,7 +15681,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>3.09508323669434</v>
+        <v>3.09508299827576</v>
       </c>
       <c r="H528" t="n">
         <v>253894</v>
@@ -15710,7 +15710,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G529" t="n">
-        <v>3.09508323669434</v>
+        <v>3.09508299827576</v>
       </c>
       <c r="H529" t="n">
         <v>186227</v>
@@ -15739,7 +15739,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G530" t="n">
-        <v>3.1950364112854</v>
+        <v>3.19503617286682</v>
       </c>
       <c r="H530" t="n">
         <v>364125</v>
@@ -15768,7 +15768,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>3.14333653450012</v>
+        <v>3.1433367729187</v>
       </c>
       <c r="H531" t="n">
         <v>265328</v>
@@ -15826,7 +15826,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>3.04683065414429</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H533" t="n">
         <v>319024</v>
@@ -15855,7 +15855,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>3.02959728240967</v>
+        <v>3.02959704399109</v>
       </c>
       <c r="H534" t="n">
         <v>317377</v>
@@ -15884,7 +15884,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>3.03304386138916</v>
+        <v>3.03304433822632</v>
       </c>
       <c r="H535" t="n">
         <v>491731</v>
@@ -15913,7 +15913,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>2.98479080200195</v>
+        <v>2.98479127883911</v>
       </c>
       <c r="H536" t="n">
         <v>519676</v>
@@ -16000,7 +16000,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>2.81245875358582</v>
+        <v>2.81245899200439</v>
       </c>
       <c r="H539" t="n">
         <v>482372</v>
@@ -16029,7 +16029,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.7848858833313</v>
+        <v>2.78488564491272</v>
       </c>
       <c r="H540" t="n">
         <v>280515</v>
@@ -16087,7 +16087,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.71595287322998</v>
+        <v>2.71595311164856</v>
       </c>
       <c r="H542" t="n">
         <v>324677</v>
@@ -16116,7 +16116,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>3.04683065414429</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H543" t="n">
         <v>812045</v>
@@ -16174,7 +16174,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>3.07440400123596</v>
+        <v>3.0744035243988</v>
       </c>
       <c r="H545" t="n">
         <v>546449</v>
@@ -16232,7 +16232,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06406354904175</v>
+        <v>3.06406378746033</v>
       </c>
       <c r="H547" t="n">
         <v>404236</v>
@@ -16261,7 +16261,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>3.04338383674622</v>
+        <v>3.04338407516479</v>
       </c>
       <c r="H548" t="n">
         <v>383699</v>
@@ -16319,7 +16319,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G550" t="n">
-        <v>3.05372381210327</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H550" t="n">
         <v>238836</v>
@@ -16377,7 +16377,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G552" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H552" t="n">
         <v>511233</v>
@@ -16406,7 +16406,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G553" t="n">
-        <v>3.00547099113464</v>
+        <v>3.00547075271606</v>
       </c>
       <c r="H553" t="n">
         <v>251650</v>
@@ -16435,7 +16435,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>2.96066427230835</v>
+        <v>2.96066451072693</v>
       </c>
       <c r="H554" t="n">
         <v>294528</v>
@@ -16464,7 +16464,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>2.90551829338074</v>
+        <v>2.90551853179932</v>
       </c>
       <c r="H555" t="n">
         <v>393098</v>
@@ -16493,7 +16493,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.90207195281982</v>
+        <v>2.90207147598267</v>
       </c>
       <c r="H556" t="n">
         <v>262821</v>
@@ -16522,7 +16522,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G557" t="n">
-        <v>3.05372381210327</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H557" t="n">
         <v>922577</v>
@@ -16551,7 +16551,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>3.07440400123596</v>
+        <v>3.0744035243988</v>
       </c>
       <c r="H558" t="n">
         <v>671261</v>
@@ -16638,7 +16638,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G561" t="n">
-        <v>2.96755790710449</v>
+        <v>2.96755766868591</v>
       </c>
       <c r="H561" t="n">
         <v>425732</v>
@@ -16696,7 +16696,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.88483834266663</v>
+        <v>2.88483858108521</v>
       </c>
       <c r="H563" t="n">
         <v>720599</v>
@@ -16725,7 +16725,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G564" t="n">
-        <v>2.8951780796051</v>
+        <v>2.89517831802368</v>
       </c>
       <c r="H564" t="n">
         <v>235509</v>
@@ -16841,7 +16841,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G568" t="n">
-        <v>2.90896439552307</v>
+        <v>2.90896463394165</v>
       </c>
       <c r="H568" t="n">
         <v>292000</v>
@@ -16870,7 +16870,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>2.86760497093201</v>
+        <v>2.86760520935059</v>
       </c>
       <c r="H569" t="n">
         <v>414211</v>
@@ -16928,7 +16928,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692525863647</v>
       </c>
       <c r="H571" t="n">
         <v>165452</v>
@@ -16957,7 +16957,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G572" t="n">
-        <v>2.8882851600647</v>
+        <v>2.88828539848328</v>
       </c>
       <c r="H572" t="n">
         <v>156197</v>
@@ -16986,7 +16986,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>2.87449860572815</v>
+        <v>2.87449836730957</v>
       </c>
       <c r="H573" t="n">
         <v>91271</v>
@@ -17015,7 +17015,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G574" t="n">
-        <v>2.99857711791992</v>
+        <v>2.99857759475708</v>
       </c>
       <c r="H574" t="n">
         <v>643404</v>
@@ -17073,7 +17073,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>2.9468777179718</v>
+        <v>2.94687795639038</v>
       </c>
       <c r="H576" t="n">
         <v>152196</v>
@@ -17102,7 +17102,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>2.99168467521667</v>
+        <v>2.99168419837952</v>
       </c>
       <c r="H577" t="n">
         <v>238890</v>
@@ -17160,7 +17160,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>2.96066427230835</v>
+        <v>2.96066451072693</v>
       </c>
       <c r="H579" t="n">
         <v>72514</v>
@@ -17218,7 +17218,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G581" t="n">
-        <v>2.96411156654358</v>
+        <v>2.96411108970642</v>
       </c>
       <c r="H581" t="n">
         <v>83737</v>
@@ -17276,7 +17276,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G583" t="n">
-        <v>2.99857711791992</v>
+        <v>2.99857759475708</v>
       </c>
       <c r="H583" t="n">
         <v>144105</v>
@@ -17334,7 +17334,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>2.9882378578186</v>
+        <v>2.98823761940002</v>
       </c>
       <c r="H585" t="n">
         <v>198148</v>
@@ -17363,7 +17363,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G586" t="n">
-        <v>2.99168467521667</v>
+        <v>2.99168419837952</v>
       </c>
       <c r="H586" t="n">
         <v>163016</v>
@@ -17392,7 +17392,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.99857711791992</v>
+        <v>2.99857759475708</v>
       </c>
       <c r="H587" t="n">
         <v>136824</v>
@@ -17450,7 +17450,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>3.04683065414429</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H589" t="n">
         <v>119110</v>
@@ -17479,7 +17479,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>3.06751036643982</v>
+        <v>3.0675106048584</v>
       </c>
       <c r="H590" t="n">
         <v>378785</v>
@@ -17508,7 +17508,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>3.07095694541931</v>
+        <v>3.07095718383789</v>
       </c>
       <c r="H591" t="n">
         <v>195836</v>
@@ -17537,7 +17537,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G592" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H592" t="n">
         <v>233898</v>
@@ -17566,7 +17566,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G593" t="n">
-        <v>3.00891733169556</v>
+        <v>3.00891709327698</v>
       </c>
       <c r="H593" t="n">
         <v>230140</v>
@@ -17595,7 +17595,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G594" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H594" t="n">
         <v>68851</v>
@@ -17624,7 +17624,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G595" t="n">
-        <v>2.99857711791992</v>
+        <v>2.99857759475708</v>
       </c>
       <c r="H595" t="n">
         <v>248356</v>
@@ -17653,7 +17653,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G596" t="n">
-        <v>3.00891733169556</v>
+        <v>3.00891709327698</v>
       </c>
       <c r="H596" t="n">
         <v>122410</v>
@@ -17682,7 +17682,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03304386138916</v>
+        <v>3.03304433822632</v>
       </c>
       <c r="H597" t="n">
         <v>163365</v>
@@ -17711,7 +17711,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>3.04683065414429</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H598" t="n">
         <v>158703</v>
@@ -17798,7 +17798,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G601" t="n">
-        <v>3.01925754547119</v>
+        <v>3.01925730705261</v>
       </c>
       <c r="H601" t="n">
         <v>220818</v>
@@ -17827,7 +17827,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G602" t="n">
-        <v>3.0227038860321</v>
+        <v>3.02270412445068</v>
       </c>
       <c r="H602" t="n">
         <v>358951</v>
@@ -17856,7 +17856,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G603" t="n">
-        <v>3.09027028083801</v>
+        <v>3.09027004241943</v>
       </c>
       <c r="H603" t="n">
         <v>195385</v>
@@ -17885,7 +17885,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G604" t="n">
-        <v>2.99425506591797</v>
+        <v>2.99425482749939</v>
       </c>
       <c r="H604" t="n">
         <v>852809</v>
@@ -17914,7 +17914,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G605" t="n">
-        <v>2.9480254650116</v>
+        <v>2.94802522659302</v>
       </c>
       <c r="H605" t="n">
         <v>276475</v>
@@ -17972,7 +17972,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>2.95513772964478</v>
+        <v>2.95513796806335</v>
       </c>
       <c r="H607" t="n">
         <v>101236</v>
@@ -18001,7 +18001,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>2.94091320037842</v>
+        <v>2.940913438797</v>
       </c>
       <c r="H608" t="n">
         <v>161778</v>
@@ -18030,7 +18030,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G609" t="n">
-        <v>2.96224975585938</v>
+        <v>2.96224999427795</v>
       </c>
       <c r="H609" t="n">
         <v>120210</v>
@@ -18146,7 +18146,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G613" t="n">
-        <v>2.75955080986023</v>
+        <v>2.75955128669739</v>
       </c>
       <c r="H613" t="n">
         <v>405706</v>
@@ -18175,7 +18175,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>2.62086224555969</v>
+        <v>2.62086200714111</v>
       </c>
       <c r="H614" t="n">
         <v>585601</v>
@@ -18204,7 +18204,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G615" t="n">
-        <v>2.64219903945923</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H615" t="n">
         <v>208013</v>
@@ -18320,7 +18320,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G619" t="n">
-        <v>2.57107615470886</v>
+        <v>2.57107639312744</v>
       </c>
       <c r="H619" t="n">
         <v>188588</v>
@@ -18378,7 +18378,7 @@
         <v>3.625</v>
       </c>
       <c r="G621" t="n">
-        <v>2.5781888961792</v>
+        <v>2.57818865776062</v>
       </c>
       <c r="H621" t="n">
         <v>419710</v>
@@ -18465,7 +18465,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.61019396781921</v>
+        <v>2.61019372940063</v>
       </c>
       <c r="H624" t="n">
         <v>152498</v>
@@ -18523,7 +18523,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G626" t="n">
-        <v>2.70265316963196</v>
+        <v>2.7026526927948</v>
       </c>
       <c r="H626" t="n">
         <v>282059</v>
@@ -18581,7 +18581,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>2.69554042816162</v>
+        <v>2.69554090499878</v>
       </c>
       <c r="H628" t="n">
         <v>49387</v>
@@ -18639,7 +18639,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>2.69909715652466</v>
+        <v>2.6990966796875</v>
       </c>
       <c r="H630" t="n">
         <v>92589</v>
@@ -18755,7 +18755,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G634" t="n">
-        <v>2.52484703063965</v>
+        <v>2.52484655380249</v>
       </c>
       <c r="H634" t="n">
         <v>311041</v>
@@ -18784,7 +18784,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>2.59241318702698</v>
+        <v>2.59241342544556</v>
       </c>
       <c r="H635" t="n">
         <v>247960</v>
@@ -18813,7 +18813,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G636" t="n">
-        <v>2.56752038002014</v>
+        <v>2.56752014160156</v>
       </c>
       <c r="H636" t="n">
         <v>270034</v>
@@ -18842,7 +18842,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>2.75955080986023</v>
+        <v>2.75955128669739</v>
       </c>
       <c r="H637" t="n">
         <v>1233044</v>
@@ -18900,7 +18900,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>2.69909715652466</v>
+        <v>2.6990966796875</v>
       </c>
       <c r="H639" t="n">
         <v>229295</v>
@@ -18958,7 +18958,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G641" t="n">
-        <v>2.74177050590515</v>
+        <v>2.74177026748657</v>
       </c>
       <c r="H641" t="n">
         <v>183565</v>
@@ -19016,7 +19016,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G643" t="n">
-        <v>2.86267852783203</v>
+        <v>2.86267828941345</v>
       </c>
       <c r="H643" t="n">
         <v>152428</v>
@@ -19074,7 +19074,7 @@
         <v>4</v>
       </c>
       <c r="G645" t="n">
-        <v>2.84489774703979</v>
+        <v>2.84489798545837</v>
       </c>
       <c r="H645" t="n">
         <v>243773</v>
@@ -19103,7 +19103,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.76310682296753</v>
+        <v>2.76310706138611</v>
       </c>
       <c r="H646" t="n">
         <v>215881</v>
@@ -19161,7 +19161,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.75955080986023</v>
+        <v>2.75955128669739</v>
       </c>
       <c r="H648" t="n">
         <v>60056</v>
@@ -19248,7 +19248,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G651" t="n">
-        <v>2.76310682296753</v>
+        <v>2.76310706138611</v>
       </c>
       <c r="H651" t="n">
         <v>100165</v>
@@ -19277,7 +19277,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G652" t="n">
-        <v>2.6884286403656</v>
+        <v>2.68842840194702</v>
       </c>
       <c r="H652" t="n">
         <v>236999</v>
@@ -19306,7 +19306,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G653" t="n">
-        <v>2.65642333030701</v>
+        <v>2.65642309188843</v>
       </c>
       <c r="H653" t="n">
         <v>170086</v>
@@ -19393,7 +19393,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>2.65642333030701</v>
+        <v>2.65642309188843</v>
       </c>
       <c r="H656" t="n">
         <v>97009</v>
@@ -19422,7 +19422,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G657" t="n">
-        <v>2.75955080986023</v>
+        <v>2.75955128669739</v>
       </c>
       <c r="H657" t="n">
         <v>241707</v>
@@ -19480,7 +19480,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G659" t="n">
-        <v>2.75243830680847</v>
+        <v>2.75243854522705</v>
       </c>
       <c r="H659" t="n">
         <v>65346</v>
@@ -19509,7 +19509,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G660" t="n">
-        <v>2.70620894432068</v>
+        <v>2.70620918273926</v>
       </c>
       <c r="H660" t="n">
         <v>139089</v>
@@ -19538,7 +19538,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>2.63864254951477</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H661" t="n">
         <v>201031</v>
@@ -19596,7 +19596,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G663" t="n">
-        <v>2.64219903945923</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H663" t="n">
         <v>40573</v>
@@ -19654,7 +19654,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>2.69554042816162</v>
+        <v>2.69554090499878</v>
       </c>
       <c r="H665" t="n">
         <v>50667</v>
@@ -19683,7 +19683,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.6884286403656</v>
+        <v>2.68842840194702</v>
       </c>
       <c r="H666" t="n">
         <v>76007</v>
@@ -19741,7 +19741,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.63864254951477</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H668" t="n">
         <v>44363</v>
@@ -19799,7 +19799,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G670" t="n">
-        <v>2.60663747787476</v>
+        <v>2.60663771629333</v>
       </c>
       <c r="H670" t="n">
         <v>58784</v>
@@ -19828,7 +19828,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>2.64575505256653</v>
+        <v>2.64575481414795</v>
       </c>
       <c r="H671" t="n">
         <v>57464</v>
@@ -19915,7 +19915,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>2.82711744308472</v>
+        <v>2.82711720466614</v>
       </c>
       <c r="H674" t="n">
         <v>96667</v>
@@ -19944,7 +19944,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G675" t="n">
-        <v>2.77377557754517</v>
+        <v>2.77377533912659</v>
       </c>
       <c r="H675" t="n">
         <v>118597</v>
@@ -19973,7 +19973,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>2.77377557754517</v>
+        <v>2.77377533912659</v>
       </c>
       <c r="H676" t="n">
         <v>49199</v>
@@ -20002,7 +20002,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G677" t="n">
-        <v>2.74532651901245</v>
+        <v>2.74532628059387</v>
       </c>
       <c r="H677" t="n">
         <v>85052</v>
@@ -20031,7 +20031,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>2.64931130409241</v>
+        <v>2.64931106567383</v>
       </c>
       <c r="H678" t="n">
         <v>409416</v>
@@ -20089,7 +20089,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G680" t="n">
-        <v>2.64219903945923</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H680" t="n">
         <v>39267</v>
@@ -20118,7 +20118,7 @@
         <v>3.625</v>
       </c>
       <c r="G681" t="n">
-        <v>2.5781888961792</v>
+        <v>2.57818865776062</v>
       </c>
       <c r="H681" t="n">
         <v>50503</v>
@@ -20205,7 +20205,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G684" t="n">
-        <v>2.64931130409241</v>
+        <v>2.64931106567383</v>
       </c>
       <c r="H684" t="n">
         <v>34184</v>
@@ -20263,7 +20263,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>2.61019396781921</v>
+        <v>2.61019372940063</v>
       </c>
       <c r="H686" t="n">
         <v>148011</v>
@@ -20292,7 +20292,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>2.68131613731384</v>
+        <v>2.68131637573242</v>
       </c>
       <c r="H687" t="n">
         <v>229731</v>
@@ -20321,7 +20321,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G688" t="n">
-        <v>2.78800010681152</v>
+        <v>2.78799986839294</v>
       </c>
       <c r="H688" t="n">
         <v>284468</v>
@@ -20350,7 +20350,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G689" t="n">
-        <v>2.60308146476746</v>
+        <v>2.60308170318604</v>
       </c>
       <c r="H689" t="n">
         <v>365229</v>
@@ -20408,7 +20408,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>2.60663747787476</v>
+        <v>2.60663771629333</v>
       </c>
       <c r="H691" t="n">
         <v>97872</v>
@@ -20466,7 +20466,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G693" t="n">
-        <v>2.72043347358704</v>
+        <v>2.72043371200562</v>
       </c>
       <c r="H693" t="n">
         <v>192286</v>
@@ -20495,7 +20495,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021956443787</v>
       </c>
       <c r="H694" t="n">
         <v>165658</v>
@@ -20524,7 +20524,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G695" t="n">
-        <v>2.76310682296753</v>
+        <v>2.76310706138611</v>
       </c>
       <c r="H695" t="n">
         <v>180565</v>
@@ -20582,7 +20582,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G697" t="n">
-        <v>2.74177050590515</v>
+        <v>2.74177026748657</v>
       </c>
       <c r="H697" t="n">
         <v>62942</v>
@@ -20640,7 +20640,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>2.76666331291199</v>
+        <v>2.76666355133057</v>
       </c>
       <c r="H699" t="n">
         <v>45647</v>
@@ -20669,7 +20669,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>2.76666331291199</v>
+        <v>2.76666355133057</v>
       </c>
       <c r="H700" t="n">
         <v>74718</v>
@@ -20756,7 +20756,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>2.76310682296753</v>
+        <v>2.76310706138611</v>
       </c>
       <c r="H703" t="n">
         <v>104868</v>
@@ -20814,7 +20814,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G705" t="n">
-        <v>2.76666331291199</v>
+        <v>2.76666355133057</v>
       </c>
       <c r="H705" t="n">
         <v>80864</v>
@@ -20843,7 +20843,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>2.69909715652466</v>
+        <v>2.6990966796875</v>
       </c>
       <c r="H706" t="n">
         <v>112009</v>
@@ -20872,7 +20872,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G707" t="n">
-        <v>2.63864254951477</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H707" t="n">
         <v>112389</v>
@@ -20901,7 +20901,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730599403381</v>
       </c>
       <c r="H708" t="n">
         <v>94175</v>
@@ -20959,7 +20959,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50350975990295</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H710" t="n">
         <v>188934</v>
@@ -20988,7 +20988,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G711" t="n">
-        <v>2.57107615470886</v>
+        <v>2.57107639312744</v>
       </c>
       <c r="H711" t="n">
         <v>108439</v>
@@ -21104,7 +21104,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G715" t="n">
-        <v>2.47861695289612</v>
+        <v>2.4786171913147</v>
       </c>
       <c r="H715" t="n">
         <v>52613</v>
@@ -21220,7 +21220,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G719" t="n">
-        <v>2.56752038002014</v>
+        <v>2.56752014160156</v>
       </c>
       <c r="H719" t="n">
         <v>87756</v>
@@ -21249,7 +21249,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>2.60308146476746</v>
+        <v>2.60308170318604</v>
       </c>
       <c r="H720" t="n">
         <v>117533</v>
@@ -21278,7 +21278,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730599403381</v>
       </c>
       <c r="H721" t="n">
         <v>64041</v>
@@ -21307,7 +21307,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G722" t="n">
-        <v>2.70620894432068</v>
+        <v>2.70620918273926</v>
       </c>
       <c r="H722" t="n">
         <v>119382</v>
@@ -21336,7 +21336,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G723" t="n">
-        <v>2.73465800285339</v>
+        <v>2.73465776443481</v>
       </c>
       <c r="H723" t="n">
         <v>62198</v>
@@ -21365,7 +21365,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>2.75955080986023</v>
+        <v>2.75955128669739</v>
       </c>
       <c r="H724" t="n">
         <v>100805</v>
@@ -21394,7 +21394,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G725" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021956443787</v>
       </c>
       <c r="H725" t="n">
         <v>81609</v>
@@ -21423,7 +21423,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>2.81289291381836</v>
+        <v>2.81289267539978</v>
       </c>
       <c r="H726" t="n">
         <v>140477</v>
@@ -21481,7 +21481,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.90179586410522</v>
+        <v>2.90179562568665</v>
       </c>
       <c r="H728" t="n">
         <v>252045</v>
@@ -21597,7 +21597,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G732" t="n">
-        <v>2.89468383789062</v>
+        <v>2.89468359947205</v>
       </c>
       <c r="H732" t="n">
         <v>171357</v>
@@ -21626,7 +21626,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>2.83067345619202</v>
+        <v>2.83067321777344</v>
       </c>
       <c r="H733" t="n">
         <v>211140</v>
@@ -21655,7 +21655,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>2.98003077507019</v>
+        <v>2.98003053665161</v>
       </c>
       <c r="H734" t="n">
         <v>1000178</v>
@@ -21713,7 +21713,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>2.78800010681152</v>
+        <v>2.78799986839294</v>
       </c>
       <c r="H736" t="n">
         <v>563012</v>
@@ -21771,7 +21771,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G738" t="n">
-        <v>2.61374998092651</v>
+        <v>2.61374974250793</v>
       </c>
       <c r="H738" t="n">
         <v>117585</v>
@@ -21858,7 +21858,7 @@
         <v>3.625</v>
       </c>
       <c r="G741" t="n">
-        <v>2.5781888961792</v>
+        <v>2.57818865776062</v>
       </c>
       <c r="H741" t="n">
         <v>86207</v>
@@ -21916,7 +21916,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G743" t="n">
-        <v>2.70265316963196</v>
+        <v>2.7026526927948</v>
       </c>
       <c r="H743" t="n">
         <v>48168</v>
@@ -22003,7 +22003,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G746" t="n">
-        <v>2.64219903945923</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H746" t="n">
         <v>56935</v>
@@ -22032,7 +22032,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G747" t="n">
-        <v>2.6884286403656</v>
+        <v>2.68842840194702</v>
       </c>
       <c r="H747" t="n">
         <v>73493</v>
@@ -22061,7 +22061,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G748" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730599403381</v>
       </c>
       <c r="H748" t="n">
         <v>100769</v>
@@ -22090,7 +22090,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G749" t="n">
-        <v>2.64219903945923</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H749" t="n">
         <v>38116</v>
@@ -22119,7 +22119,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G750" t="n">
-        <v>2.56752038002014</v>
+        <v>2.56752014160156</v>
       </c>
       <c r="H750" t="n">
         <v>41661</v>
@@ -22148,7 +22148,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.59241318702698</v>
+        <v>2.59241342544556</v>
       </c>
       <c r="H751" t="n">
         <v>21292</v>
@@ -22177,7 +22177,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57107615470886</v>
+        <v>2.57107639312744</v>
       </c>
       <c r="H752" t="n">
         <v>65965</v>
@@ -22206,7 +22206,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.62086224555969</v>
+        <v>2.62086200714111</v>
       </c>
       <c r="H753" t="n">
         <v>95272</v>
@@ -22235,7 +22235,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.59241318702698</v>
+        <v>2.59241342544556</v>
       </c>
       <c r="H754" t="n">
         <v>126933</v>
@@ -22264,7 +22264,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G755" t="n">
-        <v>2.63864254951477</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H755" t="n">
         <v>25995</v>
@@ -22293,7 +22293,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G756" t="n">
-        <v>2.61374998092651</v>
+        <v>2.61374974250793</v>
       </c>
       <c r="H756" t="n">
         <v>33799</v>
@@ -22322,7 +22322,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>2.60308146476746</v>
+        <v>2.60308170318604</v>
       </c>
       <c r="H757" t="n">
         <v>73291</v>
@@ -22351,7 +22351,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60663747787476</v>
+        <v>2.60663771629333</v>
       </c>
       <c r="H758" t="n">
         <v>38408</v>
@@ -22380,7 +22380,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>2.61019396781921</v>
+        <v>2.61019372940063</v>
       </c>
       <c r="H759" t="n">
         <v>28732</v>
@@ -22467,7 +22467,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G762" t="n">
-        <v>2.52484703063965</v>
+        <v>2.52484655380249</v>
       </c>
       <c r="H762" t="n">
         <v>59560</v>
@@ -22496,7 +22496,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>2.51773452758789</v>
+        <v>2.51773476600647</v>
       </c>
       <c r="H763" t="n">
         <v>84397</v>
@@ -22525,7 +22525,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G764" t="n">
-        <v>2.62797403335571</v>
+        <v>2.62797427177429</v>
       </c>
       <c r="H764" t="n">
         <v>24743</v>
@@ -22554,7 +22554,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>2.64931130409241</v>
+        <v>2.64931106567383</v>
       </c>
       <c r="H765" t="n">
         <v>23656</v>
@@ -22670,7 +22670,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G769" t="n">
-        <v>2.72043347358704</v>
+        <v>2.72043371200562</v>
       </c>
       <c r="H769" t="n">
         <v>128846</v>
@@ -22699,7 +22699,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.73465800285339</v>
+        <v>2.73465776443481</v>
       </c>
       <c r="H770" t="n">
         <v>66288</v>
@@ -22757,7 +22757,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G772" t="n">
-        <v>2.73110198974609</v>
+        <v>2.73110175132751</v>
       </c>
       <c r="H772" t="n">
         <v>86625</v>
@@ -22786,7 +22786,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G773" t="n">
-        <v>2.74532651901245</v>
+        <v>2.74532628059387</v>
       </c>
       <c r="H773" t="n">
         <v>45391</v>
@@ -22815,7 +22815,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G774" t="n">
-        <v>2.76666331291199</v>
+        <v>2.76666355133057</v>
       </c>
       <c r="H774" t="n">
         <v>66798</v>
@@ -22844,7 +22844,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G775" t="n">
-        <v>2.75955080986023</v>
+        <v>2.75955128669739</v>
       </c>
       <c r="H775" t="n">
         <v>67211</v>
@@ -22873,7 +22873,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G776" t="n">
-        <v>2.76666331291199</v>
+        <v>2.76666355133057</v>
       </c>
       <c r="H776" t="n">
         <v>65193</v>
@@ -22902,7 +22902,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G777" t="n">
-        <v>2.76310682296753</v>
+        <v>2.76310706138611</v>
       </c>
       <c r="H777" t="n">
         <v>26136</v>
@@ -22960,7 +22960,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G779" t="n">
-        <v>2.64219903945923</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H779" t="n">
         <v>57180</v>
@@ -22989,7 +22989,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>2.63864254951477</v>
+        <v>2.63864278793335</v>
       </c>
       <c r="H780" t="n">
         <v>78579</v>
@@ -23076,7 +23076,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.77377557754517</v>
+        <v>2.77377533912659</v>
       </c>
       <c r="H783" t="n">
         <v>120974</v>
@@ -23105,7 +23105,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>2.76666331291199</v>
+        <v>2.76666355133057</v>
       </c>
       <c r="H784" t="n">
         <v>47047</v>
@@ -23163,7 +23163,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G786" t="n">
-        <v>2.68131613731384</v>
+        <v>2.68131637573242</v>
       </c>
       <c r="H786" t="n">
         <v>39710</v>
@@ -23192,7 +23192,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>2.64575505256653</v>
+        <v>2.64575481414795</v>
       </c>
       <c r="H787" t="n">
         <v>58312</v>
@@ -23308,7 +23308,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G791" t="n">
-        <v>2.56396436691284</v>
+        <v>2.56396412849426</v>
       </c>
       <c r="H791" t="n">
         <v>79270</v>
@@ -23337,7 +23337,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>2.5959689617157</v>
+        <v>2.59596967697144</v>
       </c>
       <c r="H792" t="n">
         <v>42596</v>
@@ -23424,7 +23424,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G795" t="n">
-        <v>2.52484703063965</v>
+        <v>2.52484655380249</v>
       </c>
       <c r="H795" t="n">
         <v>316700</v>
@@ -23453,7 +23453,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G796" t="n">
-        <v>2.51417827606201</v>
+        <v>2.51417851448059</v>
       </c>
       <c r="H796" t="n">
         <v>160917</v>
@@ -23569,7 +23569,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G800" t="n">
-        <v>2.51773452758789</v>
+        <v>2.51773476600647</v>
       </c>
       <c r="H800" t="n">
         <v>122165</v>
@@ -23598,7 +23598,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G801" t="n">
-        <v>2.52484703063965</v>
+        <v>2.52484655380249</v>
       </c>
       <c r="H801" t="n">
         <v>57692</v>
@@ -23685,7 +23685,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G804" t="n">
-        <v>2.49639797210693</v>
+        <v>2.49639773368835</v>
       </c>
       <c r="H804" t="n">
         <v>123967</v>
@@ -23714,7 +23714,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>2.49284195899963</v>
+        <v>2.49284172058105</v>
       </c>
       <c r="H805" t="n">
         <v>67850</v>
@@ -23743,7 +23743,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>2.50350975990295</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H806" t="n">
         <v>42553</v>
@@ -23772,7 +23772,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>2.49639797210693</v>
+        <v>2.49639773368835</v>
       </c>
       <c r="H807" t="n">
         <v>76903</v>
@@ -23830,7 +23830,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.48572969436646</v>
+        <v>2.48572945594788</v>
       </c>
       <c r="H809" t="n">
         <v>86790</v>
@@ -23888,7 +23888,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>2.37193369865417</v>
+        <v>2.3719334602356</v>
       </c>
       <c r="H811" t="n">
         <v>148443</v>
@@ -24004,7 +24004,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>2.32570385932922</v>
+        <v>2.3257040977478</v>
       </c>
       <c r="H815" t="n">
         <v>86372</v>
@@ -24062,7 +24062,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G817" t="n">
-        <v>2.27236223220825</v>
+        <v>2.27236199378967</v>
       </c>
       <c r="H817" t="n">
         <v>146028</v>
@@ -24091,7 +24091,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G818" t="n">
-        <v>2.27591848373413</v>
+        <v>2.27591800689697</v>
       </c>
       <c r="H818" t="n">
         <v>137063</v>
@@ -24120,7 +24120,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G819" t="n">
-        <v>2.27591848373413</v>
+        <v>2.27591800689697</v>
       </c>
       <c r="H819" t="n">
         <v>243571</v>
@@ -24149,7 +24149,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G820" t="n">
-        <v>2.27591848373413</v>
+        <v>2.27591800689697</v>
       </c>
       <c r="H820" t="n">
         <v>105828</v>
@@ -24178,7 +24178,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G821" t="n">
-        <v>2.27591848373413</v>
+        <v>2.27591800689697</v>
       </c>
       <c r="H821" t="n">
         <v>116326</v>
@@ -24207,7 +24207,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G822" t="n">
-        <v>2.28658676147461</v>
+        <v>2.28658628463745</v>
       </c>
       <c r="H822" t="n">
         <v>108669</v>
@@ -24236,7 +24236,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>2.27236223220825</v>
+        <v>2.27236199378967</v>
       </c>
       <c r="H823" t="n">
         <v>63237</v>
@@ -24294,7 +24294,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>2.26880598068237</v>
+        <v>2.26880621910095</v>
       </c>
       <c r="H825" t="n">
         <v>70107</v>
@@ -24410,7 +24410,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>2.35415291786194</v>
+        <v>2.35415315628052</v>
       </c>
       <c r="H829" t="n">
         <v>234469</v>
@@ -24439,7 +24439,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>2.37193369865417</v>
+        <v>2.3719334602356</v>
       </c>
       <c r="H830" t="n">
         <v>200129</v>
@@ -24526,7 +24526,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G833" t="n">
-        <v>2.30792331695557</v>
+        <v>2.30792307853699</v>
       </c>
       <c r="H833" t="n">
         <v>113930</v>
@@ -24613,7 +24613,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G836" t="n">
-        <v>2.28658676147461</v>
+        <v>2.28658628463745</v>
       </c>
       <c r="H836" t="n">
         <v>63039</v>
@@ -24642,7 +24642,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G837" t="n">
-        <v>2.3612654209137</v>
+        <v>2.36126494407654</v>
       </c>
       <c r="H837" t="n">
         <v>143505</v>
@@ -24700,7 +24700,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.41105127334595</v>
+        <v>2.41105103492737</v>
       </c>
       <c r="H839" t="n">
         <v>166284</v>
@@ -24729,7 +24729,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44305610656738</v>
+        <v>2.4430558681488</v>
       </c>
       <c r="H840" t="n">
         <v>95367</v>
@@ -24787,7 +24787,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G842" t="n">
-        <v>2.52484703063965</v>
+        <v>2.52484655380249</v>
       </c>
       <c r="H842" t="n">
         <v>158485</v>
@@ -24845,7 +24845,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G844" t="n">
-        <v>2.53907132148743</v>
+        <v>2.53907108306885</v>
       </c>
       <c r="H844" t="n">
         <v>120928</v>
@@ -24874,7 +24874,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G845" t="n">
-        <v>2.58174467086792</v>
+        <v>2.5817449092865</v>
       </c>
       <c r="H845" t="n">
         <v>178328</v>
@@ -24932,7 +24932,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.60308146476746</v>
+        <v>2.60308170318604</v>
       </c>
       <c r="H847" t="n">
         <v>177657</v>
@@ -24961,7 +24961,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G848" t="n">
-        <v>2.47861695289612</v>
+        <v>2.4786171913147</v>
       </c>
       <c r="H848" t="n">
         <v>218311</v>
@@ -24990,7 +24990,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42883157730103</v>
+        <v>2.4288318157196</v>
       </c>
       <c r="H849" t="n">
         <v>74414</v>
@@ -25048,7 +25048,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G851" t="n">
-        <v>2.44305610656738</v>
+        <v>2.4430558681488</v>
       </c>
       <c r="H851" t="n">
         <v>61053</v>
@@ -25077,7 +25077,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G852" t="n">
-        <v>2.35415291786194</v>
+        <v>2.35415315628052</v>
       </c>
       <c r="H852" t="n">
         <v>91389</v>
@@ -25106,7 +25106,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.3612654209137</v>
+        <v>2.36126494407654</v>
       </c>
       <c r="H853" t="n">
         <v>119893</v>
@@ -25164,7 +25164,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>2.43540239334106</v>
+        <v>2.43540215492249</v>
       </c>
       <c r="H855" t="n">
         <v>60436</v>
@@ -25193,7 +25193,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G856" t="n">
-        <v>2.42057466506958</v>
+        <v>2.42057490348816</v>
       </c>
       <c r="H856" t="n">
         <v>67266</v>
@@ -25222,7 +25222,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G857" t="n">
-        <v>2.47617745399475</v>
+        <v>2.47617769241333</v>
       </c>
       <c r="H857" t="n">
         <v>233867</v>
@@ -25251,7 +25251,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>2.45764327049255</v>
+        <v>2.45764350891113</v>
       </c>
       <c r="H858" t="n">
         <v>144235</v>
@@ -25309,7 +25309,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.37238597869873</v>
+        <v>2.37238574028015</v>
       </c>
       <c r="H860" t="n">
         <v>119077</v>
@@ -25338,7 +25338,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G861" t="n">
-        <v>2.38350629806519</v>
+        <v>2.38350653648376</v>
       </c>
       <c r="H861" t="n">
         <v>36228</v>
@@ -25367,7 +25367,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G862" t="n">
-        <v>2.2648868560791</v>
+        <v>2.26488733291626</v>
       </c>
       <c r="H862" t="n">
         <v>121961</v>
@@ -25454,7 +25454,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G865" t="n">
-        <v>2.21669793128967</v>
+        <v>2.21669769287109</v>
       </c>
       <c r="H865" t="n">
         <v>86109</v>
@@ -25483,7 +25483,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G866" t="n">
-        <v>2.21669793128967</v>
+        <v>2.21669769287109</v>
       </c>
       <c r="H866" t="n">
         <v>161854</v>
@@ -25512,7 +25512,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G867" t="n">
-        <v>2.21299123764038</v>
+        <v>2.21299076080322</v>
       </c>
       <c r="H867" t="n">
         <v>65700</v>
@@ -25541,7 +25541,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G868" t="n">
-        <v>2.14997482299805</v>
+        <v>2.14997458457947</v>
       </c>
       <c r="H868" t="n">
         <v>221958</v>
@@ -25599,7 +25599,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>2.14997482299805</v>
+        <v>2.14997458457947</v>
       </c>
       <c r="H870" t="n">
         <v>174290</v>
@@ -25657,7 +25657,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05359649658203</v>
+        <v>2.05359625816345</v>
       </c>
       <c r="H872" t="n">
         <v>132549</v>
@@ -25773,7 +25773,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>2.12031960487366</v>
+        <v>2.12031984329224</v>
       </c>
       <c r="H876" t="n">
         <v>101590</v>
@@ -25860,7 +25860,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G879" t="n">
-        <v>2.06100988388062</v>
+        <v>2.06101012229919</v>
       </c>
       <c r="H879" t="n">
         <v>148826</v>
@@ -25918,7 +25918,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G881" t="n">
-        <v>2.14997482299805</v>
+        <v>2.14997458457947</v>
       </c>
       <c r="H881" t="n">
         <v>95881</v>
@@ -26005,7 +26005,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G884" t="n">
-        <v>2.03135514259338</v>
+        <v>2.03135538101196</v>
       </c>
       <c r="H884" t="n">
         <v>170336</v>
@@ -26034,7 +26034,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G885" t="n">
-        <v>1.99799370765686</v>
+        <v>1.99799358844757</v>
       </c>
       <c r="H885" t="n">
         <v>136424</v>
@@ -26063,7 +26063,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G886" t="n">
-        <v>2.01652812957764</v>
+        <v>2.01652789115906</v>
       </c>
       <c r="H886" t="n">
         <v>78138</v>
@@ -26179,7 +26179,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.28342127799988</v>
+        <v>2.2834210395813</v>
       </c>
       <c r="H890" t="n">
         <v>233336</v>
@@ -26353,7 +26353,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G896" t="n">
-        <v>2.2648868560791</v>
+        <v>2.26488733291626</v>
       </c>
       <c r="H896" t="n">
         <v>213042</v>
@@ -26382,7 +26382,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G897" t="n">
-        <v>2.2648868560791</v>
+        <v>2.26488733291626</v>
       </c>
       <c r="H897" t="n">
         <v>70512</v>
@@ -26411,7 +26411,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G898" t="n">
-        <v>2.27230095863342</v>
+        <v>2.27230072021484</v>
       </c>
       <c r="H898" t="n">
         <v>60128</v>
@@ -26440,7 +26440,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G899" t="n">
-        <v>2.27971458435059</v>
+        <v>2.27971434593201</v>
       </c>
       <c r="H899" t="n">
         <v>102850</v>
@@ -26498,7 +26498,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G901" t="n">
-        <v>2.28342127799988</v>
+        <v>2.2834210395813</v>
       </c>
       <c r="H901" t="n">
         <v>85699</v>
@@ -26585,7 +26585,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G904" t="n">
-        <v>2.26117992401123</v>
+        <v>2.26118040084839</v>
       </c>
       <c r="H904" t="n">
         <v>41843</v>
@@ -26614,7 +26614,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.28712821006775</v>
+        <v>2.28712797164917</v>
       </c>
       <c r="H905" t="n">
         <v>70844</v>
@@ -26643,7 +26643,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G906" t="n">
-        <v>2.26117992401123</v>
+        <v>2.26118040084839</v>
       </c>
       <c r="H906" t="n">
         <v>93112</v>
@@ -26701,7 +26701,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>2.28342127799988</v>
+        <v>2.2834210395813</v>
       </c>
       <c r="H908" t="n">
         <v>180734</v>
@@ -26730,7 +26730,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>2.26859378814697</v>
+        <v>2.26859402656555</v>
       </c>
       <c r="H909" t="n">
         <v>88883</v>
@@ -26759,7 +26759,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G910" t="n">
-        <v>2.23523211479187</v>
+        <v>2.23523235321045</v>
       </c>
       <c r="H910" t="n">
         <v>166947</v>
@@ -26788,7 +26788,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G911" t="n">
-        <v>2.25005960464478</v>
+        <v>2.25005984306335</v>
       </c>
       <c r="H911" t="n">
         <v>43162</v>
@@ -26846,7 +26846,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G913" t="n">
-        <v>2.21669793128967</v>
+        <v>2.21669769287109</v>
       </c>
       <c r="H913" t="n">
         <v>146027</v>
@@ -26904,7 +26904,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G915" t="n">
-        <v>2.1796293258667</v>
+        <v>2.17962956428528</v>
       </c>
       <c r="H915" t="n">
         <v>152880</v>
@@ -26933,7 +26933,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G916" t="n">
-        <v>2.1796293258667</v>
+        <v>2.17962956428528</v>
       </c>
       <c r="H916" t="n">
         <v>124102</v>
@@ -27078,7 +27078,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G921" t="n">
-        <v>2.15368127822876</v>
+        <v>2.15368151664734</v>
       </c>
       <c r="H921" t="n">
         <v>83002</v>
@@ -27136,7 +27136,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>2.19074964523315</v>
+        <v>2.19075012207031</v>
       </c>
       <c r="H923" t="n">
         <v>103378</v>
@@ -27165,7 +27165,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>2.12402677536011</v>
+        <v>2.12402653694153</v>
       </c>
       <c r="H924" t="n">
         <v>71584</v>
@@ -27194,7 +27194,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G925" t="n">
-        <v>2.12031960487366</v>
+        <v>2.12031984329224</v>
       </c>
       <c r="H925" t="n">
         <v>112906</v>
@@ -27223,7 +27223,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G926" t="n">
-        <v>2.14997482299805</v>
+        <v>2.14997458457947</v>
       </c>
       <c r="H926" t="n">
         <v>48449</v>
@@ -27426,7 +27426,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>2.14997482299805</v>
+        <v>2.14997458457947</v>
       </c>
       <c r="H933" t="n">
         <v>83565</v>
@@ -27571,7 +27571,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G938" t="n">
-        <v>2.55402135848999</v>
+        <v>2.55402159690857</v>
       </c>
       <c r="H938" t="n">
         <v>605667</v>
@@ -27600,7 +27600,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G939" t="n">
-        <v>2.52807378768921</v>
+        <v>2.52807354927063</v>
       </c>
       <c r="H939" t="n">
         <v>638409</v>
@@ -27629,7 +27629,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G940" t="n">
-        <v>2.55772829055786</v>
+        <v>2.55772852897644</v>
       </c>
       <c r="H940" t="n">
         <v>190473</v>
@@ -27658,7 +27658,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>2.63927888870239</v>
+        <v>2.63927936553955</v>
       </c>
       <c r="H941" t="n">
         <v>881119</v>
@@ -27687,7 +27687,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G942" t="n">
-        <v>2.79126024246216</v>
+        <v>2.79126000404358</v>
       </c>
       <c r="H942" t="n">
         <v>486765</v>
@@ -27716,7 +27716,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G943" t="n">
-        <v>2.78755354881287</v>
+        <v>2.78755331039429</v>
       </c>
       <c r="H943" t="n">
         <v>355837</v>
@@ -27745,7 +27745,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G944" t="n">
-        <v>2.77272582054138</v>
+        <v>2.77272605895996</v>
       </c>
       <c r="H944" t="n">
         <v>166865</v>
@@ -28064,7 +28064,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G955" t="n">
-        <v>2.67264103889465</v>
+        <v>2.67264080047607</v>
       </c>
       <c r="H955" t="n">
         <v>162705</v>
@@ -28093,7 +28093,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G956" t="n">
-        <v>2.68376111984253</v>
+        <v>2.68376159667969</v>
       </c>
       <c r="H956" t="n">
         <v>86012</v>
@@ -28151,7 +28151,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G958" t="n">
-        <v>2.72824382781982</v>
+        <v>2.72824358940125</v>
       </c>
       <c r="H958" t="n">
         <v>98599</v>
@@ -28238,7 +28238,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G961" t="n">
-        <v>2.76160550117493</v>
+        <v>2.76160526275635</v>
       </c>
       <c r="H961" t="n">
         <v>97307</v>
@@ -28267,7 +28267,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G962" t="n">
-        <v>2.76901888847351</v>
+        <v>2.76901912689209</v>
       </c>
       <c r="H962" t="n">
         <v>88960</v>
@@ -28296,7 +28296,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G963" t="n">
-        <v>2.76531195640564</v>
+        <v>2.76531219482422</v>
       </c>
       <c r="H963" t="n">
         <v>96254</v>
@@ -28325,7 +28325,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>2.76531195640564</v>
+        <v>2.76531219482422</v>
       </c>
       <c r="H964" t="n">
         <v>89082</v>
@@ -28383,7 +28383,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G966" t="n">
-        <v>2.70970916748047</v>
+        <v>2.70970964431763</v>
       </c>
       <c r="H966" t="n">
         <v>148307</v>
@@ -28412,7 +28412,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G967" t="n">
-        <v>2.72453689575195</v>
+        <v>2.72453665733337</v>
       </c>
       <c r="H967" t="n">
         <v>92773</v>
@@ -28441,7 +28441,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.70970916748047</v>
+        <v>2.70970964431763</v>
       </c>
       <c r="H968" t="n">
         <v>42501</v>
@@ -28470,7 +28470,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.68005442619324</v>
+        <v>2.68005466461182</v>
       </c>
       <c r="H969" t="n">
         <v>91180</v>
@@ -28499,7 +28499,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G970" t="n">
-        <v>2.66893410682678</v>
+        <v>2.6689338684082</v>
       </c>
       <c r="H970" t="n">
         <v>41494</v>
@@ -28644,7 +28644,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>2.80238080024719</v>
+        <v>2.80238056182861</v>
       </c>
       <c r="H975" t="n">
         <v>118604</v>
@@ -28673,7 +28673,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G976" t="n">
-        <v>2.76160550117493</v>
+        <v>2.76160526275635</v>
       </c>
       <c r="H976" t="n">
         <v>184807</v>
@@ -28760,7 +28760,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>2.89875888824463</v>
+        <v>2.89875864982605</v>
       </c>
       <c r="H979" t="n">
         <v>279460</v>
@@ -28818,7 +28818,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>2.94694805145264</v>
+        <v>2.94694757461548</v>
       </c>
       <c r="H981" t="n">
         <v>159745</v>
@@ -28847,7 +28847,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.93582725524902</v>
+        <v>2.9358274936676</v>
       </c>
       <c r="H982" t="n">
         <v>141285</v>
@@ -28876,7 +28876,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G983" t="n">
-        <v>2.95806860923767</v>
+        <v>2.95806837081909</v>
       </c>
       <c r="H983" t="n">
         <v>147298</v>
@@ -28905,7 +28905,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G984" t="n">
-        <v>3.05444645881653</v>
+        <v>3.05444669723511</v>
       </c>
       <c r="H984" t="n">
         <v>335251</v>
@@ -28992,7 +28992,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>2.84315586090088</v>
+        <v>2.84315633773804</v>
       </c>
       <c r="H987" t="n">
         <v>262064</v>
@@ -29021,7 +29021,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G988" t="n">
-        <v>2.80608773231506</v>
+        <v>2.80608749389648</v>
       </c>
       <c r="H988" t="n">
         <v>129247</v>
@@ -29079,7 +29079,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G990" t="n">
-        <v>2.92841362953186</v>
+        <v>2.92841386795044</v>
       </c>
       <c r="H990" t="n">
         <v>223860</v>
@@ -29108,7 +29108,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G991" t="n">
-        <v>2.97660279273987</v>
+        <v>2.97660255432129</v>
       </c>
       <c r="H991" t="n">
         <v>229076</v>
@@ -29166,7 +29166,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>3.22496151924133</v>
+        <v>3.22496175765991</v>
       </c>
       <c r="H993" t="n">
         <v>309322</v>
@@ -29195,7 +29195,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G994" t="n">
-        <v>3.30651307106018</v>
+        <v>3.3065128326416</v>
       </c>
       <c r="H994" t="n">
         <v>868963</v>
@@ -29224,7 +29224,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>3.39547681808472</v>
+        <v>3.39547729492188</v>
       </c>
       <c r="H995" t="n">
         <v>642201</v>
@@ -29282,7 +29282,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>3.41771817207336</v>
+        <v>3.41771841049194</v>
       </c>
       <c r="H997" t="n">
         <v>202987</v>
@@ -29340,7 +29340,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.52892422676086</v>
+        <v>3.52892374992371</v>
       </c>
       <c r="H999" t="n">
         <v>532506</v>
@@ -29369,7 +29369,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.59935402870178</v>
+        <v>3.59935426712036</v>
       </c>
       <c r="H1000" t="n">
         <v>744840</v>
@@ -29398,7 +29398,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.59564733505249</v>
+        <v>3.59564685821533</v>
       </c>
       <c r="H1001" t="n">
         <v>333775</v>
@@ -29427,7 +29427,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.68461155891418</v>
+        <v>3.68461108207703</v>
       </c>
       <c r="H1002" t="n">
         <v>738133</v>
@@ -29456,7 +29456,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.65866374969482</v>
+        <v>3.65866327285767</v>
       </c>
       <c r="H1003" t="n">
         <v>1079301</v>
@@ -29514,7 +29514,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.79581713676453</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1005" t="n">
         <v>332417</v>
@@ -29543,7 +29543,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.79581713676453</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1006" t="n">
         <v>349628</v>
@@ -29572,7 +29572,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.76616263389587</v>
+        <v>3.76616191864014</v>
       </c>
       <c r="H1007" t="n">
         <v>463372</v>
@@ -29688,7 +29688,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.79581713676453</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1011" t="n">
         <v>151303</v>
@@ -29717,7 +29717,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.76616263389587</v>
+        <v>3.76616191864014</v>
       </c>
       <c r="H1012" t="n">
         <v>191213</v>
@@ -29746,7 +29746,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.81064414978027</v>
+        <v>3.81064438819885</v>
       </c>
       <c r="H1013" t="n">
         <v>243495</v>
@@ -29775,7 +29775,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.79581713676453</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1014" t="n">
         <v>102689</v>
@@ -29804,7 +29804,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.84029960632324</v>
+        <v>3.84029936790466</v>
       </c>
       <c r="H1015" t="n">
         <v>295814</v>
@@ -29833,7 +29833,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.91443705558777</v>
+        <v>3.91443634033203</v>
       </c>
       <c r="H1016" t="n">
         <v>346021</v>
@@ -29891,7 +29891,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.90702319145203</v>
+        <v>3.90702295303345</v>
       </c>
       <c r="H1018" t="n">
         <v>323276</v>
@@ -29920,7 +29920,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.91443705558777</v>
+        <v>3.91443634033203</v>
       </c>
       <c r="H1019" t="n">
         <v>370109</v>
@@ -29949,7 +29949,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.944091796875</v>
+        <v>3.94409132003784</v>
       </c>
       <c r="H1020" t="n">
         <v>587792</v>
@@ -29978,7 +29978,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.00340127944946</v>
+        <v>4.0034008026123</v>
       </c>
       <c r="H1021" t="n">
         <v>382920</v>
@@ -30007,7 +30007,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.85512709617615</v>
+        <v>3.85512661933899</v>
       </c>
       <c r="H1022" t="n">
         <v>233331</v>
@@ -30065,7 +30065,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.86995387077332</v>
+        <v>3.86995458602905</v>
       </c>
       <c r="H1024" t="n">
         <v>264811</v>
@@ -30123,7 +30123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.85512709617615</v>
+        <v>3.85512661933899</v>
       </c>
       <c r="H1026" t="n">
         <v>83051</v>
@@ -30152,7 +30152,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.84771299362183</v>
+        <v>3.84771323204041</v>
       </c>
       <c r="H1027" t="n">
         <v>72510</v>
@@ -30210,7 +30210,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.81064414978027</v>
+        <v>3.81064438819885</v>
       </c>
       <c r="H1029" t="n">
         <v>213214</v>
@@ -30239,7 +30239,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.85512709617615</v>
+        <v>3.85512661933899</v>
       </c>
       <c r="H1030" t="n">
         <v>156105</v>
@@ -30268,7 +30268,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.78840374946594</v>
+        <v>3.78840351104736</v>
       </c>
       <c r="H1031" t="n">
         <v>116338</v>
@@ -30297,7 +30297,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.8328857421875</v>
+        <v>3.83288550376892</v>
       </c>
       <c r="H1032" t="n">
         <v>299811</v>
@@ -30326,7 +30326,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.79581713676453</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1033" t="n">
         <v>281130</v>
@@ -30384,7 +30384,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.76616263389587</v>
+        <v>3.76616191864014</v>
       </c>
       <c r="H1035" t="n">
         <v>209216</v>
@@ -30442,7 +30442,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.47332048416138</v>
+        <v>3.47332119941711</v>
       </c>
       <c r="H1037" t="n">
         <v>353099</v>
@@ -30471,7 +30471,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.6030604839325</v>
+        <v>3.60306072235107</v>
       </c>
       <c r="H1038" t="n">
         <v>205159</v>
@@ -30529,7 +30529,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.7290940284729</v>
+        <v>3.72909426689148</v>
       </c>
       <c r="H1040" t="n">
         <v>366585</v>
@@ -30558,7 +30558,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.76616263389587</v>
+        <v>3.76616191864014</v>
       </c>
       <c r="H1041" t="n">
         <v>81094</v>
@@ -30674,7 +30674,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.77357649803162</v>
+        <v>3.77357625961304</v>
       </c>
       <c r="H1045" t="n">
         <v>100770</v>
@@ -30703,7 +30703,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.8328857421875</v>
+        <v>3.83288550376892</v>
       </c>
       <c r="H1046" t="n">
         <v>155005</v>
@@ -30732,7 +30732,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.92926383018494</v>
+        <v>3.92926406860352</v>
       </c>
       <c r="H1047" t="n">
         <v>476926</v>
@@ -30790,7 +30790,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.12201976776123</v>
+        <v>4.12202024459839</v>
       </c>
       <c r="H1049" t="n">
         <v>268142</v>
@@ -30848,7 +30848,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.06271028518677</v>
+        <v>4.06271076202393</v>
       </c>
       <c r="H1051" t="n">
         <v>169274</v>
@@ -30906,7 +30906,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.79581713676453</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1053" t="n">
         <v>746712</v>
@@ -30964,7 +30964,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.78840374946594</v>
+        <v>3.78840351104736</v>
       </c>
       <c r="H1055" t="n">
         <v>373798</v>
@@ -31022,7 +31022,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.63271546363831</v>
+        <v>3.63271617889404</v>
       </c>
       <c r="H1057" t="n">
         <v>486017</v>
@@ -31080,7 +31080,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.66607713699341</v>
+        <v>3.66607737541199</v>
       </c>
       <c r="H1059" t="n">
         <v>331600</v>
@@ -31167,7 +31167,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.55857849121094</v>
+        <v>3.5585789680481</v>
       </c>
       <c r="H1062" t="n">
         <v>398454</v>
@@ -31254,7 +31254,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.04332637786865</v>
+        <v>3.04332613945007</v>
       </c>
       <c r="H1065" t="n">
         <v>379441</v>
@@ -31283,7 +31283,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.59109020233154</v>
+        <v>2.59108996391296</v>
       </c>
       <c r="H1066" t="n">
         <v>624766</v>
@@ -31312,7 +31312,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.51324653625488</v>
+        <v>2.51324605941772</v>
       </c>
       <c r="H1067" t="n">
         <v>717398</v>
@@ -31370,7 +31370,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.29083490371704</v>
+        <v>2.29083466529846</v>
       </c>
       <c r="H1069" t="n">
         <v>496099</v>
@@ -31428,7 +31428,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.06471705436707</v>
+        <v>2.06471681594849</v>
       </c>
       <c r="H1071" t="n">
         <v>384018</v>
@@ -31457,7 +31457,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.1796293258667</v>
+        <v>2.17962956428528</v>
       </c>
       <c r="H1072" t="n">
         <v>350348</v>
@@ -31486,7 +31486,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.20928430557251</v>
+        <v>2.20928406715393</v>
       </c>
       <c r="H1073" t="n">
         <v>277616</v>
@@ -31544,7 +31544,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.31307601928711</v>
+        <v>2.31307625770569</v>
       </c>
       <c r="H1075" t="n">
         <v>280521</v>
@@ -31573,7 +31573,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.37238597869873</v>
+        <v>2.37238574028015</v>
       </c>
       <c r="H1076" t="n">
         <v>180047</v>
@@ -31602,7 +31602,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.34273099899292</v>
+        <v>2.3427312374115</v>
       </c>
       <c r="H1077" t="n">
         <v>125940</v>
@@ -31631,7 +31631,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.30195593833923</v>
+        <v>2.30195546150208</v>
       </c>
       <c r="H1078" t="n">
         <v>169458</v>
@@ -31660,7 +31660,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.38721323013306</v>
+        <v>2.38721346855164</v>
       </c>
       <c r="H1079" t="n">
         <v>228291</v>
@@ -31689,7 +31689,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.28342127799988</v>
+        <v>2.2834210395813</v>
       </c>
       <c r="H1080" t="n">
         <v>79106</v>
@@ -31718,7 +31718,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.26117992401123</v>
+        <v>2.26118040084839</v>
       </c>
       <c r="H1081" t="n">
         <v>248140</v>
@@ -31805,7 +31805,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.53548717498779</v>
+        <v>2.53548741340637</v>
       </c>
       <c r="H1084" t="n">
         <v>286119</v>
@@ -31863,7 +31863,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.67264103889465</v>
+        <v>2.67264080047607</v>
       </c>
       <c r="H1086" t="n">
         <v>186894</v>
@@ -31892,7 +31892,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.66893410682678</v>
+        <v>2.6689338684082</v>
       </c>
       <c r="H1087" t="n">
         <v>146976</v>
@@ -31950,7 +31950,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.76901888847351</v>
+        <v>2.76901912689209</v>
       </c>
       <c r="H1089" t="n">
         <v>947909</v>
@@ -31979,7 +31979,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.67264103889465</v>
+        <v>2.67264080047607</v>
       </c>
       <c r="H1090" t="n">
         <v>573804</v>
@@ -32008,7 +32008,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.87651777267456</v>
+        <v>2.87651801109314</v>
       </c>
       <c r="H1091" t="n">
         <v>353324</v>
@@ -32037,7 +32037,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.82462167739868</v>
+        <v>2.8246214389801</v>
       </c>
       <c r="H1092" t="n">
         <v>216590</v>
@@ -32066,7 +32066,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.8839316368103</v>
+        <v>2.88393139839172</v>
       </c>
       <c r="H1093" t="n">
         <v>530739</v>
@@ -32095,7 +32095,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.01737856864929</v>
+        <v>3.01737809181213</v>
       </c>
       <c r="H1094" t="n">
         <v>245764</v>
@@ -32124,7 +32124,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.06927394866943</v>
+        <v>3.06927418708801</v>
       </c>
       <c r="H1095" t="n">
         <v>190108</v>
@@ -32153,7 +32153,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.17306613922119</v>
+        <v>3.17306637763977</v>
       </c>
       <c r="H1096" t="n">
         <v>403206</v>
@@ -32182,7 +32182,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.1878936290741</v>
+        <v>3.18789339065552</v>
       </c>
       <c r="H1097" t="n">
         <v>381925</v>
@@ -32240,7 +32240,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.1878936290741</v>
+        <v>3.18789339065552</v>
       </c>
       <c r="H1099" t="n">
         <v>151019</v>
@@ -32269,7 +32269,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.07668805122375</v>
+        <v>3.07668781280518</v>
       </c>
       <c r="H1100" t="n">
         <v>96382</v>
@@ -32298,7 +32298,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.11004948616028</v>
+        <v>3.1100492477417</v>
       </c>
       <c r="H1101" t="n">
         <v>167235</v>
@@ -32327,7 +32327,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.1285834312439</v>
+        <v>3.12858366966248</v>
       </c>
       <c r="H1102" t="n">
         <v>43938</v>
@@ -32385,7 +32385,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.11004948616028</v>
+        <v>3.1100492477417</v>
       </c>
       <c r="H1104" t="n">
         <v>193043</v>
@@ -32414,7 +32414,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.13599729537964</v>
+        <v>3.13599753379822</v>
       </c>
       <c r="H1105" t="n">
         <v>97662</v>
@@ -32443,7 +32443,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.03961896896362</v>
+        <v>3.0396192073822</v>
       </c>
       <c r="H1106" t="n">
         <v>142682</v>
@@ -32472,7 +32472,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.06927394866943</v>
+        <v>3.06927418708801</v>
       </c>
       <c r="H1107" t="n">
         <v>237216</v>
@@ -32530,7 +32530,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.87651777267456</v>
+        <v>2.87651801109314</v>
       </c>
       <c r="H1109" t="n">
         <v>173640</v>
@@ -32559,7 +32559,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.94324111938477</v>
+        <v>2.94324088096619</v>
       </c>
       <c r="H1110" t="n">
         <v>134071</v>
@@ -32675,7 +32675,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.06927394866943</v>
+        <v>3.06927418708801</v>
       </c>
       <c r="H1114" t="n">
         <v>319518</v>
@@ -32704,7 +32704,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.161945104599</v>
+        <v>3.16194534301758</v>
       </c>
       <c r="H1115" t="n">
         <v>341544</v>
@@ -32733,7 +32733,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.15823888778687</v>
+        <v>3.15823864936829</v>
       </c>
       <c r="H1116" t="n">
         <v>314681</v>
@@ -32849,7 +32849,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.29168558120728</v>
+        <v>3.2916853427887</v>
       </c>
       <c r="H1120" t="n">
         <v>119756</v>
@@ -32878,7 +32878,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.20642757415771</v>
+        <v>3.20642781257629</v>
       </c>
       <c r="H1121" t="n">
         <v>523519</v>
@@ -32936,7 +32936,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.22496151924133</v>
+        <v>3.22496175765991</v>
       </c>
       <c r="H1123" t="n">
         <v>114302</v>
@@ -32994,7 +32994,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17677307128906</v>
+        <v>3.1767725944519</v>
       </c>
       <c r="H1125" t="n">
         <v>216177</v>
@@ -33023,7 +33023,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.10634279251099</v>
+        <v>3.10634255409241</v>
       </c>
       <c r="H1126" t="n">
         <v>157535</v>
@@ -33110,7 +33110,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.77643275260925</v>
+        <v>2.77643251419067</v>
       </c>
       <c r="H1129" t="n">
         <v>482471</v>
@@ -33168,7 +33168,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.83944916725159</v>
+        <v>2.83944940567017</v>
       </c>
       <c r="H1131" t="n">
         <v>207485</v>
@@ -33197,7 +33197,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.77643275260925</v>
+        <v>2.77643251419067</v>
       </c>
       <c r="H1132" t="n">
         <v>136838</v>
@@ -33226,7 +33226,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.79126024246216</v>
+        <v>2.79126000404358</v>
       </c>
       <c r="H1133" t="n">
         <v>110451</v>
@@ -33255,7 +33255,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.80238080024719</v>
+        <v>2.80238056182861</v>
       </c>
       <c r="H1134" t="n">
         <v>139987</v>
@@ -33284,7 +33284,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.05444645881653</v>
+        <v>3.05444669723511</v>
       </c>
       <c r="H1135" t="n">
         <v>906769</v>
@@ -33313,7 +33313,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.93582725524902</v>
+        <v>2.9358274936676</v>
       </c>
       <c r="H1136" t="n">
         <v>472549</v>
@@ -33342,7 +33342,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.82832884788513</v>
+        <v>2.82832860946655</v>
       </c>
       <c r="H1137" t="n">
         <v>101226</v>
@@ -33429,7 +33429,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.80238080024719</v>
+        <v>2.80238056182861</v>
       </c>
       <c r="H1140" t="n">
         <v>88487</v>
@@ -33487,7 +33487,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.83574223518372</v>
+        <v>2.83574247360229</v>
       </c>
       <c r="H1142" t="n">
         <v>94920</v>
@@ -33516,7 +33516,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85798382759094</v>
+        <v>2.85798358917236</v>
       </c>
       <c r="H1143" t="n">
         <v>86988</v>
@@ -33545,7 +33545,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.83944916725159</v>
+        <v>2.83944940567017</v>
       </c>
       <c r="H1144" t="n">
         <v>60861</v>
@@ -33690,7 +33690,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.96918916702271</v>
+        <v>2.96918892860413</v>
       </c>
       <c r="H1149" t="n">
         <v>122881</v>
@@ -33719,7 +33719,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.05444645881653</v>
+        <v>3.05444669723511</v>
       </c>
       <c r="H1150" t="n">
         <v>85124</v>
@@ -33748,7 +33748,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.02108502388</v>
+        <v>3.02108478546143</v>
       </c>
       <c r="H1151" t="n">
         <v>257205</v>
@@ -33806,7 +33806,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.11004948616028</v>
+        <v>3.1100492477417</v>
       </c>
       <c r="H1153" t="n">
         <v>260642</v>
@@ -33835,7 +33835,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.11004948616028</v>
+        <v>3.1100492477417</v>
       </c>
       <c r="H1154" t="n">
         <v>78988</v>
@@ -33864,7 +33864,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.12117028236389</v>
+        <v>3.12116980552673</v>
       </c>
       <c r="H1155" t="n">
         <v>89194</v>
@@ -33893,7 +33893,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.1285834312439</v>
+        <v>3.12858366966248</v>
       </c>
       <c r="H1156" t="n">
         <v>121107</v>
@@ -33980,7 +33980,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.06556725502014</v>
+        <v>3.06556749343872</v>
       </c>
       <c r="H1159" t="n">
         <v>97598</v>
@@ -34009,7 +34009,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.04332637786865</v>
+        <v>3.04332613945007</v>
       </c>
       <c r="H1160" t="n">
         <v>76737</v>
@@ -34038,7 +34038,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.09892868995667</v>
+        <v>3.09892892837524</v>
       </c>
       <c r="H1161" t="n">
         <v>214220</v>
@@ -34067,7 +34067,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.18418645858765</v>
+        <v>3.18418669700623</v>
       </c>
       <c r="H1162" t="n">
         <v>152609</v>
@@ -34096,7 +34096,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.09151530265808</v>
+        <v>3.0915150642395</v>
       </c>
       <c r="H1163" t="n">
         <v>187881</v>
@@ -34125,7 +34125,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.10634279251099</v>
+        <v>3.10634255409241</v>
       </c>
       <c r="H1164" t="n">
         <v>90903</v>
@@ -34154,7 +34154,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.13970446586609</v>
+        <v>3.13970470428467</v>
       </c>
       <c r="H1165" t="n">
         <v>123022</v>
@@ -34183,7 +34183,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.15453171730042</v>
+        <v>3.15453147888184</v>
       </c>
       <c r="H1166" t="n">
         <v>119978</v>
@@ -34415,7 +34415,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.55857849121094</v>
+        <v>3.5585789680481</v>
       </c>
       <c r="H1174" t="n">
         <v>195254</v>
@@ -34444,7 +34444,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.65866374969482</v>
+        <v>3.65866327285767</v>
       </c>
       <c r="H1175" t="n">
         <v>294092</v>
@@ -34531,7 +34531,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.50668239593506</v>
+        <v>3.50668263435364</v>
       </c>
       <c r="H1178" t="n">
         <v>89172</v>
@@ -34560,7 +34560,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41771817207336</v>
+        <v>3.41771841049194</v>
       </c>
       <c r="H1179" t="n">
         <v>98749</v>
@@ -34589,7 +34589,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.70314574241638</v>
+        <v>3.70314598083496</v>
       </c>
       <c r="H1180" t="n">
         <v>607643</v>
@@ -34647,7 +34647,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.98115968704224</v>
+        <v>3.98115944862366</v>
       </c>
       <c r="H1182" t="n">
         <v>423717</v>
@@ -34676,7 +34676,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.91443705558777</v>
+        <v>3.91443634033203</v>
       </c>
       <c r="H1183" t="n">
         <v>304675</v>
@@ -34705,7 +34705,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.91443705558777</v>
+        <v>3.91443634033203</v>
       </c>
       <c r="H1184" t="n">
         <v>207842</v>
@@ -34734,7 +34734,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.86995387077332</v>
+        <v>3.86995458602905</v>
       </c>
       <c r="H1185" t="n">
         <v>246353</v>
@@ -34763,7 +34763,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.90702319145203</v>
+        <v>3.90702295303345</v>
       </c>
       <c r="H1186" t="n">
         <v>69541</v>
@@ -34792,7 +34792,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.92926383018494</v>
+        <v>3.92926406860352</v>
       </c>
       <c r="H1187" t="n">
         <v>142623</v>
@@ -34821,7 +34821,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.84771299362183</v>
+        <v>3.84771323204041</v>
       </c>
       <c r="H1188" t="n">
         <v>228820</v>
@@ -34850,7 +34850,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.79581713676453</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1189" t="n">
         <v>155683</v>
@@ -34966,7 +34966,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.55942916870117</v>
+        <v>4.55942869186401</v>
       </c>
       <c r="H1193" t="n">
         <v>521199</v>
@@ -35053,7 +35053,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.47046422958374</v>
+        <v>4.4704647064209</v>
       </c>
       <c r="H1196" t="n">
         <v>212780</v>
@@ -35140,7 +35140,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.50011920928955</v>
+        <v>4.50011968612671</v>
       </c>
       <c r="H1199" t="n">
         <v>371285</v>
@@ -35256,7 +35256,7 @@
         <v>6.75</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.00425148010254</v>
+        <v>5.00425100326538</v>
       </c>
       <c r="H1203" t="n">
         <v>310965</v>
@@ -35285,7 +35285,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.11545658111572</v>
+        <v>5.11545705795288</v>
       </c>
       <c r="H1204" t="n">
         <v>323143</v>
@@ -35314,7 +35314,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.38234996795654</v>
+        <v>5.3823504447937</v>
       </c>
       <c r="H1205" t="n">
         <v>508998</v>
@@ -35343,7 +35343,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.41941833496094</v>
+        <v>5.41941928863525</v>
       </c>
       <c r="H1206" t="n">
         <v>352753</v>
@@ -35372,7 +35372,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1207" t="n">
-        <v>5.59734725952148</v>
+        <v>5.59734773635864</v>
       </c>
       <c r="H1207" t="n">
         <v>525409</v>
@@ -35401,7 +35401,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.46390104293823</v>
+        <v>5.46390056610107</v>
       </c>
       <c r="H1208" t="n">
         <v>424268</v>
@@ -35430,7 +35430,7 @@
         <v>7.5</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.56027889251709</v>
+        <v>5.56027936935425</v>
       </c>
       <c r="H1209" t="n">
         <v>262844</v>
@@ -35459,7 +35459,7 @@
         <v>7.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.56027889251709</v>
+        <v>5.56027936935425</v>
       </c>
       <c r="H1210" t="n">
         <v>186425</v>
@@ -35488,7 +35488,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.58252048492432</v>
+        <v>5.58252000808716</v>
       </c>
       <c r="H1211" t="n">
         <v>199033</v>
@@ -35546,7 +35546,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.65665769577026</v>
+        <v>5.65665721893311</v>
       </c>
       <c r="H1213" t="n">
         <v>242818</v>
@@ -35575,7 +35575,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.62700271606445</v>
+        <v>5.62700223922729</v>
       </c>
       <c r="H1214" t="n">
         <v>339811</v>
@@ -35749,7 +35749,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.56769275665283</v>
+        <v>5.56769323348999</v>
       </c>
       <c r="H1220" t="n">
         <v>111918</v>
@@ -35778,7 +35778,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.52321100234985</v>
+        <v>5.5232105255127</v>
       </c>
       <c r="H1221" t="n">
         <v>113245</v>
@@ -35836,7 +35836,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.40459156036377</v>
+        <v>5.40459108352661</v>
       </c>
       <c r="H1223" t="n">
         <v>149706</v>
@@ -35894,7 +35894,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1225" t="n">
-        <v>5.15252542495728</v>
+        <v>5.15252494812012</v>
       </c>
       <c r="H1225" t="n">
         <v>390979</v>
@@ -35952,7 +35952,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.17476606369019</v>
+        <v>5.17476654052734</v>
       </c>
       <c r="H1227" t="n">
         <v>335188</v>
@@ -35981,7 +35981,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1228" t="n">
-        <v>5.16735219955444</v>
+        <v>5.16735172271729</v>
       </c>
       <c r="H1228" t="n">
         <v>343066</v>
@@ -36010,7 +36010,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>5.40459156036377</v>
+        <v>5.40459108352661</v>
       </c>
       <c r="H1229" t="n">
         <v>382212</v>
@@ -36068,7 +36068,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.59734725952148</v>
+        <v>5.59734773635864</v>
       </c>
       <c r="H1231" t="n">
         <v>248006</v>
@@ -36155,7 +36155,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.6937255859375</v>
+        <v>5.69372606277466</v>
       </c>
       <c r="H1234" t="n">
         <v>364428</v>
@@ -36213,7 +36213,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1236" t="n">
-        <v>5.65665769577026</v>
+        <v>5.65665721893311</v>
       </c>
       <c r="H1236" t="n">
         <v>288095</v>
@@ -36271,7 +36271,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.79010391235352</v>
+        <v>5.79010343551636</v>
       </c>
       <c r="H1238" t="n">
         <v>185181</v>
@@ -36300,7 +36300,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.51664686203003</v>
+        <v>6.51664733886719</v>
       </c>
       <c r="H1239" t="n">
         <v>1181498</v>
@@ -36329,7 +36329,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1240" t="n">
-        <v>6.5018196105957</v>
+        <v>6.50182008743286</v>
       </c>
       <c r="H1240" t="n">
         <v>856188</v>
@@ -36358,7 +36358,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1241" t="n">
-        <v>6.56854248046875</v>
+        <v>6.56854295730591</v>
       </c>
       <c r="H1241" t="n">
         <v>708046</v>
@@ -36387,7 +36387,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1242" t="n">
-        <v>6.59078407287598</v>
+        <v>6.59078454971313</v>
       </c>
       <c r="H1242" t="n">
         <v>525574</v>
@@ -36416,7 +36416,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1243" t="n">
-        <v>6.33871793746948</v>
+        <v>6.33871841430664</v>
       </c>
       <c r="H1243" t="n">
         <v>535392</v>
@@ -36445,7 +36445,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1244" t="n">
-        <v>6.27940893173218</v>
+        <v>6.27940940856934</v>
       </c>
       <c r="H1244" t="n">
         <v>226764</v>
@@ -36474,7 +36474,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1245" t="n">
-        <v>6.24234056472778</v>
+        <v>6.24233961105347</v>
       </c>
       <c r="H1245" t="n">
         <v>371423</v>
@@ -36503,7 +36503,7 @@
         <v>8.25</v>
       </c>
       <c r="G1246" t="n">
-        <v>6.1163067817688</v>
+        <v>6.11630725860596</v>
       </c>
       <c r="H1246" t="n">
         <v>435902</v>
@@ -36532,7 +36532,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1247" t="n">
-        <v>6.04217004776001</v>
+        <v>6.04216957092285</v>
       </c>
       <c r="H1247" t="n">
         <v>194860</v>
@@ -36561,7 +36561,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1248" t="n">
-        <v>6.24975347518921</v>
+        <v>6.24975395202637</v>
       </c>
       <c r="H1248" t="n">
         <v>354024</v>
@@ -36590,7 +36590,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1249" t="n">
-        <v>6.19785737991333</v>
+        <v>6.19785785675049</v>
       </c>
       <c r="H1249" t="n">
         <v>114330</v>
@@ -36619,7 +36619,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>6.18303060531616</v>
+        <v>6.183030128479</v>
       </c>
       <c r="H1250" t="n">
         <v>175266</v>
@@ -36648,7 +36648,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1251" t="n">
-        <v>6.62043905258179</v>
+        <v>6.62043952941895</v>
       </c>
       <c r="H1251" t="n">
         <v>688617</v>
@@ -36677,7 +36677,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1252" t="n">
-        <v>6.50923347473145</v>
+        <v>6.50923299789429</v>
       </c>
       <c r="H1252" t="n">
         <v>525737</v>
@@ -36706,7 +36706,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1253" t="n">
-        <v>6.58337116241455</v>
+        <v>6.58337068557739</v>
       </c>
       <c r="H1253" t="n">
         <v>375451</v>
@@ -36735,7 +36735,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1254" t="n">
-        <v>6.57595634460449</v>
+        <v>6.57595729827881</v>
       </c>
       <c r="H1254" t="n">
         <v>163814</v>
@@ -36764,7 +36764,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1255" t="n">
-        <v>6.89474630355835</v>
+        <v>6.89474582672119</v>
       </c>
       <c r="H1255" t="n">
         <v>430212</v>
@@ -36793,7 +36793,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.11715698242188</v>
+        <v>7.11715793609619</v>
       </c>
       <c r="H1256" t="n">
         <v>593443</v>
@@ -36822,7 +36822,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1257" t="n">
-        <v>7.05784845352173</v>
+        <v>7.05784749984741</v>
       </c>
       <c r="H1257" t="n">
         <v>838572</v>
@@ -36851,7 +36851,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1258" t="n">
-        <v>7.06526041030884</v>
+        <v>7.06526136398315</v>
       </c>
       <c r="H1258" t="n">
         <v>640753</v>
@@ -36880,7 +36880,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.05043315887451</v>
+        <v>7.05043458938599</v>
       </c>
       <c r="H1259" t="n">
         <v>255311</v>
@@ -36938,7 +36938,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1261" t="n">
-        <v>7.54715299606323</v>
+        <v>7.54715251922607</v>
       </c>
       <c r="H1261" t="n">
         <v>292983</v>
@@ -37083,7 +37083,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1266" t="n">
-        <v>7.94749307632446</v>
+        <v>7.94749212265015</v>
       </c>
       <c r="H1266" t="n">
         <v>283644</v>
@@ -37112,7 +37112,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.82887411117554</v>
+        <v>7.82887268066406</v>
       </c>
       <c r="H1267" t="n">
         <v>125181</v>
@@ -37170,7 +37170,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1269" t="n">
-        <v>7.88818359375</v>
+        <v>7.88818264007568</v>
       </c>
       <c r="H1269" t="n">
         <v>363211</v>
@@ -37199,7 +37199,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.99197483062744</v>
+        <v>7.99197435379028</v>
       </c>
       <c r="H1270" t="n">
         <v>264650</v>
@@ -37228,7 +37228,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1271" t="n">
-        <v>8.05128479003906</v>
+        <v>8.05128383636475</v>
       </c>
       <c r="H1271" t="n">
         <v>456415</v>
@@ -37257,7 +37257,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1272" t="n">
-        <v>8.00680255889893</v>
+        <v>8.00680160522461</v>
       </c>
       <c r="H1272" t="n">
         <v>329470</v>
@@ -37315,7 +37315,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.68059921264648</v>
+        <v>7.68059873580933</v>
       </c>
       <c r="H1274" t="n">
         <v>508688</v>
@@ -37344,7 +37344,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>7.54715299606323</v>
+        <v>7.54715251922607</v>
       </c>
       <c r="H1275" t="n">
         <v>266888</v>
@@ -37373,7 +37373,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.59163427352905</v>
+        <v>7.59163379669189</v>
       </c>
       <c r="H1276" t="n">
         <v>279624</v>
@@ -37489,7 +37489,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G1280" t="n">
-        <v>7.33215427398682</v>
+        <v>7.33215475082397</v>
       </c>
       <c r="H1280" t="n">
         <v>468812</v>
@@ -37547,7 +37547,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.23577737808228</v>
+        <v>7.23577642440796</v>
       </c>
       <c r="H1282" t="n">
         <v>339904</v>
@@ -37663,7 +37663,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.05784845352173</v>
+        <v>7.05784749984741</v>
       </c>
       <c r="H1286" t="n">
         <v>198903</v>
@@ -37721,7 +37721,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1288" t="n">
-        <v>7.08008909225464</v>
+        <v>7.08008861541748</v>
       </c>
       <c r="H1288" t="n">
         <v>551582</v>
@@ -37750,7 +37750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.19129467010498</v>
+        <v>7.19129371643066</v>
       </c>
       <c r="H1289" t="n">
         <v>237577</v>
@@ -37924,7 +37924,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.90300941467285</v>
+        <v>7.90300989151001</v>
       </c>
       <c r="H1295" t="n">
         <v>568968</v>
@@ -37982,7 +37982,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1297" t="n">
-        <v>8.00680255889893</v>
+        <v>8.00680160522461</v>
       </c>
       <c r="H1297" t="n">
         <v>702296</v>
@@ -38011,7 +38011,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1298" t="n">
-        <v>7.97714710235596</v>
+        <v>7.9771466255188</v>
       </c>
       <c r="H1298" t="n">
         <v>722047</v>
@@ -38098,7 +38098,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1301" t="n">
-        <v>8.49610710144043</v>
+        <v>8.49610614776611</v>
       </c>
       <c r="H1301" t="n">
         <v>302498</v>
@@ -38127,7 +38127,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1302" t="n">
-        <v>8.49610710144043</v>
+        <v>8.49610614776611</v>
       </c>
       <c r="H1302" t="n">
         <v>202294</v>
@@ -38185,7 +38185,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>8.28852367401123</v>
+        <v>8.28852272033691</v>
       </c>
       <c r="H1304" t="n">
         <v>211448</v>
@@ -38243,7 +38243,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1306" t="n">
-        <v>8.31817817687988</v>
+        <v>8.31817722320557</v>
       </c>
       <c r="H1306" t="n">
         <v>89949</v>
@@ -38272,7 +38272,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1307" t="n">
-        <v>8.51093292236328</v>
+        <v>8.5109338760376</v>
       </c>
       <c r="H1307" t="n">
         <v>424361</v>
@@ -38330,7 +38330,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1309" t="n">
-        <v>7.99197483062744</v>
+        <v>7.99197435379028</v>
       </c>
       <c r="H1309" t="n">
         <v>283023</v>
@@ -38359,7 +38359,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.84369993209839</v>
+        <v>7.84370040893555</v>
       </c>
       <c r="H1310" t="n">
         <v>221178</v>
@@ -38388,7 +38388,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1311" t="n">
-        <v>7.73990774154663</v>
+        <v>7.73990917205811</v>
       </c>
       <c r="H1311" t="n">
         <v>269913</v>
@@ -38417,7 +38417,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1312" t="n">
-        <v>7.90300941467285</v>
+        <v>7.90300989151001</v>
       </c>
       <c r="H1312" t="n">
         <v>1133698</v>
@@ -38446,7 +38446,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1313" t="n">
-        <v>7.85852766036987</v>
+        <v>7.85852813720703</v>
       </c>
       <c r="H1313" t="n">
         <v>533862</v>
@@ -38533,7 +38533,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1316" t="n">
-        <v>7.29508686065674</v>
+        <v>7.29508638381958</v>
       </c>
       <c r="H1316" t="n">
         <v>473082</v>
@@ -38620,7 +38620,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>7.69542598724365</v>
+        <v>7.69542646408081</v>
       </c>
       <c r="H1319" t="n">
         <v>388891</v>
@@ -38649,7 +38649,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1320" t="n">
-        <v>7.59163427352905</v>
+        <v>7.59163379669189</v>
       </c>
       <c r="H1320" t="n">
         <v>242496</v>
@@ -38678,7 +38678,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1321" t="n">
-        <v>7.51749706268311</v>
+        <v>7.51749801635742</v>
       </c>
       <c r="H1321" t="n">
         <v>215080</v>
@@ -38707,7 +38707,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1322" t="n">
-        <v>7.75473594665527</v>
+        <v>7.75473690032959</v>
       </c>
       <c r="H1322" t="n">
         <v>498215</v>
@@ -38736,7 +38736,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1323" t="n">
-        <v>7.50266981124878</v>
+        <v>7.50267028808594</v>
       </c>
       <c r="H1323" t="n">
         <v>392802</v>
@@ -38765,7 +38765,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1324" t="n">
-        <v>7.62128829956055</v>
+        <v>7.62128877639771</v>
       </c>
       <c r="H1324" t="n">
         <v>262438</v>
@@ -38794,7 +38794,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1325" t="n">
-        <v>7.62128829956055</v>
+        <v>7.62128877639771</v>
       </c>
       <c r="H1325" t="n">
         <v>298270</v>
@@ -38910,7 +38910,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1329" t="n">
-        <v>7.84369993209839</v>
+        <v>7.84370040893555</v>
       </c>
       <c r="H1329" t="n">
         <v>200870</v>
@@ -38939,7 +38939,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>8.00680255889893</v>
+        <v>8.00680160522461</v>
       </c>
       <c r="H1330" t="n">
         <v>408298</v>
@@ -38968,7 +38968,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1331" t="n">
-        <v>8.24403953552246</v>
+        <v>8.24404048919678</v>
       </c>
       <c r="H1331" t="n">
         <v>405165</v>
@@ -38997,7 +38997,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1332" t="n">
-        <v>7.99197483062744</v>
+        <v>7.99197435379028</v>
       </c>
       <c r="H1332" t="n">
         <v>400894</v>
@@ -39026,7 +39026,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1333" t="n">
-        <v>7.97714710235596</v>
+        <v>7.9771466255188</v>
       </c>
       <c r="H1333" t="n">
         <v>197842</v>
@@ -39055,7 +39055,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1334" t="n">
-        <v>8.0809383392334</v>
+        <v>8.08093929290771</v>
       </c>
       <c r="H1334" t="n">
         <v>250595</v>
@@ -39084,7 +39084,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G1335" t="n">
-        <v>8.16248989105225</v>
+        <v>8.16249084472656</v>
       </c>
       <c r="H1335" t="n">
         <v>181471</v>
@@ -39113,7 +39113,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1336" t="n">
-        <v>8.42196846008301</v>
+        <v>8.42196941375732</v>
       </c>
       <c r="H1336" t="n">
         <v>447036</v>
@@ -39200,7 +39200,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1339" t="n">
-        <v>9.75643634796143</v>
+        <v>9.75643539428711</v>
       </c>
       <c r="H1339" t="n">
         <v>1219155</v>
@@ -39229,7 +39229,7 @@
         <v>13.5</v>
       </c>
       <c r="G1340" t="n">
-        <v>10.0085029602051</v>
+        <v>10.0085020065308</v>
       </c>
       <c r="H1340" t="n">
         <v>837762</v>
@@ -39258,7 +39258,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1341" t="n">
-        <v>10.0010890960693</v>
+        <v>10.001088142395</v>
       </c>
       <c r="H1341" t="n">
         <v>394107</v>
@@ -39287,7 +39287,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.68229866027832</v>
+        <v>9.68229961395264</v>
       </c>
       <c r="H1342" t="n">
         <v>618401</v>
@@ -39374,7 +39374,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.9566068649292</v>
+        <v>9.95660781860352</v>
       </c>
       <c r="H1345" t="n">
         <v>608465</v>
@@ -39403,7 +39403,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1346" t="n">
-        <v>10.0752258300781</v>
+        <v>10.0752248764038</v>
       </c>
       <c r="H1346" t="n">
         <v>298506</v>
@@ -39461,7 +39461,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1348" t="n">
-        <v>10.21608543396</v>
+        <v>10.2160863876343</v>
       </c>
       <c r="H1348" t="n">
         <v>466501</v>
@@ -39519,7 +39519,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1350" t="n">
-        <v>10.1122951507568</v>
+        <v>10.1122941970825</v>
       </c>
       <c r="H1350" t="n">
         <v>618145</v>
@@ -39548,7 +39548,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1351" t="n">
-        <v>10.0603981018066</v>
+        <v>10.0603971481323</v>
       </c>
       <c r="H1351" t="n">
         <v>623280</v>
@@ -39577,7 +39577,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1352" t="n">
-        <v>10.0603981018066</v>
+        <v>10.0603971481323</v>
       </c>
       <c r="H1352" t="n">
         <v>460591</v>
@@ -39606,7 +39606,7 @@
         <v>13.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>10.0085029602051</v>
+        <v>10.0085020065308</v>
       </c>
       <c r="H1353" t="n">
         <v>305598</v>
@@ -39664,7 +39664,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.9566068649292</v>
+        <v>9.95660781860352</v>
       </c>
       <c r="H1355" t="n">
         <v>386695</v>
@@ -39693,7 +39693,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1356" t="n">
-        <v>10.1048812866211</v>
+        <v>10.1048803329468</v>
       </c>
       <c r="H1356" t="n">
         <v>410809</v>
@@ -39722,7 +39722,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1357" t="n">
-        <v>9.97884845733643</v>
+        <v>9.97884750366211</v>
       </c>
       <c r="H1357" t="n">
         <v>246480</v>
@@ -39780,7 +39780,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G1359" t="n">
-        <v>10.0285968780518</v>
+        <v>10.0285978317261</v>
       </c>
       <c r="H1359" t="n">
         <v>363619</v>
@@ -39809,7 +39809,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1360" t="n">
-        <v>10.0440378189087</v>
+        <v>10.044038772583</v>
       </c>
       <c r="H1360" t="n">
         <v>568930</v>
@@ -39838,7 +39838,7 @@
         <v>13.25</v>
       </c>
       <c r="G1361" t="n">
-        <v>10.2293243408203</v>
+        <v>10.229323387146</v>
       </c>
       <c r="H1361" t="n">
         <v>481650</v>
@@ -39925,7 +39925,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1364" t="n">
-        <v>10.329686164856</v>
+        <v>10.3296880722046</v>
       </c>
       <c r="H1364" t="n">
         <v>901307</v>
@@ -39954,7 +39954,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1365" t="n">
-        <v>10.2524852752686</v>
+        <v>10.2524843215942</v>
       </c>
       <c r="H1365" t="n">
         <v>930701</v>
@@ -40012,7 +40012,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G1367" t="n">
-        <v>10.7851819992065</v>
+        <v>10.7851810455322</v>
       </c>
       <c r="H1367" t="n">
         <v>734935</v>
@@ -40128,7 +40128,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1371" t="n">
-        <v>10.3914499282837</v>
+        <v>10.3914489746094</v>
       </c>
       <c r="H1371" t="n">
         <v>333184</v>
@@ -40157,7 +40157,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1372" t="n">
-        <v>10.6616582870483</v>
+        <v>10.661657333374</v>
       </c>
       <c r="H1372" t="n">
         <v>1102741</v>
@@ -40186,7 +40186,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G1373" t="n">
-        <v>10.8160619735718</v>
+        <v>10.8160629272461</v>
       </c>
       <c r="H1373" t="n">
         <v>496342</v>
@@ -40244,7 +40244,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1375" t="n">
-        <v>11.2252349853516</v>
+        <v>11.2252359390259</v>
       </c>
       <c r="H1375" t="n">
         <v>441675</v>
@@ -40273,7 +40273,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1376" t="n">
-        <v>11.3796405792236</v>
+        <v>11.3796396255493</v>
       </c>
       <c r="H1376" t="n">
         <v>602612</v>
@@ -40331,7 +40331,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.4722833633423</v>
+        <v>11.472282409668</v>
       </c>
       <c r="H1378" t="n">
         <v>404357</v>
@@ -40389,7 +40389,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1380" t="n">
-        <v>11.6884508132935</v>
+        <v>11.6884498596191</v>
       </c>
       <c r="H1380" t="n">
         <v>637306</v>
@@ -40418,7 +40418,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1381" t="n">
-        <v>11.9818201065063</v>
+        <v>11.981819152832</v>
       </c>
       <c r="H1381" t="n">
         <v>704671</v>
@@ -40505,7 +40505,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.1207828521729</v>
+        <v>12.1207847595215</v>
       </c>
       <c r="H1384" t="n">
         <v>271506</v>
@@ -40563,7 +40563,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>11.6575689315796</v>
+        <v>11.6575698852539</v>
       </c>
       <c r="H1386" t="n">
         <v>248187</v>
@@ -40621,7 +40621,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1388" t="n">
-        <v>11.7038898468018</v>
+        <v>11.7038908004761</v>
       </c>
       <c r="H1388" t="n">
         <v>343893</v>
@@ -40650,7 +40650,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1389" t="n">
-        <v>11.9895391464233</v>
+        <v>11.9895401000977</v>
       </c>
       <c r="H1389" t="n">
         <v>280927</v>
@@ -40766,7 +40766,7 @@
         <v>15</v>
       </c>
       <c r="G1393" t="n">
-        <v>11.5803661346436</v>
+        <v>11.5803670883179</v>
       </c>
       <c r="H1393" t="n">
         <v>123407</v>
@@ -40795,7 +40795,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1394" t="n">
-        <v>11.6575689315796</v>
+        <v>11.6575698852539</v>
       </c>
       <c r="H1394" t="n">
         <v>177496</v>
@@ -40824,7 +40824,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1395" t="n">
-        <v>11.4259624481201</v>
+        <v>11.4259614944458</v>
       </c>
       <c r="H1395" t="n">
         <v>166375</v>
@@ -40911,7 +40911,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G1398" t="n">
-        <v>11.6652898788452</v>
+        <v>11.6652889251709</v>
       </c>
       <c r="H1398" t="n">
         <v>221248</v>
@@ -40940,7 +40940,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>11.6575689315796</v>
+        <v>11.6575698852539</v>
       </c>
       <c r="H1399" t="n">
         <v>196451</v>
@@ -40998,7 +40998,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1401" t="n">
-        <v>11.9586591720581</v>
+        <v>11.9586582183838</v>
       </c>
       <c r="H1401" t="n">
         <v>275938</v>
@@ -41085,7 +41085,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1404" t="n">
-        <v>11.4800033569336</v>
+        <v>11.4800043106079</v>
       </c>
       <c r="H1404" t="n">
         <v>229570</v>
@@ -41114,7 +41114,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>12.2365884780884</v>
+        <v>12.2365875244141</v>
       </c>
       <c r="H1405" t="n">
         <v>815649</v>
@@ -41172,7 +41172,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G1407" t="n">
-        <v>11.819694519043</v>
+        <v>11.8196954727173</v>
       </c>
       <c r="H1407" t="n">
         <v>373868</v>
@@ -41201,7 +41201,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G1408" t="n">
-        <v>11.8351354598999</v>
+        <v>11.8351345062256</v>
       </c>
       <c r="H1408" t="n">
         <v>203447</v>
@@ -41230,7 +41230,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.1017112731934</v>
+        <v>11.1017122268677</v>
       </c>
       <c r="H1409" t="n">
         <v>337873</v>
@@ -41259,7 +41259,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.0476703643799</v>
+        <v>11.0476694107056</v>
       </c>
       <c r="H1410" t="n">
         <v>171270</v>
@@ -41288,7 +41288,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1411" t="n">
-        <v>11.3950805664062</v>
+        <v>11.3950824737549</v>
       </c>
       <c r="H1411" t="n">
         <v>189384</v>
@@ -41491,7 +41491,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1418" t="n">
-        <v>11.9895391464233</v>
+        <v>11.9895401000977</v>
       </c>
       <c r="H1418" t="n">
         <v>184001</v>
@@ -41607,7 +41607,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.2365884780884</v>
+        <v>12.2365875244141</v>
       </c>
       <c r="H1422" t="n">
         <v>185558</v>
@@ -41694,7 +41694,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1425" t="n">
-        <v>12.4064331054688</v>
+        <v>12.4064321517944</v>
       </c>
       <c r="H1425" t="n">
         <v>220398</v>
@@ -41868,7 +41868,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1431" t="n">
-        <v>12.8542070388794</v>
+        <v>12.8542060852051</v>
       </c>
       <c r="H1431" t="n">
         <v>391628</v>
@@ -41955,7 +41955,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.0435829162598</v>
+        <v>12.0435819625854</v>
       </c>
       <c r="H1434" t="n">
         <v>397932</v>
@@ -42042,7 +42042,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>12.0435829162598</v>
+        <v>12.0435819625854</v>
       </c>
       <c r="H1437" t="n">
         <v>179780</v>
@@ -42187,7 +42187,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.2751893997192</v>
+        <v>12.2751884460449</v>
       </c>
       <c r="H1442" t="n">
         <v>199236</v>
@@ -42245,7 +42245,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G1444" t="n">
-        <v>12.3755531311035</v>
+        <v>12.3755521774292</v>
       </c>
       <c r="H1444" t="n">
         <v>154059</v>
@@ -42332,7 +42332,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1447" t="n">
-        <v>10.5149717330933</v>
+        <v>10.5149726867676</v>
       </c>
       <c r="H1447" t="n">
         <v>1307534</v>
@@ -42419,7 +42419,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0749187469482</v>
+        <v>10.0749197006226</v>
       </c>
       <c r="H1450" t="n">
         <v>1314808</v>
@@ -42564,7 +42564,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1455" t="n">
-        <v>9.27201461791992</v>
+        <v>9.27201366424561</v>
       </c>
       <c r="H1455" t="n">
         <v>351449</v>
@@ -42622,7 +42622,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G1457" t="n">
-        <v>9.58082389831543</v>
+        <v>9.58082294464111</v>
       </c>
       <c r="H1457" t="n">
         <v>330734</v>
@@ -42651,7 +42651,7 @@
         <v>12</v>
       </c>
       <c r="G1458" t="n">
-        <v>9.26429271697998</v>
+        <v>9.26429462432861</v>
       </c>
       <c r="H1458" t="n">
         <v>357284</v>
@@ -42767,7 +42767,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.73159790039062</v>
+        <v>8.73159694671631</v>
       </c>
       <c r="H1462" t="n">
         <v>423384</v>
@@ -42796,7 +42796,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1463" t="n">
-        <v>8.77019691467285</v>
+        <v>8.77019786834717</v>
       </c>
       <c r="H1463" t="n">
         <v>308620</v>
@@ -42825,7 +42825,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1464" t="n">
-        <v>8.53859043121338</v>
+        <v>8.5385913848877</v>
       </c>
       <c r="H1464" t="n">
         <v>545701</v>
@@ -42854,7 +42854,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.52315044403076</v>
+        <v>8.52314949035645</v>
       </c>
       <c r="H1465" t="n">
         <v>397323</v>
@@ -42912,7 +42912,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>8.73931694030762</v>
+        <v>8.7393159866333</v>
       </c>
       <c r="H1467" t="n">
         <v>613279</v>
@@ -42941,7 +42941,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1468" t="n">
-        <v>8.89372158050537</v>
+        <v>8.89372253417969</v>
       </c>
       <c r="H1468" t="n">
         <v>665310</v>
@@ -42970,7 +42970,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1469" t="n">
-        <v>8.67755508422852</v>
+        <v>8.6775541305542</v>
       </c>
       <c r="H1469" t="n">
         <v>565181</v>
@@ -43057,7 +43057,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1472" t="n">
-        <v>8.8474006652832</v>
+        <v>8.84739971160889</v>
       </c>
       <c r="H1472" t="n">
         <v>457138</v>
@@ -43115,7 +43115,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1474" t="n">
-        <v>9.27201461791992</v>
+        <v>9.27201366424561</v>
       </c>
       <c r="H1474" t="n">
         <v>637336</v>
@@ -43144,7 +43144,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1475" t="n">
-        <v>9.04040622711182</v>
+        <v>9.04040718078613</v>
       </c>
       <c r="H1475" t="n">
         <v>421275</v>
@@ -43173,7 +43173,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G1476" t="n">
-        <v>9.05584716796875</v>
+        <v>9.05584621429443</v>
       </c>
       <c r="H1476" t="n">
         <v>304953</v>
@@ -43231,7 +43231,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1478" t="n">
-        <v>9.12532806396484</v>
+        <v>9.12532901763916</v>
       </c>
       <c r="H1478" t="n">
         <v>221754</v>
@@ -43289,7 +43289,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1480" t="n">
-        <v>9.15620899200439</v>
+        <v>9.15620994567871</v>
       </c>
       <c r="H1480" t="n">
         <v>244389</v>
@@ -43434,7 +43434,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1485" t="n">
-        <v>9.2025318145752</v>
+        <v>9.20253086090088</v>
       </c>
       <c r="H1485" t="n">
         <v>621775</v>
@@ -43521,7 +43521,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G1488" t="n">
-        <v>9.6271448135376</v>
+        <v>9.62714576721191</v>
       </c>
       <c r="H1488" t="n">
         <v>370289</v>
@@ -43579,7 +43579,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.71978759765625</v>
+        <v>9.71978664398193</v>
       </c>
       <c r="H1490" t="n">
         <v>386060</v>
@@ -43608,7 +43608,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1491" t="n">
-        <v>9.5653829574585</v>
+        <v>9.56538391113281</v>
       </c>
       <c r="H1491" t="n">
         <v>285731</v>
@@ -43753,7 +43753,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>9.70434665679932</v>
+        <v>9.70434761047363</v>
       </c>
       <c r="H1496" t="n">
         <v>479345</v>
@@ -43782,7 +43782,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1497" t="n">
-        <v>9.66574573516846</v>
+        <v>9.66574668884277</v>
       </c>
       <c r="H1497" t="n">
         <v>248033</v>
@@ -43811,7 +43811,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1498" t="n">
-        <v>9.58854484558105</v>
+        <v>9.58854293823242</v>
       </c>
       <c r="H1498" t="n">
         <v>260428</v>
@@ -43898,7 +43898,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1501" t="n">
-        <v>9.06356716156006</v>
+        <v>9.06356620788574</v>
       </c>
       <c r="H1501" t="n">
         <v>189209</v>
@@ -44246,7 +44246,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1513" t="n">
-        <v>9.94367504119873</v>
+        <v>9.94367599487305</v>
       </c>
       <c r="H1513" t="n">
         <v>232655</v>
@@ -44275,7 +44275,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1514" t="n">
-        <v>9.35693645477295</v>
+        <v>9.35693550109863</v>
       </c>
       <c r="H1514" t="n">
         <v>372311</v>
@@ -44391,7 +44391,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1518" t="n">
-        <v>9.12532806396484</v>
+        <v>9.12532901763916</v>
       </c>
       <c r="H1518" t="n">
         <v>128055</v>
@@ -44420,7 +44420,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1519" t="n">
-        <v>9.15620899200439</v>
+        <v>9.15620994567871</v>
       </c>
       <c r="H1519" t="n">
         <v>156153</v>
@@ -44449,7 +44449,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1520" t="n">
-        <v>9.30289459228516</v>
+        <v>9.30289554595947</v>
       </c>
       <c r="H1520" t="n">
         <v>117990</v>
@@ -44507,7 +44507,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1522" t="n">
-        <v>9.64258480072021</v>
+        <v>9.64258575439453</v>
       </c>
       <c r="H1522" t="n">
         <v>154036</v>
@@ -44623,7 +44623,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>9.95911502838135</v>
+        <v>9.95911598205566</v>
       </c>
       <c r="H1526" t="n">
         <v>107589</v>
@@ -44739,7 +44739,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1530" t="n">
-        <v>9.71978759765625</v>
+        <v>9.71978664398193</v>
       </c>
       <c r="H1530" t="n">
         <v>157471</v>
@@ -44768,7 +44768,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1531" t="n">
-        <v>9.54994297027588</v>
+        <v>9.54994201660156</v>
       </c>
       <c r="H1531" t="n">
         <v>137558</v>
@@ -44797,7 +44797,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.99408531188965</v>
+        <v>8.99408435821533</v>
       </c>
       <c r="H1532" t="n">
         <v>392300</v>
@@ -44884,7 +44884,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1535" t="n">
-        <v>9.33377552032471</v>
+        <v>9.33377456665039</v>
       </c>
       <c r="H1535" t="n">
         <v>78244</v>
@@ -45029,7 +45029,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1540" t="n">
-        <v>9.64258480072021</v>
+        <v>9.64258575439453</v>
       </c>
       <c r="H1540" t="n">
         <v>178357</v>
@@ -45058,7 +45058,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G1541" t="n">
-        <v>9.39553833007812</v>
+        <v>9.39553737640381</v>
       </c>
       <c r="H1541" t="n">
         <v>167766</v>
@@ -45087,7 +45087,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1542" t="n">
-        <v>9.04040622711182</v>
+        <v>9.04040718078613</v>
       </c>
       <c r="H1542" t="n">
         <v>215965</v>
@@ -45203,7 +45203,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1546" t="n">
-        <v>9.2102518081665</v>
+        <v>9.21025085449219</v>
       </c>
       <c r="H1546" t="n">
         <v>197903</v>
@@ -45232,7 +45232,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1547" t="n">
-        <v>9.32605648040771</v>
+        <v>9.3260555267334</v>
       </c>
       <c r="H1547" t="n">
         <v>179621</v>
@@ -45261,7 +45261,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1548" t="n">
-        <v>9.71978759765625</v>
+        <v>9.71978664398193</v>
       </c>
       <c r="H1548" t="n">
         <v>360949</v>
@@ -45290,7 +45290,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1549" t="n">
-        <v>9.71978759765625</v>
+        <v>9.71978664398193</v>
       </c>
       <c r="H1549" t="n">
         <v>482932</v>
@@ -45406,7 +45406,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>9.12532806396484</v>
+        <v>9.12532901763916</v>
       </c>
       <c r="H1553" t="n">
         <v>143035</v>
@@ -45493,7 +45493,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1556" t="n">
-        <v>9.32605648040771</v>
+        <v>9.3260555267334</v>
       </c>
       <c r="H1556" t="n">
         <v>62049</v>
@@ -45522,7 +45522,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>9.03268623352051</v>
+        <v>9.03268527984619</v>
       </c>
       <c r="H1557" t="n">
         <v>395628</v>
@@ -45551,7 +45551,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1558" t="n">
-        <v>9.30289459228516</v>
+        <v>9.30289554595947</v>
       </c>
       <c r="H1558" t="n">
         <v>93185</v>
@@ -45580,7 +45580,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1559" t="n">
-        <v>9.21797275543213</v>
+        <v>9.21797180175781</v>
       </c>
       <c r="H1559" t="n">
         <v>153524</v>
@@ -45667,7 +45667,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1562" t="n">
-        <v>8.60035228729248</v>
+        <v>8.6003532409668</v>
       </c>
       <c r="H1562" t="n">
         <v>249020</v>
@@ -45812,7 +45812,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1567" t="n">
-        <v>8.60807228088379</v>
+        <v>8.60807132720947</v>
       </c>
       <c r="H1567" t="n">
         <v>142978</v>
@@ -45841,7 +45841,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1568" t="n">
-        <v>8.27610301971436</v>
+        <v>8.27610206604004</v>
       </c>
       <c r="H1568" t="n">
         <v>170280</v>
@@ -45870,7 +45870,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1569" t="n">
-        <v>8.22206020355225</v>
+        <v>8.22205924987793</v>
       </c>
       <c r="H1569" t="n">
         <v>129147</v>
@@ -45899,7 +45899,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1570" t="n">
-        <v>7.85148859024048</v>
+        <v>7.85148906707764</v>
       </c>
       <c r="H1570" t="n">
         <v>180435</v>
@@ -45928,7 +45928,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.25702905654907</v>
+        <v>7.25702953338623</v>
       </c>
       <c r="H1571" t="n">
         <v>300725</v>
@@ -45957,7 +45957,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1572" t="n">
-        <v>6.82469606399536</v>
+        <v>6.82469654083252</v>
       </c>
       <c r="H1572" t="n">
         <v>388423</v>
@@ -45986,7 +45986,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1573" t="n">
-        <v>6.57764911651611</v>
+        <v>6.57764863967896</v>
       </c>
       <c r="H1573" t="n">
         <v>486838</v>
@@ -46102,7 +46102,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1577" t="n">
-        <v>7.26475048065186</v>
+        <v>7.2647500038147</v>
       </c>
       <c r="H1577" t="n">
         <v>298297</v>
@@ -46189,7 +46189,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.43459606170654</v>
+        <v>7.43459558486938</v>
       </c>
       <c r="H1580" t="n">
         <v>320480</v>
@@ -46218,7 +46218,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.32265090942383</v>
+        <v>7.32265186309814</v>
       </c>
       <c r="H1581" t="n">
         <v>540737</v>
@@ -46247,7 +46247,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>7.30335092544556</v>
+        <v>7.30335187911987</v>
       </c>
       <c r="H1582" t="n">
         <v>184597</v>
@@ -46334,7 +46334,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1585" t="n">
-        <v>7.43459606170654</v>
+        <v>7.43459558486938</v>
       </c>
       <c r="H1585" t="n">
         <v>132184</v>
@@ -46363,7 +46363,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.53881883621216</v>
+        <v>7.53881931304932</v>
       </c>
       <c r="H1586" t="n">
         <v>148850</v>
@@ -46392,7 +46392,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1587" t="n">
-        <v>7.51951789855957</v>
+        <v>7.51951742172241</v>
       </c>
       <c r="H1587" t="n">
         <v>131453</v>
@@ -46450,7 +46450,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.70866298675537</v>
+        <v>7.70866394042969</v>
       </c>
       <c r="H1589" t="n">
         <v>87262</v>
@@ -46508,7 +46508,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1591" t="n">
-        <v>7.51951789855957</v>
+        <v>7.51951742172241</v>
       </c>
       <c r="H1591" t="n">
         <v>97704</v>
@@ -46566,7 +46566,7 @@
         <v>9.77499961853027</v>
       </c>
       <c r="G1593" t="n">
-        <v>7.54653978347778</v>
+        <v>7.54653882980347</v>
       </c>
       <c r="H1593" t="n">
         <v>229966</v>
@@ -46624,7 +46624,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1595" t="n">
-        <v>7.15280675888062</v>
+        <v>7.15280723571777</v>
       </c>
       <c r="H1595" t="n">
         <v>127676</v>
@@ -46682,7 +46682,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.39213371276855</v>
+        <v>7.39213418960571</v>
       </c>
       <c r="H1597" t="n">
         <v>119048</v>
@@ -46740,7 +46740,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1599" t="n">
-        <v>7.3844141960144</v>
+        <v>7.38441324234009</v>
       </c>
       <c r="H1599" t="n">
         <v>131459</v>
@@ -46769,7 +46769,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1600" t="n">
-        <v>7.26475048065186</v>
+        <v>7.2647500038147</v>
       </c>
       <c r="H1600" t="n">
         <v>138249</v>
@@ -46827,7 +46827,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G1602" t="n">
-        <v>7.46161556243896</v>
+        <v>7.46161603927612</v>
       </c>
       <c r="H1602" t="n">
         <v>110984</v>
@@ -46856,7 +46856,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1603" t="n">
-        <v>7.58127975463867</v>
+        <v>7.58127927780151</v>
       </c>
       <c r="H1603" t="n">
         <v>124067</v>
@@ -46885,7 +46885,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.58513975143433</v>
+        <v>7.58514022827148</v>
       </c>
       <c r="H1604" t="n">
         <v>244599</v>
@@ -46943,7 +46943,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1606" t="n">
-        <v>6.86216259002686</v>
+        <v>6.8621621131897</v>
       </c>
       <c r="H1606" t="n">
         <v>382220</v>
@@ -47001,7 +47001,7 @@
         <v>8.71500015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.11949348449707</v>
+        <v>7.11949396133423</v>
       </c>
       <c r="H1608" t="n">
         <v>262831</v>
@@ -47117,7 +47117,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>6.97653198242188</v>
+        <v>6.97653150558472</v>
       </c>
       <c r="H1612" t="n">
         <v>102044</v>
@@ -47146,7 +47146,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1613" t="n">
-        <v>6.86216259002686</v>
+        <v>6.8621621131897</v>
       </c>
       <c r="H1613" t="n">
         <v>157913</v>
@@ -47291,7 +47291,7 @@
         <v>8.03499984741211</v>
       </c>
       <c r="G1618" t="n">
-        <v>6.5639853477478</v>
+        <v>6.56398487091064</v>
       </c>
       <c r="H1618" t="n">
         <v>231804</v>
@@ -47320,7 +47320,7 @@
         <v>8.25</v>
       </c>
       <c r="G1619" t="n">
-        <v>6.73962354660034</v>
+        <v>6.7396240234375</v>
       </c>
       <c r="H1619" t="n">
         <v>200946</v>
@@ -47523,7 +47523,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1626" t="n">
-        <v>6.08199977874756</v>
+        <v>6.08200025558472</v>
       </c>
       <c r="H1626" t="n">
         <v>412884</v>
@@ -47552,7 +47552,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1627" t="n">
-        <v>6.20045471191406</v>
+        <v>6.2004542350769</v>
       </c>
       <c r="H1627" t="n">
         <v>229989</v>
@@ -47639,7 +47639,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G1630" t="n">
-        <v>6.62933921813965</v>
+        <v>6.62933874130249</v>
       </c>
       <c r="H1630" t="n">
         <v>230256</v>
@@ -47755,7 +47755,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1634" t="n">
-        <v>6.43736171722412</v>
+        <v>6.43736219406128</v>
       </c>
       <c r="H1634" t="n">
         <v>68806</v>
@@ -47813,7 +47813,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1636" t="n">
-        <v>6.60891628265381</v>
+        <v>6.60891580581665</v>
       </c>
       <c r="H1636" t="n">
         <v>123099</v>
@@ -47842,7 +47842,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1637" t="n">
-        <v>6.52722311019897</v>
+        <v>6.52722406387329</v>
       </c>
       <c r="H1637" t="n">
         <v>107001</v>
@@ -47929,7 +47929,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1640" t="n">
-        <v>6.00847673416138</v>
+        <v>6.00847721099854</v>
       </c>
       <c r="H1640" t="n">
         <v>289133</v>
@@ -48016,7 +48016,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1643" t="n">
-        <v>6.00847673416138</v>
+        <v>6.00847721099854</v>
       </c>
       <c r="H1643" t="n">
         <v>166032</v>
@@ -48045,7 +48045,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1644" t="n">
-        <v>6.08199977874756</v>
+        <v>6.08200025558472</v>
       </c>
       <c r="H1644" t="n">
         <v>97964</v>
@@ -48161,7 +48161,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G1648" t="n">
-        <v>5.96763038635254</v>
+        <v>5.9676308631897</v>
       </c>
       <c r="H1648" t="n">
         <v>39412</v>
@@ -48190,7 +48190,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1649" t="n">
-        <v>6.06157684326172</v>
+        <v>6.06157732009888</v>
       </c>
       <c r="H1649" t="n">
         <v>104979</v>
@@ -48306,7 +48306,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G1653" t="n">
-        <v>5.58367681503296</v>
+        <v>5.5836763381958</v>
       </c>
       <c r="H1653" t="n">
         <v>282559</v>
@@ -48364,7 +48364,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1655" t="n">
-        <v>5.55508422851562</v>
+        <v>5.55508470535278</v>
       </c>
       <c r="H1655" t="n">
         <v>102311</v>
@@ -48451,7 +48451,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1658" t="n">
-        <v>5.68579196929932</v>
+        <v>5.68579149246216</v>
       </c>
       <c r="H1658" t="n">
         <v>93517</v>
@@ -48596,7 +48596,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.3631067276001</v>
+        <v>5.36310720443726</v>
       </c>
       <c r="H1663" t="n">
         <v>81236</v>
@@ -48625,7 +48625,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.40395259857178</v>
+        <v>5.40395307540894</v>
       </c>
       <c r="H1664" t="n">
         <v>59050</v>
@@ -48654,7 +48654,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1665" t="n">
-        <v>5.44479942321777</v>
+        <v>5.44479894638062</v>
       </c>
       <c r="H1665" t="n">
         <v>75688</v>
@@ -48683,7 +48683,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.65311527252197</v>
+        <v>5.65311479568481</v>
       </c>
       <c r="H1666" t="n">
         <v>82525</v>
@@ -48741,7 +48741,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1668" t="n">
-        <v>5.72255325317383</v>
+        <v>5.72255373001099</v>
       </c>
       <c r="H1668" t="n">
         <v>64288</v>
@@ -48770,7 +48770,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1669" t="n">
-        <v>5.77565336227417</v>
+        <v>5.77565383911133</v>
       </c>
       <c r="H1669" t="n">
         <v>92082</v>
@@ -48915,7 +48915,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1674" t="n">
-        <v>5.75114583969116</v>
+        <v>5.751145362854</v>
       </c>
       <c r="H1674" t="n">
         <v>161796</v>
@@ -49002,7 +49002,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.73072290420532</v>
+        <v>5.73072242736816</v>
       </c>
       <c r="H1677" t="n">
         <v>90100</v>
@@ -49060,7 +49060,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G1679" t="n">
-        <v>5.71438407897949</v>
+        <v>5.71438455581665</v>
       </c>
       <c r="H1679" t="n">
         <v>79243</v>
@@ -49292,7 +49292,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1687" t="n">
-        <v>5.87368440628052</v>
+        <v>5.87368488311768</v>
       </c>
       <c r="H1687" t="n">
         <v>79212</v>
@@ -49321,7 +49321,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1688" t="n">
-        <v>5.80833053588867</v>
+        <v>5.80833101272583</v>
       </c>
       <c r="H1688" t="n">
         <v>97902</v>
@@ -49408,7 +49408,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1691" t="n">
-        <v>5.83283853530884</v>
+        <v>5.83283805847168</v>
       </c>
       <c r="H1691" t="n">
         <v>87279</v>
@@ -49466,7 +49466,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G1693" t="n">
-        <v>5.64903020858765</v>
+        <v>5.6490306854248</v>
       </c>
       <c r="H1693" t="n">
         <v>128938</v>
@@ -49495,7 +49495,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1694" t="n">
-        <v>5.5632529258728</v>
+        <v>5.56325340270996</v>
       </c>
       <c r="H1694" t="n">
         <v>107929</v>
@@ -49553,7 +49553,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.55508422851562</v>
+        <v>5.55508470535278</v>
       </c>
       <c r="H1696" t="n">
         <v>59601</v>
@@ -49640,7 +49640,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.92605304718018</v>
+        <v>4.92605257034302</v>
       </c>
       <c r="H1699" t="n">
         <v>182048</v>
@@ -49727,7 +49727,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1702" t="n">
-        <v>4.94239091873169</v>
+        <v>4.94239139556885</v>
       </c>
       <c r="H1702" t="n">
         <v>176681</v>
@@ -49756,7 +49756,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1703" t="n">
-        <v>5.07309913635254</v>
+        <v>5.07309865951538</v>
       </c>
       <c r="H1703" t="n">
         <v>144689</v>
@@ -49785,7 +49785,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G1704" t="n">
-        <v>5.3631067276001</v>
+        <v>5.36310720443726</v>
       </c>
       <c r="H1704" t="n">
         <v>147354</v>
@@ -49930,7 +49930,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1709" t="n">
-        <v>4.89337539672852</v>
+        <v>4.89337491989136</v>
       </c>
       <c r="H1709" t="n">
         <v>266573</v>
@@ -49959,7 +49959,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.9464750289917</v>
+        <v>4.94647550582886</v>
       </c>
       <c r="H1710" t="n">
         <v>146350</v>
@@ -50046,7 +50046,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.90562963485718</v>
+        <v>4.90562915802002</v>
       </c>
       <c r="H1713" t="n">
         <v>152880</v>
@@ -50104,7 +50104,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G1715" t="n">
-        <v>4.90562963485718</v>
+        <v>4.90562915802002</v>
       </c>
       <c r="H1715" t="n">
         <v>117935</v>
@@ -50162,7 +50162,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G1717" t="n">
-        <v>4.90562963485718</v>
+        <v>4.90562915802002</v>
       </c>
       <c r="H1717" t="n">
         <v>88039</v>
@@ -50249,7 +50249,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.26099109649658</v>
+        <v>5.26099157333374</v>
       </c>
       <c r="H1720" t="n">
         <v>112619</v>
@@ -50278,7 +50278,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.13845300674438</v>
+        <v>5.13845252990723</v>
       </c>
       <c r="H1721" t="n">
         <v>68792</v>
@@ -50336,7 +50336,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G1723" t="n">
-        <v>4.84844493865967</v>
+        <v>4.84844446182251</v>
       </c>
       <c r="H1723" t="n">
         <v>174837</v>
@@ -50423,7 +50423,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1726" t="n">
-        <v>4.65646696090698</v>
+        <v>4.65646743774414</v>
       </c>
       <c r="H1726" t="n">
         <v>78099</v>
@@ -50568,7 +50568,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>5.1670446395874</v>
+        <v>5.16704511642456</v>
       </c>
       <c r="H1731" t="n">
         <v>105386</v>
@@ -50597,7 +50597,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.24873733520508</v>
+        <v>5.24873781204224</v>
       </c>
       <c r="H1732" t="n">
         <v>116489</v>
@@ -50684,7 +50684,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1735" t="n">
-        <v>5.55508422851562</v>
+        <v>5.55508470535278</v>
       </c>
       <c r="H1735" t="n">
         <v>117678</v>
@@ -50742,7 +50742,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.64086151123047</v>
+        <v>5.64086103439331</v>
       </c>
       <c r="H1737" t="n">
         <v>172699</v>
@@ -50829,7 +50829,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1740" t="n">
-        <v>5.48972988128662</v>
+        <v>5.48973035812378</v>
       </c>
       <c r="H1740" t="n">
         <v>57839</v>
@@ -50887,7 +50887,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G1742" t="n">
-        <v>5.48156118392944</v>
+        <v>5.48156070709229</v>
       </c>
       <c r="H1742" t="n">
         <v>96331</v>
@@ -50945,7 +50945,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1744" t="n">
-        <v>5.80833053588867</v>
+        <v>5.80833101272583</v>
       </c>
       <c r="H1744" t="n">
         <v>154890</v>
@@ -50974,7 +50974,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>5.84917640686035</v>
+        <v>5.84917688369751</v>
       </c>
       <c r="H1745" t="n">
         <v>101722</v>
@@ -51032,7 +51032,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1747" t="n">
-        <v>5.89819240570068</v>
+        <v>5.89819192886353</v>
       </c>
       <c r="H1747" t="n">
         <v>325146</v>
@@ -51061,7 +51061,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1748" t="n">
-        <v>6.38017702102661</v>
+        <v>6.38017749786377</v>
       </c>
       <c r="H1748" t="n">
         <v>334175</v>
@@ -51264,7 +51264,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G1755" t="n">
-        <v>5.81241512298584</v>
+        <v>5.81241464614868</v>
       </c>
       <c r="H1755" t="n">
         <v>110488</v>
@@ -51322,7 +51322,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1757" t="n">
-        <v>5.80833053588867</v>
+        <v>5.80833101272583</v>
       </c>
       <c r="H1757" t="n">
         <v>83589</v>
@@ -51351,7 +51351,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.84509229660034</v>
+        <v>5.84509181976318</v>
       </c>
       <c r="H1758" t="n">
         <v>74988</v>
@@ -51380,7 +51380,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1759" t="n">
-        <v>5.68579196929932</v>
+        <v>5.68579149246216</v>
       </c>
       <c r="H1759" t="n">
         <v>109787</v>
@@ -51409,7 +51409,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G1760" t="n">
-        <v>5.73889255523682</v>
+        <v>5.73889207839966</v>
       </c>
       <c r="H1760" t="n">
         <v>102736</v>
@@ -51496,7 +51496,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1763" t="n">
-        <v>5.77565336227417</v>
+        <v>5.77565383911133</v>
       </c>
       <c r="H1763" t="n">
         <v>115632</v>
@@ -51554,7 +51554,7 @@
         <v>6.875</v>
       </c>
       <c r="G1765" t="n">
-        <v>5.61635303497314</v>
+        <v>5.6163535118103</v>
       </c>
       <c r="H1765" t="n">
         <v>108718</v>
@@ -51670,7 +51670,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1769" t="n">
-        <v>5.50606822967529</v>
+        <v>5.50606870651245</v>
       </c>
       <c r="H1769" t="n">
         <v>130870</v>
@@ -51728,7 +51728,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1771" t="n">
-        <v>5.5632529258728</v>
+        <v>5.56325340270996</v>
       </c>
       <c r="H1771" t="n">
         <v>139949</v>
@@ -51757,7 +51757,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1772" t="n">
-        <v>5.35085344314575</v>
+        <v>5.35085296630859</v>
       </c>
       <c r="H1772" t="n">
         <v>158653</v>
@@ -51844,7 +51844,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1775" t="n">
-        <v>5.35085344314575</v>
+        <v>5.35085296630859</v>
       </c>
       <c r="H1775" t="n">
         <v>67478</v>
@@ -51873,7 +51873,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1776" t="n">
-        <v>5.48972988128662</v>
+        <v>5.48973035812378</v>
       </c>
       <c r="H1776" t="n">
         <v>54048</v>
@@ -51931,7 +51931,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1778" t="n">
-        <v>5.50606822967529</v>
+        <v>5.50606870651245</v>
       </c>
       <c r="H1778" t="n">
         <v>95547</v>
@@ -52192,7 +52192,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1787" t="n">
-        <v>5.69396066665649</v>
+        <v>5.69396114349365</v>
       </c>
       <c r="H1787" t="n">
         <v>44249</v>
@@ -52395,7 +52395,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G1794" t="n">
-        <v>6.04932355880737</v>
+        <v>6.04932308197021</v>
       </c>
       <c r="H1794" t="n">
         <v>127231</v>
@@ -52424,7 +52424,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1795" t="n">
-        <v>6.09016942977905</v>
+        <v>6.09016895294189</v>
       </c>
       <c r="H1795" t="n">
         <v>89385</v>
@@ -52482,7 +52482,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>5.95537710189819</v>
+        <v>5.95537662506104</v>
       </c>
       <c r="H1797" t="n">
         <v>75583</v>
@@ -52511,7 +52511,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1798" t="n">
-        <v>6.07791519165039</v>
+        <v>6.07791566848755</v>
       </c>
       <c r="H1798" t="n">
         <v>105220</v>
@@ -52540,7 +52540,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1799" t="n">
-        <v>6.06157684326172</v>
+        <v>6.06157732009888</v>
       </c>
       <c r="H1799" t="n">
         <v>41416</v>
@@ -52598,7 +52598,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G1801" t="n">
-        <v>5.96763038635254</v>
+        <v>5.9676308631897</v>
       </c>
       <c r="H1801" t="n">
         <v>53469</v>
@@ -52627,7 +52627,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1802" t="n">
-        <v>5.95537710189819</v>
+        <v>5.95537662506104</v>
       </c>
       <c r="H1802" t="n">
         <v>89583</v>
@@ -52656,7 +52656,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G1803" t="n">
-        <v>5.94312334060669</v>
+        <v>5.94312286376953</v>
       </c>
       <c r="H1803" t="n">
         <v>71533</v>
@@ -52772,7 +52772,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1807" t="n">
-        <v>6.08199977874756</v>
+        <v>6.08200025558472</v>
       </c>
       <c r="H1807" t="n">
         <v>234464</v>
@@ -52917,7 +52917,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1812" t="n">
-        <v>6.00847673416138</v>
+        <v>6.00847721099854</v>
       </c>
       <c r="H1812" t="n">
         <v>149562</v>
@@ -52946,7 +52946,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G1813" t="n">
-        <v>6.03298473358154</v>
+        <v>6.0329852104187</v>
       </c>
       <c r="H1813" t="n">
         <v>86799</v>
@@ -52975,7 +52975,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G1814" t="n">
-        <v>6.03298473358154</v>
+        <v>6.0329852104187</v>
       </c>
       <c r="H1814" t="n">
         <v>67458</v>
@@ -53033,7 +53033,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G1816" t="n">
-        <v>6.11467742919922</v>
+        <v>6.11467695236206</v>
       </c>
       <c r="H1816" t="n">
         <v>114444</v>
@@ -53062,7 +53062,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>6.04523897171021</v>
+        <v>6.04523849487305</v>
       </c>
       <c r="H1817" t="n">
         <v>74184</v>
@@ -53207,7 +53207,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1822" t="n">
-        <v>5.48972988128662</v>
+        <v>5.48973035812378</v>
       </c>
       <c r="H1822" t="n">
         <v>200149</v>
@@ -53294,7 +53294,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1825" t="n">
-        <v>5.9145302772522</v>
+        <v>5.91453075408936</v>
       </c>
       <c r="H1825" t="n">
         <v>167154</v>
@@ -53323,7 +53323,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G1826" t="n">
-        <v>5.89002323150635</v>
+        <v>5.89002275466919</v>
       </c>
       <c r="H1826" t="n">
         <v>102785</v>
@@ -53352,7 +53352,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1827" t="n">
-        <v>5.97171545028687</v>
+        <v>5.97171497344971</v>
       </c>
       <c r="H1827" t="n">
         <v>140010</v>
@@ -53410,7 +53410,7 @@
         <v>7.25</v>
       </c>
       <c r="G1829" t="n">
-        <v>5.92269945144653</v>
+        <v>5.92269992828369</v>
       </c>
       <c r="H1829" t="n">
         <v>217078</v>
@@ -53468,7 +53468,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1831" t="n">
-        <v>6.38017702102661</v>
+        <v>6.38017749786377</v>
       </c>
       <c r="H1831" t="n">
         <v>429221</v>
@@ -53497,7 +53497,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1832" t="n">
-        <v>6.18411588668823</v>
+        <v>6.18411540985107</v>
       </c>
       <c r="H1832" t="n">
         <v>238977</v>
@@ -53584,7 +53584,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1835" t="n">
-        <v>6.23313093185425</v>
+        <v>6.23313140869141</v>
       </c>
       <c r="H1835" t="n">
         <v>416454</v>
@@ -53613,7 +53613,7 @@
         <v>8.25</v>
       </c>
       <c r="G1836" t="n">
-        <v>6.73962354660034</v>
+        <v>6.7396240234375</v>
       </c>
       <c r="H1836" t="n">
         <v>594012</v>
@@ -53816,7 +53816,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.1235785484314</v>
+        <v>7.12357807159424</v>
       </c>
       <c r="H1843" t="n">
         <v>171034</v>
@@ -53845,7 +53845,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.20118522644043</v>
+        <v>7.20118570327759</v>
       </c>
       <c r="H1844" t="n">
         <v>235336</v>
@@ -53874,7 +53874,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.30330085754395</v>
+        <v>7.30330181121826</v>
       </c>
       <c r="H1845" t="n">
         <v>214240</v>
@@ -53903,7 +53903,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G1846" t="n">
-        <v>7.48710966110229</v>
+        <v>7.48710918426514</v>
       </c>
       <c r="H1846" t="n">
         <v>258969</v>
@@ -53932,7 +53932,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.5320405960083</v>
+        <v>7.53204107284546</v>
       </c>
       <c r="H1847" t="n">
         <v>344043</v>
@@ -53961,7 +53961,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1848" t="n">
-        <v>7.54837894439697</v>
+        <v>7.54837846755981</v>
       </c>
       <c r="H1848" t="n">
         <v>207237</v>
@@ -53990,7 +53990,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.43401050567627</v>
+        <v>7.43400955200195</v>
       </c>
       <c r="H1849" t="n">
         <v>193478</v>
@@ -54077,7 +54077,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1852" t="n">
-        <v>7.22977924346924</v>
+        <v>7.22977876663208</v>
       </c>
       <c r="H1852" t="n">
         <v>244351</v>
@@ -54106,7 +54106,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1853" t="n">
-        <v>7.25428676605225</v>
+        <v>7.25428581237793</v>
       </c>
       <c r="H1853" t="n">
         <v>219709</v>
@@ -54164,7 +54164,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1855" t="n">
-        <v>7.22160911560059</v>
+        <v>7.22160959243774</v>
       </c>
       <c r="H1855" t="n">
         <v>243336</v>
@@ -54193,7 +54193,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1856" t="n">
-        <v>7.22160911560059</v>
+        <v>7.22160959243774</v>
       </c>
       <c r="H1856" t="n">
         <v>114739</v>
@@ -54222,7 +54222,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G1857" t="n">
-        <v>7.20118522644043</v>
+        <v>7.20118570327759</v>
       </c>
       <c r="H1857" t="n">
         <v>144426</v>
@@ -54251,7 +54251,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1858" t="n">
-        <v>7.10723972320557</v>
+        <v>7.10723924636841</v>
       </c>
       <c r="H1858" t="n">
         <v>191555</v>
@@ -79951,6 +79951,64 @@
         <v>103618</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>8.02999973297119</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>8.02999973297119</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>8.02999973297119</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>78516</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>7.92500019073486</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>8.01000022888184</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>7.55000019073486</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>7.8899998664856</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>7.8899998664856</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>224166</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4473237991333</v>
+        <v>5.44732332229614</v>
       </c>
       <c r="H2" t="n">
         <v>113188</v>
@@ -456,7 +456,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G3" t="n">
-        <v>5.55361270904541</v>
+        <v>5.55361318588257</v>
       </c>
       <c r="H3" t="n">
         <v>66887</v>
@@ -514,7 +514,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G5" t="n">
-        <v>5.32774925231934</v>
+        <v>5.32774877548218</v>
       </c>
       <c r="H5" t="n">
         <v>104860</v>
@@ -543,7 +543,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G6" t="n">
-        <v>5.35099935531616</v>
+        <v>5.350998878479</v>
       </c>
       <c r="H6" t="n">
         <v>87575</v>
@@ -572,7 +572,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G7" t="n">
-        <v>5.21481657028198</v>
+        <v>5.21481609344482</v>
       </c>
       <c r="H7" t="n">
         <v>108677</v>
@@ -601,7 +601,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>5.29453325271606</v>
+        <v>5.29453277587891</v>
       </c>
       <c r="H8" t="n">
         <v>216037</v>
@@ -630,7 +630,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>5.33106994628906</v>
+        <v>5.3310694694519</v>
       </c>
       <c r="H9" t="n">
         <v>49371</v>
@@ -688,7 +688,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>4.94245052337646</v>
+        <v>4.94244956970215</v>
       </c>
       <c r="H11" t="n">
         <v>159704</v>
@@ -746,7 +746,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>4.84612560272217</v>
+        <v>4.84612512588501</v>
       </c>
       <c r="H13" t="n">
         <v>91026</v>
@@ -775,7 +775,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>4.58372402191162</v>
+        <v>4.58372354507446</v>
       </c>
       <c r="H14" t="n">
         <v>143281</v>
@@ -833,7 +833,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>4.82951784133911</v>
+        <v>4.82951736450195</v>
       </c>
       <c r="H16" t="n">
         <v>117197</v>
@@ -862,7 +862,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>4.82951784133911</v>
+        <v>4.82951736450195</v>
       </c>
       <c r="H17" t="n">
         <v>66239</v>
@@ -891,7 +891,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>4.88598299026489</v>
+        <v>4.88598394393921</v>
       </c>
       <c r="H18" t="n">
         <v>66869</v>
@@ -949,7 +949,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>4.91587781906128</v>
+        <v>4.91587829589844</v>
       </c>
       <c r="H20" t="n">
         <v>109639</v>
@@ -1007,7 +1007,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>4.97234392166138</v>
+        <v>4.97234439849854</v>
       </c>
       <c r="H22" t="n">
         <v>54344</v>
@@ -1036,7 +1036,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>4.88598299026489</v>
+        <v>4.88598394393921</v>
       </c>
       <c r="H23" t="n">
         <v>81429</v>
@@ -1094,7 +1094,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>4.93248558044434</v>
+        <v>4.93248510360718</v>
       </c>
       <c r="H25" t="n">
         <v>117119</v>
@@ -1123,7 +1123,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G26" t="n">
-        <v>4.97898721694946</v>
+        <v>4.97898626327515</v>
       </c>
       <c r="H26" t="n">
         <v>142513</v>
@@ -1152,7 +1152,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.59368801116943</v>
+        <v>4.59368848800659</v>
       </c>
       <c r="H27" t="n">
         <v>190986</v>
@@ -1181,7 +1181,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>4.4575047492981</v>
+        <v>4.45750522613525</v>
       </c>
       <c r="H28" t="n">
         <v>305032</v>
@@ -1210,7 +1210,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>4.61029577255249</v>
+        <v>4.61029624938965</v>
       </c>
       <c r="H29" t="n">
         <v>245073</v>
@@ -1239,7 +1239,7 @@
         <v>6.75</v>
       </c>
       <c r="G30" t="n">
-        <v>4.48407745361328</v>
+        <v>4.48407793045044</v>
       </c>
       <c r="H30" t="n">
         <v>162247</v>
@@ -1268,7 +1268,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>4.62690353393555</v>
+        <v>4.62690305709839</v>
       </c>
       <c r="H31" t="n">
         <v>118549</v>
@@ -1297,7 +1297,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>4.70662069320679</v>
+        <v>4.70662021636963</v>
       </c>
       <c r="H32" t="n">
         <v>54106</v>
@@ -1355,7 +1355,7 @@
         <v>7.375</v>
       </c>
       <c r="G34" t="n">
-        <v>4.89927005767822</v>
+        <v>4.89926958084106</v>
       </c>
       <c r="H34" t="n">
         <v>59630</v>
@@ -1384,7 +1384,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G35" t="n">
-        <v>5.19488763809204</v>
+        <v>5.19488668441772</v>
       </c>
       <c r="H35" t="n">
         <v>145821</v>
@@ -1442,7 +1442,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>5.21481657028198</v>
+        <v>5.21481609344482</v>
       </c>
       <c r="H37" t="n">
         <v>79314</v>
@@ -1587,7 +1587,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>5.51375436782837</v>
+        <v>5.51375484466553</v>
       </c>
       <c r="H42" t="n">
         <v>150009</v>
@@ -1616,7 +1616,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G43" t="n">
-        <v>5.69311714172363</v>
+        <v>5.69311761856079</v>
       </c>
       <c r="H43" t="n">
         <v>209250</v>
@@ -1645,7 +1645,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>5.75290489196777</v>
+        <v>5.75290536880493</v>
       </c>
       <c r="H44" t="n">
         <v>122191</v>
@@ -1674,7 +1674,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>5.53368377685547</v>
+        <v>5.53368425369263</v>
       </c>
       <c r="H45" t="n">
         <v>125352</v>
@@ -1761,7 +1761,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>5.72633266448975</v>
+        <v>5.72633218765259</v>
       </c>
       <c r="H48" t="n">
         <v>97982</v>
@@ -1790,7 +1790,7 @@
         <v>8.5</v>
       </c>
       <c r="G49" t="n">
-        <v>5.64661550521851</v>
+        <v>5.64661645889282</v>
       </c>
       <c r="H49" t="n">
         <v>71691</v>
@@ -1819,7 +1819,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>5.35432100296021</v>
+        <v>5.35432147979736</v>
       </c>
       <c r="H50" t="n">
         <v>105600</v>
@@ -1877,7 +1877,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G52" t="n">
-        <v>5.50379085540771</v>
+        <v>5.5037899017334</v>
       </c>
       <c r="H52" t="n">
         <v>91415</v>
@@ -1935,7 +1935,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>5.4473237991333</v>
+        <v>5.44732332229614</v>
       </c>
       <c r="H54" t="n">
         <v>43227</v>
@@ -1964,7 +1964,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>5.39417886734009</v>
+        <v>5.39417934417725</v>
       </c>
       <c r="H55" t="n">
         <v>67532</v>
@@ -1993,7 +1993,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.4473237991333</v>
+        <v>5.44732332229614</v>
       </c>
       <c r="H56" t="n">
         <v>148456</v>
@@ -2022,7 +2022,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G57" t="n">
-        <v>5.38421440124512</v>
+        <v>5.38421392440796</v>
       </c>
       <c r="H57" t="n">
         <v>103959</v>
@@ -2051,7 +2051,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>5.41410827636719</v>
+        <v>5.41410875320435</v>
       </c>
       <c r="H58" t="n">
         <v>147032</v>
@@ -2109,7 +2109,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>5.18160057067871</v>
+        <v>5.18160104751587</v>
       </c>
       <c r="H60" t="n">
         <v>128542</v>
@@ -2138,7 +2138,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>5.14174270629883</v>
+        <v>5.14174175262451</v>
       </c>
       <c r="H61" t="n">
         <v>103759</v>
@@ -2196,7 +2196,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>5.27460336685181</v>
+        <v>5.27460384368896</v>
       </c>
       <c r="H63" t="n">
         <v>44868</v>
@@ -2254,7 +2254,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.26796102523804</v>
+        <v>5.26796054840088</v>
       </c>
       <c r="H65" t="n">
         <v>87527</v>
@@ -2283,7 +2283,7 @@
         <v>7.5</v>
       </c>
       <c r="G66" t="n">
-        <v>4.98230791091919</v>
+        <v>4.98230886459351</v>
       </c>
       <c r="H66" t="n">
         <v>59642</v>
@@ -2370,7 +2370,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>5.07531118392944</v>
+        <v>5.0753116607666</v>
       </c>
       <c r="H69" t="n">
         <v>43182</v>
@@ -2457,7 +2457,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>5.27460336685181</v>
+        <v>5.27460384368896</v>
       </c>
       <c r="H72" t="n">
         <v>51680</v>
@@ -2515,7 +2515,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G74" t="n">
-        <v>5.04209613800049</v>
+        <v>5.04209661483765</v>
       </c>
       <c r="H74" t="n">
         <v>83664</v>
@@ -2631,7 +2631,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.11517000198364</v>
+        <v>5.11516952514648</v>
       </c>
       <c r="H78" t="n">
         <v>43914</v>
@@ -2660,7 +2660,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>5.06202554702759</v>
+        <v>5.06202507019043</v>
       </c>
       <c r="H79" t="n">
         <v>31701</v>
@@ -2689,7 +2689,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G80" t="n">
-        <v>4.98895168304443</v>
+        <v>4.98895072937012</v>
       </c>
       <c r="H80" t="n">
         <v>25738</v>
@@ -2805,7 +2805,7 @@
         <v>7.625</v>
       </c>
       <c r="G84" t="n">
-        <v>5.06534719467163</v>
+        <v>5.06534671783447</v>
       </c>
       <c r="H84" t="n">
         <v>33760</v>
@@ -2834,7 +2834,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>5.1118483543396</v>
+        <v>5.11184930801392</v>
       </c>
       <c r="H85" t="n">
         <v>15689</v>
@@ -2863,7 +2863,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>5.06202554702759</v>
+        <v>5.06202507019043</v>
       </c>
       <c r="H86" t="n">
         <v>36585</v>
@@ -2950,7 +2950,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G89" t="n">
-        <v>5.33439111709595</v>
+        <v>5.33439159393311</v>
       </c>
       <c r="H89" t="n">
         <v>158293</v>
@@ -3008,7 +3008,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G91" t="n">
-        <v>5.53747701644897</v>
+        <v>5.53747749328613</v>
       </c>
       <c r="H91" t="n">
         <v>119812</v>
@@ -3066,7 +3066,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G93" t="n">
-        <v>5.42916584014893</v>
+        <v>5.42916488647461</v>
       </c>
       <c r="H93" t="n">
         <v>60550</v>
@@ -3095,7 +3095,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>5.52393817901611</v>
+        <v>5.52393770217896</v>
       </c>
       <c r="H94" t="n">
         <v>43648</v>
@@ -3124,7 +3124,7 @@
         <v>7.5</v>
       </c>
       <c r="G95" t="n">
-        <v>5.07714891433716</v>
+        <v>5.07714986801147</v>
       </c>
       <c r="H95" t="n">
         <v>313230</v>
@@ -3153,7 +3153,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>4.66759252548218</v>
+        <v>4.66759300231934</v>
       </c>
       <c r="H96" t="n">
         <v>383206</v>
@@ -3211,7 +3211,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>4.58297348022461</v>
+        <v>4.58297395706177</v>
       </c>
       <c r="H98" t="n">
         <v>256051</v>
@@ -3298,7 +3298,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>4.47804546356201</v>
+        <v>4.47804594039917</v>
       </c>
       <c r="H101" t="n">
         <v>121440</v>
@@ -3327,7 +3327,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G102" t="n">
-        <v>4.42727422714233</v>
+        <v>4.42727375030518</v>
       </c>
       <c r="H102" t="n">
         <v>149214</v>
@@ -3356,7 +3356,7 @@
         <v>6.5</v>
       </c>
       <c r="G103" t="n">
-        <v>4.40019702911377</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H103" t="n">
         <v>103547</v>
@@ -3385,7 +3385,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G104" t="n">
-        <v>4.30542278289795</v>
+        <v>4.30542230606079</v>
       </c>
       <c r="H104" t="n">
         <v>179465</v>
@@ -3414,7 +3414,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.44758224487305</v>
+        <v>4.44758319854736</v>
       </c>
       <c r="H105" t="n">
         <v>157820</v>
@@ -3559,7 +3559,7 @@
         <v>6.25</v>
       </c>
       <c r="G110" t="n">
-        <v>4.23095798492432</v>
+        <v>4.23095750808716</v>
       </c>
       <c r="H110" t="n">
         <v>156920</v>
@@ -3617,7 +3617,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G112" t="n">
-        <v>4.15649271011353</v>
+        <v>4.15649223327637</v>
       </c>
       <c r="H112" t="n">
         <v>139833</v>
@@ -3704,7 +3704,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.02448749542236</v>
+        <v>4.02448701858521</v>
       </c>
       <c r="H115" t="n">
         <v>158085</v>
@@ -3791,7 +3791,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G118" t="n">
-        <v>3.7977077960968</v>
+        <v>3.79770731925964</v>
       </c>
       <c r="H118" t="n">
         <v>144969</v>
@@ -3849,7 +3849,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.93648314476013</v>
+        <v>3.93648362159729</v>
       </c>
       <c r="H120" t="n">
         <v>167668</v>
@@ -3878,7 +3878,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.96356129646301</v>
+        <v>3.96356081962585</v>
       </c>
       <c r="H121" t="n">
         <v>108290</v>
@@ -3907,7 +3907,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94663715362549</v>
+        <v>3.94663763046265</v>
       </c>
       <c r="H122" t="n">
         <v>66243</v>
@@ -3936,7 +3936,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>3.99402403831482</v>
+        <v>3.9940242767334</v>
       </c>
       <c r="H123" t="n">
         <v>85572</v>
@@ -3965,7 +3965,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>3.76385974884033</v>
+        <v>3.76386022567749</v>
       </c>
       <c r="H124" t="n">
         <v>198048</v>
@@ -4023,7 +4023,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.4016900062561</v>
+        <v>3.40169048309326</v>
       </c>
       <c r="H126" t="n">
         <v>297033</v>
@@ -4052,7 +4052,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>3.47615480422974</v>
+        <v>3.47615528106689</v>
       </c>
       <c r="H127" t="n">
         <v>184937</v>
@@ -4081,7 +4081,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G128" t="n">
-        <v>3.48969435691833</v>
+        <v>3.48969459533691</v>
       </c>
       <c r="H128" t="n">
         <v>107107</v>
@@ -4110,7 +4110,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G129" t="n">
-        <v>3.48969435691833</v>
+        <v>3.48969459533691</v>
       </c>
       <c r="H129" t="n">
         <v>134491</v>
@@ -4139,7 +4139,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>3.45246171951294</v>
+        <v>3.45246195793152</v>
       </c>
       <c r="H130" t="n">
         <v>186985</v>
@@ -4168,7 +4168,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>3.39830541610718</v>
+        <v>3.3983051776886</v>
       </c>
       <c r="H131" t="n">
         <v>57807</v>
@@ -4197,7 +4197,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>3.15730977058411</v>
+        <v>3.15731000900269</v>
       </c>
       <c r="H132" t="n">
         <v>707649</v>
@@ -4255,7 +4255,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G134" t="n">
-        <v>3.29540824890137</v>
+        <v>3.29540848731995</v>
       </c>
       <c r="H134" t="n">
         <v>189271</v>
@@ -4342,7 +4342,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G137" t="n">
-        <v>3.47615480422974</v>
+        <v>3.47615528106689</v>
       </c>
       <c r="H137" t="n">
         <v>87648</v>
@@ -4371,7 +4371,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49984884262085</v>
+        <v>3.49984860420227</v>
       </c>
       <c r="H138" t="n">
         <v>69291</v>
@@ -4400,7 +4400,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.48630976676941</v>
+        <v>3.48630881309509</v>
       </c>
       <c r="H139" t="n">
         <v>109570</v>
@@ -4429,7 +4429,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57092809677124</v>
+        <v>3.5709285736084</v>
       </c>
       <c r="H140" t="n">
         <v>95057</v>
@@ -4458,7 +4458,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G141" t="n">
-        <v>3.51677179336548</v>
+        <v>3.51677227020264</v>
       </c>
       <c r="H141" t="n">
         <v>72737</v>
@@ -4487,7 +4487,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G142" t="n">
-        <v>3.57431316375732</v>
+        <v>3.57431364059448</v>
       </c>
       <c r="H142" t="n">
         <v>38892</v>
@@ -4516,7 +4516,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>3.60477590560913</v>
+        <v>3.60477542877197</v>
       </c>
       <c r="H143" t="n">
         <v>103724</v>
@@ -4545,7 +4545,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G144" t="n">
-        <v>3.59462189674377</v>
+        <v>3.59462118148804</v>
       </c>
       <c r="H144" t="n">
         <v>67888</v>
@@ -4574,7 +4574,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G145" t="n">
-        <v>3.63185358047485</v>
+        <v>3.63185405731201</v>
       </c>
       <c r="H145" t="n">
         <v>19997</v>
@@ -4603,7 +4603,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.61154556274414</v>
+        <v>3.61154532432556</v>
       </c>
       <c r="H146" t="n">
         <v>52589</v>
@@ -4632,7 +4632,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.79093790054321</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H147" t="n">
         <v>91695</v>
@@ -4661,7 +4661,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>3.70293402671814</v>
+        <v>3.70293426513672</v>
       </c>
       <c r="H148" t="n">
         <v>67162</v>
@@ -4748,7 +4748,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>3.52015686035156</v>
+        <v>3.52015662193298</v>
       </c>
       <c r="H151" t="n">
         <v>107282</v>
@@ -4835,7 +4835,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.67924118041992</v>
+        <v>3.67924094200134</v>
       </c>
       <c r="H154" t="n">
         <v>20938</v>
@@ -4893,7 +4893,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>3.79093790054321</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H156" t="n">
         <v>57929</v>
@@ -4922,7 +4922,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>3.79093790054321</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H157" t="n">
         <v>34686</v>
@@ -4951,7 +4951,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>3.8383252620697</v>
+        <v>3.83832430839539</v>
       </c>
       <c r="H158" t="n">
         <v>13489</v>
@@ -4980,7 +4980,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G159" t="n">
-        <v>3.8214008808136</v>
+        <v>3.82140135765076</v>
       </c>
       <c r="H159" t="n">
         <v>39413</v>
@@ -5038,7 +5038,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G161" t="n">
-        <v>3.78416848182678</v>
+        <v>3.78416895866394</v>
       </c>
       <c r="H161" t="n">
         <v>67079</v>
@@ -5212,7 +5212,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>3.95340728759766</v>
+        <v>3.9534068107605</v>
       </c>
       <c r="H167" t="n">
         <v>79391</v>
@@ -5299,7 +5299,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G170" t="n">
-        <v>4.02448749542236</v>
+        <v>4.02448701858521</v>
       </c>
       <c r="H170" t="n">
         <v>39849</v>
@@ -5328,7 +5328,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>3.99402403831482</v>
+        <v>3.9940242767334</v>
       </c>
       <c r="H171" t="n">
         <v>44191</v>
@@ -5357,7 +5357,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G172" t="n">
-        <v>4.02787160873413</v>
+        <v>4.02787208557129</v>
       </c>
       <c r="H172" t="n">
         <v>87862</v>
@@ -5386,7 +5386,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>4.0583348274231</v>
+        <v>4.05833435058594</v>
       </c>
       <c r="H173" t="n">
         <v>31122</v>
@@ -5415,7 +5415,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>3.96356129646301</v>
+        <v>3.96356081962585</v>
       </c>
       <c r="H174" t="n">
         <v>171483</v>
@@ -5502,7 +5502,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>4.0583348274231</v>
+        <v>4.05833435058594</v>
       </c>
       <c r="H177" t="n">
         <v>34907</v>
@@ -5589,7 +5589,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.02787160873413</v>
+        <v>4.02787208557129</v>
       </c>
       <c r="H180" t="n">
         <v>95736</v>
@@ -5647,7 +5647,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G182" t="n">
-        <v>3.8890962600708</v>
+        <v>3.88909673690796</v>
       </c>
       <c r="H182" t="n">
         <v>145297</v>
@@ -5705,7 +5705,7 @@
         <v>5</v>
       </c>
       <c r="G184" t="n">
-        <v>3.38476610183716</v>
+        <v>3.38476634025574</v>
       </c>
       <c r="H184" t="n">
         <v>271176</v>
@@ -5763,7 +5763,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>3.26020693778992</v>
+        <v>3.26020669937134</v>
       </c>
       <c r="H186" t="n">
         <v>102093</v>
@@ -5792,7 +5792,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G187" t="n">
-        <v>3.28322339057922</v>
+        <v>3.28322315216064</v>
       </c>
       <c r="H187" t="n">
         <v>138480</v>
@@ -5821,7 +5821,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G188" t="n">
-        <v>3.33061027526855</v>
+        <v>3.33061051368713</v>
       </c>
       <c r="H188" t="n">
         <v>74303</v>
@@ -5879,7 +5879,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>3.30353188514709</v>
+        <v>3.30353236198425</v>
       </c>
       <c r="H190" t="n">
         <v>156871</v>
@@ -5908,7 +5908,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G191" t="n">
-        <v>3.34279537200928</v>
+        <v>3.3427951335907</v>
       </c>
       <c r="H191" t="n">
         <v>52063</v>
@@ -5937,7 +5937,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G192" t="n">
-        <v>3.3712272644043</v>
+        <v>3.37122678756714</v>
       </c>
       <c r="H192" t="n">
         <v>58791</v>
@@ -5995,7 +5995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>3.49984884262085</v>
+        <v>3.49984860420227</v>
       </c>
       <c r="H194" t="n">
         <v>152264</v>
@@ -6024,7 +6024,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G195" t="n">
-        <v>3.46261596679688</v>
+        <v>3.46261644363403</v>
       </c>
       <c r="H195" t="n">
         <v>36886</v>
@@ -6198,7 +6198,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G201" t="n">
-        <v>4.18357038497925</v>
+        <v>4.18357133865356</v>
       </c>
       <c r="H201" t="n">
         <v>191685</v>
@@ -6227,7 +6227,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>4.25803565979004</v>
+        <v>4.2580361366272</v>
       </c>
       <c r="H202" t="n">
         <v>293216</v>
@@ -6343,7 +6343,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>4.46789121627808</v>
+        <v>4.46789073944092</v>
       </c>
       <c r="H206" t="n">
         <v>146224</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>4.46789121627808</v>
+        <v>4.46789073944092</v>
       </c>
       <c r="H210" t="n">
         <v>109334</v>
@@ -6517,7 +6517,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>4.58297348022461</v>
+        <v>4.58297395706177</v>
       </c>
       <c r="H212" t="n">
         <v>170279</v>
@@ -6546,7 +6546,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G213" t="n">
-        <v>4.58974361419678</v>
+        <v>4.58974313735962</v>
       </c>
       <c r="H213" t="n">
         <v>124219</v>
@@ -6575,7 +6575,7 @@
         <v>6.75</v>
       </c>
       <c r="G214" t="n">
-        <v>4.56943416595459</v>
+        <v>4.56943464279175</v>
       </c>
       <c r="H214" t="n">
         <v>80845</v>
@@ -6604,7 +6604,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G215" t="n">
-        <v>4.56266498565674</v>
+        <v>4.56266450881958</v>
       </c>
       <c r="H215" t="n">
         <v>38526</v>
@@ -6633,7 +6633,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G216" t="n">
-        <v>4.36634826660156</v>
+        <v>4.36634874343872</v>
       </c>
       <c r="H216" t="n">
         <v>167961</v>
@@ -6662,7 +6662,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G217" t="n">
-        <v>4.37988758087158</v>
+        <v>4.37988805770874</v>
       </c>
       <c r="H217" t="n">
         <v>113733</v>
@@ -6720,7 +6720,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>4.38665676116943</v>
+        <v>4.38665771484375</v>
       </c>
       <c r="H219" t="n">
         <v>126233</v>
@@ -6778,7 +6778,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G221" t="n">
-        <v>4.40696620941162</v>
+        <v>4.4069652557373</v>
       </c>
       <c r="H221" t="n">
         <v>176630</v>
@@ -6807,7 +6807,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G222" t="n">
-        <v>4.36296367645264</v>
+        <v>4.36296415328979</v>
       </c>
       <c r="H222" t="n">
         <v>78414</v>
@@ -6836,7 +6836,7 @@
         <v>6.5</v>
       </c>
       <c r="G223" t="n">
-        <v>4.40019702911377</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H223" t="n">
         <v>131651</v>
@@ -6865,7 +6865,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="n">
-        <v>4.40019702911377</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H224" t="n">
         <v>103731</v>
@@ -6923,7 +6923,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.36634826660156</v>
+        <v>4.36634874343872</v>
       </c>
       <c r="H226" t="n">
         <v>60666</v>
@@ -7010,7 +7010,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>4.35957956314087</v>
+        <v>4.35957860946655</v>
       </c>
       <c r="H229" t="n">
         <v>200260</v>
@@ -7097,7 +7097,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G232" t="n">
-        <v>4.47804546356201</v>
+        <v>4.47804594039917</v>
       </c>
       <c r="H232" t="n">
         <v>54961</v>
@@ -7184,7 +7184,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G235" t="n">
-        <v>4.35280895233154</v>
+        <v>4.3528094291687</v>
       </c>
       <c r="H235" t="n">
         <v>100278</v>
@@ -7213,7 +7213,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G236" t="n">
-        <v>4.36634826660156</v>
+        <v>4.36634874343872</v>
       </c>
       <c r="H236" t="n">
         <v>68882</v>
@@ -7271,7 +7271,7 @@
         <v>6.375</v>
       </c>
       <c r="G238" t="n">
-        <v>4.31557703018188</v>
+        <v>4.31557655334473</v>
       </c>
       <c r="H238" t="n">
         <v>102989</v>
@@ -7300,7 +7300,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G239" t="n">
-        <v>4.41712045669556</v>
+        <v>4.4171199798584</v>
       </c>
       <c r="H239" t="n">
         <v>105717</v>
@@ -7329,7 +7329,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G240" t="n">
-        <v>4.46789121627808</v>
+        <v>4.46789073944092</v>
       </c>
       <c r="H240" t="n">
         <v>61992</v>
@@ -7358,7 +7358,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>4.4983549118042</v>
+        <v>4.49835443496704</v>
       </c>
       <c r="H241" t="n">
         <v>371749</v>
@@ -7387,7 +7387,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G242" t="n">
-        <v>4.56266498565674</v>
+        <v>4.56266450881958</v>
       </c>
       <c r="H242" t="n">
         <v>108996</v>
@@ -7416,7 +7416,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>4.46789121627808</v>
+        <v>4.46789073944092</v>
       </c>
       <c r="H243" t="n">
         <v>65647</v>
@@ -7445,7 +7445,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.48820018768311</v>
+        <v>4.48820066452026</v>
       </c>
       <c r="H244" t="n">
         <v>56395</v>
@@ -7532,7 +7532,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.51866292953491</v>
+        <v>4.51866340637207</v>
       </c>
       <c r="H247" t="n">
         <v>77287</v>
@@ -7590,7 +7590,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G249" t="n">
-        <v>4.54912567138672</v>
+        <v>4.54912519454956</v>
       </c>
       <c r="H249" t="n">
         <v>62594</v>
@@ -7677,7 +7677,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G252" t="n">
-        <v>4.71836423873901</v>
+        <v>4.71836376190186</v>
       </c>
       <c r="H252" t="n">
         <v>148227</v>
@@ -7764,7 +7764,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G255" t="n">
-        <v>4.71836423873901</v>
+        <v>4.71836376190186</v>
       </c>
       <c r="H255" t="n">
         <v>44487</v>
@@ -7793,7 +7793,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G256" t="n">
-        <v>4.72174835205078</v>
+        <v>4.7217493057251</v>
       </c>
       <c r="H256" t="n">
         <v>77207</v>
@@ -7938,7 +7938,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G261" t="n">
-        <v>4.72174835205078</v>
+        <v>4.7217493057251</v>
       </c>
       <c r="H261" t="n">
         <v>118863</v>
@@ -7967,7 +7967,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G262" t="n">
-        <v>4.76236581802368</v>
+        <v>4.76236629486084</v>
       </c>
       <c r="H262" t="n">
         <v>139601</v>
@@ -8025,7 +8025,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.78944396972656</v>
+        <v>4.7894434928894</v>
       </c>
       <c r="H264" t="n">
         <v>71071</v>
@@ -8083,7 +8083,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78944396972656</v>
+        <v>4.7894434928894</v>
       </c>
       <c r="H266" t="n">
         <v>52227</v>
@@ -8112,7 +8112,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>4.8402156829834</v>
+        <v>4.84021615982056</v>
       </c>
       <c r="H267" t="n">
         <v>41796</v>
@@ -8170,7 +8170,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>4.83683109283447</v>
+        <v>4.83683013916016</v>
       </c>
       <c r="H269" t="n">
         <v>40098</v>
@@ -8228,7 +8228,7 @@
         <v>7.125</v>
       </c>
       <c r="G271" t="n">
-        <v>4.82329177856445</v>
+        <v>4.82329130172729</v>
       </c>
       <c r="H271" t="n">
         <v>22605</v>
@@ -8257,7 +8257,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>4.8402156829834</v>
+        <v>4.84021615982056</v>
       </c>
       <c r="H272" t="n">
         <v>25459</v>
@@ -8286,7 +8286,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G273" t="n">
-        <v>4.72851896286011</v>
+        <v>4.72851800918579</v>
       </c>
       <c r="H273" t="n">
         <v>28889</v>
@@ -8344,7 +8344,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G275" t="n">
-        <v>4.82667636871338</v>
+        <v>4.82667684555054</v>
       </c>
       <c r="H275" t="n">
         <v>57170</v>
@@ -8431,7 +8431,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65066814422607</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H278" t="n">
         <v>80211</v>
@@ -8518,7 +8518,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G281" t="n">
-        <v>4.69805526733398</v>
+        <v>4.69805574417114</v>
       </c>
       <c r="H281" t="n">
         <v>48954</v>
@@ -8547,7 +8547,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>4.67097759246826</v>
+        <v>4.6709771156311</v>
       </c>
       <c r="H282" t="n">
         <v>64682</v>
@@ -8576,7 +8576,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>4.65066814422607</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H283" t="n">
         <v>39226</v>
@@ -8605,7 +8605,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>4.65066814422607</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H284" t="n">
         <v>31328</v>
@@ -8634,7 +8634,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G285" t="n">
-        <v>4.59989738464355</v>
+        <v>4.59989786148071</v>
       </c>
       <c r="H285" t="n">
         <v>152076</v>
@@ -8663,7 +8663,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G286" t="n">
-        <v>4.67097759246826</v>
+        <v>4.6709771156311</v>
       </c>
       <c r="H286" t="n">
         <v>52151</v>
@@ -8837,7 +8837,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>5.02299308776855</v>
+        <v>5.0229926109314</v>
       </c>
       <c r="H292" t="n">
         <v>56483</v>
@@ -8895,7 +8895,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G294" t="n">
-        <v>5.00268411636353</v>
+        <v>5.00268459320068</v>
       </c>
       <c r="H294" t="n">
         <v>22069</v>
@@ -8953,7 +8953,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G296" t="n">
-        <v>4.9756064414978</v>
+        <v>4.97560691833496</v>
       </c>
       <c r="H296" t="n">
         <v>73571</v>
@@ -9011,7 +9011,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>4.9756064414978</v>
+        <v>4.97560691833496</v>
       </c>
       <c r="H298" t="n">
         <v>67261</v>
@@ -9069,7 +9069,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G300" t="n">
-        <v>5.05684089660645</v>
+        <v>5.05684041976929</v>
       </c>
       <c r="H300" t="n">
         <v>83204</v>
@@ -9185,7 +9185,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.02637815475464</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H304" t="n">
         <v>31519</v>
@@ -9214,7 +9214,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>5.02299308776855</v>
+        <v>5.0229926109314</v>
       </c>
       <c r="H305" t="n">
         <v>157822</v>
@@ -9243,7 +9243,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G306" t="n">
-        <v>5.08391904830933</v>
+        <v>5.08391857147217</v>
       </c>
       <c r="H306" t="n">
         <v>115407</v>
@@ -9301,7 +9301,7 @@
         <v>7.5</v>
       </c>
       <c r="G308" t="n">
-        <v>5.07714891433716</v>
+        <v>5.07714986801147</v>
       </c>
       <c r="H308" t="n">
         <v>29858</v>
@@ -9330,7 +9330,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G309" t="n">
-        <v>5.00268411636353</v>
+        <v>5.00268459320068</v>
       </c>
       <c r="H309" t="n">
         <v>46538</v>
@@ -9388,7 +9388,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>5.27346563339233</v>
+        <v>5.27346611022949</v>
       </c>
       <c r="H311" t="n">
         <v>171397</v>
@@ -9475,7 +9475,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>5.29039001464844</v>
+        <v>5.29038953781128</v>
       </c>
       <c r="H314" t="n">
         <v>288254</v>
@@ -9504,7 +9504,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G315" t="n">
-        <v>5.23284864425659</v>
+        <v>5.23284816741943</v>
       </c>
       <c r="H315" t="n">
         <v>195604</v>
@@ -9533,7 +9533,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G316" t="n">
-        <v>5.37500858306885</v>
+        <v>5.37500905990601</v>
       </c>
       <c r="H316" t="n">
         <v>352796</v>
@@ -9620,7 +9620,7 @@
         <v>8</v>
       </c>
       <c r="G319" t="n">
-        <v>5.41562604904175</v>
+        <v>5.41562557220459</v>
       </c>
       <c r="H319" t="n">
         <v>179752</v>
@@ -9649,7 +9649,7 @@
         <v>7.875</v>
       </c>
       <c r="G320" t="n">
-        <v>5.33100748062134</v>
+        <v>5.33100652694702</v>
       </c>
       <c r="H320" t="n">
         <v>67075</v>
@@ -9765,7 +9765,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>5.21254014968872</v>
+        <v>5.21253967285156</v>
       </c>
       <c r="H324" t="n">
         <v>117109</v>
@@ -9823,7 +9823,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>5.2159252166748</v>
+        <v>5.21592473983765</v>
       </c>
       <c r="H326" t="n">
         <v>62283</v>
@@ -9910,7 +9910,7 @@
         <v>7.56500005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>5.12115144729614</v>
+        <v>5.12115097045898</v>
       </c>
       <c r="H329" t="n">
         <v>147045</v>
@@ -9939,7 +9939,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>5.13807535171509</v>
+        <v>5.13807582855225</v>
       </c>
       <c r="H330" t="n">
         <v>161802</v>
@@ -9968,7 +9968,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.94852876663208</v>
+        <v>4.94852781295776</v>
       </c>
       <c r="H331" t="n">
         <v>123182</v>
@@ -9997,7 +9997,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.83344602584839</v>
+        <v>4.83344650268555</v>
       </c>
       <c r="H332" t="n">
         <v>100510</v>
@@ -10026,7 +10026,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>4.97899055480957</v>
+        <v>4.97899103164673</v>
       </c>
       <c r="H333" t="n">
         <v>75688</v>
@@ -10113,7 +10113,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>5.13807535171509</v>
+        <v>5.13807582855225</v>
       </c>
       <c r="H336" t="n">
         <v>74359</v>
@@ -10142,7 +10142,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G337" t="n">
-        <v>5.17192268371582</v>
+        <v>5.17192316055298</v>
       </c>
       <c r="H337" t="n">
         <v>58203</v>
@@ -10171,7 +10171,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>5.11099767684937</v>
+        <v>5.11099720001221</v>
       </c>
       <c r="H338" t="n">
         <v>143535</v>
@@ -10200,7 +10200,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.09745836257935</v>
+        <v>5.09745788574219</v>
       </c>
       <c r="H339" t="n">
         <v>96823</v>
@@ -10229,7 +10229,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G340" t="n">
-        <v>5.08391904830933</v>
+        <v>5.08391857147217</v>
       </c>
       <c r="H340" t="n">
         <v>75184</v>
@@ -10258,7 +10258,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G341" t="n">
-        <v>5.09745836257935</v>
+        <v>5.09745788574219</v>
       </c>
       <c r="H341" t="n">
         <v>39402</v>
@@ -10287,7 +10287,7 @@
         <v>7.5</v>
       </c>
       <c r="G342" t="n">
-        <v>5.07714891433716</v>
+        <v>5.07714986801147</v>
       </c>
       <c r="H342" t="n">
         <v>56561</v>
@@ -10316,7 +10316,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>5.13807535171509</v>
+        <v>5.13807582855225</v>
       </c>
       <c r="H343" t="n">
         <v>63057</v>
@@ -10374,7 +10374,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.23200035095215</v>
+        <v>5.23200130462646</v>
       </c>
       <c r="H345" t="n">
         <v>74072</v>
@@ -10403,7 +10403,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G346" t="n">
-        <v>5.3905463218689</v>
+        <v>5.39054679870605</v>
       </c>
       <c r="H346" t="n">
         <v>202741</v>
@@ -10548,7 +10548,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>4.71500492095947</v>
+        <v>4.71500444412231</v>
       </c>
       <c r="H351" t="n">
         <v>350968</v>
@@ -10664,7 +10664,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>4.68053865432739</v>
+        <v>4.68053817749023</v>
       </c>
       <c r="H355" t="n">
         <v>64537</v>
@@ -10838,7 +10838,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G361" t="n">
-        <v>4.43237924575806</v>
+        <v>4.43238019943237</v>
       </c>
       <c r="H361" t="n">
         <v>127010</v>
@@ -10896,7 +10896,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>4.41170024871826</v>
+        <v>4.41170072555542</v>
       </c>
       <c r="H363" t="n">
         <v>196216</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>4.2600474357605</v>
+        <v>4.26004838943481</v>
       </c>
       <c r="H367" t="n">
         <v>48450</v>
@@ -11070,7 +11070,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>4.30485439300537</v>
+        <v>4.30485391616821</v>
       </c>
       <c r="H369" t="n">
         <v>176874</v>
@@ -11186,7 +11186,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G373" t="n">
-        <v>4.27728080749512</v>
+        <v>4.27728128433228</v>
       </c>
       <c r="H373" t="n">
         <v>87931</v>
@@ -11273,7 +11273,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G376" t="n">
-        <v>4.17732906341553</v>
+        <v>4.17732858657837</v>
       </c>
       <c r="H376" t="n">
         <v>76134</v>
@@ -11302,7 +11302,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G377" t="n">
-        <v>4.27038764953613</v>
+        <v>4.27038812637329</v>
       </c>
       <c r="H377" t="n">
         <v>79360</v>
@@ -11331,7 +11331,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>4.23592185974121</v>
+        <v>4.23592138290405</v>
       </c>
       <c r="H378" t="n">
         <v>77420</v>
@@ -11418,7 +11418,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G381" t="n">
-        <v>4.30485439300537</v>
+        <v>4.30485391616821</v>
       </c>
       <c r="H381" t="n">
         <v>127973</v>
@@ -11447,7 +11447,7 @@
         <v>6.125</v>
       </c>
       <c r="G382" t="n">
-        <v>4.22213459014893</v>
+        <v>4.22213506698608</v>
       </c>
       <c r="H382" t="n">
         <v>89002</v>
@@ -11505,7 +11505,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.35655450820923</v>
+        <v>4.35655403137207</v>
       </c>
       <c r="H384" t="n">
         <v>289251</v>
@@ -11534,7 +11534,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>4.51510000228882</v>
+        <v>4.51509952545166</v>
       </c>
       <c r="H385" t="n">
         <v>184215</v>
@@ -11679,7 +11679,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>4.49442005157471</v>
+        <v>4.49441957473755</v>
       </c>
       <c r="H390" t="n">
         <v>149419</v>
@@ -11708,7 +11708,7 @@
         <v>6.625</v>
       </c>
       <c r="G391" t="n">
-        <v>4.5667986869812</v>
+        <v>4.56679964065552</v>
       </c>
       <c r="H391" t="n">
         <v>195950</v>
@@ -11824,7 +11824,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>4.52888584136963</v>
+        <v>4.52888679504395</v>
       </c>
       <c r="H395" t="n">
         <v>77827</v>
@@ -11969,7 +11969,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>4.58403301239014</v>
+        <v>4.58403253555298</v>
       </c>
       <c r="H400" t="n">
         <v>49686</v>
@@ -12056,7 +12056,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>4.53577995300293</v>
+        <v>4.53577899932861</v>
       </c>
       <c r="H403" t="n">
         <v>44497</v>
@@ -12085,7 +12085,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>4.42548751831055</v>
+        <v>4.42548656463623</v>
       </c>
       <c r="H404" t="n">
         <v>58646</v>
@@ -12143,7 +12143,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>4.50475931167603</v>
+        <v>4.50475978851318</v>
       </c>
       <c r="H406" t="n">
         <v>51611</v>
@@ -12201,7 +12201,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G408" t="n">
-        <v>4.45995283126831</v>
+        <v>4.45995330810547</v>
       </c>
       <c r="H408" t="n">
         <v>41217</v>
@@ -12230,7 +12230,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G409" t="n">
-        <v>4.48408031463623</v>
+        <v>4.48407983779907</v>
       </c>
       <c r="H409" t="n">
         <v>27222</v>
@@ -12259,7 +12259,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G410" t="n">
-        <v>4.54956579208374</v>
+        <v>4.54956531524658</v>
       </c>
       <c r="H410" t="n">
         <v>114764</v>
@@ -12288,7 +12288,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>4.58403301239014</v>
+        <v>4.58403253555298</v>
       </c>
       <c r="H411" t="n">
         <v>48654</v>
@@ -12317,7 +12317,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>4.48408031463623</v>
+        <v>4.48407983779907</v>
       </c>
       <c r="H412" t="n">
         <v>30738</v>
@@ -12346,7 +12346,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.46340036392212</v>
+        <v>4.46339988708496</v>
       </c>
       <c r="H413" t="n">
         <v>62096</v>
@@ -12462,7 +12462,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>4.42548751831055</v>
+        <v>4.42548656463623</v>
       </c>
       <c r="H417" t="n">
         <v>91936</v>
@@ -12491,7 +12491,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G418" t="n">
-        <v>4.35655450820923</v>
+        <v>4.35655403137207</v>
       </c>
       <c r="H418" t="n">
         <v>90612</v>
@@ -12520,7 +12520,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G419" t="n">
-        <v>4.34276723861694</v>
+        <v>4.3427677154541</v>
       </c>
       <c r="H419" t="n">
         <v>265016</v>
@@ -12665,7 +12665,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G424" t="n">
-        <v>4.27728080749512</v>
+        <v>4.27728128433228</v>
       </c>
       <c r="H424" t="n">
         <v>29617</v>
@@ -12694,7 +12694,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>4.20490217208862</v>
+        <v>4.20490169525146</v>
       </c>
       <c r="H425" t="n">
         <v>58755</v>
@@ -12781,7 +12781,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G428" t="n">
-        <v>4.27038764953613</v>
+        <v>4.27038812637329</v>
       </c>
       <c r="H428" t="n">
         <v>35523</v>
@@ -12810,7 +12810,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G429" t="n">
-        <v>4.24626207351685</v>
+        <v>4.24626159667969</v>
       </c>
       <c r="H429" t="n">
         <v>38370</v>
@@ -12839,7 +12839,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>4.20490217208862</v>
+        <v>4.20490169525146</v>
       </c>
       <c r="H430" t="n">
         <v>45169</v>
@@ -12897,7 +12897,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G432" t="n">
-        <v>4.30140781402588</v>
+        <v>4.30140733718872</v>
       </c>
       <c r="H432" t="n">
         <v>53302</v>
@@ -12984,7 +12984,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>4.28072786331177</v>
+        <v>4.28072834014893</v>
       </c>
       <c r="H435" t="n">
         <v>67345</v>
@@ -13013,7 +13013,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G436" t="n">
-        <v>4.23247480392456</v>
+        <v>4.2324743270874</v>
       </c>
       <c r="H436" t="n">
         <v>100278</v>
@@ -13042,7 +13042,7 @@
         <v>6.125</v>
       </c>
       <c r="G437" t="n">
-        <v>4.22213459014893</v>
+        <v>4.22213506698608</v>
       </c>
       <c r="H437" t="n">
         <v>111044</v>
@@ -13071,7 +13071,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>4.17732906341553</v>
+        <v>4.17732858657837</v>
       </c>
       <c r="H438" t="n">
         <v>145459</v>
@@ -13100,7 +13100,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>3.52936029434204</v>
+        <v>3.52936005592346</v>
       </c>
       <c r="H439" t="n">
         <v>1797627</v>
@@ -13274,7 +13274,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G445" t="n">
-        <v>3.44526219367981</v>
+        <v>3.44526195526123</v>
       </c>
       <c r="H445" t="n">
         <v>243913</v>
@@ -13303,7 +13303,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G446" t="n">
-        <v>3.42458248138428</v>
+        <v>3.42458271980286</v>
       </c>
       <c r="H446" t="n">
         <v>285105</v>
@@ -13361,7 +13361,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G448" t="n">
-        <v>3.43699026107788</v>
+        <v>3.43699049949646</v>
       </c>
       <c r="H448" t="n">
         <v>109773</v>
@@ -13419,7 +13419,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G450" t="n">
-        <v>3.3804657459259</v>
+        <v>3.38046550750732</v>
       </c>
       <c r="H450" t="n">
         <v>226892</v>
@@ -13448,7 +13448,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G451" t="n">
-        <v>3.3280770778656</v>
+        <v>3.32807660102844</v>
       </c>
       <c r="H451" t="n">
         <v>313343</v>
@@ -13738,7 +13738,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G461" t="n">
-        <v>2.95446062088013</v>
+        <v>2.95446014404297</v>
       </c>
       <c r="H461" t="n">
         <v>328173</v>
@@ -13767,7 +13767,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G462" t="n">
-        <v>2.86898398399353</v>
+        <v>2.86898374557495</v>
       </c>
       <c r="H462" t="n">
         <v>600471</v>
@@ -13796,7 +13796,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G463" t="n">
-        <v>2.84830355644226</v>
+        <v>2.84830379486084</v>
       </c>
       <c r="H463" t="n">
         <v>341520</v>
@@ -13883,7 +13883,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G466" t="n">
-        <v>2.98479104042053</v>
+        <v>2.98479080200195</v>
       </c>
       <c r="H466" t="n">
         <v>406773</v>
@@ -13999,7 +13999,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G470" t="n">
-        <v>2.83727502822876</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H470" t="n">
         <v>239632</v>
@@ -14028,7 +14028,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G471" t="n">
-        <v>2.86898398399353</v>
+        <v>2.86898374557495</v>
       </c>
       <c r="H471" t="n">
         <v>254832</v>
@@ -14057,7 +14057,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G472" t="n">
-        <v>3.04545187950134</v>
+        <v>3.04545164108276</v>
       </c>
       <c r="H472" t="n">
         <v>1192003</v>
@@ -14086,7 +14086,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>2.97789764404297</v>
+        <v>2.97789788246155</v>
       </c>
       <c r="H473" t="n">
         <v>366433</v>
@@ -14115,7 +14115,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G474" t="n">
-        <v>3.07026743888855</v>
+        <v>3.07026767730713</v>
       </c>
       <c r="H474" t="n">
         <v>582857</v>
@@ -14173,7 +14173,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>2.94343161582947</v>
+        <v>2.94343137741089</v>
       </c>
       <c r="H476" t="n">
         <v>398406</v>
@@ -14231,7 +14231,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>2.82624530792236</v>
+        <v>2.82624506950378</v>
       </c>
       <c r="H478" t="n">
         <v>369252</v>
@@ -14434,7 +14434,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G485" t="n">
-        <v>2.85795474052429</v>
+        <v>2.85795426368713</v>
       </c>
       <c r="H485" t="n">
         <v>234792</v>
@@ -14463,7 +14463,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G486" t="n">
-        <v>2.76420640945435</v>
+        <v>2.76420593261719</v>
       </c>
       <c r="H486" t="n">
         <v>342490</v>
@@ -14492,7 +14492,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G487" t="n">
-        <v>2.79591536521912</v>
+        <v>2.79591512680054</v>
       </c>
       <c r="H487" t="n">
         <v>168936</v>
@@ -14521,7 +14521,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G488" t="n">
-        <v>2.80005097389221</v>
+        <v>2.80005121231079</v>
       </c>
       <c r="H488" t="n">
         <v>264775</v>
@@ -14550,7 +14550,7 @@
         <v>4</v>
       </c>
       <c r="G489" t="n">
-        <v>2.75731253623962</v>
+        <v>2.75731229782104</v>
       </c>
       <c r="H489" t="n">
         <v>356617</v>
@@ -14579,7 +14579,7 @@
         <v>4</v>
       </c>
       <c r="G490" t="n">
-        <v>2.75731253623962</v>
+        <v>2.75731229782104</v>
       </c>
       <c r="H490" t="n">
         <v>337390</v>
@@ -14608,7 +14608,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G491" t="n">
-        <v>2.83727502822876</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H491" t="n">
         <v>684752</v>
@@ -14637,7 +14637,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G492" t="n">
-        <v>2.78764343261719</v>
+        <v>2.78764319419861</v>
       </c>
       <c r="H492" t="n">
         <v>1174545</v>
@@ -14666,7 +14666,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>2.88139176368713</v>
+        <v>2.88139152526855</v>
       </c>
       <c r="H493" t="n">
         <v>495399</v>
@@ -14724,7 +14724,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>2.94756722450256</v>
+        <v>2.94756746292114</v>
       </c>
       <c r="H495" t="n">
         <v>203717</v>
@@ -14753,7 +14753,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G496" t="n">
-        <v>2.88690662384033</v>
+        <v>2.88690638542175</v>
       </c>
       <c r="H496" t="n">
         <v>205236</v>
@@ -14869,7 +14869,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93240261077881</v>
+        <v>2.93240189552307</v>
       </c>
       <c r="H500" t="n">
         <v>107995</v>
@@ -14956,7 +14956,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G503" t="n">
-        <v>2.79591536521912</v>
+        <v>2.79591512680054</v>
       </c>
       <c r="H503" t="n">
         <v>234420</v>
@@ -15043,7 +15043,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>2.82624530792236</v>
+        <v>2.82624506950378</v>
       </c>
       <c r="H506" t="n">
         <v>127666</v>
@@ -15101,7 +15101,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G508" t="n">
-        <v>2.80005097389221</v>
+        <v>2.80005121231079</v>
       </c>
       <c r="H508" t="n">
         <v>47300</v>
@@ -15159,7 +15159,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G510" t="n">
-        <v>2.88690662384033</v>
+        <v>2.88690638542175</v>
       </c>
       <c r="H510" t="n">
         <v>93443</v>
@@ -15188,7 +15188,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G511" t="n">
-        <v>2.83727502822876</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H511" t="n">
         <v>100855</v>
@@ -15217,7 +15217,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>2.90207147598267</v>
+        <v>2.90207171440125</v>
       </c>
       <c r="H512" t="n">
         <v>89744</v>
@@ -15246,7 +15246,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>2.93998432159424</v>
+        <v>2.93998456001282</v>
       </c>
       <c r="H513" t="n">
         <v>127430</v>
@@ -15333,7 +15333,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G516" t="n">
-        <v>3.22605586051941</v>
+        <v>3.22605538368225</v>
       </c>
       <c r="H516" t="n">
         <v>664170</v>
@@ -15391,7 +15391,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>3.11921000480652</v>
+        <v>3.11920976638794</v>
       </c>
       <c r="H518" t="n">
         <v>467928</v>
@@ -15449,7 +15449,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>3.05717015266418</v>
+        <v>3.05717039108276</v>
       </c>
       <c r="H520" t="n">
         <v>210541</v>
@@ -15478,7 +15478,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G521" t="n">
-        <v>3.17780327796936</v>
+        <v>3.1778028011322</v>
       </c>
       <c r="H521" t="n">
         <v>462498</v>
@@ -15507,7 +15507,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G522" t="n">
-        <v>3.16746258735657</v>
+        <v>3.16746282577515</v>
       </c>
       <c r="H522" t="n">
         <v>493955</v>
@@ -15536,7 +15536,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.13299655914307</v>
+        <v>3.13299632072449</v>
       </c>
       <c r="H523" t="n">
         <v>379353</v>
@@ -15594,7 +15594,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>3.08819055557251</v>
+        <v>3.08819031715393</v>
       </c>
       <c r="H525" t="n">
         <v>388946</v>
@@ -15652,7 +15652,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G527" t="n">
-        <v>3.14678287506104</v>
+        <v>3.14678311347961</v>
       </c>
       <c r="H527" t="n">
         <v>306906</v>
@@ -15681,7 +15681,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>3.09508299827576</v>
+        <v>3.09508347511292</v>
       </c>
       <c r="H528" t="n">
         <v>253894</v>
@@ -15710,7 +15710,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G529" t="n">
-        <v>3.09508299827576</v>
+        <v>3.09508347511292</v>
       </c>
       <c r="H529" t="n">
         <v>186227</v>
@@ -15739,7 +15739,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G530" t="n">
-        <v>3.1950364112854</v>
+        <v>3.19503664970398</v>
       </c>
       <c r="H530" t="n">
         <v>364125</v>
@@ -15797,7 +15797,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G532" t="n">
-        <v>3.05027723312378</v>
+        <v>3.05027747154236</v>
       </c>
       <c r="H532" t="n">
         <v>444837</v>
@@ -15826,7 +15826,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>3.04683017730713</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H533" t="n">
         <v>319024</v>
@@ -15855,7 +15855,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>3.02959728240967</v>
+        <v>3.02959752082825</v>
       </c>
       <c r="H534" t="n">
         <v>317377</v>
@@ -15884,7 +15884,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>3.03304386138916</v>
+        <v>3.03304362297058</v>
       </c>
       <c r="H535" t="n">
         <v>491731</v>
@@ -15913,7 +15913,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>2.98479104042053</v>
+        <v>2.98479080200195</v>
       </c>
       <c r="H536" t="n">
         <v>519676</v>
@@ -15942,7 +15942,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H537" t="n">
         <v>1557885</v>
@@ -16000,7 +16000,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>2.81245899200439</v>
+        <v>2.81245851516724</v>
       </c>
       <c r="H539" t="n">
         <v>482372</v>
@@ -16029,7 +16029,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.78488564491272</v>
+        <v>2.7848858833313</v>
       </c>
       <c r="H540" t="n">
         <v>280515</v>
@@ -16116,7 +16116,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>3.04683017730713</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H543" t="n">
         <v>812045</v>
@@ -16203,7 +16203,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>3.08819055557251</v>
+        <v>3.08819031715393</v>
       </c>
       <c r="H546" t="n">
         <v>146187</v>
@@ -16232,7 +16232,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06406402587891</v>
+        <v>3.06406354904175</v>
       </c>
       <c r="H547" t="n">
         <v>404236</v>
@@ -16261,7 +16261,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>3.04338431358337</v>
+        <v>3.04338383674622</v>
       </c>
       <c r="H548" t="n">
         <v>383699</v>
@@ -16290,7 +16290,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G549" t="n">
-        <v>3.02615094184875</v>
+        <v>3.02615070343018</v>
       </c>
       <c r="H549" t="n">
         <v>326890</v>
@@ -16348,7 +16348,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G551" t="n">
-        <v>3.01236391067505</v>
+        <v>3.01236414909363</v>
       </c>
       <c r="H551" t="n">
         <v>293142</v>
@@ -16406,7 +16406,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G553" t="n">
-        <v>3.00547122955322</v>
+        <v>3.00547099113464</v>
       </c>
       <c r="H553" t="n">
         <v>251650</v>
@@ -16464,7 +16464,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>2.90551853179932</v>
+        <v>2.90551829338074</v>
       </c>
       <c r="H555" t="n">
         <v>393098</v>
@@ -16493,7 +16493,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.90207147598267</v>
+        <v>2.90207171440125</v>
       </c>
       <c r="H556" t="n">
         <v>262821</v>
@@ -16609,7 +16609,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G560" t="n">
-        <v>2.92275142669678</v>
+        <v>2.9227511882782</v>
       </c>
       <c r="H560" t="n">
         <v>1429089</v>
@@ -16667,7 +16667,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G562" t="n">
-        <v>2.87794518470764</v>
+        <v>2.87794542312622</v>
       </c>
       <c r="H562" t="n">
         <v>486870</v>
@@ -16754,7 +16754,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H565" t="n">
         <v>871376</v>
@@ -16783,7 +16783,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>2.87794518470764</v>
+        <v>2.87794542312622</v>
       </c>
       <c r="H566" t="n">
         <v>234339</v>
@@ -16812,7 +16812,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H567" t="n">
         <v>188660</v>
@@ -16899,7 +16899,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G570" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H570" t="n">
         <v>233390</v>
@@ -16986,7 +16986,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>2.87449860572815</v>
+        <v>2.87449836730957</v>
       </c>
       <c r="H573" t="n">
         <v>91271</v>
@@ -17044,7 +17044,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>2.98134446144104</v>
+        <v>2.98134398460388</v>
       </c>
       <c r="H575" t="n">
         <v>190507</v>
@@ -17102,7 +17102,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>2.99168419837952</v>
+        <v>2.9916844367981</v>
       </c>
       <c r="H577" t="n">
         <v>238890</v>
@@ -17131,7 +17131,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G578" t="n">
-        <v>2.97789764404297</v>
+        <v>2.97789788246155</v>
       </c>
       <c r="H578" t="n">
         <v>86085</v>
@@ -17218,7 +17218,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G581" t="n">
-        <v>2.96411156654358</v>
+        <v>2.964111328125</v>
       </c>
       <c r="H581" t="n">
         <v>83737</v>
@@ -17247,7 +17247,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>2.97789764404297</v>
+        <v>2.97789788246155</v>
       </c>
       <c r="H582" t="n">
         <v>144591</v>
@@ -17305,7 +17305,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G584" t="n">
-        <v>2.98134446144104</v>
+        <v>2.98134398460388</v>
       </c>
       <c r="H584" t="n">
         <v>63477</v>
@@ -17334,7 +17334,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>2.98823761940002</v>
+        <v>2.9882378578186</v>
       </c>
       <c r="H585" t="n">
         <v>198148</v>
@@ -17363,7 +17363,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G586" t="n">
-        <v>2.99168419837952</v>
+        <v>2.9916844367981</v>
       </c>
       <c r="H586" t="n">
         <v>163016</v>
@@ -17421,7 +17421,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G588" t="n">
-        <v>3.03649044036865</v>
+        <v>3.03649091720581</v>
       </c>
       <c r="H588" t="n">
         <v>252004</v>
@@ -17450,7 +17450,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>3.04683017730713</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H589" t="n">
         <v>119110</v>
@@ -17508,7 +17508,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>3.07095670700073</v>
+        <v>3.07095646858215</v>
       </c>
       <c r="H591" t="n">
         <v>195836</v>
@@ -17682,7 +17682,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03304386138916</v>
+        <v>3.03304362297058</v>
       </c>
       <c r="H597" t="n">
         <v>163365</v>
@@ -17711,7 +17711,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>3.04683017730713</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H598" t="n">
         <v>158703</v>
@@ -17740,7 +17740,7 @@
         <v>4.375</v>
       </c>
       <c r="G599" t="n">
-        <v>3.01581072807312</v>
+        <v>3.0158109664917</v>
       </c>
       <c r="H599" t="n">
         <v>198096</v>
@@ -17769,7 +17769,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>3.03649044036865</v>
+        <v>3.03649091720581</v>
       </c>
       <c r="H600" t="n">
         <v>224765</v>
@@ -17798,7 +17798,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G601" t="n">
-        <v>3.01925706863403</v>
+        <v>3.01925730705261</v>
       </c>
       <c r="H601" t="n">
         <v>220818</v>
@@ -17856,7 +17856,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G603" t="n">
-        <v>3.09027028083801</v>
+        <v>3.09027004241943</v>
       </c>
       <c r="H603" t="n">
         <v>195385</v>
@@ -17885,7 +17885,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G604" t="n">
-        <v>2.99425482749939</v>
+        <v>2.99425506591797</v>
       </c>
       <c r="H604" t="n">
         <v>852809</v>
@@ -17914,7 +17914,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G605" t="n">
-        <v>2.9480254650116</v>
+        <v>2.94802522659302</v>
       </c>
       <c r="H605" t="n">
         <v>276475</v>
@@ -17943,7 +17943,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>2.98714256286621</v>
+        <v>2.98714280128479</v>
       </c>
       <c r="H606" t="n">
         <v>223287</v>
@@ -17972,7 +17972,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>2.95513772964478</v>
+        <v>2.95513796806335</v>
       </c>
       <c r="H607" t="n">
         <v>101236</v>
@@ -18001,7 +18001,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>2.94091367721558</v>
+        <v>2.94091320037842</v>
       </c>
       <c r="H608" t="n">
         <v>161778</v>
@@ -18059,7 +18059,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.91957664489746</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H610" t="n">
         <v>241159</v>
@@ -18088,7 +18088,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.87690281867981</v>
+        <v>2.87690305709839</v>
       </c>
       <c r="H611" t="n">
         <v>124383</v>
@@ -18233,7 +18233,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>2.65286731719971</v>
+        <v>2.65286707878113</v>
       </c>
       <c r="H616" t="n">
         <v>243214</v>
@@ -18262,7 +18262,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G617" t="n">
-        <v>2.69198441505432</v>
+        <v>2.69198489189148</v>
       </c>
       <c r="H617" t="n">
         <v>341053</v>
@@ -18291,7 +18291,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G618" t="n">
-        <v>2.65286731719971</v>
+        <v>2.65286707878113</v>
       </c>
       <c r="H618" t="n">
         <v>259078</v>
@@ -18320,7 +18320,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G619" t="n">
-        <v>2.57107663154602</v>
+        <v>2.57107639312744</v>
       </c>
       <c r="H619" t="n">
         <v>188588</v>
@@ -18349,7 +18349,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.58530116081238</v>
+        <v>2.58530068397522</v>
       </c>
       <c r="H620" t="n">
         <v>177506</v>
@@ -18378,7 +18378,7 @@
         <v>3.625</v>
       </c>
       <c r="G621" t="n">
-        <v>2.57818865776062</v>
+        <v>2.57818841934204</v>
       </c>
       <c r="H621" t="n">
         <v>419710</v>
@@ -18436,7 +18436,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.58530116081238</v>
+        <v>2.58530068397522</v>
       </c>
       <c r="H623" t="n">
         <v>152678</v>
@@ -18494,7 +18494,7 @@
         <v>3.75</v>
       </c>
       <c r="G625" t="n">
-        <v>2.66709160804749</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H625" t="n">
         <v>177538</v>
@@ -18610,7 +18610,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G629" t="n">
-        <v>2.69198441505432</v>
+        <v>2.69198489189148</v>
       </c>
       <c r="H629" t="n">
         <v>99972</v>
@@ -18639,7 +18639,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>2.69909691810608</v>
+        <v>2.69909715652466</v>
       </c>
       <c r="H630" t="n">
         <v>92589</v>
@@ -18726,7 +18726,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>2.49995446205139</v>
+        <v>2.49995422363281</v>
       </c>
       <c r="H633" t="n">
         <v>289300</v>
@@ -18784,7 +18784,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H635" t="n">
         <v>247960</v>
@@ -18813,7 +18813,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G636" t="n">
-        <v>2.56752014160156</v>
+        <v>2.56752038002014</v>
       </c>
       <c r="H636" t="n">
         <v>270034</v>
@@ -18900,7 +18900,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>2.69909691810608</v>
+        <v>2.69909715652466</v>
       </c>
       <c r="H639" t="n">
         <v>229295</v>
@@ -18929,7 +18929,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.71687769889832</v>
+        <v>2.71687746047974</v>
       </c>
       <c r="H640" t="n">
         <v>85746</v>
@@ -18958,7 +18958,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G641" t="n">
-        <v>2.74177050590515</v>
+        <v>2.74177026748657</v>
       </c>
       <c r="H641" t="n">
         <v>183565</v>
@@ -18987,7 +18987,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G642" t="n">
-        <v>2.79155611991882</v>
+        <v>2.79155588150024</v>
       </c>
       <c r="H642" t="n">
         <v>251313</v>
@@ -19016,7 +19016,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G643" t="n">
-        <v>2.86267852783203</v>
+        <v>2.86267876625061</v>
       </c>
       <c r="H643" t="n">
         <v>152428</v>
@@ -19045,7 +19045,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>2.91957664489746</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H644" t="n">
         <v>153060</v>
@@ -19074,7 +19074,7 @@
         <v>4</v>
       </c>
       <c r="G645" t="n">
-        <v>2.84489774703979</v>
+        <v>2.84489750862122</v>
       </c>
       <c r="H645" t="n">
         <v>243773</v>
@@ -19306,7 +19306,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G653" t="n">
-        <v>2.65642356872559</v>
+        <v>2.65642333030701</v>
       </c>
       <c r="H653" t="n">
         <v>170086</v>
@@ -19364,7 +19364,7 @@
         <v>3.75</v>
       </c>
       <c r="G655" t="n">
-        <v>2.66709160804749</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H655" t="n">
         <v>134163</v>
@@ -19393,7 +19393,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>2.65642356872559</v>
+        <v>2.65642333030701</v>
       </c>
       <c r="H656" t="n">
         <v>97009</v>
@@ -19480,7 +19480,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G659" t="n">
-        <v>2.75243854522705</v>
+        <v>2.75243830680847</v>
       </c>
       <c r="H659" t="n">
         <v>65346</v>
@@ -19509,7 +19509,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G660" t="n">
-        <v>2.70620894432068</v>
+        <v>2.70620918273926</v>
       </c>
       <c r="H660" t="n">
         <v>139089</v>
@@ -19625,7 +19625,7 @@
         <v>3.75</v>
       </c>
       <c r="G664" t="n">
-        <v>2.66709160804749</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H664" t="n">
         <v>56567</v>
@@ -19799,7 +19799,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G670" t="n">
-        <v>2.60663771629333</v>
+        <v>2.60663747787476</v>
       </c>
       <c r="H670" t="n">
         <v>58784</v>
@@ -19828,7 +19828,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>2.64575529098511</v>
+        <v>2.64575505256653</v>
       </c>
       <c r="H671" t="n">
         <v>57464</v>
@@ -19857,7 +19857,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>2.70976495742798</v>
+        <v>2.70976519584656</v>
       </c>
       <c r="H672" t="n">
         <v>74089</v>
@@ -19915,7 +19915,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>2.82711744308472</v>
+        <v>2.82711720466614</v>
       </c>
       <c r="H674" t="n">
         <v>96667</v>
@@ -19944,7 +19944,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G675" t="n">
-        <v>2.77377533912659</v>
+        <v>2.77377557754517</v>
       </c>
       <c r="H675" t="n">
         <v>118597</v>
@@ -19973,7 +19973,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>2.77377533912659</v>
+        <v>2.77377557754517</v>
       </c>
       <c r="H676" t="n">
         <v>49199</v>
@@ -20031,7 +20031,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>2.64931106567383</v>
+        <v>2.64931082725525</v>
       </c>
       <c r="H678" t="n">
         <v>409416</v>
@@ -20118,7 +20118,7 @@
         <v>3.625</v>
       </c>
       <c r="G681" t="n">
-        <v>2.57818865776062</v>
+        <v>2.57818841934204</v>
       </c>
       <c r="H681" t="n">
         <v>50503</v>
@@ -20147,7 +20147,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G682" t="n">
-        <v>2.69198441505432</v>
+        <v>2.69198489189148</v>
       </c>
       <c r="H682" t="n">
         <v>95363</v>
@@ -20176,7 +20176,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H683" t="n">
         <v>25234</v>
@@ -20205,7 +20205,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G684" t="n">
-        <v>2.64931106567383</v>
+        <v>2.64931082725525</v>
       </c>
       <c r="H684" t="n">
         <v>34184</v>
@@ -20234,7 +20234,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H685" t="n">
         <v>54057</v>
@@ -20292,7 +20292,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>2.68131613731384</v>
+        <v>2.68131589889526</v>
       </c>
       <c r="H687" t="n">
         <v>229731</v>
@@ -20350,7 +20350,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G689" t="n">
-        <v>2.60308122634888</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H689" t="n">
         <v>365229</v>
@@ -20379,7 +20379,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>2.54973959922791</v>
+        <v>2.54973983764648</v>
       </c>
       <c r="H690" t="n">
         <v>163363</v>
@@ -20408,7 +20408,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>2.60663771629333</v>
+        <v>2.60663747787476</v>
       </c>
       <c r="H691" t="n">
         <v>97872</v>
@@ -20437,7 +20437,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.65286731719971</v>
+        <v>2.65286707878113</v>
       </c>
       <c r="H692" t="n">
         <v>158013</v>
@@ -20466,7 +20466,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G693" t="n">
-        <v>2.72043347358704</v>
+        <v>2.72043371200562</v>
       </c>
       <c r="H693" t="n">
         <v>192286</v>
@@ -20582,7 +20582,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G697" t="n">
-        <v>2.74177050590515</v>
+        <v>2.74177026748657</v>
       </c>
       <c r="H697" t="n">
         <v>62942</v>
@@ -20698,7 +20698,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>2.70976495742798</v>
+        <v>2.70976519584656</v>
       </c>
       <c r="H701" t="n">
         <v>83109</v>
@@ -20785,7 +20785,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G704" t="n">
-        <v>2.78088760375977</v>
+        <v>2.78088784217834</v>
       </c>
       <c r="H704" t="n">
         <v>85479</v>
@@ -20843,7 +20843,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>2.69909691810608</v>
+        <v>2.69909715652466</v>
       </c>
       <c r="H706" t="n">
         <v>112009</v>
@@ -20901,7 +20901,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730647087097</v>
       </c>
       <c r="H708" t="n">
         <v>94175</v>
@@ -20930,7 +20930,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G709" t="n">
-        <v>2.55685186386108</v>
+        <v>2.55685210227966</v>
       </c>
       <c r="H709" t="n">
         <v>130291</v>
@@ -20988,7 +20988,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G711" t="n">
-        <v>2.57107663154602</v>
+        <v>2.57107639312744</v>
       </c>
       <c r="H711" t="n">
         <v>108439</v>
@@ -21133,7 +21133,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>2.54973959922791</v>
+        <v>2.54973983764648</v>
       </c>
       <c r="H716" t="n">
         <v>153913</v>
@@ -21220,7 +21220,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G719" t="n">
-        <v>2.56752014160156</v>
+        <v>2.56752038002014</v>
       </c>
       <c r="H719" t="n">
         <v>87756</v>
@@ -21249,7 +21249,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>2.60308122634888</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H720" t="n">
         <v>117533</v>
@@ -21278,7 +21278,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730647087097</v>
       </c>
       <c r="H721" t="n">
         <v>64041</v>
@@ -21307,7 +21307,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G722" t="n">
-        <v>2.70620894432068</v>
+        <v>2.70620918273926</v>
       </c>
       <c r="H722" t="n">
         <v>119382</v>
@@ -21481,7 +21481,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.90179586410522</v>
+        <v>2.90179562568665</v>
       </c>
       <c r="H728" t="n">
         <v>252045</v>
@@ -21510,7 +21510,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G729" t="n">
-        <v>2.91246390342712</v>
+        <v>2.9124641418457</v>
       </c>
       <c r="H729" t="n">
         <v>172660</v>
@@ -21539,7 +21539,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G730" t="n">
-        <v>2.91957664489746</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H730" t="n">
         <v>108550</v>
@@ -21568,7 +21568,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>2.91957664489746</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H731" t="n">
         <v>155862</v>
@@ -21597,7 +21597,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G732" t="n">
-        <v>2.89468359947205</v>
+        <v>2.89468383789062</v>
       </c>
       <c r="H732" t="n">
         <v>171357</v>
@@ -21626,7 +21626,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>2.8306736946106</v>
+        <v>2.83067345619202</v>
       </c>
       <c r="H733" t="n">
         <v>211140</v>
@@ -21655,7 +21655,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>2.98003053665161</v>
+        <v>2.98003077507019</v>
       </c>
       <c r="H734" t="n">
         <v>1000178</v>
@@ -21742,7 +21742,7 @@
         <v>3.75</v>
       </c>
       <c r="G737" t="n">
-        <v>2.66709160804749</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H737" t="n">
         <v>139990</v>
@@ -21771,7 +21771,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G738" t="n">
-        <v>2.61374998092651</v>
+        <v>2.61374974250793</v>
       </c>
       <c r="H738" t="n">
         <v>117585</v>
@@ -21829,7 +21829,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G740" t="n">
-        <v>2.59952521324158</v>
+        <v>2.59952545166016</v>
       </c>
       <c r="H740" t="n">
         <v>76380</v>
@@ -21858,7 +21858,7 @@
         <v>3.625</v>
       </c>
       <c r="G741" t="n">
-        <v>2.57818865776062</v>
+        <v>2.57818841934204</v>
       </c>
       <c r="H741" t="n">
         <v>86207</v>
@@ -21887,7 +21887,7 @@
         <v>3.75</v>
       </c>
       <c r="G742" t="n">
-        <v>2.66709160804749</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H742" t="n">
         <v>63963</v>
@@ -21945,7 +21945,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G744" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H744" t="n">
         <v>59599</v>
@@ -22061,7 +22061,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G748" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730647087097</v>
       </c>
       <c r="H748" t="n">
         <v>100769</v>
@@ -22119,7 +22119,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G750" t="n">
-        <v>2.56752014160156</v>
+        <v>2.56752038002014</v>
       </c>
       <c r="H750" t="n">
         <v>41661</v>
@@ -22148,7 +22148,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H751" t="n">
         <v>21292</v>
@@ -22177,7 +22177,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57107663154602</v>
+        <v>2.57107639312744</v>
       </c>
       <c r="H752" t="n">
         <v>65965</v>
@@ -22235,7 +22235,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H754" t="n">
         <v>126933</v>
@@ -22293,7 +22293,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G756" t="n">
-        <v>2.61374998092651</v>
+        <v>2.61374974250793</v>
       </c>
       <c r="H756" t="n">
         <v>33799</v>
@@ -22322,7 +22322,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>2.60308122634888</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H757" t="n">
         <v>73291</v>
@@ -22351,7 +22351,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>2.60663771629333</v>
+        <v>2.60663747787476</v>
       </c>
       <c r="H758" t="n">
         <v>38408</v>
@@ -22409,7 +22409,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>2.56040787696838</v>
+        <v>2.56040811538696</v>
       </c>
       <c r="H760" t="n">
         <v>41797</v>
@@ -22496,7 +22496,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>2.51773452758789</v>
+        <v>2.51773428916931</v>
       </c>
       <c r="H763" t="n">
         <v>84397</v>
@@ -22525,7 +22525,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G764" t="n">
-        <v>2.62797451019287</v>
+        <v>2.62797427177429</v>
       </c>
       <c r="H764" t="n">
         <v>24743</v>
@@ -22554,7 +22554,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>2.64931106567383</v>
+        <v>2.64931082725525</v>
       </c>
       <c r="H765" t="n">
         <v>23656</v>
@@ -22583,7 +22583,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.62441849708557</v>
+        <v>2.62441873550415</v>
       </c>
       <c r="H766" t="n">
         <v>72814</v>
@@ -22612,7 +22612,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.65286731719971</v>
+        <v>2.65286707878113</v>
       </c>
       <c r="H767" t="n">
         <v>90927</v>
@@ -22641,7 +22641,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G768" t="n">
-        <v>2.67420411109924</v>
+        <v>2.67420363426208</v>
       </c>
       <c r="H768" t="n">
         <v>56118</v>
@@ -22670,7 +22670,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G769" t="n">
-        <v>2.72043347358704</v>
+        <v>2.72043371200562</v>
       </c>
       <c r="H769" t="n">
         <v>128846</v>
@@ -22757,7 +22757,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G772" t="n">
-        <v>2.73110175132751</v>
+        <v>2.73110198974609</v>
       </c>
       <c r="H772" t="n">
         <v>86625</v>
@@ -22931,7 +22931,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71687769889832</v>
+        <v>2.71687746047974</v>
       </c>
       <c r="H778" t="n">
         <v>35869</v>
@@ -23047,7 +23047,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>2.8413417339325</v>
+        <v>2.84134149551392</v>
       </c>
       <c r="H782" t="n">
         <v>317244</v>
@@ -23076,7 +23076,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.77377533912659</v>
+        <v>2.77377557754517</v>
       </c>
       <c r="H783" t="n">
         <v>120974</v>
@@ -23163,7 +23163,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G786" t="n">
-        <v>2.68131613731384</v>
+        <v>2.68131589889526</v>
       </c>
       <c r="H786" t="n">
         <v>39710</v>
@@ -23192,7 +23192,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>2.64575529098511</v>
+        <v>2.64575505256653</v>
       </c>
       <c r="H787" t="n">
         <v>58312</v>
@@ -23221,7 +23221,7 @@
         <v>3.75</v>
       </c>
       <c r="G788" t="n">
-        <v>2.66709160804749</v>
+        <v>2.66709184646606</v>
       </c>
       <c r="H788" t="n">
         <v>41349</v>
@@ -23250,7 +23250,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G789" t="n">
-        <v>2.67420411109924</v>
+        <v>2.67420363426208</v>
       </c>
       <c r="H789" t="n">
         <v>36914</v>
@@ -23482,7 +23482,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>2.52129077911377</v>
+        <v>2.52129101753235</v>
       </c>
       <c r="H797" t="n">
         <v>223749</v>
@@ -23511,7 +23511,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.49995446205139</v>
+        <v>2.49995422363281</v>
       </c>
       <c r="H798" t="n">
         <v>79031</v>
@@ -23540,7 +23540,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G799" t="n">
-        <v>2.51062226295471</v>
+        <v>2.51062202453613</v>
       </c>
       <c r="H799" t="n">
         <v>101854</v>
@@ -23569,7 +23569,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G800" t="n">
-        <v>2.51773452758789</v>
+        <v>2.51773428916931</v>
       </c>
       <c r="H800" t="n">
         <v>122165</v>
@@ -23627,7 +23627,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G802" t="n">
-        <v>2.51062226295471</v>
+        <v>2.51062202453613</v>
       </c>
       <c r="H802" t="n">
         <v>81492</v>
@@ -23685,7 +23685,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G804" t="n">
-        <v>2.49639797210693</v>
+        <v>2.49639773368835</v>
       </c>
       <c r="H804" t="n">
         <v>123967</v>
@@ -23714,7 +23714,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>2.49284172058105</v>
+        <v>2.49284195899963</v>
       </c>
       <c r="H805" t="n">
         <v>67850</v>
@@ -23772,7 +23772,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>2.49639797210693</v>
+        <v>2.49639773368835</v>
       </c>
       <c r="H807" t="n">
         <v>76903</v>
@@ -23830,7 +23830,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.48572969436646</v>
+        <v>2.48572945594788</v>
       </c>
       <c r="H809" t="n">
         <v>86790</v>
@@ -23859,7 +23859,7 @@
         <v>3.375</v>
       </c>
       <c r="G810" t="n">
-        <v>2.40038275718689</v>
+        <v>2.40038251876831</v>
       </c>
       <c r="H810" t="n">
         <v>202451</v>
@@ -23917,7 +23917,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>2.3754894733429</v>
+        <v>2.37548995018005</v>
       </c>
       <c r="H812" t="n">
         <v>91593</v>
@@ -23946,7 +23946,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G813" t="n">
-        <v>2.3754894733429</v>
+        <v>2.37548995018005</v>
       </c>
       <c r="H813" t="n">
         <v>67492</v>
@@ -24004,7 +24004,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>2.3257040977478</v>
+        <v>2.32570385932922</v>
       </c>
       <c r="H815" t="n">
         <v>86372</v>
@@ -24062,7 +24062,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G817" t="n">
-        <v>2.27236199378967</v>
+        <v>2.27236223220825</v>
       </c>
       <c r="H817" t="n">
         <v>146028</v>
@@ -24091,7 +24091,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G818" t="n">
-        <v>2.27591824531555</v>
+        <v>2.27591872215271</v>
       </c>
       <c r="H818" t="n">
         <v>137063</v>
@@ -24120,7 +24120,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G819" t="n">
-        <v>2.27591824531555</v>
+        <v>2.27591872215271</v>
       </c>
       <c r="H819" t="n">
         <v>243571</v>
@@ -24149,7 +24149,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G820" t="n">
-        <v>2.27591824531555</v>
+        <v>2.27591872215271</v>
       </c>
       <c r="H820" t="n">
         <v>105828</v>
@@ -24178,7 +24178,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G821" t="n">
-        <v>2.27591824531555</v>
+        <v>2.27591872215271</v>
       </c>
       <c r="H821" t="n">
         <v>116326</v>
@@ -24207,7 +24207,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G822" t="n">
-        <v>2.28658628463745</v>
+        <v>2.28658652305603</v>
       </c>
       <c r="H822" t="n">
         <v>108669</v>
@@ -24236,7 +24236,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>2.27236199378967</v>
+        <v>2.27236223220825</v>
       </c>
       <c r="H823" t="n">
         <v>63237</v>
@@ -24323,7 +24323,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G826" t="n">
-        <v>2.29014277458191</v>
+        <v>2.29014301300049</v>
       </c>
       <c r="H826" t="n">
         <v>59872</v>
@@ -24352,7 +24352,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>2.29014277458191</v>
+        <v>2.29014301300049</v>
       </c>
       <c r="H827" t="n">
         <v>88835</v>
@@ -24381,7 +24381,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G828" t="n">
-        <v>2.32214832305908</v>
+        <v>2.32214784622192</v>
       </c>
       <c r="H828" t="n">
         <v>344993</v>
@@ -24613,7 +24613,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G836" t="n">
-        <v>2.28658628463745</v>
+        <v>2.28658652305603</v>
       </c>
       <c r="H836" t="n">
         <v>63039</v>
@@ -24642,7 +24642,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G837" t="n">
-        <v>2.36126518249512</v>
+        <v>2.3612654209137</v>
       </c>
       <c r="H837" t="n">
         <v>143505</v>
@@ -24671,7 +24671,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G838" t="n">
-        <v>2.3754894733429</v>
+        <v>2.37548995018005</v>
       </c>
       <c r="H838" t="n">
         <v>153463</v>
@@ -24758,7 +24758,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>2.52129077911377</v>
+        <v>2.52129101753235</v>
       </c>
       <c r="H841" t="n">
         <v>189397</v>
@@ -24874,7 +24874,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G845" t="n">
-        <v>2.58174467086792</v>
+        <v>2.5817449092865</v>
       </c>
       <c r="H845" t="n">
         <v>178328</v>
@@ -24903,7 +24903,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>2.58530116081238</v>
+        <v>2.58530068397522</v>
       </c>
       <c r="H846" t="n">
         <v>68274</v>
@@ -24932,7 +24932,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.60308122634888</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H847" t="n">
         <v>177657</v>
@@ -24990,7 +24990,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>2.4288318157196</v>
+        <v>2.42883133888245</v>
       </c>
       <c r="H849" t="n">
         <v>74414</v>
@@ -25019,7 +25019,7 @@
         <v>3.375</v>
       </c>
       <c r="G850" t="n">
-        <v>2.40038275718689</v>
+        <v>2.40038251876831</v>
       </c>
       <c r="H850" t="n">
         <v>114787</v>
@@ -25106,7 +25106,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.36126518249512</v>
+        <v>2.3612654209137</v>
       </c>
       <c r="H853" t="n">
         <v>119893</v>
@@ -25135,7 +25135,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>2.36497187614441</v>
+        <v>2.36497211456299</v>
       </c>
       <c r="H854" t="n">
         <v>91183</v>
@@ -25164,7 +25164,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>2.43540215492249</v>
+        <v>2.43540239334106</v>
       </c>
       <c r="H855" t="n">
         <v>60436</v>
@@ -25193,7 +25193,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G856" t="n">
-        <v>2.42057514190674</v>
+        <v>2.42057490348816</v>
       </c>
       <c r="H856" t="n">
         <v>67266</v>
@@ -25222,7 +25222,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G857" t="n">
-        <v>2.47617745399475</v>
+        <v>2.47617769241333</v>
       </c>
       <c r="H857" t="n">
         <v>233867</v>
@@ -25309,7 +25309,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.37238574028015</v>
+        <v>2.37238597869873</v>
       </c>
       <c r="H860" t="n">
         <v>119077</v>
@@ -25715,7 +25715,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>2.07583737373352</v>
+        <v>2.0758376121521</v>
       </c>
       <c r="H874" t="n">
         <v>63145</v>
@@ -25773,7 +25773,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>2.12031984329224</v>
+        <v>2.12031960487366</v>
       </c>
       <c r="H876" t="n">
         <v>101590</v>
@@ -26005,7 +26005,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G884" t="n">
-        <v>2.03135538101196</v>
+        <v>2.03135561943054</v>
       </c>
       <c r="H884" t="n">
         <v>170336</v>
@@ -26063,7 +26063,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G886" t="n">
-        <v>2.01652812957764</v>
+        <v>2.01652789115906</v>
       </c>
       <c r="H886" t="n">
         <v>78138</v>
@@ -26179,7 +26179,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.28342127799988</v>
+        <v>2.2834210395813</v>
       </c>
       <c r="H890" t="n">
         <v>233336</v>
@@ -26498,7 +26498,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G901" t="n">
-        <v>2.28342127799988</v>
+        <v>2.2834210395813</v>
       </c>
       <c r="H901" t="n">
         <v>85699</v>
@@ -26556,7 +26556,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G903" t="n">
-        <v>2.24264621734619</v>
+        <v>2.24264597892761</v>
       </c>
       <c r="H903" t="n">
         <v>227407</v>
@@ -26585,7 +26585,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G904" t="n">
-        <v>2.26118016242981</v>
+        <v>2.26118040084839</v>
       </c>
       <c r="H904" t="n">
         <v>41843</v>
@@ -26643,7 +26643,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G906" t="n">
-        <v>2.26118016242981</v>
+        <v>2.26118040084839</v>
       </c>
       <c r="H906" t="n">
         <v>93112</v>
@@ -26701,7 +26701,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>2.28342127799988</v>
+        <v>2.2834210395813</v>
       </c>
       <c r="H908" t="n">
         <v>180734</v>
@@ -27078,7 +27078,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G921" t="n">
-        <v>2.15368151664734</v>
+        <v>2.15368127822876</v>
       </c>
       <c r="H921" t="n">
         <v>83002</v>
@@ -27194,7 +27194,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G925" t="n">
-        <v>2.12031984329224</v>
+        <v>2.12031960487366</v>
       </c>
       <c r="H925" t="n">
         <v>112906</v>
@@ -27281,7 +27281,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G928" t="n">
-        <v>2.09807848930359</v>
+        <v>2.09807872772217</v>
       </c>
       <c r="H928" t="n">
         <v>56531</v>
@@ -27455,7 +27455,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>2.16850876808167</v>
+        <v>2.16850900650024</v>
       </c>
       <c r="H934" t="n">
         <v>79342</v>
@@ -27484,7 +27484,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G935" t="n">
-        <v>2.24264621734619</v>
+        <v>2.24264597892761</v>
       </c>
       <c r="H935" t="n">
         <v>97802</v>
@@ -27600,7 +27600,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G939" t="n">
-        <v>2.52807331085205</v>
+        <v>2.52807354927063</v>
       </c>
       <c r="H939" t="n">
         <v>638409</v>
@@ -27658,7 +27658,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>2.63927888870239</v>
+        <v>2.63927912712097</v>
       </c>
       <c r="H941" t="n">
         <v>881119</v>
@@ -27774,7 +27774,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G945" t="n">
-        <v>2.75789856910706</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H945" t="n">
         <v>174113</v>
@@ -27803,7 +27803,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>2.75789856910706</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H946" t="n">
         <v>251163</v>
@@ -27832,7 +27832,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G947" t="n">
-        <v>2.75789856910706</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H947" t="n">
         <v>162510</v>
@@ -27977,7 +27977,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G952" t="n">
-        <v>2.75789856910706</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H952" t="n">
         <v>75069</v>
@@ -28064,7 +28064,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G955" t="n">
-        <v>2.67264080047607</v>
+        <v>2.67264103889465</v>
       </c>
       <c r="H955" t="n">
         <v>162705</v>
@@ -28093,7 +28093,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G956" t="n">
-        <v>2.68376135826111</v>
+        <v>2.68376111984253</v>
       </c>
       <c r="H956" t="n">
         <v>86012</v>
@@ -28180,7 +28180,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>2.71712327003479</v>
+        <v>2.71712303161621</v>
       </c>
       <c r="H959" t="n">
         <v>67572</v>
@@ -28209,7 +28209,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G960" t="n">
-        <v>2.75789856910706</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H960" t="n">
         <v>33375</v>
@@ -28354,7 +28354,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G965" t="n">
-        <v>2.75789856910706</v>
+        <v>2.75789833068848</v>
       </c>
       <c r="H965" t="n">
         <v>122286</v>
@@ -28383,7 +28383,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G966" t="n">
-        <v>2.70970916748047</v>
+        <v>2.70970940589905</v>
       </c>
       <c r="H966" t="n">
         <v>148307</v>
@@ -28412,7 +28412,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G967" t="n">
-        <v>2.72453689575195</v>
+        <v>2.72453665733337</v>
       </c>
       <c r="H967" t="n">
         <v>92773</v>
@@ -28441,7 +28441,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.70970916748047</v>
+        <v>2.70970940589905</v>
       </c>
       <c r="H968" t="n">
         <v>42501</v>
@@ -28557,7 +28557,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>2.91729307174683</v>
+        <v>2.91729331016541</v>
       </c>
       <c r="H972" t="n">
         <v>834985</v>
@@ -28760,7 +28760,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>2.89875864982605</v>
+        <v>2.89875888824463</v>
       </c>
       <c r="H979" t="n">
         <v>279460</v>
@@ -28789,7 +28789,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G980" t="n">
-        <v>2.90987944602966</v>
+        <v>2.90987920761108</v>
       </c>
       <c r="H980" t="n">
         <v>729798</v>
@@ -28934,7 +28934,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G985" t="n">
-        <v>2.9877233505249</v>
+        <v>2.98772311210632</v>
       </c>
       <c r="H985" t="n">
         <v>231299</v>
@@ -29021,7 +29021,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G988" t="n">
-        <v>2.80608725547791</v>
+        <v>2.80608749389648</v>
       </c>
       <c r="H988" t="n">
         <v>129247</v>
@@ -29050,7 +29050,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>2.96177530288696</v>
+        <v>2.96177506446838</v>
       </c>
       <c r="H989" t="n">
         <v>478994</v>
@@ -29137,7 +29137,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G992" t="n">
-        <v>3.23608231544495</v>
+        <v>3.23608207702637</v>
       </c>
       <c r="H992" t="n">
         <v>1152288</v>
@@ -29195,7 +29195,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G994" t="n">
-        <v>3.30651259422302</v>
+        <v>3.3065128326416</v>
       </c>
       <c r="H994" t="n">
         <v>868963</v>
@@ -29253,7 +29253,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G996" t="n">
-        <v>3.40659761428833</v>
+        <v>3.40659737586975</v>
       </c>
       <c r="H996" t="n">
         <v>206522</v>
@@ -29282,7 +29282,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>3.4177188873291</v>
+        <v>3.41771841049194</v>
       </c>
       <c r="H997" t="n">
         <v>202987</v>
@@ -29514,7 +29514,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1005" t="n">
         <v>332417</v>
@@ -29543,7 +29543,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1006" t="n">
         <v>349628</v>
@@ -29688,7 +29688,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1011" t="n">
         <v>151303</v>
@@ -29775,7 +29775,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1014" t="n">
         <v>102689</v>
@@ -29804,7 +29804,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.8402988910675</v>
+        <v>3.84029936790466</v>
       </c>
       <c r="H1015" t="n">
         <v>295814</v>
@@ -30007,7 +30007,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.85512638092041</v>
+        <v>3.85512685775757</v>
       </c>
       <c r="H1022" t="n">
         <v>233331</v>
@@ -30065,7 +30065,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.86995434761047</v>
+        <v>3.86995387077332</v>
       </c>
       <c r="H1024" t="n">
         <v>264811</v>
@@ -30123,7 +30123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.85512638092041</v>
+        <v>3.85512685775757</v>
       </c>
       <c r="H1026" t="n">
         <v>83051</v>
@@ -30152,7 +30152,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.84771275520325</v>
+        <v>3.84771323204041</v>
       </c>
       <c r="H1027" t="n">
         <v>72510</v>
@@ -30239,7 +30239,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.85512638092041</v>
+        <v>3.85512685775757</v>
       </c>
       <c r="H1030" t="n">
         <v>156105</v>
@@ -30326,7 +30326,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1033" t="n">
         <v>281130</v>
@@ -30471,7 +30471,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.60306119918823</v>
+        <v>3.60306072235107</v>
       </c>
       <c r="H1038" t="n">
         <v>205159</v>
@@ -30529,7 +30529,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.72909450531006</v>
+        <v>3.7290940284729</v>
       </c>
       <c r="H1040" t="n">
         <v>366585</v>
@@ -30819,7 +30819,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.04788303375244</v>
+        <v>4.0478835105896</v>
       </c>
       <c r="H1050" t="n">
         <v>270277</v>
@@ -30848,7 +30848,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.06271076202393</v>
+        <v>4.06271123886108</v>
       </c>
       <c r="H1051" t="n">
         <v>169274</v>
@@ -30906,7 +30906,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1053" t="n">
         <v>746712</v>
@@ -31022,7 +31022,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.63271570205688</v>
+        <v>3.63271617889404</v>
       </c>
       <c r="H1057" t="n">
         <v>486017</v>
@@ -31080,7 +31080,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.66607761383057</v>
+        <v>3.66607713699341</v>
       </c>
       <c r="H1059" t="n">
         <v>331600</v>
@@ -31138,7 +31138,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.62159514427185</v>
+        <v>3.62159538269043</v>
       </c>
       <c r="H1061" t="n">
         <v>217946</v>
@@ -31225,7 +31225,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.09522247314453</v>
+        <v>3.09522223472595</v>
       </c>
       <c r="H1064" t="n">
         <v>371613</v>
@@ -31341,7 +31341,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.24264621734619</v>
+        <v>2.24264597892761</v>
       </c>
       <c r="H1068" t="n">
         <v>472775</v>
@@ -31370,7 +31370,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.29083490371704</v>
+        <v>2.29083514213562</v>
       </c>
       <c r="H1069" t="n">
         <v>496099</v>
@@ -31428,7 +31428,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.06471705436707</v>
+        <v>2.06471729278564</v>
       </c>
       <c r="H1071" t="n">
         <v>384018</v>
@@ -31515,7 +31515,7 @@
         <v>3.125</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.31678295135498</v>
+        <v>2.3167827129364</v>
       </c>
       <c r="H1074" t="n">
         <v>253242</v>
@@ -31573,7 +31573,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.37238574028015</v>
+        <v>2.37238597869873</v>
       </c>
       <c r="H1076" t="n">
         <v>180047</v>
@@ -31602,7 +31602,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.34273099899292</v>
+        <v>2.34273076057434</v>
       </c>
       <c r="H1077" t="n">
         <v>125940</v>
@@ -31631,7 +31631,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.30195546150208</v>
+        <v>2.30195569992065</v>
       </c>
       <c r="H1078" t="n">
         <v>169458</v>
@@ -31660,7 +31660,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.38721323013306</v>
+        <v>2.38721299171448</v>
       </c>
       <c r="H1079" t="n">
         <v>228291</v>
@@ -31689,7 +31689,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.28342127799988</v>
+        <v>2.2834210395813</v>
       </c>
       <c r="H1080" t="n">
         <v>79106</v>
@@ -31718,7 +31718,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.26118016242981</v>
+        <v>2.26118040084839</v>
       </c>
       <c r="H1081" t="n">
         <v>248140</v>
@@ -31863,7 +31863,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.67264080047607</v>
+        <v>2.67264103889465</v>
       </c>
       <c r="H1086" t="n">
         <v>186894</v>
@@ -31979,7 +31979,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.67264080047607</v>
+        <v>2.67264103889465</v>
       </c>
       <c r="H1090" t="n">
         <v>573804</v>
@@ -32153,7 +32153,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.17306637763977</v>
+        <v>3.17306590080261</v>
       </c>
       <c r="H1096" t="n">
         <v>403206</v>
@@ -32182,7 +32182,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.18789339065552</v>
+        <v>3.18789386749268</v>
       </c>
       <c r="H1097" t="n">
         <v>381925</v>
@@ -32240,7 +32240,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.18789339065552</v>
+        <v>3.18789386749268</v>
       </c>
       <c r="H1099" t="n">
         <v>151019</v>
@@ -32327,7 +32327,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.12858366966248</v>
+        <v>3.1285834312439</v>
       </c>
       <c r="H1102" t="n">
         <v>43938</v>
@@ -32356,7 +32356,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.11375617980957</v>
+        <v>3.11375641822815</v>
       </c>
       <c r="H1103" t="n">
         <v>64482</v>
@@ -32414,7 +32414,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.13599753379822</v>
+        <v>3.13599729537964</v>
       </c>
       <c r="H1105" t="n">
         <v>97662</v>
@@ -32646,7 +32646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.9877233505249</v>
+        <v>2.98772311210632</v>
       </c>
       <c r="H1113" t="n">
         <v>369835</v>
@@ -32791,7 +32791,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.26944398880005</v>
+        <v>3.26944422721863</v>
       </c>
       <c r="H1118" t="n">
         <v>303345</v>
@@ -32820,7 +32820,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.31392621994019</v>
+        <v>3.31392598152161</v>
       </c>
       <c r="H1119" t="n">
         <v>234448</v>
@@ -32849,7 +32849,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.29168510437012</v>
+        <v>3.29168558120728</v>
       </c>
       <c r="H1120" t="n">
         <v>119756</v>
@@ -33603,7 +33603,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.00996422767639</v>
+        <v>3.00996446609497</v>
       </c>
       <c r="H1146" t="n">
         <v>287815</v>
@@ -33748,7 +33748,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.02108478546143</v>
+        <v>3.02108502388</v>
       </c>
       <c r="H1151" t="n">
         <v>257205</v>
@@ -33777,7 +33777,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.08780837059021</v>
+        <v>3.08780860900879</v>
       </c>
       <c r="H1152" t="n">
         <v>145042</v>
@@ -33864,7 +33864,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.12116980552673</v>
+        <v>3.12117004394531</v>
       </c>
       <c r="H1155" t="n">
         <v>89194</v>
@@ -33893,7 +33893,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.12858366966248</v>
+        <v>3.1285834312439</v>
       </c>
       <c r="H1156" t="n">
         <v>121107</v>
@@ -33922,7 +33922,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.08780837059021</v>
+        <v>3.08780860900879</v>
       </c>
       <c r="H1157" t="n">
         <v>89877</v>
@@ -33980,7 +33980,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.06556749343872</v>
+        <v>3.06556725502014</v>
       </c>
       <c r="H1159" t="n">
         <v>97598</v>
@@ -34096,7 +34096,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.09151530265808</v>
+        <v>3.0915150642395</v>
       </c>
       <c r="H1163" t="n">
         <v>187881</v>
@@ -34386,7 +34386,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.37323617935181</v>
+        <v>3.37323665618896</v>
       </c>
       <c r="H1173" t="n">
         <v>32881</v>
@@ -34502,7 +34502,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.58081960678101</v>
+        <v>3.58082008361816</v>
       </c>
       <c r="H1177" t="n">
         <v>88222</v>
@@ -34560,7 +34560,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.4177188873291</v>
+        <v>3.41771841049194</v>
       </c>
       <c r="H1179" t="n">
         <v>98749</v>
@@ -34589,7 +34589,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.7031455039978</v>
+        <v>3.70314598083496</v>
       </c>
       <c r="H1180" t="n">
         <v>607643</v>
@@ -34734,7 +34734,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.86995434761047</v>
+        <v>3.86995387077332</v>
       </c>
       <c r="H1185" t="n">
         <v>246353</v>
@@ -34821,7 +34821,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.84771275520325</v>
+        <v>3.84771323204041</v>
       </c>
       <c r="H1188" t="n">
         <v>228820</v>
@@ -34850,7 +34850,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581689834595</v>
       </c>
       <c r="H1189" t="n">
         <v>155683</v>
@@ -34937,7 +34937,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.48529243469238</v>
+        <v>4.48529195785522</v>
       </c>
       <c r="H1192" t="n">
         <v>501739</v>
@@ -34995,7 +34995,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.48529243469238</v>
+        <v>4.48529195785522</v>
       </c>
       <c r="H1194" t="n">
         <v>253918</v>
@@ -35111,7 +35111,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.44080877304077</v>
+        <v>4.44080924987793</v>
       </c>
       <c r="H1198" t="n">
         <v>307984</v>
@@ -35198,7 +35198,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.81149435043335</v>
+        <v>4.81149482727051</v>
       </c>
       <c r="H1201" t="n">
         <v>691478</v>
@@ -35343,7 +35343,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.41941833496094</v>
+        <v>5.4194188117981</v>
       </c>
       <c r="H1206" t="n">
         <v>352753</v>
@@ -35372,7 +35372,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1207" t="n">
-        <v>5.5973482131958</v>
+        <v>5.59734773635864</v>
       </c>
       <c r="H1207" t="n">
         <v>525409</v>
@@ -35430,7 +35430,7 @@
         <v>7.5</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.56027889251709</v>
+        <v>5.56027936935425</v>
       </c>
       <c r="H1209" t="n">
         <v>262844</v>
@@ -35459,7 +35459,7 @@
         <v>7.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.56027889251709</v>
+        <v>5.56027936935425</v>
       </c>
       <c r="H1210" t="n">
         <v>186425</v>
@@ -35517,7 +35517,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.73820829391479</v>
+        <v>5.73820781707764</v>
       </c>
       <c r="H1212" t="n">
         <v>297846</v>
@@ -35575,7 +35575,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.62700271606445</v>
+        <v>5.62700319290161</v>
       </c>
       <c r="H1214" t="n">
         <v>339811</v>
@@ -35807,7 +35807,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1222" t="n">
-        <v>5.44166040420532</v>
+        <v>5.44165992736816</v>
       </c>
       <c r="H1222" t="n">
         <v>341867</v>
@@ -35836,7 +35836,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.40459108352661</v>
+        <v>5.40459156036377</v>
       </c>
       <c r="H1223" t="n">
         <v>149706</v>
@@ -35865,7 +35865,7 @@
         <v>7.25</v>
       </c>
       <c r="G1224" t="n">
-        <v>5.37493658065796</v>
+        <v>5.3749361038208</v>
       </c>
       <c r="H1224" t="n">
         <v>174643</v>
@@ -35981,7 +35981,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1228" t="n">
-        <v>5.1673526763916</v>
+        <v>5.16735219955444</v>
       </c>
       <c r="H1228" t="n">
         <v>343066</v>
@@ -36010,7 +36010,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>5.40459108352661</v>
+        <v>5.40459156036377</v>
       </c>
       <c r="H1229" t="n">
         <v>382212</v>
@@ -36068,7 +36068,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.5973482131958</v>
+        <v>5.59734773635864</v>
       </c>
       <c r="H1231" t="n">
         <v>248006</v>
@@ -36155,7 +36155,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.6937255859375</v>
+        <v>5.69372606277466</v>
       </c>
       <c r="H1234" t="n">
         <v>364428</v>
@@ -36474,7 +36474,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1245" t="n">
-        <v>6.24233961105347</v>
+        <v>6.24234008789062</v>
       </c>
       <c r="H1245" t="n">
         <v>371423</v>
@@ -36503,7 +36503,7 @@
         <v>8.25</v>
       </c>
       <c r="G1246" t="n">
-        <v>6.11630725860596</v>
+        <v>6.1163067817688</v>
       </c>
       <c r="H1246" t="n">
         <v>435902</v>
@@ -36532,7 +36532,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1247" t="n">
-        <v>6.04216957092285</v>
+        <v>6.04217004776001</v>
       </c>
       <c r="H1247" t="n">
         <v>194860</v>
@@ -36619,7 +36619,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>6.18303060531616</v>
+        <v>6.183030128479</v>
       </c>
       <c r="H1250" t="n">
         <v>175266</v>
@@ -36648,7 +36648,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1251" t="n">
-        <v>6.62043905258179</v>
+        <v>6.62043952941895</v>
       </c>
       <c r="H1251" t="n">
         <v>688617</v>
@@ -36706,7 +36706,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1253" t="n">
-        <v>6.58337020874023</v>
+        <v>6.58337116241455</v>
       </c>
       <c r="H1253" t="n">
         <v>375451</v>
@@ -37141,7 +37141,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.87335538864136</v>
+        <v>7.87335443496704</v>
       </c>
       <c r="H1268" t="n">
         <v>337710</v>
@@ -37315,7 +37315,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.68059778213501</v>
+        <v>7.68059873580933</v>
       </c>
       <c r="H1274" t="n">
         <v>508688</v>
@@ -37373,7 +37373,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.59163475036621</v>
+        <v>7.59163379669189</v>
       </c>
       <c r="H1276" t="n">
         <v>279624</v>
@@ -37489,7 +37489,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G1280" t="n">
-        <v>7.33215522766113</v>
+        <v>7.33215427398682</v>
       </c>
       <c r="H1280" t="n">
         <v>468812</v>
@@ -37547,7 +37547,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.23577642440796</v>
+        <v>7.23577690124512</v>
       </c>
       <c r="H1282" t="n">
         <v>339904</v>
@@ -37953,7 +37953,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.87335538864136</v>
+        <v>7.87335443496704</v>
       </c>
       <c r="H1296" t="n">
         <v>326366</v>
@@ -38011,7 +38011,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1298" t="n">
-        <v>7.97714614868164</v>
+        <v>7.97714710235596</v>
       </c>
       <c r="H1298" t="n">
         <v>722047</v>
@@ -38301,7 +38301,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1308" t="n">
-        <v>8.16990375518799</v>
+        <v>8.16990280151367</v>
       </c>
       <c r="H1308" t="n">
         <v>576399</v>
@@ -38359,7 +38359,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.84370040893555</v>
+        <v>7.84370136260986</v>
       </c>
       <c r="H1310" t="n">
         <v>221178</v>
@@ -38388,7 +38388,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1311" t="n">
-        <v>7.73990869522095</v>
+        <v>7.73990774154663</v>
       </c>
       <c r="H1311" t="n">
         <v>269913</v>
@@ -38620,7 +38620,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>7.69542551040649</v>
+        <v>7.69542646408081</v>
       </c>
       <c r="H1319" t="n">
         <v>388891</v>
@@ -38649,7 +38649,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1320" t="n">
-        <v>7.59163475036621</v>
+        <v>7.59163379669189</v>
       </c>
       <c r="H1320" t="n">
         <v>242496</v>
@@ -38707,7 +38707,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1322" t="n">
-        <v>7.75473642349243</v>
+        <v>7.75473546981812</v>
       </c>
       <c r="H1322" t="n">
         <v>498215</v>
@@ -38910,7 +38910,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1329" t="n">
-        <v>7.84370040893555</v>
+        <v>7.84370136260986</v>
       </c>
       <c r="H1329" t="n">
         <v>200870</v>
@@ -39026,7 +39026,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1333" t="n">
-        <v>7.97714614868164</v>
+        <v>7.97714710235596</v>
       </c>
       <c r="H1333" t="n">
         <v>197842</v>
@@ -39287,7 +39287,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.68230056762695</v>
+        <v>9.68229961395264</v>
       </c>
       <c r="H1342" t="n">
         <v>618401</v>
@@ -39345,7 +39345,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1344" t="n">
-        <v>9.99367523193359</v>
+        <v>9.99367427825928</v>
       </c>
       <c r="H1344" t="n">
         <v>540353</v>
@@ -39490,7 +39490,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1349" t="n">
-        <v>10.2383270263672</v>
+        <v>10.2383279800415</v>
       </c>
       <c r="H1349" t="n">
         <v>493981</v>
@@ -39519,7 +39519,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1350" t="n">
-        <v>10.1122932434082</v>
+        <v>10.1122941970825</v>
       </c>
       <c r="H1350" t="n">
         <v>618145</v>
@@ -39635,7 +39635,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1354" t="n">
-        <v>10.1271228790283</v>
+        <v>10.127121925354</v>
       </c>
       <c r="H1354" t="n">
         <v>513857</v>
@@ -39867,7 +39867,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1362" t="n">
-        <v>10.0208759307861</v>
+        <v>10.0208768844604</v>
       </c>
       <c r="H1362" t="n">
         <v>891294</v>
@@ -39896,7 +39896,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1363" t="n">
-        <v>9.9205150604248</v>
+        <v>9.92051410675049</v>
       </c>
       <c r="H1363" t="n">
         <v>442173</v>
@@ -39925,7 +39925,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1364" t="n">
-        <v>10.3296871185303</v>
+        <v>10.329686164856</v>
       </c>
       <c r="H1364" t="n">
         <v>901307</v>
@@ -39983,7 +39983,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.5226926803589</v>
+        <v>10.5226936340332</v>
       </c>
       <c r="H1366" t="n">
         <v>856596</v>
@@ -40157,7 +40157,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1372" t="n">
-        <v>10.661657333374</v>
+        <v>10.6616582870483</v>
       </c>
       <c r="H1372" t="n">
         <v>1102741</v>
@@ -40244,7 +40244,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1375" t="n">
-        <v>11.2252359390259</v>
+        <v>11.2252349853516</v>
       </c>
       <c r="H1375" t="n">
         <v>441675</v>
@@ -40389,7 +40389,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1380" t="n">
-        <v>11.6884498596191</v>
+        <v>11.6884508132935</v>
       </c>
       <c r="H1380" t="n">
         <v>637306</v>
@@ -40447,7 +40447,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.7888135910034</v>
+        <v>11.7888126373291</v>
       </c>
       <c r="H1382" t="n">
         <v>401929</v>
@@ -40505,7 +40505,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.1207847595215</v>
+        <v>12.1207838058472</v>
       </c>
       <c r="H1384" t="n">
         <v>271506</v>
@@ -40563,7 +40563,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>11.6575698852539</v>
+        <v>11.6575689315796</v>
       </c>
       <c r="H1386" t="n">
         <v>248187</v>
@@ -40679,7 +40679,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1390" t="n">
-        <v>11.8582944869995</v>
+        <v>11.8582954406738</v>
       </c>
       <c r="H1390" t="n">
         <v>217840</v>
@@ -40708,7 +40708,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.4954442977905</v>
+        <v>11.4954433441162</v>
       </c>
       <c r="H1391" t="n">
         <v>232147</v>
@@ -40766,7 +40766,7 @@
         <v>15</v>
       </c>
       <c r="G1393" t="n">
-        <v>11.5803661346436</v>
+        <v>11.5803670883179</v>
       </c>
       <c r="H1393" t="n">
         <v>123407</v>
@@ -40795,7 +40795,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1394" t="n">
-        <v>11.6575698852539</v>
+        <v>11.6575689315796</v>
       </c>
       <c r="H1394" t="n">
         <v>177496</v>
@@ -40824,7 +40824,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1395" t="n">
-        <v>11.4259614944458</v>
+        <v>11.4259624481201</v>
       </c>
       <c r="H1395" t="n">
         <v>166375</v>
@@ -40882,7 +40882,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1397" t="n">
-        <v>11.449122428894</v>
+        <v>11.4491233825684</v>
       </c>
       <c r="H1397" t="n">
         <v>322076</v>
@@ -40940,7 +40940,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>11.6575698852539</v>
+        <v>11.6575689315796</v>
       </c>
       <c r="H1399" t="n">
         <v>196451</v>
@@ -41085,7 +41085,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1404" t="n">
-        <v>11.4800043106079</v>
+        <v>11.4800033569336</v>
       </c>
       <c r="H1404" t="n">
         <v>229570</v>
@@ -41114,7 +41114,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>12.2365875244141</v>
+        <v>12.2365884780884</v>
       </c>
       <c r="H1405" t="n">
         <v>815649</v>
@@ -41172,7 +41172,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G1407" t="n">
-        <v>11.8196954727173</v>
+        <v>11.819694519043</v>
       </c>
       <c r="H1407" t="n">
         <v>373868</v>
@@ -41607,7 +41607,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.2365875244141</v>
+        <v>12.2365884780884</v>
       </c>
       <c r="H1422" t="n">
         <v>185558</v>
@@ -41636,7 +41636,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1423" t="n">
-        <v>12.1671056747437</v>
+        <v>12.1671047210693</v>
       </c>
       <c r="H1423" t="n">
         <v>126683</v>
@@ -42100,7 +42100,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1439" t="n">
-        <v>12.5376758575439</v>
+        <v>12.5376768112183</v>
       </c>
       <c r="H1439" t="n">
         <v>197205</v>
@@ -42419,7 +42419,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0749206542969</v>
+        <v>10.0749197006226</v>
       </c>
       <c r="H1450" t="n">
         <v>1314808</v>
@@ -42448,7 +42448,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1451" t="n">
-        <v>9.76610946655273</v>
+        <v>9.76610851287842</v>
       </c>
       <c r="H1451" t="n">
         <v>587568</v>
@@ -42506,7 +42506,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1453" t="n">
-        <v>9.61942481994629</v>
+        <v>9.61942386627197</v>
       </c>
       <c r="H1453" t="n">
         <v>427074</v>
@@ -42564,7 +42564,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1455" t="n">
-        <v>9.27201366424561</v>
+        <v>9.27201461791992</v>
       </c>
       <c r="H1455" t="n">
         <v>351449</v>
@@ -42593,7 +42593,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1456" t="n">
-        <v>9.34149646759033</v>
+        <v>9.34149551391602</v>
       </c>
       <c r="H1456" t="n">
         <v>567062</v>
@@ -42622,7 +42622,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G1457" t="n">
-        <v>9.58082294464111</v>
+        <v>9.58082389831543</v>
       </c>
       <c r="H1457" t="n">
         <v>330734</v>
@@ -42767,7 +42767,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.73159694671631</v>
+        <v>8.73159790039062</v>
       </c>
       <c r="H1462" t="n">
         <v>423384</v>
@@ -42825,7 +42825,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1464" t="n">
-        <v>8.5385913848877</v>
+        <v>8.53859043121338</v>
       </c>
       <c r="H1464" t="n">
         <v>545701</v>
@@ -42912,7 +42912,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>8.7393159866333</v>
+        <v>8.73931694030762</v>
       </c>
       <c r="H1467" t="n">
         <v>613279</v>
@@ -43115,7 +43115,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1474" t="n">
-        <v>9.27201366424561</v>
+        <v>9.27201461791992</v>
       </c>
       <c r="H1474" t="n">
         <v>637336</v>
@@ -43144,7 +43144,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1475" t="n">
-        <v>9.04040718078613</v>
+        <v>9.04040622711182</v>
       </c>
       <c r="H1475" t="n">
         <v>421275</v>
@@ -43579,7 +43579,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.71978759765625</v>
+        <v>9.71978855133057</v>
       </c>
       <c r="H1490" t="n">
         <v>386060</v>
@@ -43637,7 +43637,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1492" t="n">
-        <v>9.57310199737549</v>
+        <v>9.5731029510498</v>
       </c>
       <c r="H1492" t="n">
         <v>226612</v>
@@ -43695,7 +43695,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>9.76610946655273</v>
+        <v>9.76610851287842</v>
       </c>
       <c r="H1494" t="n">
         <v>593274</v>
@@ -43840,7 +43840,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.51134204864502</v>
+        <v>9.5113410949707</v>
       </c>
       <c r="H1499" t="n">
         <v>222491</v>
@@ -44130,7 +44130,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>9.51134204864502</v>
+        <v>9.5113410949707</v>
       </c>
       <c r="H1509" t="n">
         <v>192211</v>
@@ -44159,7 +44159,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G1510" t="n">
-        <v>10.2447652816772</v>
+        <v>10.2447643280029</v>
       </c>
       <c r="H1510" t="n">
         <v>587994</v>
@@ -44217,7 +44217,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1512" t="n">
-        <v>10.0671997070312</v>
+        <v>10.0671987533569</v>
       </c>
       <c r="H1512" t="n">
         <v>378676</v>
@@ -44246,7 +44246,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1513" t="n">
-        <v>9.94367504119873</v>
+        <v>9.94367408752441</v>
       </c>
       <c r="H1513" t="n">
         <v>232655</v>
@@ -44478,7 +44478,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1521" t="n">
-        <v>9.57310199737549</v>
+        <v>9.5731029510498</v>
       </c>
       <c r="H1521" t="n">
         <v>157823</v>
@@ -44507,7 +44507,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1522" t="n">
-        <v>9.64258575439453</v>
+        <v>9.64258480072021</v>
       </c>
       <c r="H1522" t="n">
         <v>154036</v>
@@ -44565,7 +44565,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1524" t="n">
-        <v>9.9205150604248</v>
+        <v>9.92051410675049</v>
       </c>
       <c r="H1524" t="n">
         <v>123851</v>
@@ -44594,7 +44594,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1525" t="n">
-        <v>9.9127950668335</v>
+        <v>9.91279411315918</v>
       </c>
       <c r="H1525" t="n">
         <v>121880</v>
@@ -44739,7 +44739,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1530" t="n">
-        <v>9.71978759765625</v>
+        <v>9.71978855133057</v>
       </c>
       <c r="H1530" t="n">
         <v>157471</v>
@@ -44768,7 +44768,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1531" t="n">
-        <v>9.54994201660156</v>
+        <v>9.54994297027588</v>
       </c>
       <c r="H1531" t="n">
         <v>137558</v>
@@ -44942,7 +44942,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1537" t="n">
-        <v>9.61170482635498</v>
+        <v>9.61170387268066</v>
       </c>
       <c r="H1537" t="n">
         <v>191883</v>
@@ -45000,7 +45000,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1539" t="n">
-        <v>9.34149646759033</v>
+        <v>9.34149551391602</v>
       </c>
       <c r="H1539" t="n">
         <v>162896</v>
@@ -45029,7 +45029,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1540" t="n">
-        <v>9.64258575439453</v>
+        <v>9.64258480072021</v>
       </c>
       <c r="H1540" t="n">
         <v>178357</v>
@@ -45087,7 +45087,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1542" t="n">
-        <v>9.04040718078613</v>
+        <v>9.04040622711182</v>
       </c>
       <c r="H1542" t="n">
         <v>215965</v>
@@ -45261,7 +45261,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1548" t="n">
-        <v>9.71978759765625</v>
+        <v>9.71978855133057</v>
       </c>
       <c r="H1548" t="n">
         <v>360949</v>
@@ -45290,7 +45290,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1549" t="n">
-        <v>9.71978759765625</v>
+        <v>9.71978855133057</v>
       </c>
       <c r="H1549" t="n">
         <v>482932</v>
@@ -45522,7 +45522,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>9.03268623352051</v>
+        <v>9.03268718719482</v>
       </c>
       <c r="H1557" t="n">
         <v>395628</v>
@@ -45667,7 +45667,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1562" t="n">
-        <v>8.60035228729248</v>
+        <v>8.6003532409668</v>
       </c>
       <c r="H1562" t="n">
         <v>249020</v>
@@ -45812,7 +45812,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1567" t="n">
-        <v>8.60807132720947</v>
+        <v>8.60807228088379</v>
       </c>
       <c r="H1567" t="n">
         <v>142978</v>
@@ -45928,7 +45928,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.25703001022339</v>
+        <v>7.25702953338623</v>
       </c>
       <c r="H1571" t="n">
         <v>300725</v>
@@ -45957,7 +45957,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1572" t="n">
-        <v>6.82469654083252</v>
+        <v>6.82469606399536</v>
       </c>
       <c r="H1572" t="n">
         <v>388423</v>
@@ -46044,7 +46044,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1575" t="n">
-        <v>6.87873792648315</v>
+        <v>6.878737449646</v>
       </c>
       <c r="H1575" t="n">
         <v>351634</v>
@@ -46160,7 +46160,7 @@
         <v>9.5</v>
       </c>
       <c r="G1579" t="n">
-        <v>7.33423233032227</v>
+        <v>7.33423137664795</v>
       </c>
       <c r="H1579" t="n">
         <v>470457</v>
@@ -46363,7 +46363,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.53881978988647</v>
+        <v>7.53881883621216</v>
       </c>
       <c r="H1586" t="n">
         <v>148850</v>
@@ -46450,7 +46450,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.70866394042969</v>
+        <v>7.70866298675537</v>
       </c>
       <c r="H1589" t="n">
         <v>87262</v>
@@ -46682,7 +46682,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.39213371276855</v>
+        <v>7.39213466644287</v>
       </c>
       <c r="H1597" t="n">
         <v>119048</v>
@@ -46711,7 +46711,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.30721092224121</v>
+        <v>7.30721187591553</v>
       </c>
       <c r="H1598" t="n">
         <v>68013</v>
@@ -46740,7 +46740,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1599" t="n">
-        <v>7.38441324234009</v>
+        <v>7.3844141960144</v>
       </c>
       <c r="H1599" t="n">
         <v>131459</v>
@@ -46943,7 +46943,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1606" t="n">
-        <v>6.8621621131897</v>
+        <v>6.86216259002686</v>
       </c>
       <c r="H1606" t="n">
         <v>382220</v>
@@ -47001,7 +47001,7 @@
         <v>8.71500015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.11949396133423</v>
+        <v>7.11949348449707</v>
       </c>
       <c r="H1608" t="n">
         <v>262831</v>
@@ -47146,7 +47146,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1613" t="n">
-        <v>6.8621621131897</v>
+        <v>6.86216259002686</v>
       </c>
       <c r="H1613" t="n">
         <v>157913</v>
@@ -47320,7 +47320,7 @@
         <v>8.25</v>
       </c>
       <c r="G1619" t="n">
-        <v>6.7396240234375</v>
+        <v>6.73962354660034</v>
       </c>
       <c r="H1619" t="n">
         <v>200946</v>
@@ -47378,7 +47378,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1621" t="n">
-        <v>6.82131719589233</v>
+        <v>6.82131671905518</v>
       </c>
       <c r="H1621" t="n">
         <v>171424</v>
@@ -47523,7 +47523,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1626" t="n">
-        <v>6.08200025558472</v>
+        <v>6.08199977874756</v>
       </c>
       <c r="H1626" t="n">
         <v>412884</v>
@@ -47552,7 +47552,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1627" t="n">
-        <v>6.2004542350769</v>
+        <v>6.20045471191406</v>
       </c>
       <c r="H1627" t="n">
         <v>229989</v>
@@ -47639,7 +47639,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G1630" t="n">
-        <v>6.62933874130249</v>
+        <v>6.62933921813965</v>
       </c>
       <c r="H1630" t="n">
         <v>230256</v>
@@ -47755,7 +47755,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1634" t="n">
-        <v>6.43736219406128</v>
+        <v>6.43736171722412</v>
       </c>
       <c r="H1634" t="n">
         <v>68806</v>
@@ -47784,7 +47784,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1635" t="n">
-        <v>6.63342332839966</v>
+        <v>6.63342380523682</v>
       </c>
       <c r="H1635" t="n">
         <v>78913</v>
@@ -47842,7 +47842,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1637" t="n">
-        <v>6.52722358703613</v>
+        <v>6.52722311019897</v>
       </c>
       <c r="H1637" t="n">
         <v>107001</v>
@@ -47871,7 +47871,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1638" t="n">
-        <v>6.32299280166626</v>
+        <v>6.3229923248291</v>
       </c>
       <c r="H1638" t="n">
         <v>157553</v>
@@ -47900,7 +47900,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1639" t="n">
-        <v>6.00439262390137</v>
+        <v>6.00439214706421</v>
       </c>
       <c r="H1639" t="n">
         <v>279915</v>
@@ -47929,7 +47929,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1640" t="n">
-        <v>6.00847721099854</v>
+        <v>6.00847673416138</v>
       </c>
       <c r="H1640" t="n">
         <v>289133</v>
@@ -48016,7 +48016,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1643" t="n">
-        <v>6.00847721099854</v>
+        <v>6.00847673416138</v>
       </c>
       <c r="H1643" t="n">
         <v>166032</v>
@@ -48045,7 +48045,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1644" t="n">
-        <v>6.08200025558472</v>
+        <v>6.08199977874756</v>
       </c>
       <c r="H1644" t="n">
         <v>97964</v>
@@ -48132,7 +48132,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1647" t="n">
-        <v>5.99622344970703</v>
+        <v>5.99622297286987</v>
       </c>
       <c r="H1647" t="n">
         <v>78300</v>
@@ -48248,7 +48248,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1651" t="n">
-        <v>5.97988414764404</v>
+        <v>5.9798846244812</v>
       </c>
       <c r="H1651" t="n">
         <v>60691</v>
@@ -48422,7 +48422,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G1657" t="n">
-        <v>5.49381494522095</v>
+        <v>5.49381446838379</v>
       </c>
       <c r="H1657" t="n">
         <v>106623</v>
@@ -48538,7 +48538,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1661" t="n">
-        <v>5.726637840271</v>
+        <v>5.72663831710815</v>
       </c>
       <c r="H1661" t="n">
         <v>76329</v>
@@ -48683,7 +48683,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.65311479568481</v>
+        <v>5.65311527252197</v>
       </c>
       <c r="H1666" t="n">
         <v>82525</v>
@@ -48886,7 +48886,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.57959222793579</v>
+        <v>5.57959175109863</v>
       </c>
       <c r="H1673" t="n">
         <v>200936</v>
@@ -49002,7 +49002,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.73072242736816</v>
+        <v>5.73072290420532</v>
       </c>
       <c r="H1677" t="n">
         <v>90100</v>
@@ -49031,7 +49031,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.81649923324585</v>
+        <v>5.81649971008301</v>
       </c>
       <c r="H1678" t="n">
         <v>109309</v>
@@ -49147,7 +49147,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1682" t="n">
-        <v>5.726637840271</v>
+        <v>5.72663831710815</v>
       </c>
       <c r="H1682" t="n">
         <v>125768</v>
@@ -49234,7 +49234,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1685" t="n">
-        <v>5.99622344970703</v>
+        <v>5.99622297286987</v>
       </c>
       <c r="H1685" t="n">
         <v>182349</v>
@@ -49669,7 +49669,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.90971374511719</v>
+        <v>4.90971422195435</v>
       </c>
       <c r="H1700" t="n">
         <v>305560</v>
@@ -49698,7 +49698,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G1701" t="n">
-        <v>4.832106590271</v>
+        <v>4.83210611343384</v>
       </c>
       <c r="H1701" t="n">
         <v>122503</v>
@@ -49727,7 +49727,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1702" t="n">
-        <v>4.94239139556885</v>
+        <v>4.94239091873169</v>
       </c>
       <c r="H1702" t="n">
         <v>176681</v>
@@ -49756,7 +49756,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1703" t="n">
-        <v>5.07309865951538</v>
+        <v>5.07309913635254</v>
       </c>
       <c r="H1703" t="n">
         <v>144689</v>
@@ -49930,7 +49930,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1709" t="n">
-        <v>4.89337491989136</v>
+        <v>4.89337539672852</v>
       </c>
       <c r="H1709" t="n">
         <v>266573</v>
@@ -49959,7 +49959,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.94647550582886</v>
+        <v>4.9464750289917</v>
       </c>
       <c r="H1710" t="n">
         <v>146350</v>
@@ -50046,7 +50046,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.90562915802002</v>
+        <v>4.90562963485718</v>
       </c>
       <c r="H1713" t="n">
         <v>152880</v>
@@ -50104,7 +50104,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G1715" t="n">
-        <v>4.90562915802002</v>
+        <v>4.90562963485718</v>
       </c>
       <c r="H1715" t="n">
         <v>117935</v>
@@ -50162,7 +50162,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G1717" t="n">
-        <v>4.90562915802002</v>
+        <v>4.90562963485718</v>
       </c>
       <c r="H1717" t="n">
         <v>88039</v>
@@ -50249,7 +50249,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.26099157333374</v>
+        <v>5.26099109649658</v>
       </c>
       <c r="H1720" t="n">
         <v>112619</v>
@@ -50278,7 +50278,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.13845252990723</v>
+        <v>5.13845300674438</v>
       </c>
       <c r="H1721" t="n">
         <v>68792</v>
@@ -50336,7 +50336,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G1723" t="n">
-        <v>4.84844446182251</v>
+        <v>4.84844493865967</v>
       </c>
       <c r="H1723" t="n">
         <v>174837</v>
@@ -50568,7 +50568,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>5.16704511642456</v>
+        <v>5.1670446395874</v>
       </c>
       <c r="H1731" t="n">
         <v>105386</v>
@@ -50597,7 +50597,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.24873781204224</v>
+        <v>5.24873733520508</v>
       </c>
       <c r="H1732" t="n">
         <v>116489</v>
@@ -50655,7 +50655,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.45705270767212</v>
+        <v>5.45705318450928</v>
       </c>
       <c r="H1734" t="n">
         <v>97393</v>
@@ -50742,7 +50742,7 @@
         <v>6.90500020980835</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.64086103439331</v>
+        <v>5.64086151123047</v>
       </c>
       <c r="H1737" t="n">
         <v>172699</v>
@@ -50829,7 +50829,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1740" t="n">
-        <v>5.48973035812378</v>
+        <v>5.48972988128662</v>
       </c>
       <c r="H1740" t="n">
         <v>57839</v>
@@ -50887,7 +50887,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G1742" t="n">
-        <v>5.48156070709229</v>
+        <v>5.48156118392944</v>
       </c>
       <c r="H1742" t="n">
         <v>96331</v>
@@ -50974,7 +50974,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>5.84917688369751</v>
+        <v>5.84917640686035</v>
       </c>
       <c r="H1745" t="n">
         <v>101722</v>
@@ -51003,7 +51003,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G1746" t="n">
-        <v>5.79607629776001</v>
+        <v>5.79607677459717</v>
       </c>
       <c r="H1746" t="n">
         <v>99799</v>
@@ -51032,7 +51032,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1747" t="n">
-        <v>5.89819192886353</v>
+        <v>5.89819240570068</v>
       </c>
       <c r="H1747" t="n">
         <v>325146</v>
@@ -51177,7 +51177,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1752" t="n">
-        <v>5.81649923324585</v>
+        <v>5.81649971008301</v>
       </c>
       <c r="H1752" t="n">
         <v>194799</v>
@@ -51206,7 +51206,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G1753" t="n">
-        <v>5.91044616699219</v>
+        <v>5.91044569015503</v>
       </c>
       <c r="H1753" t="n">
         <v>105152</v>
@@ -51264,7 +51264,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G1755" t="n">
-        <v>5.81241464614868</v>
+        <v>5.81241512298584</v>
       </c>
       <c r="H1755" t="n">
         <v>110488</v>
@@ -51409,7 +51409,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G1760" t="n">
-        <v>5.73889207839966</v>
+        <v>5.73889255523682</v>
       </c>
       <c r="H1760" t="n">
         <v>102736</v>
@@ -51525,7 +51525,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1764" t="n">
-        <v>5.726637840271</v>
+        <v>5.72663831710815</v>
       </c>
       <c r="H1764" t="n">
         <v>92720</v>
@@ -51670,7 +51670,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1769" t="n">
-        <v>5.50606870651245</v>
+        <v>5.50606822967529</v>
       </c>
       <c r="H1769" t="n">
         <v>130870</v>
@@ -51873,7 +51873,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1776" t="n">
-        <v>5.48973035812378</v>
+        <v>5.48972988128662</v>
       </c>
       <c r="H1776" t="n">
         <v>54048</v>
@@ -51931,7 +51931,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1778" t="n">
-        <v>5.50606870651245</v>
+        <v>5.50606822967529</v>
       </c>
       <c r="H1778" t="n">
         <v>95547</v>
@@ -52018,7 +52018,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1781" t="n">
-        <v>5.57959222793579</v>
+        <v>5.57959175109863</v>
       </c>
       <c r="H1781" t="n">
         <v>63483</v>
@@ -52192,7 +52192,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1787" t="n">
-        <v>5.69396114349365</v>
+        <v>5.69396066665649</v>
       </c>
       <c r="H1787" t="n">
         <v>44249</v>
@@ -52279,7 +52279,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1790" t="n">
-        <v>5.99213886260986</v>
+        <v>5.99213838577271</v>
       </c>
       <c r="H1790" t="n">
         <v>144515</v>
@@ -52395,7 +52395,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G1794" t="n">
-        <v>6.04932308197021</v>
+        <v>6.04932355880737</v>
       </c>
       <c r="H1794" t="n">
         <v>127231</v>
@@ -52482,7 +52482,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>5.95537662506104</v>
+        <v>5.95537710189819</v>
       </c>
       <c r="H1797" t="n">
         <v>75583</v>
@@ -52511,7 +52511,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1798" t="n">
-        <v>6.07791566848755</v>
+        <v>6.07791519165039</v>
       </c>
       <c r="H1798" t="n">
         <v>105220</v>
@@ -52627,7 +52627,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1802" t="n">
-        <v>5.95537662506104</v>
+        <v>5.95537710189819</v>
       </c>
       <c r="H1802" t="n">
         <v>89583</v>
@@ -52772,7 +52772,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1807" t="n">
-        <v>6.08200025558472</v>
+        <v>6.08199977874756</v>
       </c>
       <c r="H1807" t="n">
         <v>234464</v>
@@ -52917,7 +52917,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1812" t="n">
-        <v>6.00847721099854</v>
+        <v>6.00847673416138</v>
       </c>
       <c r="H1812" t="n">
         <v>149562</v>
@@ -53033,7 +53033,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G1816" t="n">
-        <v>6.11467695236206</v>
+        <v>6.11467742919922</v>
       </c>
       <c r="H1816" t="n">
         <v>114444</v>
@@ -53062,7 +53062,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>6.04523849487305</v>
+        <v>6.04523897171021</v>
       </c>
       <c r="H1817" t="n">
         <v>74184</v>
@@ -53207,7 +53207,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1822" t="n">
-        <v>5.48973035812378</v>
+        <v>5.48972988128662</v>
       </c>
       <c r="H1822" t="n">
         <v>200149</v>
@@ -53294,7 +53294,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1825" t="n">
-        <v>5.91453075408936</v>
+        <v>5.9145302772522</v>
       </c>
       <c r="H1825" t="n">
         <v>167154</v>
@@ -53323,7 +53323,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G1826" t="n">
-        <v>5.89002275466919</v>
+        <v>5.89002323150635</v>
       </c>
       <c r="H1826" t="n">
         <v>102785</v>
@@ -53352,7 +53352,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1827" t="n">
-        <v>5.97171497344971</v>
+        <v>5.97171545028687</v>
       </c>
       <c r="H1827" t="n">
         <v>140010</v>
@@ -53410,7 +53410,7 @@
         <v>7.25</v>
       </c>
       <c r="G1829" t="n">
-        <v>5.92269992828369</v>
+        <v>5.92269945144653</v>
       </c>
       <c r="H1829" t="n">
         <v>217078</v>
@@ -53497,7 +53497,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1832" t="n">
-        <v>6.18411540985107</v>
+        <v>6.18411588668823</v>
       </c>
       <c r="H1832" t="n">
         <v>238977</v>
@@ -53613,7 +53613,7 @@
         <v>8.25</v>
       </c>
       <c r="G1836" t="n">
-        <v>6.7396240234375</v>
+        <v>6.73962354660034</v>
       </c>
       <c r="H1836" t="n">
         <v>594012</v>
@@ -53642,7 +53642,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G1837" t="n">
-        <v>6.79272317886353</v>
+        <v>6.79272365570068</v>
       </c>
       <c r="H1837" t="n">
         <v>638134</v>
@@ -53816,7 +53816,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.12357807159424</v>
+        <v>7.1235785484314</v>
       </c>
       <c r="H1843" t="n">
         <v>171034</v>
@@ -53845,7 +53845,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.20118570327759</v>
+        <v>7.20118522644043</v>
       </c>
       <c r="H1844" t="n">
         <v>235336</v>
@@ -53874,7 +53874,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.3033013343811</v>
+        <v>7.30330085754395</v>
       </c>
       <c r="H1845" t="n">
         <v>214240</v>
@@ -53932,7 +53932,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.53204154968262</v>
+        <v>7.5320405960083</v>
       </c>
       <c r="H1847" t="n">
         <v>344043</v>
@@ -53990,7 +53990,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.43400955200195</v>
+        <v>7.43401050567627</v>
       </c>
       <c r="H1849" t="n">
         <v>193478</v>
@@ -54106,7 +54106,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1853" t="n">
-        <v>7.25428581237793</v>
+        <v>7.25428676605225</v>
       </c>
       <c r="H1853" t="n">
         <v>219709</v>
@@ -54135,7 +54135,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1854" t="n">
-        <v>7.19710159301758</v>
+        <v>7.19710206985474</v>
       </c>
       <c r="H1854" t="n">
         <v>197744</v>
@@ -54164,7 +54164,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1855" t="n">
-        <v>7.22160959243774</v>
+        <v>7.22160911560059</v>
       </c>
       <c r="H1855" t="n">
         <v>243336</v>
@@ -54193,7 +54193,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1856" t="n">
-        <v>7.22160959243774</v>
+        <v>7.22160911560059</v>
       </c>
       <c r="H1856" t="n">
         <v>114739</v>
@@ -54222,7 +54222,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G1857" t="n">
-        <v>7.20118570327759</v>
+        <v>7.20118522644043</v>
       </c>
       <c r="H1857" t="n">
         <v>144426</v>
@@ -80067,6 +80067,35 @@
         <v>71135</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>7.94999980926514</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>7.82499980926514</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>7.82499980926514</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>50992</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.44732332229614</v>
+        <v>5.4473237991333</v>
       </c>
       <c r="H2" t="n">
         <v>113188</v>
@@ -456,7 +456,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G3" t="n">
-        <v>5.55361318588257</v>
+        <v>5.55361270904541</v>
       </c>
       <c r="H3" t="n">
         <v>66887</v>
@@ -485,7 +485,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G4" t="n">
-        <v>5.38089370727539</v>
+        <v>5.38089418411255</v>
       </c>
       <c r="H4" t="n">
         <v>67853</v>
@@ -572,7 +572,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G7" t="n">
-        <v>5.21481609344482</v>
+        <v>5.21481657028198</v>
       </c>
       <c r="H7" t="n">
         <v>108677</v>
@@ -601,7 +601,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>5.29453277587891</v>
+        <v>5.29453229904175</v>
       </c>
       <c r="H8" t="n">
         <v>216037</v>
@@ -630,7 +630,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>5.3310694694519</v>
+        <v>5.33106994628906</v>
       </c>
       <c r="H9" t="n">
         <v>49371</v>
@@ -688,7 +688,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>4.94244956970215</v>
+        <v>4.94245004653931</v>
       </c>
       <c r="H11" t="n">
         <v>159704</v>
@@ -746,7 +746,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>4.84612512588501</v>
+        <v>4.84612560272217</v>
       </c>
       <c r="H13" t="n">
         <v>91026</v>
@@ -833,7 +833,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>4.82951736450195</v>
+        <v>4.82951784133911</v>
       </c>
       <c r="H16" t="n">
         <v>117197</v>
@@ -862,7 +862,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>4.82951736450195</v>
+        <v>4.82951784133911</v>
       </c>
       <c r="H17" t="n">
         <v>66239</v>
@@ -891,7 +891,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>4.88598394393921</v>
+        <v>4.88598346710205</v>
       </c>
       <c r="H18" t="n">
         <v>66869</v>
@@ -949,7 +949,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>4.91587829589844</v>
+        <v>4.91587734222412</v>
       </c>
       <c r="H20" t="n">
         <v>109639</v>
@@ -1007,7 +1007,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>4.97234439849854</v>
+        <v>4.97234392166138</v>
       </c>
       <c r="H22" t="n">
         <v>54344</v>
@@ -1036,7 +1036,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>4.88598394393921</v>
+        <v>4.88598346710205</v>
       </c>
       <c r="H23" t="n">
         <v>81429</v>
@@ -1094,7 +1094,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>4.93248510360718</v>
+        <v>4.93248462677002</v>
       </c>
       <c r="H25" t="n">
         <v>117119</v>
@@ -1123,7 +1123,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G26" t="n">
-        <v>4.97898626327515</v>
+        <v>4.97898721694946</v>
       </c>
       <c r="H26" t="n">
         <v>142513</v>
@@ -1239,7 +1239,7 @@
         <v>6.75</v>
       </c>
       <c r="G30" t="n">
-        <v>4.48407793045044</v>
+        <v>4.48407745361328</v>
       </c>
       <c r="H30" t="n">
         <v>162247</v>
@@ -1268,7 +1268,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>4.62690305709839</v>
+        <v>4.62690401077271</v>
       </c>
       <c r="H31" t="n">
         <v>118549</v>
@@ -1384,7 +1384,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G35" t="n">
-        <v>5.19488668441772</v>
+        <v>5.19488716125488</v>
       </c>
       <c r="H35" t="n">
         <v>145821</v>
@@ -1413,7 +1413,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G36" t="n">
-        <v>5.02881050109863</v>
+        <v>5.02880954742432</v>
       </c>
       <c r="H36" t="n">
         <v>65011</v>
@@ -1442,7 +1442,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>5.21481609344482</v>
+        <v>5.21481657028198</v>
       </c>
       <c r="H37" t="n">
         <v>79314</v>
@@ -1471,7 +1471,7 @@
         <v>7.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.02548837661743</v>
+        <v>5.02548885345459</v>
       </c>
       <c r="H38" t="n">
         <v>81136</v>
@@ -1558,7 +1558,7 @@
         <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>5.31446218490601</v>
+        <v>5.31446170806885</v>
       </c>
       <c r="H41" t="n">
         <v>66693</v>
@@ -1616,7 +1616,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G43" t="n">
-        <v>5.69311761856079</v>
+        <v>5.69311714172363</v>
       </c>
       <c r="H43" t="n">
         <v>209250</v>
@@ -1674,7 +1674,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>5.53368425369263</v>
+        <v>5.53368377685547</v>
       </c>
       <c r="H45" t="n">
         <v>125352</v>
@@ -1703,7 +1703,7 @@
         <v>8.6850004196167</v>
       </c>
       <c r="G46" t="n">
-        <v>5.76951313018799</v>
+        <v>5.7695140838623</v>
       </c>
       <c r="H46" t="n">
         <v>141716</v>
@@ -1761,7 +1761,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>5.72633218765259</v>
+        <v>5.72633361816406</v>
       </c>
       <c r="H48" t="n">
         <v>97982</v>
@@ -1790,7 +1790,7 @@
         <v>8.5</v>
       </c>
       <c r="G49" t="n">
-        <v>5.64661645889282</v>
+        <v>5.64661550521851</v>
       </c>
       <c r="H49" t="n">
         <v>71691</v>
@@ -1819,7 +1819,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>5.35432147979736</v>
+        <v>5.35432052612305</v>
       </c>
       <c r="H50" t="n">
         <v>105600</v>
@@ -1848,7 +1848,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G51" t="n">
-        <v>5.387535572052</v>
+        <v>5.38753604888916</v>
       </c>
       <c r="H51" t="n">
         <v>191706</v>
@@ -1906,7 +1906,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>5.45396709442139</v>
+        <v>5.45396661758423</v>
       </c>
       <c r="H53" t="n">
         <v>56712</v>
@@ -1935,7 +1935,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>5.44732332229614</v>
+        <v>5.4473237991333</v>
       </c>
       <c r="H54" t="n">
         <v>43227</v>
@@ -1964,7 +1964,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>5.39417934417725</v>
+        <v>5.39417886734009</v>
       </c>
       <c r="H55" t="n">
         <v>67532</v>
@@ -1993,7 +1993,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.44732332229614</v>
+        <v>5.4473237991333</v>
       </c>
       <c r="H56" t="n">
         <v>148456</v>
@@ -2022,7 +2022,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G57" t="n">
-        <v>5.38421392440796</v>
+        <v>5.38421440124512</v>
       </c>
       <c r="H57" t="n">
         <v>103959</v>
@@ -2051,7 +2051,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>5.41410875320435</v>
+        <v>5.41410827636719</v>
       </c>
       <c r="H58" t="n">
         <v>147032</v>
@@ -2080,7 +2080,7 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>5.31446218490601</v>
+        <v>5.31446170806885</v>
       </c>
       <c r="H59" t="n">
         <v>81757</v>
@@ -2254,7 +2254,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.26796054840088</v>
+        <v>5.26796007156372</v>
       </c>
       <c r="H65" t="n">
         <v>87527</v>
@@ -2283,7 +2283,7 @@
         <v>7.5</v>
       </c>
       <c r="G66" t="n">
-        <v>4.98230886459351</v>
+        <v>4.98230791091919</v>
       </c>
       <c r="H66" t="n">
         <v>59642</v>
@@ -2341,7 +2341,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G68" t="n">
-        <v>5.01220178604126</v>
+        <v>5.01220273971558</v>
       </c>
       <c r="H68" t="n">
         <v>65134</v>
@@ -2428,7 +2428,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>5.08859777450562</v>
+        <v>5.0885968208313</v>
       </c>
       <c r="H71" t="n">
         <v>44738</v>
@@ -2602,7 +2602,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>5.04873895645142</v>
+        <v>5.04873943328857</v>
       </c>
       <c r="H77" t="n">
         <v>29830</v>
@@ -2689,7 +2689,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G80" t="n">
-        <v>4.98895072937012</v>
+        <v>4.98895215988159</v>
       </c>
       <c r="H80" t="n">
         <v>25738</v>
@@ -2718,7 +2718,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>4.95905780792236</v>
+        <v>4.95905733108521</v>
       </c>
       <c r="H81" t="n">
         <v>101223</v>
@@ -2747,7 +2747,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>5.05538272857666</v>
+        <v>5.0553822517395</v>
       </c>
       <c r="H82" t="n">
         <v>36158</v>
@@ -2776,7 +2776,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.20152997970581</v>
+        <v>5.20153045654297</v>
       </c>
       <c r="H83" t="n">
         <v>54605</v>
@@ -2834,7 +2834,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>5.11184930801392</v>
+        <v>5.1118483543396</v>
       </c>
       <c r="H85" t="n">
         <v>15689</v>
@@ -2921,7 +2921,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.0719895362854</v>
+        <v>5.07199001312256</v>
       </c>
       <c r="H88" t="n">
         <v>6172</v>
@@ -3008,7 +3008,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G91" t="n">
-        <v>5.53747749328613</v>
+        <v>5.53747797012329</v>
       </c>
       <c r="H91" t="n">
         <v>119812</v>
@@ -3037,7 +3037,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G92" t="n">
-        <v>5.54763174057007</v>
+        <v>5.54763126373291</v>
       </c>
       <c r="H92" t="n">
         <v>108705</v>
@@ -3066,7 +3066,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G93" t="n">
-        <v>5.42916488647461</v>
+        <v>5.42916536331177</v>
       </c>
       <c r="H93" t="n">
         <v>60550</v>
@@ -3095,7 +3095,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>5.52393770217896</v>
+        <v>5.52393865585327</v>
       </c>
       <c r="H94" t="n">
         <v>43648</v>
@@ -3153,7 +3153,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>4.66759300231934</v>
+        <v>4.66759252548218</v>
       </c>
       <c r="H96" t="n">
         <v>383206</v>
@@ -3240,7 +3240,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>4.63712978363037</v>
+        <v>4.63712882995605</v>
       </c>
       <c r="H99" t="n">
         <v>136516</v>
@@ -3269,7 +3269,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>4.43404388427734</v>
+        <v>4.4340443611145</v>
       </c>
       <c r="H100" t="n">
         <v>87516</v>
@@ -3327,7 +3327,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G102" t="n">
-        <v>4.42727375030518</v>
+        <v>4.42727470397949</v>
       </c>
       <c r="H102" t="n">
         <v>149214</v>
@@ -3385,7 +3385,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G104" t="n">
-        <v>4.30542230606079</v>
+        <v>4.30542278289795</v>
       </c>
       <c r="H104" t="n">
         <v>179465</v>
@@ -3414,7 +3414,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.44758319854736</v>
+        <v>4.44758272171021</v>
       </c>
       <c r="H105" t="n">
         <v>157820</v>
@@ -3443,7 +3443,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G106" t="n">
-        <v>4.49496936798096</v>
+        <v>4.4949688911438</v>
       </c>
       <c r="H106" t="n">
         <v>258125</v>
@@ -3472,7 +3472,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>4.34942436218262</v>
+        <v>4.34942531585693</v>
       </c>
       <c r="H107" t="n">
         <v>210950</v>
@@ -3501,7 +3501,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>4.29865312576294</v>
+        <v>4.29865264892578</v>
       </c>
       <c r="H108" t="n">
         <v>89317</v>
@@ -3588,7 +3588,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>4.2478814125061</v>
+        <v>4.24788188934326</v>
       </c>
       <c r="H111" t="n">
         <v>89664</v>
@@ -3617,7 +3617,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G112" t="n">
-        <v>4.15649223327637</v>
+        <v>4.15649318695068</v>
       </c>
       <c r="H112" t="n">
         <v>139833</v>
@@ -3646,7 +3646,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>4.04818058013916</v>
+        <v>4.048180103302</v>
       </c>
       <c r="H113" t="n">
         <v>122772</v>
@@ -3733,7 +3733,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G116" t="n">
-        <v>3.87217283248901</v>
+        <v>3.87217259407043</v>
       </c>
       <c r="H116" t="n">
         <v>159201</v>
@@ -3762,7 +3762,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>3.865403175354</v>
+        <v>3.86540293693542</v>
       </c>
       <c r="H117" t="n">
         <v>92272</v>
@@ -3791,7 +3791,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G118" t="n">
-        <v>3.79770731925964</v>
+        <v>3.79770755767822</v>
       </c>
       <c r="H118" t="n">
         <v>144969</v>
@@ -3820,7 +3820,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>4.01094818115234</v>
+        <v>4.01094770431519</v>
       </c>
       <c r="H119" t="n">
         <v>162964</v>
@@ -3849,7 +3849,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.93648362159729</v>
+        <v>3.93648314476013</v>
       </c>
       <c r="H120" t="n">
         <v>167668</v>
@@ -3878,7 +3878,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.96356081962585</v>
+        <v>3.96356129646301</v>
       </c>
       <c r="H121" t="n">
         <v>108290</v>
@@ -3965,7 +3965,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>3.76386022567749</v>
+        <v>3.76385998725891</v>
       </c>
       <c r="H124" t="n">
         <v>198048</v>
@@ -4023,7 +4023,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.40169048309326</v>
+        <v>3.40169072151184</v>
       </c>
       <c r="H126" t="n">
         <v>297033</v>
@@ -4052,7 +4052,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>3.47615528106689</v>
+        <v>3.47615504264832</v>
       </c>
       <c r="H127" t="n">
         <v>184937</v>
@@ -4081,7 +4081,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G128" t="n">
-        <v>3.48969459533691</v>
+        <v>3.48969388008118</v>
       </c>
       <c r="H128" t="n">
         <v>107107</v>
@@ -4110,7 +4110,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G129" t="n">
-        <v>3.48969459533691</v>
+        <v>3.48969388008118</v>
       </c>
       <c r="H129" t="n">
         <v>134491</v>
@@ -4197,7 +4197,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>3.15731000900269</v>
+        <v>3.15731024742126</v>
       </c>
       <c r="H132" t="n">
         <v>707649</v>
@@ -4255,7 +4255,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G134" t="n">
-        <v>3.29540848731995</v>
+        <v>3.29540872573853</v>
       </c>
       <c r="H134" t="n">
         <v>189271</v>
@@ -4284,7 +4284,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G135" t="n">
-        <v>3.32519435882568</v>
+        <v>3.32519459724426</v>
       </c>
       <c r="H135" t="n">
         <v>50898</v>
@@ -4313,7 +4313,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.58785247802734</v>
+        <v>3.58785223960876</v>
       </c>
       <c r="H136" t="n">
         <v>115636</v>
@@ -4342,7 +4342,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G137" t="n">
-        <v>3.47615528106689</v>
+        <v>3.47615504264832</v>
       </c>
       <c r="H137" t="n">
         <v>87648</v>
@@ -4371,7 +4371,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49984860420227</v>
+        <v>3.49984836578369</v>
       </c>
       <c r="H138" t="n">
         <v>69291</v>
@@ -4400,7 +4400,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.48630881309509</v>
+        <v>3.48630952835083</v>
       </c>
       <c r="H139" t="n">
         <v>109570</v>
@@ -4429,7 +4429,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>3.5709285736084</v>
+        <v>3.57092881202698</v>
       </c>
       <c r="H140" t="n">
         <v>95057</v>
@@ -4487,7 +4487,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G142" t="n">
-        <v>3.57431364059448</v>
+        <v>3.57431316375732</v>
       </c>
       <c r="H142" t="n">
         <v>38892</v>
@@ -4516,7 +4516,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>3.60477542877197</v>
+        <v>3.60477638244629</v>
       </c>
       <c r="H143" t="n">
         <v>103724</v>
@@ -4545,7 +4545,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G144" t="n">
-        <v>3.59462118148804</v>
+        <v>3.5946216583252</v>
       </c>
       <c r="H144" t="n">
         <v>67888</v>
@@ -4574,7 +4574,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G145" t="n">
-        <v>3.63185405731201</v>
+        <v>3.63185453414917</v>
       </c>
       <c r="H145" t="n">
         <v>19997</v>
@@ -4603,7 +4603,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.61154532432556</v>
+        <v>3.61154580116272</v>
       </c>
       <c r="H146" t="n">
         <v>52589</v>
@@ -4632,7 +4632,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.79093837738037</v>
+        <v>3.79093861579895</v>
       </c>
       <c r="H147" t="n">
         <v>91695</v>
@@ -4661,7 +4661,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>3.70293426513672</v>
+        <v>3.70293378829956</v>
       </c>
       <c r="H148" t="n">
         <v>67162</v>
@@ -4690,7 +4690,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>3.78078436851501</v>
+        <v>3.78078413009644</v>
       </c>
       <c r="H149" t="n">
         <v>32010</v>
@@ -4719,7 +4719,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G150" t="n">
-        <v>3.71308851242065</v>
+        <v>3.71308827400208</v>
       </c>
       <c r="H150" t="n">
         <v>72315</v>
@@ -4777,7 +4777,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G152" t="n">
-        <v>3.56077432632446</v>
+        <v>3.56077456474304</v>
       </c>
       <c r="H152" t="n">
         <v>56391</v>
@@ -4806,7 +4806,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>3.61493039131165</v>
+        <v>3.6149308681488</v>
       </c>
       <c r="H153" t="n">
         <v>30739</v>
@@ -4835,7 +4835,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.67924094200134</v>
+        <v>3.67924118041992</v>
       </c>
       <c r="H154" t="n">
         <v>20938</v>
@@ -4864,7 +4864,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G155" t="n">
-        <v>3.64877796173096</v>
+        <v>3.6487774848938</v>
       </c>
       <c r="H155" t="n">
         <v>28077</v>
@@ -4893,7 +4893,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>3.79093837738037</v>
+        <v>3.79093861579895</v>
       </c>
       <c r="H156" t="n">
         <v>57929</v>
@@ -4922,7 +4922,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>3.79093837738037</v>
+        <v>3.79093861579895</v>
       </c>
       <c r="H157" t="n">
         <v>34686</v>
@@ -4951,7 +4951,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>3.83832430839539</v>
+        <v>3.83832478523254</v>
       </c>
       <c r="H158" t="n">
         <v>13489</v>
@@ -5067,7 +5067,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G162" t="n">
-        <v>3.81124639511108</v>
+        <v>3.81124711036682</v>
       </c>
       <c r="H162" t="n">
         <v>24479</v>
@@ -5096,7 +5096,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G163" t="n">
-        <v>3.81124639511108</v>
+        <v>3.81124711036682</v>
       </c>
       <c r="H163" t="n">
         <v>58927</v>
@@ -5183,7 +5183,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>3.98725414276123</v>
+        <v>3.98725438117981</v>
       </c>
       <c r="H166" t="n">
         <v>125514</v>
@@ -5212,7 +5212,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>3.9534068107605</v>
+        <v>3.95340728759766</v>
       </c>
       <c r="H167" t="n">
         <v>79391</v>
@@ -5357,7 +5357,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G172" t="n">
-        <v>4.02787208557129</v>
+        <v>4.02787160873413</v>
       </c>
       <c r="H172" t="n">
         <v>87862</v>
@@ -5386,7 +5386,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>4.05833435058594</v>
+        <v>4.0583348274231</v>
       </c>
       <c r="H173" t="n">
         <v>31122</v>
@@ -5415,7 +5415,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>3.96356081962585</v>
+        <v>3.96356129646301</v>
       </c>
       <c r="H174" t="n">
         <v>171483</v>
@@ -5444,7 +5444,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>3.93986821174622</v>
+        <v>3.93986773490906</v>
       </c>
       <c r="H175" t="n">
         <v>201408</v>
@@ -5473,7 +5473,7 @@
         <v>6</v>
       </c>
       <c r="G176" t="n">
-        <v>4.06171989440918</v>
+        <v>4.06171941757202</v>
       </c>
       <c r="H176" t="n">
         <v>92361</v>
@@ -5502,7 +5502,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>4.05833435058594</v>
+        <v>4.0583348274231</v>
       </c>
       <c r="H177" t="n">
         <v>34907</v>
@@ -5560,7 +5560,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.98725414276123</v>
+        <v>3.98725438117981</v>
       </c>
       <c r="H179" t="n">
         <v>91126</v>
@@ -5589,7 +5589,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.02787208557129</v>
+        <v>4.02787160873413</v>
       </c>
       <c r="H180" t="n">
         <v>95736</v>
@@ -5618,7 +5618,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G181" t="n">
-        <v>3.96694612503052</v>
+        <v>3.96694588661194</v>
       </c>
       <c r="H181" t="n">
         <v>146337</v>
@@ -5647,7 +5647,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G182" t="n">
-        <v>3.88909673690796</v>
+        <v>3.8890962600708</v>
       </c>
       <c r="H182" t="n">
         <v>145297</v>
@@ -5705,7 +5705,7 @@
         <v>5</v>
       </c>
       <c r="G184" t="n">
-        <v>3.38476634025574</v>
+        <v>3.38476657867432</v>
       </c>
       <c r="H184" t="n">
         <v>271176</v>
@@ -5734,7 +5734,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>3.31707119941711</v>
+        <v>3.31707072257996</v>
       </c>
       <c r="H185" t="n">
         <v>255286</v>
@@ -5792,7 +5792,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G187" t="n">
-        <v>3.28322315216064</v>
+        <v>3.2832236289978</v>
       </c>
       <c r="H187" t="n">
         <v>138480</v>
@@ -5879,7 +5879,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>3.30353236198425</v>
+        <v>3.30353188514709</v>
       </c>
       <c r="H190" t="n">
         <v>156871</v>
@@ -5937,7 +5937,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G192" t="n">
-        <v>3.37122678756714</v>
+        <v>3.3712272644043</v>
       </c>
       <c r="H192" t="n">
         <v>58791</v>
@@ -5966,7 +5966,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G193" t="n">
-        <v>3.34956479072571</v>
+        <v>3.34956455230713</v>
       </c>
       <c r="H193" t="n">
         <v>82212</v>
@@ -5995,7 +5995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>3.49984860420227</v>
+        <v>3.49984836578369</v>
       </c>
       <c r="H194" t="n">
         <v>152264</v>
@@ -6024,7 +6024,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G195" t="n">
-        <v>3.46261644363403</v>
+        <v>3.4626157283783</v>
       </c>
       <c r="H195" t="n">
         <v>36886</v>
@@ -6198,7 +6198,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G201" t="n">
-        <v>4.18357133865356</v>
+        <v>4.18357086181641</v>
       </c>
       <c r="H201" t="n">
         <v>191685</v>
@@ -6256,7 +6256,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>4.24449729919434</v>
+        <v>4.24449682235718</v>
       </c>
       <c r="H203" t="n">
         <v>64155</v>
@@ -6285,7 +6285,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>4.26480579376221</v>
+        <v>4.26480531692505</v>
       </c>
       <c r="H204" t="n">
         <v>104103</v>
@@ -6314,7 +6314,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>4.4408130645752</v>
+        <v>4.44081258773804</v>
       </c>
       <c r="H205" t="n">
         <v>291963</v>
@@ -6343,7 +6343,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>4.46789073944092</v>
+        <v>4.46789121627808</v>
       </c>
       <c r="H206" t="n">
         <v>146224</v>
@@ -6372,7 +6372,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>4.46450662612915</v>
+        <v>4.46450710296631</v>
       </c>
       <c r="H207" t="n">
         <v>103319</v>
@@ -6401,7 +6401,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>4.4408130645752</v>
+        <v>4.44081258773804</v>
       </c>
       <c r="H208" t="n">
         <v>91882</v>
@@ -6430,7 +6430,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>4.4408130645752</v>
+        <v>4.44081258773804</v>
       </c>
       <c r="H209" t="n">
         <v>86447</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>4.46789073944092</v>
+        <v>4.46789121627808</v>
       </c>
       <c r="H210" t="n">
         <v>109334</v>
@@ -6546,7 +6546,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G213" t="n">
-        <v>4.58974313735962</v>
+        <v>4.58974266052246</v>
       </c>
       <c r="H213" t="n">
         <v>124219</v>
@@ -6575,7 +6575,7 @@
         <v>6.75</v>
       </c>
       <c r="G214" t="n">
-        <v>4.56943464279175</v>
+        <v>4.56943416595459</v>
       </c>
       <c r="H214" t="n">
         <v>80845</v>
@@ -6633,7 +6633,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G216" t="n">
-        <v>4.36634874343872</v>
+        <v>4.3663477897644</v>
       </c>
       <c r="H216" t="n">
         <v>167961</v>
@@ -6662,7 +6662,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G217" t="n">
-        <v>4.37988805770874</v>
+        <v>4.37988758087158</v>
       </c>
       <c r="H217" t="n">
         <v>113733</v>
@@ -6691,7 +6691,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>4.30203771591187</v>
+        <v>4.30203819274902</v>
       </c>
       <c r="H218" t="n">
         <v>284256</v>
@@ -6720,7 +6720,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>4.38665771484375</v>
+        <v>4.38665676116943</v>
       </c>
       <c r="H219" t="n">
         <v>126233</v>
@@ -6749,7 +6749,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G220" t="n">
-        <v>4.43404388427734</v>
+        <v>4.4340443611145</v>
       </c>
       <c r="H220" t="n">
         <v>204726</v>
@@ -6778,7 +6778,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G221" t="n">
-        <v>4.4069652557373</v>
+        <v>4.40696620941162</v>
       </c>
       <c r="H221" t="n">
         <v>176630</v>
@@ -6923,7 +6923,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.36634874343872</v>
+        <v>4.3663477897644</v>
       </c>
       <c r="H226" t="n">
         <v>60666</v>
@@ -6952,7 +6952,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.43404388427734</v>
+        <v>4.4340443611145</v>
       </c>
       <c r="H227" t="n">
         <v>73554</v>
@@ -6981,7 +6981,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>4.43404388427734</v>
+        <v>4.4340443611145</v>
       </c>
       <c r="H228" t="n">
         <v>55444</v>
@@ -7010,7 +7010,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>4.35957860946655</v>
+        <v>4.35957908630371</v>
       </c>
       <c r="H229" t="n">
         <v>200260</v>
@@ -7039,7 +7039,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.41035079956055</v>
+        <v>4.41035032272339</v>
       </c>
       <c r="H230" t="n">
         <v>130320</v>
@@ -7155,7 +7155,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G234" t="n">
-        <v>4.29526805877686</v>
+        <v>4.29526853561401</v>
       </c>
       <c r="H234" t="n">
         <v>197038</v>
@@ -7184,7 +7184,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G235" t="n">
-        <v>4.3528094291687</v>
+        <v>4.35280990600586</v>
       </c>
       <c r="H235" t="n">
         <v>100278</v>
@@ -7213,7 +7213,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G236" t="n">
-        <v>4.36634874343872</v>
+        <v>4.3663477897644</v>
       </c>
       <c r="H236" t="n">
         <v>68882</v>
@@ -7242,7 +7242,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G237" t="n">
-        <v>4.24449729919434</v>
+        <v>4.24449682235718</v>
       </c>
       <c r="H237" t="n">
         <v>65977</v>
@@ -7271,7 +7271,7 @@
         <v>6.375</v>
       </c>
       <c r="G238" t="n">
-        <v>4.31557655334473</v>
+        <v>4.31557703018188</v>
       </c>
       <c r="H238" t="n">
         <v>102989</v>
@@ -7329,7 +7329,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G240" t="n">
-        <v>4.46789073944092</v>
+        <v>4.46789121627808</v>
       </c>
       <c r="H240" t="n">
         <v>61992</v>
@@ -7416,7 +7416,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>4.46789073944092</v>
+        <v>4.46789121627808</v>
       </c>
       <c r="H243" t="n">
         <v>65647</v>
@@ -7445,7 +7445,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.48820066452026</v>
+        <v>4.48819971084595</v>
       </c>
       <c r="H244" t="n">
         <v>56395</v>
@@ -7503,7 +7503,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>4.45435190200806</v>
+        <v>4.45435237884521</v>
       </c>
       <c r="H246" t="n">
         <v>58966</v>
@@ -7590,7 +7590,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G249" t="n">
-        <v>4.54912519454956</v>
+        <v>4.54912567138672</v>
       </c>
       <c r="H249" t="n">
         <v>62594</v>
@@ -7648,7 +7648,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>4.85375547409058</v>
+        <v>4.85375499725342</v>
       </c>
       <c r="H251" t="n">
         <v>195110</v>
@@ -7706,7 +7706,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G253" t="n">
-        <v>4.75898170471191</v>
+        <v>4.75898122787476</v>
       </c>
       <c r="H253" t="n">
         <v>40012</v>
@@ -7793,7 +7793,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G256" t="n">
-        <v>4.7217493057251</v>
+        <v>4.72174882888794</v>
       </c>
       <c r="H256" t="n">
         <v>77207</v>
@@ -7822,7 +7822,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.79282903671265</v>
+        <v>4.79282855987549</v>
       </c>
       <c r="H257" t="n">
         <v>58206</v>
@@ -7851,7 +7851,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G258" t="n">
-        <v>4.8639087677002</v>
+        <v>4.86390924453735</v>
       </c>
       <c r="H258" t="n">
         <v>67486</v>
@@ -7880,7 +7880,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G259" t="n">
-        <v>4.8165225982666</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H259" t="n">
         <v>83473</v>
@@ -7909,7 +7909,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G260" t="n">
-        <v>4.78605937957764</v>
+        <v>4.78605985641479</v>
       </c>
       <c r="H260" t="n">
         <v>69615</v>
@@ -7938,7 +7938,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G261" t="n">
-        <v>4.7217493057251</v>
+        <v>4.72174882888794</v>
       </c>
       <c r="H261" t="n">
         <v>118863</v>
@@ -7996,7 +7996,7 @@
         <v>7</v>
       </c>
       <c r="G263" t="n">
-        <v>4.73867273330688</v>
+        <v>4.73867225646973</v>
       </c>
       <c r="H263" t="n">
         <v>75411</v>
@@ -8025,7 +8025,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.7894434928894</v>
+        <v>4.78944444656372</v>
       </c>
       <c r="H264" t="n">
         <v>71071</v>
@@ -8054,7 +8054,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>4.86729383468628</v>
+        <v>4.86729335784912</v>
       </c>
       <c r="H265" t="n">
         <v>82243</v>
@@ -8083,7 +8083,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>4.7894434928894</v>
+        <v>4.78944444656372</v>
       </c>
       <c r="H266" t="n">
         <v>52227</v>
@@ -8112,7 +8112,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>4.84021615982056</v>
+        <v>4.8402156829834</v>
       </c>
       <c r="H267" t="n">
         <v>41796</v>
@@ -8141,7 +8141,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>4.8165225982666</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H268" t="n">
         <v>15823</v>
@@ -8170,7 +8170,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>4.83683013916016</v>
+        <v>4.83683109283447</v>
       </c>
       <c r="H269" t="n">
         <v>40098</v>
@@ -8228,7 +8228,7 @@
         <v>7.125</v>
       </c>
       <c r="G271" t="n">
-        <v>4.82329130172729</v>
+        <v>4.82329225540161</v>
       </c>
       <c r="H271" t="n">
         <v>22605</v>
@@ -8257,7 +8257,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>4.84021615982056</v>
+        <v>4.8402156829834</v>
       </c>
       <c r="H272" t="n">
         <v>25459</v>
@@ -8286,7 +8286,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G273" t="n">
-        <v>4.72851800918579</v>
+        <v>4.72851848602295</v>
       </c>
       <c r="H273" t="n">
         <v>28889</v>
@@ -8402,7 +8402,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G277" t="n">
-        <v>4.8165225982666</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H277" t="n">
         <v>53288</v>
@@ -8431,7 +8431,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65066862106323</v>
+        <v>4.65066909790039</v>
       </c>
       <c r="H278" t="n">
         <v>80211</v>
@@ -8460,7 +8460,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G279" t="n">
-        <v>4.63712978363037</v>
+        <v>4.63712882995605</v>
       </c>
       <c r="H279" t="n">
         <v>115147</v>
@@ -8489,7 +8489,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.65743827819824</v>
+        <v>4.6574387550354</v>
       </c>
       <c r="H280" t="n">
         <v>45461</v>
@@ -8518,7 +8518,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G281" t="n">
-        <v>4.69805574417114</v>
+        <v>4.69805526733398</v>
       </c>
       <c r="H281" t="n">
         <v>48954</v>
@@ -8576,7 +8576,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>4.65066862106323</v>
+        <v>4.65066909790039</v>
       </c>
       <c r="H283" t="n">
         <v>39226</v>
@@ -8605,7 +8605,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>4.65066862106323</v>
+        <v>4.65066909790039</v>
       </c>
       <c r="H284" t="n">
         <v>31328</v>
@@ -8634,7 +8634,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G285" t="n">
-        <v>4.59989786148071</v>
+        <v>4.59989738464355</v>
       </c>
       <c r="H285" t="n">
         <v>152076</v>
@@ -8692,7 +8692,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74205780029297</v>
+        <v>4.74205732345581</v>
       </c>
       <c r="H287" t="n">
         <v>26431</v>
@@ -8721,7 +8721,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>4.79282903671265</v>
+        <v>4.79282855987549</v>
       </c>
       <c r="H288" t="n">
         <v>40804</v>
@@ -8808,7 +8808,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G291" t="n">
-        <v>5.07037973403931</v>
+        <v>5.07037925720215</v>
       </c>
       <c r="H291" t="n">
         <v>225000</v>
@@ -8837,7 +8837,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>5.0229926109314</v>
+        <v>5.02299308776855</v>
       </c>
       <c r="H292" t="n">
         <v>56483</v>
@@ -8866,7 +8866,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G293" t="n">
-        <v>5.06699514389038</v>
+        <v>5.06699562072754</v>
       </c>
       <c r="H293" t="n">
         <v>44482</v>
@@ -8895,7 +8895,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G294" t="n">
-        <v>5.00268459320068</v>
+        <v>5.00268507003784</v>
       </c>
       <c r="H294" t="n">
         <v>22069</v>
@@ -8924,7 +8924,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G295" t="n">
-        <v>4.9992995262146</v>
+        <v>4.99930000305176</v>
       </c>
       <c r="H295" t="n">
         <v>48006</v>
@@ -8953,7 +8953,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G296" t="n">
-        <v>4.97560691833496</v>
+        <v>4.9756064414978</v>
       </c>
       <c r="H296" t="n">
         <v>73571</v>
@@ -9011,7 +9011,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>4.97560691833496</v>
+        <v>4.9756064414978</v>
       </c>
       <c r="H298" t="n">
         <v>67261</v>
@@ -9040,7 +9040,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93160438537598</v>
+        <v>4.93160390853882</v>
       </c>
       <c r="H299" t="n">
         <v>39182</v>
@@ -9069,7 +9069,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G300" t="n">
-        <v>5.05684041976929</v>
+        <v>5.05684089660645</v>
       </c>
       <c r="H300" t="n">
         <v>83204</v>
@@ -9156,7 +9156,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G303" t="n">
-        <v>5.0399169921875</v>
+        <v>5.03991746902466</v>
       </c>
       <c r="H303" t="n">
         <v>64927</v>
@@ -9185,7 +9185,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637815475464</v>
       </c>
       <c r="H304" t="n">
         <v>31519</v>
@@ -9214,7 +9214,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>5.0229926109314</v>
+        <v>5.02299308776855</v>
       </c>
       <c r="H305" t="n">
         <v>157822</v>
@@ -9243,7 +9243,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G306" t="n">
-        <v>5.08391857147217</v>
+        <v>5.08391952514648</v>
       </c>
       <c r="H306" t="n">
         <v>115407</v>
@@ -9272,7 +9272,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G307" t="n">
-        <v>5.07037973403931</v>
+        <v>5.07037925720215</v>
       </c>
       <c r="H307" t="n">
         <v>101547</v>
@@ -9330,7 +9330,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G309" t="n">
-        <v>5.00268459320068</v>
+        <v>5.00268507003784</v>
       </c>
       <c r="H309" t="n">
         <v>46538</v>
@@ -9359,7 +9359,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G310" t="n">
-        <v>5.06699514389038</v>
+        <v>5.06699562072754</v>
       </c>
       <c r="H310" t="n">
         <v>54701</v>
@@ -9417,7 +9417,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.24638748168945</v>
+        <v>5.24638795852661</v>
       </c>
       <c r="H312" t="n">
         <v>141942</v>
@@ -9446,7 +9446,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G313" t="n">
-        <v>5.29377508163452</v>
+        <v>5.29377412796021</v>
       </c>
       <c r="H313" t="n">
         <v>49635</v>
@@ -9533,7 +9533,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G316" t="n">
-        <v>5.37500905990601</v>
+        <v>5.37500953674316</v>
       </c>
       <c r="H316" t="n">
         <v>352796</v>
@@ -9765,7 +9765,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>5.21253967285156</v>
+        <v>5.2125391960144</v>
       </c>
       <c r="H324" t="n">
         <v>117109</v>
@@ -9910,7 +9910,7 @@
         <v>7.56500005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>5.12115097045898</v>
+        <v>5.12115144729614</v>
       </c>
       <c r="H329" t="n">
         <v>147045</v>
@@ -9939,7 +9939,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>5.13807582855225</v>
+        <v>5.13807487487793</v>
       </c>
       <c r="H330" t="n">
         <v>161802</v>
@@ -9968,7 +9968,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.94852781295776</v>
+        <v>4.94852828979492</v>
       </c>
       <c r="H331" t="n">
         <v>123182</v>
@@ -10055,7 +10055,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>4.92483472824097</v>
+        <v>4.92483520507812</v>
       </c>
       <c r="H334" t="n">
         <v>56297</v>
@@ -10113,7 +10113,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>5.13807582855225</v>
+        <v>5.13807487487793</v>
       </c>
       <c r="H336" t="n">
         <v>74359</v>
@@ -10142,7 +10142,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G337" t="n">
-        <v>5.17192316055298</v>
+        <v>5.17192268371582</v>
       </c>
       <c r="H337" t="n">
         <v>58203</v>
@@ -10171,7 +10171,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>5.11099720001221</v>
+        <v>5.11099672317505</v>
       </c>
       <c r="H338" t="n">
         <v>143535</v>
@@ -10200,7 +10200,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.09745788574219</v>
+        <v>5.09745836257935</v>
       </c>
       <c r="H339" t="n">
         <v>96823</v>
@@ -10229,7 +10229,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G340" t="n">
-        <v>5.08391857147217</v>
+        <v>5.08391952514648</v>
       </c>
       <c r="H340" t="n">
         <v>75184</v>
@@ -10258,7 +10258,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G341" t="n">
-        <v>5.09745788574219</v>
+        <v>5.09745836257935</v>
       </c>
       <c r="H341" t="n">
         <v>39402</v>
@@ -10316,7 +10316,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>5.13807582855225</v>
+        <v>5.13807487487793</v>
       </c>
       <c r="H343" t="n">
         <v>63057</v>
@@ -10345,7 +10345,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G344" t="n">
-        <v>5.09068822860718</v>
+        <v>5.09068775177002</v>
       </c>
       <c r="H344" t="n">
         <v>61634</v>
@@ -10374,7 +10374,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.23200130462646</v>
+        <v>5.23200082778931</v>
       </c>
       <c r="H345" t="n">
         <v>74072</v>
@@ -10403,7 +10403,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G346" t="n">
-        <v>5.39054679870605</v>
+        <v>5.3905463218689</v>
       </c>
       <c r="H346" t="n">
         <v>202741</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>5.156174659729</v>
+        <v>5.15617513656616</v>
       </c>
       <c r="H348" t="n">
         <v>77577</v>
@@ -10519,7 +10519,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G350" t="n">
-        <v>4.81840372085571</v>
+        <v>4.81840324401855</v>
       </c>
       <c r="H350" t="n">
         <v>315554</v>
@@ -10548,7 +10548,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>4.71500444412231</v>
+        <v>4.71500396728516</v>
       </c>
       <c r="H351" t="n">
         <v>350968</v>
@@ -10577,7 +10577,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G352" t="n">
-        <v>4.62539196014404</v>
+        <v>4.6253924369812</v>
       </c>
       <c r="H352" t="n">
         <v>133593</v>
@@ -10606,7 +10606,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>4.67709159851074</v>
+        <v>4.67709112167358</v>
       </c>
       <c r="H353" t="n">
         <v>174018</v>
@@ -10635,7 +10635,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>4.72189807891846</v>
+        <v>4.72189855575562</v>
       </c>
       <c r="H354" t="n">
         <v>62590</v>
@@ -10693,7 +10693,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>4.63917875289917</v>
+        <v>4.63917827606201</v>
       </c>
       <c r="H356" t="n">
         <v>106842</v>
@@ -10780,7 +10780,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G359" t="n">
-        <v>4.6184983253479</v>
+        <v>4.61849880218506</v>
       </c>
       <c r="H359" t="n">
         <v>63329</v>
@@ -10838,7 +10838,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G361" t="n">
-        <v>4.43238019943237</v>
+        <v>4.43237972259521</v>
       </c>
       <c r="H361" t="n">
         <v>127010</v>
@@ -10867,7 +10867,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>4.41514682769775</v>
+        <v>4.41514730453491</v>
       </c>
       <c r="H362" t="n">
         <v>118228</v>
@@ -10925,7 +10925,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G364" t="n">
-        <v>4.4461669921875</v>
+        <v>4.44616651535034</v>
       </c>
       <c r="H364" t="n">
         <v>42653</v>
@@ -10954,7 +10954,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>4.36689376831055</v>
+        <v>4.36689424514771</v>
       </c>
       <c r="H365" t="n">
         <v>92594</v>
@@ -10983,7 +10983,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>4.27383470535278</v>
+        <v>4.27383422851562</v>
       </c>
       <c r="H366" t="n">
         <v>59223</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>4.26004838943481</v>
+        <v>4.26004791259766</v>
       </c>
       <c r="H367" t="n">
         <v>48450</v>
@@ -11041,7 +11041,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>4.23936796188354</v>
+        <v>4.23936891555786</v>
       </c>
       <c r="H368" t="n">
         <v>56785</v>
@@ -11099,7 +11099,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G370" t="n">
-        <v>4.37378740310669</v>
+        <v>4.37378692626953</v>
       </c>
       <c r="H370" t="n">
         <v>115367</v>
@@ -11128,7 +11128,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>4.32898139953613</v>
+        <v>4.32898044586182</v>
       </c>
       <c r="H371" t="n">
         <v>89129</v>
@@ -11186,7 +11186,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G373" t="n">
-        <v>4.27728128433228</v>
+        <v>4.27728080749512</v>
       </c>
       <c r="H373" t="n">
         <v>87931</v>
@@ -11215,7 +11215,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>4.17043542861938</v>
+        <v>4.17043590545654</v>
       </c>
       <c r="H374" t="n">
         <v>551406</v>
@@ -11244,7 +11244,7 @@
         <v>6.25</v>
       </c>
       <c r="G375" t="n">
-        <v>4.30830097198486</v>
+        <v>4.30830192565918</v>
       </c>
       <c r="H375" t="n">
         <v>83151</v>
@@ -11331,7 +11331,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>4.23592138290405</v>
+        <v>4.23592185974121</v>
       </c>
       <c r="H378" t="n">
         <v>77420</v>
@@ -11389,7 +11389,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G380" t="n">
-        <v>4.26349496841431</v>
+        <v>4.26349401473999</v>
       </c>
       <c r="H380" t="n">
         <v>44696</v>
@@ -11476,7 +11476,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>4.37378740310669</v>
+        <v>4.37378692626953</v>
       </c>
       <c r="H383" t="n">
         <v>133689</v>
@@ -11534,7 +11534,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>4.51509952545166</v>
+        <v>4.51510000228882</v>
       </c>
       <c r="H385" t="n">
         <v>184215</v>
@@ -11592,7 +11592,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>4.44961309432983</v>
+        <v>4.44961357116699</v>
       </c>
       <c r="H387" t="n">
         <v>59662</v>
@@ -11621,7 +11621,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>4.37723350524902</v>
+        <v>4.37723398208618</v>
       </c>
       <c r="H388" t="n">
         <v>60247</v>
@@ -11650,7 +11650,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G389" t="n">
-        <v>4.32898139953613</v>
+        <v>4.32898044586182</v>
       </c>
       <c r="H389" t="n">
         <v>38008</v>
@@ -11679,7 +11679,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>4.49441957473755</v>
+        <v>4.49442005157471</v>
       </c>
       <c r="H390" t="n">
         <v>149419</v>
@@ -11737,7 +11737,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>4.62883901596069</v>
+        <v>4.62883853912354</v>
       </c>
       <c r="H392" t="n">
         <v>73105</v>
@@ -11795,7 +11795,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G394" t="n">
-        <v>4.61505174636841</v>
+        <v>4.61505222320557</v>
       </c>
       <c r="H394" t="n">
         <v>74456</v>
@@ -11824,7 +11824,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>4.52888679504395</v>
+        <v>4.52888631820679</v>
       </c>
       <c r="H395" t="n">
         <v>77827</v>
@@ -11853,7 +11853,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>4.70811080932617</v>
+        <v>4.70811128616333</v>
       </c>
       <c r="H396" t="n">
         <v>978763</v>
@@ -11911,7 +11911,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>4.62539196014404</v>
+        <v>4.6253924369812</v>
       </c>
       <c r="H398" t="n">
         <v>86308</v>
@@ -11940,7 +11940,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>4.50820589065552</v>
+        <v>4.50820636749268</v>
       </c>
       <c r="H399" t="n">
         <v>56545</v>
@@ -12085,7 +12085,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>4.42548656463623</v>
+        <v>4.42548704147339</v>
       </c>
       <c r="H404" t="n">
         <v>58646</v>
@@ -12143,7 +12143,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>4.50475978851318</v>
+        <v>4.50475931167603</v>
       </c>
       <c r="H406" t="n">
         <v>51611</v>
@@ -12172,7 +12172,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G407" t="n">
-        <v>4.4461669921875</v>
+        <v>4.44616651535034</v>
       </c>
       <c r="H407" t="n">
         <v>69081</v>
@@ -12201,7 +12201,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G408" t="n">
-        <v>4.45995330810547</v>
+        <v>4.45995283126831</v>
       </c>
       <c r="H408" t="n">
         <v>41217</v>
@@ -12259,7 +12259,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G410" t="n">
-        <v>4.54956531524658</v>
+        <v>4.54956579208374</v>
       </c>
       <c r="H410" t="n">
         <v>114764</v>
@@ -12375,7 +12375,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.39102029800415</v>
+        <v>4.39101982116699</v>
       </c>
       <c r="H414" t="n">
         <v>238804</v>
@@ -12404,7 +12404,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G415" t="n">
-        <v>4.4461669921875</v>
+        <v>4.44616651535034</v>
       </c>
       <c r="H415" t="n">
         <v>62047</v>
@@ -12433,7 +12433,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.42203998565674</v>
+        <v>4.4220404624939</v>
       </c>
       <c r="H416" t="n">
         <v>143532</v>
@@ -12462,7 +12462,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>4.42548656463623</v>
+        <v>4.42548704147339</v>
       </c>
       <c r="H417" t="n">
         <v>91936</v>
@@ -12578,7 +12578,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G421" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281549453735</v>
       </c>
       <c r="H421" t="n">
         <v>57686</v>
@@ -12607,7 +12607,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>4.23936796188354</v>
+        <v>4.23936891555786</v>
       </c>
       <c r="H422" t="n">
         <v>82552</v>
@@ -12665,7 +12665,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G424" t="n">
-        <v>4.27728128433228</v>
+        <v>4.27728080749512</v>
       </c>
       <c r="H424" t="n">
         <v>29617</v>
@@ -12868,7 +12868,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281549453735</v>
       </c>
       <c r="H431" t="n">
         <v>97071</v>
@@ -12926,7 +12926,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281549453735</v>
       </c>
       <c r="H433" t="n">
         <v>49792</v>
@@ -12984,7 +12984,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>4.28072834014893</v>
+        <v>4.28072786331177</v>
       </c>
       <c r="H435" t="n">
         <v>67345</v>
@@ -13013,7 +13013,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G436" t="n">
-        <v>4.2324743270874</v>
+        <v>4.23247480392456</v>
       </c>
       <c r="H436" t="n">
         <v>100278</v>
@@ -13100,7 +13100,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>3.52936005592346</v>
+        <v>3.52936053276062</v>
       </c>
       <c r="H439" t="n">
         <v>1797627</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>3.44664096832275</v>
+        <v>3.4466404914856</v>
       </c>
       <c r="H440" t="n">
         <v>1056990</v>
@@ -13158,7 +13158,7 @@
         <v>5</v>
       </c>
       <c r="G441" t="n">
-        <v>3.44664096832275</v>
+        <v>3.4466404914856</v>
       </c>
       <c r="H441" t="n">
         <v>454580</v>
@@ -13187,7 +13187,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>3.37770843505859</v>
+        <v>3.37770795822144</v>
       </c>
       <c r="H442" t="n">
         <v>276428</v>
@@ -13216,7 +13216,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G443" t="n">
-        <v>3.37081456184387</v>
+        <v>3.37081480026245</v>
       </c>
       <c r="H443" t="n">
         <v>202384</v>
@@ -13245,7 +13245,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G444" t="n">
-        <v>3.4425048828125</v>
+        <v>3.44250464439392</v>
       </c>
       <c r="H444" t="n">
         <v>322860</v>
@@ -13274,7 +13274,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G445" t="n">
-        <v>3.44526195526123</v>
+        <v>3.44526243209839</v>
       </c>
       <c r="H445" t="n">
         <v>243913</v>
@@ -13303,7 +13303,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G446" t="n">
-        <v>3.42458271980286</v>
+        <v>3.42458248138428</v>
       </c>
       <c r="H446" t="n">
         <v>285105</v>
@@ -13332,7 +13332,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>3.42596077919006</v>
+        <v>3.42596125602722</v>
       </c>
       <c r="H447" t="n">
         <v>173870</v>
@@ -13390,7 +13390,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.42596077919006</v>
+        <v>3.42596125602722</v>
       </c>
       <c r="H449" t="n">
         <v>172863</v>
@@ -13419,7 +13419,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G450" t="n">
-        <v>3.38046550750732</v>
+        <v>3.38046479225159</v>
       </c>
       <c r="H450" t="n">
         <v>226892</v>
@@ -13448,7 +13448,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G451" t="n">
-        <v>3.32807660102844</v>
+        <v>3.32807636260986</v>
       </c>
       <c r="H451" t="n">
         <v>313343</v>
@@ -13535,7 +13535,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G454" t="n">
-        <v>3.05372381210327</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H454" t="n">
         <v>402906</v>
@@ -13622,7 +13622,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>3.06751036643982</v>
+        <v>3.06751012802124</v>
       </c>
       <c r="H457" t="n">
         <v>523527</v>
@@ -13651,7 +13651,7 @@
         <v>4.40399980545044</v>
       </c>
       <c r="G458" t="n">
-        <v>3.03580093383789</v>
+        <v>3.03580117225647</v>
       </c>
       <c r="H458" t="n">
         <v>266731</v>
@@ -13680,7 +13680,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G459" t="n">
-        <v>2.95308184623718</v>
+        <v>2.95308208465576</v>
       </c>
       <c r="H459" t="n">
         <v>409593</v>
@@ -13738,7 +13738,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G461" t="n">
-        <v>2.95446014404297</v>
+        <v>2.95446038246155</v>
       </c>
       <c r="H461" t="n">
         <v>328173</v>
@@ -13825,7 +13825,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G464" t="n">
-        <v>2.87725567817688</v>
+        <v>2.8772554397583</v>
       </c>
       <c r="H464" t="n">
         <v>725032</v>
@@ -13883,7 +13883,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G466" t="n">
-        <v>2.98479080200195</v>
+        <v>2.98479104042053</v>
       </c>
       <c r="H466" t="n">
         <v>406773</v>
@@ -13941,7 +13941,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G468" t="n">
-        <v>2.89655733108521</v>
+        <v>2.89655709266663</v>
       </c>
       <c r="H468" t="n">
         <v>587468</v>
@@ -13970,7 +13970,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>2.8607120513916</v>
+        <v>2.86071181297302</v>
       </c>
       <c r="H469" t="n">
         <v>326227</v>
@@ -14057,7 +14057,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G472" t="n">
-        <v>3.04545164108276</v>
+        <v>3.04545211791992</v>
       </c>
       <c r="H472" t="n">
         <v>1192003</v>
@@ -14086,7 +14086,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>2.97789788246155</v>
+        <v>2.97789764404297</v>
       </c>
       <c r="H473" t="n">
         <v>366433</v>
@@ -14115,7 +14115,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G474" t="n">
-        <v>3.07026767730713</v>
+        <v>3.07026743888855</v>
       </c>
       <c r="H474" t="n">
         <v>582857</v>
@@ -14173,7 +14173,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>2.94343137741089</v>
+        <v>2.94343090057373</v>
       </c>
       <c r="H476" t="n">
         <v>398406</v>
@@ -14202,7 +14202,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.8607120513916</v>
+        <v>2.86071181297302</v>
       </c>
       <c r="H477" t="n">
         <v>523481</v>
@@ -14231,7 +14231,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G478" t="n">
-        <v>2.82624506950378</v>
+        <v>2.82624554634094</v>
       </c>
       <c r="H478" t="n">
         <v>369252</v>
@@ -14318,7 +14318,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G481" t="n">
-        <v>2.70492386817932</v>
+        <v>2.70492362976074</v>
       </c>
       <c r="H481" t="n">
         <v>410944</v>
@@ -14347,7 +14347,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692525863647</v>
       </c>
       <c r="H482" t="n">
         <v>511759</v>
@@ -14376,7 +14376,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G483" t="n">
-        <v>2.87311983108521</v>
+        <v>2.87312006950378</v>
       </c>
       <c r="H483" t="n">
         <v>492450</v>
@@ -14405,7 +14405,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G484" t="n">
-        <v>2.85519766807556</v>
+        <v>2.85519742965698</v>
       </c>
       <c r="H484" t="n">
         <v>386325</v>
@@ -14434,7 +14434,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G485" t="n">
-        <v>2.85795426368713</v>
+        <v>2.85795450210571</v>
       </c>
       <c r="H485" t="n">
         <v>234792</v>
@@ -14521,7 +14521,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G488" t="n">
-        <v>2.80005121231079</v>
+        <v>2.80005073547363</v>
       </c>
       <c r="H488" t="n">
         <v>264775</v>
@@ -14550,7 +14550,7 @@
         <v>4</v>
       </c>
       <c r="G489" t="n">
-        <v>2.75731229782104</v>
+        <v>2.7573127746582</v>
       </c>
       <c r="H489" t="n">
         <v>356617</v>
@@ -14579,7 +14579,7 @@
         <v>4</v>
       </c>
       <c r="G490" t="n">
-        <v>2.75731229782104</v>
+        <v>2.7573127746582</v>
       </c>
       <c r="H490" t="n">
         <v>337390</v>
@@ -14637,7 +14637,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G492" t="n">
-        <v>2.78764319419861</v>
+        <v>2.78764295578003</v>
       </c>
       <c r="H492" t="n">
         <v>1174545</v>
@@ -14695,7 +14695,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G494" t="n">
-        <v>2.90896463394165</v>
+        <v>2.90896439552307</v>
       </c>
       <c r="H494" t="n">
         <v>188877</v>
@@ -14753,7 +14753,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G496" t="n">
-        <v>2.88690638542175</v>
+        <v>2.88690662384033</v>
       </c>
       <c r="H496" t="n">
         <v>205236</v>
@@ -14811,7 +14811,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G498" t="n">
-        <v>2.95308184623718</v>
+        <v>2.95308208465576</v>
       </c>
       <c r="H498" t="n">
         <v>254114</v>
@@ -14869,7 +14869,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93240189552307</v>
+        <v>2.93240237236023</v>
       </c>
       <c r="H500" t="n">
         <v>107995</v>
@@ -14898,7 +14898,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G501" t="n">
-        <v>2.87725567817688</v>
+        <v>2.8772554397583</v>
       </c>
       <c r="H501" t="n">
         <v>128616</v>
@@ -14927,7 +14927,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G502" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H502" t="n">
         <v>359617</v>
@@ -14985,7 +14985,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G504" t="n">
-        <v>2.81935214996338</v>
+        <v>2.81935238838196</v>
       </c>
       <c r="H504" t="n">
         <v>148517</v>
@@ -15043,7 +15043,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>2.82624506950378</v>
+        <v>2.82624554634094</v>
       </c>
       <c r="H506" t="n">
         <v>127666</v>
@@ -15101,7 +15101,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G508" t="n">
-        <v>2.80005121231079</v>
+        <v>2.80005073547363</v>
       </c>
       <c r="H508" t="n">
         <v>47300</v>
@@ -15130,7 +15130,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G509" t="n">
-        <v>2.89931392669678</v>
+        <v>2.89931440353394</v>
       </c>
       <c r="H509" t="n">
         <v>204187</v>
@@ -15159,7 +15159,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G510" t="n">
-        <v>2.88690638542175</v>
+        <v>2.88690662384033</v>
       </c>
       <c r="H510" t="n">
         <v>93443</v>
@@ -15246,7 +15246,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>2.93998456001282</v>
+        <v>2.9399847984314</v>
       </c>
       <c r="H513" t="n">
         <v>127430</v>
@@ -15275,7 +15275,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G514" t="n">
-        <v>2.95032453536987</v>
+        <v>2.95032477378845</v>
       </c>
       <c r="H514" t="n">
         <v>134249</v>
@@ -15391,7 +15391,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>3.11920976638794</v>
+        <v>3.1192102432251</v>
       </c>
       <c r="H518" t="n">
         <v>467928</v>
@@ -15449,7 +15449,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>3.05717039108276</v>
+        <v>3.05717062950134</v>
       </c>
       <c r="H520" t="n">
         <v>210541</v>
@@ -15507,7 +15507,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G522" t="n">
-        <v>3.16746282577515</v>
+        <v>3.16746258735657</v>
       </c>
       <c r="H522" t="n">
         <v>493955</v>
@@ -15536,7 +15536,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.13299632072449</v>
+        <v>3.13299679756165</v>
       </c>
       <c r="H523" t="n">
         <v>379353</v>
@@ -15594,7 +15594,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>3.08819031715393</v>
+        <v>3.08819007873535</v>
       </c>
       <c r="H525" t="n">
         <v>388946</v>
@@ -15681,7 +15681,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>3.09508347511292</v>
+        <v>3.09508299827576</v>
       </c>
       <c r="H528" t="n">
         <v>253894</v>
@@ -15710,7 +15710,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G529" t="n">
-        <v>3.09508347511292</v>
+        <v>3.09508299827576</v>
       </c>
       <c r="H529" t="n">
         <v>186227</v>
@@ -15739,7 +15739,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G530" t="n">
-        <v>3.19503664970398</v>
+        <v>3.1950364112854</v>
       </c>
       <c r="H530" t="n">
         <v>364125</v>
@@ -15768,7 +15768,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>3.14333653450012</v>
+        <v>3.1433367729187</v>
       </c>
       <c r="H531" t="n">
         <v>265328</v>
@@ -15797,7 +15797,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G532" t="n">
-        <v>3.05027747154236</v>
+        <v>3.0502769947052</v>
       </c>
       <c r="H532" t="n">
         <v>444837</v>
@@ -15826,7 +15826,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>3.04683041572571</v>
+        <v>3.04683065414429</v>
       </c>
       <c r="H533" t="n">
         <v>319024</v>
@@ -15855,7 +15855,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>3.02959752082825</v>
+        <v>3.02959704399109</v>
       </c>
       <c r="H534" t="n">
         <v>317377</v>
@@ -15884,7 +15884,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>3.03304362297058</v>
+        <v>3.03304386138916</v>
       </c>
       <c r="H535" t="n">
         <v>491731</v>
@@ -15913,7 +15913,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>2.98479080200195</v>
+        <v>2.98479104042053</v>
       </c>
       <c r="H536" t="n">
         <v>519676</v>
@@ -15971,7 +15971,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G538" t="n">
-        <v>2.91585803031921</v>
+        <v>2.91585826873779</v>
       </c>
       <c r="H538" t="n">
         <v>630323</v>
@@ -16000,7 +16000,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>2.81245851516724</v>
+        <v>2.81245899200439</v>
       </c>
       <c r="H539" t="n">
         <v>482372</v>
@@ -16058,7 +16058,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G541" t="n">
-        <v>2.78143906593323</v>
+        <v>2.78143882751465</v>
       </c>
       <c r="H541" t="n">
         <v>442828</v>
@@ -16116,7 +16116,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>3.04683041572571</v>
+        <v>3.04683065414429</v>
       </c>
       <c r="H543" t="n">
         <v>812045</v>
@@ -16145,7 +16145,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>3.08129692077637</v>
+        <v>3.08129668235779</v>
       </c>
       <c r="H544" t="n">
         <v>443706</v>
@@ -16203,7 +16203,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>3.08819031715393</v>
+        <v>3.08819007873535</v>
       </c>
       <c r="H546" t="n">
         <v>146187</v>
@@ -16232,7 +16232,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06406354904175</v>
+        <v>3.06406378746033</v>
       </c>
       <c r="H547" t="n">
         <v>404236</v>
@@ -16261,7 +16261,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>3.04338383674622</v>
+        <v>3.04338359832764</v>
       </c>
       <c r="H548" t="n">
         <v>383699</v>
@@ -16319,7 +16319,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G550" t="n">
-        <v>3.05372381210327</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H550" t="n">
         <v>238836</v>
@@ -16406,7 +16406,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G553" t="n">
-        <v>3.00547099113464</v>
+        <v>3.00547122955322</v>
       </c>
       <c r="H553" t="n">
         <v>251650</v>
@@ -16522,7 +16522,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G557" t="n">
-        <v>3.05372381210327</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H557" t="n">
         <v>922577</v>
@@ -16580,7 +16580,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>3.06061720848083</v>
+        <v>3.06061744689941</v>
       </c>
       <c r="H559" t="n">
         <v>415498</v>
@@ -16667,7 +16667,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G562" t="n">
-        <v>2.87794542312622</v>
+        <v>2.87794518470764</v>
       </c>
       <c r="H562" t="n">
         <v>486870</v>
@@ -16783,7 +16783,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>2.87794542312622</v>
+        <v>2.87794518470764</v>
       </c>
       <c r="H566" t="n">
         <v>234339</v>
@@ -16841,7 +16841,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G568" t="n">
-        <v>2.90896463394165</v>
+        <v>2.90896439552307</v>
       </c>
       <c r="H568" t="n">
         <v>292000</v>
@@ -16928,7 +16928,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692525863647</v>
       </c>
       <c r="H571" t="n">
         <v>165452</v>
@@ -16957,7 +16957,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G572" t="n">
-        <v>2.8882851600647</v>
+        <v>2.88828539848328</v>
       </c>
       <c r="H572" t="n">
         <v>156197</v>
@@ -17044,7 +17044,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>2.98134398460388</v>
+        <v>2.98134422302246</v>
       </c>
       <c r="H575" t="n">
         <v>190507</v>
@@ -17073,7 +17073,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>2.94687819480896</v>
+        <v>2.94687795639038</v>
       </c>
       <c r="H576" t="n">
         <v>152196</v>
@@ -17131,7 +17131,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G578" t="n">
-        <v>2.97789788246155</v>
+        <v>2.97789764404297</v>
       </c>
       <c r="H578" t="n">
         <v>86085</v>
@@ -17189,7 +17189,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G580" t="n">
-        <v>2.99513053894043</v>
+        <v>2.99513077735901</v>
       </c>
       <c r="H580" t="n">
         <v>44953</v>
@@ -17218,7 +17218,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G581" t="n">
-        <v>2.964111328125</v>
+        <v>2.96411108970642</v>
       </c>
       <c r="H581" t="n">
         <v>83737</v>
@@ -17247,7 +17247,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>2.97789788246155</v>
+        <v>2.97789764404297</v>
       </c>
       <c r="H582" t="n">
         <v>144591</v>
@@ -17305,7 +17305,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G584" t="n">
-        <v>2.98134398460388</v>
+        <v>2.98134422302246</v>
       </c>
       <c r="H584" t="n">
         <v>63477</v>
@@ -17334,7 +17334,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>2.9882378578186</v>
+        <v>2.98823738098145</v>
       </c>
       <c r="H585" t="n">
         <v>198148</v>
@@ -17421,7 +17421,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G588" t="n">
-        <v>3.03649091720581</v>
+        <v>3.03649067878723</v>
       </c>
       <c r="H588" t="n">
         <v>252004</v>
@@ -17450,7 +17450,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>3.04683041572571</v>
+        <v>3.04683065414429</v>
       </c>
       <c r="H589" t="n">
         <v>119110</v>
@@ -17479,7 +17479,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>3.06751036643982</v>
+        <v>3.06751012802124</v>
       </c>
       <c r="H590" t="n">
         <v>378785</v>
@@ -17508,7 +17508,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>3.07095646858215</v>
+        <v>3.07095742225647</v>
       </c>
       <c r="H591" t="n">
         <v>195836</v>
@@ -17566,7 +17566,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G593" t="n">
-        <v>3.00891733169556</v>
+        <v>3.00891709327698</v>
       </c>
       <c r="H593" t="n">
         <v>230140</v>
@@ -17653,7 +17653,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G596" t="n">
-        <v>3.00891733169556</v>
+        <v>3.00891709327698</v>
       </c>
       <c r="H596" t="n">
         <v>122410</v>
@@ -17682,7 +17682,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03304362297058</v>
+        <v>3.03304386138916</v>
       </c>
       <c r="H597" t="n">
         <v>163365</v>
@@ -17711,7 +17711,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>3.04683041572571</v>
+        <v>3.04683065414429</v>
       </c>
       <c r="H598" t="n">
         <v>158703</v>
@@ -17769,7 +17769,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>3.03649091720581</v>
+        <v>3.03649067878723</v>
       </c>
       <c r="H600" t="n">
         <v>224765</v>
@@ -17798,7 +17798,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G601" t="n">
-        <v>3.01925730705261</v>
+        <v>3.01925754547119</v>
       </c>
       <c r="H601" t="n">
         <v>220818</v>
@@ -17856,7 +17856,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G603" t="n">
-        <v>3.09027004241943</v>
+        <v>3.09027028083801</v>
       </c>
       <c r="H603" t="n">
         <v>195385</v>
@@ -17914,7 +17914,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G605" t="n">
-        <v>2.94802522659302</v>
+        <v>2.94802570343018</v>
       </c>
       <c r="H605" t="n">
         <v>276475</v>
@@ -17943,7 +17943,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>2.98714280128479</v>
+        <v>2.98714256286621</v>
       </c>
       <c r="H606" t="n">
         <v>223287</v>
@@ -17972,7 +17972,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>2.95513796806335</v>
+        <v>2.95513772964478</v>
       </c>
       <c r="H607" t="n">
         <v>101236</v>
@@ -18001,7 +18001,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>2.94091320037842</v>
+        <v>2.940913438797</v>
       </c>
       <c r="H608" t="n">
         <v>161778</v>
@@ -18030,7 +18030,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G609" t="n">
-        <v>2.96224999427795</v>
+        <v>2.96224975585938</v>
       </c>
       <c r="H609" t="n">
         <v>120210</v>
@@ -18088,7 +18088,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.87690305709839</v>
+        <v>2.87690281867981</v>
       </c>
       <c r="H611" t="n">
         <v>124383</v>
@@ -18175,7 +18175,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>2.62086200714111</v>
+        <v>2.62086224555969</v>
       </c>
       <c r="H614" t="n">
         <v>585601</v>
@@ -18233,7 +18233,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>2.65286707878113</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H616" t="n">
         <v>243214</v>
@@ -18262,7 +18262,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G617" t="n">
-        <v>2.69198489189148</v>
+        <v>2.6919846534729</v>
       </c>
       <c r="H617" t="n">
         <v>341053</v>
@@ -18291,7 +18291,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G618" t="n">
-        <v>2.65286707878113</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H618" t="n">
         <v>259078</v>
@@ -18320,7 +18320,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G619" t="n">
-        <v>2.57107639312744</v>
+        <v>2.57107663154602</v>
       </c>
       <c r="H619" t="n">
         <v>188588</v>
@@ -18349,7 +18349,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.58530068397522</v>
+        <v>2.5853009223938</v>
       </c>
       <c r="H620" t="n">
         <v>177506</v>
@@ -18378,7 +18378,7 @@
         <v>3.625</v>
       </c>
       <c r="G621" t="n">
-        <v>2.57818841934204</v>
+        <v>2.5781888961792</v>
       </c>
       <c r="H621" t="n">
         <v>419710</v>
@@ -18436,7 +18436,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.58530068397522</v>
+        <v>2.5853009223938</v>
       </c>
       <c r="H623" t="n">
         <v>152678</v>
@@ -18465,7 +18465,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.61019372940063</v>
+        <v>2.61019396781921</v>
       </c>
       <c r="H624" t="n">
         <v>152498</v>
@@ -18581,7 +18581,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>2.6955406665802</v>
+        <v>2.69554090499878</v>
       </c>
       <c r="H628" t="n">
         <v>49387</v>
@@ -18610,7 +18610,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G629" t="n">
-        <v>2.69198489189148</v>
+        <v>2.6919846534729</v>
       </c>
       <c r="H629" t="n">
         <v>99972</v>
@@ -18697,7 +18697,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G632" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H632" t="n">
         <v>425725</v>
@@ -18726,7 +18726,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>2.49995422363281</v>
+        <v>2.49995398521423</v>
       </c>
       <c r="H633" t="n">
         <v>289300</v>
@@ -18784,7 +18784,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>2.59241318702698</v>
+        <v>2.5924129486084</v>
       </c>
       <c r="H635" t="n">
         <v>247960</v>
@@ -18813,7 +18813,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G636" t="n">
-        <v>2.56752038002014</v>
+        <v>2.56752014160156</v>
       </c>
       <c r="H636" t="n">
         <v>270034</v>
@@ -18871,7 +18871,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H638" t="n">
         <v>395672</v>
@@ -18987,7 +18987,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G642" t="n">
-        <v>2.79155588150024</v>
+        <v>2.79155611991882</v>
       </c>
       <c r="H642" t="n">
         <v>251313</v>
@@ -19016,7 +19016,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G643" t="n">
-        <v>2.86267876625061</v>
+        <v>2.86267852783203</v>
       </c>
       <c r="H643" t="n">
         <v>152428</v>
@@ -19074,7 +19074,7 @@
         <v>4</v>
       </c>
       <c r="G645" t="n">
-        <v>2.84489750862122</v>
+        <v>2.84489774703979</v>
       </c>
       <c r="H645" t="n">
         <v>243773</v>
@@ -19103,7 +19103,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H646" t="n">
         <v>215881</v>
@@ -19132,7 +19132,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.72398972511292</v>
+        <v>2.72398996353149</v>
       </c>
       <c r="H647" t="n">
         <v>181176</v>
@@ -19248,7 +19248,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G651" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H651" t="n">
         <v>100165</v>
@@ -19306,7 +19306,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G653" t="n">
-        <v>2.65642333030701</v>
+        <v>2.65642309188843</v>
       </c>
       <c r="H653" t="n">
         <v>170086</v>
@@ -19393,7 +19393,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>2.65642333030701</v>
+        <v>2.65642309188843</v>
       </c>
       <c r="H656" t="n">
         <v>97009</v>
@@ -19451,7 +19451,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H658" t="n">
         <v>72786</v>
@@ -19480,7 +19480,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G659" t="n">
-        <v>2.75243830680847</v>
+        <v>2.75243854522705</v>
       </c>
       <c r="H659" t="n">
         <v>65346</v>
@@ -19509,7 +19509,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G660" t="n">
-        <v>2.70620918273926</v>
+        <v>2.70620894432068</v>
       </c>
       <c r="H660" t="n">
         <v>139089</v>
@@ -19654,7 +19654,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>2.6955406665802</v>
+        <v>2.69554090499878</v>
       </c>
       <c r="H665" t="n">
         <v>50667</v>
@@ -19712,7 +19712,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H667" t="n">
         <v>75420</v>
@@ -19770,7 +19770,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H669" t="n">
         <v>23840</v>
@@ -19828,7 +19828,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>2.64575505256653</v>
+        <v>2.64575481414795</v>
       </c>
       <c r="H671" t="n">
         <v>57464</v>
@@ -19857,7 +19857,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>2.70976519584656</v>
+        <v>2.70976495742798</v>
       </c>
       <c r="H672" t="n">
         <v>74089</v>
@@ -19915,7 +19915,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>2.82711720466614</v>
+        <v>2.82711744308472</v>
       </c>
       <c r="H674" t="n">
         <v>96667</v>
@@ -19944,7 +19944,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G675" t="n">
-        <v>2.77377557754517</v>
+        <v>2.77377533912659</v>
       </c>
       <c r="H675" t="n">
         <v>118597</v>
@@ -19973,7 +19973,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>2.77377557754517</v>
+        <v>2.77377533912659</v>
       </c>
       <c r="H676" t="n">
         <v>49199</v>
@@ -20031,7 +20031,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>2.64931082725525</v>
+        <v>2.64931106567383</v>
       </c>
       <c r="H678" t="n">
         <v>409416</v>
@@ -20118,7 +20118,7 @@
         <v>3.625</v>
       </c>
       <c r="G681" t="n">
-        <v>2.57818841934204</v>
+        <v>2.5781888961792</v>
       </c>
       <c r="H681" t="n">
         <v>50503</v>
@@ -20147,7 +20147,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G682" t="n">
-        <v>2.69198489189148</v>
+        <v>2.6919846534729</v>
       </c>
       <c r="H682" t="n">
         <v>95363</v>
@@ -20176,7 +20176,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>2.65997934341431</v>
+        <v>2.65997958183289</v>
       </c>
       <c r="H683" t="n">
         <v>25234</v>
@@ -20205,7 +20205,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G684" t="n">
-        <v>2.64931082725525</v>
+        <v>2.64931106567383</v>
       </c>
       <c r="H684" t="n">
         <v>34184</v>
@@ -20234,7 +20234,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65997934341431</v>
+        <v>2.65997958183289</v>
       </c>
       <c r="H685" t="n">
         <v>54057</v>
@@ -20263,7 +20263,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>2.61019372940063</v>
+        <v>2.61019396781921</v>
       </c>
       <c r="H686" t="n">
         <v>148011</v>
@@ -20292,7 +20292,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>2.68131589889526</v>
+        <v>2.68131613731384</v>
       </c>
       <c r="H687" t="n">
         <v>229731</v>
@@ -20350,7 +20350,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G689" t="n">
-        <v>2.60308146476746</v>
+        <v>2.60308170318604</v>
       </c>
       <c r="H689" t="n">
         <v>365229</v>
@@ -20437,7 +20437,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.65286707878113</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H692" t="n">
         <v>158013</v>
@@ -20466,7 +20466,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G693" t="n">
-        <v>2.72043371200562</v>
+        <v>2.72043347358704</v>
       </c>
       <c r="H693" t="n">
         <v>192286</v>
@@ -20495,7 +20495,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021908760071</v>
       </c>
       <c r="H694" t="n">
         <v>165658</v>
@@ -20524,7 +20524,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G695" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H695" t="n">
         <v>180565</v>
@@ -20640,7 +20640,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H699" t="n">
         <v>45647</v>
@@ -20669,7 +20669,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H700" t="n">
         <v>74718</v>
@@ -20698,7 +20698,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>2.70976519584656</v>
+        <v>2.70976495742798</v>
       </c>
       <c r="H701" t="n">
         <v>83109</v>
@@ -20727,7 +20727,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H702" t="n">
         <v>154866</v>
@@ -20756,7 +20756,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H703" t="n">
         <v>104868</v>
@@ -20785,7 +20785,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G704" t="n">
-        <v>2.78088784217834</v>
+        <v>2.78088760375977</v>
       </c>
       <c r="H704" t="n">
         <v>85479</v>
@@ -20814,7 +20814,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G705" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H705" t="n">
         <v>80864</v>
@@ -20901,7 +20901,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>2.61730647087097</v>
+        <v>2.61730623245239</v>
       </c>
       <c r="H708" t="n">
         <v>94175</v>
@@ -20930,7 +20930,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G709" t="n">
-        <v>2.55685210227966</v>
+        <v>2.55685186386108</v>
       </c>
       <c r="H709" t="n">
         <v>130291</v>
@@ -20959,7 +20959,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50350999832153</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H710" t="n">
         <v>188934</v>
@@ -20988,7 +20988,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G711" t="n">
-        <v>2.57107639312744</v>
+        <v>2.57107663154602</v>
       </c>
       <c r="H711" t="n">
         <v>108439</v>
@@ -21017,7 +21017,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G712" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H712" t="n">
         <v>44213</v>
@@ -21075,7 +21075,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G714" t="n">
-        <v>2.52840304374695</v>
+        <v>2.52840280532837</v>
       </c>
       <c r="H714" t="n">
         <v>47336</v>
@@ -21104,7 +21104,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G715" t="n">
-        <v>2.4786171913147</v>
+        <v>2.47861695289612</v>
       </c>
       <c r="H715" t="n">
         <v>52613</v>
@@ -21191,7 +21191,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H718" t="n">
         <v>63101</v>
@@ -21220,7 +21220,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G719" t="n">
-        <v>2.56752038002014</v>
+        <v>2.56752014160156</v>
       </c>
       <c r="H719" t="n">
         <v>87756</v>
@@ -21249,7 +21249,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>2.60308146476746</v>
+        <v>2.60308170318604</v>
       </c>
       <c r="H720" t="n">
         <v>117533</v>
@@ -21278,7 +21278,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61730647087097</v>
+        <v>2.61730623245239</v>
       </c>
       <c r="H721" t="n">
         <v>64041</v>
@@ -21307,7 +21307,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G722" t="n">
-        <v>2.70620918273926</v>
+        <v>2.70620894432068</v>
       </c>
       <c r="H722" t="n">
         <v>119382</v>
@@ -21336,7 +21336,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G723" t="n">
-        <v>2.73465776443481</v>
+        <v>2.73465824127197</v>
       </c>
       <c r="H723" t="n">
         <v>62198</v>
@@ -21394,7 +21394,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G725" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021908760071</v>
       </c>
       <c r="H725" t="n">
         <v>81609</v>
@@ -21423,7 +21423,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>2.81289267539978</v>
+        <v>2.81289291381836</v>
       </c>
       <c r="H726" t="n">
         <v>140477</v>
@@ -21481,7 +21481,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.90179562568665</v>
+        <v>2.90179586410522</v>
       </c>
       <c r="H728" t="n">
         <v>252045</v>
@@ -21510,7 +21510,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G729" t="n">
-        <v>2.9124641418457</v>
+        <v>2.91246390342712</v>
       </c>
       <c r="H729" t="n">
         <v>172660</v>
@@ -21684,7 +21684,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G735" t="n">
-        <v>2.916020154953</v>
+        <v>2.91602039337158</v>
       </c>
       <c r="H735" t="n">
         <v>572778</v>
@@ -21771,7 +21771,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G738" t="n">
-        <v>2.61374974250793</v>
+        <v>2.61374998092651</v>
       </c>
       <c r="H738" t="n">
         <v>117585</v>
@@ -21800,7 +21800,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G739" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H739" t="n">
         <v>111814</v>
@@ -21829,7 +21829,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G740" t="n">
-        <v>2.59952545166016</v>
+        <v>2.59952569007874</v>
       </c>
       <c r="H740" t="n">
         <v>76380</v>
@@ -21858,7 +21858,7 @@
         <v>3.625</v>
       </c>
       <c r="G741" t="n">
-        <v>2.57818841934204</v>
+        <v>2.5781888961792</v>
       </c>
       <c r="H741" t="n">
         <v>86207</v>
@@ -21945,7 +21945,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G744" t="n">
-        <v>2.65997934341431</v>
+        <v>2.65997958183289</v>
       </c>
       <c r="H744" t="n">
         <v>59599</v>
@@ -21974,7 +21974,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G745" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H745" t="n">
         <v>44399</v>
@@ -22061,7 +22061,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G748" t="n">
-        <v>2.61730647087097</v>
+        <v>2.61730623245239</v>
       </c>
       <c r="H748" t="n">
         <v>100769</v>
@@ -22119,7 +22119,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G750" t="n">
-        <v>2.56752038002014</v>
+        <v>2.56752014160156</v>
       </c>
       <c r="H750" t="n">
         <v>41661</v>
@@ -22148,7 +22148,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.59241318702698</v>
+        <v>2.5924129486084</v>
       </c>
       <c r="H751" t="n">
         <v>21292</v>
@@ -22177,7 +22177,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57107639312744</v>
+        <v>2.57107663154602</v>
       </c>
       <c r="H752" t="n">
         <v>65965</v>
@@ -22206,7 +22206,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.62086200714111</v>
+        <v>2.62086224555969</v>
       </c>
       <c r="H753" t="n">
         <v>95272</v>
@@ -22235,7 +22235,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.59241318702698</v>
+        <v>2.5924129486084</v>
       </c>
       <c r="H754" t="n">
         <v>126933</v>
@@ -22293,7 +22293,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G756" t="n">
-        <v>2.61374974250793</v>
+        <v>2.61374998092651</v>
       </c>
       <c r="H756" t="n">
         <v>33799</v>
@@ -22322,7 +22322,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>2.60308146476746</v>
+        <v>2.60308170318604</v>
       </c>
       <c r="H757" t="n">
         <v>73291</v>
@@ -22380,7 +22380,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>2.61019372940063</v>
+        <v>2.61019396781921</v>
       </c>
       <c r="H759" t="n">
         <v>28732</v>
@@ -22409,7 +22409,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>2.56040811538696</v>
+        <v>2.56040787696838</v>
       </c>
       <c r="H760" t="n">
         <v>41797</v>
@@ -22438,7 +22438,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G761" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H761" t="n">
         <v>45443</v>
@@ -22496,7 +22496,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>2.51773428916931</v>
+        <v>2.51773452758789</v>
       </c>
       <c r="H763" t="n">
         <v>84397</v>
@@ -22554,7 +22554,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>2.64931082725525</v>
+        <v>2.64931106567383</v>
       </c>
       <c r="H765" t="n">
         <v>23656</v>
@@ -22583,7 +22583,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.62441873550415</v>
+        <v>2.62441825866699</v>
       </c>
       <c r="H766" t="n">
         <v>72814</v>
@@ -22612,7 +22612,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.65286707878113</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H767" t="n">
         <v>90927</v>
@@ -22641,7 +22641,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G768" t="n">
-        <v>2.67420363426208</v>
+        <v>2.67420387268066</v>
       </c>
       <c r="H768" t="n">
         <v>56118</v>
@@ -22670,7 +22670,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G769" t="n">
-        <v>2.72043371200562</v>
+        <v>2.72043347358704</v>
       </c>
       <c r="H769" t="n">
         <v>128846</v>
@@ -22699,7 +22699,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.73465776443481</v>
+        <v>2.73465824127197</v>
       </c>
       <c r="H770" t="n">
         <v>66288</v>
@@ -22728,7 +22728,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>2.7951123714447</v>
+        <v>2.79511213302612</v>
       </c>
       <c r="H771" t="n">
         <v>92920</v>
@@ -22815,7 +22815,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G774" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H774" t="n">
         <v>66798</v>
@@ -22873,7 +22873,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G776" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H776" t="n">
         <v>65193</v>
@@ -22902,7 +22902,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G777" t="n">
-        <v>2.76310706138611</v>
+        <v>2.76310729980469</v>
       </c>
       <c r="H777" t="n">
         <v>26136</v>
@@ -23018,7 +23018,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G781" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H781" t="n">
         <v>137677</v>
@@ -23047,7 +23047,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>2.84134149551392</v>
+        <v>2.8413417339325</v>
       </c>
       <c r="H782" t="n">
         <v>317244</v>
@@ -23076,7 +23076,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.77377557754517</v>
+        <v>2.77377533912659</v>
       </c>
       <c r="H783" t="n">
         <v>120974</v>
@@ -23105,7 +23105,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H784" t="n">
         <v>47047</v>
@@ -23134,7 +23134,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G785" t="n">
-        <v>2.73821401596069</v>
+        <v>2.73821425437927</v>
       </c>
       <c r="H785" t="n">
         <v>84891</v>
@@ -23163,7 +23163,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G786" t="n">
-        <v>2.68131589889526</v>
+        <v>2.68131613731384</v>
       </c>
       <c r="H786" t="n">
         <v>39710</v>
@@ -23192,7 +23192,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>2.64575505256653</v>
+        <v>2.64575481414795</v>
       </c>
       <c r="H787" t="n">
         <v>58312</v>
@@ -23250,7 +23250,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G789" t="n">
-        <v>2.67420363426208</v>
+        <v>2.67420387268066</v>
       </c>
       <c r="H789" t="n">
         <v>36914</v>
@@ -23279,7 +23279,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H790" t="n">
         <v>53946</v>
@@ -23337,7 +23337,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>2.59596920013428</v>
+        <v>2.5959689617157</v>
       </c>
       <c r="H792" t="n">
         <v>42596</v>
@@ -23366,7 +23366,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G793" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H793" t="n">
         <v>165011</v>
@@ -23395,7 +23395,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H794" t="n">
         <v>126965</v>
@@ -23482,7 +23482,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>2.52129101753235</v>
+        <v>2.52129077911377</v>
       </c>
       <c r="H797" t="n">
         <v>223749</v>
@@ -23511,7 +23511,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.49995422363281</v>
+        <v>2.49995398521423</v>
       </c>
       <c r="H798" t="n">
         <v>79031</v>
@@ -23540,7 +23540,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G799" t="n">
-        <v>2.51062202453613</v>
+        <v>2.51062250137329</v>
       </c>
       <c r="H799" t="n">
         <v>101854</v>
@@ -23569,7 +23569,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G800" t="n">
-        <v>2.51773428916931</v>
+        <v>2.51773452758789</v>
       </c>
       <c r="H800" t="n">
         <v>122165</v>
@@ -23627,7 +23627,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G802" t="n">
-        <v>2.51062202453613</v>
+        <v>2.51062250137329</v>
       </c>
       <c r="H802" t="n">
         <v>81492</v>
@@ -23656,7 +23656,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G803" t="n">
-        <v>2.52840304374695</v>
+        <v>2.52840280532837</v>
       </c>
       <c r="H803" t="n">
         <v>48628</v>
@@ -23685,7 +23685,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G804" t="n">
-        <v>2.49639773368835</v>
+        <v>2.49639797210693</v>
       </c>
       <c r="H804" t="n">
         <v>123967</v>
@@ -23714,7 +23714,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>2.49284195899963</v>
+        <v>2.49284172058105</v>
       </c>
       <c r="H805" t="n">
         <v>67850</v>
@@ -23743,7 +23743,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>2.50350999832153</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H806" t="n">
         <v>42553</v>
@@ -23772,7 +23772,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>2.49639773368835</v>
+        <v>2.49639797210693</v>
       </c>
       <c r="H807" t="n">
         <v>76903</v>
@@ -23801,7 +23801,7 @@
         <v>3.5</v>
       </c>
       <c r="G808" t="n">
-        <v>2.48928546905518</v>
+        <v>2.48928570747375</v>
       </c>
       <c r="H808" t="n">
         <v>47766</v>
@@ -23917,7 +23917,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>2.37548995018005</v>
+        <v>2.37548971176147</v>
       </c>
       <c r="H812" t="n">
         <v>91593</v>
@@ -23946,7 +23946,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G813" t="n">
-        <v>2.37548995018005</v>
+        <v>2.37548971176147</v>
       </c>
       <c r="H813" t="n">
         <v>67492</v>
@@ -23975,7 +23975,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G814" t="n">
-        <v>2.34704041481018</v>
+        <v>2.34704065322876</v>
       </c>
       <c r="H814" t="n">
         <v>64507</v>
@@ -24004,7 +24004,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>2.32570385932922</v>
+        <v>2.32570433616638</v>
       </c>
       <c r="H815" t="n">
         <v>86372</v>
@@ -24062,7 +24062,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G817" t="n">
-        <v>2.27236223220825</v>
+        <v>2.27236199378967</v>
       </c>
       <c r="H817" t="n">
         <v>146028</v>
@@ -24091,7 +24091,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G818" t="n">
-        <v>2.27591872215271</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H818" t="n">
         <v>137063</v>
@@ -24120,7 +24120,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G819" t="n">
-        <v>2.27591872215271</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H819" t="n">
         <v>243571</v>
@@ -24149,7 +24149,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G820" t="n">
-        <v>2.27591872215271</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H820" t="n">
         <v>105828</v>
@@ -24178,7 +24178,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G821" t="n">
-        <v>2.27591872215271</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H821" t="n">
         <v>116326</v>
@@ -24207,7 +24207,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G822" t="n">
-        <v>2.28658652305603</v>
+        <v>2.28658676147461</v>
       </c>
       <c r="H822" t="n">
         <v>108669</v>
@@ -24236,7 +24236,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>2.27236223220825</v>
+        <v>2.27236199378967</v>
       </c>
       <c r="H823" t="n">
         <v>63237</v>
@@ -24294,7 +24294,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>2.26880598068237</v>
+        <v>2.26880621910095</v>
       </c>
       <c r="H825" t="n">
         <v>70107</v>
@@ -24381,7 +24381,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G828" t="n">
-        <v>2.32214784622192</v>
+        <v>2.3221480846405</v>
       </c>
       <c r="H828" t="n">
         <v>344993</v>
@@ -24410,7 +24410,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>2.35415291786194</v>
+        <v>2.35415267944336</v>
       </c>
       <c r="H829" t="n">
         <v>234469</v>
@@ -24468,7 +24468,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G831" t="n">
-        <v>2.35770916938782</v>
+        <v>2.3577094078064</v>
       </c>
       <c r="H831" t="n">
         <v>178502</v>
@@ -24497,7 +24497,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>2.36837768554688</v>
+        <v>2.36837720870972</v>
       </c>
       <c r="H832" t="n">
         <v>96015</v>
@@ -24555,7 +24555,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G834" t="n">
-        <v>2.30081105232239</v>
+        <v>2.30081081390381</v>
       </c>
       <c r="H834" t="n">
         <v>103372</v>
@@ -24613,7 +24613,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G836" t="n">
-        <v>2.28658652305603</v>
+        <v>2.28658676147461</v>
       </c>
       <c r="H836" t="n">
         <v>63039</v>
@@ -24642,7 +24642,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G837" t="n">
-        <v>2.3612654209137</v>
+        <v>2.36126518249512</v>
       </c>
       <c r="H837" t="n">
         <v>143505</v>
@@ -24671,7 +24671,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G838" t="n">
-        <v>2.37548995018005</v>
+        <v>2.37548971176147</v>
       </c>
       <c r="H838" t="n">
         <v>153463</v>
@@ -24758,7 +24758,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>2.52129101753235</v>
+        <v>2.52129077911377</v>
       </c>
       <c r="H841" t="n">
         <v>189397</v>
@@ -24816,7 +24816,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G843" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H843" t="n">
         <v>56530</v>
@@ -24874,7 +24874,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G845" t="n">
-        <v>2.5817449092865</v>
+        <v>2.58174467086792</v>
       </c>
       <c r="H845" t="n">
         <v>178328</v>
@@ -24903,7 +24903,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>2.58530068397522</v>
+        <v>2.5853009223938</v>
       </c>
       <c r="H846" t="n">
         <v>68274</v>
@@ -24932,7 +24932,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.60308146476746</v>
+        <v>2.60308170318604</v>
       </c>
       <c r="H847" t="n">
         <v>177657</v>
@@ -24961,7 +24961,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G848" t="n">
-        <v>2.4786171913147</v>
+        <v>2.47861695289612</v>
       </c>
       <c r="H848" t="n">
         <v>218311</v>
@@ -25077,7 +25077,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G852" t="n">
-        <v>2.35415291786194</v>
+        <v>2.35415267944336</v>
       </c>
       <c r="H852" t="n">
         <v>91389</v>
@@ -25106,7 +25106,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.3612654209137</v>
+        <v>2.36126518249512</v>
       </c>
       <c r="H853" t="n">
         <v>119893</v>
@@ -25193,7 +25193,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G856" t="n">
-        <v>2.42057490348816</v>
+        <v>2.42057466506958</v>
       </c>
       <c r="H856" t="n">
         <v>67266</v>
@@ -25222,7 +25222,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G857" t="n">
-        <v>2.47617769241333</v>
+        <v>2.47617745399475</v>
       </c>
       <c r="H857" t="n">
         <v>233867</v>
@@ -25309,7 +25309,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.37238597869873</v>
+        <v>2.37238574028015</v>
       </c>
       <c r="H860" t="n">
         <v>119077</v>
@@ -25338,7 +25338,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G861" t="n">
-        <v>2.38350605964661</v>
+        <v>2.38350629806519</v>
       </c>
       <c r="H861" t="n">
         <v>36228</v>
@@ -25570,7 +25570,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>2.09437203407288</v>
+        <v>2.0943717956543</v>
       </c>
       <c r="H869" t="n">
         <v>106032</v>
@@ -25628,7 +25628,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G871" t="n">
-        <v>2.09437203407288</v>
+        <v>2.0943717956543</v>
       </c>
       <c r="H871" t="n">
         <v>47525</v>
@@ -25657,7 +25657,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05359625816345</v>
+        <v>2.05359649658203</v>
       </c>
       <c r="H872" t="n">
         <v>132549</v>
@@ -25715,7 +25715,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>2.0758376121521</v>
+        <v>2.07583737373352</v>
       </c>
       <c r="H874" t="n">
         <v>63145</v>
@@ -25773,7 +25773,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>2.12031960487366</v>
+        <v>2.12031984329224</v>
       </c>
       <c r="H876" t="n">
         <v>101590</v>
@@ -25802,7 +25802,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G877" t="n">
-        <v>2.20187067985535</v>
+        <v>2.20187091827393</v>
       </c>
       <c r="H877" t="n">
         <v>165127</v>
@@ -25831,7 +25831,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>2.09437203407288</v>
+        <v>2.0943717956543</v>
       </c>
       <c r="H878" t="n">
         <v>212088</v>
@@ -25976,7 +25976,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G883" t="n">
-        <v>2.1091992855072</v>
+        <v>2.10919904708862</v>
       </c>
       <c r="H883" t="n">
         <v>127362</v>
@@ -26005,7 +26005,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G884" t="n">
-        <v>2.03135561943054</v>
+        <v>2.03135514259338</v>
       </c>
       <c r="H884" t="n">
         <v>170336</v>
@@ -26063,7 +26063,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G886" t="n">
-        <v>2.01652789115906</v>
+        <v>2.01652812957764</v>
       </c>
       <c r="H886" t="n">
         <v>78138</v>
@@ -26092,7 +26092,7 @@
         <v>2.75</v>
       </c>
       <c r="G887" t="n">
-        <v>2.03876876831055</v>
+        <v>2.03876900672913</v>
       </c>
       <c r="H887" t="n">
         <v>88705</v>
@@ -26121,7 +26121,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>2.37609267234802</v>
+        <v>2.37609243392944</v>
       </c>
       <c r="H888" t="n">
         <v>1054436</v>
@@ -26179,7 +26179,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.2834210395813</v>
+        <v>2.28342151641846</v>
       </c>
       <c r="H890" t="n">
         <v>233336</v>
@@ -26266,7 +26266,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G893" t="n">
-        <v>2.24635291099548</v>
+        <v>2.2463526725769</v>
       </c>
       <c r="H893" t="n">
         <v>100791</v>
@@ -26440,7 +26440,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G899" t="n">
-        <v>2.27971458435059</v>
+        <v>2.27971434593201</v>
       </c>
       <c r="H899" t="n">
         <v>102850</v>
@@ -26469,7 +26469,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.30566263198853</v>
+        <v>2.30566239356995</v>
       </c>
       <c r="H900" t="n">
         <v>66468</v>
@@ -26498,7 +26498,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G901" t="n">
-        <v>2.2834210395813</v>
+        <v>2.28342151641846</v>
       </c>
       <c r="H901" t="n">
         <v>85699</v>
@@ -26585,7 +26585,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G904" t="n">
-        <v>2.26118040084839</v>
+        <v>2.26117992401123</v>
       </c>
       <c r="H904" t="n">
         <v>41843</v>
@@ -26643,7 +26643,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G906" t="n">
-        <v>2.26118040084839</v>
+        <v>2.26117992401123</v>
       </c>
       <c r="H906" t="n">
         <v>93112</v>
@@ -26672,7 +26672,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.24635291099548</v>
+        <v>2.2463526725769</v>
       </c>
       <c r="H907" t="n">
         <v>113173</v>
@@ -26701,7 +26701,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>2.2834210395813</v>
+        <v>2.28342151641846</v>
       </c>
       <c r="H908" t="n">
         <v>180734</v>
@@ -26730,7 +26730,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>2.26859378814697</v>
+        <v>2.26859354972839</v>
       </c>
       <c r="H909" t="n">
         <v>88883</v>
@@ -26788,7 +26788,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G911" t="n">
-        <v>2.2500593662262</v>
+        <v>2.25005960464478</v>
       </c>
       <c r="H911" t="n">
         <v>43162</v>
@@ -27049,7 +27049,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G920" t="n">
-        <v>2.17221570014954</v>
+        <v>2.17221593856812</v>
       </c>
       <c r="H920" t="n">
         <v>133484</v>
@@ -27078,7 +27078,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G921" t="n">
-        <v>2.15368127822876</v>
+        <v>2.15368151664734</v>
       </c>
       <c r="H921" t="n">
         <v>83002</v>
@@ -27136,7 +27136,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>2.19074988365173</v>
+        <v>2.19074964523315</v>
       </c>
       <c r="H923" t="n">
         <v>103378</v>
@@ -27194,7 +27194,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G925" t="n">
-        <v>2.12031960487366</v>
+        <v>2.12031984329224</v>
       </c>
       <c r="H925" t="n">
         <v>112906</v>
@@ -27252,7 +27252,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G927" t="n">
-        <v>2.1091992855072</v>
+        <v>2.10919904708862</v>
       </c>
       <c r="H927" t="n">
         <v>127215</v>
@@ -27310,7 +27310,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G929" t="n">
-        <v>2.15738821029663</v>
+        <v>2.15738844871521</v>
       </c>
       <c r="H929" t="n">
         <v>49771</v>
@@ -27368,7 +27368,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>2.19816374778748</v>
+        <v>2.1981635093689</v>
       </c>
       <c r="H931" t="n">
         <v>48763</v>
@@ -27397,7 +27397,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G932" t="n">
-        <v>2.19816374778748</v>
+        <v>2.1981635093689</v>
       </c>
       <c r="H932" t="n">
         <v>51651</v>
@@ -27455,7 +27455,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>2.16850900650024</v>
+        <v>2.16850876808167</v>
       </c>
       <c r="H934" t="n">
         <v>79342</v>
@@ -27571,7 +27571,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G938" t="n">
-        <v>2.55402159690857</v>
+        <v>2.55402135848999</v>
       </c>
       <c r="H938" t="n">
         <v>605667</v>
@@ -27600,7 +27600,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G939" t="n">
-        <v>2.52807354927063</v>
+        <v>2.52807378768921</v>
       </c>
       <c r="H939" t="n">
         <v>638409</v>
@@ -27658,7 +27658,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>2.63927912712097</v>
+        <v>2.63927888870239</v>
       </c>
       <c r="H941" t="n">
         <v>881119</v>
@@ -27687,7 +27687,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G942" t="n">
-        <v>2.79126000404358</v>
+        <v>2.79126024246216</v>
       </c>
       <c r="H942" t="n">
         <v>486765</v>
@@ -27890,7 +27890,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G949" t="n">
-        <v>2.73565745353699</v>
+        <v>2.73565721511841</v>
       </c>
       <c r="H949" t="n">
         <v>92966</v>
@@ -27919,7 +27919,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G950" t="n">
-        <v>2.73565745353699</v>
+        <v>2.73565721511841</v>
       </c>
       <c r="H950" t="n">
         <v>94593</v>
@@ -28006,7 +28006,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>2.73565745353699</v>
+        <v>2.73565721511841</v>
       </c>
       <c r="H953" t="n">
         <v>100795</v>
@@ -28122,7 +28122,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G957" t="n">
-        <v>2.69858884811401</v>
+        <v>2.69858908653259</v>
       </c>
       <c r="H957" t="n">
         <v>64578</v>
@@ -28151,7 +28151,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G958" t="n">
-        <v>2.72824358940125</v>
+        <v>2.72824382781982</v>
       </c>
       <c r="H958" t="n">
         <v>98599</v>
@@ -28238,7 +28238,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G961" t="n">
-        <v>2.76160526275635</v>
+        <v>2.76160550117493</v>
       </c>
       <c r="H961" t="n">
         <v>97307</v>
@@ -28267,7 +28267,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G962" t="n">
-        <v>2.76901912689209</v>
+        <v>2.76901888847351</v>
       </c>
       <c r="H962" t="n">
         <v>88960</v>
@@ -28296,7 +28296,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G963" t="n">
-        <v>2.76531219482422</v>
+        <v>2.76531195640564</v>
       </c>
       <c r="H963" t="n">
         <v>96254</v>
@@ -28325,7 +28325,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>2.76531219482422</v>
+        <v>2.76531195640564</v>
       </c>
       <c r="H964" t="n">
         <v>89082</v>
@@ -28383,7 +28383,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G966" t="n">
-        <v>2.70970940589905</v>
+        <v>2.70970916748047</v>
       </c>
       <c r="H966" t="n">
         <v>148307</v>
@@ -28412,7 +28412,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G967" t="n">
-        <v>2.72453665733337</v>
+        <v>2.72453689575195</v>
       </c>
       <c r="H967" t="n">
         <v>92773</v>
@@ -28441,7 +28441,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.70970940589905</v>
+        <v>2.70970916748047</v>
       </c>
       <c r="H968" t="n">
         <v>42501</v>
@@ -28499,7 +28499,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G970" t="n">
-        <v>2.6689338684082</v>
+        <v>2.66893410682678</v>
       </c>
       <c r="H970" t="n">
         <v>41494</v>
@@ -28528,7 +28528,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>2.75048470497131</v>
+        <v>2.75048494338989</v>
       </c>
       <c r="H971" t="n">
         <v>125515</v>
@@ -28557,7 +28557,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>2.91729331016541</v>
+        <v>2.91729307174683</v>
       </c>
       <c r="H972" t="n">
         <v>834985</v>
@@ -28615,7 +28615,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G974" t="n">
-        <v>2.85427641868591</v>
+        <v>2.85427665710449</v>
       </c>
       <c r="H974" t="n">
         <v>200919</v>
@@ -28673,7 +28673,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G976" t="n">
-        <v>2.76160526275635</v>
+        <v>2.76160550117493</v>
       </c>
       <c r="H976" t="n">
         <v>184807</v>
@@ -28760,7 +28760,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>2.89875888824463</v>
+        <v>2.89875864982605</v>
       </c>
       <c r="H979" t="n">
         <v>279460</v>
@@ -28789,7 +28789,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G980" t="n">
-        <v>2.90987920761108</v>
+        <v>2.90987944602966</v>
       </c>
       <c r="H980" t="n">
         <v>729798</v>
@@ -28847,7 +28847,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.93582725524902</v>
+        <v>2.9358274936676</v>
       </c>
       <c r="H982" t="n">
         <v>141285</v>
@@ -28876,7 +28876,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G983" t="n">
-        <v>2.95806837081909</v>
+        <v>2.95806860923767</v>
       </c>
       <c r="H983" t="n">
         <v>147298</v>
@@ -28905,7 +28905,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G984" t="n">
-        <v>3.05444669723511</v>
+        <v>3.05444645881653</v>
       </c>
       <c r="H984" t="n">
         <v>335251</v>
@@ -28934,7 +28934,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G985" t="n">
-        <v>2.98772311210632</v>
+        <v>2.98772358894348</v>
       </c>
       <c r="H985" t="n">
         <v>231299</v>
@@ -29021,7 +29021,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G988" t="n">
-        <v>2.80608749389648</v>
+        <v>2.80608773231506</v>
       </c>
       <c r="H988" t="n">
         <v>129247</v>
@@ -29050,7 +29050,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>2.96177506446838</v>
+        <v>2.96177554130554</v>
       </c>
       <c r="H989" t="n">
         <v>478994</v>
@@ -29108,7 +29108,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G991" t="n">
-        <v>2.97660279273987</v>
+        <v>2.97660255432129</v>
       </c>
       <c r="H991" t="n">
         <v>229076</v>
@@ -29166,7 +29166,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>3.22496175765991</v>
+        <v>3.22496151924133</v>
       </c>
       <c r="H993" t="n">
         <v>309322</v>
@@ -29195,7 +29195,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G994" t="n">
-        <v>3.3065128326416</v>
+        <v>3.30651259422302</v>
       </c>
       <c r="H994" t="n">
         <v>868963</v>
@@ -29224,7 +29224,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>3.39547657966614</v>
+        <v>3.39547681808472</v>
       </c>
       <c r="H995" t="n">
         <v>642201</v>
@@ -29253,7 +29253,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G996" t="n">
-        <v>3.40659737586975</v>
+        <v>3.40659785270691</v>
       </c>
       <c r="H996" t="n">
         <v>206522</v>
@@ -29282,7 +29282,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>3.41771841049194</v>
+        <v>3.41771817207336</v>
       </c>
       <c r="H997" t="n">
         <v>202987</v>
@@ -29311,7 +29311,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G998" t="n">
-        <v>3.48073482513428</v>
+        <v>3.4807345867157</v>
       </c>
       <c r="H998" t="n">
         <v>434716</v>
@@ -29340,7 +29340,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G999" t="n">
-        <v>3.52892398834229</v>
+        <v>3.52892374992371</v>
       </c>
       <c r="H999" t="n">
         <v>532506</v>
@@ -29398,7 +29398,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.59564709663391</v>
+        <v>3.59564733505249</v>
       </c>
       <c r="H1001" t="n">
         <v>333775</v>
@@ -29427,7 +29427,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.68461179733276</v>
+        <v>3.68461155891418</v>
       </c>
       <c r="H1002" t="n">
         <v>738133</v>
@@ -29456,7 +29456,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.65866351127625</v>
+        <v>3.65866374969482</v>
       </c>
       <c r="H1003" t="n">
         <v>1079301</v>
@@ -29485,7 +29485,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.82547187805176</v>
+        <v>3.82547211647034</v>
       </c>
       <c r="H1004" t="n">
         <v>554441</v>
@@ -29514,7 +29514,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.79581689834595</v>
+        <v>3.79581737518311</v>
       </c>
       <c r="H1005" t="n">
         <v>332417</v>
@@ -29543,7 +29543,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.79581689834595</v>
+        <v>3.79581737518311</v>
       </c>
       <c r="H1006" t="n">
         <v>349628</v>
@@ -29601,7 +29601,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.81805849075317</v>
+        <v>3.81805872917175</v>
       </c>
       <c r="H1008" t="n">
         <v>172882</v>
@@ -29659,7 +29659,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.81805849075317</v>
+        <v>3.81805872917175</v>
       </c>
       <c r="H1010" t="n">
         <v>141592</v>
@@ -29688,7 +29688,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.79581689834595</v>
+        <v>3.79581737518311</v>
       </c>
       <c r="H1011" t="n">
         <v>151303</v>
@@ -29746,7 +29746,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.81064438819885</v>
+        <v>3.81064414978027</v>
       </c>
       <c r="H1013" t="n">
         <v>243495</v>
@@ -29775,7 +29775,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.79581689834595</v>
+        <v>3.79581737518311</v>
       </c>
       <c r="H1014" t="n">
         <v>102689</v>
@@ -29804,7 +29804,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.84029936790466</v>
+        <v>3.84029960632324</v>
       </c>
       <c r="H1015" t="n">
         <v>295814</v>
@@ -29862,7 +29862,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.95891904830933</v>
+        <v>3.95891928672791</v>
       </c>
       <c r="H1017" t="n">
         <v>495513</v>
@@ -29949,7 +29949,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.94409155845642</v>
+        <v>3.944091796875</v>
       </c>
       <c r="H1020" t="n">
         <v>587792</v>
@@ -30007,7 +30007,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.85512685775757</v>
+        <v>3.85512661933899</v>
       </c>
       <c r="H1022" t="n">
         <v>233331</v>
@@ -30123,7 +30123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.85512685775757</v>
+        <v>3.85512661933899</v>
       </c>
       <c r="H1026" t="n">
         <v>83051</v>
@@ -30152,7 +30152,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.84771323204041</v>
+        <v>3.84771299362183</v>
       </c>
       <c r="H1027" t="n">
         <v>72510</v>
@@ -30181,7 +30181,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.81805849075317</v>
+        <v>3.81805872917175</v>
       </c>
       <c r="H1028" t="n">
         <v>102175</v>
@@ -30210,7 +30210,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.81064438819885</v>
+        <v>3.81064414978027</v>
       </c>
       <c r="H1029" t="n">
         <v>213214</v>
@@ -30239,7 +30239,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.85512685775757</v>
+        <v>3.85512661933899</v>
       </c>
       <c r="H1030" t="n">
         <v>156105</v>
@@ -30268,7 +30268,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.78840398788452</v>
+        <v>3.78840327262878</v>
       </c>
       <c r="H1031" t="n">
         <v>116338</v>
@@ -30297,7 +30297,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.83288621902466</v>
+        <v>3.8328857421875</v>
       </c>
       <c r="H1032" t="n">
         <v>299811</v>
@@ -30326,7 +30326,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.79581689834595</v>
+        <v>3.79581737518311</v>
       </c>
       <c r="H1033" t="n">
         <v>281130</v>
@@ -30355,7 +30355,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.81805849075317</v>
+        <v>3.81805872917175</v>
       </c>
       <c r="H1034" t="n">
         <v>149802</v>
@@ -30413,7 +30413,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.60676741600037</v>
+        <v>3.60676765441895</v>
       </c>
       <c r="H1036" t="n">
         <v>192935</v>
@@ -30442,7 +30442,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.47332072257996</v>
+        <v>3.47332096099854</v>
       </c>
       <c r="H1037" t="n">
         <v>353099</v>
@@ -30471,7 +30471,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.60306072235107</v>
+        <v>3.6030604839325</v>
       </c>
       <c r="H1038" t="n">
         <v>205159</v>
@@ -30500,7 +30500,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.7809898853302</v>
+        <v>3.78098964691162</v>
       </c>
       <c r="H1039" t="n">
         <v>191733</v>
@@ -30587,7 +30587,7 @@
         <v>5</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.70685243606567</v>
+        <v>3.70685291290283</v>
       </c>
       <c r="H1042" t="n">
         <v>87676</v>
@@ -30616,7 +30616,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.67719793319702</v>
+        <v>3.67719841003418</v>
       </c>
       <c r="H1043" t="n">
         <v>66231</v>
@@ -30645,7 +30645,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.7809898853302</v>
+        <v>3.78098964691162</v>
       </c>
       <c r="H1044" t="n">
         <v>103859</v>
@@ -30674,7 +30674,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.77357625961304</v>
+        <v>3.77357649803162</v>
       </c>
       <c r="H1045" t="n">
         <v>100770</v>
@@ -30703,7 +30703,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.83288621902466</v>
+        <v>3.8328857421875</v>
       </c>
       <c r="H1046" t="n">
         <v>155005</v>
@@ -30732,7 +30732,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.92926359176636</v>
+        <v>3.92926383018494</v>
       </c>
       <c r="H1047" t="n">
         <v>476926</v>
@@ -30819,7 +30819,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.0478835105896</v>
+        <v>4.04788303375244</v>
       </c>
       <c r="H1050" t="n">
         <v>270277</v>
@@ -30848,7 +30848,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.06271123886108</v>
+        <v>4.06271028518677</v>
       </c>
       <c r="H1051" t="n">
         <v>169274</v>
@@ -30877,7 +30877,7 @@
         <v>5.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.07753753662109</v>
+        <v>4.07753801345825</v>
       </c>
       <c r="H1052" t="n">
         <v>302357</v>
@@ -30906,7 +30906,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.79581689834595</v>
+        <v>3.79581737518311</v>
       </c>
       <c r="H1053" t="n">
         <v>746712</v>
@@ -30964,7 +30964,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.78840398788452</v>
+        <v>3.78840327262878</v>
       </c>
       <c r="H1055" t="n">
         <v>373798</v>
@@ -30993,7 +30993,7 @@
         <v>5</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.70685243606567</v>
+        <v>3.70685291290283</v>
       </c>
       <c r="H1056" t="n">
         <v>254047</v>
@@ -31022,7 +31022,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.63271617889404</v>
+        <v>3.63271546363831</v>
       </c>
       <c r="H1057" t="n">
         <v>486017</v>
@@ -31080,7 +31080,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.66607713699341</v>
+        <v>3.66607737541199</v>
       </c>
       <c r="H1059" t="n">
         <v>331600</v>
@@ -31109,7 +31109,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.71426677703857</v>
+        <v>3.71426653862</v>
       </c>
       <c r="H1060" t="n">
         <v>412668</v>
@@ -31138,7 +31138,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.62159538269043</v>
+        <v>3.62159514427185</v>
       </c>
       <c r="H1061" t="n">
         <v>217946</v>
@@ -31167,7 +31167,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.55857872962952</v>
+        <v>3.55857849121094</v>
       </c>
       <c r="H1062" t="n">
         <v>398454</v>
@@ -31370,7 +31370,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.29083514213562</v>
+        <v>2.29083466529846</v>
       </c>
       <c r="H1069" t="n">
         <v>496099</v>
@@ -31399,7 +31399,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.15738821029663</v>
+        <v>2.15738844871521</v>
       </c>
       <c r="H1070" t="n">
         <v>234532</v>
@@ -31428,7 +31428,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.06471729278564</v>
+        <v>2.06471705436707</v>
       </c>
       <c r="H1071" t="n">
         <v>384018</v>
@@ -31486,7 +31486,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.20928430557251</v>
+        <v>2.20928406715393</v>
       </c>
       <c r="H1073" t="n">
         <v>277616</v>
@@ -31515,7 +31515,7 @@
         <v>3.125</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.3167827129364</v>
+        <v>2.31678318977356</v>
       </c>
       <c r="H1074" t="n">
         <v>253242</v>
@@ -31573,7 +31573,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.37238597869873</v>
+        <v>2.37238574028015</v>
       </c>
       <c r="H1076" t="n">
         <v>180047</v>
@@ -31602,7 +31602,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.34273076057434</v>
+        <v>2.34273099899292</v>
       </c>
       <c r="H1077" t="n">
         <v>125940</v>
@@ -31660,7 +31660,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.38721299171448</v>
+        <v>2.38721346855164</v>
       </c>
       <c r="H1079" t="n">
         <v>228291</v>
@@ -31689,7 +31689,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.2834210395813</v>
+        <v>2.28342151641846</v>
       </c>
       <c r="H1080" t="n">
         <v>79106</v>
@@ -31718,7 +31718,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.26118040084839</v>
+        <v>2.26117992401123</v>
       </c>
       <c r="H1081" t="n">
         <v>248140</v>
@@ -31805,7 +31805,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.53548741340637</v>
+        <v>2.53548717498779</v>
       </c>
       <c r="H1084" t="n">
         <v>286119</v>
@@ -31834,7 +31834,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.62815856933594</v>
+        <v>2.62815880775452</v>
       </c>
       <c r="H1085" t="n">
         <v>155985</v>
@@ -31892,7 +31892,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.6689338684082</v>
+        <v>2.66893410682678</v>
       </c>
       <c r="H1087" t="n">
         <v>146976</v>
@@ -31950,7 +31950,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.76901912689209</v>
+        <v>2.76901888847351</v>
       </c>
       <c r="H1089" t="n">
         <v>947909</v>
@@ -32037,7 +32037,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.8246214389801</v>
+        <v>2.82462167739868</v>
       </c>
       <c r="H1092" t="n">
         <v>216590</v>
@@ -32095,7 +32095,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.01737809181213</v>
+        <v>3.01737856864929</v>
       </c>
       <c r="H1094" t="n">
         <v>245764</v>
@@ -32153,7 +32153,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.17306590080261</v>
+        <v>3.17306637763977</v>
       </c>
       <c r="H1096" t="n">
         <v>403206</v>
@@ -32182,7 +32182,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.18789386749268</v>
+        <v>3.18789315223694</v>
       </c>
       <c r="H1097" t="n">
         <v>381925</v>
@@ -32240,7 +32240,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.18789386749268</v>
+        <v>3.18789315223694</v>
       </c>
       <c r="H1099" t="n">
         <v>151019</v>
@@ -32269,7 +32269,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.07668781280518</v>
+        <v>3.07668805122375</v>
       </c>
       <c r="H1100" t="n">
         <v>96382</v>
@@ -32298,7 +32298,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.11004972457886</v>
+        <v>3.11004948616028</v>
       </c>
       <c r="H1101" t="n">
         <v>167235</v>
@@ -32356,7 +32356,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.11375641822815</v>
+        <v>3.11375617980957</v>
       </c>
       <c r="H1103" t="n">
         <v>64482</v>
@@ -32385,7 +32385,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.11004972457886</v>
+        <v>3.11004948616028</v>
       </c>
       <c r="H1104" t="n">
         <v>193043</v>
@@ -32617,7 +32617,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.97289609909058</v>
+        <v>2.97289633750916</v>
       </c>
       <c r="H1112" t="n">
         <v>174569</v>
@@ -32646,7 +32646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.98772311210632</v>
+        <v>2.98772358894348</v>
       </c>
       <c r="H1113" t="n">
         <v>369835</v>
@@ -32791,7 +32791,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.26944422721863</v>
+        <v>3.26944398880005</v>
       </c>
       <c r="H1118" t="n">
         <v>303345</v>
@@ -32820,7 +32820,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.31392598152161</v>
+        <v>3.31392621994019</v>
       </c>
       <c r="H1119" t="n">
         <v>234448</v>
@@ -32936,7 +32936,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.22496175765991</v>
+        <v>3.22496151924133</v>
       </c>
       <c r="H1123" t="n">
         <v>114302</v>
@@ -32994,7 +32994,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17677283287048</v>
+        <v>3.1767725944519</v>
       </c>
       <c r="H1125" t="n">
         <v>216177</v>
@@ -33023,7 +33023,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.10634255409241</v>
+        <v>3.10634279251099</v>
       </c>
       <c r="H1126" t="n">
         <v>157535</v>
@@ -33110,7 +33110,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.77643251419067</v>
+        <v>2.77643275260925</v>
       </c>
       <c r="H1129" t="n">
         <v>482471</v>
@@ -33139,7 +33139,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.75048470497131</v>
+        <v>2.75048494338989</v>
       </c>
       <c r="H1130" t="n">
         <v>211708</v>
@@ -33197,7 +33197,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.77643251419067</v>
+        <v>2.77643275260925</v>
       </c>
       <c r="H1132" t="n">
         <v>136838</v>
@@ -33226,7 +33226,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.79126000404358</v>
+        <v>2.79126024246216</v>
       </c>
       <c r="H1133" t="n">
         <v>110451</v>
@@ -33284,7 +33284,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.05444669723511</v>
+        <v>3.05444645881653</v>
       </c>
       <c r="H1135" t="n">
         <v>906769</v>
@@ -33313,7 +33313,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.93582725524902</v>
+        <v>2.9358274936676</v>
       </c>
       <c r="H1136" t="n">
         <v>472549</v>
@@ -33400,7 +33400,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.75419163703918</v>
+        <v>2.75419139862061</v>
       </c>
       <c r="H1139" t="n">
         <v>261862</v>
@@ -33487,7 +33487,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.83574247360229</v>
+        <v>2.83574223518372</v>
       </c>
       <c r="H1142" t="n">
         <v>94920</v>
@@ -33661,7 +33661,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.97289609909058</v>
+        <v>2.97289633750916</v>
       </c>
       <c r="H1148" t="n">
         <v>101837</v>
@@ -33719,7 +33719,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.05444669723511</v>
+        <v>3.05444645881653</v>
       </c>
       <c r="H1150" t="n">
         <v>85124</v>
@@ -33777,7 +33777,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.08780860900879</v>
+        <v>3.08780837059021</v>
       </c>
       <c r="H1152" t="n">
         <v>145042</v>
@@ -33806,7 +33806,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.11004972457886</v>
+        <v>3.11004948616028</v>
       </c>
       <c r="H1153" t="n">
         <v>260642</v>
@@ -33835,7 +33835,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.11004972457886</v>
+        <v>3.11004948616028</v>
       </c>
       <c r="H1154" t="n">
         <v>78988</v>
@@ -33864,7 +33864,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.12117004394531</v>
+        <v>3.12117028236389</v>
       </c>
       <c r="H1155" t="n">
         <v>89194</v>
@@ -33922,7 +33922,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.08780860900879</v>
+        <v>3.08780837059021</v>
       </c>
       <c r="H1157" t="n">
         <v>89877</v>
@@ -33980,7 +33980,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.06556725502014</v>
+        <v>3.06556749343872</v>
       </c>
       <c r="H1159" t="n">
         <v>97598</v>
@@ -34038,7 +34038,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.09892892837524</v>
+        <v>3.09892868995667</v>
       </c>
       <c r="H1161" t="n">
         <v>214220</v>
@@ -34067,7 +34067,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.18418645858765</v>
+        <v>3.18418669700623</v>
       </c>
       <c r="H1162" t="n">
         <v>152609</v>
@@ -34096,7 +34096,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.0915150642395</v>
+        <v>3.09151530265808</v>
       </c>
       <c r="H1163" t="n">
         <v>187881</v>
@@ -34125,7 +34125,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.10634255409241</v>
+        <v>3.10634279251099</v>
       </c>
       <c r="H1164" t="n">
         <v>90903</v>
@@ -34183,7 +34183,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.15453171730042</v>
+        <v>3.15453147888184</v>
       </c>
       <c r="H1166" t="n">
         <v>119978</v>
@@ -34212,7 +34212,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.22125482559204</v>
+        <v>3.2212553024292</v>
       </c>
       <c r="H1167" t="n">
         <v>93532</v>
@@ -34241,7 +34241,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.19160032272339</v>
+        <v>3.19160008430481</v>
       </c>
       <c r="H1168" t="n">
         <v>55140</v>
@@ -34328,7 +34328,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.35099482536316</v>
+        <v>3.35099506378174</v>
       </c>
       <c r="H1171" t="n">
         <v>67426</v>
@@ -34386,7 +34386,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.37323665618896</v>
+        <v>3.37323594093323</v>
       </c>
       <c r="H1173" t="n">
         <v>32881</v>
@@ -34415,7 +34415,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.55857872962952</v>
+        <v>3.55857849121094</v>
       </c>
       <c r="H1174" t="n">
         <v>195254</v>
@@ -34444,7 +34444,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.65866351127625</v>
+        <v>3.65866374969482</v>
       </c>
       <c r="H1175" t="n">
         <v>294092</v>
@@ -34502,7 +34502,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.58082008361816</v>
+        <v>3.58081936836243</v>
       </c>
       <c r="H1177" t="n">
         <v>88222</v>
@@ -34531,7 +34531,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.50668287277222</v>
+        <v>3.50668239593506</v>
       </c>
       <c r="H1178" t="n">
         <v>89172</v>
@@ -34560,7 +34560,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41771841049194</v>
+        <v>3.41771817207336</v>
       </c>
       <c r="H1179" t="n">
         <v>98749</v>
@@ -34589,7 +34589,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.70314598083496</v>
+        <v>3.70314574241638</v>
       </c>
       <c r="H1180" t="n">
         <v>607643</v>
@@ -34618,7 +34618,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.67719793319702</v>
+        <v>3.67719841003418</v>
       </c>
       <c r="H1181" t="n">
         <v>296317</v>
@@ -34792,7 +34792,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.92926359176636</v>
+        <v>3.92926383018494</v>
       </c>
       <c r="H1187" t="n">
         <v>142623</v>
@@ -34821,7 +34821,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.84771323204041</v>
+        <v>3.84771299362183</v>
       </c>
       <c r="H1188" t="n">
         <v>228820</v>
@@ -34850,7 +34850,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.79581689834595</v>
+        <v>3.79581737518311</v>
       </c>
       <c r="H1189" t="n">
         <v>155683</v>
@@ -34879,7 +34879,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.86254072189331</v>
+        <v>3.86254048347473</v>
       </c>
       <c r="H1190" t="n">
         <v>93171</v>
@@ -34908,7 +34908,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.34443140029907</v>
+        <v>4.34443187713623</v>
       </c>
       <c r="H1191" t="n">
         <v>1051492</v>
@@ -34966,7 +34966,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.55942916870117</v>
+        <v>4.55942869186401</v>
       </c>
       <c r="H1193" t="n">
         <v>521199</v>
@@ -35024,7 +35024,7 @@
         <v>6</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.44822311401367</v>
+        <v>4.44822359085083</v>
       </c>
       <c r="H1195" t="n">
         <v>130702</v>
@@ -35140,7 +35140,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.50011873245239</v>
+        <v>4.50011920928955</v>
       </c>
       <c r="H1199" t="n">
         <v>371285</v>
@@ -35169,7 +35169,7 @@
         <v>6</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.44822311401367</v>
+        <v>4.44822359085083</v>
       </c>
       <c r="H1200" t="n">
         <v>179244</v>
@@ -35227,7 +35227,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.01907873153687</v>
+        <v>5.01907825469971</v>
       </c>
       <c r="H1202" t="n">
         <v>675366</v>
@@ -35256,7 +35256,7 @@
         <v>6.75</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.00425148010254</v>
+        <v>5.00425100326538</v>
       </c>
       <c r="H1203" t="n">
         <v>310965</v>
@@ -35343,7 +35343,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.4194188117981</v>
+        <v>5.41941833496094</v>
       </c>
       <c r="H1206" t="n">
         <v>352753</v>
@@ -35372,7 +35372,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1207" t="n">
-        <v>5.59734773635864</v>
+        <v>5.59734725952148</v>
       </c>
       <c r="H1207" t="n">
         <v>525409</v>
@@ -35401,7 +35401,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.46390056610107</v>
+        <v>5.46390104293823</v>
       </c>
       <c r="H1208" t="n">
         <v>424268</v>
@@ -35430,7 +35430,7 @@
         <v>7.5</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.56027936935425</v>
+        <v>5.56027889251709</v>
       </c>
       <c r="H1209" t="n">
         <v>262844</v>
@@ -35459,7 +35459,7 @@
         <v>7.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.56027936935425</v>
+        <v>5.56027889251709</v>
       </c>
       <c r="H1210" t="n">
         <v>186425</v>
@@ -35488,7 +35488,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.58252000808716</v>
+        <v>5.58252048492432</v>
       </c>
       <c r="H1211" t="n">
         <v>199033</v>
@@ -35575,7 +35575,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.62700319290161</v>
+        <v>5.62700271606445</v>
       </c>
       <c r="H1214" t="n">
         <v>339811</v>
@@ -35662,7 +35662,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1217" t="n">
-        <v>5.70855283737183</v>
+        <v>5.70855331420898</v>
       </c>
       <c r="H1217" t="n">
         <v>336560</v>
@@ -35749,7 +35749,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.56769275665283</v>
+        <v>5.56769323348999</v>
       </c>
       <c r="H1220" t="n">
         <v>111918</v>
@@ -35778,7 +35778,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.5232105255127</v>
+        <v>5.52321100234985</v>
       </c>
       <c r="H1221" t="n">
         <v>113245</v>
@@ -35865,7 +35865,7 @@
         <v>7.25</v>
       </c>
       <c r="G1224" t="n">
-        <v>5.3749361038208</v>
+        <v>5.37493658065796</v>
       </c>
       <c r="H1224" t="n">
         <v>174643</v>
@@ -35894,7 +35894,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1225" t="n">
-        <v>5.15252494812012</v>
+        <v>5.15252542495728</v>
       </c>
       <c r="H1225" t="n">
         <v>390979</v>
@@ -35923,7 +35923,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1226" t="n">
-        <v>5.09321546554565</v>
+        <v>5.09321594238281</v>
       </c>
       <c r="H1226" t="n">
         <v>195209</v>
@@ -36039,7 +36039,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.50838327407837</v>
+        <v>5.50838279724121</v>
       </c>
       <c r="H1230" t="n">
         <v>619855</v>
@@ -36068,7 +36068,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.59734773635864</v>
+        <v>5.59734725952148</v>
       </c>
       <c r="H1231" t="n">
         <v>248006</v>
@@ -36155,7 +36155,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.69372606277466</v>
+        <v>5.6937255859375</v>
       </c>
       <c r="H1234" t="n">
         <v>364428</v>
@@ -36271,7 +36271,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.79010343551636</v>
+        <v>5.79010391235352</v>
       </c>
       <c r="H1238" t="n">
         <v>185181</v>
@@ -36300,7 +36300,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.51664733886719</v>
+        <v>6.51664638519287</v>
       </c>
       <c r="H1239" t="n">
         <v>1181498</v>
@@ -36358,7 +36358,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1241" t="n">
-        <v>6.56854295730591</v>
+        <v>6.56854248046875</v>
       </c>
       <c r="H1241" t="n">
         <v>708046</v>
@@ -36387,7 +36387,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1242" t="n">
-        <v>6.59078454971313</v>
+        <v>6.59078359603882</v>
       </c>
       <c r="H1242" t="n">
         <v>525574</v>
@@ -36416,7 +36416,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1243" t="n">
-        <v>6.33871793746948</v>
+        <v>6.33871841430664</v>
       </c>
       <c r="H1243" t="n">
         <v>535392</v>
@@ -36474,7 +36474,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1245" t="n">
-        <v>6.24234008789062</v>
+        <v>6.24234056472778</v>
       </c>
       <c r="H1245" t="n">
         <v>371423</v>
@@ -36561,7 +36561,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1248" t="n">
-        <v>6.24975347518921</v>
+        <v>6.24975395202637</v>
       </c>
       <c r="H1248" t="n">
         <v>354024</v>
@@ -36590,7 +36590,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1249" t="n">
-        <v>6.19785785675049</v>
+        <v>6.19785737991333</v>
       </c>
       <c r="H1249" t="n">
         <v>114330</v>
@@ -36619,7 +36619,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>6.183030128479</v>
+        <v>6.18303060531616</v>
       </c>
       <c r="H1250" t="n">
         <v>175266</v>
@@ -36648,7 +36648,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1251" t="n">
-        <v>6.62043952941895</v>
+        <v>6.62043905258179</v>
       </c>
       <c r="H1251" t="n">
         <v>688617</v>
@@ -36735,7 +36735,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1254" t="n">
-        <v>6.57595634460449</v>
+        <v>6.57595682144165</v>
       </c>
       <c r="H1254" t="n">
         <v>163814</v>
@@ -36793,7 +36793,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.11715745925903</v>
+        <v>7.11715698242188</v>
       </c>
       <c r="H1256" t="n">
         <v>593443</v>
@@ -36822,7 +36822,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1257" t="n">
-        <v>7.05784797668457</v>
+        <v>7.05784749984741</v>
       </c>
       <c r="H1257" t="n">
         <v>838572</v>
@@ -36851,7 +36851,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1258" t="n">
-        <v>7.065260887146</v>
+        <v>7.06526041030884</v>
       </c>
       <c r="H1258" t="n">
         <v>640753</v>
@@ -36880,7 +36880,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.05043363571167</v>
+        <v>7.05043411254883</v>
       </c>
       <c r="H1259" t="n">
         <v>255311</v>
@@ -36909,7 +36909,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1260" t="n">
-        <v>7.47301483154297</v>
+        <v>7.47301530838013</v>
       </c>
       <c r="H1260" t="n">
         <v>545649</v>
@@ -36938,7 +36938,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1261" t="n">
-        <v>7.54715251922607</v>
+        <v>7.54715299606323</v>
       </c>
       <c r="H1261" t="n">
         <v>292983</v>
@@ -36996,7 +36996,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>7.93266439437866</v>
+        <v>7.93266534805298</v>
       </c>
       <c r="H1263" t="n">
         <v>408058</v>
@@ -37025,7 +37025,7 @@
         <v>10.5</v>
       </c>
       <c r="G1264" t="n">
-        <v>7.78439140319824</v>
+        <v>7.78439044952393</v>
       </c>
       <c r="H1264" t="n">
         <v>534440</v>
@@ -37054,7 +37054,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1265" t="n">
-        <v>7.93266439437866</v>
+        <v>7.93266534805298</v>
       </c>
       <c r="H1265" t="n">
         <v>476309</v>
@@ -37083,7 +37083,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1266" t="n">
-        <v>7.94749307632446</v>
+        <v>7.94749212265015</v>
       </c>
       <c r="H1266" t="n">
         <v>283644</v>
@@ -37141,7 +37141,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.87335443496704</v>
+        <v>7.8733549118042</v>
       </c>
       <c r="H1268" t="n">
         <v>337710</v>
@@ -37170,7 +37170,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1269" t="n">
-        <v>7.88818311691284</v>
+        <v>7.88818359375</v>
       </c>
       <c r="H1269" t="n">
         <v>363211</v>
@@ -37228,7 +37228,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1271" t="n">
-        <v>8.05128383636475</v>
+        <v>8.05128479003906</v>
       </c>
       <c r="H1271" t="n">
         <v>456415</v>
@@ -37286,7 +37286,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1273" t="n">
-        <v>7.44336032867432</v>
+        <v>7.44335985183716</v>
       </c>
       <c r="H1273" t="n">
         <v>832254</v>
@@ -37315,7 +37315,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.68059873580933</v>
+        <v>7.68059921264648</v>
       </c>
       <c r="H1274" t="n">
         <v>508688</v>
@@ -37344,7 +37344,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>7.54715251922607</v>
+        <v>7.54715299606323</v>
       </c>
       <c r="H1275" t="n">
         <v>266888</v>
@@ -37373,7 +37373,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.59163379669189</v>
+        <v>7.59163475036621</v>
       </c>
       <c r="H1276" t="n">
         <v>279624</v>
@@ -37402,7 +37402,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1277" t="n">
-        <v>7.30250072479248</v>
+        <v>7.30250024795532</v>
       </c>
       <c r="H1277" t="n">
         <v>314055</v>
@@ -37431,7 +37431,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>7.3840503692627</v>
+        <v>7.38404989242554</v>
       </c>
       <c r="H1278" t="n">
         <v>359960</v>
@@ -37460,7 +37460,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1279" t="n">
-        <v>7.47301483154297</v>
+        <v>7.47301530838013</v>
       </c>
       <c r="H1279" t="n">
         <v>387332</v>
@@ -37489,7 +37489,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G1280" t="n">
-        <v>7.33215427398682</v>
+        <v>7.33215475082397</v>
       </c>
       <c r="H1280" t="n">
         <v>468812</v>
@@ -37518,7 +37518,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.35439586639404</v>
+        <v>7.35439682006836</v>
       </c>
       <c r="H1281" t="n">
         <v>158098</v>
@@ -37547,7 +37547,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.23577690124512</v>
+        <v>7.23577737808228</v>
       </c>
       <c r="H1282" t="n">
         <v>339904</v>
@@ -37576,7 +37576,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>7.35439586639404</v>
+        <v>7.35439682006836</v>
       </c>
       <c r="H1283" t="n">
         <v>177031</v>
@@ -37605,7 +37605,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1284" t="n">
-        <v>7.30250072479248</v>
+        <v>7.30250024795532</v>
       </c>
       <c r="H1284" t="n">
         <v>165936</v>
@@ -37634,7 +37634,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.32474040985107</v>
+        <v>7.32474088668823</v>
       </c>
       <c r="H1285" t="n">
         <v>250867</v>
@@ -37663,7 +37663,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.05784797668457</v>
+        <v>7.05784749984741</v>
       </c>
       <c r="H1286" t="n">
         <v>198903</v>
@@ -37692,7 +37692,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1287" t="n">
-        <v>7.32474040985107</v>
+        <v>7.32474088668823</v>
       </c>
       <c r="H1287" t="n">
         <v>347288</v>
@@ -37721,7 +37721,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1288" t="n">
-        <v>7.08008861541748</v>
+        <v>7.08008909225464</v>
       </c>
       <c r="H1288" t="n">
         <v>551582</v>
@@ -37750,7 +37750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.19129419326782</v>
+        <v>7.19129467010498</v>
       </c>
       <c r="H1289" t="n">
         <v>237577</v>
@@ -37866,7 +37866,7 @@
         <v>10</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.41370487213135</v>
+        <v>7.41370582580566</v>
       </c>
       <c r="H1293" t="n">
         <v>202382</v>
@@ -37895,7 +37895,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1294" t="n">
-        <v>7.47301483154297</v>
+        <v>7.47301530838013</v>
       </c>
       <c r="H1294" t="n">
         <v>249714</v>
@@ -37924,7 +37924,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.90301036834717</v>
+        <v>7.90300941467285</v>
       </c>
       <c r="H1295" t="n">
         <v>568968</v>
@@ -37953,7 +37953,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.87335443496704</v>
+        <v>7.8733549118042</v>
       </c>
       <c r="H1296" t="n">
         <v>326366</v>
@@ -38040,7 +38040,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1299" t="n">
-        <v>8.45162296295166</v>
+        <v>8.45162391662598</v>
       </c>
       <c r="H1299" t="n">
         <v>538848</v>
@@ -38156,7 +38156,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1303" t="n">
-        <v>8.34783172607422</v>
+        <v>8.34783267974854</v>
       </c>
       <c r="H1303" t="n">
         <v>239055</v>
@@ -38185,7 +38185,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>8.28852272033691</v>
+        <v>8.28852367401123</v>
       </c>
       <c r="H1304" t="n">
         <v>211448</v>
@@ -38214,7 +38214,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1305" t="n">
-        <v>8.45162296295166</v>
+        <v>8.45162391662598</v>
       </c>
       <c r="H1305" t="n">
         <v>122972</v>
@@ -38243,7 +38243,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1306" t="n">
-        <v>8.31817817687988</v>
+        <v>8.31817722320557</v>
       </c>
       <c r="H1306" t="n">
         <v>89949</v>
@@ -38301,7 +38301,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1308" t="n">
-        <v>8.16990280151367</v>
+        <v>8.1699047088623</v>
       </c>
       <c r="H1308" t="n">
         <v>576399</v>
@@ -38359,7 +38359,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.84370136260986</v>
+        <v>7.84369993209839</v>
       </c>
       <c r="H1310" t="n">
         <v>221178</v>
@@ -38417,7 +38417,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1312" t="n">
-        <v>7.90301036834717</v>
+        <v>7.90300941467285</v>
       </c>
       <c r="H1312" t="n">
         <v>1133698</v>
@@ -38446,7 +38446,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1313" t="n">
-        <v>7.85852718353271</v>
+        <v>7.85852766036987</v>
       </c>
       <c r="H1313" t="n">
         <v>533862</v>
@@ -38475,7 +38475,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.44336032867432</v>
+        <v>7.44335985183716</v>
       </c>
       <c r="H1314" t="n">
         <v>524870</v>
@@ -38504,7 +38504,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1315" t="n">
-        <v>7.30250072479248</v>
+        <v>7.30250024795532</v>
       </c>
       <c r="H1315" t="n">
         <v>832363</v>
@@ -38533,7 +38533,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1316" t="n">
-        <v>7.29508686065674</v>
+        <v>7.29508590698242</v>
       </c>
       <c r="H1316" t="n">
         <v>473082</v>
@@ -38562,7 +38562,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1317" t="n">
-        <v>7.44336032867432</v>
+        <v>7.44335985183716</v>
       </c>
       <c r="H1317" t="n">
         <v>378883</v>
@@ -38591,7 +38591,7 @@
         <v>10.5</v>
       </c>
       <c r="G1318" t="n">
-        <v>7.78439140319824</v>
+        <v>7.78439044952393</v>
       </c>
       <c r="H1318" t="n">
         <v>575662</v>
@@ -38620,7 +38620,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>7.69542646408081</v>
+        <v>7.69542598724365</v>
       </c>
       <c r="H1319" t="n">
         <v>388891</v>
@@ -38649,7 +38649,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1320" t="n">
-        <v>7.59163379669189</v>
+        <v>7.59163475036621</v>
       </c>
       <c r="H1320" t="n">
         <v>242496</v>
@@ -38678,7 +38678,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1321" t="n">
-        <v>7.51749706268311</v>
+        <v>7.51749801635742</v>
       </c>
       <c r="H1321" t="n">
         <v>215080</v>
@@ -38707,7 +38707,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1322" t="n">
-        <v>7.75473546981812</v>
+        <v>7.75473642349243</v>
       </c>
       <c r="H1322" t="n">
         <v>498215</v>
@@ -38765,7 +38765,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1324" t="n">
-        <v>7.62128877639771</v>
+        <v>7.62128829956055</v>
       </c>
       <c r="H1324" t="n">
         <v>262438</v>
@@ -38794,7 +38794,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1325" t="n">
-        <v>7.62128877639771</v>
+        <v>7.62128829956055</v>
       </c>
       <c r="H1325" t="n">
         <v>298270</v>
@@ -38823,7 +38823,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>7.65094375610352</v>
+        <v>7.65094423294067</v>
       </c>
       <c r="H1326" t="n">
         <v>193591</v>
@@ -38852,7 +38852,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1327" t="n">
-        <v>7.91783809661865</v>
+        <v>7.91783857345581</v>
       </c>
       <c r="H1327" t="n">
         <v>540331</v>
@@ -38881,7 +38881,7 @@
         <v>10.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>7.78439140319824</v>
+        <v>7.78439044952393</v>
       </c>
       <c r="H1328" t="n">
         <v>198079</v>
@@ -38910,7 +38910,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1329" t="n">
-        <v>7.84370136260986</v>
+        <v>7.84369993209839</v>
       </c>
       <c r="H1329" t="n">
         <v>200870</v>
@@ -39084,7 +39084,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G1335" t="n">
-        <v>8.16248893737793</v>
+        <v>8.16248989105225</v>
       </c>
       <c r="H1335" t="n">
         <v>181471</v>
@@ -39171,7 +39171,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1338" t="n">
-        <v>9.59333419799805</v>
+        <v>9.59333515167236</v>
       </c>
       <c r="H1338" t="n">
         <v>1383755</v>
@@ -39200,7 +39200,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1339" t="n">
-        <v>9.75643730163574</v>
+        <v>9.75643634796143</v>
       </c>
       <c r="H1339" t="n">
         <v>1219155</v>
@@ -39229,7 +39229,7 @@
         <v>13.5</v>
       </c>
       <c r="G1340" t="n">
-        <v>10.0085029602051</v>
+        <v>10.0085020065308</v>
       </c>
       <c r="H1340" t="n">
         <v>837762</v>
@@ -39287,7 +39287,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.68229961395264</v>
+        <v>9.68229866027832</v>
       </c>
       <c r="H1342" t="n">
         <v>618401</v>
@@ -39374,7 +39374,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.9566068649292</v>
+        <v>9.95660591125488</v>
       </c>
       <c r="H1345" t="n">
         <v>608465</v>
@@ -39403,7 +39403,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1346" t="n">
-        <v>10.0752248764038</v>
+        <v>10.0752258300781</v>
       </c>
       <c r="H1346" t="n">
         <v>298506</v>
@@ -39432,7 +39432,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1347" t="n">
-        <v>10.097466468811</v>
+        <v>10.0974655151367</v>
       </c>
       <c r="H1347" t="n">
         <v>478691</v>
@@ -39461,7 +39461,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1348" t="n">
-        <v>10.2160863876343</v>
+        <v>10.21608543396</v>
       </c>
       <c r="H1348" t="n">
         <v>466501</v>
@@ -39490,7 +39490,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1349" t="n">
-        <v>10.2383279800415</v>
+        <v>10.2383270263672</v>
       </c>
       <c r="H1349" t="n">
         <v>493981</v>
@@ -39519,7 +39519,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1350" t="n">
-        <v>10.1122941970825</v>
+        <v>10.1122951507568</v>
       </c>
       <c r="H1350" t="n">
         <v>618145</v>
@@ -39606,7 +39606,7 @@
         <v>13.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>10.0085029602051</v>
+        <v>10.0085020065308</v>
       </c>
       <c r="H1353" t="n">
         <v>305598</v>
@@ -39664,7 +39664,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.9566068649292</v>
+        <v>9.95660591125488</v>
       </c>
       <c r="H1355" t="n">
         <v>386695</v>
@@ -39780,7 +39780,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G1359" t="n">
-        <v>10.0285978317261</v>
+        <v>10.0285968780518</v>
       </c>
       <c r="H1359" t="n">
         <v>363619</v>
@@ -39809,7 +39809,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1360" t="n">
-        <v>10.0440378189087</v>
+        <v>10.044038772583</v>
       </c>
       <c r="H1360" t="n">
         <v>568930</v>
@@ -39838,7 +39838,7 @@
         <v>13.25</v>
       </c>
       <c r="G1361" t="n">
-        <v>10.2293243408203</v>
+        <v>10.229323387146</v>
       </c>
       <c r="H1361" t="n">
         <v>481650</v>
@@ -39896,7 +39896,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1363" t="n">
-        <v>9.92051410675049</v>
+        <v>9.9205150604248</v>
       </c>
       <c r="H1363" t="n">
         <v>442173</v>
@@ -39925,7 +39925,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1364" t="n">
-        <v>10.329686164856</v>
+        <v>10.3296871185303</v>
       </c>
       <c r="H1364" t="n">
         <v>901307</v>
@@ -39954,7 +39954,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1365" t="n">
-        <v>10.2524843215942</v>
+        <v>10.2524852752686</v>
       </c>
       <c r="H1365" t="n">
         <v>930701</v>
@@ -39983,7 +39983,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.5226936340332</v>
+        <v>10.5226926803589</v>
       </c>
       <c r="H1366" t="n">
         <v>856596</v>
@@ -40012,7 +40012,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G1367" t="n">
-        <v>10.7851810455322</v>
+        <v>10.7851819992065</v>
       </c>
       <c r="H1367" t="n">
         <v>734935</v>
@@ -40041,7 +40041,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1368" t="n">
-        <v>10.7234201431274</v>
+        <v>10.7234210968018</v>
       </c>
       <c r="H1368" t="n">
         <v>437605</v>
@@ -40128,7 +40128,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1371" t="n">
-        <v>10.3914499282837</v>
+        <v>10.3914489746094</v>
       </c>
       <c r="H1371" t="n">
         <v>333184</v>
@@ -40157,7 +40157,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1372" t="n">
-        <v>10.6616582870483</v>
+        <v>10.661657333374</v>
       </c>
       <c r="H1372" t="n">
         <v>1102741</v>
@@ -40186,7 +40186,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G1373" t="n">
-        <v>10.8160619735718</v>
+        <v>10.8160629272461</v>
       </c>
       <c r="H1373" t="n">
         <v>496342</v>
@@ -40273,7 +40273,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1376" t="n">
-        <v>11.3796396255493</v>
+        <v>11.3796405792236</v>
       </c>
       <c r="H1376" t="n">
         <v>602612</v>
@@ -40302,7 +40302,7 @@
         <v>14.75</v>
       </c>
       <c r="G1377" t="n">
-        <v>11.3873596191406</v>
+        <v>11.3873615264893</v>
       </c>
       <c r="H1377" t="n">
         <v>440958</v>
@@ -40331,7 +40331,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.4722833633423</v>
+        <v>11.472282409668</v>
       </c>
       <c r="H1378" t="n">
         <v>404357</v>
@@ -40418,7 +40418,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1381" t="n">
-        <v>11.981819152832</v>
+        <v>11.9818201065063</v>
       </c>
       <c r="H1381" t="n">
         <v>704671</v>
@@ -40447,7 +40447,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.7888126373291</v>
+        <v>11.7888145446777</v>
       </c>
       <c r="H1382" t="n">
         <v>401929</v>
@@ -40650,7 +40650,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1389" t="n">
-        <v>11.9895401000977</v>
+        <v>11.9895391464233</v>
       </c>
       <c r="H1389" t="n">
         <v>280927</v>
@@ -40708,7 +40708,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.4954433441162</v>
+        <v>11.4954452514648</v>
       </c>
       <c r="H1391" t="n">
         <v>232147</v>
@@ -40737,7 +40737,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1392" t="n">
-        <v>11.6035270690918</v>
+        <v>11.6035280227661</v>
       </c>
       <c r="H1392" t="n">
         <v>165498</v>
@@ -40766,7 +40766,7 @@
         <v>15</v>
       </c>
       <c r="G1393" t="n">
-        <v>11.5803670883179</v>
+        <v>11.5803661346436</v>
       </c>
       <c r="H1393" t="n">
         <v>123407</v>
@@ -40853,7 +40853,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1396" t="n">
-        <v>11.4414024353027</v>
+        <v>11.4414014816284</v>
       </c>
       <c r="H1396" t="n">
         <v>226584</v>
@@ -40882,7 +40882,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1397" t="n">
-        <v>11.4491233825684</v>
+        <v>11.449122428894</v>
       </c>
       <c r="H1397" t="n">
         <v>322076</v>
@@ -40969,7 +40969,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1400" t="n">
-        <v>11.6344089508057</v>
+        <v>11.634407043457</v>
       </c>
       <c r="H1400" t="n">
         <v>333893</v>
@@ -40998,7 +40998,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1401" t="n">
-        <v>11.9586591720581</v>
+        <v>11.9586582183838</v>
       </c>
       <c r="H1401" t="n">
         <v>275938</v>
@@ -41056,7 +41056,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1403" t="n">
-        <v>11.4414024353027</v>
+        <v>11.4414014816284</v>
       </c>
       <c r="H1403" t="n">
         <v>185872</v>
@@ -41288,7 +41288,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1411" t="n">
-        <v>11.3950815200806</v>
+        <v>11.3950805664062</v>
       </c>
       <c r="H1411" t="n">
         <v>189384</v>
@@ -41317,7 +41317,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G1412" t="n">
-        <v>11.5958070755005</v>
+        <v>11.5958080291748</v>
       </c>
       <c r="H1412" t="n">
         <v>305262</v>
@@ -41346,7 +41346,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1413" t="n">
-        <v>11.8505754470825</v>
+        <v>11.8505764007568</v>
       </c>
       <c r="H1413" t="n">
         <v>145591</v>
@@ -41433,7 +41433,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1416" t="n">
-        <v>11.6035270690918</v>
+        <v>11.6035280227661</v>
       </c>
       <c r="H1416" t="n">
         <v>121057</v>
@@ -41491,7 +41491,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1418" t="n">
-        <v>11.9895401000977</v>
+        <v>11.9895391464233</v>
       </c>
       <c r="H1418" t="n">
         <v>184001</v>
@@ -41520,7 +41520,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G1419" t="n">
-        <v>12.0667409896851</v>
+        <v>12.0667419433594</v>
       </c>
       <c r="H1419" t="n">
         <v>201420</v>
@@ -41578,7 +41578,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1421" t="n">
-        <v>12.3987131118774</v>
+        <v>12.3987121582031</v>
       </c>
       <c r="H1421" t="n">
         <v>274686</v>
@@ -41636,7 +41636,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1423" t="n">
-        <v>12.1671047210693</v>
+        <v>12.1671056747437</v>
       </c>
       <c r="H1423" t="n">
         <v>126683</v>
@@ -41665,7 +41665,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1424" t="n">
-        <v>12.3987131118774</v>
+        <v>12.3987121582031</v>
       </c>
       <c r="H1424" t="n">
         <v>122796</v>
@@ -41810,7 +41810,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G1429" t="n">
-        <v>12.3292303085327</v>
+        <v>12.329231262207</v>
       </c>
       <c r="H1429" t="n">
         <v>169314</v>
@@ -41955,7 +41955,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.0435819625854</v>
+        <v>12.0435829162598</v>
       </c>
       <c r="H1434" t="n">
         <v>397932</v>
@@ -41984,7 +41984,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1435" t="n">
-        <v>11.8505754470825</v>
+        <v>11.8505764007568</v>
       </c>
       <c r="H1435" t="n">
         <v>237731</v>
@@ -42013,7 +42013,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1436" t="n">
-        <v>12.0899028778076</v>
+        <v>12.0899038314819</v>
       </c>
       <c r="H1436" t="n">
         <v>189948</v>
@@ -42042,7 +42042,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>12.0435819625854</v>
+        <v>12.0435829162598</v>
       </c>
       <c r="H1437" t="n">
         <v>179780</v>
@@ -42245,7 +42245,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G1444" t="n">
-        <v>12.3755521774292</v>
+        <v>12.3755531311035</v>
       </c>
       <c r="H1444" t="n">
         <v>154059</v>
@@ -42274,7 +42274,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1445" t="n">
-        <v>11.5108852386475</v>
+        <v>11.5108842849731</v>
       </c>
       <c r="H1445" t="n">
         <v>2072355</v>
@@ -42332,7 +42332,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1447" t="n">
-        <v>10.5149726867676</v>
+        <v>10.5149717330933</v>
       </c>
       <c r="H1447" t="n">
         <v>1307534</v>
@@ -42361,7 +42361,7 @@
         <v>13</v>
       </c>
       <c r="G1448" t="n">
-        <v>10.0363178253174</v>
+        <v>10.0363168716431</v>
       </c>
       <c r="H1448" t="n">
         <v>1134592</v>
@@ -42390,7 +42390,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>9.68890762329102</v>
+        <v>9.6889066696167</v>
       </c>
       <c r="H1449" t="n">
         <v>800971</v>
@@ -42419,7 +42419,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0749197006226</v>
+        <v>10.0749187469482</v>
       </c>
       <c r="H1450" t="n">
         <v>1314808</v>
@@ -42448,7 +42448,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1451" t="n">
-        <v>9.76610851287842</v>
+        <v>9.76610946655273</v>
       </c>
       <c r="H1451" t="n">
         <v>587568</v>
@@ -42506,7 +42506,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1453" t="n">
-        <v>9.61942386627197</v>
+        <v>9.61942481994629</v>
       </c>
       <c r="H1453" t="n">
         <v>427074</v>
@@ -42564,7 +42564,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1455" t="n">
-        <v>9.27201461791992</v>
+        <v>9.27201366424561</v>
       </c>
       <c r="H1455" t="n">
         <v>351449</v>
@@ -42593,7 +42593,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1456" t="n">
-        <v>9.34149551391602</v>
+        <v>9.34149646759033</v>
       </c>
       <c r="H1456" t="n">
         <v>567062</v>
@@ -42651,7 +42651,7 @@
         <v>12</v>
       </c>
       <c r="G1458" t="n">
-        <v>9.26429271697998</v>
+        <v>9.2642936706543</v>
       </c>
       <c r="H1458" t="n">
         <v>357284</v>
@@ -42738,7 +42738,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.71615695953369</v>
+        <v>8.71615505218506</v>
       </c>
       <c r="H1461" t="n">
         <v>263441</v>
@@ -42825,7 +42825,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1464" t="n">
-        <v>8.53859043121338</v>
+        <v>8.5385913848877</v>
       </c>
       <c r="H1464" t="n">
         <v>545701</v>
@@ -42854,7 +42854,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.52315044403076</v>
+        <v>8.52314949035645</v>
       </c>
       <c r="H1465" t="n">
         <v>397323</v>
@@ -42999,7 +42999,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.723876953125</v>
+        <v>8.72387599945068</v>
       </c>
       <c r="H1470" t="n">
         <v>331845</v>
@@ -43115,7 +43115,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1474" t="n">
-        <v>9.27201461791992</v>
+        <v>9.27201366424561</v>
       </c>
       <c r="H1474" t="n">
         <v>637336</v>
@@ -43231,7 +43231,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1478" t="n">
-        <v>9.12532901763916</v>
+        <v>9.12532806396484</v>
       </c>
       <c r="H1478" t="n">
         <v>221754</v>
@@ -43289,7 +43289,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1480" t="n">
-        <v>9.15620994567871</v>
+        <v>9.15620899200439</v>
       </c>
       <c r="H1480" t="n">
         <v>244389</v>
@@ -43318,7 +43318,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1481" t="n">
-        <v>8.71615695953369</v>
+        <v>8.71615505218506</v>
       </c>
       <c r="H1481" t="n">
         <v>404867</v>
@@ -43347,7 +43347,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.723876953125</v>
+        <v>8.72387599945068</v>
       </c>
       <c r="H1482" t="n">
         <v>214386</v>
@@ -43434,7 +43434,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1485" t="n">
-        <v>9.2025318145752</v>
+        <v>9.20253086090088</v>
       </c>
       <c r="H1485" t="n">
         <v>621775</v>
@@ -43492,7 +43492,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1487" t="n">
-        <v>9.60398483276367</v>
+        <v>9.60398387908936</v>
       </c>
       <c r="H1487" t="n">
         <v>810378</v>
@@ -43550,7 +43550,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1489" t="n">
-        <v>9.59626483917236</v>
+        <v>9.59626388549805</v>
       </c>
       <c r="H1489" t="n">
         <v>245362</v>
@@ -43579,7 +43579,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.71978855133057</v>
+        <v>9.71978759765625</v>
       </c>
       <c r="H1490" t="n">
         <v>386060</v>
@@ -43666,7 +43666,7 @@
         <v>12.25</v>
       </c>
       <c r="G1493" t="n">
-        <v>9.45729923248291</v>
+        <v>9.45730018615723</v>
       </c>
       <c r="H1493" t="n">
         <v>648412</v>
@@ -43695,7 +43695,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>9.76610851287842</v>
+        <v>9.76610946655273</v>
       </c>
       <c r="H1494" t="n">
         <v>593274</v>
@@ -43753,7 +43753,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>9.70434665679932</v>
+        <v>9.70434761047363</v>
       </c>
       <c r="H1496" t="n">
         <v>479345</v>
@@ -43840,7 +43840,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.5113410949707</v>
+        <v>9.51134204864502</v>
       </c>
       <c r="H1499" t="n">
         <v>222491</v>
@@ -43869,7 +43869,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1500" t="n">
-        <v>9.00952625274658</v>
+        <v>9.00952434539795</v>
       </c>
       <c r="H1500" t="n">
         <v>531730</v>
@@ -44072,7 +44072,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G1507" t="n">
-        <v>9.44185924530029</v>
+        <v>9.44185829162598</v>
       </c>
       <c r="H1507" t="n">
         <v>297324</v>
@@ -44130,7 +44130,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>9.5113410949707</v>
+        <v>9.51134204864502</v>
       </c>
       <c r="H1509" t="n">
         <v>192211</v>
@@ -44159,7 +44159,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G1510" t="n">
-        <v>10.2447643280029</v>
+        <v>10.2447652816772</v>
       </c>
       <c r="H1510" t="n">
         <v>587994</v>
@@ -44188,7 +44188,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G1511" t="n">
-        <v>10.3374071121216</v>
+        <v>10.3374080657959</v>
       </c>
       <c r="H1511" t="n">
         <v>531221</v>
@@ -44217,7 +44217,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1512" t="n">
-        <v>10.0671987533569</v>
+        <v>10.0671997070312</v>
       </c>
       <c r="H1512" t="n">
         <v>378676</v>
@@ -44246,7 +44246,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1513" t="n">
-        <v>9.94367408752441</v>
+        <v>9.94367599487305</v>
       </c>
       <c r="H1513" t="n">
         <v>232655</v>
@@ -44304,7 +44304,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1515" t="n">
-        <v>9.36465644836426</v>
+        <v>9.36465740203857</v>
       </c>
       <c r="H1515" t="n">
         <v>333489</v>
@@ -44391,7 +44391,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1518" t="n">
-        <v>9.12532901763916</v>
+        <v>9.12532806396484</v>
       </c>
       <c r="H1518" t="n">
         <v>128055</v>
@@ -44420,7 +44420,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1519" t="n">
-        <v>9.15620994567871</v>
+        <v>9.15620899200439</v>
       </c>
       <c r="H1519" t="n">
         <v>156153</v>
@@ -44449,7 +44449,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1520" t="n">
-        <v>9.30289554595947</v>
+        <v>9.30289363861084</v>
       </c>
       <c r="H1520" t="n">
         <v>117990</v>
@@ -44565,7 +44565,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1524" t="n">
-        <v>9.92051410675049</v>
+        <v>9.9205150604248</v>
       </c>
       <c r="H1524" t="n">
         <v>123851</v>
@@ -44681,7 +44681,7 @@
         <v>13</v>
       </c>
       <c r="G1528" t="n">
-        <v>10.0363178253174</v>
+        <v>10.0363168716431</v>
       </c>
       <c r="H1528" t="n">
         <v>214843</v>
@@ -44739,7 +44739,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1530" t="n">
-        <v>9.71978855133057</v>
+        <v>9.71978759765625</v>
       </c>
       <c r="H1530" t="n">
         <v>157471</v>
@@ -44768,7 +44768,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1531" t="n">
-        <v>9.54994297027588</v>
+        <v>9.54994201660156</v>
       </c>
       <c r="H1531" t="n">
         <v>137558</v>
@@ -44797,7 +44797,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.99408435821533</v>
+        <v>8.99408531188965</v>
       </c>
       <c r="H1532" t="n">
         <v>392300</v>
@@ -44855,7 +44855,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1534" t="n">
-        <v>9.4495792388916</v>
+        <v>9.44957828521729</v>
       </c>
       <c r="H1534" t="n">
         <v>194792</v>
@@ -44913,7 +44913,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1536" t="n">
-        <v>9.36465644836426</v>
+        <v>9.36465740203857</v>
       </c>
       <c r="H1536" t="n">
         <v>130194</v>
@@ -44942,7 +44942,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1537" t="n">
-        <v>9.61170387268066</v>
+        <v>9.61170482635498</v>
       </c>
       <c r="H1537" t="n">
         <v>191883</v>
@@ -44971,7 +44971,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1538" t="n">
-        <v>9.49590110778809</v>
+        <v>9.49590015411377</v>
       </c>
       <c r="H1538" t="n">
         <v>573431</v>
@@ -45000,7 +45000,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1539" t="n">
-        <v>9.34149551391602</v>
+        <v>9.34149646759033</v>
       </c>
       <c r="H1539" t="n">
         <v>162896</v>
@@ -45058,7 +45058,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G1541" t="n">
-        <v>9.39553833007812</v>
+        <v>9.39553737640381</v>
       </c>
       <c r="H1541" t="n">
         <v>167766</v>
@@ -45174,7 +45174,7 @@
         <v>12.25</v>
       </c>
       <c r="G1545" t="n">
-        <v>9.45729923248291</v>
+        <v>9.45730018615723</v>
       </c>
       <c r="H1545" t="n">
         <v>166522</v>
@@ -45261,7 +45261,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1548" t="n">
-        <v>9.71978855133057</v>
+        <v>9.71978759765625</v>
       </c>
       <c r="H1548" t="n">
         <v>360949</v>
@@ -45290,7 +45290,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1549" t="n">
-        <v>9.71978855133057</v>
+        <v>9.71978759765625</v>
       </c>
       <c r="H1549" t="n">
         <v>482932</v>
@@ -45406,7 +45406,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>9.12532901763916</v>
+        <v>9.12532806396484</v>
       </c>
       <c r="H1553" t="n">
         <v>143035</v>
@@ -45464,7 +45464,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G1555" t="n">
-        <v>9.44185924530029</v>
+        <v>9.44185829162598</v>
       </c>
       <c r="H1555" t="n">
         <v>93721</v>
@@ -45522,7 +45522,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>9.03268718719482</v>
+        <v>9.03268623352051</v>
       </c>
       <c r="H1557" t="n">
         <v>395628</v>
@@ -45551,7 +45551,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1558" t="n">
-        <v>9.30289554595947</v>
+        <v>9.30289363861084</v>
       </c>
       <c r="H1558" t="n">
         <v>93185</v>
@@ -45580,7 +45580,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1559" t="n">
-        <v>9.21797180175781</v>
+        <v>9.21797275543213</v>
       </c>
       <c r="H1559" t="n">
         <v>153524</v>
@@ -45609,7 +45609,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1560" t="n">
-        <v>9.00952625274658</v>
+        <v>9.00952434539795</v>
       </c>
       <c r="H1560" t="n">
         <v>123789</v>
@@ -45667,7 +45667,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1562" t="n">
-        <v>8.6003532409668</v>
+        <v>8.60035228729248</v>
       </c>
       <c r="H1562" t="n">
         <v>249020</v>
@@ -45725,7 +45725,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1564" t="n">
-        <v>8.71615695953369</v>
+        <v>8.71615505218506</v>
       </c>
       <c r="H1564" t="n">
         <v>146362</v>
@@ -45754,7 +45754,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1565" t="n">
-        <v>8.29154205322266</v>
+        <v>8.29154300689697</v>
       </c>
       <c r="H1565" t="n">
         <v>337131</v>
@@ -45841,7 +45841,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1568" t="n">
-        <v>8.27610301971436</v>
+        <v>8.27610206604004</v>
       </c>
       <c r="H1568" t="n">
         <v>170280</v>
@@ -45870,7 +45870,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1569" t="n">
-        <v>8.22205924987793</v>
+        <v>8.22206020355225</v>
       </c>
       <c r="H1569" t="n">
         <v>129147</v>
@@ -45899,7 +45899,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1570" t="n">
-        <v>7.85148906707764</v>
+        <v>7.85148954391479</v>
       </c>
       <c r="H1570" t="n">
         <v>180435</v>
@@ -45928,7 +45928,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.25702953338623</v>
+        <v>7.25702905654907</v>
       </c>
       <c r="H1571" t="n">
         <v>300725</v>
@@ -45957,7 +45957,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1572" t="n">
-        <v>6.82469606399536</v>
+        <v>6.82469654083252</v>
       </c>
       <c r="H1572" t="n">
         <v>388423</v>
@@ -46015,7 +46015,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.0871844291687</v>
+        <v>7.08718490600586</v>
       </c>
       <c r="H1574" t="n">
         <v>668311</v>
@@ -46044,7 +46044,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1575" t="n">
-        <v>6.878737449646</v>
+        <v>6.87873792648315</v>
       </c>
       <c r="H1575" t="n">
         <v>351634</v>
@@ -46073,7 +46073,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>7.10648536682129</v>
+        <v>7.10648488998413</v>
       </c>
       <c r="H1576" t="n">
         <v>414498</v>
@@ -46102,7 +46102,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1577" t="n">
-        <v>7.26475048065186</v>
+        <v>7.26474952697754</v>
       </c>
       <c r="H1577" t="n">
         <v>298297</v>
@@ -46160,7 +46160,7 @@
         <v>9.5</v>
       </c>
       <c r="G1579" t="n">
-        <v>7.33423137664795</v>
+        <v>7.33423280715942</v>
       </c>
       <c r="H1579" t="n">
         <v>470457</v>
@@ -46189,7 +46189,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.43459558486938</v>
+        <v>7.43459606170654</v>
       </c>
       <c r="H1580" t="n">
         <v>320480</v>
@@ -46218,7 +46218,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.32265138626099</v>
+        <v>7.32265090942383</v>
       </c>
       <c r="H1581" t="n">
         <v>540737</v>
@@ -46247,7 +46247,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>7.30335187911987</v>
+        <v>7.30335092544556</v>
       </c>
       <c r="H1582" t="n">
         <v>184597</v>
@@ -46276,7 +46276,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.48863697052002</v>
+        <v>7.48863744735718</v>
       </c>
       <c r="H1583" t="n">
         <v>187636</v>
@@ -46334,7 +46334,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1585" t="n">
-        <v>7.43459558486938</v>
+        <v>7.43459606170654</v>
       </c>
       <c r="H1585" t="n">
         <v>132184</v>
@@ -46363,7 +46363,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.53881883621216</v>
+        <v>7.53881978988647</v>
       </c>
       <c r="H1586" t="n">
         <v>148850</v>
@@ -46421,7 +46421,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1588" t="n">
-        <v>7.75112581253052</v>
+        <v>7.7511248588562</v>
       </c>
       <c r="H1588" t="n">
         <v>180788</v>
@@ -46450,7 +46450,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.70866298675537</v>
+        <v>7.70866394042969</v>
       </c>
       <c r="H1589" t="n">
         <v>87262</v>
@@ -46537,7 +46537,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G1592" t="n">
-        <v>7.5619797706604</v>
+        <v>7.56197929382324</v>
       </c>
       <c r="H1592" t="n">
         <v>86752</v>
@@ -46595,7 +46595,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G1594" t="n">
-        <v>7.23000907897949</v>
+        <v>7.23000812530518</v>
       </c>
       <c r="H1594" t="n">
         <v>220097</v>
@@ -46653,7 +46653,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.36511278152466</v>
+        <v>7.36511421203613</v>
       </c>
       <c r="H1596" t="n">
         <v>104930</v>
@@ -46740,7 +46740,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1599" t="n">
-        <v>7.3844141960144</v>
+        <v>7.38441324234009</v>
       </c>
       <c r="H1599" t="n">
         <v>131459</v>
@@ -46769,7 +46769,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1600" t="n">
-        <v>7.26475048065186</v>
+        <v>7.26474952697754</v>
       </c>
       <c r="H1600" t="n">
         <v>138249</v>
@@ -46798,7 +46798,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1601" t="n">
-        <v>7.3882737159729</v>
+        <v>7.38827419281006</v>
       </c>
       <c r="H1601" t="n">
         <v>124837</v>
@@ -46827,7 +46827,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G1602" t="n">
-        <v>7.46161603927612</v>
+        <v>7.46161651611328</v>
       </c>
       <c r="H1602" t="n">
         <v>110984</v>
@@ -46856,7 +46856,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1603" t="n">
-        <v>7.58128023147583</v>
+        <v>7.58127975463867</v>
       </c>
       <c r="H1603" t="n">
         <v>124067</v>
@@ -46885,7 +46885,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.58514022827148</v>
+        <v>7.58514070510864</v>
       </c>
       <c r="H1604" t="n">
         <v>244599</v>
@@ -80096,6 +80096,35 @@
         <v>50992</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>7.73000001907349</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>7.88500022888184</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>7.67500019073486</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>7.78999996185303</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>7.78999996185303</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>137867</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4473237991333</v>
+        <v>5.44732332229614</v>
       </c>
       <c r="H2" t="n">
         <v>113188</v>
@@ -485,7 +485,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G4" t="n">
-        <v>5.38089370727539</v>
+        <v>5.38089275360107</v>
       </c>
       <c r="H4" t="n">
         <v>67853</v>
@@ -543,7 +543,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G6" t="n">
-        <v>5.350998878479</v>
+        <v>5.35099983215332</v>
       </c>
       <c r="H6" t="n">
         <v>87575</v>
@@ -601,7 +601,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>5.29453277587891</v>
+        <v>5.29453229904175</v>
       </c>
       <c r="H8" t="n">
         <v>216037</v>
@@ -630,7 +630,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>5.33106899261475</v>
+        <v>5.3310694694519</v>
       </c>
       <c r="H9" t="n">
         <v>49371</v>
@@ -659,7 +659,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G10" t="n">
-        <v>5.1683144569397</v>
+        <v>5.16831493377686</v>
       </c>
       <c r="H10" t="n">
         <v>83186</v>
@@ -688,7 +688,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>4.94245004653931</v>
+        <v>4.94244956970215</v>
       </c>
       <c r="H11" t="n">
         <v>159704</v>
@@ -775,7 +775,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5837230682373</v>
+        <v>4.58372402191162</v>
       </c>
       <c r="H14" t="n">
         <v>143281</v>
@@ -891,7 +891,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>4.88598346710205</v>
+        <v>4.88598394393921</v>
       </c>
       <c r="H18" t="n">
         <v>66869</v>
@@ -920,7 +920,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G19" t="n">
-        <v>4.87601947784424</v>
+        <v>4.87601900100708</v>
       </c>
       <c r="H19" t="n">
         <v>45031</v>
@@ -978,7 +978,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>4.96902227401733</v>
+        <v>4.96902179718018</v>
       </c>
       <c r="H21" t="n">
         <v>82995</v>
@@ -1007,7 +1007,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>4.97234439849854</v>
+        <v>4.97234392166138</v>
       </c>
       <c r="H22" t="n">
         <v>54344</v>
@@ -1036,7 +1036,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>4.88598346710205</v>
+        <v>4.88598394393921</v>
       </c>
       <c r="H23" t="n">
         <v>81429</v>
@@ -1094,7 +1094,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>4.93248605728149</v>
+        <v>4.93248510360718</v>
       </c>
       <c r="H25" t="n">
         <v>117119</v>
@@ -1123,7 +1123,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G26" t="n">
-        <v>4.9789867401123</v>
+        <v>4.97898626327515</v>
       </c>
       <c r="H26" t="n">
         <v>142513</v>
@@ -1239,7 +1239,7 @@
         <v>6.75</v>
       </c>
       <c r="G30" t="n">
-        <v>4.48407793045044</v>
+        <v>4.48407745361328</v>
       </c>
       <c r="H30" t="n">
         <v>162247</v>
@@ -1297,7 +1297,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>4.70662069320679</v>
+        <v>4.70662021636963</v>
       </c>
       <c r="H32" t="n">
         <v>54106</v>
@@ -1326,7 +1326,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.67340469360352</v>
+        <v>4.67340517044067</v>
       </c>
       <c r="H33" t="n">
         <v>87459</v>
@@ -1500,7 +1500,7 @@
         <v>7.75</v>
       </c>
       <c r="G39" t="n">
-        <v>5.14838457107544</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H39" t="n">
         <v>73305</v>
@@ -1529,7 +1529,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G40" t="n">
-        <v>5.24138832092285</v>
+        <v>5.24138784408569</v>
       </c>
       <c r="H40" t="n">
         <v>51694</v>
@@ -1616,7 +1616,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G43" t="n">
-        <v>5.69311761856079</v>
+        <v>5.69311714172363</v>
       </c>
       <c r="H43" t="n">
         <v>209250</v>
@@ -1645,7 +1645,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>5.75290536880493</v>
+        <v>5.75290584564209</v>
       </c>
       <c r="H44" t="n">
         <v>122191</v>
@@ -1674,7 +1674,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>5.53368330001831</v>
+        <v>5.53368425369263</v>
       </c>
       <c r="H45" t="n">
         <v>125352</v>
@@ -1732,7 +1732,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G47" t="n">
-        <v>5.68315362930298</v>
+        <v>5.68315315246582</v>
       </c>
       <c r="H47" t="n">
         <v>127631</v>
@@ -1790,7 +1790,7 @@
         <v>8.5</v>
       </c>
       <c r="G49" t="n">
-        <v>5.64661645889282</v>
+        <v>5.64661598205566</v>
       </c>
       <c r="H49" t="n">
         <v>71691</v>
@@ -1819,7 +1819,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>5.35432052612305</v>
+        <v>5.35432100296021</v>
       </c>
       <c r="H50" t="n">
         <v>105600</v>
@@ -1848,7 +1848,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G51" t="n">
-        <v>5.387535572052</v>
+        <v>5.38753652572632</v>
       </c>
       <c r="H51" t="n">
         <v>191706</v>
@@ -1906,7 +1906,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>5.45396709442139</v>
+        <v>5.45396661758423</v>
       </c>
       <c r="H53" t="n">
         <v>56712</v>
@@ -1935,7 +1935,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>5.4473237991333</v>
+        <v>5.44732332229614</v>
       </c>
       <c r="H54" t="n">
         <v>43227</v>
@@ -1964,7 +1964,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>5.39417886734009</v>
+        <v>5.39417934417725</v>
       </c>
       <c r="H55" t="n">
         <v>67532</v>
@@ -1993,7 +1993,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.4473237991333</v>
+        <v>5.44732332229614</v>
       </c>
       <c r="H56" t="n">
         <v>148456</v>
@@ -2022,7 +2022,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G57" t="n">
-        <v>5.38421392440796</v>
+        <v>5.38421487808228</v>
       </c>
       <c r="H57" t="n">
         <v>103959</v>
@@ -2109,7 +2109,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>5.18160152435303</v>
+        <v>5.18160057067871</v>
       </c>
       <c r="H60" t="n">
         <v>128542</v>
@@ -2167,7 +2167,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G62" t="n">
-        <v>5.24138832092285</v>
+        <v>5.24138784408569</v>
       </c>
       <c r="H62" t="n">
         <v>164574</v>
@@ -2225,7 +2225,7 @@
         <v>7.75</v>
       </c>
       <c r="G64" t="n">
-        <v>5.14838457107544</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H64" t="n">
         <v>96421</v>
@@ -2283,7 +2283,7 @@
         <v>7.5</v>
       </c>
       <c r="G66" t="n">
-        <v>4.98230886459351</v>
+        <v>4.98230791091919</v>
       </c>
       <c r="H66" t="n">
         <v>59642</v>
@@ -2312,7 +2312,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>4.96902227401733</v>
+        <v>4.96902179718018</v>
       </c>
       <c r="H67" t="n">
         <v>106491</v>
@@ -2341,7 +2341,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G68" t="n">
-        <v>5.01220226287842</v>
+        <v>5.01220178604126</v>
       </c>
       <c r="H68" t="n">
         <v>65134</v>
@@ -2399,7 +2399,7 @@
         <v>7.75</v>
       </c>
       <c r="G70" t="n">
-        <v>5.14838457107544</v>
+        <v>5.1483850479126</v>
       </c>
       <c r="H70" t="n">
         <v>22243</v>
@@ -2428,7 +2428,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>5.08859777450562</v>
+        <v>5.08859729766846</v>
       </c>
       <c r="H71" t="n">
         <v>44738</v>
@@ -2486,7 +2486,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G73" t="n">
-        <v>5.28124666213989</v>
+        <v>5.28124713897705</v>
       </c>
       <c r="H73" t="n">
         <v>23904</v>
@@ -2515,7 +2515,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G74" t="n">
-        <v>5.04209613800049</v>
+        <v>5.04209566116333</v>
       </c>
       <c r="H74" t="n">
         <v>83664</v>
@@ -2660,7 +2660,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>5.06202507019043</v>
+        <v>5.06202554702759</v>
       </c>
       <c r="H79" t="n">
         <v>31701</v>
@@ -2689,7 +2689,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G80" t="n">
-        <v>4.98895168304443</v>
+        <v>4.98895120620728</v>
       </c>
       <c r="H80" t="n">
         <v>25738</v>
@@ -2718,7 +2718,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>4.95905733108521</v>
+        <v>4.95905828475952</v>
       </c>
       <c r="H81" t="n">
         <v>101223</v>
@@ -2776,7 +2776,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.20153045654297</v>
+        <v>5.20152950286865</v>
       </c>
       <c r="H83" t="n">
         <v>54605</v>
@@ -2834,7 +2834,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>5.1118483543396</v>
+        <v>5.11184883117676</v>
       </c>
       <c r="H85" t="n">
         <v>15689</v>
@@ -2863,7 +2863,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>5.06202507019043</v>
+        <v>5.06202554702759</v>
       </c>
       <c r="H86" t="n">
         <v>36585</v>
@@ -2979,7 +2979,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G90" t="n">
-        <v>5.74733304977417</v>
+        <v>5.74733257293701</v>
       </c>
       <c r="H90" t="n">
         <v>226380</v>
@@ -3037,7 +3037,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G92" t="n">
-        <v>5.54763221740723</v>
+        <v>5.54763126373291</v>
       </c>
       <c r="H92" t="n">
         <v>108705</v>
@@ -3066,7 +3066,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G93" t="n">
-        <v>5.42916488647461</v>
+        <v>5.42916536331177</v>
       </c>
       <c r="H93" t="n">
         <v>60550</v>
@@ -3095,7 +3095,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>5.52393865585327</v>
+        <v>5.52393817901611</v>
       </c>
       <c r="H94" t="n">
         <v>43648</v>
@@ -3153,7 +3153,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>4.66759347915649</v>
+        <v>4.66759300231934</v>
       </c>
       <c r="H96" t="n">
         <v>383206</v>
@@ -3269,7 +3269,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>4.4340443611145</v>
+        <v>4.43404388427734</v>
       </c>
       <c r="H100" t="n">
         <v>87516</v>
@@ -3327,7 +3327,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G102" t="n">
-        <v>4.42727375030518</v>
+        <v>4.42727470397949</v>
       </c>
       <c r="H102" t="n">
         <v>149214</v>
@@ -3356,7 +3356,7 @@
         <v>6.5</v>
       </c>
       <c r="G103" t="n">
-        <v>4.40019655227661</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H103" t="n">
         <v>103547</v>
@@ -3385,7 +3385,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G104" t="n">
-        <v>4.30542278289795</v>
+        <v>4.30542325973511</v>
       </c>
       <c r="H104" t="n">
         <v>179465</v>
@@ -3414,7 +3414,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.44758224487305</v>
+        <v>4.44758319854736</v>
       </c>
       <c r="H105" t="n">
         <v>157820</v>
@@ -3472,7 +3472,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>4.34942436218262</v>
+        <v>4.34942483901978</v>
       </c>
       <c r="H107" t="n">
         <v>210950</v>
@@ -3501,7 +3501,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>4.29865312576294</v>
+        <v>4.29865264892578</v>
       </c>
       <c r="H108" t="n">
         <v>89317</v>
@@ -3559,7 +3559,7 @@
         <v>6.25</v>
       </c>
       <c r="G110" t="n">
-        <v>4.23095798492432</v>
+        <v>4.23095703125</v>
       </c>
       <c r="H110" t="n">
         <v>156920</v>
@@ -3617,7 +3617,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G112" t="n">
-        <v>4.15649271011353</v>
+        <v>4.15649318695068</v>
       </c>
       <c r="H112" t="n">
         <v>139833</v>
@@ -3704,7 +3704,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.02448701858521</v>
+        <v>4.02448797225952</v>
       </c>
       <c r="H115" t="n">
         <v>158085</v>
@@ -3733,7 +3733,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G116" t="n">
-        <v>3.87217235565186</v>
+        <v>3.87217330932617</v>
       </c>
       <c r="H116" t="n">
         <v>159201</v>
@@ -3762,7 +3762,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>3.865403175354</v>
+        <v>3.86540222167969</v>
       </c>
       <c r="H117" t="n">
         <v>92272</v>
@@ -3791,7 +3791,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G118" t="n">
-        <v>3.79770731925964</v>
+        <v>3.79770755767822</v>
       </c>
       <c r="H118" t="n">
         <v>144969</v>
@@ -3820,7 +3820,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>4.01094770431519</v>
+        <v>4.01094722747803</v>
       </c>
       <c r="H119" t="n">
         <v>162964</v>
@@ -3849,7 +3849,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>3.93648266792297</v>
+        <v>3.93648362159729</v>
       </c>
       <c r="H120" t="n">
         <v>167668</v>
@@ -3907,7 +3907,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94663763046265</v>
+        <v>3.94663715362549</v>
       </c>
       <c r="H122" t="n">
         <v>66243</v>
@@ -3936,7 +3936,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>3.99402379989624</v>
+        <v>3.99402475357056</v>
       </c>
       <c r="H123" t="n">
         <v>85572</v>
@@ -3994,7 +3994,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32925605773926</v>
+        <v>3.32925629615784</v>
       </c>
       <c r="H125" t="n">
         <v>312851</v>
@@ -4023,7 +4023,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.40169024467468</v>
+        <v>3.40168976783752</v>
       </c>
       <c r="H126" t="n">
         <v>297033</v>
@@ -4139,7 +4139,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>3.45246195793152</v>
+        <v>3.45246171951294</v>
       </c>
       <c r="H130" t="n">
         <v>186985</v>
@@ -4168,7 +4168,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>3.3983051776886</v>
+        <v>3.39830565452576</v>
       </c>
       <c r="H131" t="n">
         <v>57807</v>
@@ -4197,7 +4197,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>3.15730977058411</v>
+        <v>3.15731000900269</v>
       </c>
       <c r="H132" t="n">
         <v>707649</v>
@@ -4226,7 +4226,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22906708717346</v>
+        <v>3.22906684875488</v>
       </c>
       <c r="H133" t="n">
         <v>75468</v>
@@ -4255,7 +4255,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G134" t="n">
-        <v>3.29540824890137</v>
+        <v>3.29540848731995</v>
       </c>
       <c r="H134" t="n">
         <v>189271</v>
@@ -4284,7 +4284,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G135" t="n">
-        <v>3.3251941204071</v>
+        <v>3.32519435882568</v>
       </c>
       <c r="H135" t="n">
         <v>50898</v>
@@ -4313,7 +4313,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.58785271644592</v>
+        <v>3.58785200119019</v>
       </c>
       <c r="H136" t="n">
         <v>115636</v>
@@ -4371,7 +4371,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49984836578369</v>
+        <v>3.49984812736511</v>
       </c>
       <c r="H138" t="n">
         <v>69291</v>
@@ -4429,7 +4429,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>3.5709285736084</v>
+        <v>3.57092881202698</v>
       </c>
       <c r="H140" t="n">
         <v>95057</v>
@@ -4458,7 +4458,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G141" t="n">
-        <v>3.51677179336548</v>
+        <v>3.51677227020264</v>
       </c>
       <c r="H141" t="n">
         <v>72737</v>
@@ -4487,7 +4487,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G142" t="n">
-        <v>3.57431268692017</v>
+        <v>3.57431292533875</v>
       </c>
       <c r="H142" t="n">
         <v>38892</v>
@@ -4574,7 +4574,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G145" t="n">
-        <v>3.63185381889343</v>
+        <v>3.63185429573059</v>
       </c>
       <c r="H145" t="n">
         <v>19997</v>
@@ -4603,7 +4603,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.61154556274414</v>
+        <v>3.6115460395813</v>
       </c>
       <c r="H146" t="n">
         <v>52589</v>
@@ -4632,7 +4632,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.79093766212463</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H147" t="n">
         <v>91695</v>
@@ -4661,7 +4661,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>3.70293426513672</v>
+        <v>3.70293474197388</v>
       </c>
       <c r="H148" t="n">
         <v>67162</v>
@@ -4690,7 +4690,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>3.78078365325928</v>
+        <v>3.78078436851501</v>
       </c>
       <c r="H149" t="n">
         <v>32010</v>
@@ -4719,7 +4719,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G150" t="n">
-        <v>3.71308898925781</v>
+        <v>3.71308851242065</v>
       </c>
       <c r="H150" t="n">
         <v>72315</v>
@@ -4777,7 +4777,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G152" t="n">
-        <v>3.56077456474304</v>
+        <v>3.56077480316162</v>
       </c>
       <c r="H152" t="n">
         <v>56391</v>
@@ -4864,7 +4864,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G155" t="n">
-        <v>3.64877843856812</v>
+        <v>3.64877796173096</v>
       </c>
       <c r="H155" t="n">
         <v>28077</v>
@@ -4893,7 +4893,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G156" t="n">
-        <v>3.79093766212463</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H156" t="n">
         <v>57929</v>
@@ -4922,7 +4922,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>3.79093766212463</v>
+        <v>3.79093837738037</v>
       </c>
       <c r="H157" t="n">
         <v>34686</v>
@@ -4951,7 +4951,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>3.83832502365112</v>
+        <v>3.83832454681396</v>
       </c>
       <c r="H158" t="n">
         <v>13489</v>
@@ -5183,7 +5183,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>3.98725461959839</v>
+        <v>3.98725414276123</v>
       </c>
       <c r="H166" t="n">
         <v>125514</v>
@@ -5212,7 +5212,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>3.9534068107605</v>
+        <v>3.95340728759766</v>
       </c>
       <c r="H167" t="n">
         <v>79391</v>
@@ -5241,7 +5241,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G168" t="n">
-        <v>4.13618469238281</v>
+        <v>4.13618421554565</v>
       </c>
       <c r="H168" t="n">
         <v>165803</v>
@@ -5270,7 +5270,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>4.07525825500488</v>
+        <v>4.0752592086792</v>
       </c>
       <c r="H169" t="n">
         <v>48601</v>
@@ -5299,7 +5299,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G170" t="n">
-        <v>4.02448701858521</v>
+        <v>4.02448797225952</v>
       </c>
       <c r="H170" t="n">
         <v>39849</v>
@@ -5328,7 +5328,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>3.99402379989624</v>
+        <v>3.99402475357056</v>
       </c>
       <c r="H171" t="n">
         <v>44191</v>
@@ -5357,7 +5357,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G172" t="n">
-        <v>4.02787208557129</v>
+        <v>4.02787113189697</v>
       </c>
       <c r="H172" t="n">
         <v>87862</v>
@@ -5386,7 +5386,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>4.05833387374878</v>
+        <v>4.0583348274231</v>
       </c>
       <c r="H173" t="n">
         <v>31122</v>
@@ -5444,7 +5444,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>3.93986892700195</v>
+        <v>3.93986797332764</v>
       </c>
       <c r="H175" t="n">
         <v>201408</v>
@@ -5502,7 +5502,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>4.05833387374878</v>
+        <v>4.0583348274231</v>
       </c>
       <c r="H177" t="n">
         <v>34907</v>
@@ -5531,7 +5531,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>4.07525825500488</v>
+        <v>4.0752592086792</v>
       </c>
       <c r="H178" t="n">
         <v>17063</v>
@@ -5560,7 +5560,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.98725461959839</v>
+        <v>3.98725414276123</v>
       </c>
       <c r="H179" t="n">
         <v>91126</v>
@@ -5589,7 +5589,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>4.02787208557129</v>
+        <v>4.02787113189697</v>
       </c>
       <c r="H180" t="n">
         <v>95736</v>
@@ -5618,7 +5618,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G181" t="n">
-        <v>3.96694612503052</v>
+        <v>3.96694564819336</v>
       </c>
       <c r="H181" t="n">
         <v>146337</v>
@@ -5705,7 +5705,7 @@
         <v>5</v>
       </c>
       <c r="G184" t="n">
-        <v>3.38476657867432</v>
+        <v>3.38476634025574</v>
       </c>
       <c r="H184" t="n">
         <v>271176</v>
@@ -5734,7 +5734,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>3.31707143783569</v>
+        <v>3.31707096099854</v>
       </c>
       <c r="H185" t="n">
         <v>255286</v>
@@ -5792,7 +5792,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G187" t="n">
-        <v>3.28322291374207</v>
+        <v>3.28322315216064</v>
       </c>
       <c r="H187" t="n">
         <v>138480</v>
@@ -5821,7 +5821,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G188" t="n">
-        <v>3.33060956001282</v>
+        <v>3.3306097984314</v>
       </c>
       <c r="H188" t="n">
         <v>74303</v>
@@ -5850,7 +5850,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>3.38815069198608</v>
+        <v>3.38815140724182</v>
       </c>
       <c r="H189" t="n">
         <v>81134</v>
@@ -5879,7 +5879,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>3.30353188514709</v>
+        <v>3.30353164672852</v>
       </c>
       <c r="H190" t="n">
         <v>156871</v>
@@ -5937,7 +5937,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G192" t="n">
-        <v>3.37122678756714</v>
+        <v>3.37122750282288</v>
       </c>
       <c r="H192" t="n">
         <v>58791</v>
@@ -5966,7 +5966,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G193" t="n">
-        <v>3.34956502914429</v>
+        <v>3.34956479072571</v>
       </c>
       <c r="H193" t="n">
         <v>82212</v>
@@ -5995,7 +5995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>3.49984836578369</v>
+        <v>3.49984812736511</v>
       </c>
       <c r="H194" t="n">
         <v>152264</v>
@@ -6024,7 +6024,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G195" t="n">
-        <v>3.46261596679688</v>
+        <v>3.46261620521545</v>
       </c>
       <c r="H195" t="n">
         <v>36886</v>
@@ -6053,7 +6053,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>4.11587572097778</v>
+        <v>4.11587619781494</v>
       </c>
       <c r="H196" t="n">
         <v>609931</v>
@@ -6140,7 +6140,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>4.35619449615479</v>
+        <v>4.35619497299194</v>
       </c>
       <c r="H199" t="n">
         <v>608292</v>
@@ -6256,7 +6256,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>4.24449682235718</v>
+        <v>4.24449729919434</v>
       </c>
       <c r="H203" t="n">
         <v>64155</v>
@@ -6285,7 +6285,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>4.26480531692505</v>
+        <v>4.26480579376221</v>
       </c>
       <c r="H204" t="n">
         <v>104103</v>
@@ -6314,7 +6314,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>4.44081354141235</v>
+        <v>4.4408130645752</v>
       </c>
       <c r="H205" t="n">
         <v>291963</v>
@@ -6343,7 +6343,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>4.46789121627808</v>
+        <v>4.46789169311523</v>
       </c>
       <c r="H206" t="n">
         <v>146224</v>
@@ -6401,7 +6401,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>4.44081354141235</v>
+        <v>4.4408130645752</v>
       </c>
       <c r="H208" t="n">
         <v>91882</v>
@@ -6430,7 +6430,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>4.44081354141235</v>
+        <v>4.4408130645752</v>
       </c>
       <c r="H209" t="n">
         <v>86447</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>4.46789121627808</v>
+        <v>4.46789169311523</v>
       </c>
       <c r="H210" t="n">
         <v>109334</v>
@@ -6575,7 +6575,7 @@
         <v>6.75</v>
       </c>
       <c r="G214" t="n">
-        <v>4.56943511962891</v>
+        <v>4.56943464279175</v>
       </c>
       <c r="H214" t="n">
         <v>80845</v>
@@ -6604,7 +6604,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G215" t="n">
-        <v>4.56266498565674</v>
+        <v>4.56266450881958</v>
       </c>
       <c r="H215" t="n">
         <v>38526</v>
@@ -6691,7 +6691,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>4.30203771591187</v>
+        <v>4.30203819274902</v>
       </c>
       <c r="H218" t="n">
         <v>284256</v>
@@ -6720,7 +6720,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>4.38665676116943</v>
+        <v>4.38665723800659</v>
       </c>
       <c r="H219" t="n">
         <v>126233</v>
@@ -6749,7 +6749,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G220" t="n">
-        <v>4.4340443611145</v>
+        <v>4.43404388427734</v>
       </c>
       <c r="H220" t="n">
         <v>204726</v>
@@ -6778,7 +6778,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G221" t="n">
-        <v>4.40696620941162</v>
+        <v>4.40696573257446</v>
       </c>
       <c r="H221" t="n">
         <v>176630</v>
@@ -6807,7 +6807,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G222" t="n">
-        <v>4.36296415328979</v>
+        <v>4.36296367645264</v>
       </c>
       <c r="H222" t="n">
         <v>78414</v>
@@ -6836,7 +6836,7 @@
         <v>6.5</v>
       </c>
       <c r="G223" t="n">
-        <v>4.40019655227661</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H223" t="n">
         <v>131651</v>
@@ -6865,7 +6865,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="n">
-        <v>4.40019655227661</v>
+        <v>4.40019607543945</v>
       </c>
       <c r="H224" t="n">
         <v>103731</v>
@@ -6952,7 +6952,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.4340443611145</v>
+        <v>4.43404388427734</v>
       </c>
       <c r="H227" t="n">
         <v>73554</v>
@@ -6981,7 +6981,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>4.4340443611145</v>
+        <v>4.43404388427734</v>
       </c>
       <c r="H228" t="n">
         <v>55444</v>
@@ -7126,7 +7126,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G233" t="n">
-        <v>4.43742799758911</v>
+        <v>4.43742895126343</v>
       </c>
       <c r="H233" t="n">
         <v>66735</v>
@@ -7242,7 +7242,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G237" t="n">
-        <v>4.24449682235718</v>
+        <v>4.24449729919434</v>
       </c>
       <c r="H237" t="n">
         <v>65977</v>
@@ -7271,7 +7271,7 @@
         <v>6.375</v>
       </c>
       <c r="G238" t="n">
-        <v>4.31557750701904</v>
+        <v>4.31557703018188</v>
       </c>
       <c r="H238" t="n">
         <v>102989</v>
@@ -7329,7 +7329,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G240" t="n">
-        <v>4.46789121627808</v>
+        <v>4.46789169311523</v>
       </c>
       <c r="H240" t="n">
         <v>61992</v>
@@ -7387,7 +7387,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G242" t="n">
-        <v>4.56266498565674</v>
+        <v>4.56266450881958</v>
       </c>
       <c r="H242" t="n">
         <v>108996</v>
@@ -7416,7 +7416,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>4.46789121627808</v>
+        <v>4.46789169311523</v>
       </c>
       <c r="H243" t="n">
         <v>65647</v>
@@ -7445,7 +7445,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.48819971084595</v>
+        <v>4.48820018768311</v>
       </c>
       <c r="H244" t="n">
         <v>56395</v>
@@ -7503,7 +7503,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>4.45435190200806</v>
+        <v>4.45435237884521</v>
       </c>
       <c r="H246" t="n">
         <v>58966</v>
@@ -7532,7 +7532,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.51866340637207</v>
+        <v>4.51866245269775</v>
       </c>
       <c r="H247" t="n">
         <v>77287</v>
@@ -7619,7 +7619,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G250" t="n">
-        <v>4.62359094619751</v>
+        <v>4.62359046936035</v>
       </c>
       <c r="H250" t="n">
         <v>229951</v>
@@ -7677,7 +7677,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G252" t="n">
-        <v>4.71836471557617</v>
+        <v>4.71836423873901</v>
       </c>
       <c r="H252" t="n">
         <v>148227</v>
@@ -7764,7 +7764,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G255" t="n">
-        <v>4.71836471557617</v>
+        <v>4.71836423873901</v>
       </c>
       <c r="H255" t="n">
         <v>44487</v>
@@ -7822,7 +7822,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.79282903671265</v>
+        <v>4.79282855987549</v>
       </c>
       <c r="H257" t="n">
         <v>58206</v>
@@ -7880,7 +7880,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G259" t="n">
-        <v>4.81652164459229</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H259" t="n">
         <v>83473</v>
@@ -7996,7 +7996,7 @@
         <v>7</v>
       </c>
       <c r="G263" t="n">
-        <v>4.73867273330688</v>
+        <v>4.73867321014404</v>
       </c>
       <c r="H263" t="n">
         <v>75411</v>
@@ -8025,7 +8025,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.78944444656372</v>
+        <v>4.78944396972656</v>
       </c>
       <c r="H264" t="n">
         <v>71071</v>
@@ -8083,7 +8083,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78944444656372</v>
+        <v>4.78944396972656</v>
       </c>
       <c r="H266" t="n">
         <v>52227</v>
@@ -8112,7 +8112,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>4.8402156829834</v>
+        <v>4.84021520614624</v>
       </c>
       <c r="H267" t="n">
         <v>41796</v>
@@ -8141,7 +8141,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>4.81652164459229</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H268" t="n">
         <v>15823</v>
@@ -8228,7 +8228,7 @@
         <v>7.125</v>
       </c>
       <c r="G271" t="n">
-        <v>4.82329225540161</v>
+        <v>4.82329177856445</v>
       </c>
       <c r="H271" t="n">
         <v>22605</v>
@@ -8257,7 +8257,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>4.8402156829834</v>
+        <v>4.84021520614624</v>
       </c>
       <c r="H272" t="n">
         <v>25459</v>
@@ -8286,7 +8286,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G273" t="n">
-        <v>4.72851800918579</v>
+        <v>4.72851896286011</v>
       </c>
       <c r="H273" t="n">
         <v>28889</v>
@@ -8344,7 +8344,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G275" t="n">
-        <v>4.82667589187622</v>
+        <v>4.82667684555054</v>
       </c>
       <c r="H275" t="n">
         <v>57170</v>
@@ -8402,7 +8402,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G277" t="n">
-        <v>4.81652164459229</v>
+        <v>4.81652212142944</v>
       </c>
       <c r="H277" t="n">
         <v>53288</v>
@@ -8518,7 +8518,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G281" t="n">
-        <v>4.69805574417114</v>
+        <v>4.6980562210083</v>
       </c>
       <c r="H281" t="n">
         <v>48954</v>
@@ -8692,7 +8692,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74205780029297</v>
+        <v>4.74205732345581</v>
       </c>
       <c r="H287" t="n">
         <v>26431</v>
@@ -8721,7 +8721,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>4.79282903671265</v>
+        <v>4.79282855987549</v>
       </c>
       <c r="H288" t="n">
         <v>40804</v>
@@ -8750,7 +8750,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G289" t="n">
-        <v>5.00945377349854</v>
+        <v>5.00945472717285</v>
       </c>
       <c r="H289" t="n">
         <v>353566</v>
@@ -8779,7 +8779,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>5.04330110549927</v>
+        <v>5.04330205917358</v>
       </c>
       <c r="H290" t="n">
         <v>270928</v>
@@ -8808,7 +8808,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G291" t="n">
-        <v>5.07037973403931</v>
+        <v>5.07038021087646</v>
       </c>
       <c r="H291" t="n">
         <v>225000</v>
@@ -8866,7 +8866,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G293" t="n">
-        <v>5.06699514389038</v>
+        <v>5.06699466705322</v>
       </c>
       <c r="H293" t="n">
         <v>44482</v>
@@ -8895,7 +8895,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G294" t="n">
-        <v>5.00268459320068</v>
+        <v>5.00268411636353</v>
       </c>
       <c r="H294" t="n">
         <v>22069</v>
@@ -8982,7 +8982,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G297" t="n">
-        <v>4.96883773803711</v>
+        <v>4.96883726119995</v>
       </c>
       <c r="H297" t="n">
         <v>116952</v>
@@ -9069,7 +9069,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G300" t="n">
-        <v>5.0568413734436</v>
+        <v>5.05684041976929</v>
       </c>
       <c r="H300" t="n">
         <v>83204</v>
@@ -9098,7 +9098,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>5.06361055374146</v>
+        <v>5.0636100769043</v>
       </c>
       <c r="H301" t="n">
         <v>60114</v>
@@ -9127,7 +9127,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>5.04330110549927</v>
+        <v>5.04330205917358</v>
       </c>
       <c r="H302" t="n">
         <v>60086</v>
@@ -9156,7 +9156,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G303" t="n">
-        <v>5.0399169921875</v>
+        <v>5.03991746902466</v>
       </c>
       <c r="H303" t="n">
         <v>64927</v>
@@ -9185,7 +9185,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637815475464</v>
       </c>
       <c r="H304" t="n">
         <v>31519</v>
@@ -9272,7 +9272,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G307" t="n">
-        <v>5.07037973403931</v>
+        <v>5.07038021087646</v>
       </c>
       <c r="H307" t="n">
         <v>101547</v>
@@ -9330,7 +9330,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G309" t="n">
-        <v>5.00268459320068</v>
+        <v>5.00268411636353</v>
       </c>
       <c r="H309" t="n">
         <v>46538</v>
@@ -9359,7 +9359,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G310" t="n">
-        <v>5.06699514389038</v>
+        <v>5.06699466705322</v>
       </c>
       <c r="H310" t="n">
         <v>54701</v>
@@ -9388,7 +9388,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>5.27346611022949</v>
+        <v>5.27346563339233</v>
       </c>
       <c r="H311" t="n">
         <v>171397</v>
@@ -9475,7 +9475,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>5.29039001464844</v>
+        <v>5.29038953781128</v>
       </c>
       <c r="H314" t="n">
         <v>288254</v>
@@ -9504,7 +9504,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G315" t="n">
-        <v>5.23284912109375</v>
+        <v>5.23284816741943</v>
       </c>
       <c r="H315" t="n">
         <v>195604</v>
@@ -9562,7 +9562,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>5.3817777633667</v>
+        <v>5.38177824020386</v>
       </c>
       <c r="H317" t="n">
         <v>83970</v>
@@ -9591,7 +9591,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G318" t="n">
-        <v>5.3817777633667</v>
+        <v>5.38177824020386</v>
       </c>
       <c r="H318" t="n">
         <v>112172</v>
@@ -9620,7 +9620,7 @@
         <v>8</v>
       </c>
       <c r="G319" t="n">
-        <v>5.41562557220459</v>
+        <v>5.41562604904175</v>
       </c>
       <c r="H319" t="n">
         <v>179752</v>
@@ -9678,7 +9678,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>5.40208673477173</v>
+        <v>5.40208721160889</v>
       </c>
       <c r="H321" t="n">
         <v>71386</v>
@@ -9707,7 +9707,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>5.3817777633667</v>
+        <v>5.38177824020386</v>
       </c>
       <c r="H322" t="n">
         <v>126667</v>
@@ -9794,7 +9794,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>5.17869234085083</v>
+        <v>5.17869281768799</v>
       </c>
       <c r="H325" t="n">
         <v>114001</v>
@@ -9852,7 +9852,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>5.17869234085083</v>
+        <v>5.17869281768799</v>
       </c>
       <c r="H327" t="n">
         <v>28662</v>
@@ -9881,7 +9881,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>5.1448450088501</v>
+        <v>5.14484453201294</v>
       </c>
       <c r="H328" t="n">
         <v>90125</v>
@@ -9968,7 +9968,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.94852781295776</v>
+        <v>4.94852828979492</v>
       </c>
       <c r="H331" t="n">
         <v>123182</v>
@@ -10026,7 +10026,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>4.97899198532104</v>
+        <v>4.97899150848389</v>
       </c>
       <c r="H333" t="n">
         <v>75688</v>
@@ -10055,7 +10055,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>4.92483472824097</v>
+        <v>4.92483520507812</v>
       </c>
       <c r="H334" t="n">
         <v>56297</v>
@@ -10142,7 +10142,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G337" t="n">
-        <v>5.17192316055298</v>
+        <v>5.17192268371582</v>
       </c>
       <c r="H337" t="n">
         <v>58203</v>
@@ -10171,7 +10171,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>5.11099672317505</v>
+        <v>5.11099720001221</v>
       </c>
       <c r="H338" t="n">
         <v>143535</v>
@@ -10374,7 +10374,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.23200035095215</v>
+        <v>5.23200082778931</v>
       </c>
       <c r="H345" t="n">
         <v>74072</v>
@@ -10403,7 +10403,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G346" t="n">
-        <v>5.39054584503174</v>
+        <v>5.39054679870605</v>
       </c>
       <c r="H346" t="n">
         <v>202741</v>
@@ -10432,7 +10432,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G347" t="n">
-        <v>5.26302051544189</v>
+        <v>5.26302099227905</v>
       </c>
       <c r="H347" t="n">
         <v>109151</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>5.156174659729</v>
+        <v>5.15617418289185</v>
       </c>
       <c r="H348" t="n">
         <v>77577</v>
@@ -10490,7 +10490,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G349" t="n">
-        <v>5.12170839309692</v>
+        <v>5.12170791625977</v>
       </c>
       <c r="H349" t="n">
         <v>53144</v>
@@ -10519,7 +10519,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G350" t="n">
-        <v>4.81840372085571</v>
+        <v>4.81840419769287</v>
       </c>
       <c r="H350" t="n">
         <v>315554</v>
@@ -10548,7 +10548,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>4.71500492095947</v>
+        <v>4.71500539779663</v>
       </c>
       <c r="H351" t="n">
         <v>350968</v>
@@ -10635,7 +10635,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>4.72189807891846</v>
+        <v>4.7218976020813</v>
       </c>
       <c r="H354" t="n">
         <v>62590</v>
@@ -10751,7 +10751,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G358" t="n">
-        <v>4.58747911453247</v>
+        <v>4.58747959136963</v>
       </c>
       <c r="H358" t="n">
         <v>52219</v>
@@ -10896,7 +10896,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>4.41170072555542</v>
+        <v>4.41170024871826</v>
       </c>
       <c r="H363" t="n">
         <v>196216</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>4.26004886627197</v>
+        <v>4.26004791259766</v>
       </c>
       <c r="H367" t="n">
         <v>48450</v>
@@ -11041,7 +11041,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>4.23936796188354</v>
+        <v>4.2393684387207</v>
       </c>
       <c r="H368" t="n">
         <v>56785</v>
@@ -11070,7 +11070,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>4.30485439300537</v>
+        <v>4.30485486984253</v>
       </c>
       <c r="H369" t="n">
         <v>176874</v>
@@ -11128,7 +11128,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>4.32898139953613</v>
+        <v>4.32898092269897</v>
       </c>
       <c r="H371" t="n">
         <v>89129</v>
@@ -11157,7 +11157,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G372" t="n">
-        <v>4.32208728790283</v>
+        <v>4.32208776473999</v>
       </c>
       <c r="H372" t="n">
         <v>57654</v>
@@ -11244,7 +11244,7 @@
         <v>6.25</v>
       </c>
       <c r="G375" t="n">
-        <v>4.30830144882202</v>
+        <v>4.30830097198486</v>
       </c>
       <c r="H375" t="n">
         <v>83151</v>
@@ -11273,7 +11273,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G376" t="n">
-        <v>4.17732906341553</v>
+        <v>4.17732858657837</v>
       </c>
       <c r="H376" t="n">
         <v>76134</v>
@@ -11302,7 +11302,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G377" t="n">
-        <v>4.27038812637329</v>
+        <v>4.27038860321045</v>
       </c>
       <c r="H377" t="n">
         <v>79360</v>
@@ -11331,7 +11331,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>4.23592138290405</v>
+        <v>4.23592233657837</v>
       </c>
       <c r="H378" t="n">
         <v>77420</v>
@@ -11418,7 +11418,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G381" t="n">
-        <v>4.30485439300537</v>
+        <v>4.30485486984253</v>
       </c>
       <c r="H381" t="n">
         <v>127973</v>
@@ -11534,7 +11534,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>4.51509952545166</v>
+        <v>4.5150990486145</v>
       </c>
       <c r="H385" t="n">
         <v>184215</v>
@@ -11621,7 +11621,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>4.37723398208618</v>
+        <v>4.37723350524902</v>
       </c>
       <c r="H388" t="n">
         <v>60247</v>
@@ -11650,7 +11650,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G389" t="n">
-        <v>4.32898139953613</v>
+        <v>4.32898092269897</v>
       </c>
       <c r="H389" t="n">
         <v>38008</v>
@@ -11679,7 +11679,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>4.49441957473755</v>
+        <v>4.49442005157471</v>
       </c>
       <c r="H390" t="n">
         <v>149419</v>
@@ -11708,7 +11708,7 @@
         <v>6.625</v>
       </c>
       <c r="G391" t="n">
-        <v>4.5667986869812</v>
+        <v>4.56679821014404</v>
       </c>
       <c r="H391" t="n">
         <v>195950</v>
@@ -11766,7 +11766,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>4.59781837463379</v>
+        <v>4.59781932830811</v>
       </c>
       <c r="H393" t="n">
         <v>107005</v>
@@ -11824,7 +11824,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>4.52888584136963</v>
+        <v>4.52888631820679</v>
       </c>
       <c r="H395" t="n">
         <v>77827</v>
@@ -11882,7 +11882,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G397" t="n">
-        <v>4.64262580871582</v>
+        <v>4.64262533187866</v>
       </c>
       <c r="H397" t="n">
         <v>509615</v>
@@ -11940,7 +11940,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>4.50820589065552</v>
+        <v>4.50820636749268</v>
       </c>
       <c r="H399" t="n">
         <v>56545</v>
@@ -11969,7 +11969,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>4.58403253555298</v>
+        <v>4.58403205871582</v>
       </c>
       <c r="H400" t="n">
         <v>49686</v>
@@ -11998,7 +11998,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.59781837463379</v>
+        <v>4.59781932830811</v>
       </c>
       <c r="H401" t="n">
         <v>46066</v>
@@ -12027,7 +12027,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>4.5219931602478</v>
+        <v>4.52199268341064</v>
       </c>
       <c r="H402" t="n">
         <v>98507</v>
@@ -12085,7 +12085,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>4.42548656463623</v>
+        <v>4.42548704147339</v>
       </c>
       <c r="H404" t="n">
         <v>58646</v>
@@ -12201,7 +12201,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G408" t="n">
-        <v>4.45995283126831</v>
+        <v>4.45995330810547</v>
       </c>
       <c r="H408" t="n">
         <v>41217</v>
@@ -12288,7 +12288,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>4.58403253555298</v>
+        <v>4.58403205871582</v>
       </c>
       <c r="H411" t="n">
         <v>48654</v>
@@ -12346,7 +12346,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.46340036392212</v>
+        <v>4.46339988708496</v>
       </c>
       <c r="H413" t="n">
         <v>62096</v>
@@ -12433,7 +12433,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>4.42203998565674</v>
+        <v>4.4220404624939</v>
       </c>
       <c r="H416" t="n">
         <v>143532</v>
@@ -12462,7 +12462,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>4.42548656463623</v>
+        <v>4.42548704147339</v>
       </c>
       <c r="H417" t="n">
         <v>91936</v>
@@ -12549,7 +12549,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G420" t="n">
-        <v>4.32208728790283</v>
+        <v>4.32208776473999</v>
       </c>
       <c r="H420" t="n">
         <v>25521</v>
@@ -12578,7 +12578,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G421" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281454086304</v>
       </c>
       <c r="H421" t="n">
         <v>57686</v>
@@ -12607,7 +12607,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>4.23936796188354</v>
+        <v>4.2393684387207</v>
       </c>
       <c r="H422" t="n">
         <v>82552</v>
@@ -12694,7 +12694,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>4.20490169525146</v>
+        <v>4.20490121841431</v>
       </c>
       <c r="H425" t="n">
         <v>58755</v>
@@ -12752,7 +12752,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G427" t="n">
-        <v>4.28762102127075</v>
+        <v>4.28762149810791</v>
       </c>
       <c r="H427" t="n">
         <v>84276</v>
@@ -12781,7 +12781,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G428" t="n">
-        <v>4.27038812637329</v>
+        <v>4.27038860321045</v>
       </c>
       <c r="H428" t="n">
         <v>35523</v>
@@ -12839,7 +12839,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>4.20490169525146</v>
+        <v>4.20490121841431</v>
       </c>
       <c r="H430" t="n">
         <v>45169</v>
@@ -12868,7 +12868,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281454086304</v>
       </c>
       <c r="H431" t="n">
         <v>97071</v>
@@ -12897,7 +12897,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G432" t="n">
-        <v>4.30140781402588</v>
+        <v>4.30140733718872</v>
       </c>
       <c r="H432" t="n">
         <v>53302</v>
@@ -12926,7 +12926,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281454086304</v>
       </c>
       <c r="H433" t="n">
         <v>49792</v>
@@ -12984,7 +12984,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>4.28072738647461</v>
+        <v>4.28072786331177</v>
       </c>
       <c r="H435" t="n">
         <v>67345</v>
@@ -13013,7 +13013,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G436" t="n">
-        <v>4.23247480392456</v>
+        <v>4.23247528076172</v>
       </c>
       <c r="H436" t="n">
         <v>100278</v>
@@ -13071,7 +13071,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>4.17732906341553</v>
+        <v>4.17732858657837</v>
       </c>
       <c r="H438" t="n">
         <v>145459</v>
@@ -13100,7 +13100,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>3.5293595790863</v>
+        <v>3.52936029434204</v>
       </c>
       <c r="H439" t="n">
         <v>1797627</v>
@@ -13187,7 +13187,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>3.37770843505859</v>
+        <v>3.37770819664001</v>
       </c>
       <c r="H442" t="n">
         <v>276428</v>
@@ -13216,7 +13216,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G443" t="n">
-        <v>3.37081456184387</v>
+        <v>3.37081503868103</v>
       </c>
       <c r="H443" t="n">
         <v>202384</v>
@@ -13245,7 +13245,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G444" t="n">
-        <v>3.44250512123108</v>
+        <v>3.4425048828125</v>
       </c>
       <c r="H444" t="n">
         <v>322860</v>
@@ -13303,7 +13303,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G446" t="n">
-        <v>3.42458200454712</v>
+        <v>3.42458248138428</v>
       </c>
       <c r="H446" t="n">
         <v>285105</v>
@@ -13332,7 +13332,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>3.42596077919006</v>
+        <v>3.42596125602722</v>
       </c>
       <c r="H447" t="n">
         <v>173870</v>
@@ -13390,7 +13390,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.42596077919006</v>
+        <v>3.42596125602722</v>
       </c>
       <c r="H449" t="n">
         <v>172863</v>
@@ -13477,7 +13477,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G452" t="n">
-        <v>3.23984265327454</v>
+        <v>3.23984217643738</v>
       </c>
       <c r="H452" t="n">
         <v>504346</v>
@@ -13506,7 +13506,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G453" t="n">
-        <v>3.15436625480652</v>
+        <v>3.15436553955078</v>
       </c>
       <c r="H453" t="n">
         <v>362204</v>
@@ -13535,7 +13535,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G454" t="n">
-        <v>3.05372333526611</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H454" t="n">
         <v>402906</v>
@@ -13564,7 +13564,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G455" t="n">
-        <v>2.99719882011414</v>
+        <v>2.99719905853271</v>
       </c>
       <c r="H455" t="n">
         <v>496484</v>
@@ -13622,7 +13622,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>3.06751036643982</v>
+        <v>3.06751012802124</v>
       </c>
       <c r="H457" t="n">
         <v>523527</v>
@@ -13651,7 +13651,7 @@
         <v>4.40399980545044</v>
       </c>
       <c r="G458" t="n">
-        <v>3.03580093383789</v>
+        <v>3.03580117225647</v>
       </c>
       <c r="H458" t="n">
         <v>266731</v>
@@ -13680,7 +13680,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G459" t="n">
-        <v>2.95308184623718</v>
+        <v>2.9530816078186</v>
       </c>
       <c r="H459" t="n">
         <v>409593</v>
@@ -13709,7 +13709,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G460" t="n">
-        <v>2.9365382194519</v>
+        <v>2.93653798103333</v>
       </c>
       <c r="H460" t="n">
         <v>451958</v>
@@ -13738,7 +13738,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G461" t="n">
-        <v>2.95446038246155</v>
+        <v>2.95445990562439</v>
       </c>
       <c r="H461" t="n">
         <v>328173</v>
@@ -13767,7 +13767,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G462" t="n">
-        <v>2.86898422241211</v>
+        <v>2.86898398399353</v>
       </c>
       <c r="H462" t="n">
         <v>600471</v>
@@ -13796,7 +13796,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G463" t="n">
-        <v>2.84830403327942</v>
+        <v>2.84830379486084</v>
       </c>
       <c r="H463" t="n">
         <v>341520</v>
@@ -13825,7 +13825,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G464" t="n">
-        <v>2.87725567817688</v>
+        <v>2.8772554397583</v>
       </c>
       <c r="H464" t="n">
         <v>725032</v>
@@ -13883,7 +13883,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G466" t="n">
-        <v>2.98479080200195</v>
+        <v>2.98479104042053</v>
       </c>
       <c r="H466" t="n">
         <v>406773</v>
@@ -13941,7 +13941,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G468" t="n">
-        <v>2.89655733108521</v>
+        <v>2.89655685424805</v>
       </c>
       <c r="H468" t="n">
         <v>587468</v>
@@ -13970,7 +13970,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>2.86071181297302</v>
+        <v>2.8607120513916</v>
       </c>
       <c r="H469" t="n">
         <v>326227</v>
@@ -14028,7 +14028,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G471" t="n">
-        <v>2.86898422241211</v>
+        <v>2.86898398399353</v>
       </c>
       <c r="H471" t="n">
         <v>254832</v>
@@ -14057,7 +14057,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G472" t="n">
-        <v>3.04545187950134</v>
+        <v>3.0454523563385</v>
       </c>
       <c r="H472" t="n">
         <v>1192003</v>
@@ -14144,7 +14144,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G475" t="n">
-        <v>3.00960683822632</v>
+        <v>3.00960659980774</v>
       </c>
       <c r="H475" t="n">
         <v>430262</v>
@@ -14173,7 +14173,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>2.94343090057373</v>
+        <v>2.94343161582947</v>
       </c>
       <c r="H476" t="n">
         <v>398406</v>
@@ -14202,7 +14202,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.86071181297302</v>
+        <v>2.8607120513916</v>
       </c>
       <c r="H477" t="n">
         <v>523481</v>
@@ -14260,7 +14260,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G479" t="n">
-        <v>2.80556559562683</v>
+        <v>2.80556583404541</v>
       </c>
       <c r="H479" t="n">
         <v>259091</v>
@@ -14376,7 +14376,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G483" t="n">
-        <v>2.87312006950378</v>
+        <v>2.87311983108521</v>
       </c>
       <c r="H483" t="n">
         <v>492450</v>
@@ -14434,7 +14434,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G485" t="n">
-        <v>2.85795450210571</v>
+        <v>2.85795474052429</v>
       </c>
       <c r="H485" t="n">
         <v>234792</v>
@@ -14492,7 +14492,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G487" t="n">
-        <v>2.79591536521912</v>
+        <v>2.79591512680054</v>
       </c>
       <c r="H487" t="n">
         <v>168936</v>
@@ -14521,7 +14521,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G488" t="n">
-        <v>2.80005073547363</v>
+        <v>2.80005097389221</v>
       </c>
       <c r="H488" t="n">
         <v>264775</v>
@@ -14550,7 +14550,7 @@
         <v>4</v>
       </c>
       <c r="G489" t="n">
-        <v>2.75731253623962</v>
+        <v>2.7573127746582</v>
       </c>
       <c r="H489" t="n">
         <v>356617</v>
@@ -14579,7 +14579,7 @@
         <v>4</v>
       </c>
       <c r="G490" t="n">
-        <v>2.75731253623962</v>
+        <v>2.7573127746582</v>
       </c>
       <c r="H490" t="n">
         <v>337390</v>
@@ -14637,7 +14637,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G492" t="n">
-        <v>2.78764319419861</v>
+        <v>2.78764343261719</v>
       </c>
       <c r="H492" t="n">
         <v>1174545</v>
@@ -14724,7 +14724,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G495" t="n">
-        <v>2.94756722450256</v>
+        <v>2.94756746292114</v>
       </c>
       <c r="H495" t="n">
         <v>203717</v>
@@ -14782,7 +14782,7 @@
         <v>4.25</v>
       </c>
       <c r="G497" t="n">
-        <v>2.92964482307434</v>
+        <v>2.92964458465576</v>
       </c>
       <c r="H497" t="n">
         <v>315673</v>
@@ -14811,7 +14811,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G498" t="n">
-        <v>2.95308184623718</v>
+        <v>2.9530816078186</v>
       </c>
       <c r="H498" t="n">
         <v>254114</v>
@@ -14840,7 +14840,7 @@
         <v>4.25</v>
       </c>
       <c r="G499" t="n">
-        <v>2.92964482307434</v>
+        <v>2.92964458465576</v>
       </c>
       <c r="H499" t="n">
         <v>242699</v>
@@ -14898,7 +14898,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G501" t="n">
-        <v>2.87725567817688</v>
+        <v>2.8772554397583</v>
       </c>
       <c r="H501" t="n">
         <v>128616</v>
@@ -14927,7 +14927,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G502" t="n">
-        <v>2.82210922241211</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H502" t="n">
         <v>359617</v>
@@ -14956,7 +14956,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G503" t="n">
-        <v>2.79591536521912</v>
+        <v>2.79591512680054</v>
       </c>
       <c r="H503" t="n">
         <v>234420</v>
@@ -15014,7 +15014,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>2.86760497093201</v>
+        <v>2.86760520935059</v>
       </c>
       <c r="H505" t="n">
         <v>191845</v>
@@ -15072,7 +15072,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G507" t="n">
-        <v>2.85106182098389</v>
+        <v>2.85106134414673</v>
       </c>
       <c r="H507" t="n">
         <v>106347</v>
@@ -15101,7 +15101,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G508" t="n">
-        <v>2.80005073547363</v>
+        <v>2.80005097389221</v>
       </c>
       <c r="H508" t="n">
         <v>47300</v>
@@ -15130,7 +15130,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G509" t="n">
-        <v>2.89931440353394</v>
+        <v>2.89931416511536</v>
       </c>
       <c r="H509" t="n">
         <v>204187</v>
@@ -15217,7 +15217,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>2.90207147598267</v>
+        <v>2.90207171440125</v>
       </c>
       <c r="H512" t="n">
         <v>89744</v>
@@ -15246,7 +15246,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>2.9399847984314</v>
+        <v>2.93998456001282</v>
       </c>
       <c r="H513" t="n">
         <v>127430</v>
@@ -15304,7 +15304,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.0744035243988</v>
+        <v>3.07440328598022</v>
       </c>
       <c r="H515" t="n">
         <v>445325</v>
@@ -15333,7 +15333,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G516" t="n">
-        <v>3.22605562210083</v>
+        <v>3.22605609893799</v>
       </c>
       <c r="H516" t="n">
         <v>664170</v>
@@ -15362,7 +15362,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>3.16401600837708</v>
+        <v>3.16401648521423</v>
       </c>
       <c r="H517" t="n">
         <v>613794</v>
@@ -15391,7 +15391,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>3.1192102432251</v>
+        <v>3.11920976638794</v>
       </c>
       <c r="H518" t="n">
         <v>467928</v>
@@ -15420,7 +15420,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H519" t="n">
         <v>718475</v>
@@ -15507,7 +15507,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G522" t="n">
-        <v>3.16746282577515</v>
+        <v>3.16746234893799</v>
       </c>
       <c r="H522" t="n">
         <v>493955</v>
@@ -15565,7 +15565,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>3.0744035243988</v>
+        <v>3.07440328598022</v>
       </c>
       <c r="H524" t="n">
         <v>415874</v>
@@ -15594,7 +15594,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>3.08819031715393</v>
+        <v>3.08819079399109</v>
       </c>
       <c r="H525" t="n">
         <v>388946</v>
@@ -15652,7 +15652,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G527" t="n">
-        <v>3.14678311347961</v>
+        <v>3.14678335189819</v>
       </c>
       <c r="H527" t="n">
         <v>306906</v>
@@ -15681,7 +15681,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>3.09508323669434</v>
+        <v>3.09508347511292</v>
       </c>
       <c r="H528" t="n">
         <v>253894</v>
@@ -15710,7 +15710,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G529" t="n">
-        <v>3.09508323669434</v>
+        <v>3.09508347511292</v>
       </c>
       <c r="H529" t="n">
         <v>186227</v>
@@ -15739,7 +15739,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G530" t="n">
-        <v>3.19503593444824</v>
+        <v>3.19503617286682</v>
       </c>
       <c r="H530" t="n">
         <v>364125</v>
@@ -15768,7 +15768,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>3.14333581924438</v>
+        <v>3.14333629608154</v>
       </c>
       <c r="H531" t="n">
         <v>265328</v>
@@ -15855,7 +15855,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>3.02959752082825</v>
+        <v>3.02959728240967</v>
       </c>
       <c r="H534" t="n">
         <v>317377</v>
@@ -15884,7 +15884,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>3.03304362297058</v>
+        <v>3.03304386138916</v>
       </c>
       <c r="H535" t="n">
         <v>491731</v>
@@ -15913,7 +15913,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>2.98479080200195</v>
+        <v>2.98479104042053</v>
       </c>
       <c r="H536" t="n">
         <v>519676</v>
@@ -15942,7 +15942,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>2.84003162384033</v>
+        <v>2.84003233909607</v>
       </c>
       <c r="H537" t="n">
         <v>1557885</v>
@@ -15971,7 +15971,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G538" t="n">
-        <v>2.91585826873779</v>
+        <v>2.91585850715637</v>
       </c>
       <c r="H538" t="n">
         <v>630323</v>
@@ -16000,7 +16000,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>2.81245923042297</v>
+        <v>2.81245899200439</v>
       </c>
       <c r="H539" t="n">
         <v>482372</v>
@@ -16029,7 +16029,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.78488540649414</v>
+        <v>2.78488564491272</v>
       </c>
       <c r="H540" t="n">
         <v>280515</v>
@@ -16174,7 +16174,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>3.0744035243988</v>
+        <v>3.07440328598022</v>
       </c>
       <c r="H545" t="n">
         <v>546449</v>
@@ -16203,7 +16203,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>3.08819031715393</v>
+        <v>3.08819079399109</v>
       </c>
       <c r="H546" t="n">
         <v>146187</v>
@@ -16261,7 +16261,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>3.04338383674622</v>
+        <v>3.04338407516479</v>
       </c>
       <c r="H548" t="n">
         <v>383699</v>
@@ -16319,7 +16319,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G550" t="n">
-        <v>3.05372333526611</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H550" t="n">
         <v>238836</v>
@@ -16348,7 +16348,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G551" t="n">
-        <v>3.01236367225647</v>
+        <v>3.01236391067505</v>
       </c>
       <c r="H551" t="n">
         <v>293142</v>
@@ -16377,7 +16377,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G552" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H552" t="n">
         <v>511233</v>
@@ -16464,7 +16464,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>2.90551853179932</v>
+        <v>2.90551829338074</v>
       </c>
       <c r="H555" t="n">
         <v>393098</v>
@@ -16493,7 +16493,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.90207147598267</v>
+        <v>2.90207171440125</v>
       </c>
       <c r="H556" t="n">
         <v>262821</v>
@@ -16522,7 +16522,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G557" t="n">
-        <v>3.05372333526611</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H557" t="n">
         <v>922577</v>
@@ -16551,7 +16551,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>3.0744035243988</v>
+        <v>3.07440328598022</v>
       </c>
       <c r="H558" t="n">
         <v>671261</v>
@@ -16638,7 +16638,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G561" t="n">
-        <v>2.96755743026733</v>
+        <v>2.96755766868591</v>
       </c>
       <c r="H561" t="n">
         <v>425732</v>
@@ -16754,7 +16754,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>2.84003162384033</v>
+        <v>2.84003233909607</v>
       </c>
       <c r="H565" t="n">
         <v>871376</v>
@@ -16812,7 +16812,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.84003162384033</v>
+        <v>2.84003233909607</v>
       </c>
       <c r="H567" t="n">
         <v>188660</v>
@@ -16870,7 +16870,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>2.86760497093201</v>
+        <v>2.86760520935059</v>
       </c>
       <c r="H569" t="n">
         <v>414211</v>
@@ -16899,7 +16899,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G570" t="n">
-        <v>2.84003162384033</v>
+        <v>2.84003233909607</v>
       </c>
       <c r="H570" t="n">
         <v>233390</v>
@@ -17044,7 +17044,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>2.98134422302246</v>
+        <v>2.98134398460388</v>
       </c>
       <c r="H575" t="n">
         <v>190507</v>
@@ -17305,7 +17305,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G584" t="n">
-        <v>2.98134422302246</v>
+        <v>2.98134398460388</v>
       </c>
       <c r="H584" t="n">
         <v>63477</v>
@@ -17421,7 +17421,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G588" t="n">
-        <v>3.03649067878723</v>
+        <v>3.03649044036865</v>
       </c>
       <c r="H588" t="n">
         <v>252004</v>
@@ -17479,7 +17479,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>3.06751036643982</v>
+        <v>3.06751012802124</v>
       </c>
       <c r="H590" t="n">
         <v>378785</v>
@@ -17508,7 +17508,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>3.07095670700073</v>
+        <v>3.07095718383789</v>
       </c>
       <c r="H591" t="n">
         <v>195836</v>
@@ -17537,7 +17537,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G592" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H592" t="n">
         <v>233898</v>
@@ -17566,7 +17566,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G593" t="n">
-        <v>3.00891733169556</v>
+        <v>3.00891709327698</v>
       </c>
       <c r="H593" t="n">
         <v>230140</v>
@@ -17595,7 +17595,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G594" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H594" t="n">
         <v>68851</v>
@@ -17653,7 +17653,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G596" t="n">
-        <v>3.00891733169556</v>
+        <v>3.00891709327698</v>
       </c>
       <c r="H596" t="n">
         <v>122410</v>
@@ -17682,7 +17682,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03304362297058</v>
+        <v>3.03304386138916</v>
       </c>
       <c r="H597" t="n">
         <v>163365</v>
@@ -17769,7 +17769,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>3.03649067878723</v>
+        <v>3.03649044036865</v>
       </c>
       <c r="H600" t="n">
         <v>224765</v>
@@ -17827,7 +17827,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G602" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H602" t="n">
         <v>358951</v>
@@ -17885,7 +17885,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G604" t="n">
-        <v>2.99425482749939</v>
+        <v>2.99425506591797</v>
       </c>
       <c r="H604" t="n">
         <v>852809</v>
@@ -17943,7 +17943,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G606" t="n">
-        <v>2.98714232444763</v>
+        <v>2.98714256286621</v>
       </c>
       <c r="H606" t="n">
         <v>223287</v>
@@ -17972,7 +17972,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>2.9551374912262</v>
+        <v>2.95513772964478</v>
       </c>
       <c r="H607" t="n">
         <v>101236</v>
@@ -18001,7 +18001,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>2.94091320037842</v>
+        <v>2.940913438797</v>
       </c>
       <c r="H608" t="n">
         <v>161778</v>
@@ -18059,7 +18059,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.9195761680603</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H610" t="n">
         <v>241159</v>
@@ -18175,7 +18175,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>2.62086224555969</v>
+        <v>2.62086200714111</v>
       </c>
       <c r="H614" t="n">
         <v>585601</v>
@@ -18233,7 +18233,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>2.65286707878113</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H616" t="n">
         <v>243214</v>
@@ -18262,7 +18262,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G617" t="n">
-        <v>2.69198489189148</v>
+        <v>2.6919846534729</v>
       </c>
       <c r="H617" t="n">
         <v>341053</v>
@@ -18291,7 +18291,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G618" t="n">
-        <v>2.65286707878113</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H618" t="n">
         <v>259078</v>
@@ -18320,7 +18320,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G619" t="n">
-        <v>2.57107615470886</v>
+        <v>2.57107639312744</v>
       </c>
       <c r="H619" t="n">
         <v>188588</v>
@@ -18349,7 +18349,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.5853009223938</v>
+        <v>2.58530068397522</v>
       </c>
       <c r="H620" t="n">
         <v>177506</v>
@@ -18378,7 +18378,7 @@
         <v>3.625</v>
       </c>
       <c r="G621" t="n">
-        <v>2.5781888961792</v>
+        <v>2.57818865776062</v>
       </c>
       <c r="H621" t="n">
         <v>419710</v>
@@ -18407,7 +18407,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57463240623474</v>
+        <v>2.57463264465332</v>
       </c>
       <c r="H622" t="n">
         <v>394435</v>
@@ -18436,7 +18436,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.5853009223938</v>
+        <v>2.58530068397522</v>
       </c>
       <c r="H623" t="n">
         <v>152678</v>
@@ -18494,7 +18494,7 @@
         <v>3.75</v>
       </c>
       <c r="G625" t="n">
-        <v>2.66709184646606</v>
+        <v>2.66709160804749</v>
       </c>
       <c r="H625" t="n">
         <v>177538</v>
@@ -18552,7 +18552,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G627" t="n">
-        <v>2.67776012420654</v>
+        <v>2.6777606010437</v>
       </c>
       <c r="H627" t="n">
         <v>149817</v>
@@ -18610,7 +18610,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G629" t="n">
-        <v>2.69198489189148</v>
+        <v>2.6919846534729</v>
       </c>
       <c r="H629" t="n">
         <v>99972</v>
@@ -18639,7 +18639,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>2.6990966796875</v>
+        <v>2.69909691810608</v>
       </c>
       <c r="H630" t="n">
         <v>92589</v>
@@ -18668,7 +18668,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G631" t="n">
-        <v>2.66353535652161</v>
+        <v>2.66353559494019</v>
       </c>
       <c r="H631" t="n">
         <v>148678</v>
@@ -18697,7 +18697,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G632" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H632" t="n">
         <v>425725</v>
@@ -18784,7 +18784,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H635" t="n">
         <v>247960</v>
@@ -18813,7 +18813,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G636" t="n">
-        <v>2.56752014160156</v>
+        <v>2.56752038002014</v>
       </c>
       <c r="H636" t="n">
         <v>270034</v>
@@ -18900,7 +18900,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>2.6990966796875</v>
+        <v>2.69909691810608</v>
       </c>
       <c r="H639" t="n">
         <v>229295</v>
@@ -18929,7 +18929,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.71687746047974</v>
+        <v>2.71687769889832</v>
       </c>
       <c r="H640" t="n">
         <v>85746</v>
@@ -18987,7 +18987,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G642" t="n">
-        <v>2.79155564308167</v>
+        <v>2.79155588150024</v>
       </c>
       <c r="H642" t="n">
         <v>251313</v>
@@ -19016,7 +19016,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G643" t="n">
-        <v>2.86267876625061</v>
+        <v>2.86267852783203</v>
       </c>
       <c r="H643" t="n">
         <v>152428</v>
@@ -19045,7 +19045,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>2.9195761680603</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H644" t="n">
         <v>153060</v>
@@ -19074,7 +19074,7 @@
         <v>4</v>
       </c>
       <c r="G645" t="n">
-        <v>2.84489798545837</v>
+        <v>2.84489774703979</v>
       </c>
       <c r="H645" t="n">
         <v>243773</v>
@@ -19219,7 +19219,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>2.74888277053833</v>
+        <v>2.74888229370117</v>
       </c>
       <c r="H650" t="n">
         <v>185580</v>
@@ -19306,7 +19306,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G653" t="n">
-        <v>2.65642356872559</v>
+        <v>2.65642333030701</v>
       </c>
       <c r="H653" t="n">
         <v>170086</v>
@@ -19335,7 +19335,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G654" t="n">
-        <v>2.66353535652161</v>
+        <v>2.66353559494019</v>
       </c>
       <c r="H654" t="n">
         <v>170243</v>
@@ -19364,7 +19364,7 @@
         <v>3.75</v>
       </c>
       <c r="G655" t="n">
-        <v>2.66709184646606</v>
+        <v>2.66709160804749</v>
       </c>
       <c r="H655" t="n">
         <v>134163</v>
@@ -19393,7 +19393,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>2.65642356872559</v>
+        <v>2.65642333030701</v>
       </c>
       <c r="H656" t="n">
         <v>97009</v>
@@ -19567,7 +19567,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.66353535652161</v>
+        <v>2.66353559494019</v>
       </c>
       <c r="H662" t="n">
         <v>68534</v>
@@ -19625,7 +19625,7 @@
         <v>3.75</v>
       </c>
       <c r="G664" t="n">
-        <v>2.66709184646606</v>
+        <v>2.66709160804749</v>
       </c>
       <c r="H664" t="n">
         <v>56567</v>
@@ -19828,7 +19828,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>2.64575505256653</v>
+        <v>2.64575481414795</v>
       </c>
       <c r="H671" t="n">
         <v>57464</v>
@@ -19857,7 +19857,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>2.70976495742798</v>
+        <v>2.70976519584656</v>
       </c>
       <c r="H672" t="n">
         <v>74089</v>
@@ -19915,7 +19915,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>2.82711696624756</v>
+        <v>2.82711720466614</v>
       </c>
       <c r="H674" t="n">
         <v>96667</v>
@@ -20002,7 +20002,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G677" t="n">
-        <v>2.74532628059387</v>
+        <v>2.74532651901245</v>
       </c>
       <c r="H677" t="n">
         <v>85052</v>
@@ -20031,7 +20031,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>2.64931106567383</v>
+        <v>2.64931130409241</v>
       </c>
       <c r="H678" t="n">
         <v>409416</v>
@@ -20060,7 +20060,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.66353535652161</v>
+        <v>2.66353559494019</v>
       </c>
       <c r="H679" t="n">
         <v>63414</v>
@@ -20118,7 +20118,7 @@
         <v>3.625</v>
       </c>
       <c r="G681" t="n">
-        <v>2.5781888961792</v>
+        <v>2.57818865776062</v>
       </c>
       <c r="H681" t="n">
         <v>50503</v>
@@ -20147,7 +20147,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G682" t="n">
-        <v>2.69198489189148</v>
+        <v>2.6919846534729</v>
       </c>
       <c r="H682" t="n">
         <v>95363</v>
@@ -20176,7 +20176,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H683" t="n">
         <v>25234</v>
@@ -20205,7 +20205,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G684" t="n">
-        <v>2.64931106567383</v>
+        <v>2.64931130409241</v>
       </c>
       <c r="H684" t="n">
         <v>34184</v>
@@ -20234,7 +20234,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H685" t="n">
         <v>54057</v>
@@ -20321,7 +20321,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G688" t="n">
-        <v>2.78800010681152</v>
+        <v>2.78799986839294</v>
       </c>
       <c r="H688" t="n">
         <v>284468</v>
@@ -20437,7 +20437,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.65286707878113</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H692" t="n">
         <v>158013</v>
@@ -20466,7 +20466,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G693" t="n">
-        <v>2.72043347358704</v>
+        <v>2.72043371200562</v>
       </c>
       <c r="H693" t="n">
         <v>192286</v>
@@ -20495,7 +20495,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021908760071</v>
       </c>
       <c r="H694" t="n">
         <v>165658</v>
@@ -20553,7 +20553,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>2.74888277053833</v>
+        <v>2.74888229370117</v>
       </c>
       <c r="H696" t="n">
         <v>138064</v>
@@ -20611,7 +20611,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G698" t="n">
-        <v>2.74888277053833</v>
+        <v>2.74888229370117</v>
       </c>
       <c r="H698" t="n">
         <v>53646</v>
@@ -20698,7 +20698,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>2.70976495742798</v>
+        <v>2.70976519584656</v>
       </c>
       <c r="H701" t="n">
         <v>83109</v>
@@ -20843,7 +20843,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>2.6990966796875</v>
+        <v>2.69909691810608</v>
       </c>
       <c r="H706" t="n">
         <v>112009</v>
@@ -20930,7 +20930,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G709" t="n">
-        <v>2.55685186386108</v>
+        <v>2.55685210227966</v>
       </c>
       <c r="H709" t="n">
         <v>130291</v>
@@ -20959,7 +20959,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50350999832153</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H710" t="n">
         <v>188934</v>
@@ -20988,7 +20988,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G711" t="n">
-        <v>2.57107615470886</v>
+        <v>2.57107639312744</v>
       </c>
       <c r="H711" t="n">
         <v>108439</v>
@@ -21017,7 +21017,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G712" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H712" t="n">
         <v>44213</v>
@@ -21191,7 +21191,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H718" t="n">
         <v>63101</v>
@@ -21220,7 +21220,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G719" t="n">
-        <v>2.56752014160156</v>
+        <v>2.56752038002014</v>
       </c>
       <c r="H719" t="n">
         <v>87756</v>
@@ -21394,7 +21394,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G725" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021908760071</v>
       </c>
       <c r="H725" t="n">
         <v>81609</v>
@@ -21452,7 +21452,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.82356119155884</v>
+        <v>2.82356142997742</v>
       </c>
       <c r="H727" t="n">
         <v>169231</v>
@@ -21481,7 +21481,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.90179586410522</v>
+        <v>2.90179562568665</v>
       </c>
       <c r="H728" t="n">
         <v>252045</v>
@@ -21510,7 +21510,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G729" t="n">
-        <v>2.91246438026428</v>
+        <v>2.9124641418457</v>
       </c>
       <c r="H729" t="n">
         <v>172660</v>
@@ -21539,7 +21539,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G730" t="n">
-        <v>2.9195761680603</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H730" t="n">
         <v>108550</v>
@@ -21568,7 +21568,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>2.9195761680603</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H731" t="n">
         <v>155862</v>
@@ -21626,7 +21626,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>2.83067345619202</v>
+        <v>2.83067321777344</v>
       </c>
       <c r="H733" t="n">
         <v>211140</v>
@@ -21684,7 +21684,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G735" t="n">
-        <v>2.916020154953</v>
+        <v>2.91602039337158</v>
       </c>
       <c r="H735" t="n">
         <v>572778</v>
@@ -21713,7 +21713,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>2.78800010681152</v>
+        <v>2.78799986839294</v>
       </c>
       <c r="H736" t="n">
         <v>563012</v>
@@ -21742,7 +21742,7 @@
         <v>3.75</v>
       </c>
       <c r="G737" t="n">
-        <v>2.66709184646606</v>
+        <v>2.66709160804749</v>
       </c>
       <c r="H737" t="n">
         <v>139990</v>
@@ -21829,7 +21829,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G740" t="n">
-        <v>2.59952545166016</v>
+        <v>2.59952521324158</v>
       </c>
       <c r="H740" t="n">
         <v>76380</v>
@@ -21858,7 +21858,7 @@
         <v>3.625</v>
       </c>
       <c r="G741" t="n">
-        <v>2.5781888961792</v>
+        <v>2.57818865776062</v>
       </c>
       <c r="H741" t="n">
         <v>86207</v>
@@ -21887,7 +21887,7 @@
         <v>3.75</v>
       </c>
       <c r="G742" t="n">
-        <v>2.66709184646606</v>
+        <v>2.66709160804749</v>
       </c>
       <c r="H742" t="n">
         <v>63963</v>
@@ -21945,7 +21945,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G744" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H744" t="n">
         <v>59599</v>
@@ -22119,7 +22119,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G750" t="n">
-        <v>2.56752014160156</v>
+        <v>2.56752038002014</v>
       </c>
       <c r="H750" t="n">
         <v>41661</v>
@@ -22148,7 +22148,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H751" t="n">
         <v>21292</v>
@@ -22177,7 +22177,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57107615470886</v>
+        <v>2.57107639312744</v>
       </c>
       <c r="H752" t="n">
         <v>65965</v>
@@ -22206,7 +22206,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.62086224555969</v>
+        <v>2.62086200714111</v>
       </c>
       <c r="H753" t="n">
         <v>95272</v>
@@ -22235,7 +22235,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H754" t="n">
         <v>126933</v>
@@ -22409,7 +22409,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>2.56040811538696</v>
+        <v>2.56040787696838</v>
       </c>
       <c r="H760" t="n">
         <v>41797</v>
@@ -22554,7 +22554,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>2.64931106567383</v>
+        <v>2.64931130409241</v>
       </c>
       <c r="H765" t="n">
         <v>23656</v>
@@ -22612,7 +22612,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.65286707878113</v>
+        <v>2.65286731719971</v>
       </c>
       <c r="H767" t="n">
         <v>90927</v>
@@ -22670,7 +22670,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G769" t="n">
-        <v>2.72043347358704</v>
+        <v>2.72043371200562</v>
       </c>
       <c r="H769" t="n">
         <v>128846</v>
@@ -22728,7 +22728,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>2.7951123714447</v>
+        <v>2.79511213302612</v>
       </c>
       <c r="H771" t="n">
         <v>92920</v>
@@ -22786,7 +22786,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G773" t="n">
-        <v>2.74532628059387</v>
+        <v>2.74532651901245</v>
       </c>
       <c r="H773" t="n">
         <v>45391</v>
@@ -22931,7 +22931,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71687746047974</v>
+        <v>2.71687769889832</v>
       </c>
       <c r="H778" t="n">
         <v>35869</v>
@@ -23192,7 +23192,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>2.64575505256653</v>
+        <v>2.64575481414795</v>
       </c>
       <c r="H787" t="n">
         <v>58312</v>
@@ -23221,7 +23221,7 @@
         <v>3.75</v>
       </c>
       <c r="G788" t="n">
-        <v>2.66709184646606</v>
+        <v>2.66709160804749</v>
       </c>
       <c r="H788" t="n">
         <v>41349</v>
@@ -23308,7 +23308,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G791" t="n">
-        <v>2.56396436691284</v>
+        <v>2.56396412849426</v>
       </c>
       <c r="H791" t="n">
         <v>79270</v>
@@ -23482,7 +23482,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>2.52129054069519</v>
+        <v>2.52129077911377</v>
       </c>
       <c r="H797" t="n">
         <v>223749</v>
@@ -23714,7 +23714,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>2.49284195899963</v>
+        <v>2.49284172058105</v>
       </c>
       <c r="H805" t="n">
         <v>67850</v>
@@ -23743,7 +23743,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>2.50350999832153</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H806" t="n">
         <v>42553</v>
@@ -23801,7 +23801,7 @@
         <v>3.5</v>
       </c>
       <c r="G808" t="n">
-        <v>2.48928546905518</v>
+        <v>2.48928594589233</v>
       </c>
       <c r="H808" t="n">
         <v>47766</v>
@@ -23830,7 +23830,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.48572945594788</v>
+        <v>2.4857292175293</v>
       </c>
       <c r="H809" t="n">
         <v>86790</v>
@@ -23888,7 +23888,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>2.3719334602356</v>
+        <v>2.37193369865417</v>
       </c>
       <c r="H811" t="n">
         <v>148443</v>
@@ -23975,7 +23975,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G814" t="n">
-        <v>2.34704041481018</v>
+        <v>2.34704065322876</v>
       </c>
       <c r="H814" t="n">
         <v>64507</v>
@@ -24033,7 +24033,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G816" t="n">
-        <v>2.29369902610779</v>
+        <v>2.29369878768921</v>
       </c>
       <c r="H816" t="n">
         <v>115001</v>
@@ -24091,7 +24091,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G818" t="n">
-        <v>2.27591848373413</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H818" t="n">
         <v>137063</v>
@@ -24120,7 +24120,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G819" t="n">
-        <v>2.27591848373413</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H819" t="n">
         <v>243571</v>
@@ -24149,7 +24149,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G820" t="n">
-        <v>2.27591848373413</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H820" t="n">
         <v>105828</v>
@@ -24178,7 +24178,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G821" t="n">
-        <v>2.27591848373413</v>
+        <v>2.27591824531555</v>
       </c>
       <c r="H821" t="n">
         <v>116326</v>
@@ -24265,7 +24265,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>2.29369902610779</v>
+        <v>2.29369878768921</v>
       </c>
       <c r="H824" t="n">
         <v>57282</v>
@@ -24381,7 +24381,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G828" t="n">
-        <v>2.3221480846405</v>
+        <v>2.32214784622192</v>
       </c>
       <c r="H828" t="n">
         <v>344993</v>
@@ -24410,7 +24410,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>2.35415291786194</v>
+        <v>2.35415315628052</v>
       </c>
       <c r="H829" t="n">
         <v>234469</v>
@@ -24439,7 +24439,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>2.3719334602356</v>
+        <v>2.37193369865417</v>
       </c>
       <c r="H830" t="n">
         <v>200129</v>
@@ -24468,7 +24468,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G831" t="n">
-        <v>2.35770893096924</v>
+        <v>2.35770916938782</v>
       </c>
       <c r="H831" t="n">
         <v>178502</v>
@@ -24497,7 +24497,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>2.36837720870972</v>
+        <v>2.3683774471283</v>
       </c>
       <c r="H832" t="n">
         <v>96015</v>
@@ -24526,7 +24526,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G833" t="n">
-        <v>2.30792331695557</v>
+        <v>2.30792307853699</v>
       </c>
       <c r="H833" t="n">
         <v>113930</v>
@@ -24555,7 +24555,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G834" t="n">
-        <v>2.30081105232239</v>
+        <v>2.30081129074097</v>
       </c>
       <c r="H834" t="n">
         <v>103372</v>
@@ -24584,7 +24584,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>2.29369902610779</v>
+        <v>2.29369878768921</v>
       </c>
       <c r="H835" t="n">
         <v>41499</v>
@@ -24729,7 +24729,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44305562973022</v>
+        <v>2.44305610656738</v>
       </c>
       <c r="H840" t="n">
         <v>95367</v>
@@ -24758,7 +24758,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>2.52129054069519</v>
+        <v>2.52129077911377</v>
       </c>
       <c r="H841" t="n">
         <v>189397</v>
@@ -24816,7 +24816,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G843" t="n">
-        <v>2.54262757301331</v>
+        <v>2.54262733459473</v>
       </c>
       <c r="H843" t="n">
         <v>56530</v>
@@ -24845,7 +24845,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G844" t="n">
-        <v>2.53907132148743</v>
+        <v>2.53907108306885</v>
       </c>
       <c r="H844" t="n">
         <v>120928</v>
@@ -24903,7 +24903,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5853009223938</v>
+        <v>2.58530068397522</v>
       </c>
       <c r="H846" t="n">
         <v>68274</v>
@@ -24990,7 +24990,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42883133888245</v>
+        <v>2.42883157730103</v>
       </c>
       <c r="H849" t="n">
         <v>74414</v>
@@ -25048,7 +25048,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G851" t="n">
-        <v>2.44305562973022</v>
+        <v>2.44305610656738</v>
       </c>
       <c r="H851" t="n">
         <v>61053</v>
@@ -25077,7 +25077,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G852" t="n">
-        <v>2.35415291786194</v>
+        <v>2.35415315628052</v>
       </c>
       <c r="H852" t="n">
         <v>91389</v>
@@ -25135,7 +25135,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>2.36497211456299</v>
+        <v>2.36497187614441</v>
       </c>
       <c r="H854" t="n">
         <v>91183</v>
@@ -25164,7 +25164,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>2.43540215492249</v>
+        <v>2.43540239334106</v>
       </c>
       <c r="H855" t="n">
         <v>60436</v>
@@ -25251,7 +25251,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>2.45764327049255</v>
+        <v>2.45764350891113</v>
       </c>
       <c r="H858" t="n">
         <v>144235</v>
@@ -25309,7 +25309,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.37238597869873</v>
+        <v>2.37238574028015</v>
       </c>
       <c r="H860" t="n">
         <v>119077</v>
@@ -25338,7 +25338,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G861" t="n">
-        <v>2.38350629806519</v>
+        <v>2.38350653648376</v>
       </c>
       <c r="H861" t="n">
         <v>36228</v>
@@ -25657,7 +25657,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05359625816345</v>
+        <v>2.05359649658203</v>
       </c>
       <c r="H872" t="n">
         <v>132549</v>
@@ -25715,7 +25715,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>2.07583737373352</v>
+        <v>2.0758376121521</v>
       </c>
       <c r="H874" t="n">
         <v>63145</v>
@@ -25773,7 +25773,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>2.12031984329224</v>
+        <v>2.12031960487366</v>
       </c>
       <c r="H876" t="n">
         <v>101590</v>
@@ -26266,7 +26266,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G893" t="n">
-        <v>2.2463526725769</v>
+        <v>2.24635291099548</v>
       </c>
       <c r="H893" t="n">
         <v>100791</v>
@@ -26295,7 +26295,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>2.23152565956116</v>
+        <v>2.23152542114258</v>
       </c>
       <c r="H894" t="n">
         <v>75028</v>
@@ -26411,7 +26411,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G898" t="n">
-        <v>2.27230072021484</v>
+        <v>2.27230048179626</v>
       </c>
       <c r="H898" t="n">
         <v>60128</v>
@@ -26440,7 +26440,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G899" t="n">
-        <v>2.27971458435059</v>
+        <v>2.27971434593201</v>
       </c>
       <c r="H899" t="n">
         <v>102850</v>
@@ -26614,7 +26614,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.28712844848633</v>
+        <v>2.28712821006775</v>
       </c>
       <c r="H905" t="n">
         <v>70844</v>
@@ -26672,7 +26672,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.2463526725769</v>
+        <v>2.24635291099548</v>
       </c>
       <c r="H907" t="n">
         <v>113173</v>
@@ -26730,7 +26730,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>2.26859402656555</v>
+        <v>2.26859378814697</v>
       </c>
       <c r="H909" t="n">
         <v>88883</v>
@@ -26759,7 +26759,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G910" t="n">
-        <v>2.23523235321045</v>
+        <v>2.23523211479187</v>
       </c>
       <c r="H910" t="n">
         <v>166947</v>
@@ -27020,7 +27020,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>2.1610951423645</v>
+        <v>2.16109490394592</v>
       </c>
       <c r="H919" t="n">
         <v>85520</v>
@@ -27078,7 +27078,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G921" t="n">
-        <v>2.15368127822876</v>
+        <v>2.15368151664734</v>
       </c>
       <c r="H921" t="n">
         <v>83002</v>
@@ -27136,7 +27136,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>2.19074988365173</v>
+        <v>2.19075012207031</v>
       </c>
       <c r="H923" t="n">
         <v>103378</v>
@@ -27165,7 +27165,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>2.12402677536011</v>
+        <v>2.12402653694153</v>
       </c>
       <c r="H924" t="n">
         <v>71584</v>
@@ -27194,7 +27194,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G925" t="n">
-        <v>2.12031984329224</v>
+        <v>2.12031960487366</v>
       </c>
       <c r="H925" t="n">
         <v>112906</v>
@@ -27281,7 +27281,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G928" t="n">
-        <v>2.09807872772217</v>
+        <v>2.09807848930359</v>
       </c>
       <c r="H928" t="n">
         <v>56531</v>
@@ -27310,7 +27310,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G929" t="n">
-        <v>2.15738868713379</v>
+        <v>2.15738844871521</v>
       </c>
       <c r="H929" t="n">
         <v>49771</v>
@@ -27455,7 +27455,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>2.16850900650024</v>
+        <v>2.16850876808167</v>
       </c>
       <c r="H934" t="n">
         <v>79342</v>
@@ -27542,7 +27542,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G937" t="n">
-        <v>2.29824876785278</v>
+        <v>2.2982485294342</v>
       </c>
       <c r="H937" t="n">
         <v>121304</v>
@@ -27658,7 +27658,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>2.63927912712097</v>
+        <v>2.63927936553955</v>
       </c>
       <c r="H941" t="n">
         <v>881119</v>
@@ -27687,7 +27687,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G942" t="n">
-        <v>2.79126024246216</v>
+        <v>2.79126048088074</v>
       </c>
       <c r="H942" t="n">
         <v>486765</v>
@@ -27745,7 +27745,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G944" t="n">
-        <v>2.77272582054138</v>
+        <v>2.77272605895996</v>
       </c>
       <c r="H944" t="n">
         <v>166865</v>
@@ -28035,7 +28035,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G954" t="n">
-        <v>2.70600271224976</v>
+        <v>2.70600247383118</v>
       </c>
       <c r="H954" t="n">
         <v>111884</v>
@@ -28180,7 +28180,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>2.71712279319763</v>
+        <v>2.71712303161621</v>
       </c>
       <c r="H959" t="n">
         <v>67572</v>
@@ -28267,7 +28267,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G962" t="n">
-        <v>2.76901912689209</v>
+        <v>2.76901888847351</v>
       </c>
       <c r="H962" t="n">
         <v>88960</v>
@@ -28470,7 +28470,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.68005442619324</v>
+        <v>2.68005466461182</v>
       </c>
       <c r="H969" t="n">
         <v>91180</v>
@@ -28557,7 +28557,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>2.91729331016541</v>
+        <v>2.91729307174683</v>
       </c>
       <c r="H972" t="n">
         <v>834985</v>
@@ -28702,7 +28702,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>2.80979442596436</v>
+        <v>2.80979466438293</v>
       </c>
       <c r="H977" t="n">
         <v>59739</v>
@@ -28731,7 +28731,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G978" t="n">
-        <v>2.86169028282166</v>
+        <v>2.86169004440308</v>
       </c>
       <c r="H978" t="n">
         <v>118454</v>
@@ -28760,7 +28760,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>2.89875888824463</v>
+        <v>2.89875864982605</v>
       </c>
       <c r="H979" t="n">
         <v>279460</v>
@@ -28789,7 +28789,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G980" t="n">
-        <v>2.90987920761108</v>
+        <v>2.90987944602966</v>
       </c>
       <c r="H980" t="n">
         <v>729798</v>
@@ -28847,7 +28847,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.9358274936676</v>
+        <v>2.93582725524902</v>
       </c>
       <c r="H982" t="n">
         <v>141285</v>
@@ -28905,7 +28905,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G984" t="n">
-        <v>3.05444669723511</v>
+        <v>3.05444645881653</v>
       </c>
       <c r="H984" t="n">
         <v>335251</v>
@@ -28963,7 +28963,7 @@
         <v>3.875</v>
       </c>
       <c r="G986" t="n">
-        <v>2.87281084060669</v>
+        <v>2.87281107902527</v>
       </c>
       <c r="H986" t="n">
         <v>309138</v>
@@ -28992,7 +28992,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>2.84315633773804</v>
+        <v>2.84315609931946</v>
       </c>
       <c r="H987" t="n">
         <v>262064</v>
@@ -29224,7 +29224,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>3.3954770565033</v>
+        <v>3.39547681808472</v>
       </c>
       <c r="H995" t="n">
         <v>642201</v>
@@ -29282,7 +29282,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>3.41771841049194</v>
+        <v>3.41771817207336</v>
       </c>
       <c r="H997" t="n">
         <v>202987</v>
@@ -29311,7 +29311,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G998" t="n">
-        <v>3.48073482513428</v>
+        <v>3.48073506355286</v>
       </c>
       <c r="H998" t="n">
         <v>434716</v>
@@ -29369,7 +29369,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.59935402870178</v>
+        <v>3.5993537902832</v>
       </c>
       <c r="H1000" t="n">
         <v>744840</v>
@@ -29398,7 +29398,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.59564709663391</v>
+        <v>3.59564685821533</v>
       </c>
       <c r="H1001" t="n">
         <v>333775</v>
@@ -29456,7 +29456,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.65866351127625</v>
+        <v>3.65866327285767</v>
       </c>
       <c r="H1003" t="n">
         <v>1079301</v>
@@ -29514,7 +29514,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1005" t="n">
         <v>332417</v>
@@ -29543,7 +29543,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1006" t="n">
         <v>349628</v>
@@ -29572,7 +29572,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.76616191864014</v>
+        <v>3.76616239547729</v>
       </c>
       <c r="H1007" t="n">
         <v>463372</v>
@@ -29688,7 +29688,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1011" t="n">
         <v>151303</v>
@@ -29717,7 +29717,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.76616191864014</v>
+        <v>3.76616239547729</v>
       </c>
       <c r="H1012" t="n">
         <v>191213</v>
@@ -29746,7 +29746,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.81064414978027</v>
+        <v>3.81064462661743</v>
       </c>
       <c r="H1013" t="n">
         <v>243495</v>
@@ -29775,7 +29775,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1014" t="n">
         <v>102689</v>
@@ -29804,7 +29804,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.8402988910675</v>
+        <v>3.84029936790466</v>
       </c>
       <c r="H1015" t="n">
         <v>295814</v>
@@ -29862,7 +29862,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.95891857147217</v>
+        <v>3.95891904830933</v>
       </c>
       <c r="H1017" t="n">
         <v>495513</v>
@@ -30007,7 +30007,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.85512685775757</v>
+        <v>3.85512638092041</v>
       </c>
       <c r="H1022" t="n">
         <v>233331</v>
@@ -30036,7 +30036,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.88478112220764</v>
+        <v>3.8847815990448</v>
       </c>
       <c r="H1023" t="n">
         <v>170141</v>
@@ -30094,7 +30094,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.88478112220764</v>
+        <v>3.8847815990448</v>
       </c>
       <c r="H1025" t="n">
         <v>156435</v>
@@ -30123,7 +30123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.85512685775757</v>
+        <v>3.85512638092041</v>
       </c>
       <c r="H1026" t="n">
         <v>83051</v>
@@ -30152,7 +30152,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.84771299362183</v>
+        <v>3.84771347045898</v>
       </c>
       <c r="H1027" t="n">
         <v>72510</v>
@@ -30210,7 +30210,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.81064414978027</v>
+        <v>3.81064462661743</v>
       </c>
       <c r="H1029" t="n">
         <v>213214</v>
@@ -30239,7 +30239,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.85512685775757</v>
+        <v>3.85512638092041</v>
       </c>
       <c r="H1030" t="n">
         <v>156105</v>
@@ -30326,7 +30326,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1033" t="n">
         <v>281130</v>
@@ -30384,7 +30384,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.76616191864014</v>
+        <v>3.76616239547729</v>
       </c>
       <c r="H1035" t="n">
         <v>209216</v>
@@ -30442,7 +30442,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.47332143783569</v>
+        <v>3.47332119941711</v>
       </c>
       <c r="H1037" t="n">
         <v>353099</v>
@@ -30558,7 +30558,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.76616191864014</v>
+        <v>3.76616239547729</v>
       </c>
       <c r="H1041" t="n">
         <v>81094</v>
@@ -30674,7 +30674,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.77357602119446</v>
+        <v>3.77357697486877</v>
       </c>
       <c r="H1045" t="n">
         <v>100770</v>
@@ -30906,7 +30906,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1053" t="n">
         <v>746712</v>
@@ -31022,7 +31022,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.63271617889404</v>
+        <v>3.63271594047546</v>
       </c>
       <c r="H1057" t="n">
         <v>486017</v>
@@ -31051,7 +31051,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.56599235534668</v>
+        <v>3.56599187850952</v>
       </c>
       <c r="H1058" t="n">
         <v>421740</v>
@@ -31080,7 +31080,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.66607761383057</v>
+        <v>3.66607785224915</v>
       </c>
       <c r="H1059" t="n">
         <v>331600</v>
@@ -31138,7 +31138,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.62159562110901</v>
+        <v>3.62159514427185</v>
       </c>
       <c r="H1061" t="n">
         <v>217946</v>
@@ -31167,7 +31167,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.55857920646667</v>
+        <v>3.5585789680481</v>
       </c>
       <c r="H1062" t="n">
         <v>398454</v>
@@ -31225,7 +31225,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.09522199630737</v>
+        <v>3.09522223472595</v>
       </c>
       <c r="H1064" t="n">
         <v>371613</v>
@@ -31312,7 +31312,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.51324605941772</v>
+        <v>2.5132462978363</v>
       </c>
       <c r="H1067" t="n">
         <v>717398</v>
@@ -31370,7 +31370,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.29083514213562</v>
+        <v>2.29083466529846</v>
       </c>
       <c r="H1069" t="n">
         <v>496099</v>
@@ -31399,7 +31399,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.15738868713379</v>
+        <v>2.15738844871521</v>
       </c>
       <c r="H1070" t="n">
         <v>234532</v>
@@ -31515,7 +31515,7 @@
         <v>3.125</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.31678318977356</v>
+        <v>2.31678295135498</v>
       </c>
       <c r="H1074" t="n">
         <v>253242</v>
@@ -31573,7 +31573,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.37238597869873</v>
+        <v>2.37238574028015</v>
       </c>
       <c r="H1076" t="n">
         <v>180047</v>
@@ -31747,7 +31747,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.29824876785278</v>
+        <v>2.2982485294342</v>
       </c>
       <c r="H1082" t="n">
         <v>115709</v>
@@ -31776,7 +31776,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.33531737327576</v>
+        <v>2.33531713485718</v>
       </c>
       <c r="H1083" t="n">
         <v>321839</v>
@@ -31805,7 +31805,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.53548741340637</v>
+        <v>2.53548717498779</v>
       </c>
       <c r="H1084" t="n">
         <v>286119</v>
@@ -31834,7 +31834,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.62815856933594</v>
+        <v>2.62815880775452</v>
       </c>
       <c r="H1085" t="n">
         <v>155985</v>
@@ -31921,7 +31921,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.57996940612793</v>
+        <v>2.57996964454651</v>
       </c>
       <c r="H1088" t="n">
         <v>215479</v>
@@ -31950,7 +31950,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.76901912689209</v>
+        <v>2.76901888847351</v>
       </c>
       <c r="H1089" t="n">
         <v>947909</v>
@@ -32095,7 +32095,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.01737833023071</v>
+        <v>3.01737809181213</v>
       </c>
       <c r="H1094" t="n">
         <v>245764</v>
@@ -32124,7 +32124,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.06927418708801</v>
+        <v>3.06927394866943</v>
       </c>
       <c r="H1095" t="n">
         <v>190108</v>
@@ -32269,7 +32269,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.07668781280518</v>
+        <v>3.07668805122375</v>
       </c>
       <c r="H1100" t="n">
         <v>96382</v>
@@ -32356,7 +32356,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.11375594139099</v>
+        <v>3.11375617980957</v>
       </c>
       <c r="H1103" t="n">
         <v>64482</v>
@@ -32472,7 +32472,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.06927418708801</v>
+        <v>3.06927394866943</v>
       </c>
       <c r="H1107" t="n">
         <v>237216</v>
@@ -32588,7 +32588,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.00255107879639</v>
+        <v>3.00255084037781</v>
       </c>
       <c r="H1111" t="n">
         <v>218512</v>
@@ -32617,7 +32617,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.97289633750916</v>
+        <v>2.97289609909058</v>
       </c>
       <c r="H1112" t="n">
         <v>174569</v>
@@ -32675,7 +32675,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.06927418708801</v>
+        <v>3.06927394866943</v>
       </c>
       <c r="H1114" t="n">
         <v>319518</v>
@@ -32733,7 +32733,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.15823841094971</v>
+        <v>3.15823864936829</v>
       </c>
       <c r="H1116" t="n">
         <v>314681</v>
@@ -32820,7 +32820,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.31392598152161</v>
+        <v>3.31392621994019</v>
       </c>
       <c r="H1119" t="n">
         <v>234448</v>
@@ -32849,7 +32849,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.2916853427887</v>
+        <v>3.29168558120728</v>
       </c>
       <c r="H1120" t="n">
         <v>119756</v>
@@ -32878,7 +32878,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.20642757415771</v>
+        <v>3.20642781257629</v>
       </c>
       <c r="H1121" t="n">
         <v>523519</v>
@@ -32907,7 +32907,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.28056502342224</v>
+        <v>3.28056526184082</v>
       </c>
       <c r="H1122" t="n">
         <v>86046</v>
@@ -32994,7 +32994,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17677235603333</v>
+        <v>3.17677283287048</v>
       </c>
       <c r="H1125" t="n">
         <v>216177</v>
@@ -33023,7 +33023,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.10634255409241</v>
+        <v>3.10634279251099</v>
       </c>
       <c r="H1126" t="n">
         <v>157535</v>
@@ -33081,7 +33081,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.7393639087677</v>
+        <v>2.73936414718628</v>
       </c>
       <c r="H1128" t="n">
         <v>597174</v>
@@ -33110,7 +33110,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.77643251419067</v>
+        <v>2.77643275260925</v>
       </c>
       <c r="H1129" t="n">
         <v>482471</v>
@@ -33197,7 +33197,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.77643251419067</v>
+        <v>2.77643275260925</v>
       </c>
       <c r="H1132" t="n">
         <v>136838</v>
@@ -33226,7 +33226,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.79126024246216</v>
+        <v>2.79126048088074</v>
       </c>
       <c r="H1133" t="n">
         <v>110451</v>
@@ -33284,7 +33284,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.05444669723511</v>
+        <v>3.05444645881653</v>
       </c>
       <c r="H1135" t="n">
         <v>906769</v>
@@ -33313,7 +33313,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.9358274936676</v>
+        <v>2.93582725524902</v>
       </c>
       <c r="H1136" t="n">
         <v>472549</v>
@@ -33371,7 +33371,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.80979442596436</v>
+        <v>2.80979466438293</v>
       </c>
       <c r="H1138" t="n">
         <v>188394</v>
@@ -33516,7 +33516,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85798358917236</v>
+        <v>2.85798335075378</v>
       </c>
       <c r="H1143" t="n">
         <v>86988</v>
@@ -33574,7 +33574,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.9543616771698</v>
+        <v>2.95436143875122</v>
       </c>
       <c r="H1145" t="n">
         <v>154435</v>
@@ -33603,7 +33603,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.00996446609497</v>
+        <v>3.00996422767639</v>
       </c>
       <c r="H1146" t="n">
         <v>287815</v>
@@ -33632,7 +33632,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.00255107879639</v>
+        <v>3.00255084037781</v>
       </c>
       <c r="H1147" t="n">
         <v>144248</v>
@@ -33661,7 +33661,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.97289633750916</v>
+        <v>2.97289609909058</v>
       </c>
       <c r="H1148" t="n">
         <v>101837</v>
@@ -33719,7 +33719,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.05444669723511</v>
+        <v>3.05444645881653</v>
       </c>
       <c r="H1150" t="n">
         <v>85124</v>
@@ -33864,7 +33864,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.12116980552673</v>
+        <v>3.12117004394531</v>
       </c>
       <c r="H1155" t="n">
         <v>89194</v>
@@ -34067,7 +34067,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.1841869354248</v>
+        <v>3.18418669700623</v>
       </c>
       <c r="H1162" t="n">
         <v>152609</v>
@@ -34125,7 +34125,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.10634255409241</v>
+        <v>3.10634279251099</v>
       </c>
       <c r="H1164" t="n">
         <v>90903</v>
@@ -34154,7 +34154,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.13970422744751</v>
+        <v>3.13970446586609</v>
       </c>
       <c r="H1165" t="n">
         <v>123022</v>
@@ -34183,7 +34183,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.15453147888184</v>
+        <v>3.15453171730042</v>
       </c>
       <c r="H1166" t="n">
         <v>119978</v>
@@ -34212,7 +34212,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.22125482559204</v>
+        <v>3.22125458717346</v>
       </c>
       <c r="H1167" t="n">
         <v>93532</v>
@@ -34328,7 +34328,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.35099482536316</v>
+        <v>3.35099506378174</v>
       </c>
       <c r="H1171" t="n">
         <v>67426</v>
@@ -34357,7 +34357,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.32875347137451</v>
+        <v>3.32875370979309</v>
       </c>
       <c r="H1172" t="n">
         <v>50708</v>
@@ -34415,7 +34415,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.55857920646667</v>
+        <v>3.5585789680481</v>
       </c>
       <c r="H1174" t="n">
         <v>195254</v>
@@ -34444,7 +34444,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.65866351127625</v>
+        <v>3.65866327285767</v>
       </c>
       <c r="H1175" t="n">
         <v>294092</v>
@@ -34502,7 +34502,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.58082008361816</v>
+        <v>3.58081984519958</v>
       </c>
       <c r="H1177" t="n">
         <v>88222</v>
@@ -34531,7 +34531,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.50668287277222</v>
+        <v>3.50668263435364</v>
       </c>
       <c r="H1178" t="n">
         <v>89172</v>
@@ -34560,7 +34560,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.41771841049194</v>
+        <v>3.41771817207336</v>
       </c>
       <c r="H1179" t="n">
         <v>98749</v>
@@ -34589,7 +34589,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.70314574241638</v>
+        <v>3.70314598083496</v>
       </c>
       <c r="H1180" t="n">
         <v>607643</v>
@@ -34821,7 +34821,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.84771299362183</v>
+        <v>3.84771347045898</v>
       </c>
       <c r="H1188" t="n">
         <v>228820</v>
@@ -34850,7 +34850,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.79581665992737</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1189" t="n">
         <v>155683</v>
@@ -34879,7 +34879,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.86254048347473</v>
+        <v>3.86254000663757</v>
       </c>
       <c r="H1190" t="n">
         <v>93171</v>
@@ -34966,7 +34966,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.55942916870117</v>
+        <v>4.55942869186401</v>
       </c>
       <c r="H1193" t="n">
         <v>521199</v>
@@ -35053,7 +35053,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.4704647064209</v>
+        <v>4.47046422958374</v>
       </c>
       <c r="H1196" t="n">
         <v>212780</v>
@@ -35227,7 +35227,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.01907825469971</v>
+        <v>5.01907873153687</v>
       </c>
       <c r="H1202" t="n">
         <v>675366</v>
@@ -35256,7 +35256,7 @@
         <v>6.75</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.00425148010254</v>
+        <v>5.00425100326538</v>
       </c>
       <c r="H1203" t="n">
         <v>310965</v>
@@ -35372,7 +35372,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1207" t="n">
-        <v>5.59734773635864</v>
+        <v>5.5973482131958</v>
       </c>
       <c r="H1207" t="n">
         <v>525409</v>
@@ -35401,7 +35401,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.46390104293823</v>
+        <v>5.46390056610107</v>
       </c>
       <c r="H1208" t="n">
         <v>424268</v>
@@ -35430,7 +35430,7 @@
         <v>7.5</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.56027936935425</v>
+        <v>5.56027984619141</v>
       </c>
       <c r="H1209" t="n">
         <v>262844</v>
@@ -35459,7 +35459,7 @@
         <v>7.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.56027936935425</v>
+        <v>5.56027984619141</v>
       </c>
       <c r="H1210" t="n">
         <v>186425</v>
@@ -35488,7 +35488,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.58252048492432</v>
+        <v>5.58252096176147</v>
       </c>
       <c r="H1211" t="n">
         <v>199033</v>
@@ -35517,7 +35517,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.73820781707764</v>
+        <v>5.73820734024048</v>
       </c>
       <c r="H1212" t="n">
         <v>297846</v>
@@ -35575,7 +35575,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.62700223922729</v>
+        <v>5.62700271606445</v>
       </c>
       <c r="H1214" t="n">
         <v>339811</v>
@@ -35633,7 +35633,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.76044940948486</v>
+        <v>5.76044893264771</v>
       </c>
       <c r="H1216" t="n">
         <v>234743</v>
@@ -35720,7 +35720,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>5.61958885192871</v>
+        <v>5.61958932876587</v>
       </c>
       <c r="H1219" t="n">
         <v>104998</v>
@@ -35865,7 +35865,7 @@
         <v>7.25</v>
       </c>
       <c r="G1224" t="n">
-        <v>5.37493658065796</v>
+        <v>5.3749361038208</v>
       </c>
       <c r="H1224" t="n">
         <v>174643</v>
@@ -35923,7 +35923,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1226" t="n">
-        <v>5.0932149887085</v>
+        <v>5.09321546554565</v>
       </c>
       <c r="H1226" t="n">
         <v>195209</v>
@@ -35952,7 +35952,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.17476654052734</v>
+        <v>5.1747670173645</v>
       </c>
       <c r="H1227" t="n">
         <v>335188</v>
@@ -36068,7 +36068,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.59734773635864</v>
+        <v>5.5973482131958</v>
       </c>
       <c r="H1231" t="n">
         <v>248006</v>
@@ -36126,7 +36126,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.76044940948486</v>
+        <v>5.76044893264771</v>
       </c>
       <c r="H1233" t="n">
         <v>508299</v>
@@ -36184,7 +36184,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.66407108306885</v>
+        <v>5.66407060623169</v>
       </c>
       <c r="H1235" t="n">
         <v>427727</v>
@@ -36242,7 +36242,7 @@
         <v>7.75</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.74562168121338</v>
+        <v>5.74562215805054</v>
       </c>
       <c r="H1237" t="n">
         <v>409520</v>
@@ -36271,7 +36271,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.79010438919067</v>
+        <v>5.79010391235352</v>
       </c>
       <c r="H1238" t="n">
         <v>185181</v>
@@ -36300,7 +36300,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>6.51664781570435</v>
+        <v>6.51664733886719</v>
       </c>
       <c r="H1239" t="n">
         <v>1181498</v>
@@ -36329,7 +36329,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1240" t="n">
-        <v>6.5018196105957</v>
+        <v>6.50182008743286</v>
       </c>
       <c r="H1240" t="n">
         <v>856188</v>
@@ -36416,7 +36416,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1243" t="n">
-        <v>6.33871793746948</v>
+        <v>6.33871841430664</v>
       </c>
       <c r="H1243" t="n">
         <v>535392</v>
@@ -36445,7 +36445,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1244" t="n">
-        <v>6.27940845489502</v>
+        <v>6.27940893173218</v>
       </c>
       <c r="H1244" t="n">
         <v>226764</v>
@@ -36474,7 +36474,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1245" t="n">
-        <v>6.24233961105347</v>
+        <v>6.24234008789062</v>
       </c>
       <c r="H1245" t="n">
         <v>371423</v>
@@ -36706,7 +36706,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1253" t="n">
-        <v>6.58337068557739</v>
+        <v>6.58337116241455</v>
       </c>
       <c r="H1253" t="n">
         <v>375451</v>
@@ -36735,7 +36735,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1254" t="n">
-        <v>6.57595634460449</v>
+        <v>6.57595682144165</v>
       </c>
       <c r="H1254" t="n">
         <v>163814</v>
@@ -36793,7 +36793,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.11715841293335</v>
+        <v>7.11715793609619</v>
       </c>
       <c r="H1256" t="n">
         <v>593443</v>
@@ -36909,7 +36909,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1260" t="n">
-        <v>7.47301483154297</v>
+        <v>7.47301578521729</v>
       </c>
       <c r="H1260" t="n">
         <v>545649</v>
@@ -36938,7 +36938,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1261" t="n">
-        <v>7.54715204238892</v>
+        <v>7.54715394973755</v>
       </c>
       <c r="H1261" t="n">
         <v>292983</v>
@@ -37083,7 +37083,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1266" t="n">
-        <v>7.94749307632446</v>
+        <v>7.94749212265015</v>
       </c>
       <c r="H1266" t="n">
         <v>283644</v>
@@ -37286,7 +37286,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1273" t="n">
-        <v>7.44335985183716</v>
+        <v>7.44336032867432</v>
       </c>
       <c r="H1273" t="n">
         <v>832254</v>
@@ -37315,7 +37315,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.68059778213501</v>
+        <v>7.68059873580933</v>
       </c>
       <c r="H1274" t="n">
         <v>508688</v>
@@ -37344,7 +37344,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>7.54715204238892</v>
+        <v>7.54715394973755</v>
       </c>
       <c r="H1275" t="n">
         <v>266888</v>
@@ -37373,7 +37373,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.59163331985474</v>
+        <v>7.59163427352905</v>
       </c>
       <c r="H1276" t="n">
         <v>279624</v>
@@ -37402,7 +37402,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1277" t="n">
-        <v>7.30250072479248</v>
+        <v>7.30250024795532</v>
       </c>
       <c r="H1277" t="n">
         <v>314055</v>
@@ -37460,7 +37460,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1279" t="n">
-        <v>7.47301483154297</v>
+        <v>7.47301578521729</v>
       </c>
       <c r="H1279" t="n">
         <v>387332</v>
@@ -37489,7 +37489,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G1280" t="n">
-        <v>7.33215522766113</v>
+        <v>7.33215570449829</v>
       </c>
       <c r="H1280" t="n">
         <v>468812</v>
@@ -37605,7 +37605,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1284" t="n">
-        <v>7.30250072479248</v>
+        <v>7.30250024795532</v>
       </c>
       <c r="H1284" t="n">
         <v>165936</v>
@@ -37634,7 +37634,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.32474088668823</v>
+        <v>7.32474136352539</v>
       </c>
       <c r="H1285" t="n">
         <v>250867</v>
@@ -37692,7 +37692,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1287" t="n">
-        <v>7.32474088668823</v>
+        <v>7.32474136352539</v>
       </c>
       <c r="H1287" t="n">
         <v>347288</v>
@@ -37721,7 +37721,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1288" t="n">
-        <v>7.08008861541748</v>
+        <v>7.08008909225464</v>
       </c>
       <c r="H1288" t="n">
         <v>551582</v>
@@ -37750,7 +37750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.19129419326782</v>
+        <v>7.19129371643066</v>
       </c>
       <c r="H1289" t="n">
         <v>237577</v>
@@ -37837,7 +37837,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.2802586555481</v>
+        <v>7.28025817871094</v>
       </c>
       <c r="H1292" t="n">
         <v>172742</v>
@@ -37895,7 +37895,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1294" t="n">
-        <v>7.47301483154297</v>
+        <v>7.47301578521729</v>
       </c>
       <c r="H1294" t="n">
         <v>249714</v>
@@ -38098,7 +38098,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1301" t="n">
-        <v>8.49610710144043</v>
+        <v>8.49610614776611</v>
       </c>
       <c r="H1301" t="n">
         <v>302498</v>
@@ -38127,7 +38127,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1302" t="n">
-        <v>8.49610710144043</v>
+        <v>8.49610614776611</v>
       </c>
       <c r="H1302" t="n">
         <v>202294</v>
@@ -38243,7 +38243,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1306" t="n">
-        <v>8.31817722320557</v>
+        <v>8.31817817687988</v>
       </c>
       <c r="H1306" t="n">
         <v>89949</v>
@@ -38359,7 +38359,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.84369993209839</v>
+        <v>7.84370088577271</v>
       </c>
       <c r="H1310" t="n">
         <v>221178</v>
@@ -38475,7 +38475,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.44335985183716</v>
+        <v>7.44336032867432</v>
       </c>
       <c r="H1314" t="n">
         <v>524870</v>
@@ -38504,7 +38504,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1315" t="n">
-        <v>7.30250072479248</v>
+        <v>7.30250024795532</v>
       </c>
       <c r="H1315" t="n">
         <v>832363</v>
@@ -38533,7 +38533,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1316" t="n">
-        <v>7.29508590698242</v>
+        <v>7.29508638381958</v>
       </c>
       <c r="H1316" t="n">
         <v>473082</v>
@@ -38562,7 +38562,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1317" t="n">
-        <v>7.44335985183716</v>
+        <v>7.44336032867432</v>
       </c>
       <c r="H1317" t="n">
         <v>378883</v>
@@ -38620,7 +38620,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>7.69542598724365</v>
+        <v>7.69542694091797</v>
       </c>
       <c r="H1319" t="n">
         <v>388891</v>
@@ -38649,7 +38649,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1320" t="n">
-        <v>7.59163331985474</v>
+        <v>7.59163427352905</v>
       </c>
       <c r="H1320" t="n">
         <v>242496</v>
@@ -38678,7 +38678,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1321" t="n">
-        <v>7.51749753952026</v>
+        <v>7.51749849319458</v>
       </c>
       <c r="H1321" t="n">
         <v>215080</v>
@@ -38707,7 +38707,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1322" t="n">
-        <v>7.75473594665527</v>
+        <v>7.75473546981812</v>
       </c>
       <c r="H1322" t="n">
         <v>498215</v>
@@ -38736,7 +38736,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1323" t="n">
-        <v>7.5026707649231</v>
+        <v>7.50267028808594</v>
       </c>
       <c r="H1323" t="n">
         <v>392802</v>
@@ -38765,7 +38765,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1324" t="n">
-        <v>7.62128829956055</v>
+        <v>7.62128925323486</v>
       </c>
       <c r="H1324" t="n">
         <v>262438</v>
@@ -38794,7 +38794,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1325" t="n">
-        <v>7.62128829956055</v>
+        <v>7.62128925323486</v>
       </c>
       <c r="H1325" t="n">
         <v>298270</v>
@@ -38852,7 +38852,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1327" t="n">
-        <v>7.91783714294434</v>
+        <v>7.91783809661865</v>
       </c>
       <c r="H1327" t="n">
         <v>540331</v>
@@ -38910,7 +38910,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1329" t="n">
-        <v>7.84369993209839</v>
+        <v>7.84370088577271</v>
       </c>
       <c r="H1329" t="n">
         <v>200870</v>
@@ -39055,7 +39055,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1334" t="n">
-        <v>8.0809383392334</v>
+        <v>8.08093929290771</v>
       </c>
       <c r="H1334" t="n">
         <v>250595</v>
@@ -39113,7 +39113,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1336" t="n">
-        <v>8.42196941375732</v>
+        <v>8.42196846008301</v>
       </c>
       <c r="H1336" t="n">
         <v>447036</v>
@@ -39229,7 +39229,7 @@
         <v>13.5</v>
       </c>
       <c r="G1340" t="n">
-        <v>10.0085029602051</v>
+        <v>10.0085020065308</v>
       </c>
       <c r="H1340" t="n">
         <v>837762</v>
@@ -39345,7 +39345,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1344" t="n">
-        <v>9.99367523193359</v>
+        <v>9.99367427825928</v>
       </c>
       <c r="H1344" t="n">
         <v>540353</v>
@@ -39374,7 +39374,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.9566068649292</v>
+        <v>9.95660591125488</v>
       </c>
       <c r="H1345" t="n">
         <v>608465</v>
@@ -39403,7 +39403,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1346" t="n">
-        <v>10.0752258300781</v>
+        <v>10.0752248764038</v>
       </c>
       <c r="H1346" t="n">
         <v>298506</v>
@@ -39490,7 +39490,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1349" t="n">
-        <v>10.2383279800415</v>
+        <v>10.2383289337158</v>
       </c>
       <c r="H1349" t="n">
         <v>493981</v>
@@ -39606,7 +39606,7 @@
         <v>13.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>10.0085029602051</v>
+        <v>10.0085020065308</v>
       </c>
       <c r="H1353" t="n">
         <v>305598</v>
@@ -39635,7 +39635,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1354" t="n">
-        <v>10.1271209716797</v>
+        <v>10.127121925354</v>
       </c>
       <c r="H1354" t="n">
         <v>513857</v>
@@ -39664,7 +39664,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.9566068649292</v>
+        <v>9.95660591125488</v>
       </c>
       <c r="H1355" t="n">
         <v>386695</v>
@@ -39722,7 +39722,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1357" t="n">
-        <v>9.97884654998779</v>
+        <v>9.97884750366211</v>
       </c>
       <c r="H1357" t="n">
         <v>246480</v>
@@ -39780,7 +39780,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G1359" t="n">
-        <v>10.0285978317261</v>
+        <v>10.0285968780518</v>
       </c>
       <c r="H1359" t="n">
         <v>363619</v>
@@ -39838,7 +39838,7 @@
         <v>13.25</v>
       </c>
       <c r="G1361" t="n">
-        <v>10.2293243408203</v>
+        <v>10.229323387146</v>
       </c>
       <c r="H1361" t="n">
         <v>481650</v>
@@ -39896,7 +39896,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1363" t="n">
-        <v>9.92051410675049</v>
+        <v>9.92051315307617</v>
       </c>
       <c r="H1363" t="n">
         <v>442173</v>
@@ -39954,7 +39954,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1365" t="n">
-        <v>10.2524843215942</v>
+        <v>10.2524852752686</v>
       </c>
       <c r="H1365" t="n">
         <v>930701</v>
@@ -40244,7 +40244,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1375" t="n">
-        <v>11.2252359390259</v>
+        <v>11.2252349853516</v>
       </c>
       <c r="H1375" t="n">
         <v>441675</v>
@@ -40331,7 +40331,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.472282409668</v>
+        <v>11.4722833633423</v>
       </c>
       <c r="H1378" t="n">
         <v>404357</v>
@@ -40447,7 +40447,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.7888145446777</v>
+        <v>11.7888135910034</v>
       </c>
       <c r="H1382" t="n">
         <v>401929</v>
@@ -40534,7 +40534,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1385" t="n">
-        <v>11.7810926437378</v>
+        <v>11.7810935974121</v>
       </c>
       <c r="H1385" t="n">
         <v>702886</v>
@@ -40563,7 +40563,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>11.6575698852539</v>
+        <v>11.6575689315796</v>
       </c>
       <c r="H1386" t="n">
         <v>248187</v>
@@ -40679,7 +40679,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1390" t="n">
-        <v>11.8582954406738</v>
+        <v>11.8582944869995</v>
       </c>
       <c r="H1390" t="n">
         <v>217840</v>
@@ -40708,7 +40708,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.4954433441162</v>
+        <v>11.4954442977905</v>
       </c>
       <c r="H1391" t="n">
         <v>232147</v>
@@ -40795,7 +40795,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1394" t="n">
-        <v>11.6575698852539</v>
+        <v>11.6575689315796</v>
       </c>
       <c r="H1394" t="n">
         <v>177496</v>
@@ -40853,7 +40853,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1396" t="n">
-        <v>11.4414024353027</v>
+        <v>11.4414014816284</v>
       </c>
       <c r="H1396" t="n">
         <v>226584</v>
@@ -40882,7 +40882,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1397" t="n">
-        <v>11.449122428894</v>
+        <v>11.4491233825684</v>
       </c>
       <c r="H1397" t="n">
         <v>322076</v>
@@ -40940,7 +40940,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>11.6575698852539</v>
+        <v>11.6575689315796</v>
       </c>
       <c r="H1399" t="n">
         <v>196451</v>
@@ -40969,7 +40969,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1400" t="n">
-        <v>11.6344079971313</v>
+        <v>11.6344089508057</v>
       </c>
       <c r="H1400" t="n">
         <v>333893</v>
@@ -41056,7 +41056,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1403" t="n">
-        <v>11.4414024353027</v>
+        <v>11.4414014816284</v>
       </c>
       <c r="H1403" t="n">
         <v>185872</v>
@@ -41201,7 +41201,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G1408" t="n">
-        <v>11.8351354598999</v>
+        <v>11.8351345062256</v>
       </c>
       <c r="H1408" t="n">
         <v>203447</v>
@@ -41259,7 +41259,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.0476694107056</v>
+        <v>11.0476703643799</v>
       </c>
       <c r="H1410" t="n">
         <v>171270</v>
@@ -41375,7 +41375,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1414" t="n">
-        <v>11.7810926437378</v>
+        <v>11.7810935974121</v>
       </c>
       <c r="H1414" t="n">
         <v>153562</v>
@@ -41404,7 +41404,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.5649251937866</v>
+        <v>11.5649261474609</v>
       </c>
       <c r="H1415" t="n">
         <v>274874</v>
@@ -41578,7 +41578,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1421" t="n">
-        <v>12.3987121582031</v>
+        <v>12.3987131118774</v>
       </c>
       <c r="H1421" t="n">
         <v>274686</v>
@@ -41636,7 +41636,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1423" t="n">
-        <v>12.1671056747437</v>
+        <v>12.1671047210693</v>
       </c>
       <c r="H1423" t="n">
         <v>126683</v>
@@ -41665,7 +41665,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1424" t="n">
-        <v>12.3987121582031</v>
+        <v>12.3987131118774</v>
       </c>
       <c r="H1424" t="n">
         <v>122796</v>
@@ -41781,7 +41781,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G1428" t="n">
-        <v>12.2674684524536</v>
+        <v>12.2674694061279</v>
       </c>
       <c r="H1428" t="n">
         <v>570682</v>
@@ -41810,7 +41810,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G1429" t="n">
-        <v>12.3292293548584</v>
+        <v>12.3292303085327</v>
       </c>
       <c r="H1429" t="n">
         <v>169314</v>
@@ -41955,7 +41955,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.0435829162598</v>
+        <v>12.0435819625854</v>
       </c>
       <c r="H1434" t="n">
         <v>397932</v>
@@ -42042,7 +42042,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>12.0435829162598</v>
+        <v>12.0435819625854</v>
       </c>
       <c r="H1437" t="n">
         <v>179780</v>
@@ -42071,7 +42071,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1438" t="n">
-        <v>12.3137903213501</v>
+        <v>12.3137912750244</v>
       </c>
       <c r="H1438" t="n">
         <v>314877</v>
@@ -42187,7 +42187,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.2751893997192</v>
+        <v>12.2751884460449</v>
       </c>
       <c r="H1442" t="n">
         <v>199236</v>
@@ -42216,7 +42216,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="n">
-        <v>12.3523921966553</v>
+        <v>12.352391242981</v>
       </c>
       <c r="H1443" t="n">
         <v>136530</v>
@@ -42303,7 +42303,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1446" t="n">
-        <v>10.83922290802</v>
+        <v>10.8392238616943</v>
       </c>
       <c r="H1446" t="n">
         <v>1445495</v>
@@ -42332,7 +42332,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1447" t="n">
-        <v>10.5149736404419</v>
+        <v>10.5149726867676</v>
       </c>
       <c r="H1447" t="n">
         <v>1307534</v>
@@ -42419,7 +42419,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0749197006226</v>
+        <v>10.0749187469482</v>
       </c>
       <c r="H1450" t="n">
         <v>1314808</v>
@@ -42477,7 +42477,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>9.72750949859619</v>
+        <v>9.72750854492188</v>
       </c>
       <c r="H1452" t="n">
         <v>423397</v>
@@ -42506,7 +42506,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1453" t="n">
-        <v>9.61942481994629</v>
+        <v>9.61942386627197</v>
       </c>
       <c r="H1453" t="n">
         <v>427074</v>
@@ -42651,7 +42651,7 @@
         <v>12</v>
       </c>
       <c r="G1458" t="n">
-        <v>9.26429462432861</v>
+        <v>9.2642936706543</v>
       </c>
       <c r="H1458" t="n">
         <v>357284</v>
@@ -42680,7 +42680,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1459" t="n">
-        <v>9.10988807678223</v>
+        <v>9.10988903045654</v>
       </c>
       <c r="H1459" t="n">
         <v>314944</v>
@@ -42738,7 +42738,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.71615505218506</v>
+        <v>8.71615600585938</v>
       </c>
       <c r="H1461" t="n">
         <v>263441</v>
@@ -42767,7 +42767,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.73159599304199</v>
+        <v>8.73159694671631</v>
       </c>
       <c r="H1462" t="n">
         <v>423384</v>
@@ -42796,7 +42796,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1463" t="n">
-        <v>8.77019691467285</v>
+        <v>8.77019786834717</v>
       </c>
       <c r="H1463" t="n">
         <v>308620</v>
@@ -42854,7 +42854,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.52314949035645</v>
+        <v>8.52315044403076</v>
       </c>
       <c r="H1465" t="n">
         <v>397323</v>
@@ -42999,7 +42999,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.723876953125</v>
+        <v>8.72387599945068</v>
       </c>
       <c r="H1470" t="n">
         <v>331845</v>
@@ -43057,7 +43057,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1472" t="n">
-        <v>8.8474006652832</v>
+        <v>8.84739971160889</v>
       </c>
       <c r="H1472" t="n">
         <v>457138</v>
@@ -43202,7 +43202,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1477" t="n">
-        <v>9.10988807678223</v>
+        <v>9.10988903045654</v>
       </c>
       <c r="H1477" t="n">
         <v>164981</v>
@@ -43231,7 +43231,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1478" t="n">
-        <v>9.12532901763916</v>
+        <v>9.12532806396484</v>
       </c>
       <c r="H1478" t="n">
         <v>221754</v>
@@ -43318,7 +43318,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1481" t="n">
-        <v>8.71615505218506</v>
+        <v>8.71615600585938</v>
       </c>
       <c r="H1481" t="n">
         <v>404867</v>
@@ -43347,7 +43347,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.723876953125</v>
+        <v>8.72387599945068</v>
       </c>
       <c r="H1482" t="n">
         <v>214386</v>
@@ -43376,7 +43376,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1483" t="n">
-        <v>8.6621150970459</v>
+        <v>8.66211414337158</v>
       </c>
       <c r="H1483" t="n">
         <v>195852</v>
@@ -43463,7 +43463,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1486" t="n">
-        <v>9.31833362579346</v>
+        <v>9.31833457946777</v>
       </c>
       <c r="H1486" t="n">
         <v>306731</v>
@@ -43492,7 +43492,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1487" t="n">
-        <v>9.60398387908936</v>
+        <v>9.60398483276367</v>
       </c>
       <c r="H1487" t="n">
         <v>810378</v>
@@ -43521,7 +43521,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G1488" t="n">
-        <v>9.6271448135376</v>
+        <v>9.62714576721191</v>
       </c>
       <c r="H1488" t="n">
         <v>370289</v>
@@ -43782,7 +43782,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1497" t="n">
-        <v>9.66574573516846</v>
+        <v>9.66574668884277</v>
       </c>
       <c r="H1497" t="n">
         <v>248033</v>
@@ -43811,7 +43811,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1498" t="n">
-        <v>9.58854389190674</v>
+        <v>9.58854293823242</v>
       </c>
       <c r="H1498" t="n">
         <v>260428</v>
@@ -43869,7 +43869,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1500" t="n">
-        <v>9.00952529907227</v>
+        <v>9.00952625274658</v>
       </c>
       <c r="H1500" t="n">
         <v>531730</v>
@@ -43898,7 +43898,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1501" t="n">
-        <v>9.06356716156006</v>
+        <v>9.06356620788574</v>
       </c>
       <c r="H1501" t="n">
         <v>189209</v>
@@ -44159,7 +44159,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G1510" t="n">
-        <v>10.2447662353516</v>
+        <v>10.2447652816772</v>
       </c>
       <c r="H1510" t="n">
         <v>587994</v>
@@ -44217,7 +44217,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1512" t="n">
-        <v>10.0671987533569</v>
+        <v>10.0671997070312</v>
       </c>
       <c r="H1512" t="n">
         <v>378676</v>
@@ -44304,7 +44304,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1515" t="n">
-        <v>9.36465549468994</v>
+        <v>9.36465644836426</v>
       </c>
       <c r="H1515" t="n">
         <v>333489</v>
@@ -44391,7 +44391,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1518" t="n">
-        <v>9.12532901763916</v>
+        <v>9.12532806396484</v>
       </c>
       <c r="H1518" t="n">
         <v>128055</v>
@@ -44507,7 +44507,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1522" t="n">
-        <v>9.64258575439453</v>
+        <v>9.64258480072021</v>
       </c>
       <c r="H1522" t="n">
         <v>154036</v>
@@ -44536,7 +44536,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1523" t="n">
-        <v>9.79699039459229</v>
+        <v>9.79698944091797</v>
       </c>
       <c r="H1523" t="n">
         <v>82403</v>
@@ -44565,7 +44565,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1524" t="n">
-        <v>9.92051410675049</v>
+        <v>9.92051315307617</v>
       </c>
       <c r="H1524" t="n">
         <v>123851</v>
@@ -44652,7 +44652,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1527" t="n">
-        <v>10.2833652496338</v>
+        <v>10.2833662033081</v>
       </c>
       <c r="H1527" t="n">
         <v>248048</v>
@@ -44710,7 +44710,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1529" t="n">
-        <v>9.88963413238525</v>
+        <v>9.88963317871094</v>
       </c>
       <c r="H1529" t="n">
         <v>160472</v>
@@ -44797,7 +44797,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.99408531188965</v>
+        <v>8.99408435821533</v>
       </c>
       <c r="H1532" t="n">
         <v>392300</v>
@@ -44826,7 +44826,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1533" t="n">
-        <v>9.23341178894043</v>
+        <v>9.23341274261475</v>
       </c>
       <c r="H1533" t="n">
         <v>160295</v>
@@ -44913,7 +44913,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1536" t="n">
-        <v>9.36465549468994</v>
+        <v>9.36465644836426</v>
       </c>
       <c r="H1536" t="n">
         <v>130194</v>
@@ -44942,7 +44942,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1537" t="n">
-        <v>9.61170482635498</v>
+        <v>9.61170387268066</v>
       </c>
       <c r="H1537" t="n">
         <v>191883</v>
@@ -45029,7 +45029,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1540" t="n">
-        <v>9.64258575439453</v>
+        <v>9.64258480072021</v>
       </c>
       <c r="H1540" t="n">
         <v>178357</v>
@@ -45058,7 +45058,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G1541" t="n">
-        <v>9.39553833007812</v>
+        <v>9.39553737640381</v>
       </c>
       <c r="H1541" t="n">
         <v>167766</v>
@@ -45319,7 +45319,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1550" t="n">
-        <v>9.37237739562988</v>
+        <v>9.37237644195557</v>
       </c>
       <c r="H1550" t="n">
         <v>121403</v>
@@ -45377,7 +45377,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1552" t="n">
-        <v>9.10988807678223</v>
+        <v>9.10988903045654</v>
       </c>
       <c r="H1552" t="n">
         <v>134055</v>
@@ -45406,7 +45406,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>9.12532901763916</v>
+        <v>9.12532806396484</v>
       </c>
       <c r="H1553" t="n">
         <v>143035</v>
@@ -45580,7 +45580,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1559" t="n">
-        <v>9.2179708480835</v>
+        <v>9.21797180175781</v>
       </c>
       <c r="H1559" t="n">
         <v>153524</v>
@@ -45609,7 +45609,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1560" t="n">
-        <v>9.00952529907227</v>
+        <v>9.00952625274658</v>
       </c>
       <c r="H1560" t="n">
         <v>123789</v>
@@ -45725,7 +45725,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1564" t="n">
-        <v>8.71615505218506</v>
+        <v>8.71615600585938</v>
       </c>
       <c r="H1564" t="n">
         <v>146362</v>
@@ -45754,7 +45754,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1565" t="n">
-        <v>8.29154205322266</v>
+        <v>8.29154109954834</v>
       </c>
       <c r="H1565" t="n">
         <v>337131</v>
@@ -45783,7 +45783,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1566" t="n">
-        <v>8.6621150970459</v>
+        <v>8.66211414337158</v>
       </c>
       <c r="H1566" t="n">
         <v>180359</v>
@@ -45928,7 +45928,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.25703001022339</v>
+        <v>7.25702953338623</v>
       </c>
       <c r="H1571" t="n">
         <v>300725</v>
@@ -45957,7 +45957,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1572" t="n">
-        <v>6.82469654083252</v>
+        <v>6.82469606399536</v>
       </c>
       <c r="H1572" t="n">
         <v>388423</v>
@@ -46044,7 +46044,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1575" t="n">
-        <v>6.87873792648315</v>
+        <v>6.878737449646</v>
       </c>
       <c r="H1575" t="n">
         <v>351634</v>
@@ -46073,7 +46073,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>7.10648536682129</v>
+        <v>7.10648441314697</v>
       </c>
       <c r="H1576" t="n">
         <v>414498</v>
@@ -46131,7 +46131,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1578" t="n">
-        <v>7.06788301467896</v>
+        <v>7.06788349151611</v>
       </c>
       <c r="H1578" t="n">
         <v>383161</v>
@@ -46160,7 +46160,7 @@
         <v>9.5</v>
       </c>
       <c r="G1579" t="n">
-        <v>7.33423185348511</v>
+        <v>7.33423280715942</v>
       </c>
       <c r="H1579" t="n">
         <v>470457</v>
@@ -46247,7 +46247,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>7.30335092544556</v>
+        <v>7.30335140228271</v>
       </c>
       <c r="H1582" t="n">
         <v>184597</v>
@@ -46276,7 +46276,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.48863744735718</v>
+        <v>7.48863697052002</v>
       </c>
       <c r="H1583" t="n">
         <v>187636</v>
@@ -46305,7 +46305,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1584" t="n">
-        <v>7.42687559127808</v>
+        <v>7.42687511444092</v>
       </c>
       <c r="H1584" t="n">
         <v>167303</v>
@@ -46363,7 +46363,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G1586" t="n">
-        <v>7.53881931304932</v>
+        <v>7.53881883621216</v>
       </c>
       <c r="H1586" t="n">
         <v>148850</v>
@@ -46392,7 +46392,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1587" t="n">
-        <v>7.51951742172241</v>
+        <v>7.51951789855957</v>
       </c>
       <c r="H1587" t="n">
         <v>131453</v>
@@ -46421,7 +46421,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1588" t="n">
-        <v>7.75112533569336</v>
+        <v>7.75112628936768</v>
       </c>
       <c r="H1588" t="n">
         <v>180788</v>
@@ -46450,7 +46450,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.70866441726685</v>
+        <v>7.70866346359253</v>
       </c>
       <c r="H1589" t="n">
         <v>87262</v>
@@ -46479,7 +46479,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>7.42687559127808</v>
+        <v>7.42687511444092</v>
       </c>
       <c r="H1590" t="n">
         <v>132697</v>
@@ -46508,7 +46508,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1591" t="n">
-        <v>7.51951742172241</v>
+        <v>7.51951789855957</v>
       </c>
       <c r="H1591" t="n">
         <v>97704</v>
@@ -46595,7 +46595,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G1594" t="n">
-        <v>7.23000955581665</v>
+        <v>7.23000860214233</v>
       </c>
       <c r="H1594" t="n">
         <v>220097</v>
@@ -46624,7 +46624,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1595" t="n">
-        <v>7.15280628204346</v>
+        <v>7.15280675888062</v>
       </c>
       <c r="H1595" t="n">
         <v>127676</v>
@@ -46653,7 +46653,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.36511421203613</v>
+        <v>7.36511373519897</v>
       </c>
       <c r="H1596" t="n">
         <v>104930</v>
@@ -46682,7 +46682,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.3921332359314</v>
+        <v>7.39213371276855</v>
       </c>
       <c r="H1597" t="n">
         <v>119048</v>
@@ -46711,7 +46711,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.30721092224121</v>
+        <v>7.30721187591553</v>
       </c>
       <c r="H1598" t="n">
         <v>68013</v>
@@ -46740,7 +46740,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1599" t="n">
-        <v>7.38441324234009</v>
+        <v>7.38441371917725</v>
       </c>
       <c r="H1599" t="n">
         <v>131459</v>
@@ -46827,7 +46827,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G1602" t="n">
-        <v>7.46161651611328</v>
+        <v>7.46161603927612</v>
       </c>
       <c r="H1602" t="n">
         <v>110984</v>
@@ -46914,7 +46914,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1605" t="n">
-        <v>7.18076276779175</v>
+        <v>7.18076324462891</v>
       </c>
       <c r="H1605" t="n">
         <v>471465</v>
@@ -46972,7 +46972,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G1607" t="n">
-        <v>6.78455543518066</v>
+        <v>6.78455495834351</v>
       </c>
       <c r="H1607" t="n">
         <v>363439</v>
@@ -47001,7 +47001,7 @@
         <v>8.71500015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.11949396133423</v>
+        <v>7.11949348449707</v>
       </c>
       <c r="H1608" t="n">
         <v>262831</v>
@@ -47030,7 +47030,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G1609" t="n">
-        <v>7.24203205108643</v>
+        <v>7.24203252792358</v>
       </c>
       <c r="H1609" t="n">
         <v>146612</v>
@@ -47204,7 +47204,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G1615" t="n">
-        <v>6.55581617355347</v>
+        <v>6.55581569671631</v>
       </c>
       <c r="H1615" t="n">
         <v>153375</v>
@@ -47233,7 +47233,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1616" t="n">
-        <v>6.71511650085449</v>
+        <v>6.71511602401733</v>
       </c>
       <c r="H1616" t="n">
         <v>143815</v>
@@ -47349,7 +47349,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1620" t="n">
-        <v>6.69060802459717</v>
+        <v>6.69060850143433</v>
       </c>
       <c r="H1620" t="n">
         <v>79563</v>
@@ -47871,7 +47871,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1638" t="n">
-        <v>6.32299280166626</v>
+        <v>6.3229923248291</v>
       </c>
       <c r="H1638" t="n">
         <v>157553</v>
@@ -48132,7 +48132,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1647" t="n">
-        <v>5.99622344970703</v>
+        <v>5.99622297286987</v>
       </c>
       <c r="H1647" t="n">
         <v>78300</v>
@@ -48190,7 +48190,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1649" t="n">
-        <v>6.06157732009888</v>
+        <v>6.06157684326172</v>
       </c>
       <c r="H1649" t="n">
         <v>104979</v>
@@ -48364,7 +48364,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1655" t="n">
-        <v>5.55508422851562</v>
+        <v>5.55508470535278</v>
       </c>
       <c r="H1655" t="n">
         <v>102311</v>
@@ -48422,7 +48422,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G1657" t="n">
-        <v>5.49381494522095</v>
+        <v>5.49381446838379</v>
       </c>
       <c r="H1657" t="n">
         <v>106623</v>
@@ -48451,7 +48451,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1658" t="n">
-        <v>5.68579196929932</v>
+        <v>5.68579244613647</v>
       </c>
       <c r="H1658" t="n">
         <v>93517</v>
@@ -48480,7 +48480,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G1659" t="n">
-        <v>5.82875347137451</v>
+        <v>5.82875394821167</v>
       </c>
       <c r="H1659" t="n">
         <v>75512</v>
@@ -48596,7 +48596,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.36310720443726</v>
+        <v>5.3631067276001</v>
       </c>
       <c r="H1663" t="n">
         <v>81236</v>
@@ -48654,7 +48654,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1665" t="n">
-        <v>5.44479942321777</v>
+        <v>5.44479894638062</v>
       </c>
       <c r="H1665" t="n">
         <v>75688</v>
@@ -48683,7 +48683,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.65311479568481</v>
+        <v>5.65311527252197</v>
       </c>
       <c r="H1666" t="n">
         <v>82525</v>
@@ -48886,7 +48886,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.57959175109863</v>
+        <v>5.57959127426147</v>
       </c>
       <c r="H1673" t="n">
         <v>200936</v>
@@ -49002,7 +49002,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.73072242736816</v>
+        <v>5.73072290420532</v>
       </c>
       <c r="H1677" t="n">
         <v>90100</v>
@@ -49205,7 +49205,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1684" t="n">
-        <v>5.94720792770386</v>
+        <v>5.9472074508667</v>
       </c>
       <c r="H1684" t="n">
         <v>136663</v>
@@ -49234,7 +49234,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1685" t="n">
-        <v>5.99622344970703</v>
+        <v>5.99622297286987</v>
       </c>
       <c r="H1685" t="n">
         <v>182349</v>
@@ -49321,7 +49321,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1688" t="n">
-        <v>5.80833101272583</v>
+        <v>5.80833053588867</v>
       </c>
       <c r="H1688" t="n">
         <v>97902</v>
@@ -49524,7 +49524,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1695" t="n">
-        <v>5.55916881561279</v>
+        <v>5.55916833877563</v>
       </c>
       <c r="H1695" t="n">
         <v>35182</v>
@@ -49553,7 +49553,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.55508422851562</v>
+        <v>5.55508470535278</v>
       </c>
       <c r="H1696" t="n">
         <v>59601</v>
@@ -49582,7 +49582,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1697" t="n">
-        <v>5.13028335571289</v>
+        <v>5.13028383255005</v>
       </c>
       <c r="H1697" t="n">
         <v>245037</v>
@@ -49611,7 +49611,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1698" t="n">
-        <v>5.09760618209839</v>
+        <v>5.09760665893555</v>
       </c>
       <c r="H1698" t="n">
         <v>255928</v>
@@ -49785,7 +49785,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G1704" t="n">
-        <v>5.36310720443726</v>
+        <v>5.3631067276001</v>
       </c>
       <c r="H1704" t="n">
         <v>147354</v>
@@ -49814,7 +49814,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1705" t="n">
-        <v>5.19563722610474</v>
+        <v>5.19563770294189</v>
       </c>
       <c r="H1705" t="n">
         <v>289386</v>
@@ -49843,7 +49843,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.13028335571289</v>
+        <v>5.13028383255005</v>
       </c>
       <c r="H1706" t="n">
         <v>126204</v>
@@ -49901,7 +49901,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G1708" t="n">
-        <v>4.9873218536377</v>
+        <v>4.98732137680054</v>
       </c>
       <c r="H1708" t="n">
         <v>271407</v>
@@ -50017,7 +50017,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.9873218536377</v>
+        <v>4.98732137680054</v>
       </c>
       <c r="H1712" t="n">
         <v>101199</v>
@@ -50191,7 +50191,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1718" t="n">
-        <v>5.1221137046814</v>
+        <v>5.12211418151855</v>
       </c>
       <c r="H1718" t="n">
         <v>127462</v>
@@ -50394,7 +50394,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1725" t="n">
-        <v>4.86069869995117</v>
+        <v>4.86069822311401</v>
       </c>
       <c r="H1725" t="n">
         <v>85791</v>
@@ -50510,7 +50510,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G1729" t="n">
-        <v>4.9873218536377</v>
+        <v>4.98732137680054</v>
       </c>
       <c r="H1729" t="n">
         <v>102212</v>
@@ -50597,7 +50597,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.24873781204224</v>
+        <v>5.24873733520508</v>
       </c>
       <c r="H1732" t="n">
         <v>116489</v>
@@ -50655,7 +50655,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.45705270767212</v>
+        <v>5.45705318450928</v>
       </c>
       <c r="H1734" t="n">
         <v>97393</v>
@@ -50684,7 +50684,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1735" t="n">
-        <v>5.55508422851562</v>
+        <v>5.55508470535278</v>
       </c>
       <c r="H1735" t="n">
         <v>117678</v>
@@ -50771,7 +50771,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1738" t="n">
-        <v>5.55916881561279</v>
+        <v>5.55916833877563</v>
       </c>
       <c r="H1738" t="n">
         <v>103462</v>
@@ -50858,7 +50858,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1741" t="n">
-        <v>5.4080376625061</v>
+        <v>5.40803813934326</v>
       </c>
       <c r="H1741" t="n">
         <v>107763</v>
@@ -50945,7 +50945,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1744" t="n">
-        <v>5.80833101272583</v>
+        <v>5.80833053588867</v>
       </c>
       <c r="H1744" t="n">
         <v>154890</v>
@@ -51003,7 +51003,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G1746" t="n">
-        <v>5.79607629776001</v>
+        <v>5.79607677459717</v>
       </c>
       <c r="H1746" t="n">
         <v>99799</v>
@@ -51032,7 +51032,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1747" t="n">
-        <v>5.89819192886353</v>
+        <v>5.89819240570068</v>
       </c>
       <c r="H1747" t="n">
         <v>325146</v>
@@ -51090,7 +51090,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1749" t="n">
-        <v>6.30256938934326</v>
+        <v>6.30256986618042</v>
       </c>
       <c r="H1749" t="n">
         <v>133657</v>
@@ -51119,7 +51119,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1750" t="n">
-        <v>6.11059236526489</v>
+        <v>6.11059188842773</v>
       </c>
       <c r="H1750" t="n">
         <v>137681</v>
@@ -51235,7 +51235,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1754" t="n">
-        <v>5.76748418807983</v>
+        <v>5.76748466491699</v>
       </c>
       <c r="H1754" t="n">
         <v>99129</v>
@@ -51264,7 +51264,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G1755" t="n">
-        <v>5.81241464614868</v>
+        <v>5.81241512298584</v>
       </c>
       <c r="H1755" t="n">
         <v>110488</v>
@@ -51322,7 +51322,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1757" t="n">
-        <v>5.80833101272583</v>
+        <v>5.80833053588867</v>
       </c>
       <c r="H1757" t="n">
         <v>83589</v>
@@ -51351,7 +51351,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.84509181976318</v>
+        <v>5.84509229660034</v>
       </c>
       <c r="H1758" t="n">
         <v>74988</v>
@@ -51380,7 +51380,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1759" t="n">
-        <v>5.68579196929932</v>
+        <v>5.68579244613647</v>
       </c>
       <c r="H1759" t="n">
         <v>109787</v>
@@ -51409,7 +51409,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G1760" t="n">
-        <v>5.7388916015625</v>
+        <v>5.73889207839966</v>
       </c>
       <c r="H1760" t="n">
         <v>102736</v>
@@ -51757,7 +51757,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1772" t="n">
-        <v>5.35085296630859</v>
+        <v>5.35085344314575</v>
       </c>
       <c r="H1772" t="n">
         <v>158653</v>
@@ -51786,7 +51786,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1773" t="n">
-        <v>5.4080376625061</v>
+        <v>5.40803813934326</v>
       </c>
       <c r="H1773" t="n">
         <v>132257</v>
@@ -51815,7 +51815,7 @@
         <v>6.625</v>
       </c>
       <c r="G1774" t="n">
-        <v>5.41212272644043</v>
+        <v>5.41212224960327</v>
       </c>
       <c r="H1774" t="n">
         <v>69823</v>
@@ -51844,7 +51844,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1775" t="n">
-        <v>5.35085296630859</v>
+        <v>5.35085344314575</v>
       </c>
       <c r="H1775" t="n">
         <v>67478</v>
@@ -51960,7 +51960,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G1779" t="n">
-        <v>5.54283046722412</v>
+        <v>5.54282999038696</v>
       </c>
       <c r="H1779" t="n">
         <v>33197</v>
@@ -51989,7 +51989,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G1780" t="n">
-        <v>5.47747611999512</v>
+        <v>5.47747564315796</v>
       </c>
       <c r="H1780" t="n">
         <v>95034</v>
@@ -52018,7 +52018,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1781" t="n">
-        <v>5.57959175109863</v>
+        <v>5.57959127426147</v>
       </c>
       <c r="H1781" t="n">
         <v>63483</v>
@@ -52105,7 +52105,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1784" t="n">
-        <v>5.66945314407349</v>
+        <v>5.66945362091064</v>
       </c>
       <c r="H1784" t="n">
         <v>188901</v>
@@ -52134,7 +52134,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G1785" t="n">
-        <v>5.69804525375366</v>
+        <v>5.69804573059082</v>
       </c>
       <c r="H1785" t="n">
         <v>99730</v>
@@ -52163,7 +52163,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G1786" t="n">
-        <v>5.69804525375366</v>
+        <v>5.69804573059082</v>
       </c>
       <c r="H1786" t="n">
         <v>96870</v>
@@ -52192,7 +52192,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1787" t="n">
-        <v>5.69396114349365</v>
+        <v>5.69396066665649</v>
       </c>
       <c r="H1787" t="n">
         <v>44249</v>
@@ -52221,7 +52221,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1788" t="n">
-        <v>5.93086957931519</v>
+        <v>5.93086910247803</v>
       </c>
       <c r="H1788" t="n">
         <v>181927</v>
@@ -52453,7 +52453,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G1796" t="n">
-        <v>5.92678451538086</v>
+        <v>5.92678499221802</v>
       </c>
       <c r="H1796" t="n">
         <v>103029</v>
@@ -52511,7 +52511,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1798" t="n">
-        <v>6.07791566848755</v>
+        <v>6.07791519165039</v>
       </c>
       <c r="H1798" t="n">
         <v>105220</v>
@@ -52540,7 +52540,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1799" t="n">
-        <v>6.06157732009888</v>
+        <v>6.06157684326172</v>
       </c>
       <c r="H1799" t="n">
         <v>41416</v>
@@ -52656,7 +52656,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G1803" t="n">
-        <v>5.94312286376953</v>
+        <v>5.94312334060669</v>
       </c>
       <c r="H1803" t="n">
         <v>71533</v>
@@ -52685,7 +52685,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1804" t="n">
-        <v>5.93086957931519</v>
+        <v>5.93086910247803</v>
       </c>
       <c r="H1804" t="n">
         <v>88744</v>
@@ -52714,7 +52714,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1805" t="n">
-        <v>5.94720792770386</v>
+        <v>5.9472074508667</v>
       </c>
       <c r="H1805" t="n">
         <v>135890</v>
@@ -52830,7 +52830,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.94720792770386</v>
+        <v>5.9472074508667</v>
       </c>
       <c r="H1809" t="n">
         <v>124551</v>
@@ -52888,7 +52888,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1811" t="n">
-        <v>6.14327001571655</v>
+        <v>6.14326953887939</v>
       </c>
       <c r="H1811" t="n">
         <v>164549</v>
@@ -53004,7 +53004,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1815" t="n">
-        <v>6.09425401687622</v>
+        <v>6.09425354003906</v>
       </c>
       <c r="H1815" t="n">
         <v>75203</v>
@@ -53062,7 +53062,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1817" t="n">
-        <v>6.04523897171021</v>
+        <v>6.04523849487305</v>
       </c>
       <c r="H1817" t="n">
         <v>74184</v>
@@ -53120,7 +53120,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G1819" t="n">
-        <v>5.47747611999512</v>
+        <v>5.47747564315796</v>
       </c>
       <c r="H1819" t="n">
         <v>447189</v>
@@ -53381,7 +53381,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1828" t="n">
-        <v>5.94720792770386</v>
+        <v>5.9472074508667</v>
       </c>
       <c r="H1828" t="n">
         <v>137475</v>
@@ -53410,7 +53410,7 @@
         <v>7.25</v>
       </c>
       <c r="G1829" t="n">
-        <v>5.92270040512085</v>
+        <v>5.92269992828369</v>
       </c>
       <c r="H1829" t="n">
         <v>217078</v>
@@ -53700,7 +53700,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G1839" t="n">
-        <v>6.92343235015869</v>
+        <v>6.92343187332153</v>
       </c>
       <c r="H1839" t="n">
         <v>298498</v>
@@ -53758,7 +53758,7 @@
         <v>8.875</v>
       </c>
       <c r="G1841" t="n">
-        <v>7.25020122528076</v>
+        <v>7.25020170211792</v>
       </c>
       <c r="H1841" t="n">
         <v>295358</v>
@@ -53816,7 +53816,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.12357902526855</v>
+        <v>7.1235785484314</v>
       </c>
       <c r="H1843" t="n">
         <v>171034</v>
@@ -53845,7 +53845,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.20118522644043</v>
+        <v>7.20118570327759</v>
       </c>
       <c r="H1844" t="n">
         <v>235336</v>
@@ -53932,7 +53932,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.53204011917114</v>
+        <v>7.53204107284546</v>
       </c>
       <c r="H1847" t="n">
         <v>344043</v>
@@ -54019,7 +54019,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.23386240005493</v>
+        <v>7.23386287689209</v>
       </c>
       <c r="H1850" t="n">
         <v>242066</v>
@@ -54048,7 +54048,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1851" t="n">
-        <v>7.33597850799561</v>
+        <v>7.33597803115845</v>
       </c>
       <c r="H1851" t="n">
         <v>120639</v>
@@ -54106,7 +54106,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1853" t="n">
-        <v>7.25428628921509</v>
+        <v>7.25428676605225</v>
       </c>
       <c r="H1853" t="n">
         <v>219709</v>
@@ -54135,7 +54135,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1854" t="n">
-        <v>7.19710159301758</v>
+        <v>7.19710254669189</v>
       </c>
       <c r="H1854" t="n">
         <v>197744</v>
@@ -54164,7 +54164,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1855" t="n">
-        <v>7.22160959243774</v>
+        <v>7.22160911560059</v>
       </c>
       <c r="H1855" t="n">
         <v>243336</v>
@@ -54193,7 +54193,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1856" t="n">
-        <v>7.22160959243774</v>
+        <v>7.22160911560059</v>
       </c>
       <c r="H1856" t="n">
         <v>114739</v>
@@ -54222,7 +54222,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G1857" t="n">
-        <v>7.20118522644043</v>
+        <v>7.20118570327759</v>
       </c>
       <c r="H1857" t="n">
         <v>144426</v>
@@ -54251,7 +54251,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1858" t="n">
-        <v>7.10724020004272</v>
+        <v>7.10723924636841</v>
       </c>
       <c r="H1858" t="n">
         <v>191555</v>
@@ -54309,7 +54309,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G1860" t="n">
-        <v>7.08681726455688</v>
+        <v>7.08681678771973</v>
       </c>
       <c r="H1860" t="n">
         <v>311000</v>
@@ -80154,6 +80154,35 @@
         <v>53354</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>7.92500019073486</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>8.02499961853027</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>7.86999988555908</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>7.86999988555908</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>7.86999988555908</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>47917</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRT.MI.xlsx
+++ b/data/PRT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4473237991333</v>
+        <v>5.44732332229614</v>
       </c>
       <c r="H2" t="n">
         <v>113188</v>
@@ -456,7 +456,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G3" t="n">
-        <v>5.55361270904541</v>
+        <v>5.55361223220825</v>
       </c>
       <c r="H3" t="n">
         <v>66887</v>
@@ -514,7 +514,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G5" t="n">
-        <v>5.32774877548218</v>
+        <v>5.32774829864502</v>
       </c>
       <c r="H5" t="n">
         <v>104860</v>
@@ -543,7 +543,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G6" t="n">
-        <v>5.35099983215332</v>
+        <v>5.350998878479</v>
       </c>
       <c r="H6" t="n">
         <v>87575</v>
@@ -601,7 +601,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>5.29453277587891</v>
+        <v>5.29453325271606</v>
       </c>
       <c r="H8" t="n">
         <v>216037</v>
@@ -688,7 +688,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>4.94245052337646</v>
+        <v>4.94244956970215</v>
       </c>
       <c r="H11" t="n">
         <v>159704</v>
@@ -717,7 +717,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>4.74980020523071</v>
+        <v>4.74980068206787</v>
       </c>
       <c r="H12" t="n">
         <v>154245</v>
@@ -746,7 +746,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>4.84612607955933</v>
+        <v>4.84612560272217</v>
       </c>
       <c r="H13" t="n">
         <v>91026</v>
@@ -804,7 +804,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>4.74980020523071</v>
+        <v>4.74980068206787</v>
       </c>
       <c r="H15" t="n">
         <v>132498</v>
@@ -833,7 +833,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>4.82951784133911</v>
+        <v>4.82951736450195</v>
       </c>
       <c r="H16" t="n">
         <v>117197</v>
@@ -862,7 +862,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>4.82951784133911</v>
+        <v>4.82951736450195</v>
       </c>
       <c r="H17" t="n">
         <v>66239</v>
@@ -920,7 +920,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G19" t="n">
-        <v>4.87601852416992</v>
+        <v>4.87601900100708</v>
       </c>
       <c r="H19" t="n">
         <v>45031</v>
@@ -949,7 +949,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>4.91587829589844</v>
+        <v>4.91587734222412</v>
       </c>
       <c r="H20" t="n">
         <v>109639</v>
@@ -978,7 +978,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>4.96902275085449</v>
+        <v>4.96902227401733</v>
       </c>
       <c r="H21" t="n">
         <v>82995</v>
@@ -1007,7 +1007,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G22" t="n">
-        <v>4.97234344482422</v>
+        <v>4.97234439849854</v>
       </c>
       <c r="H22" t="n">
         <v>54344</v>
@@ -1065,7 +1065,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>4.94909286499023</v>
+        <v>4.94909334182739</v>
       </c>
       <c r="H24" t="n">
         <v>115223</v>
@@ -1094,7 +1094,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G25" t="n">
-        <v>4.93248605728149</v>
+        <v>4.93248558044434</v>
       </c>
       <c r="H25" t="n">
         <v>117119</v>
@@ -1123,7 +1123,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G26" t="n">
-        <v>4.9789867401123</v>
+        <v>4.97898721694946</v>
       </c>
       <c r="H26" t="n">
         <v>142513</v>
@@ -1152,7 +1152,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.59368896484375</v>
+        <v>4.59368848800659</v>
       </c>
       <c r="H27" t="n">
         <v>190986</v>
@@ -1239,7 +1239,7 @@
         <v>6.75</v>
       </c>
       <c r="G30" t="n">
-        <v>4.48407697677612</v>
+        <v>4.48407793045044</v>
       </c>
       <c r="H30" t="n">
         <v>162247</v>
@@ -1268,7 +1268,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>4.62690401077271</v>
+        <v>4.62690353393555</v>
       </c>
       <c r="H31" t="n">
         <v>118549</v>
@@ -1326,7 +1326,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G33" t="n">
-        <v>4.67340517044067</v>
+        <v>4.67340564727783</v>
       </c>
       <c r="H33" t="n">
         <v>87459</v>
@@ -1355,7 +1355,7 @@
         <v>7.375</v>
       </c>
       <c r="G34" t="n">
-        <v>4.89927005767822</v>
+        <v>4.89926958084106</v>
       </c>
       <c r="H34" t="n">
         <v>59630</v>
@@ -1384,7 +1384,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G35" t="n">
-        <v>5.19488668441772</v>
+        <v>5.19488716125488</v>
       </c>
       <c r="H35" t="n">
         <v>145821</v>
@@ -1413,7 +1413,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G36" t="n">
-        <v>5.02880954742432</v>
+        <v>5.02881050109863</v>
       </c>
       <c r="H36" t="n">
         <v>65011</v>
@@ -1471,7 +1471,7 @@
         <v>7.56500005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>5.02548789978027</v>
+        <v>5.02548837661743</v>
       </c>
       <c r="H38" t="n">
         <v>81136</v>
@@ -1500,7 +1500,7 @@
         <v>7.75</v>
       </c>
       <c r="G39" t="n">
-        <v>5.1483850479126</v>
+        <v>5.14838552474976</v>
       </c>
       <c r="H39" t="n">
         <v>73305</v>
@@ -1529,7 +1529,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G40" t="n">
-        <v>5.24138784408569</v>
+        <v>5.24138832092285</v>
       </c>
       <c r="H40" t="n">
         <v>51694</v>
@@ -1587,7 +1587,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>5.51375532150269</v>
+        <v>5.51375389099121</v>
       </c>
       <c r="H42" t="n">
         <v>150009</v>
@@ -1616,7 +1616,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G43" t="n">
-        <v>5.69311714172363</v>
+        <v>5.69311761856079</v>
       </c>
       <c r="H43" t="n">
         <v>209250</v>
@@ -1645,7 +1645,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>5.75290489196777</v>
+        <v>5.75290536880493</v>
       </c>
       <c r="H44" t="n">
         <v>122191</v>
@@ -1674,7 +1674,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>5.53368425369263</v>
+        <v>5.53368377685547</v>
       </c>
       <c r="H45" t="n">
         <v>125352</v>
@@ -1732,7 +1732,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G47" t="n">
-        <v>5.68315410614014</v>
+        <v>5.68315362930298</v>
       </c>
       <c r="H47" t="n">
         <v>127631</v>
@@ -1790,7 +1790,7 @@
         <v>8.5</v>
       </c>
       <c r="G49" t="n">
-        <v>5.64661598205566</v>
+        <v>5.64661550521851</v>
       </c>
       <c r="H49" t="n">
         <v>71691</v>
@@ -1819,7 +1819,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>5.35432100296021</v>
+        <v>5.35432147979736</v>
       </c>
       <c r="H50" t="n">
         <v>105600</v>
@@ -1848,7 +1848,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G51" t="n">
-        <v>5.38753604888916</v>
+        <v>5.387535572052</v>
       </c>
       <c r="H51" t="n">
         <v>191706</v>
@@ -1877,7 +1877,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G52" t="n">
-        <v>5.5037899017334</v>
+        <v>5.50379037857056</v>
       </c>
       <c r="H52" t="n">
         <v>91415</v>
@@ -1935,7 +1935,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>5.4473237991333</v>
+        <v>5.44732332229614</v>
       </c>
       <c r="H54" t="n">
         <v>43227</v>
@@ -1964,7 +1964,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>5.39417934417725</v>
+        <v>5.3941798210144</v>
       </c>
       <c r="H55" t="n">
         <v>67532</v>
@@ -1993,7 +1993,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.4473237991333</v>
+        <v>5.44732332229614</v>
       </c>
       <c r="H56" t="n">
         <v>148456</v>
@@ -2022,7 +2022,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G57" t="n">
-        <v>5.38421440124512</v>
+        <v>5.38421392440796</v>
       </c>
       <c r="H57" t="n">
         <v>103959</v>
@@ -2051,7 +2051,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>5.41410732269287</v>
+        <v>5.41410827636719</v>
       </c>
       <c r="H58" t="n">
         <v>147032</v>
@@ -2109,7 +2109,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>5.18160104751587</v>
+        <v>5.18160057067871</v>
       </c>
       <c r="H60" t="n">
         <v>128542</v>
@@ -2167,7 +2167,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G62" t="n">
-        <v>5.24138784408569</v>
+        <v>5.24138832092285</v>
       </c>
       <c r="H62" t="n">
         <v>164574</v>
@@ -2196,7 +2196,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>5.27460336685181</v>
+        <v>5.27460384368896</v>
       </c>
       <c r="H63" t="n">
         <v>44868</v>
@@ -2225,7 +2225,7 @@
         <v>7.75</v>
       </c>
       <c r="G64" t="n">
-        <v>5.1483850479126</v>
+        <v>5.14838552474976</v>
       </c>
       <c r="H64" t="n">
         <v>96421</v>
@@ -2254,7 +2254,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.26796054840088</v>
+        <v>5.26796007156372</v>
       </c>
       <c r="H65" t="n">
         <v>87527</v>
@@ -2283,7 +2283,7 @@
         <v>7.5</v>
       </c>
       <c r="G66" t="n">
-        <v>4.98230886459351</v>
+        <v>4.98230838775635</v>
       </c>
       <c r="H66" t="n">
         <v>59642</v>
@@ -2312,7 +2312,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>4.96902275085449</v>
+        <v>4.96902227401733</v>
       </c>
       <c r="H67" t="n">
         <v>106491</v>
@@ -2341,7 +2341,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G68" t="n">
-        <v>5.01220226287842</v>
+        <v>5.01220178604126</v>
       </c>
       <c r="H68" t="n">
         <v>65134</v>
@@ -2399,7 +2399,7 @@
         <v>7.75</v>
       </c>
       <c r="G70" t="n">
-        <v>5.1483850479126</v>
+        <v>5.14838552474976</v>
       </c>
       <c r="H70" t="n">
         <v>22243</v>
@@ -2457,7 +2457,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>5.27460336685181</v>
+        <v>5.27460384368896</v>
       </c>
       <c r="H72" t="n">
         <v>51680</v>
@@ -2486,7 +2486,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G73" t="n">
-        <v>5.28124713897705</v>
+        <v>5.28124666213989</v>
       </c>
       <c r="H73" t="n">
         <v>23904</v>
@@ -2515,7 +2515,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G74" t="n">
-        <v>5.04209566116333</v>
+        <v>5.04209661483765</v>
       </c>
       <c r="H74" t="n">
         <v>83664</v>
@@ -2573,7 +2573,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>5.08195447921753</v>
+        <v>5.08195543289185</v>
       </c>
       <c r="H76" t="n">
         <v>52690</v>
@@ -2602,7 +2602,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>5.04873895645142</v>
+        <v>5.04873847961426</v>
       </c>
       <c r="H77" t="n">
         <v>29830</v>
@@ -2631,7 +2631,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G78" t="n">
-        <v>5.11516952514648</v>
+        <v>5.11516904830933</v>
       </c>
       <c r="H78" t="n">
         <v>43914</v>
@@ -2689,7 +2689,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G80" t="n">
-        <v>4.98895168304443</v>
+        <v>4.98895120620728</v>
       </c>
       <c r="H80" t="n">
         <v>25738</v>
@@ -2747,7 +2747,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>5.05538272857666</v>
+        <v>5.0553822517395</v>
       </c>
       <c r="H82" t="n">
         <v>36158</v>
@@ -2834,7 +2834,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>5.11184883117676</v>
+        <v>5.1118483543396</v>
       </c>
       <c r="H85" t="n">
         <v>15689</v>
@@ -2892,7 +2892,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.08195447921753</v>
+        <v>5.08195543289185</v>
       </c>
       <c r="H87" t="n">
         <v>21885</v>
@@ -2950,7 +2950,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G89" t="n">
-        <v>5.33439207077026</v>
+        <v>5.33439159393311</v>
       </c>
       <c r="H89" t="n">
         <v>158293</v>
@@ -2979,7 +2979,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G90" t="n">
-        <v>5.74733304977417</v>
+        <v>5.74733257293701</v>
       </c>
       <c r="H90" t="n">
         <v>226380</v>
@@ -3008,7 +3008,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G91" t="n">
-        <v>5.53747797012329</v>
+        <v>5.53747701644897</v>
       </c>
       <c r="H91" t="n">
         <v>119812</v>
@@ -3037,7 +3037,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G92" t="n">
-        <v>5.54763174057007</v>
+        <v>5.54763126373291</v>
       </c>
       <c r="H92" t="n">
         <v>108705</v>
@@ -3066,7 +3066,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G93" t="n">
-        <v>5.42916536331177</v>
+        <v>5.42916488647461</v>
       </c>
       <c r="H93" t="n">
         <v>60550</v>
@@ -3124,7 +3124,7 @@
         <v>7.5</v>
       </c>
       <c r="G95" t="n">
-        <v>5.07714986801147</v>
+        <v>5.07714939117432</v>
       </c>
       <c r="H95" t="n">
         <v>313230</v>
@@ -3153,7 +3153,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>4.66759252548218</v>
+        <v>4.66759300231934</v>
       </c>
       <c r="H96" t="n">
         <v>383206</v>
@@ -3182,7 +3182,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G97" t="n">
-        <v>4.66420745849609</v>
+        <v>4.66420793533325</v>
       </c>
       <c r="H97" t="n">
         <v>146046</v>
@@ -3240,7 +3240,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>4.63712930679321</v>
+        <v>4.63712978363037</v>
       </c>
       <c r="H99" t="n">
         <v>136516</v>
@@ -3269,7 +3269,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>4.4340443611145</v>
+        <v>4.43404340744019</v>
       </c>
       <c r="H100" t="n">
         <v>87516</v>
@@ -3298,7 +3298,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>4.47804498672485</v>
+        <v>4.47804594039917</v>
       </c>
       <c r="H101" t="n">
         <v>121440</v>
@@ -3327,7 +3327,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G102" t="n">
-        <v>4.42727422714233</v>
+        <v>4.42727470397949</v>
       </c>
       <c r="H102" t="n">
         <v>149214</v>
@@ -3356,7 +3356,7 @@
         <v>6.5</v>
       </c>
       <c r="G103" t="n">
-        <v>4.40019607543945</v>
+        <v>4.40019655227661</v>
       </c>
       <c r="H103" t="n">
         <v>103547</v>
@@ -3385,7 +3385,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G104" t="n">
-        <v>4.30542278289795</v>
+        <v>4.30542230606079</v>
       </c>
       <c r="H104" t="n">
         <v>179465</v>
@@ -3414,7 +3414,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.44758319854736</v>
+        <v>4.44758272171021</v>
       </c>
       <c r="H105" t="n">
         <v>157820</v>
@@ -3443,7 +3443,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G106" t="n">
-        <v>4.49496984481812</v>
+        <v>4.49496936798096</v>
       </c>
       <c r="H106" t="n">
         <v>258125</v>
@@ -3472,7 +3472,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>4.34942483901978</v>
+        <v>4.34942436218262</v>
       </c>
       <c r="H107" t="n">
         <v>210950</v>
@@ -3501,7 +3501,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>4.29865312576294</v>
+        <v>4.29865264892578</v>
       </c>
       <c r="H108" t="n">
         <v>89317</v>
@@ -3559,7 +3559,7 @@
         <v>6.25</v>
       </c>
       <c r="G110" t="n">
-        <v>4.23095750808716</v>
+        <v>4.23095798492432</v>
       </c>
       <c r="H110" t="n">
         <v>156920</v>
@@ -3588,7 +3588,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G111" t="n">
-        <v>4.24788236618042</v>
+        <v>4.24788188934326</v>
       </c>
       <c r="H111" t="n">
         <v>89664</v>
@@ -3704,7 +3704,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G115" t="n">
-        <v>4.02448701858521</v>
+        <v>4.02448749542236</v>
       </c>
       <c r="H115" t="n">
         <v>158085</v>
@@ -3791,7 +3791,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G118" t="n">
-        <v>3.79770827293396</v>
+        <v>3.7977077960968</v>
       </c>
       <c r="H118" t="n">
         <v>144969</v>
@@ -3878,7 +3878,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.96356201171875</v>
+        <v>3.96356129646301</v>
       </c>
       <c r="H121" t="n">
         <v>108290</v>
@@ -3936,7 +3936,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>3.99402403831482</v>
+        <v>3.9940242767334</v>
       </c>
       <c r="H123" t="n">
         <v>85572</v>
@@ -3965,7 +3965,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G124" t="n">
-        <v>3.76385974884033</v>
+        <v>3.76386022567749</v>
       </c>
       <c r="H124" t="n">
         <v>198048</v>
@@ -3994,7 +3994,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32925653457642</v>
+        <v>3.32925629615784</v>
       </c>
       <c r="H125" t="n">
         <v>312851</v>
@@ -4023,7 +4023,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.40169024467468</v>
+        <v>3.40169072151184</v>
       </c>
       <c r="H126" t="n">
         <v>297033</v>
@@ -4052,7 +4052,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>3.47615456581116</v>
+        <v>3.47615551948547</v>
       </c>
       <c r="H127" t="n">
         <v>184937</v>
@@ -4081,7 +4081,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G128" t="n">
-        <v>3.48969411849976</v>
+        <v>3.48969459533691</v>
       </c>
       <c r="H128" t="n">
         <v>107107</v>
@@ -4110,7 +4110,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G129" t="n">
-        <v>3.48969411849976</v>
+        <v>3.48969459533691</v>
       </c>
       <c r="H129" t="n">
         <v>134491</v>
@@ -4139,7 +4139,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>3.4524610042572</v>
+        <v>3.45246195793152</v>
       </c>
       <c r="H130" t="n">
         <v>186985</v>
@@ -4168,7 +4168,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>3.39830541610718</v>
+        <v>3.39830565452576</v>
       </c>
       <c r="H131" t="n">
         <v>57807</v>
@@ -4197,7 +4197,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>3.15730977058411</v>
+        <v>3.15731000900269</v>
       </c>
       <c r="H132" t="n">
         <v>707649</v>
@@ -4226,7 +4226,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22906708717346</v>
+        <v>3.22906684875488</v>
       </c>
       <c r="H133" t="n">
         <v>75468</v>
@@ -4255,7 +4255,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G134" t="n">
-        <v>3.29540824890137</v>
+        <v>3.29540872573853</v>
       </c>
       <c r="H134" t="n">
         <v>189271</v>
@@ -4284,7 +4284,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G135" t="n">
-        <v>3.32519435882568</v>
+        <v>3.32519483566284</v>
       </c>
       <c r="H135" t="n">
         <v>50898</v>
@@ -4313,7 +4313,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.58785200119019</v>
+        <v>3.58785247802734</v>
       </c>
       <c r="H136" t="n">
         <v>115636</v>
@@ -4342,7 +4342,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G137" t="n">
-        <v>3.47615456581116</v>
+        <v>3.47615551948547</v>
       </c>
       <c r="H137" t="n">
         <v>87648</v>
@@ -4371,7 +4371,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49984884262085</v>
+        <v>3.49984860420227</v>
       </c>
       <c r="H138" t="n">
         <v>69291</v>
@@ -4429,7 +4429,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57092881202698</v>
+        <v>3.57092809677124</v>
       </c>
       <c r="H140" t="n">
         <v>95057</v>
@@ -4458,7 +4458,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G141" t="n">
-        <v>3.51677274703979</v>
+        <v>3.51677250862122</v>
       </c>
       <c r="H141" t="n">
         <v>72737</v>
@@ -4516,7 +4516,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>3.60477566719055</v>
+        <v>3.60477590560913</v>
       </c>
       <c r="H143" t="n">
         <v>103724</v>
@@ -4545,7 +4545,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G144" t="n">
-        <v>3.59462189674377</v>
+        <v>3.59462141990662</v>
       </c>
       <c r="H144" t="n">
         <v>67888</v>
@@ -4574,7 +4574,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G145" t="n">
-        <v>3.63185429573059</v>
+        <v>3.63185405731201</v>
       </c>
       <c r="H145" t="n">
         <v>19997</v>
@@ -4603,7 +4603,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.61154556274414</v>
+        <v>3.61154580116272</v>
       </c>
       <c r="H146" t="n">
         <v>52589</v>
@@ -4661,7 +4661,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>3.7029345035553</v>
+        <v>3.70293378829956</v>
       </c>
       <c r="H148" t="n">
         <v>67162</v>
@@ -4690,7 +4690,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>3.78078389167786</v>
+        <v>3.78078413009644</v>
       </c>
       <c r="H149" t="n">
         <v>32010</v>
@@ -4777,7 +4777,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G152" t="n">
-        <v>3.56077408790588</v>
+        <v>3.56077432632446</v>
       </c>
       <c r="H152" t="n">
         <v>56391</v>
@@ -4806,7 +4806,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>3.61493062973022</v>
+        <v>3.61493015289307</v>
       </c>
       <c r="H153" t="n">
         <v>30739</v>
@@ -4835,7 +4835,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.67924094200134</v>
+        <v>3.67924070358276</v>
       </c>
       <c r="H154" t="n">
         <v>20938</v>
@@ -4864,7 +4864,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G155" t="n">
-        <v>3.64877820014954</v>
+        <v>3.64877843856812</v>
       </c>
       <c r="H155" t="n">
         <v>28077</v>
@@ -5009,7 +5009,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G160" t="n">
-        <v>3.81801629066467</v>
+        <v>3.81801581382751</v>
       </c>
       <c r="H160" t="n">
         <v>42795</v>
@@ -5038,7 +5038,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G161" t="n">
-        <v>3.78416919708252</v>
+        <v>3.78416895866394</v>
       </c>
       <c r="H161" t="n">
         <v>67079</v>
@@ -5067,7 +5067,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G162" t="n">
-        <v>3.8112473487854</v>
+        <v>3.81124687194824</v>
       </c>
       <c r="H162" t="n">
         <v>24479</v>
@@ -5096,7 +5096,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G163" t="n">
-        <v>3.8112473487854</v>
+        <v>3.81124687194824</v>
       </c>
       <c r="H163" t="n">
         <v>58927</v>
@@ -5125,7 +5125,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>3.75709009170532</v>
+        <v>3.75709080696106</v>
       </c>
       <c r="H164" t="n">
         <v>50697</v>
@@ -5154,7 +5154,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>3.75709009170532</v>
+        <v>3.75709080696106</v>
       </c>
       <c r="H165" t="n">
         <v>73841</v>
@@ -5183,7 +5183,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>3.98725485801697</v>
+        <v>3.98725461959839</v>
       </c>
       <c r="H166" t="n">
         <v>125514</v>
@@ -5212,7 +5212,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>3.95340752601624</v>
+        <v>3.9534068107605</v>
       </c>
       <c r="H167" t="n">
         <v>79391</v>
@@ -5241,7 +5241,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G168" t="n">
-        <v>4.13618516921997</v>
+        <v>4.1361837387085</v>
       </c>
       <c r="H168" t="n">
         <v>165803</v>
@@ -5299,7 +5299,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G170" t="n">
-        <v>4.02448701858521</v>
+        <v>4.02448749542236</v>
       </c>
       <c r="H170" t="n">
         <v>39849</v>
@@ -5328,7 +5328,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>3.99402403831482</v>
+        <v>3.9940242767334</v>
       </c>
       <c r="H171" t="n">
         <v>44191</v>
@@ -5386,7 +5386,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>4.05833530426025</v>
+        <v>4.0583348274231</v>
       </c>
       <c r="H173" t="n">
         <v>31122</v>
@@ -5415,7 +5415,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>3.96356201171875</v>
+        <v>3.96356129646301</v>
       </c>
       <c r="H174" t="n">
         <v>171483</v>
@@ -5502,7 +5502,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>4.05833530426025</v>
+        <v>4.0583348274231</v>
       </c>
       <c r="H177" t="n">
         <v>34907</v>
@@ -5560,7 +5560,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.98725485801697</v>
+        <v>3.98725461959839</v>
       </c>
       <c r="H179" t="n">
         <v>91126</v>
@@ -5618,7 +5618,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G181" t="n">
-        <v>3.9669463634491</v>
+        <v>3.96694660186768</v>
       </c>
       <c r="H181" t="n">
         <v>146337</v>
@@ -5705,7 +5705,7 @@
         <v>5</v>
       </c>
       <c r="G184" t="n">
-        <v>3.38476634025574</v>
+        <v>3.38476657867432</v>
       </c>
       <c r="H184" t="n">
         <v>271176</v>
@@ -5734,7 +5734,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>3.31707096099854</v>
+        <v>3.31707143783569</v>
       </c>
       <c r="H185" t="n">
         <v>255286</v>
@@ -5763,7 +5763,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>3.26020693778992</v>
+        <v>3.26020669937134</v>
       </c>
       <c r="H186" t="n">
         <v>102093</v>
@@ -5821,7 +5821,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G188" t="n">
-        <v>3.33061027526855</v>
+        <v>3.33061003684998</v>
       </c>
       <c r="H188" t="n">
         <v>74303</v>
@@ -5850,7 +5850,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>3.38815140724182</v>
+        <v>3.38815116882324</v>
       </c>
       <c r="H189" t="n">
         <v>81134</v>
@@ -5908,7 +5908,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G191" t="n">
-        <v>3.34279561042786</v>
+        <v>3.34279537200928</v>
       </c>
       <c r="H191" t="n">
         <v>52063</v>
@@ -5937,7 +5937,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G192" t="n">
-        <v>3.3712272644043</v>
+        <v>3.37122750282288</v>
       </c>
       <c r="H192" t="n">
         <v>58791</v>
@@ -5966,7 +5966,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G193" t="n">
-        <v>3.34956407546997</v>
+        <v>3.34956479072571</v>
       </c>
       <c r="H193" t="n">
         <v>82212</v>
@@ -5995,7 +5995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>3.49984884262085</v>
+        <v>3.49984860420227</v>
       </c>
       <c r="H194" t="n">
         <v>152264</v>
@@ -6024,7 +6024,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G195" t="n">
-        <v>3.46261548995972</v>
+        <v>3.46261596679688</v>
       </c>
       <c r="H195" t="n">
         <v>36886</v>
@@ -6053,7 +6053,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>4.11587524414062</v>
+        <v>4.11587572097778</v>
       </c>
       <c r="H196" t="n">
         <v>609931</v>
@@ -6256,7 +6256,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>4.24449729919434</v>
+        <v>4.24449682235718</v>
       </c>
       <c r="H203" t="n">
         <v>64155</v>
@@ -6285,7 +6285,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>4.26480531692505</v>
+        <v>4.26480579376221</v>
       </c>
       <c r="H204" t="n">
         <v>104103</v>
@@ -6314,7 +6314,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>4.44081401824951</v>
+        <v>4.4408130645752</v>
       </c>
       <c r="H205" t="n">
         <v>291963</v>
@@ -6343,7 +6343,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>4.46789073944092</v>
+        <v>4.46789121627808</v>
       </c>
       <c r="H206" t="n">
         <v>146224</v>
@@ -6372,7 +6372,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>4.46450567245483</v>
+        <v>4.46450662612915</v>
       </c>
       <c r="H207" t="n">
         <v>103319</v>
@@ -6401,7 +6401,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>4.44081401824951</v>
+        <v>4.4408130645752</v>
       </c>
       <c r="H208" t="n">
         <v>91882</v>
@@ -6430,7 +6430,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>4.44081401824951</v>
+        <v>4.4408130645752</v>
       </c>
       <c r="H209" t="n">
         <v>86447</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>4.46789073944092</v>
+        <v>4.46789121627808</v>
       </c>
       <c r="H210" t="n">
         <v>109334</v>
@@ -6546,7 +6546,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G213" t="n">
-        <v>4.58974361419678</v>
+        <v>4.58974313735962</v>
       </c>
       <c r="H213" t="n">
         <v>124219</v>
@@ -6575,7 +6575,7 @@
         <v>6.75</v>
       </c>
       <c r="G214" t="n">
-        <v>4.56943416595459</v>
+        <v>4.56943464279175</v>
       </c>
       <c r="H214" t="n">
         <v>80845</v>
@@ -6662,7 +6662,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G217" t="n">
-        <v>4.37988662719727</v>
+        <v>4.37988758087158</v>
       </c>
       <c r="H217" t="n">
         <v>113733</v>
@@ -6749,7 +6749,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G220" t="n">
-        <v>4.4340443611145</v>
+        <v>4.43404340744019</v>
       </c>
       <c r="H220" t="n">
         <v>204726</v>
@@ -6807,7 +6807,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G222" t="n">
-        <v>4.36296463012695</v>
+        <v>4.36296415328979</v>
       </c>
       <c r="H222" t="n">
         <v>78414</v>
@@ -6836,7 +6836,7 @@
         <v>6.5</v>
       </c>
       <c r="G223" t="n">
-        <v>4.40019607543945</v>
+        <v>4.40019655227661</v>
       </c>
       <c r="H223" t="n">
         <v>131651</v>
@@ -6865,7 +6865,7 @@
         <v>6.5</v>
       </c>
       <c r="G224" t="n">
-        <v>4.40019607543945</v>
+        <v>4.40019655227661</v>
       </c>
       <c r="H224" t="n">
         <v>103731</v>
@@ -6952,7 +6952,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>4.4340443611145</v>
+        <v>4.43404340744019</v>
       </c>
       <c r="H227" t="n">
         <v>73554</v>
@@ -6981,7 +6981,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>4.4340443611145</v>
+        <v>4.43404340744019</v>
       </c>
       <c r="H228" t="n">
         <v>55444</v>
@@ -7010,7 +7010,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>4.35957956314087</v>
+        <v>4.35957860946655</v>
       </c>
       <c r="H229" t="n">
         <v>200260</v>
@@ -7039,7 +7039,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>4.41034984588623</v>
+        <v>4.41035079956055</v>
       </c>
       <c r="H230" t="n">
         <v>130320</v>
@@ -7097,7 +7097,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G232" t="n">
-        <v>4.47804498672485</v>
+        <v>4.47804594039917</v>
       </c>
       <c r="H232" t="n">
         <v>54961</v>
@@ -7155,7 +7155,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G234" t="n">
-        <v>4.29526805877686</v>
+        <v>4.29526853561401</v>
       </c>
       <c r="H234" t="n">
         <v>197038</v>
@@ -7184,7 +7184,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G235" t="n">
-        <v>4.35280895233154</v>
+        <v>4.3528094291687</v>
       </c>
       <c r="H235" t="n">
         <v>100278</v>
@@ -7242,7 +7242,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G237" t="n">
-        <v>4.24449729919434</v>
+        <v>4.24449682235718</v>
       </c>
       <c r="H237" t="n">
         <v>65977</v>
@@ -7271,7 +7271,7 @@
         <v>6.375</v>
       </c>
       <c r="G238" t="n">
-        <v>4.31557655334473</v>
+        <v>4.31557703018188</v>
       </c>
       <c r="H238" t="n">
         <v>102989</v>
@@ -7300,7 +7300,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G239" t="n">
-        <v>4.41712045669556</v>
+        <v>4.4171199798584</v>
       </c>
       <c r="H239" t="n">
         <v>105717</v>
@@ -7329,7 +7329,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G240" t="n">
-        <v>4.46789073944092</v>
+        <v>4.46789121627808</v>
       </c>
       <c r="H240" t="n">
         <v>61992</v>
@@ -7416,7 +7416,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>4.46789073944092</v>
+        <v>4.46789121627808</v>
       </c>
       <c r="H243" t="n">
         <v>65647</v>
@@ -7445,7 +7445,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.48819971084595</v>
+        <v>4.48820018768311</v>
       </c>
       <c r="H244" t="n">
         <v>56395</v>
@@ -7503,7 +7503,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>4.45435285568237</v>
+        <v>4.45435237884521</v>
       </c>
       <c r="H246" t="n">
         <v>58966</v>
@@ -7590,7 +7590,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G249" t="n">
-        <v>4.54912567138672</v>
+        <v>4.54912614822388</v>
       </c>
       <c r="H249" t="n">
         <v>62594</v>
@@ -7619,7 +7619,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G250" t="n">
-        <v>4.62359094619751</v>
+        <v>4.62359046936035</v>
       </c>
       <c r="H250" t="n">
         <v>229951</v>
@@ -7648,7 +7648,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>4.85375452041626</v>
+        <v>4.85375499725342</v>
       </c>
       <c r="H251" t="n">
         <v>195110</v>
@@ -7706,7 +7706,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G253" t="n">
-        <v>4.75898218154907</v>
+        <v>4.75898122787476</v>
       </c>
       <c r="H253" t="n">
         <v>40012</v>
@@ -7822,7 +7822,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.79282903671265</v>
+        <v>4.7928295135498</v>
       </c>
       <c r="H257" t="n">
         <v>58206</v>
@@ -7851,7 +7851,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G258" t="n">
-        <v>4.86390924453735</v>
+        <v>4.8639087677002</v>
       </c>
       <c r="H258" t="n">
         <v>67486</v>
@@ -7880,7 +7880,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G259" t="n">
-        <v>4.81652212142944</v>
+        <v>4.8165225982666</v>
       </c>
       <c r="H259" t="n">
         <v>83473</v>
@@ -7967,7 +7967,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G262" t="n">
-        <v>4.76236581802368</v>
+        <v>4.76236629486084</v>
       </c>
       <c r="H262" t="n">
         <v>139601</v>
@@ -7996,7 +7996,7 @@
         <v>7</v>
       </c>
       <c r="G263" t="n">
-        <v>4.73867273330688</v>
+        <v>4.73867225646973</v>
       </c>
       <c r="H263" t="n">
         <v>75411</v>
@@ -8025,7 +8025,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.78944396972656</v>
+        <v>4.78944444656372</v>
       </c>
       <c r="H264" t="n">
         <v>71071</v>
@@ -8054,7 +8054,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G265" t="n">
-        <v>4.86729335784912</v>
+        <v>4.86729383468628</v>
       </c>
       <c r="H265" t="n">
         <v>82243</v>
@@ -8083,7 +8083,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78944396972656</v>
+        <v>4.78944444656372</v>
       </c>
       <c r="H266" t="n">
         <v>52227</v>
@@ -8112,7 +8112,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>4.84021520614624</v>
+        <v>4.8402156829834</v>
       </c>
       <c r="H267" t="n">
         <v>41796</v>
@@ -8141,7 +8141,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>4.81652212142944</v>
+        <v>4.8165225982666</v>
       </c>
       <c r="H268" t="n">
         <v>15823</v>
@@ -8170,7 +8170,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>4.83683109283447</v>
+        <v>4.83683061599731</v>
       </c>
       <c r="H269" t="n">
         <v>40098</v>
@@ -8199,7 +8199,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G270" t="n">
-        <v>4.83006143569946</v>
+        <v>4.83006238937378</v>
       </c>
       <c r="H270" t="n">
         <v>13830</v>
@@ -8228,7 +8228,7 @@
         <v>7.125</v>
       </c>
       <c r="G271" t="n">
-        <v>4.82329225540161</v>
+        <v>4.82329177856445</v>
       </c>
       <c r="H271" t="n">
         <v>22605</v>
@@ -8257,7 +8257,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>4.84021520614624</v>
+        <v>4.8402156829834</v>
       </c>
       <c r="H272" t="n">
         <v>25459</v>
@@ -8315,7 +8315,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G274" t="n">
-        <v>4.83006143569946</v>
+        <v>4.83006238937378</v>
       </c>
       <c r="H274" t="n">
         <v>32565</v>
@@ -8344,7 +8344,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G275" t="n">
-        <v>4.82667684555054</v>
+        <v>4.82667636871338</v>
       </c>
       <c r="H275" t="n">
         <v>57170</v>
@@ -8373,7 +8373,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G276" t="n">
-        <v>4.80298328399658</v>
+        <v>4.80298376083374</v>
       </c>
       <c r="H276" t="n">
         <v>89643</v>
@@ -8402,7 +8402,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G277" t="n">
-        <v>4.81652212142944</v>
+        <v>4.8165225982666</v>
       </c>
       <c r="H277" t="n">
         <v>53288</v>
@@ -8431,7 +8431,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65066814422607</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H278" t="n">
         <v>80211</v>
@@ -8460,7 +8460,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G279" t="n">
-        <v>4.63712930679321</v>
+        <v>4.63712978363037</v>
       </c>
       <c r="H279" t="n">
         <v>115147</v>
@@ -8489,7 +8489,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.65743827819824</v>
+        <v>4.6574387550354</v>
       </c>
       <c r="H280" t="n">
         <v>45461</v>
@@ -8576,7 +8576,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>4.65066814422607</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H283" t="n">
         <v>39226</v>
@@ -8605,7 +8605,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>4.65066814422607</v>
+        <v>4.65066862106323</v>
       </c>
       <c r="H284" t="n">
         <v>31328</v>
@@ -8692,7 +8692,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74205684661865</v>
+        <v>4.74205780029297</v>
       </c>
       <c r="H287" t="n">
         <v>26431</v>
@@ -8721,7 +8721,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>4.79282903671265</v>
+        <v>4.7928295135498</v>
       </c>
       <c r="H288" t="n">
         <v>40804</v>
@@ -8750,7 +8750,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G289" t="n">
-        <v>5.00945425033569</v>
+        <v>5.00945377349854</v>
       </c>
       <c r="H289" t="n">
         <v>353566</v>
@@ -8779,7 +8779,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>5.04330158233643</v>
+        <v>5.04330205917358</v>
       </c>
       <c r="H290" t="n">
         <v>270928</v>
@@ -8808,7 +8808,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G291" t="n">
-        <v>5.07037973403931</v>
+        <v>5.07038021087646</v>
       </c>
       <c r="H291" t="n">
         <v>225000</v>
@@ -8866,7 +8866,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G293" t="n">
-        <v>5.06699419021606</v>
+        <v>5.06699562072754</v>
       </c>
       <c r="H293" t="n">
         <v>44482</v>
@@ -8924,7 +8924,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G295" t="n">
-        <v>4.99930047988892</v>
+        <v>4.99930000305176</v>
       </c>
       <c r="H295" t="n">
         <v>48006</v>
@@ -8953,7 +8953,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G296" t="n">
-        <v>4.9756064414978</v>
+        <v>4.97560596466064</v>
       </c>
       <c r="H296" t="n">
         <v>73571</v>
@@ -9011,7 +9011,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>4.9756064414978</v>
+        <v>4.97560596466064</v>
       </c>
       <c r="H298" t="n">
         <v>67261</v>
@@ -9069,7 +9069,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G300" t="n">
-        <v>5.05684089660645</v>
+        <v>5.05684041976929</v>
       </c>
       <c r="H300" t="n">
         <v>83204</v>
@@ -9127,7 +9127,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>5.04330158233643</v>
+        <v>5.04330205917358</v>
       </c>
       <c r="H302" t="n">
         <v>60086</v>
@@ -9156,7 +9156,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G303" t="n">
-        <v>5.03991651535034</v>
+        <v>5.03991746902466</v>
       </c>
       <c r="H303" t="n">
         <v>64927</v>
@@ -9243,7 +9243,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G306" t="n">
-        <v>5.08391952514648</v>
+        <v>5.08391857147217</v>
       </c>
       <c r="H306" t="n">
         <v>115407</v>
@@ -9272,7 +9272,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G307" t="n">
-        <v>5.07037973403931</v>
+        <v>5.07038021087646</v>
       </c>
       <c r="H307" t="n">
         <v>101547</v>
@@ -9301,7 +9301,7 @@
         <v>7.5</v>
       </c>
       <c r="G308" t="n">
-        <v>5.07714986801147</v>
+        <v>5.07714939117432</v>
       </c>
       <c r="H308" t="n">
         <v>29858</v>
@@ -9359,7 +9359,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G310" t="n">
-        <v>5.06699419021606</v>
+        <v>5.06699562072754</v>
       </c>
       <c r="H310" t="n">
         <v>54701</v>
@@ -9388,7 +9388,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>5.27346563339233</v>
+        <v>5.27346611022949</v>
       </c>
       <c r="H311" t="n">
         <v>171397</v>
@@ -9446,7 +9446,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G313" t="n">
-        <v>5.29377412796021</v>
+        <v>5.29377460479736</v>
       </c>
       <c r="H313" t="n">
         <v>49635</v>
@@ -9504,7 +9504,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G315" t="n">
-        <v>5.23284864425659</v>
+        <v>5.23284816741943</v>
       </c>
       <c r="H315" t="n">
         <v>195604</v>
@@ -9620,7 +9620,7 @@
         <v>8</v>
       </c>
       <c r="G319" t="n">
-        <v>5.41562557220459</v>
+        <v>5.41562604904175</v>
       </c>
       <c r="H319" t="n">
         <v>179752</v>
@@ -9678,7 +9678,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>5.40208673477173</v>
+        <v>5.40208721160889</v>
       </c>
       <c r="H321" t="n">
         <v>71386</v>
@@ -9765,7 +9765,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>5.21253967285156</v>
+        <v>5.2125391960144</v>
       </c>
       <c r="H324" t="n">
         <v>117109</v>
@@ -9794,7 +9794,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>5.17869234085083</v>
+        <v>5.17869329452515</v>
       </c>
       <c r="H325" t="n">
         <v>114001</v>
@@ -9852,7 +9852,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>5.17869234085083</v>
+        <v>5.17869329452515</v>
       </c>
       <c r="H327" t="n">
         <v>28662</v>
@@ -9881,7 +9881,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>5.1448450088501</v>
+        <v>5.14484405517578</v>
       </c>
       <c r="H328" t="n">
         <v>90125</v>
@@ -9939,7 +9939,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>5.13807487487793</v>
+        <v>5.13807535171509</v>
       </c>
       <c r="H330" t="n">
         <v>161802</v>
@@ -9997,7 +9997,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.83344602584839</v>
+        <v>4.83344554901123</v>
       </c>
       <c r="H332" t="n">
         <v>100510</v>
@@ -10026,7 +10026,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>4.97899103164673</v>
+        <v>4.97899150848389</v>
       </c>
       <c r="H333" t="n">
         <v>75688</v>
@@ -10055,7 +10055,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>4.92483472824097</v>
+        <v>4.92483520507812</v>
       </c>
       <c r="H334" t="n">
         <v>56297</v>
@@ -10084,7 +10084,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>4.95868301391602</v>
+        <v>4.95868253707886</v>
       </c>
       <c r="H335" t="n">
         <v>87438</v>
@@ -10113,7 +10113,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G336" t="n">
-        <v>5.13807487487793</v>
+        <v>5.13807535171509</v>
       </c>
       <c r="H336" t="n">
         <v>74359</v>
@@ -10229,7 +10229,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G340" t="n">
-        <v>5.08391952514648</v>
+        <v>5.08391857147217</v>
       </c>
       <c r="H340" t="n">
         <v>75184</v>
@@ -10287,7 +10287,7 @@
         <v>7.5</v>
       </c>
       <c r="G342" t="n">
-        <v>5.07714986801147</v>
+        <v>5.07714939117432</v>
       </c>
       <c r="H342" t="n">
         <v>56561</v>
@@ -10316,7 +10316,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>5.13807487487793</v>
+        <v>5.13807535171509</v>
       </c>
       <c r="H343" t="n">
         <v>63057</v>
@@ -10345,7 +10345,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G344" t="n">
-        <v>5.09068870544434</v>
+        <v>5.09068822860718</v>
       </c>
       <c r="H344" t="n">
         <v>61634</v>
@@ -10374,7 +10374,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.23200035095215</v>
+        <v>5.23200082778931</v>
       </c>
       <c r="H345" t="n">
         <v>74072</v>
@@ -10403,7 +10403,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G346" t="n">
-        <v>5.3905463218689</v>
+        <v>5.39054679870605</v>
       </c>
       <c r="H346" t="n">
         <v>202741</v>
@@ -10461,7 +10461,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>5.156174659729</v>
+        <v>5.15617513656616</v>
       </c>
       <c r="H348" t="n">
         <v>77577</v>
@@ -10519,7 +10519,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G350" t="n">
-        <v>4.81840419769287</v>
+        <v>4.81840372085571</v>
       </c>
       <c r="H350" t="n">
         <v>315554</v>
@@ -10548,7 +10548,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G351" t="n">
-        <v>4.71500492095947</v>
+        <v>4.71500444412231</v>
       </c>
       <c r="H351" t="n">
         <v>350968</v>
@@ -10606,7 +10606,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G353" t="n">
-        <v>4.67709112167358</v>
+        <v>4.67709159851074</v>
       </c>
       <c r="H353" t="n">
         <v>174018</v>
@@ -10635,7 +10635,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>4.7218976020813</v>
+        <v>4.72189807891846</v>
       </c>
       <c r="H354" t="n">
         <v>62590</v>
@@ -10751,7 +10751,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G358" t="n">
-        <v>4.58747816085815</v>
+        <v>4.58747911453247</v>
       </c>
       <c r="H358" t="n">
         <v>52219</v>
@@ -10809,7 +10809,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G360" t="n">
-        <v>4.54611873626709</v>
+        <v>4.54611921310425</v>
       </c>
       <c r="H360" t="n">
         <v>35793</v>
@@ -10838,7 +10838,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G361" t="n">
-        <v>4.43237972259521</v>
+        <v>4.43238019943237</v>
       </c>
       <c r="H361" t="n">
         <v>127010</v>
@@ -10954,7 +10954,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>4.36689376831055</v>
+        <v>4.36689424514771</v>
       </c>
       <c r="H365" t="n">
         <v>92594</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>4.26004791259766</v>
+        <v>4.26004838943481</v>
       </c>
       <c r="H367" t="n">
         <v>48450</v>
@@ -11070,7 +11070,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>4.30485486984253</v>
+        <v>4.30485439300537</v>
       </c>
       <c r="H369" t="n">
         <v>176874</v>
@@ -11157,7 +11157,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G372" t="n">
-        <v>4.32208824157715</v>
+        <v>4.32208776473999</v>
       </c>
       <c r="H372" t="n">
         <v>57654</v>
@@ -11215,7 +11215,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>4.17043590545654</v>
+        <v>4.17043542861938</v>
       </c>
       <c r="H374" t="n">
         <v>551406</v>
@@ -11244,7 +11244,7 @@
         <v>6.25</v>
       </c>
       <c r="G375" t="n">
-        <v>4.30830097198486</v>
+        <v>4.30830144882202</v>
       </c>
       <c r="H375" t="n">
         <v>83151</v>
@@ -11331,7 +11331,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>4.23592185974121</v>
+        <v>4.23592233657837</v>
       </c>
       <c r="H378" t="n">
         <v>77420</v>
@@ -11418,7 +11418,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G381" t="n">
-        <v>4.30485486984253</v>
+        <v>4.30485439300537</v>
       </c>
       <c r="H381" t="n">
         <v>127973</v>
@@ -11534,7 +11534,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>4.51510000228882</v>
+        <v>4.51509952545166</v>
       </c>
       <c r="H385" t="n">
         <v>184215</v>
@@ -11563,7 +11563,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>4.4978666305542</v>
+        <v>4.49786615371704</v>
       </c>
       <c r="H386" t="n">
         <v>69957</v>
@@ -11679,7 +11679,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>4.49442005157471</v>
+        <v>4.49441957473755</v>
       </c>
       <c r="H390" t="n">
         <v>149419</v>
@@ -11708,7 +11708,7 @@
         <v>6.625</v>
       </c>
       <c r="G391" t="n">
-        <v>4.56679916381836</v>
+        <v>4.56679964065552</v>
       </c>
       <c r="H391" t="n">
         <v>195950</v>
@@ -11737,7 +11737,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>4.62883949279785</v>
+        <v>4.62883853912354</v>
       </c>
       <c r="H392" t="n">
         <v>73105</v>
@@ -11795,7 +11795,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G394" t="n">
-        <v>4.61505270004272</v>
+        <v>4.61505222320557</v>
       </c>
       <c r="H394" t="n">
         <v>74456</v>
@@ -11824,7 +11824,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>4.52888631820679</v>
+        <v>4.52888584136963</v>
       </c>
       <c r="H395" t="n">
         <v>77827</v>
@@ -11882,7 +11882,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G397" t="n">
-        <v>4.64262533187866</v>
+        <v>4.64262580871582</v>
       </c>
       <c r="H397" t="n">
         <v>509615</v>
@@ -11969,7 +11969,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G400" t="n">
-        <v>4.58403205871582</v>
+        <v>4.58403158187866</v>
       </c>
       <c r="H400" t="n">
         <v>49686</v>
@@ -12027,7 +12027,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>4.5219931602478</v>
+        <v>4.52199268341064</v>
       </c>
       <c r="H402" t="n">
         <v>98507</v>
@@ -12056,7 +12056,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>4.53577947616577</v>
+        <v>4.53577899932861</v>
       </c>
       <c r="H403" t="n">
         <v>44497</v>
@@ -12085,7 +12085,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>4.42548704147339</v>
+        <v>4.42548656463623</v>
       </c>
       <c r="H404" t="n">
         <v>58646</v>
@@ -12114,7 +12114,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>4.4978666305542</v>
+        <v>4.49786615371704</v>
       </c>
       <c r="H405" t="n">
         <v>38550</v>
@@ -12143,7 +12143,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>4.50475931167603</v>
+        <v>4.50475978851318</v>
       </c>
       <c r="H406" t="n">
         <v>51611</v>
@@ -12201,7 +12201,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G408" t="n">
-        <v>4.45995283126831</v>
+        <v>4.45995330810547</v>
       </c>
       <c r="H408" t="n">
         <v>41217</v>
@@ -12259,7 +12259,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G410" t="n">
-        <v>4.54956531524658</v>
+        <v>4.54956579208374</v>
       </c>
       <c r="H410" t="n">
         <v>114764</v>
@@ -12288,7 +12288,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>4.58403205871582</v>
+        <v>4.58403158187866</v>
       </c>
       <c r="H411" t="n">
         <v>48654</v>
@@ -12346,7 +12346,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.46339988708496</v>
+        <v>4.46340036392212</v>
       </c>
       <c r="H413" t="n">
         <v>62096</v>
@@ -12462,7 +12462,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>4.42548704147339</v>
+        <v>4.42548656463623</v>
       </c>
       <c r="H417" t="n">
         <v>91936</v>
@@ -12549,7 +12549,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G420" t="n">
-        <v>4.32208824157715</v>
+        <v>4.32208776473999</v>
       </c>
       <c r="H420" t="n">
         <v>25521</v>
@@ -12578,7 +12578,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G421" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281549453735</v>
       </c>
       <c r="H421" t="n">
         <v>57686</v>
@@ -12694,7 +12694,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>4.20490121841431</v>
+        <v>4.20490217208862</v>
       </c>
       <c r="H425" t="n">
         <v>58755</v>
@@ -12810,7 +12810,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G429" t="n">
-        <v>4.24626207351685</v>
+        <v>4.24626159667969</v>
       </c>
       <c r="H429" t="n">
         <v>38370</v>
@@ -12839,7 +12839,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>4.20490121841431</v>
+        <v>4.20490217208862</v>
       </c>
       <c r="H430" t="n">
         <v>45169</v>
@@ -12868,7 +12868,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281549453735</v>
       </c>
       <c r="H431" t="n">
         <v>97071</v>
@@ -12926,7 +12926,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>4.2428150177002</v>
+        <v>4.24281549453735</v>
       </c>
       <c r="H433" t="n">
         <v>49792</v>
@@ -13013,7 +13013,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G436" t="n">
-        <v>4.23247480392456</v>
+        <v>4.23247528076172</v>
       </c>
       <c r="H436" t="n">
         <v>100278</v>
@@ -13100,7 +13100,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>3.52936053276062</v>
+        <v>3.52936005592346</v>
       </c>
       <c r="H439" t="n">
         <v>1797627</v>
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="G440" t="n">
-        <v>3.44664072990417</v>
+        <v>3.44664096832275</v>
       </c>
       <c r="H440" t="n">
         <v>1056990</v>
@@ -13158,7 +13158,7 @@
         <v>5</v>
       </c>
       <c r="G441" t="n">
-        <v>3.44664072990417</v>
+        <v>3.44664096832275</v>
       </c>
       <c r="H441" t="n">
         <v>454580</v>
@@ -13187,7 +13187,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>3.37770795822144</v>
+        <v>3.37770843505859</v>
       </c>
       <c r="H442" t="n">
         <v>276428</v>
@@ -13216,7 +13216,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G443" t="n">
-        <v>3.37081480026245</v>
+        <v>3.37081456184387</v>
       </c>
       <c r="H443" t="n">
         <v>202384</v>
@@ -13245,7 +13245,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G444" t="n">
-        <v>3.44250512123108</v>
+        <v>3.44250440597534</v>
       </c>
       <c r="H444" t="n">
         <v>322860</v>
@@ -13274,7 +13274,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G445" t="n">
-        <v>3.44526219367981</v>
+        <v>3.44526243209839</v>
       </c>
       <c r="H445" t="n">
         <v>243913</v>
@@ -13303,7 +13303,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G446" t="n">
-        <v>3.4245822429657</v>
+        <v>3.42458248138428</v>
       </c>
       <c r="H446" t="n">
         <v>285105</v>
@@ -13332,7 +13332,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>3.42596101760864</v>
+        <v>3.42596125602722</v>
       </c>
       <c r="H447" t="n">
         <v>173870</v>
@@ -13361,7 +13361,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G448" t="n">
-        <v>3.4369900226593</v>
+        <v>3.43699049949646</v>
       </c>
       <c r="H448" t="n">
         <v>109773</v>
@@ -13390,7 +13390,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.42596101760864</v>
+        <v>3.42596125602722</v>
       </c>
       <c r="H449" t="n">
         <v>172863</v>
@@ -13419,7 +13419,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G450" t="n">
-        <v>3.38046503067017</v>
+        <v>3.3804657459259</v>
       </c>
       <c r="H450" t="n">
         <v>226892</v>
@@ -13448,7 +13448,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G451" t="n">
-        <v>3.32807612419128</v>
+        <v>3.32807636260986</v>
       </c>
       <c r="H451" t="n">
         <v>313343</v>
@@ -13535,7 +13535,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G454" t="n">
-        <v>3.05372381210327</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H454" t="n">
         <v>402906</v>
@@ -13593,7 +13593,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>3.12954998016357</v>
+        <v>3.129549741745</v>
       </c>
       <c r="H456" t="n">
         <v>719609</v>
@@ -13651,7 +13651,7 @@
         <v>4.40399980545044</v>
       </c>
       <c r="G458" t="n">
-        <v>3.03580164909363</v>
+        <v>3.03580117225647</v>
       </c>
       <c r="H458" t="n">
         <v>266731</v>
@@ -13680,7 +13680,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G459" t="n">
-        <v>2.95308208465576</v>
+        <v>2.95308184623718</v>
       </c>
       <c r="H459" t="n">
         <v>409593</v>
@@ -13796,7 +13796,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G463" t="n">
-        <v>2.84830355644226</v>
+        <v>2.84830379486084</v>
       </c>
       <c r="H463" t="n">
         <v>341520</v>
@@ -13883,7 +13883,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G466" t="n">
-        <v>2.98479056358337</v>
+        <v>2.98479080200195</v>
       </c>
       <c r="H466" t="n">
         <v>406773</v>
@@ -13941,7 +13941,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G468" t="n">
-        <v>2.89655709266663</v>
+        <v>2.89655685424805</v>
       </c>
       <c r="H468" t="n">
         <v>587468</v>
@@ -13970,7 +13970,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>2.8607120513916</v>
+        <v>2.86071181297302</v>
       </c>
       <c r="H469" t="n">
         <v>326227</v>
@@ -13999,7 +13999,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G470" t="n">
-        <v>2.83727502822876</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H470" t="n">
         <v>239632</v>
@@ -14057,7 +14057,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G472" t="n">
-        <v>3.04545187950134</v>
+        <v>3.0454523563385</v>
       </c>
       <c r="H472" t="n">
         <v>1192003</v>
@@ -14086,7 +14086,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>2.97789764404297</v>
+        <v>2.97789812088013</v>
       </c>
       <c r="H473" t="n">
         <v>366433</v>
@@ -14115,7 +14115,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G474" t="n">
-        <v>3.07026791572571</v>
+        <v>3.07026743888855</v>
       </c>
       <c r="H474" t="n">
         <v>582857</v>
@@ -14144,7 +14144,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G475" t="n">
-        <v>3.0096070766449</v>
+        <v>3.00960683822632</v>
       </c>
       <c r="H475" t="n">
         <v>430262</v>
@@ -14173,7 +14173,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>2.94343113899231</v>
+        <v>2.94343161582947</v>
       </c>
       <c r="H476" t="n">
         <v>398406</v>
@@ -14202,7 +14202,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.8607120513916</v>
+        <v>2.86071181297302</v>
       </c>
       <c r="H477" t="n">
         <v>523481</v>
@@ -14347,7 +14347,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692525863647</v>
       </c>
       <c r="H482" t="n">
         <v>511759</v>
@@ -14405,7 +14405,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G484" t="n">
-        <v>2.85519742965698</v>
+        <v>2.85519766807556</v>
       </c>
       <c r="H484" t="n">
         <v>386325</v>
@@ -14463,7 +14463,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G486" t="n">
-        <v>2.76420617103577</v>
+        <v>2.76420593261719</v>
       </c>
       <c r="H486" t="n">
         <v>342490</v>
@@ -14521,7 +14521,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G488" t="n">
-        <v>2.80005073547363</v>
+        <v>2.80005097389221</v>
       </c>
       <c r="H488" t="n">
         <v>264775</v>
@@ -14550,7 +14550,7 @@
         <v>4</v>
       </c>
       <c r="G489" t="n">
-        <v>2.75731253623962</v>
+        <v>2.7573127746582</v>
       </c>
       <c r="H489" t="n">
         <v>356617</v>
@@ -14579,7 +14579,7 @@
         <v>4</v>
       </c>
       <c r="G490" t="n">
-        <v>2.75731253623962</v>
+        <v>2.7573127746582</v>
       </c>
       <c r="H490" t="n">
         <v>337390</v>
@@ -14608,7 +14608,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G491" t="n">
-        <v>2.83727502822876</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H491" t="n">
         <v>684752</v>
@@ -14666,7 +14666,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>2.88139176368713</v>
+        <v>2.88139128684998</v>
       </c>
       <c r="H493" t="n">
         <v>495399</v>
@@ -14782,7 +14782,7 @@
         <v>4.25</v>
       </c>
       <c r="G497" t="n">
-        <v>2.92964434623718</v>
+        <v>2.92964458465576</v>
       </c>
       <c r="H497" t="n">
         <v>315673</v>
@@ -14811,7 +14811,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G498" t="n">
-        <v>2.95308208465576</v>
+        <v>2.95308184623718</v>
       </c>
       <c r="H498" t="n">
         <v>254114</v>
@@ -14840,7 +14840,7 @@
         <v>4.25</v>
       </c>
       <c r="G499" t="n">
-        <v>2.92964434623718</v>
+        <v>2.92964458465576</v>
       </c>
       <c r="H499" t="n">
         <v>242699</v>
@@ -14869,7 +14869,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93240237236023</v>
+        <v>2.93240213394165</v>
       </c>
       <c r="H500" t="n">
         <v>107995</v>
@@ -14927,7 +14927,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G502" t="n">
-        <v>2.82210922241211</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H502" t="n">
         <v>359617</v>
@@ -14985,7 +14985,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G504" t="n">
-        <v>2.81935238838196</v>
+        <v>2.8193519115448</v>
       </c>
       <c r="H504" t="n">
         <v>148517</v>
@@ -15014,7 +15014,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>2.86760544776917</v>
+        <v>2.86760497093201</v>
       </c>
       <c r="H505" t="n">
         <v>191845</v>
@@ -15101,7 +15101,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G508" t="n">
-        <v>2.80005073547363</v>
+        <v>2.80005097389221</v>
       </c>
       <c r="H508" t="n">
         <v>47300</v>
@@ -15130,7 +15130,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G509" t="n">
-        <v>2.89931416511536</v>
+        <v>2.89931440353394</v>
       </c>
       <c r="H509" t="n">
         <v>204187</v>
@@ -15188,7 +15188,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G511" t="n">
-        <v>2.83727502822876</v>
+        <v>2.83727478981018</v>
       </c>
       <c r="H511" t="n">
         <v>100855</v>
@@ -15333,7 +15333,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G516" t="n">
-        <v>3.22605538368225</v>
+        <v>3.22605609893799</v>
       </c>
       <c r="H516" t="n">
         <v>664170</v>
@@ -15362,7 +15362,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>3.16401672363281</v>
+        <v>3.16401624679565</v>
       </c>
       <c r="H517" t="n">
         <v>613794</v>
@@ -15391,7 +15391,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>3.11920952796936</v>
+        <v>3.11921000480652</v>
       </c>
       <c r="H518" t="n">
         <v>467928</v>
@@ -15420,7 +15420,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H519" t="n">
         <v>718475</v>
@@ -15478,7 +15478,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G521" t="n">
-        <v>3.17780327796936</v>
+        <v>3.17780256271362</v>
       </c>
       <c r="H521" t="n">
         <v>462498</v>
@@ -15507,7 +15507,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G522" t="n">
-        <v>3.16746306419373</v>
+        <v>3.16746258735657</v>
       </c>
       <c r="H522" t="n">
         <v>493955</v>
@@ -15536,7 +15536,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.13299632072449</v>
+        <v>3.13299655914307</v>
       </c>
       <c r="H523" t="n">
         <v>379353</v>
@@ -15623,7 +15623,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>3.13988947868347</v>
+        <v>3.13988971710205</v>
       </c>
       <c r="H526" t="n">
         <v>374300</v>
@@ -15681,7 +15681,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>3.09508323669434</v>
+        <v>3.09508347511292</v>
       </c>
       <c r="H528" t="n">
         <v>253894</v>
@@ -15710,7 +15710,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G529" t="n">
-        <v>3.09508323669434</v>
+        <v>3.09508347511292</v>
       </c>
       <c r="H529" t="n">
         <v>186227</v>
@@ -15739,7 +15739,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G530" t="n">
-        <v>3.1950364112854</v>
+        <v>3.19503617286682</v>
       </c>
       <c r="H530" t="n">
         <v>364125</v>
@@ -15768,7 +15768,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>3.14333653450012</v>
+        <v>3.1433367729187</v>
       </c>
       <c r="H531" t="n">
         <v>265328</v>
@@ -15826,7 +15826,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>3.04683065414429</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H533" t="n">
         <v>319024</v>
@@ -15855,7 +15855,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>3.02959728240967</v>
+        <v>3.02959752082825</v>
       </c>
       <c r="H534" t="n">
         <v>317377</v>
@@ -15913,7 +15913,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>2.98479056358337</v>
+        <v>2.98479080200195</v>
       </c>
       <c r="H536" t="n">
         <v>519676</v>
@@ -15942,7 +15942,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H537" t="n">
         <v>1557885</v>
@@ -16029,7 +16029,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.78488612174988</v>
+        <v>2.7848858833313</v>
       </c>
       <c r="H540" t="n">
         <v>280515</v>
@@ -16058,7 +16058,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G541" t="n">
-        <v>2.78143930435181</v>
+        <v>2.78143906593323</v>
       </c>
       <c r="H541" t="n">
         <v>442828</v>
@@ -16087,7 +16087,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.71595335006714</v>
+        <v>2.71595287322998</v>
       </c>
       <c r="H542" t="n">
         <v>324677</v>
@@ -16116,7 +16116,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>3.04683065414429</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H543" t="n">
         <v>812045</v>
@@ -16145,7 +16145,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>3.08129692077637</v>
+        <v>3.08129644393921</v>
       </c>
       <c r="H544" t="n">
         <v>443706</v>
@@ -16232,7 +16232,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06406378746033</v>
+        <v>3.06406354904175</v>
       </c>
       <c r="H547" t="n">
         <v>404236</v>
@@ -16261,7 +16261,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>3.04338383674622</v>
+        <v>3.04338407516479</v>
       </c>
       <c r="H548" t="n">
         <v>383699</v>
@@ -16290,7 +16290,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G549" t="n">
-        <v>3.02615070343018</v>
+        <v>3.02615022659302</v>
       </c>
       <c r="H549" t="n">
         <v>326890</v>
@@ -16319,7 +16319,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G550" t="n">
-        <v>3.05372381210327</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H550" t="n">
         <v>238836</v>
@@ -16348,7 +16348,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G551" t="n">
-        <v>3.01236414909363</v>
+        <v>3.01236391067505</v>
       </c>
       <c r="H551" t="n">
         <v>293142</v>
@@ -16377,7 +16377,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G552" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H552" t="n">
         <v>511233</v>
@@ -16406,7 +16406,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G553" t="n">
-        <v>3.00547075271606</v>
+        <v>3.00547122955322</v>
       </c>
       <c r="H553" t="n">
         <v>251650</v>
@@ -16435,7 +16435,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>2.96066427230835</v>
+        <v>2.96066451072693</v>
       </c>
       <c r="H554" t="n">
         <v>294528</v>
@@ -16522,7 +16522,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G557" t="n">
-        <v>3.05372381210327</v>
+        <v>3.05372357368469</v>
       </c>
       <c r="H557" t="n">
         <v>922577</v>
@@ -16580,7 +16580,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>3.06061720848083</v>
+        <v>3.06061697006226</v>
       </c>
       <c r="H559" t="n">
         <v>415498</v>
@@ -16609,7 +16609,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G560" t="n">
-        <v>2.92275142669678</v>
+        <v>2.9227511882782</v>
       </c>
       <c r="H560" t="n">
         <v>1429089</v>
@@ -16638,7 +16638,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G561" t="n">
-        <v>2.96755790710449</v>
+        <v>2.96755766868591</v>
       </c>
       <c r="H561" t="n">
         <v>425732</v>
@@ -16667,7 +16667,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G562" t="n">
-        <v>2.87794518470764</v>
+        <v>2.8779456615448</v>
       </c>
       <c r="H562" t="n">
         <v>486870</v>
@@ -16696,7 +16696,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.88483810424805</v>
+        <v>2.88483834266663</v>
       </c>
       <c r="H563" t="n">
         <v>720599</v>
@@ -16754,7 +16754,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H565" t="n">
         <v>871376</v>
@@ -16783,7 +16783,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>2.87794518470764</v>
+        <v>2.8779456615448</v>
       </c>
       <c r="H566" t="n">
         <v>234339</v>
@@ -16812,7 +16812,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H567" t="n">
         <v>188660</v>
@@ -16870,7 +16870,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>2.86760544776917</v>
+        <v>2.86760497093201</v>
       </c>
       <c r="H569" t="n">
         <v>414211</v>
@@ -16899,7 +16899,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G570" t="n">
-        <v>2.84003186225891</v>
+        <v>2.84003210067749</v>
       </c>
       <c r="H570" t="n">
         <v>233390</v>
@@ -16928,7 +16928,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G571" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692525863647</v>
       </c>
       <c r="H571" t="n">
         <v>165452</v>
@@ -16986,7 +16986,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>2.87449860572815</v>
+        <v>2.87449836730957</v>
       </c>
       <c r="H573" t="n">
         <v>91271</v>
@@ -17073,7 +17073,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>2.9468777179718</v>
+        <v>2.94687795639038</v>
       </c>
       <c r="H576" t="n">
         <v>152196</v>
@@ -17131,7 +17131,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G578" t="n">
-        <v>2.97789764404297</v>
+        <v>2.97789812088013</v>
       </c>
       <c r="H578" t="n">
         <v>86085</v>
@@ -17160,7 +17160,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>2.96066427230835</v>
+        <v>2.96066451072693</v>
       </c>
       <c r="H579" t="n">
         <v>72514</v>
@@ -17189,7 +17189,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G580" t="n">
-        <v>2.99513077735901</v>
+        <v>2.99513053894043</v>
       </c>
       <c r="H580" t="n">
         <v>44953</v>
@@ -17218,7 +17218,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G581" t="n">
-        <v>2.96411108970642</v>
+        <v>2.964111328125</v>
       </c>
       <c r="H581" t="n">
         <v>83737</v>
@@ -17247,7 +17247,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>2.97789764404297</v>
+        <v>2.97789812088013</v>
       </c>
       <c r="H582" t="n">
         <v>144591</v>
@@ -17334,7 +17334,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>2.9882378578186</v>
+        <v>2.98823761940002</v>
       </c>
       <c r="H585" t="n">
         <v>198148</v>
@@ -17450,7 +17450,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>3.04683065414429</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H589" t="n">
         <v>119110</v>
@@ -17508,7 +17508,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>3.07095694541931</v>
+        <v>3.07095718383789</v>
       </c>
       <c r="H591" t="n">
         <v>195836</v>
@@ -17537,7 +17537,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G592" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H592" t="n">
         <v>233898</v>
@@ -17566,7 +17566,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G593" t="n">
-        <v>3.00891780853271</v>
+        <v>3.00891733169556</v>
       </c>
       <c r="H593" t="n">
         <v>230140</v>
@@ -17595,7 +17595,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G594" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H594" t="n">
         <v>68851</v>
@@ -17653,7 +17653,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G596" t="n">
-        <v>3.00891780853271</v>
+        <v>3.00891733169556</v>
       </c>
       <c r="H596" t="n">
         <v>122410</v>
@@ -17711,7 +17711,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>3.04683065414429</v>
+        <v>3.04683041572571</v>
       </c>
       <c r="H598" t="n">
         <v>158703</v>
@@ -17798,7 +17798,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G601" t="n">
-        <v>3.01925730705261</v>
+        <v>3.01925754547119</v>
       </c>
       <c r="H601" t="n">
         <v>220818</v>
@@ -17827,7 +17827,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G602" t="n">
-        <v>3.02270412445068</v>
+        <v>3.02270436286926</v>
       </c>
       <c r="H602" t="n">
         <v>358951</v>
@@ -17856,7 +17856,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G603" t="n">
-        <v>3.09027028083801</v>
+        <v>3.09027004241943</v>
       </c>
       <c r="H603" t="n">
         <v>195385</v>
@@ -17972,7 +17972,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>2.95513796806335</v>
+        <v>2.9551374912262</v>
       </c>
       <c r="H607" t="n">
         <v>101236</v>
@@ -18030,7 +18030,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G609" t="n">
-        <v>2.96224999427795</v>
+        <v>2.96224975585938</v>
       </c>
       <c r="H609" t="n">
         <v>120210</v>
@@ -18059,7 +18059,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.91957664489746</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H610" t="n">
         <v>241159</v>
@@ -18088,7 +18088,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.87690258026123</v>
+        <v>2.87690305709839</v>
       </c>
       <c r="H611" t="n">
         <v>124383</v>
@@ -18117,7 +18117,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G612" t="n">
-        <v>2.85912203788757</v>
+        <v>2.85912227630615</v>
       </c>
       <c r="H612" t="n">
         <v>360962</v>
@@ -18204,7 +18204,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G615" t="n">
-        <v>2.64219856262207</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H615" t="n">
         <v>208013</v>
@@ -18262,7 +18262,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G617" t="n">
-        <v>2.69198441505432</v>
+        <v>2.6919846534729</v>
       </c>
       <c r="H617" t="n">
         <v>341053</v>
@@ -18320,7 +18320,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G619" t="n">
-        <v>2.57107663154602</v>
+        <v>2.57107615470886</v>
       </c>
       <c r="H619" t="n">
         <v>188588</v>
@@ -18378,7 +18378,7 @@
         <v>3.625</v>
       </c>
       <c r="G621" t="n">
-        <v>2.5781888961792</v>
+        <v>2.57818865776062</v>
       </c>
       <c r="H621" t="n">
         <v>419710</v>
@@ -18465,7 +18465,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.61019372940063</v>
+        <v>2.61019396781921</v>
       </c>
       <c r="H624" t="n">
         <v>152498</v>
@@ -18523,7 +18523,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G626" t="n">
-        <v>2.70265316963196</v>
+        <v>2.7026526927948</v>
       </c>
       <c r="H626" t="n">
         <v>282059</v>
@@ -18610,7 +18610,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G629" t="n">
-        <v>2.69198441505432</v>
+        <v>2.6919846534729</v>
       </c>
       <c r="H629" t="n">
         <v>99972</v>
@@ -18639,7 +18639,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>2.6990966796875</v>
+        <v>2.69909715652466</v>
       </c>
       <c r="H630" t="n">
         <v>92589</v>
@@ -18668,7 +18668,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G631" t="n">
-        <v>2.66353559494019</v>
+        <v>2.66353583335876</v>
       </c>
       <c r="H631" t="n">
         <v>148678</v>
@@ -18726,7 +18726,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G633" t="n">
-        <v>2.49995422363281</v>
+        <v>2.49995398521423</v>
       </c>
       <c r="H633" t="n">
         <v>289300</v>
@@ -18755,7 +18755,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G634" t="n">
-        <v>2.52484679222107</v>
+        <v>2.52484703063965</v>
       </c>
       <c r="H634" t="n">
         <v>311041</v>
@@ -18784,7 +18784,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H635" t="n">
         <v>247960</v>
@@ -18900,7 +18900,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>2.6990966796875</v>
+        <v>2.69909715652466</v>
       </c>
       <c r="H639" t="n">
         <v>229295</v>
@@ -18929,7 +18929,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.71687746047974</v>
+        <v>2.71687722206116</v>
       </c>
       <c r="H640" t="n">
         <v>85746</v>
@@ -18958,7 +18958,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G641" t="n">
-        <v>2.74177050590515</v>
+        <v>2.74177026748657</v>
       </c>
       <c r="H641" t="n">
         <v>183565</v>
@@ -18987,7 +18987,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G642" t="n">
-        <v>2.79155611991882</v>
+        <v>2.79155588150024</v>
       </c>
       <c r="H642" t="n">
         <v>251313</v>
@@ -19045,7 +19045,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>2.91957664489746</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H644" t="n">
         <v>153060</v>
@@ -19132,7 +19132,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.72398996353149</v>
+        <v>2.72398972511292</v>
       </c>
       <c r="H647" t="n">
         <v>181176</v>
@@ -19219,7 +19219,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>2.74888253211975</v>
+        <v>2.74888229370117</v>
       </c>
       <c r="H650" t="n">
         <v>185580</v>
@@ -19335,7 +19335,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G654" t="n">
-        <v>2.66353559494019</v>
+        <v>2.66353583335876</v>
       </c>
       <c r="H654" t="n">
         <v>170243</v>
@@ -19480,7 +19480,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G659" t="n">
-        <v>2.75243830680847</v>
+        <v>2.75243878364563</v>
       </c>
       <c r="H659" t="n">
         <v>65346</v>
@@ -19567,7 +19567,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.66353559494019</v>
+        <v>2.66353583335876</v>
       </c>
       <c r="H662" t="n">
         <v>68534</v>
@@ -19596,7 +19596,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G663" t="n">
-        <v>2.64219856262207</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H663" t="n">
         <v>40573</v>
@@ -19712,7 +19712,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H667" t="n">
         <v>75420</v>
@@ -19770,7 +19770,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H669" t="n">
         <v>23840</v>
@@ -20002,7 +20002,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G677" t="n">
-        <v>2.74532604217529</v>
+        <v>2.74532628059387</v>
       </c>
       <c r="H677" t="n">
         <v>85052</v>
@@ -20031,7 +20031,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>2.64931082725525</v>
+        <v>2.64931130409241</v>
       </c>
       <c r="H678" t="n">
         <v>409416</v>
@@ -20060,7 +20060,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.66353559494019</v>
+        <v>2.66353583335876</v>
       </c>
       <c r="H679" t="n">
         <v>63414</v>
@@ -20089,7 +20089,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G680" t="n">
-        <v>2.64219856262207</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H680" t="n">
         <v>39267</v>
@@ -20118,7 +20118,7 @@
         <v>3.625</v>
       </c>
       <c r="G681" t="n">
-        <v>2.5781888961792</v>
+        <v>2.57818865776062</v>
       </c>
       <c r="H681" t="n">
         <v>50503</v>
@@ -20147,7 +20147,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G682" t="n">
-        <v>2.69198441505432</v>
+        <v>2.6919846534729</v>
       </c>
       <c r="H682" t="n">
         <v>95363</v>
@@ -20176,7 +20176,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H683" t="n">
         <v>25234</v>
@@ -20205,7 +20205,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G684" t="n">
-        <v>2.64931082725525</v>
+        <v>2.64931130409241</v>
       </c>
       <c r="H684" t="n">
         <v>34184</v>
@@ -20234,7 +20234,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H685" t="n">
         <v>54057</v>
@@ -20263,7 +20263,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>2.61019372940063</v>
+        <v>2.61019396781921</v>
       </c>
       <c r="H686" t="n">
         <v>148011</v>
@@ -20292,7 +20292,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>2.68131613731384</v>
+        <v>2.68131589889526</v>
       </c>
       <c r="H687" t="n">
         <v>229731</v>
@@ -20321,7 +20321,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G688" t="n">
-        <v>2.78799986839294</v>
+        <v>2.7880003452301</v>
       </c>
       <c r="H688" t="n">
         <v>284468</v>
@@ -20350,7 +20350,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G689" t="n">
-        <v>2.60308122634888</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H689" t="n">
         <v>365229</v>
@@ -20379,7 +20379,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>2.54973959922791</v>
+        <v>2.54973983764648</v>
       </c>
       <c r="H690" t="n">
         <v>163363</v>
@@ -20466,7 +20466,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G693" t="n">
-        <v>2.72043347358704</v>
+        <v>2.72043371200562</v>
       </c>
       <c r="H693" t="n">
         <v>192286</v>
@@ -20495,7 +20495,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021908760071</v>
       </c>
       <c r="H694" t="n">
         <v>165658</v>
@@ -20553,7 +20553,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>2.74888253211975</v>
+        <v>2.74888229370117</v>
       </c>
       <c r="H696" t="n">
         <v>138064</v>
@@ -20582,7 +20582,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G697" t="n">
-        <v>2.74177050590515</v>
+        <v>2.74177026748657</v>
       </c>
       <c r="H697" t="n">
         <v>62942</v>
@@ -20611,7 +20611,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G698" t="n">
-        <v>2.74888253211975</v>
+        <v>2.74888229370117</v>
       </c>
       <c r="H698" t="n">
         <v>53646</v>
@@ -20640,7 +20640,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H699" t="n">
         <v>45647</v>
@@ -20669,7 +20669,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H700" t="n">
         <v>74718</v>
@@ -20785,7 +20785,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G704" t="n">
-        <v>2.78088760375977</v>
+        <v>2.78088784217834</v>
       </c>
       <c r="H704" t="n">
         <v>85479</v>
@@ -20814,7 +20814,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G705" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H705" t="n">
         <v>80864</v>
@@ -20843,7 +20843,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>2.6990966796875</v>
+        <v>2.69909715652466</v>
       </c>
       <c r="H706" t="n">
         <v>112009</v>
@@ -20901,7 +20901,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730599403381</v>
       </c>
       <c r="H708" t="n">
         <v>94175</v>
@@ -20959,7 +20959,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50350999832153</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H710" t="n">
         <v>188934</v>
@@ -20988,7 +20988,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G711" t="n">
-        <v>2.57107663154602</v>
+        <v>2.57107615470886</v>
       </c>
       <c r="H711" t="n">
         <v>108439</v>
@@ -21075,7 +21075,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G714" t="n">
-        <v>2.52840328216553</v>
+        <v>2.52840304374695</v>
       </c>
       <c r="H714" t="n">
         <v>47336</v>
@@ -21104,7 +21104,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G715" t="n">
-        <v>2.4786171913147</v>
+        <v>2.47861695289612</v>
       </c>
       <c r="H715" t="n">
         <v>52613</v>
@@ -21133,7 +21133,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>2.54973959922791</v>
+        <v>2.54973983764648</v>
       </c>
       <c r="H716" t="n">
         <v>153913</v>
@@ -21249,7 +21249,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>2.60308122634888</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H720" t="n">
         <v>117533</v>
@@ -21278,7 +21278,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730599403381</v>
       </c>
       <c r="H721" t="n">
         <v>64041</v>
@@ -21394,7 +21394,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G725" t="n">
-        <v>2.77021932601929</v>
+        <v>2.77021908760071</v>
       </c>
       <c r="H725" t="n">
         <v>81609</v>
@@ -21423,7 +21423,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>2.81289291381836</v>
+        <v>2.81289267539978</v>
       </c>
       <c r="H726" t="n">
         <v>140477</v>
@@ -21452,7 +21452,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G727" t="n">
-        <v>2.82356119155884</v>
+        <v>2.82356095314026</v>
       </c>
       <c r="H727" t="n">
         <v>169231</v>
@@ -21539,7 +21539,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G730" t="n">
-        <v>2.91957664489746</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H730" t="n">
         <v>108550</v>
@@ -21568,7 +21568,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>2.91957664489746</v>
+        <v>2.91957640647888</v>
       </c>
       <c r="H731" t="n">
         <v>155862</v>
@@ -21626,7 +21626,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>2.83067345619202</v>
+        <v>2.83067321777344</v>
       </c>
       <c r="H733" t="n">
         <v>211140</v>
@@ -21684,7 +21684,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G735" t="n">
-        <v>2.916020154953</v>
+        <v>2.91602039337158</v>
       </c>
       <c r="H735" t="n">
         <v>572778</v>
@@ -21713,7 +21713,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>2.78799986839294</v>
+        <v>2.7880003452301</v>
       </c>
       <c r="H736" t="n">
         <v>563012</v>
@@ -21771,7 +21771,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G738" t="n">
-        <v>2.61374998092651</v>
+        <v>2.61374974250793</v>
       </c>
       <c r="H738" t="n">
         <v>117585</v>
@@ -21800,7 +21800,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G739" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H739" t="n">
         <v>111814</v>
@@ -21829,7 +21829,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G740" t="n">
-        <v>2.59952521324158</v>
+        <v>2.59952545166016</v>
       </c>
       <c r="H740" t="n">
         <v>76380</v>
@@ -21858,7 +21858,7 @@
         <v>3.625</v>
       </c>
       <c r="G741" t="n">
-        <v>2.5781888961792</v>
+        <v>2.57818865776062</v>
       </c>
       <c r="H741" t="n">
         <v>86207</v>
@@ -21916,7 +21916,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G743" t="n">
-        <v>2.70265316963196</v>
+        <v>2.7026526927948</v>
       </c>
       <c r="H743" t="n">
         <v>48168</v>
@@ -21945,7 +21945,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G744" t="n">
-        <v>2.65997958183289</v>
+        <v>2.65997934341431</v>
       </c>
       <c r="H744" t="n">
         <v>59599</v>
@@ -21974,7 +21974,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G745" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H745" t="n">
         <v>44399</v>
@@ -22003,7 +22003,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G746" t="n">
-        <v>2.64219856262207</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H746" t="n">
         <v>56935</v>
@@ -22061,7 +22061,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G748" t="n">
-        <v>2.61730623245239</v>
+        <v>2.61730599403381</v>
       </c>
       <c r="H748" t="n">
         <v>100769</v>
@@ -22090,7 +22090,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G749" t="n">
-        <v>2.64219856262207</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H749" t="n">
         <v>38116</v>
@@ -22148,7 +22148,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H751" t="n">
         <v>21292</v>
@@ -22177,7 +22177,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57107663154602</v>
+        <v>2.57107615470886</v>
       </c>
       <c r="H752" t="n">
         <v>65965</v>
@@ -22235,7 +22235,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.5924129486084</v>
+        <v>2.59241318702698</v>
       </c>
       <c r="H754" t="n">
         <v>126933</v>
@@ -22293,7 +22293,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G756" t="n">
-        <v>2.61374998092651</v>
+        <v>2.61374974250793</v>
       </c>
       <c r="H756" t="n">
         <v>33799</v>
@@ -22322,7 +22322,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>2.60308122634888</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H757" t="n">
         <v>73291</v>
@@ -22380,7 +22380,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>2.61019372940063</v>
+        <v>2.61019396781921</v>
       </c>
       <c r="H759" t="n">
         <v>28732</v>
@@ -22409,7 +22409,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G760" t="n">
-        <v>2.56040787696838</v>
+        <v>2.56040811538696</v>
       </c>
       <c r="H760" t="n">
         <v>41797</v>
@@ -22438,7 +22438,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G761" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H761" t="n">
         <v>45443</v>
@@ -22467,7 +22467,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G762" t="n">
-        <v>2.52484679222107</v>
+        <v>2.52484703063965</v>
       </c>
       <c r="H762" t="n">
         <v>59560</v>
@@ -22525,7 +22525,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G764" t="n">
-        <v>2.62797451019287</v>
+        <v>2.62797427177429</v>
       </c>
       <c r="H764" t="n">
         <v>24743</v>
@@ -22554,7 +22554,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>2.64931082725525</v>
+        <v>2.64931130409241</v>
       </c>
       <c r="H765" t="n">
         <v>23656</v>
@@ -22583,7 +22583,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.62441873550415</v>
+        <v>2.62441849708557</v>
       </c>
       <c r="H766" t="n">
         <v>72814</v>
@@ -22641,7 +22641,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G768" t="n">
-        <v>2.67420411109924</v>
+        <v>2.67420387268066</v>
       </c>
       <c r="H768" t="n">
         <v>56118</v>
@@ -22670,7 +22670,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G769" t="n">
-        <v>2.72043347358704</v>
+        <v>2.72043371200562</v>
       </c>
       <c r="H769" t="n">
         <v>128846</v>
@@ -22757,7 +22757,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G772" t="n">
-        <v>2.73110175132751</v>
+        <v>2.73110198974609</v>
       </c>
       <c r="H772" t="n">
         <v>86625</v>
@@ -22786,7 +22786,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G773" t="n">
-        <v>2.74532604217529</v>
+        <v>2.74532628059387</v>
       </c>
       <c r="H773" t="n">
         <v>45391</v>
@@ -22815,7 +22815,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G774" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H774" t="n">
         <v>66798</v>
@@ -22873,7 +22873,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G776" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H776" t="n">
         <v>65193</v>
@@ -22931,7 +22931,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71687746047974</v>
+        <v>2.71687722206116</v>
       </c>
       <c r="H778" t="n">
         <v>35869</v>
@@ -22960,7 +22960,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G779" t="n">
-        <v>2.64219856262207</v>
+        <v>2.64219880104065</v>
       </c>
       <c r="H779" t="n">
         <v>57180</v>
@@ -23105,7 +23105,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>2.76666307449341</v>
+        <v>2.76666331291199</v>
       </c>
       <c r="H784" t="n">
         <v>47047</v>
@@ -23163,7 +23163,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G786" t="n">
-        <v>2.68131613731384</v>
+        <v>2.68131589889526</v>
       </c>
       <c r="H786" t="n">
         <v>39710</v>
@@ -23250,7 +23250,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G789" t="n">
-        <v>2.67420411109924</v>
+        <v>2.67420387268066</v>
       </c>
       <c r="H789" t="n">
         <v>36914</v>
@@ -23279,7 +23279,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G790" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H790" t="n">
         <v>53946</v>
@@ -23337,7 +23337,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>2.59596920013428</v>
+        <v>2.59596943855286</v>
       </c>
       <c r="H792" t="n">
         <v>42596</v>
@@ -23366,7 +23366,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G793" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H793" t="n">
         <v>165011</v>
@@ -23395,7 +23395,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>2.63153076171875</v>
+        <v>2.63153052330017</v>
       </c>
       <c r="H794" t="n">
         <v>126965</v>
@@ -23424,7 +23424,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G795" t="n">
-        <v>2.52484679222107</v>
+        <v>2.52484703063965</v>
       </c>
       <c r="H795" t="n">
         <v>316700</v>
@@ -23453,7 +23453,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G796" t="n">
-        <v>2.51417851448059</v>
+        <v>2.51417875289917</v>
       </c>
       <c r="H796" t="n">
         <v>160917</v>
@@ -23482,7 +23482,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>2.52129101753235</v>
+        <v>2.52129077911377</v>
       </c>
       <c r="H797" t="n">
         <v>223749</v>
@@ -23511,7 +23511,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G798" t="n">
-        <v>2.49995422363281</v>
+        <v>2.49995398521423</v>
       </c>
       <c r="H798" t="n">
         <v>79031</v>
@@ -23598,7 +23598,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G801" t="n">
-        <v>2.52484679222107</v>
+        <v>2.52484703063965</v>
       </c>
       <c r="H801" t="n">
         <v>57692</v>
@@ -23656,7 +23656,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G803" t="n">
-        <v>2.52840328216553</v>
+        <v>2.52840304374695</v>
       </c>
       <c r="H803" t="n">
         <v>48628</v>
@@ -23743,7 +23743,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>2.50350999832153</v>
+        <v>2.50351023674011</v>
       </c>
       <c r="H806" t="n">
         <v>42553</v>
@@ -23830,7 +23830,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.48572969436646</v>
+        <v>2.48572945594788</v>
       </c>
       <c r="H809" t="n">
         <v>86790</v>
@@ -23888,7 +23888,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>2.3719334602356</v>
+        <v>2.37193393707275</v>
       </c>
       <c r="H811" t="n">
         <v>148443</v>
@@ -23917,7 +23917,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>2.37548971176147</v>
+        <v>2.3754894733429</v>
       </c>
       <c r="H812" t="n">
         <v>91593</v>
@@ -23946,7 +23946,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G813" t="n">
-        <v>2.37548971176147</v>
+        <v>2.3754894733429</v>
       </c>
       <c r="H813" t="n">
         <v>67492</v>
@@ -23975,7 +23975,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G814" t="n">
-        <v>2.34704041481018</v>
+        <v>2.34704065322876</v>
       </c>
       <c r="H814" t="n">
         <v>64507</v>
@@ -24062,7 +24062,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G817" t="n">
-        <v>2.27236223220825</v>
+        <v>2.27236199378967</v>
       </c>
       <c r="H817" t="n">
         <v>146028</v>
@@ -24207,7 +24207,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G822" t="n">
-        <v>2.28658652305603</v>
+        <v>2.28658676147461</v>
       </c>
       <c r="H822" t="n">
         <v>108669</v>
@@ -24236,7 +24236,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>2.27236223220825</v>
+        <v>2.27236199378967</v>
       </c>
       <c r="H823" t="n">
         <v>63237</v>
@@ -24294,7 +24294,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>2.26880598068237</v>
+        <v>2.26880621910095</v>
       </c>
       <c r="H825" t="n">
         <v>70107</v>
@@ -24323,7 +24323,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G826" t="n">
-        <v>2.29014301300049</v>
+        <v>2.29014277458191</v>
       </c>
       <c r="H826" t="n">
         <v>59872</v>
@@ -24352,7 +24352,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G827" t="n">
-        <v>2.29014301300049</v>
+        <v>2.29014277458191</v>
       </c>
       <c r="H827" t="n">
         <v>88835</v>
@@ -24410,7 +24410,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>2.35415291786194</v>
+        <v>2.35415267944336</v>
       </c>
       <c r="H829" t="n">
         <v>234469</v>
@@ -24439,7 +24439,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>2.3719334602356</v>
+        <v>2.37193393707275</v>
       </c>
       <c r="H830" t="n">
         <v>200129</v>
@@ -24468,7 +24468,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G831" t="n">
-        <v>2.35770893096924</v>
+        <v>2.3577094078064</v>
       </c>
       <c r="H831" t="n">
         <v>178502</v>
@@ -24497,7 +24497,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G832" t="n">
-        <v>2.36837768554688</v>
+        <v>2.3683774471283</v>
       </c>
       <c r="H832" t="n">
         <v>96015</v>
@@ -24555,7 +24555,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G834" t="n">
-        <v>2.30081081390381</v>
+        <v>2.30081105232239</v>
       </c>
       <c r="H834" t="n">
         <v>103372</v>
@@ -24613,7 +24613,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G836" t="n">
-        <v>2.28658652305603</v>
+        <v>2.28658676147461</v>
       </c>
       <c r="H836" t="n">
         <v>63039</v>
@@ -24642,7 +24642,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G837" t="n">
-        <v>2.3612654209137</v>
+        <v>2.36126518249512</v>
       </c>
       <c r="H837" t="n">
         <v>143505</v>
@@ -24671,7 +24671,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G838" t="n">
-        <v>2.37548971176147</v>
+        <v>2.3754894733429</v>
       </c>
       <c r="H838" t="n">
         <v>153463</v>
@@ -24700,7 +24700,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G839" t="n">
-        <v>2.41105103492737</v>
+        <v>2.41105079650879</v>
       </c>
       <c r="H839" t="n">
         <v>166284</v>
@@ -24729,7 +24729,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44305562973022</v>
+        <v>2.4430558681488</v>
       </c>
       <c r="H840" t="n">
         <v>95367</v>
@@ -24758,7 +24758,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>2.52129101753235</v>
+        <v>2.52129077911377</v>
       </c>
       <c r="H841" t="n">
         <v>189397</v>
@@ -24787,7 +24787,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G842" t="n">
-        <v>2.52484679222107</v>
+        <v>2.52484703063965</v>
       </c>
       <c r="H842" t="n">
         <v>158485</v>
@@ -24845,7 +24845,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G844" t="n">
-        <v>2.53907132148743</v>
+        <v>2.53907108306885</v>
       </c>
       <c r="H844" t="n">
         <v>120928</v>
@@ -24932,7 +24932,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G847" t="n">
-        <v>2.60308122634888</v>
+        <v>2.60308146476746</v>
       </c>
       <c r="H847" t="n">
         <v>177657</v>
@@ -24961,7 +24961,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G848" t="n">
-        <v>2.4786171913147</v>
+        <v>2.47861695289612</v>
       </c>
       <c r="H848" t="n">
         <v>218311</v>
@@ -24990,7 +24990,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42883157730103</v>
+        <v>2.42883133888245</v>
       </c>
       <c r="H849" t="n">
         <v>74414</v>
@@ -25048,7 +25048,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G851" t="n">
-        <v>2.44305562973022</v>
+        <v>2.4430558681488</v>
       </c>
       <c r="H851" t="n">
         <v>61053</v>
@@ -25077,7 +25077,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G852" t="n">
-        <v>2.35415291786194</v>
+        <v>2.35415267944336</v>
       </c>
       <c r="H852" t="n">
         <v>91389</v>
@@ -25106,7 +25106,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.3612654209137</v>
+        <v>2.36126518249512</v>
       </c>
       <c r="H853" t="n">
         <v>119893</v>
@@ -25193,7 +25193,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G856" t="n">
-        <v>2.42057490348816</v>
+        <v>2.42057514190674</v>
       </c>
       <c r="H856" t="n">
         <v>67266</v>
@@ -25222,7 +25222,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G857" t="n">
-        <v>2.47617769241333</v>
+        <v>2.47617745399475</v>
       </c>
       <c r="H857" t="n">
         <v>233867</v>
@@ -25280,7 +25280,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G859" t="n">
-        <v>2.39092016220093</v>
+        <v>2.39091992378235</v>
       </c>
       <c r="H859" t="n">
         <v>61436</v>
@@ -25396,7 +25396,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G863" t="n">
-        <v>2.23893928527832</v>
+        <v>2.23893904685974</v>
       </c>
       <c r="H863" t="n">
         <v>135055</v>
@@ -25425,7 +25425,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>2.23893928527832</v>
+        <v>2.23893904685974</v>
       </c>
       <c r="H864" t="n">
         <v>25269</v>
@@ -25541,7 +25541,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G868" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H868" t="n">
         <v>221958</v>
@@ -25570,7 +25570,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>2.09437155723572</v>
+        <v>2.09437203407288</v>
       </c>
       <c r="H869" t="n">
         <v>106032</v>
@@ -25599,7 +25599,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G870" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H870" t="n">
         <v>174290</v>
@@ -25628,7 +25628,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G871" t="n">
-        <v>2.09437155723572</v>
+        <v>2.09437203407288</v>
       </c>
       <c r="H871" t="n">
         <v>47525</v>
@@ -25657,7 +25657,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05359625816345</v>
+        <v>2.05359649658203</v>
       </c>
       <c r="H872" t="n">
         <v>132549</v>
@@ -25744,7 +25744,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G875" t="n">
-        <v>2.08325147628784</v>
+        <v>2.08325123786926</v>
       </c>
       <c r="H875" t="n">
         <v>54340</v>
@@ -25773,7 +25773,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>2.12031960487366</v>
+        <v>2.12032008171082</v>
       </c>
       <c r="H876" t="n">
         <v>101590</v>
@@ -25831,7 +25831,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>2.09437155723572</v>
+        <v>2.09437203407288</v>
       </c>
       <c r="H878" t="n">
         <v>212088</v>
@@ -25860,7 +25860,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G879" t="n">
-        <v>2.06101012229919</v>
+        <v>2.06100988388062</v>
       </c>
       <c r="H879" t="n">
         <v>148826</v>
@@ -25918,7 +25918,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G881" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H881" t="n">
         <v>95881</v>
@@ -25947,7 +25947,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G882" t="n">
-        <v>2.11661291122437</v>
+        <v>2.11661314964294</v>
       </c>
       <c r="H882" t="n">
         <v>130719</v>
@@ -25976,7 +25976,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G883" t="n">
-        <v>2.1091992855072</v>
+        <v>2.10919904708862</v>
       </c>
       <c r="H883" t="n">
         <v>127362</v>
@@ -26005,7 +26005,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G884" t="n">
-        <v>2.03135538101196</v>
+        <v>2.03135514259338</v>
       </c>
       <c r="H884" t="n">
         <v>170336</v>
@@ -26034,7 +26034,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G885" t="n">
-        <v>1.99799370765686</v>
+        <v>1.99799346923828</v>
       </c>
       <c r="H885" t="n">
         <v>136424</v>
@@ -26121,7 +26121,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>2.3760929107666</v>
+        <v>2.37609243392944</v>
       </c>
       <c r="H888" t="n">
         <v>1054436</v>
@@ -26179,7 +26179,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.28342127799988</v>
+        <v>2.28342151641846</v>
       </c>
       <c r="H890" t="n">
         <v>233336</v>
@@ -26208,7 +26208,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>2.23893928527832</v>
+        <v>2.23893904685974</v>
       </c>
       <c r="H891" t="n">
         <v>286863</v>
@@ -26237,7 +26237,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G892" t="n">
-        <v>2.25376629829407</v>
+        <v>2.25376653671265</v>
       </c>
       <c r="H892" t="n">
         <v>141181</v>
@@ -26324,7 +26324,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G895" t="n">
-        <v>2.23893928527832</v>
+        <v>2.23893904685974</v>
       </c>
       <c r="H895" t="n">
         <v>70675</v>
@@ -26411,7 +26411,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G898" t="n">
-        <v>2.27230072021484</v>
+        <v>2.27230048179626</v>
       </c>
       <c r="H898" t="n">
         <v>60128</v>
@@ -26469,7 +26469,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.30566215515137</v>
+        <v>2.30566263198853</v>
       </c>
       <c r="H900" t="n">
         <v>66468</v>
@@ -26498,7 +26498,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G901" t="n">
-        <v>2.28342127799988</v>
+        <v>2.28342151641846</v>
       </c>
       <c r="H901" t="n">
         <v>85699</v>
@@ -26701,7 +26701,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>2.28342127799988</v>
+        <v>2.28342151641846</v>
       </c>
       <c r="H908" t="n">
         <v>180734</v>
@@ -26730,7 +26730,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>2.26859354972839</v>
+        <v>2.26859378814697</v>
       </c>
       <c r="H909" t="n">
         <v>88883</v>
@@ -26759,7 +26759,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G910" t="n">
-        <v>2.23523235321045</v>
+        <v>2.23523259162903</v>
       </c>
       <c r="H910" t="n">
         <v>166947</v>
@@ -26788,7 +26788,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G911" t="n">
-        <v>2.2500593662262</v>
+        <v>2.25005960464478</v>
       </c>
       <c r="H911" t="n">
         <v>43162</v>
@@ -26904,7 +26904,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G915" t="n">
-        <v>2.17962956428528</v>
+        <v>2.1796293258667</v>
       </c>
       <c r="H915" t="n">
         <v>152880</v>
@@ -26933,7 +26933,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G916" t="n">
-        <v>2.17962956428528</v>
+        <v>2.1796293258667</v>
       </c>
       <c r="H916" t="n">
         <v>124102</v>
@@ -26962,7 +26962,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G917" t="n">
-        <v>2.18333625793457</v>
+        <v>2.18333601951599</v>
       </c>
       <c r="H917" t="n">
         <v>84961</v>
@@ -27078,7 +27078,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G921" t="n">
-        <v>2.15368127822876</v>
+        <v>2.15368151664734</v>
       </c>
       <c r="H921" t="n">
         <v>83002</v>
@@ -27165,7 +27165,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>2.12402653694153</v>
+        <v>2.12402677536011</v>
       </c>
       <c r="H924" t="n">
         <v>71584</v>
@@ -27194,7 +27194,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G925" t="n">
-        <v>2.12031960487366</v>
+        <v>2.12032008171082</v>
       </c>
       <c r="H925" t="n">
         <v>112906</v>
@@ -27223,7 +27223,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G926" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H926" t="n">
         <v>48449</v>
@@ -27252,7 +27252,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G927" t="n">
-        <v>2.1091992855072</v>
+        <v>2.10919904708862</v>
       </c>
       <c r="H927" t="n">
         <v>127215</v>
@@ -27368,7 +27368,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>2.1981635093689</v>
+        <v>2.19816374778748</v>
       </c>
       <c r="H931" t="n">
         <v>48763</v>
@@ -27397,7 +27397,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G932" t="n">
-        <v>2.1981635093689</v>
+        <v>2.19816374778748</v>
       </c>
       <c r="H932" t="n">
         <v>51651</v>
@@ -27426,7 +27426,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>2.14997458457947</v>
+        <v>2.14997482299805</v>
       </c>
       <c r="H933" t="n">
         <v>83565</v>
@@ -27455,7 +27455,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>2.16850852966309</v>
+        <v>2.16850876808167</v>
       </c>
       <c r="H934" t="n">
         <v>79342</v>
@@ -27513,7 +27513,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>2.25376629829407</v>
+        <v>2.25376653671265</v>
       </c>
       <c r="H936" t="n">
         <v>53078</v>
@@ -27542,7 +27542,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G937" t="n">
-        <v>2.2982485294342</v>
+        <v>2.29824829101562</v>
       </c>
       <c r="H937" t="n">
         <v>121304</v>
@@ -27600,7 +27600,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G939" t="n">
-        <v>2.52807354927063</v>
+        <v>2.52807331085205</v>
       </c>
       <c r="H939" t="n">
         <v>638409</v>
@@ -27658,7 +27658,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G941" t="n">
-        <v>2.63927912712097</v>
+        <v>2.63927888870239</v>
       </c>
       <c r="H941" t="n">
         <v>881119</v>
@@ -27687,7 +27687,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G942" t="n">
-        <v>2.79126024246216</v>
+        <v>2.79126000404358</v>
       </c>
       <c r="H942" t="n">
         <v>486765</v>
@@ -27774,7 +27774,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G945" t="n">
-        <v>2.75789833068848</v>
+        <v>2.75789856910706</v>
       </c>
       <c r="H945" t="n">
         <v>174113</v>
@@ -27803,7 +27803,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G946" t="n">
-        <v>2.75789833068848</v>
+        <v>2.75789856910706</v>
       </c>
       <c r="H946" t="n">
         <v>251163</v>
@@ -27832,7 +27832,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G947" t="n">
-        <v>2.75789833068848</v>
+        <v>2.75789856910706</v>
       </c>
       <c r="H947" t="n">
         <v>162510</v>
@@ -27861,7 +27861,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G948" t="n">
-        <v>2.74307107925415</v>
+        <v>2.74307084083557</v>
       </c>
       <c r="H948" t="n">
         <v>138242</v>
@@ -27890,7 +27890,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G949" t="n">
-        <v>2.73565769195557</v>
+        <v>2.73565745353699</v>
       </c>
       <c r="H949" t="n">
         <v>92966</v>
@@ -27919,7 +27919,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G950" t="n">
-        <v>2.73565769195557</v>
+        <v>2.73565745353699</v>
       </c>
       <c r="H950" t="n">
         <v>94593</v>
@@ -27948,7 +27948,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G951" t="n">
-        <v>2.74307107925415</v>
+        <v>2.74307084083557</v>
       </c>
       <c r="H951" t="n">
         <v>95891</v>
@@ -27977,7 +27977,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G952" t="n">
-        <v>2.75789833068848</v>
+        <v>2.75789856910706</v>
       </c>
       <c r="H952" t="n">
         <v>75069</v>
@@ -28006,7 +28006,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>2.73565769195557</v>
+        <v>2.73565745353699</v>
       </c>
       <c r="H953" t="n">
         <v>100795</v>
@@ -28035,7 +28035,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G954" t="n">
-        <v>2.70600247383118</v>
+        <v>2.70600271224976</v>
       </c>
       <c r="H954" t="n">
         <v>111884</v>
@@ -28064,7 +28064,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G955" t="n">
-        <v>2.67264103889465</v>
+        <v>2.67264080047607</v>
       </c>
       <c r="H955" t="n">
         <v>162705</v>
@@ -28093,7 +28093,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G956" t="n">
-        <v>2.68376159667969</v>
+        <v>2.68376135826111</v>
       </c>
       <c r="H956" t="n">
         <v>86012</v>
@@ -28122,7 +28122,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G957" t="n">
-        <v>2.69858884811401</v>
+        <v>2.69858908653259</v>
       </c>
       <c r="H957" t="n">
         <v>64578</v>
@@ -28180,7 +28180,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>2.71712303161621</v>
+        <v>2.71712327003479</v>
       </c>
       <c r="H959" t="n">
         <v>67572</v>
@@ -28209,7 +28209,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G960" t="n">
-        <v>2.75789833068848</v>
+        <v>2.75789856910706</v>
       </c>
       <c r="H960" t="n">
         <v>33375</v>
@@ -28238,7 +28238,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G961" t="n">
-        <v>2.76160502433777</v>
+        <v>2.76160526275635</v>
       </c>
       <c r="H961" t="n">
         <v>97307</v>
@@ -28354,7 +28354,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G965" t="n">
-        <v>2.75789833068848</v>
+        <v>2.75789856910706</v>
       </c>
       <c r="H965" t="n">
         <v>122286</v>
@@ -28412,7 +28412,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G967" t="n">
-        <v>2.72453665733337</v>
+        <v>2.72453689575195</v>
       </c>
       <c r="H967" t="n">
         <v>92773</v>
@@ -28499,7 +28499,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G970" t="n">
-        <v>2.6689338684082</v>
+        <v>2.66893410682678</v>
       </c>
       <c r="H970" t="n">
         <v>41494</v>
@@ -28615,7 +28615,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G974" t="n">
-        <v>2.85427641868591</v>
+        <v>2.85427665710449</v>
       </c>
       <c r="H974" t="n">
         <v>200919</v>
@@ -28673,7 +28673,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G976" t="n">
-        <v>2.76160502433777</v>
+        <v>2.76160526275635</v>
       </c>
       <c r="H976" t="n">
         <v>184807</v>
@@ -28731,7 +28731,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G978" t="n">
-        <v>2.86169004440308</v>
+        <v>2.86169028282166</v>
       </c>
       <c r="H978" t="n">
         <v>118454</v>
@@ -28789,7 +28789,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G980" t="n">
-        <v>2.90987944602966</v>
+        <v>2.90987968444824</v>
       </c>
       <c r="H980" t="n">
         <v>729798</v>
@@ -28818,7 +28818,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>2.94694781303406</v>
+        <v>2.94694805145264</v>
       </c>
       <c r="H981" t="n">
         <v>159745</v>
@@ -28876,7 +28876,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G983" t="n">
-        <v>2.95806837081909</v>
+        <v>2.95806860923767</v>
       </c>
       <c r="H983" t="n">
         <v>147298</v>
@@ -28905,7 +28905,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G984" t="n">
-        <v>3.05444645881653</v>
+        <v>3.05444669723511</v>
       </c>
       <c r="H984" t="n">
         <v>335251</v>
@@ -29021,7 +29021,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G988" t="n">
-        <v>2.80608725547791</v>
+        <v>2.80608749389648</v>
       </c>
       <c r="H988" t="n">
         <v>129247</v>
@@ -29137,7 +29137,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G992" t="n">
-        <v>3.23608255386353</v>
+        <v>3.23608231544495</v>
       </c>
       <c r="H992" t="n">
         <v>1152288</v>
@@ -29166,7 +29166,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>3.22496175765991</v>
+        <v>3.22496199607849</v>
       </c>
       <c r="H993" t="n">
         <v>309322</v>
@@ -29224,7 +29224,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>3.3954770565033</v>
+        <v>3.39547657966614</v>
       </c>
       <c r="H995" t="n">
         <v>642201</v>
@@ -29427,7 +29427,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.68461179733276</v>
+        <v>3.68461155891418</v>
       </c>
       <c r="H1002" t="n">
         <v>738133</v>
@@ -29514,7 +29514,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1005" t="n">
         <v>332417</v>
@@ -29543,7 +29543,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1006" t="n">
         <v>349628</v>
@@ -29572,7 +29572,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.76616263389587</v>
+        <v>3.76616215705872</v>
       </c>
       <c r="H1007" t="n">
         <v>463372</v>
@@ -29601,7 +29601,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.81805825233459</v>
+        <v>3.81805849075317</v>
       </c>
       <c r="H1008" t="n">
         <v>172882</v>
@@ -29630,7 +29630,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.80323052406311</v>
+        <v>3.80323100090027</v>
       </c>
       <c r="H1009" t="n">
         <v>201805</v>
@@ -29659,7 +29659,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.81805825233459</v>
+        <v>3.81805849075317</v>
       </c>
       <c r="H1010" t="n">
         <v>141592</v>
@@ -29688,7 +29688,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1011" t="n">
         <v>151303</v>
@@ -29717,7 +29717,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.76616263389587</v>
+        <v>3.76616215705872</v>
       </c>
       <c r="H1012" t="n">
         <v>191213</v>
@@ -29746,7 +29746,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.81064486503601</v>
+        <v>3.81064462661743</v>
       </c>
       <c r="H1013" t="n">
         <v>243495</v>
@@ -29775,7 +29775,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1014" t="n">
         <v>102689</v>
@@ -29804,7 +29804,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.84029936790466</v>
+        <v>3.84029912948608</v>
       </c>
       <c r="H1015" t="n">
         <v>295814</v>
@@ -29833,7 +29833,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.91443657875061</v>
+        <v>3.91443705558777</v>
       </c>
       <c r="H1016" t="n">
         <v>346021</v>
@@ -29862,7 +29862,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.95891904830933</v>
+        <v>3.95891928672791</v>
       </c>
       <c r="H1017" t="n">
         <v>495513</v>
@@ -29920,7 +29920,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.91443657875061</v>
+        <v>3.91443705558777</v>
       </c>
       <c r="H1019" t="n">
         <v>370109</v>
@@ -29949,7 +29949,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.94409155845642</v>
+        <v>3.94409132003784</v>
       </c>
       <c r="H1020" t="n">
         <v>587792</v>
@@ -30007,7 +30007,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.85512685775757</v>
+        <v>3.85512661933899</v>
       </c>
       <c r="H1022" t="n">
         <v>233331</v>
@@ -30065,7 +30065,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.86995482444763</v>
+        <v>3.86995434761047</v>
       </c>
       <c r="H1024" t="n">
         <v>264811</v>
@@ -30123,7 +30123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.85512685775757</v>
+        <v>3.85512661933899</v>
       </c>
       <c r="H1026" t="n">
         <v>83051</v>
@@ -30152,7 +30152,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.84771323204041</v>
+        <v>3.84771251678467</v>
       </c>
       <c r="H1027" t="n">
         <v>72510</v>
@@ -30181,7 +30181,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.81805825233459</v>
+        <v>3.81805849075317</v>
       </c>
       <c r="H1028" t="n">
         <v>102175</v>
@@ -30210,7 +30210,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.81064486503601</v>
+        <v>3.81064462661743</v>
       </c>
       <c r="H1029" t="n">
         <v>213214</v>
@@ -30239,7 +30239,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.85512685775757</v>
+        <v>3.85512661933899</v>
       </c>
       <c r="H1030" t="n">
         <v>156105</v>
@@ -30268,7 +30268,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.78840351104736</v>
+        <v>3.78840398788452</v>
       </c>
       <c r="H1031" t="n">
         <v>116338</v>
@@ -30297,7 +30297,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.83288621902466</v>
+        <v>3.83288598060608</v>
       </c>
       <c r="H1032" t="n">
         <v>299811</v>
@@ -30326,7 +30326,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1033" t="n">
         <v>281130</v>
@@ -30355,7 +30355,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.81805825233459</v>
+        <v>3.81805849075317</v>
       </c>
       <c r="H1034" t="n">
         <v>149802</v>
@@ -30384,7 +30384,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.76616263389587</v>
+        <v>3.76616215705872</v>
       </c>
       <c r="H1035" t="n">
         <v>209216</v>
@@ -30442,7 +30442,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.47332096099854</v>
+        <v>3.47332048416138</v>
       </c>
       <c r="H1037" t="n">
         <v>353099</v>
@@ -30500,7 +30500,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.78098940849304</v>
+        <v>3.7809898853302</v>
       </c>
       <c r="H1039" t="n">
         <v>191733</v>
@@ -30529,7 +30529,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.7290940284729</v>
+        <v>3.72909450531006</v>
       </c>
       <c r="H1040" t="n">
         <v>366585</v>
@@ -30558,7 +30558,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.76616263389587</v>
+        <v>3.76616215705872</v>
       </c>
       <c r="H1041" t="n">
         <v>81094</v>
@@ -30616,7 +30616,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.67719793319702</v>
+        <v>3.6771981716156</v>
       </c>
       <c r="H1043" t="n">
         <v>66231</v>
@@ -30645,7 +30645,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.78098940849304</v>
+        <v>3.7809898853302</v>
       </c>
       <c r="H1044" t="n">
         <v>103859</v>
@@ -30674,7 +30674,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.77357625961304</v>
+        <v>3.77357649803162</v>
       </c>
       <c r="H1045" t="n">
         <v>100770</v>
@@ -30703,7 +30703,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.83288621902466</v>
+        <v>3.83288598060608</v>
       </c>
       <c r="H1046" t="n">
         <v>155005</v>
@@ -30790,7 +30790,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.12202024459839</v>
+        <v>4.12201976776123</v>
       </c>
       <c r="H1049" t="n">
         <v>268142</v>
@@ -30819,7 +30819,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.04788303375244</v>
+        <v>4.0478835105896</v>
       </c>
       <c r="H1050" t="n">
         <v>270277</v>
@@ -30848,7 +30848,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.06271076202393</v>
+        <v>4.06271028518677</v>
       </c>
       <c r="H1051" t="n">
         <v>169274</v>
@@ -30906,7 +30906,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1053" t="n">
         <v>746712</v>
@@ -30935,7 +30935,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.80323052406311</v>
+        <v>3.80323100090027</v>
       </c>
       <c r="H1054" t="n">
         <v>424779</v>
@@ -30964,7 +30964,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.78840351104736</v>
+        <v>3.78840398788452</v>
       </c>
       <c r="H1055" t="n">
         <v>373798</v>
@@ -31080,7 +31080,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.66607785224915</v>
+        <v>3.66607737541199</v>
       </c>
       <c r="H1059" t="n">
         <v>331600</v>
@@ -31167,7 +31167,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.55857825279236</v>
+        <v>3.55857872962952</v>
       </c>
       <c r="H1062" t="n">
         <v>398454</v>
@@ -31196,7 +31196,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.16565179824829</v>
+        <v>3.16565203666687</v>
       </c>
       <c r="H1063" t="n">
         <v>429417</v>
@@ -31225,7 +31225,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.09522223472595</v>
+        <v>3.09522247314453</v>
       </c>
       <c r="H1064" t="n">
         <v>371613</v>
@@ -31370,7 +31370,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.29083490371704</v>
+        <v>2.29083466529846</v>
       </c>
       <c r="H1069" t="n">
         <v>496099</v>
@@ -31457,7 +31457,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.17962956428528</v>
+        <v>2.1796293258667</v>
       </c>
       <c r="H1072" t="n">
         <v>350348</v>
@@ -31631,7 +31631,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.30195546150208</v>
+        <v>2.30195569992065</v>
       </c>
       <c r="H1078" t="n">
         <v>169458</v>
@@ -31660,7 +31660,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.38721346855164</v>
+        <v>2.38721323013306</v>
       </c>
       <c r="H1079" t="n">
         <v>228291</v>
@@ -31689,7 +31689,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.28342127799988</v>
+        <v>2.28342151641846</v>
       </c>
       <c r="H1080" t="n">
         <v>79106</v>
@@ -31747,7 +31747,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.2982485294342</v>
+        <v>2.29824829101562</v>
       </c>
       <c r="H1082" t="n">
         <v>115709</v>
@@ -31805,7 +31805,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.53548765182495</v>
+        <v>2.53548741340637</v>
       </c>
       <c r="H1084" t="n">
         <v>286119</v>
@@ -31834,7 +31834,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.62815880775452</v>
+        <v>2.62815856933594</v>
       </c>
       <c r="H1085" t="n">
         <v>155985</v>
@@ -31863,7 +31863,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.67264103889465</v>
+        <v>2.67264080047607</v>
       </c>
       <c r="H1086" t="n">
         <v>186894</v>
@@ -31892,7 +31892,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.6689338684082</v>
+        <v>2.66893410682678</v>
       </c>
       <c r="H1087" t="n">
         <v>146976</v>
@@ -31979,7 +31979,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.67264103889465</v>
+        <v>2.67264080047607</v>
       </c>
       <c r="H1090" t="n">
         <v>573804</v>
@@ -32008,7 +32008,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.87651777267456</v>
+        <v>2.87651753425598</v>
       </c>
       <c r="H1091" t="n">
         <v>353324</v>
@@ -32095,7 +32095,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.01737809181213</v>
+        <v>3.01737833023071</v>
       </c>
       <c r="H1094" t="n">
         <v>245764</v>
@@ -32153,7 +32153,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.17306613922119</v>
+        <v>3.17306637763977</v>
       </c>
       <c r="H1096" t="n">
         <v>403206</v>
@@ -32269,7 +32269,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.07668805122375</v>
+        <v>3.07668781280518</v>
       </c>
       <c r="H1100" t="n">
         <v>96382</v>
@@ -32298,7 +32298,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.11004948616028</v>
+        <v>3.11004972457886</v>
       </c>
       <c r="H1101" t="n">
         <v>167235</v>
@@ -32385,7 +32385,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.11004948616028</v>
+        <v>3.11004972457886</v>
       </c>
       <c r="H1104" t="n">
         <v>193043</v>
@@ -32530,7 +32530,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.87651777267456</v>
+        <v>2.87651753425598</v>
       </c>
       <c r="H1109" t="n">
         <v>173640</v>
@@ -32704,7 +32704,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.16194534301758</v>
+        <v>3.161945104599</v>
       </c>
       <c r="H1115" t="n">
         <v>341544</v>
@@ -32733,7 +32733,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.15823864936829</v>
+        <v>3.15823888778687</v>
       </c>
       <c r="H1116" t="n">
         <v>314681</v>
@@ -32762,7 +32762,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.18047952651978</v>
+        <v>3.18047976493835</v>
       </c>
       <c r="H1117" t="n">
         <v>401340</v>
@@ -32849,7 +32849,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.2916853427887</v>
+        <v>3.29168510437012</v>
       </c>
       <c r="H1120" t="n">
         <v>119756</v>
@@ -32878,7 +32878,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.20642733573914</v>
+        <v>3.20642757415771</v>
       </c>
       <c r="H1121" t="n">
         <v>523519</v>
@@ -32907,7 +32907,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.28056478500366</v>
+        <v>3.28056502342224</v>
       </c>
       <c r="H1122" t="n">
         <v>86046</v>
@@ -32936,7 +32936,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.22496175765991</v>
+        <v>3.22496199607849</v>
       </c>
       <c r="H1123" t="n">
         <v>114302</v>
@@ -32965,7 +32965,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.18047952651978</v>
+        <v>3.18047976493835</v>
       </c>
       <c r="H1124" t="n">
         <v>309808</v>
@@ -33023,7 +33023,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.10634279251099</v>
+        <v>3.10634255409241</v>
       </c>
       <c r="H1126" t="n">
         <v>157535</v>
@@ -33110,7 +33110,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.77643251419067</v>
+        <v>2.77643275260925</v>
       </c>
       <c r="H1129" t="n">
         <v>482471</v>
@@ -33168,7 +33168,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.83944940567017</v>
+        <v>2.83944916725159</v>
       </c>
       <c r="H1131" t="n">
         <v>207485</v>
@@ -33197,7 +33197,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.77643251419067</v>
+        <v>2.77643275260925</v>
       </c>
       <c r="H1132" t="n">
         <v>136838</v>
@@ -33226,7 +33226,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.79126024246216</v>
+        <v>2.79126000404358</v>
       </c>
       <c r="H1133" t="n">
         <v>110451</v>
@@ -33284,7 +33284,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.05444645881653</v>
+        <v>3.05444669723511</v>
       </c>
       <c r="H1135" t="n">
         <v>906769</v>
@@ -33342,7 +33342,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.82832884788513</v>
+        <v>2.82832860946655</v>
       </c>
       <c r="H1137" t="n">
         <v>101226</v>
@@ -33400,7 +33400,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.75419139862061</v>
+        <v>2.75419163703918</v>
       </c>
       <c r="H1139" t="n">
         <v>261862</v>
@@ -33545,7 +33545,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.83944940567017</v>
+        <v>2.83944916725159</v>
       </c>
       <c r="H1144" t="n">
         <v>60861</v>
@@ -33690,7 +33690,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.96918916702271</v>
+        <v>2.96918892860413</v>
       </c>
       <c r="H1149" t="n">
         <v>122881</v>
@@ -33719,7 +33719,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.05444645881653</v>
+        <v>3.05444669723511</v>
       </c>
       <c r="H1150" t="n">
         <v>85124</v>
@@ -33748,7 +33748,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.02108454704285</v>
+        <v>3.02108478546143</v>
       </c>
       <c r="H1151" t="n">
         <v>257205</v>
@@ -33777,7 +33777,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.08780837059021</v>
+        <v>3.08780813217163</v>
       </c>
       <c r="H1152" t="n">
         <v>145042</v>
@@ -33806,7 +33806,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.11004948616028</v>
+        <v>3.11004972457886</v>
       </c>
       <c r="H1153" t="n">
         <v>260642</v>
@@ -33835,7 +33835,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.11004948616028</v>
+        <v>3.11004972457886</v>
       </c>
       <c r="H1154" t="n">
         <v>78988</v>
@@ -33922,7 +33922,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.08780837059021</v>
+        <v>3.08780813217163</v>
       </c>
       <c r="H1157" t="n">
         <v>89877</v>
@@ -33951,7 +33951,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.13229036331177</v>
+        <v>3.13229060173035</v>
       </c>
       <c r="H1158" t="n">
         <v>83303</v>
@@ -33980,7 +33980,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.06556725502014</v>
+        <v>3.0655677318573</v>
       </c>
       <c r="H1159" t="n">
         <v>97598</v>
@@ -34038,7 +34038,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.09892892837524</v>
+        <v>3.09892868995667</v>
       </c>
       <c r="H1161" t="n">
         <v>214220</v>
@@ -34096,7 +34096,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.09151530265808</v>
+        <v>3.09151554107666</v>
       </c>
       <c r="H1163" t="n">
         <v>187881</v>
@@ -34125,7 +34125,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.10634279251099</v>
+        <v>3.10634255409241</v>
       </c>
       <c r="H1164" t="n">
         <v>90903</v>
@@ -34241,7 +34241,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.19160056114197</v>
+        <v>3.19160008430481</v>
       </c>
       <c r="H1168" t="n">
         <v>55140</v>
@@ -34299,7 +34299,7 @@
         <v>4.375</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.24349641799927</v>
+        <v>3.24349594116211</v>
       </c>
       <c r="H1170" t="n">
         <v>72591</v>
@@ -34386,7 +34386,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.37323617935181</v>
+        <v>3.37323594093323</v>
       </c>
       <c r="H1173" t="n">
         <v>32881</v>
@@ -34415,7 +34415,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.55857825279236</v>
+        <v>3.55857872962952</v>
       </c>
       <c r="H1174" t="n">
         <v>195254</v>
@@ -34473,7 +34473,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.56969904899597</v>
+        <v>3.56969928741455</v>
       </c>
       <c r="H1176" t="n">
         <v>136880</v>
@@ -34589,7 +34589,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.70314574241638</v>
+        <v>3.70314526557922</v>
       </c>
       <c r="H1180" t="n">
         <v>607643</v>
@@ -34618,7 +34618,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.67719793319702</v>
+        <v>3.6771981716156</v>
       </c>
       <c r="H1181" t="n">
         <v>296317</v>
@@ -34647,7 +34647,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.98115992546082</v>
+        <v>3.98115968704224</v>
       </c>
       <c r="H1182" t="n">
         <v>423717</v>
@@ -34676,7 +34676,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.91443657875061</v>
+        <v>3.91443705558777</v>
       </c>
       <c r="H1183" t="n">
         <v>304675</v>
@@ -34705,7 +34705,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.91443657875061</v>
+        <v>3.91443705558777</v>
       </c>
       <c r="H1184" t="n">
         <v>207842</v>
@@ -34734,7 +34734,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.86995482444763</v>
+        <v>3.86995434761047</v>
       </c>
       <c r="H1185" t="n">
         <v>246353</v>
@@ -34821,7 +34821,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.84771323204041</v>
+        <v>3.84771251678467</v>
       </c>
       <c r="H1188" t="n">
         <v>228820</v>
@@ -34850,7 +34850,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.79581737518311</v>
+        <v>3.79581713676453</v>
       </c>
       <c r="H1189" t="n">
         <v>155683</v>
@@ -34879,7 +34879,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.86254072189331</v>
+        <v>3.86254096031189</v>
       </c>
       <c r="H1190" t="n">
         <v>93171</v>
@@ -35024,7 +35024,7 @@
         <v>6</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.44822359085083</v>
+        <v>4.44822311401367</v>
       </c>
       <c r="H1195" t="n">
         <v>130702</v>
@@ -35053,7 +35053,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.4704647064209</v>
+        <v>4.47046518325806</v>
       </c>
       <c r="H1196" t="n">
         <v>212780</v>
@@ -35082,7 +35082,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.50753259658813</v>
+        <v>4.50753307342529</v>
       </c>
       <c r="H1197" t="n">
         <v>141521</v>
@@ -35140,7 +35140,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.50011873245239</v>
+        <v>4.50011920928955</v>
       </c>
       <c r="H1199" t="n">
         <v>371285</v>
@@ -35169,7 +35169,7 @@
         <v>6</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.44822359085083</v>
+        <v>4.44822311401367</v>
       </c>
       <c r="H1200" t="n">
         <v>179244</v>
@@ -35198,7 +35198,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.81149482727051</v>
+        <v>4.81149435043335</v>
       </c>
       <c r="H1201" t="n">
         <v>691478</v>
@@ -35314,7 +35314,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.3823504447937</v>
+        <v>5.38234996795654</v>
       </c>
       <c r="H1205" t="n">
         <v>508998</v>
@@ -35430,7 +35430,7 @@
         <v>7.5</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.56027936935425</v>
+        <v>5.56027889251709</v>
       </c>
       <c r="H1209" t="n">
         <v>262844</v>
@@ -35459,7 +35459,7 @@
         <v>7.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.56027936935425</v>
+        <v>5.56027889251709</v>
       </c>
       <c r="H1210" t="n">
         <v>186425</v>
@@ -35488,7 +35488,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.58252048492432</v>
+        <v>5.58252000808716</v>
       </c>
       <c r="H1211" t="n">
         <v>199033</v>
@@ -35517,7 +35517,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.73820781707764</v>
+        <v>5.73820829391479</v>
       </c>
       <c r="H1212" t="n">
         <v>297846</v>
@@ -35546,7 +35546,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.65665769577026</v>
+        <v>5.65665721893311</v>
       </c>
       <c r="H1213" t="n">
         <v>242818</v>
@@ -35575,7 +35575,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.62700223922729</v>
+        <v>5.62700271606445</v>
       </c>
       <c r="H1214" t="n">
         <v>339811</v>
@@ -35633,7 +35633,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.76044940948486</v>
+        <v>5.76044988632202</v>
       </c>
       <c r="H1216" t="n">
         <v>234743</v>
@@ -35662,7 +35662,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1217" t="n">
-        <v>5.70855283737183</v>
+        <v>5.70855331420898</v>
       </c>
       <c r="H1217" t="n">
         <v>336560</v>
@@ -35749,7 +35749,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.56769323348999</v>
+        <v>5.56769275665283</v>
       </c>
       <c r="H1220" t="n">
         <v>111918</v>
@@ -35778,7 +35778,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.52321004867554</v>
+        <v>5.5232105255127</v>
       </c>
       <c r="H1221" t="n">
         <v>113245</v>
@@ -35865,7 +35865,7 @@
         <v>7.25</v>
       </c>
       <c r="G1224" t="n">
-        <v>5.37493705749512</v>
+        <v>5.37493658065796</v>
       </c>
       <c r="H1224" t="n">
         <v>174643</v>
@@ -35923,7 +35923,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1226" t="n">
-        <v>5.0932149887085</v>
+        <v>5.09321546554565</v>
       </c>
       <c r="H1226" t="n">
         <v>195209</v>
@@ -35952,7 +35952,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.17476654052734</v>
+        <v>5.17476606369019</v>
       </c>
       <c r="H1227" t="n">
         <v>335188</v>
@@ -36039,7 +36039,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.50838279724121</v>
+        <v>5.50838327407837</v>
       </c>
       <c r="H1230" t="n">
         <v>619855</v>
@@ -36126,7 +36126,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.76044940948486</v>
+        <v>5.76044988632202</v>
       </c>
       <c r="H1233" t="n">
         <v>508299</v>
@@ -36155,7 +36155,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.6937255859375</v>
+        <v>5.69372510910034</v>
       </c>
       <c r="H1234" t="n">
         <v>364428</v>
@@ -36184,7 +36184,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.66407108306885</v>
+        <v>5.66407155990601</v>
       </c>
       <c r="H1235" t="n">
         <v>427727</v>
@@ -36213,7 +36213,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1236" t="n">
-        <v>5.65665769577026</v>
+        <v>5.65665721893311</v>
       </c>
       <c r="H1236" t="n">
         <v>288095</v>
@@ -36271,7 +36271,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.79010391235352</v>
+        <v>5.79010343551636</v>
       </c>
       <c r="H1238" t="n">
         <v>185181</v>
@@ -36329,7 +36329,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1240" t="n">
-        <v>6.5018196105957</v>
+        <v>6.50182008743286</v>
       </c>
       <c r="H1240" t="n">
         <v>856188</v>
@@ -36416,7 +36416,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1243" t="n">
-        <v>6.33871793746948</v>
+        <v>6.33871841430664</v>
       </c>
       <c r="H1243" t="n">
         <v>535392</v>
@@ -36532,7 +36532,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1247" t="n">
-        <v>6.04216909408569</v>
+        <v>6.04216957092285</v>
       </c>
       <c r="H1247" t="n">
         <v>194860</v>
@@ -36561,7 +36561,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1248" t="n">
-        <v>6.24975395202637</v>
+        <v>6.24975347518921</v>
       </c>
       <c r="H1248" t="n">
         <v>354024</v>
@@ -36590,7 +36590,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1249" t="n">
-        <v>6.19785785675049</v>
+        <v>6.19785737991333</v>
       </c>
       <c r="H1249" t="n">
         <v>114330</v>
@@ -36619,7 +36619,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>6.18303060531616</v>
+        <v>6.18303108215332</v>
       </c>
       <c r="H1250" t="n">
         <v>175266</v>
@@ -36648,7 +36648,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1251" t="n">
-        <v>6.62043905258179</v>
+        <v>6.62043857574463</v>
       </c>
       <c r="H1251" t="n">
         <v>688617</v>
@@ -36677,7 +36677,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1252" t="n">
-        <v>6.50923347473145</v>
+        <v>6.5092339515686</v>
       </c>
       <c r="H1252" t="n">
         <v>525737</v>
@@ -36706,7 +36706,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1253" t="n">
-        <v>6.58337068557739</v>
+        <v>6.58337020874023</v>
       </c>
       <c r="H1253" t="n">
         <v>375451</v>
@@ -36735,7 +36735,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1254" t="n">
-        <v>6.57595682144165</v>
+        <v>6.57595634460449</v>
       </c>
       <c r="H1254" t="n">
         <v>163814</v>
@@ -36793,7 +36793,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.11715650558472</v>
+        <v>7.11715745925903</v>
       </c>
       <c r="H1256" t="n">
         <v>593443</v>
@@ -36851,7 +36851,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1258" t="n">
-        <v>7.06526136398315</v>
+        <v>7.065260887146</v>
       </c>
       <c r="H1258" t="n">
         <v>640753</v>
@@ -36880,7 +36880,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.05043363571167</v>
+        <v>7.05043411254883</v>
       </c>
       <c r="H1259" t="n">
         <v>255311</v>
@@ -36938,7 +36938,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1261" t="n">
-        <v>7.54715251922607</v>
+        <v>7.54715299606323</v>
       </c>
       <c r="H1261" t="n">
         <v>292983</v>
@@ -36967,7 +36967,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1262" t="n">
-        <v>7.60646104812622</v>
+        <v>7.60646200180054</v>
       </c>
       <c r="H1262" t="n">
         <v>273509</v>
@@ -37112,7 +37112,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.82887315750122</v>
+        <v>7.82887411117554</v>
       </c>
       <c r="H1267" t="n">
         <v>125181</v>
@@ -37141,7 +37141,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.87335538864136</v>
+        <v>7.87335586547852</v>
       </c>
       <c r="H1268" t="n">
         <v>337710</v>
@@ -37170,7 +37170,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1269" t="n">
-        <v>7.88818311691284</v>
+        <v>7.88818264007568</v>
       </c>
       <c r="H1269" t="n">
         <v>363211</v>
@@ -37199,7 +37199,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.99197483062744</v>
+        <v>7.99197387695312</v>
       </c>
       <c r="H1270" t="n">
         <v>264650</v>
@@ -37286,7 +37286,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1273" t="n">
-        <v>7.44336032867432</v>
+        <v>7.44336080551147</v>
       </c>
       <c r="H1273" t="n">
         <v>832254</v>
@@ -37315,7 +37315,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.68059873580933</v>
+        <v>7.68059825897217</v>
       </c>
       <c r="H1274" t="n">
         <v>508688</v>
@@ -37344,7 +37344,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>7.54715251922607</v>
+        <v>7.54715299606323</v>
       </c>
       <c r="H1275" t="n">
         <v>266888</v>
@@ -37373,7 +37373,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.59163475036621</v>
+        <v>7.59163427352905</v>
       </c>
       <c r="H1276" t="n">
         <v>279624</v>
@@ -37431,7 +37431,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1278" t="n">
-        <v>7.38405084609985</v>
+        <v>7.3840503692627</v>
       </c>
       <c r="H1278" t="n">
         <v>359960</v>
@@ -37489,7 +37489,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G1280" t="n">
-        <v>7.33215570449829</v>
+        <v>7.33215475082397</v>
       </c>
       <c r="H1280" t="n">
         <v>468812</v>
@@ -37518,7 +37518,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.35439586639404</v>
+        <v>7.3543963432312</v>
       </c>
       <c r="H1281" t="n">
         <v>158098</v>
@@ -37576,7 +37576,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>7.35439586639404</v>
+        <v>7.3543963432312</v>
       </c>
       <c r="H1283" t="n">
         <v>177031</v>
@@ -37634,7 +37634,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.32474088668823</v>
+        <v>7.32474040985107</v>
       </c>
       <c r="H1285" t="n">
         <v>250867</v>
@@ -37692,7 +37692,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1287" t="n">
-        <v>7.32474088668823</v>
+        <v>7.32474040985107</v>
       </c>
       <c r="H1287" t="n">
         <v>347288</v>
@@ -37721,7 +37721,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1288" t="n">
-        <v>7.08008861541748</v>
+        <v>7.08008813858032</v>
       </c>
       <c r="H1288" t="n">
         <v>551582</v>
@@ -37779,7 +37779,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1290" t="n">
-        <v>7.02077865600586</v>
+        <v>7.02077960968018</v>
       </c>
       <c r="H1290" t="n">
         <v>173390</v>
@@ -37808,7 +37808,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1291" t="n">
-        <v>7.13939809799194</v>
+        <v>7.1393985748291</v>
       </c>
       <c r="H1291" t="n">
         <v>109710</v>
@@ -37837,7 +37837,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.28025770187378</v>
+        <v>7.2802586555481</v>
       </c>
       <c r="H1292" t="n">
         <v>172742</v>
@@ -37953,7 +37953,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.87335538864136</v>
+        <v>7.87335586547852</v>
       </c>
       <c r="H1296" t="n">
         <v>326366</v>
@@ -38011,7 +38011,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1298" t="n">
-        <v>7.97714614868164</v>
+        <v>7.97714710235596</v>
       </c>
       <c r="H1298" t="n">
         <v>722047</v>
@@ -38040,7 +38040,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1299" t="n">
-        <v>8.45162391662598</v>
+        <v>8.45162296295166</v>
       </c>
       <c r="H1299" t="n">
         <v>538848</v>
@@ -38098,7 +38098,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1301" t="n">
-        <v>8.49610614776611</v>
+        <v>8.49610710144043</v>
       </c>
       <c r="H1301" t="n">
         <v>302498</v>
@@ -38127,7 +38127,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1302" t="n">
-        <v>8.49610614776611</v>
+        <v>8.49610710144043</v>
       </c>
       <c r="H1302" t="n">
         <v>202294</v>
@@ -38156,7 +38156,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1303" t="n">
-        <v>8.34783267974854</v>
+        <v>8.34783172607422</v>
       </c>
       <c r="H1303" t="n">
         <v>239055</v>
@@ -38214,7 +38214,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1305" t="n">
-        <v>8.45162391662598</v>
+        <v>8.45162296295166</v>
       </c>
       <c r="H1305" t="n">
         <v>122972</v>
@@ -38243,7 +38243,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1306" t="n">
-        <v>8.3181791305542</v>
+        <v>8.31817722320557</v>
       </c>
       <c r="H1306" t="n">
         <v>89949</v>
@@ -38272,7 +38272,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1307" t="n">
-        <v>8.5109338760376</v>
+        <v>8.51093292236328</v>
       </c>
       <c r="H1307" t="n">
         <v>424361</v>
@@ -38330,7 +38330,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1309" t="n">
-        <v>7.99197483062744</v>
+        <v>7.99197387695312</v>
       </c>
       <c r="H1309" t="n">
         <v>283023</v>
@@ -38359,7 +38359,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.84370040893555</v>
+        <v>7.84369993209839</v>
       </c>
       <c r="H1310" t="n">
         <v>221178</v>
@@ -38388,7 +38388,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1311" t="n">
-        <v>7.73990964889526</v>
+        <v>7.73990869522095</v>
       </c>
       <c r="H1311" t="n">
         <v>269913</v>
@@ -38475,7 +38475,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.44336032867432</v>
+        <v>7.44336080551147</v>
       </c>
       <c r="H1314" t="n">
         <v>524870</v>
@@ -38562,7 +38562,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1317" t="n">
-        <v>7.44336032867432</v>
+        <v>7.44336080551147</v>
       </c>
       <c r="H1317" t="n">
         <v>378883</v>
@@ -38620,7 +38620,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>7.69542646408081</v>
+        <v>7.69542503356934</v>
       </c>
       <c r="H1319" t="n">
         <v>388891</v>
@@ -38649,7 +38649,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1320" t="n">
-        <v>7.59163475036621</v>
+        <v>7.59163427352905</v>
       </c>
       <c r="H1320" t="n">
         <v>242496</v>
@@ -38678,7 +38678,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1321" t="n">
-        <v>7.51749753952026</v>
+        <v>7.51749706268311</v>
       </c>
       <c r="H1321" t="n">
         <v>215080</v>
@@ -38736,7 +38736,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1323" t="n">
-        <v>7.50267028808594</v>
+        <v>7.50266981124878</v>
       </c>
       <c r="H1323" t="n">
         <v>392802</v>
@@ -38765,7 +38765,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1324" t="n">
-        <v>7.62128973007202</v>
+        <v>7.62128925323486</v>
       </c>
       <c r="H1324" t="n">
         <v>262438</v>
@@ -38794,7 +38794,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1325" t="n">
-        <v>7.62128973007202</v>
+        <v>7.62128925323486</v>
       </c>
       <c r="H1325" t="n">
         <v>298270</v>
@@ -38852,7 +38852,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1327" t="n">
-        <v>7.91783809661865</v>
+        <v>7.91783857345581</v>
       </c>
       <c r="H1327" t="n">
         <v>540331</v>
@@ -38910,7 +38910,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1329" t="n">
-        <v>7.84370040893555</v>
+        <v>7.84369993209839</v>
       </c>
       <c r="H1329" t="n">
         <v>200870</v>
@@ -38968,7 +38968,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1331" t="n">
-        <v>8.24404048919678</v>
+        <v>8.24403953552246</v>
       </c>
       <c r="H1331" t="n">
         <v>405165</v>
@@ -38997,7 +38997,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1332" t="n">
-        <v>7.99197483062744</v>
+        <v>7.99197387695312</v>
       </c>
       <c r="H1332" t="n">
         <v>400894</v>
@@ -39026,7 +39026,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1333" t="n">
-        <v>7.97714614868164</v>
+        <v>7.97714710235596</v>
       </c>
       <c r="H1333" t="n">
         <v>197842</v>
@@ -39084,7 +39084,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G1335" t="n">
-        <v>8.16248989105225</v>
+        <v>8.16248893737793</v>
       </c>
       <c r="H1335" t="n">
         <v>181471</v>
@@ -39171,7 +39171,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1338" t="n">
-        <v>9.59333324432373</v>
+        <v>9.59333515167236</v>
       </c>
       <c r="H1338" t="n">
         <v>1383755</v>
@@ -39258,7 +39258,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1341" t="n">
-        <v>10.001088142395</v>
+        <v>10.0010890960693</v>
       </c>
       <c r="H1341" t="n">
         <v>394107</v>
@@ -39287,7 +39287,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.68229961395264</v>
+        <v>9.68230056762695</v>
       </c>
       <c r="H1342" t="n">
         <v>618401</v>
@@ -39374,7 +39374,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.95660781860352</v>
+        <v>9.9566068649292</v>
       </c>
       <c r="H1345" t="n">
         <v>608465</v>
@@ -39403,7 +39403,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1346" t="n">
-        <v>10.0752258300781</v>
+        <v>10.0752248764038</v>
       </c>
       <c r="H1346" t="n">
         <v>298506</v>
@@ -39432,7 +39432,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1347" t="n">
-        <v>10.0974674224854</v>
+        <v>10.097466468811</v>
       </c>
       <c r="H1347" t="n">
         <v>478691</v>
@@ -39519,7 +39519,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1350" t="n">
-        <v>10.1122941970825</v>
+        <v>10.1122932434082</v>
       </c>
       <c r="H1350" t="n">
         <v>618145</v>
@@ -39548,7 +39548,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1351" t="n">
-        <v>10.0603971481323</v>
+        <v>10.0603981018066</v>
       </c>
       <c r="H1351" t="n">
         <v>623280</v>
@@ -39577,7 +39577,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1352" t="n">
-        <v>10.0603971481323</v>
+        <v>10.0603981018066</v>
       </c>
       <c r="H1352" t="n">
         <v>460591</v>
@@ -39664,7 +39664,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.95660781860352</v>
+        <v>9.9566068649292</v>
       </c>
       <c r="H1355" t="n">
         <v>386695</v>
@@ -39722,7 +39722,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1357" t="n">
-        <v>9.97884654998779</v>
+        <v>9.97884845733643</v>
       </c>
       <c r="H1357" t="n">
         <v>246480</v>
@@ -39751,7 +39751,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1358" t="n">
-        <v>10.0826406478882</v>
+        <v>10.0826396942139</v>
       </c>
       <c r="H1358" t="n">
         <v>240274</v>
@@ -39809,7 +39809,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1360" t="n">
-        <v>10.044038772583</v>
+        <v>10.0440378189087</v>
       </c>
       <c r="H1360" t="n">
         <v>568930</v>
@@ -39867,7 +39867,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1362" t="n">
-        <v>10.0208768844604</v>
+        <v>10.0208759307861</v>
       </c>
       <c r="H1362" t="n">
         <v>891294</v>
@@ -39983,7 +39983,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.5226936340332</v>
+        <v>10.5226926803589</v>
       </c>
       <c r="H1366" t="n">
         <v>856596</v>
@@ -40128,7 +40128,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1371" t="n">
-        <v>10.3914489746094</v>
+        <v>10.3914499282837</v>
       </c>
       <c r="H1371" t="n">
         <v>333184</v>
@@ -40186,7 +40186,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G1373" t="n">
-        <v>10.8160629272461</v>
+        <v>10.8160619735718</v>
       </c>
       <c r="H1373" t="n">
         <v>496342</v>
@@ -40244,7 +40244,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1375" t="n">
-        <v>11.2252349853516</v>
+        <v>11.2252359390259</v>
       </c>
       <c r="H1375" t="n">
         <v>441675</v>
@@ -40331,7 +40331,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.472282409668</v>
+        <v>11.4722833633423</v>
       </c>
       <c r="H1378" t="n">
         <v>404357</v>
@@ -40360,7 +40360,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G1379" t="n">
-        <v>11.4028024673462</v>
+        <v>11.4028015136719</v>
       </c>
       <c r="H1379" t="n">
         <v>448881</v>
@@ -40534,7 +40534,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1385" t="n">
-        <v>11.7810935974121</v>
+        <v>11.7810926437378</v>
       </c>
       <c r="H1385" t="n">
         <v>702886</v>
@@ -40650,7 +40650,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1389" t="n">
-        <v>11.9895391464233</v>
+        <v>11.9895401000977</v>
       </c>
       <c r="H1389" t="n">
         <v>280927</v>
@@ -40679,7 +40679,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1390" t="n">
-        <v>11.8582954406738</v>
+        <v>11.8582944869995</v>
       </c>
       <c r="H1390" t="n">
         <v>217840</v>
@@ -40766,7 +40766,7 @@
         <v>15</v>
       </c>
       <c r="G1393" t="n">
-        <v>11.5803670883179</v>
+        <v>11.5803661346436</v>
       </c>
       <c r="H1393" t="n">
         <v>123407</v>
@@ -41027,7 +41027,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G1402" t="n">
-        <v>11.4028024673462</v>
+        <v>11.4028015136719</v>
       </c>
       <c r="H1402" t="n">
         <v>251157</v>
@@ -41114,7 +41114,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>12.2365884780884</v>
+        <v>12.2365875244141</v>
       </c>
       <c r="H1405" t="n">
         <v>815649</v>
@@ -41230,7 +41230,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.1017122268677</v>
+        <v>11.1017112731934</v>
       </c>
       <c r="H1409" t="n">
         <v>337873</v>
@@ -41259,7 +41259,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.0476694107056</v>
+        <v>11.0476703643799</v>
       </c>
       <c r="H1410" t="n">
         <v>171270</v>
@@ -41288,7 +41288,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1411" t="n">
-        <v>11.3950824737549</v>
+        <v>11.3950815200806</v>
       </c>
       <c r="H1411" t="n">
         <v>189384</v>
@@ -41317,7 +41317,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G1412" t="n">
-        <v>11.5958080291748</v>
+        <v>11.5958070755005</v>
       </c>
       <c r="H1412" t="n">
         <v>305262</v>
@@ -41375,7 +41375,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1414" t="n">
-        <v>11.7810935974121</v>
+        <v>11.7810926437378</v>
       </c>
       <c r="H1414" t="n">
         <v>153562</v>
@@ -41491,7 +41491,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1418" t="n">
-        <v>11.9895391464233</v>
+        <v>11.9895401000977</v>
       </c>
       <c r="H1418" t="n">
         <v>184001</v>
@@ -41520,7 +41520,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G1419" t="n">
-        <v>12.0667419433594</v>
+        <v>12.0667409896851</v>
       </c>
       <c r="H1419" t="n">
         <v>201420</v>
@@ -41607,7 +41607,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.2365884780884</v>
+        <v>12.2365875244141</v>
       </c>
       <c r="H1422" t="n">
         <v>185558</v>
@@ -41694,7 +41694,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1425" t="n">
-        <v>12.4064321517944</v>
+        <v>12.4064331054688</v>
       </c>
       <c r="H1425" t="n">
         <v>220398</v>
@@ -41897,7 +41897,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1432" t="n">
-        <v>12.2829084396362</v>
+        <v>12.2829093933105</v>
       </c>
       <c r="H1432" t="n">
         <v>407092</v>
@@ -42100,7 +42100,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1439" t="n">
-        <v>12.5376768112183</v>
+        <v>12.5376758575439</v>
       </c>
       <c r="H1439" t="n">
         <v>197205</v>
@@ -42274,7 +42274,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1445" t="n">
-        <v>11.5108842849731</v>
+        <v>11.5108852386475</v>
       </c>
       <c r="H1445" t="n">
         <v>2072355</v>
@@ -42332,7 +42332,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1447" t="n">
-        <v>10.5149736404419</v>
+        <v>10.5149726867676</v>
       </c>
       <c r="H1447" t="n">
         <v>1307534</v>
@@ -42361,7 +42361,7 @@
         <v>13</v>
       </c>
       <c r="G1448" t="n">
-        <v>10.0363187789917</v>
+        <v>10.0363178253174</v>
       </c>
       <c r="H1448" t="n">
         <v>1134592</v>
@@ -42390,7 +42390,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>9.6889066696167</v>
+        <v>9.68890762329102</v>
       </c>
       <c r="H1449" t="n">
         <v>800971</v>
@@ -42651,7 +42651,7 @@
         <v>12</v>
       </c>
       <c r="G1458" t="n">
-        <v>9.2642936706543</v>
+        <v>9.26429271697998</v>
       </c>
       <c r="H1458" t="n">
         <v>357284</v>
@@ -42767,7 +42767,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.73159599304199</v>
+        <v>8.73159694671631</v>
       </c>
       <c r="H1462" t="n">
         <v>423384</v>
@@ -42854,7 +42854,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.52314949035645</v>
+        <v>8.52315044403076</v>
       </c>
       <c r="H1465" t="n">
         <v>397323</v>
@@ -42883,7 +42883,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1466" t="n">
-        <v>8.31470489501953</v>
+        <v>8.31470394134521</v>
       </c>
       <c r="H1466" t="n">
         <v>500316</v>
@@ -42999,7 +42999,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.72387599945068</v>
+        <v>8.723876953125</v>
       </c>
       <c r="H1470" t="n">
         <v>331845</v>
@@ -43057,7 +43057,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1472" t="n">
-        <v>8.84739971160889</v>
+        <v>8.8474006652832</v>
       </c>
       <c r="H1472" t="n">
         <v>457138</v>
@@ -43173,7 +43173,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G1476" t="n">
-        <v>9.05584716796875</v>
+        <v>9.05584621429443</v>
       </c>
       <c r="H1476" t="n">
         <v>304953</v>
@@ -43260,7 +43260,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1479" t="n">
-        <v>9.07900810241699</v>
+        <v>9.07900714874268</v>
       </c>
       <c r="H1479" t="n">
         <v>292280</v>
@@ -43347,7 +43347,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.72387599945068</v>
+        <v>8.723876953125</v>
       </c>
       <c r="H1482" t="n">
         <v>214386</v>
@@ -43376,7 +43376,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1483" t="n">
-        <v>8.6621150970459</v>
+        <v>8.66211414337158</v>
       </c>
       <c r="H1483" t="n">
         <v>195852</v>
@@ -43492,7 +43492,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1487" t="n">
-        <v>9.60398387908936</v>
+        <v>9.60398483276367</v>
       </c>
       <c r="H1487" t="n">
         <v>810378</v>
@@ -43608,7 +43608,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1491" t="n">
-        <v>9.56538391113281</v>
+        <v>9.5653829574585</v>
       </c>
       <c r="H1491" t="n">
         <v>285731</v>
@@ -43637,7 +43637,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1492" t="n">
-        <v>9.5731029510498</v>
+        <v>9.57310199737549</v>
       </c>
       <c r="H1492" t="n">
         <v>226612</v>
@@ -43840,7 +43840,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.5113410949707</v>
+        <v>9.51134204864502</v>
       </c>
       <c r="H1499" t="n">
         <v>222491</v>
@@ -43869,7 +43869,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1500" t="n">
-        <v>9.00952529907227</v>
+        <v>9.00952625274658</v>
       </c>
       <c r="H1500" t="n">
         <v>531730</v>
@@ -44014,7 +44014,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>9.25657367706299</v>
+        <v>9.25657272338867</v>
       </c>
       <c r="H1505" t="n">
         <v>261035</v>
@@ -44130,7 +44130,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>9.5113410949707</v>
+        <v>9.51134204864502</v>
       </c>
       <c r="H1509" t="n">
         <v>192211</v>
@@ -44188,7 +44188,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G1511" t="n">
-        <v>10.3374080657959</v>
+        <v>10.3374071121216</v>
       </c>
       <c r="H1511" t="n">
         <v>531221</v>
@@ -44217,7 +44217,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1512" t="n">
-        <v>10.0671987533569</v>
+        <v>10.0671997070312</v>
       </c>
       <c r="H1512" t="n">
         <v>378676</v>
@@ -44333,7 +44333,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1516" t="n">
-        <v>9.07900810241699</v>
+        <v>9.07900714874268</v>
       </c>
       <c r="H1516" t="n">
         <v>226969</v>
@@ -44449,7 +44449,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1520" t="n">
-        <v>9.30289459228516</v>
+        <v>9.30289554595947</v>
       </c>
       <c r="H1520" t="n">
         <v>117990</v>
@@ -44478,7 +44478,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1521" t="n">
-        <v>9.5731029510498</v>
+        <v>9.57310199737549</v>
       </c>
       <c r="H1521" t="n">
         <v>157823</v>
@@ -44594,7 +44594,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1525" t="n">
-        <v>9.91279411315918</v>
+        <v>9.9127950668335</v>
       </c>
       <c r="H1525" t="n">
         <v>121880</v>
@@ -44623,7 +44623,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>9.95911598205566</v>
+        <v>9.95911502838135</v>
       </c>
       <c r="H1526" t="n">
         <v>107589</v>
@@ -44681,7 +44681,7 @@
         <v>13</v>
       </c>
       <c r="G1528" t="n">
-        <v>10.0363187789917</v>
+        <v>10.0363178253174</v>
       </c>
       <c r="H1528" t="n">
         <v>214843</v>
@@ -44797,7 +44797,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.99408531188965</v>
+        <v>8.99408435821533</v>
       </c>
       <c r="H1532" t="n">
         <v>392300</v>
@@ -44855,7 +44855,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1534" t="n">
-        <v>9.44957828521729</v>
+        <v>9.4495792388916</v>
       </c>
       <c r="H1534" t="n">
         <v>194792</v>
@@ -44942,7 +44942,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1537" t="n">
-        <v>9.61170387268066</v>
+        <v>9.61170482635498</v>
       </c>
       <c r="H1537" t="n">
         <v>191883</v>
@@ -45203,7 +45203,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1546" t="n">
-        <v>9.21025085449219</v>
+        <v>9.2102518081665</v>
       </c>
       <c r="H1546" t="n">
         <v>197903</v>
@@ -45551,7 +45551,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1558" t="n">
-        <v>9.30289459228516</v>
+        <v>9.30289554595947</v>
       </c>
       <c r="H1558" t="n">
         <v>93185</v>
@@ -45609,7 +45609,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1560" t="n">
-        <v>9.00952529907227</v>
+        <v>9.00952625274658</v>
       </c>
       <c r="H1560" t="n">
         <v>123789</v>
@@ -45667,7 +45667,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1562" t="n">
-        <v>8.6003532409668</v>
+        <v>8.60035228729248</v>
       </c>
       <c r="H1562" t="n">
         <v>249020</v>
@@ -45783,7 +45783,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1566" t="n">
-        <v>8.6621150970459</v>
+        <v>8.66211414337158</v>
       </c>
       <c r="H1566" t="n">
         <v>180359</v>
@@ -45899,7 +45899,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1570" t="n">
-        <v>7.85148811340332</v>
+        <v>7.85148906707764</v>
       </c>
       <c r="H1570" t="n">
         <v>180435</v>
@@ -45928,7 +45928,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.25702953338623</v>
+        <v>7.25703001022339</v>
       </c>
       <c r="H1571" t="n">
         <v>300725</v>
@@ -45986,7 +45986,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1573" t="n">
-        <v>6.57764863967896</v>
+        <v>6.57764911651611</v>
       </c>
       <c r="H1573" t="n">
         <v>486838</v>
@@ -46015,7 +46015,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.08718490600586</v>
+        <v>7.0871844291687</v>
       </c>
       <c r="H1574" t="n">
         <v>668311</v>
@@ -46073,7 +46073,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>7.10648488998413</v>
+        <v>7.10648536682129</v>
       </c>
       <c r="H1576" t="n">
         <v>414498</v>
@@ -46102,7 +46102,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1577" t="n">
-        <v>7.2647500038147</v>
+        <v>7.26475048065186</v>
       </c>
       <c r="H1577" t="n">
         <v>298297</v>
@@ -46160,7 +46160,7 @@
         <v>9.5</v>
       </c>
       <c r="G1579" t="n">
-        <v>7.33423280715942</v>
+        <v>7.33423233032227</v>
       </c>
       <c r="H1579" t="n">
         <v>470457</v>
@@ -46189,7 +46189,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.43459510803223</v>
+        <v>7.43459558486938</v>
       </c>
       <c r="H1580" t="n">
         <v>320480</v>
@@ -46218,7 +46218,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.32265186309814</v>
+        <v>7.32265138626099</v>
       </c>
       <c r="H1581" t="n">
         <v>540737</v>
@@ -46276,7 +46276,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.48863744735718</v>
+        <v>7.48863697052002</v>
       </c>
       <c r="H1583" t="n">
         <v>187636</v>
@@ -46334,7 +46334,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1585" t="n">
-        <v>7.43459510803223</v>
+        <v>7.43459558486938</v>
       </c>
       <c r="H1585" t="n">
         <v>132184</v>
@@ -46421,7 +46421,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1588" t="n">
-        <v>7.7511248588562</v>
+        <v>7.75112581253052</v>
       </c>
       <c r="H1588" t="n">
         <v>180788</v>
@@ -46537,7 +46537,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G1592" t="n">
-        <v>7.56197881698608</v>
+        <v>7.5619797706604</v>
       </c>
       <c r="H1592" t="n">
         <v>86752</v>
@@ -46624,7 +46624,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1595" t="n">
-        <v>7.15280723571777</v>
+        <v>7.15280675888062</v>
       </c>
       <c r="H1595" t="n">
         <v>127676</v>
@@ -46653,7 +46653,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.36511325836182</v>
+        <v>7.36511278152466</v>
       </c>
       <c r="H1596" t="n">
         <v>104930</v>
@@ -46711,7 +46711,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.30721139907837</v>
+        <v>7.30721092224121</v>
       </c>
       <c r="H1598" t="n">
         <v>68013</v>
@@ -46769,7 +46769,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1600" t="n">
-        <v>7.2647500038147</v>
+        <v>7.26475048065186</v>
       </c>
       <c r="H1600" t="n">
         <v>138249</v>
@@ -46798,7 +46798,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1601" t="n">
-        <v>7.38827419281006</v>
+        <v>7.3882737159729</v>
       </c>
       <c r="H1601" t="n">
         <v>124837</v>
@@ -46856,7 +46856,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1603" t="n">
-        <v>7.58127927780151</v>
+        <v>7.58128023147583</v>
       </c>
       <c r="H1603" t="n">
         <v>124067</v>
@@ -47117,7 +47117,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>6.97653150558472</v>
+        <v>6.97653198242188</v>
       </c>
       <c r="H1612" t="n">
         <v>102044</v>
@@ -47291,7 +47291,7 @@
         <v>8.03499984741211</v>
       </c>
       <c r="G1618" t="n">
-        <v>6.56398487091064</v>
+        <v>6.5639853477478</v>
       </c>
       <c r="H1618" t="n">
         <v>231804</v>
@@ -47378,7 +47378,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1621" t="n">
-        <v>6.82131671905518</v>
+        <v>6.82131719589233</v>
       </c>
       <c r="H1621" t="n">
         <v>171424</v>
@@ -47784,7 +47784,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1635" t="n">
-        <v>6.63342380523682</v>
+        <v>6.63342332839966</v>
       </c>
       <c r="H1635" t="n">
         <v>78913</v>
@@ -47813,7 +47813,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1636" t="n">
-        <v>6.60891580581665</v>
+        <v>6.60891628265381</v>
       </c>
       <c r="H1636" t="n">
         <v>123099</v>
@@ -47842,7 +47842,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1637" t="n">
-        <v>6.52722406387329</v>
+        <v>6.52722358703613</v>
       </c>
       <c r="H1637" t="n">
         <v>107001</v>
@@ -47871,7 +47871,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1638" t="n">
-        <v>6.3229923248291</v>
+        <v>6.32299280166626</v>
       </c>
       <c r="H1638" t="n">
         <v>157553</v>
@@ -47900,7 +47900,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1639" t="n">
-        <v>6.00439214706421</v>
+        <v>6.00439262390137</v>
       </c>
       <c r="H1639" t="n">
         <v>279915</v>
@@ -48132,7 +48132,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1647" t="n">
-        <v>5.99622297286987</v>
+        <v>5.99622344970703</v>
       </c>
       <c r="H1647" t="n">
         <v>78300</v>
@@ -48161,7 +48161,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G1648" t="n">
-        <v>5.9676308631897</v>
+        <v>5.96763038635254</v>
       </c>
       <c r="H1648" t="n">
         <v>39412</v>
@@ -48190,7 +48190,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1649" t="n">
-        <v>6.06157732009888</v>
+        <v>6.06157684326172</v>
       </c>
       <c r="H1649" t="n">
         <v>104979</v>
@@ -48248,7 +48248,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1651" t="n">
-        <v>5.9798846244812</v>
+        <v>5.97988414764404</v>
       </c>
       <c r="H1651" t="n">
         <v>60691</v>
@@ -48306,7 +48306,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G1653" t="n">
-        <v>5.5836763381958</v>
+        <v>5.58367681503296</v>
       </c>
       <c r="H1653" t="n">
         <v>282559</v>
@@ -48364,7 +48364,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1655" t="n">
-        <v>5.55508470535278</v>
+        <v>5.55508422851562</v>
       </c>
       <c r="H1655" t="n">
         <v>102311</v>
@@ -48422,7 +48422,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G1657" t="n">
-        <v>5.49381446838379</v>
+        <v>5.49381494522095</v>
       </c>
       <c r="H1657" t="n">
         <v>106623</v>
@@ -48451,7 +48451,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1658" t="n">
-        <v>5.68579149246216</v>
+        <v>5.68579196929932</v>
       </c>
       <c r="H1658" t="n">
         <v>93517</v>
@@ -48538,7 +48538,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1661" t="n">
-        <v>5.72663831710815</v>
+        <v>5.726637840271</v>
       </c>
       <c r="H1661" t="n">
         <v>76329</v>
@@ -48596,7 +48596,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.36310720443726</v>
+        <v>5.3631067276001</v>
       </c>
       <c r="H1663" t="n">
         <v>81236</v>
@@ -48625,7 +48625,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.40395307540894</v>
+        <v>5.40395259857178</v>
       </c>
       <c r="H1664" t="n">
         <v>59050</v>
@@ -48654,7 +48654,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1665" t="n">
-        <v>5.44479894638062</v>
+        <v>5.44479942321777</v>
       </c>
       <c r="H1665" t="n">
         <v>75688</v>
@@ -48741,7 +48741,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1668" t="n">
-        <v>5.72255373001099</v>
+        <v>5.72255325317383</v>
       </c>
       <c r="H1668" t="n">
         <v>64288</v>
@@ -48770,7 +48770,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1669" t="n">
-        <v>5.77565383911133</v>
+        <v>5.77565336227417</v>
       </c>
       <c r="H1669" t="n">
         <v>92082</v>
@@ -48886,7 +48886,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.57959175109863</v>
+        <v>5.57959222793579</v>
       </c>
       <c r="H1673" t="n">
         <v>200936</v>
@@ -48915,7 +48915,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1674" t="n">
-        <v>5.751145362854</v>
+        <v>5.75114583969116</v>
       </c>
       <c r="H1674" t="n">
         <v>161796</v>
@@ -49031,7 +49031,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.81649971008301</v>
+        <v>5.81649923324585</v>
       </c>
       <c r="H1678" t="n">
         <v>109309</v>
@@ -49060,7 +49060,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G1679" t="n">
-        <v>5.71438455581665</v>
+        <v>5.71438407897949</v>
       </c>
       <c r="H1679" t="n">
         <v>79243</v>
@@ -49147,7 +49147,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1682" t="n">
-        <v>5.72663831710815</v>
+        <v>5.726637840271</v>
       </c>
       <c r="H1682" t="n">
         <v>125768</v>
@@ -49234,7 +49234,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1685" t="n">
-        <v>5.99622297286987</v>
+        <v>5.99622344970703</v>
       </c>
       <c r="H1685" t="n">
         <v>182349</v>
@@ -49292,7 +49292,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1687" t="n">
-        <v>5.87368488311768</v>
+        <v>5.87368440628052</v>
       </c>
       <c r="H1687" t="n">
         <v>79212</v>
@@ -49321,7 +49321,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1688" t="n">
-        <v>5.80833101272583</v>
+        <v>5.80833053588867</v>
       </c>
       <c r="H1688" t="n">
         <v>97902</v>
@@ -49408,7 +49408,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1691" t="n">
-        <v>5.83283805847168</v>
+        <v>5.83283853530884</v>
       </c>
       <c r="H1691" t="n">
         <v>87279</v>
@@ -49466,7 +49466,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G1693" t="n">
-        <v>5.6490306854248</v>
+        <v>5.64903020858765</v>
       </c>
       <c r="H1693" t="n">
         <v>128938</v>
@@ -49495,7 +49495,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1694" t="n">
-        <v>5.56325340270996</v>
+        <v>5.5632529258728</v>
       </c>
       <c r="H1694" t="n">
         <v>107929</v>
@@ -49553,7 +49553,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.55508470535278</v>
+        <v>5.55508422851562</v>
       </c>
       <c r="H1696" t="n">
         <v>59601</v>
@@ -49640,7 +49640,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.92605257034302</v>
+        <v>4.92605304718018</v>
       </c>
       <c r="H1699" t="n">
         <v>182048</v>
@@ -49669,7 +49669,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.90971422195435</v>
+        <v>4.90971374511719</v>
       </c>
       <c r="H1700" t="n">
         <v>305560</v>
@@ -49698,7 +49698,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G1701" t="n">
-        <v>4.83210611343384</v>
+        <v>4.832106590271</v>
       </c>
       <c r="H1701" t="n">
         <v>122503</v>
@@ -49785,7 +49785,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G1704" t="n">
-        <v>5.36310720443726</v>
+        <v>5.3631067276001</v>
       </c>
       <c r="H1704" t="n">
         <v>147354</v>
@@ -50423,7 +50423,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1726" t="n">
-        <v>4.65646743774414</v>
+        <v>4.65646696090698</v>
       </c>
       <c r="H1726" t="n">
         <v>78099</v>
@@ -50655,7 +50655,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.45705318450928</v>
+        <v>5.45705270767212</v>
       </c>
       <c r="H1734" t="n">
         <v>97393</v>
@@ -50684,7 +50684,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1735" t="n">
-        <v>5.55508470535278</v>
+        <v>5.55508422851562</v>
       </c>
       <c r="H1735" t="n">
         <v>117678</v>
@@ -50945,7 +50945,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1744" t="n">
-        <v>5.80833101272583</v>
+        <v>5.80833053588867</v>
       </c>
       <c r="H1744" t="n">
         <v>154890</v>
@@ -51003,7 +51003,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G1746" t="n">
-        <v>5.79607677459717</v>
+        <v>5.79607629776001</v>
       </c>
       <c r="H1746" t="n">
         <v>99799</v>
@@ -51061,7 +51061,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1748" t="n">
-        <v>6.38017749786377</v>
+        <v>6.38017702102661</v>
       </c>
       <c r="H1748" t="n">
         <v>334175</v>
@@ -51177,7 +51177,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1752" t="n">
-        <v>5.81649971008301</v>
+        <v>5.81649923324585</v>
       </c>
       <c r="H1752" t="n">
         <v>194799</v>
@@ -51206,7 +51206,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G1753" t="n">
-        <v>5.91044569015503</v>
+        <v>5.91044616699219</v>
       </c>
       <c r="H1753" t="n">
         <v>105152</v>
@@ -51322,7 +51322,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1757" t="n">
-        <v>5.80833101272583</v>
+        <v>5.80833053588867</v>
       </c>
       <c r="H1757" t="n">
         <v>83589</v>
@@ -51351,7 +51351,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.84509181976318</v>
+        <v>5.84509229660034</v>
       </c>
       <c r="H1758" t="n">
         <v>74988</v>
@@ -51380,7 +51380,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1759" t="n">
-        <v>5.68579149246216</v>
+        <v>5.68579196929932</v>
       </c>
       <c r="H1759" t="n">
         <v>109787</v>
@@ -51496,7 +51496,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1763" t="n">
-        <v>5.77565383911133</v>
+        <v>5.77565336227417</v>
       </c>
       <c r="H1763" t="n">
         <v>115632</v>
@@ -51525,7 +51525,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1764" t="n">
-        <v>5.72663831710815</v>
+        <v>5.726637840271</v>
       </c>
       <c r="H1764" t="n">
         <v>92720</v>
@@ -51554,7 +51554,7 @@
         <v>6.875</v>
       </c>
       <c r="G1765" t="n">
-        <v>5.6163535118103</v>
+        <v>5.61635303497314</v>
       </c>
       <c r="H1765" t="n">
         <v>108718</v>
@@ -51728,7 +51728,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1771" t="n">
-        <v>5.56325340270996</v>
+        <v>5.5632529258728</v>
       </c>
       <c r="H1771" t="n">
         <v>139949</v>
@@ -51757,7 +51757,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1772" t="n">
-        <v>5.35085296630859</v>
+        <v>5.35085344314575</v>
       </c>
       <c r="H1772" t="n">
         <v>158653</v>
@@ -51844,7 +51844,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1775" t="n">
-        <v>5.35085296630859</v>
+        <v>5.35085344314575</v>
       </c>
       <c r="H1775" t="n">
         <v>67478</v>
@@ -52018,7 +52018,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1781" t="n">
-        <v>5.57959175109863</v>
+        <v>5.57959222793579</v>
       </c>
       <c r="H1781" t="n">
         <v>63483</v>
@@ -52279,7 +52279,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1790" t="n">
-        <v>5.99213838577271</v>
+        <v>5.99213886260986</v>
       </c>
       <c r="H1790" t="n">
         <v>144515</v>
@@ -52424,7 +52424,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1795" t="n">
-        <v>6.09016895294189</v>
+        <v>6.09016942977905</v>
       </c>
       <c r="H1795" t="n">
         <v>89385</v>
@@ -52540,7 +52540,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1799" t="n">
-        <v>6.06157732009888</v>
+        <v>6.06157684326172</v>
       </c>
       <c r="H1799" t="n">
         <v>41416</v>
@@ -52598,7 +52598,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G1801" t="n">
-        <v>5.9676308631897</v>
+        <v>5.96763038635254</v>
       </c>
       <c r="H1801" t="n">
         <v>53469</v>
@@ -52656,7 +52656,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G1803" t="n">
-        <v>5.94312286376953</v>
+        <v>5.94312334060669</v>
       </c>
       <c r="H1803" t="n">
         <v>71533</v>
@@ -52946,7 +52946,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G1813" t="n">
-        <v>6.0329852104187</v>
+        <v>6.03298473358154</v>
       </c>
       <c r="H1813" t="n">
         <v>86799</v>
@@ -52975,7 +52975,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G1814" t="n">
-        <v>6.0329852104187</v>
+        <v>6.03298473358154</v>
       </c>
       <c r="H1814" t="n">
         <v>67458</v>
@@ -53468,7 +53468,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1831" t="n">
-        <v>6.38017749786377</v>
+        <v>6.38017702102661</v>
       </c>
       <c r="H1831" t="n">
         <v>429221</v>
@@ -53584,7 +53584,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1835" t="n">
-        <v>6.23313140869141</v>
+        <v>6.23313093185425</v>
       </c>
       <c r="H1835" t="n">
         <v>416454</v>
@@ -53642,7 +53642,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G1837" t="n">
-        <v>6.79272365570068</v>
+        <v>6.79272317886353</v>
       </c>
       <c r="H1837" t="n">
         <v>638134</v>
@@ -53874,7 +53874,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.30330181121826</v>
+        <v>7.3033013343811</v>
       </c>
       <c r="H1845" t="n">
         <v>214240</v>
@@ -53903,7 +53903,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G1846" t="n">
-        <v>7.48710918426514</v>
+        <v>7.48710966110229</v>
       </c>
       <c r="H1846" t="n">
         <v>258969</v>
@@ -53932,7 +53932,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.53204107284546</v>
+        <v>7.53204154968262</v>
       </c>
       <c r="H1847" t="n">
         <v>344043</v>
@@ -53961,7 +53961,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1848" t="n">
-        <v>7.54837846755981</v>
+        <v>7.54837894439697</v>
       </c>
       <c r="H1848" t="n">
         <v>207237</v>
@@ -54077,7 +54077,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1852" t="n">
-        <v>7.22977876663208</v>
+        <v>7.22977924346924</v>
       </c>
       <c r="H1852" t="n">
         <v>244351</v>
@@ -54135,7 +54135,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1854" t="n">
-        <v>7.19710206985474</v>
+        <v>7.19710159301758</v>
       </c>
       <c r="H1854" t="n">
         <v>197744</v>
@@ -54251,7 +54251,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1858" t="n">
-        <v>7.10723924636841</v>
+        <v>7.10723972320557</v>
       </c>
       <c r="H1858" t="n">
         <v>191555</v>
@@ -80200,7 +80200,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="E2753" t="n">
-        <v>7.80499982833862</v>
+        <v>7.80000019073486</v>
       </c>
       <c r="F2753" t="n">
         <v>7.80000019073486</v>
@@ -80212,6 +80212,35 @@
         <v>72761</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>7.78999996185303</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>7.78999996185303</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>184424</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
